--- a/wwwroot/ExcelModel/CrazyLine_PHY_sheet.xlsx
+++ b/wwwroot/ExcelModel/CrazyLine_PHY_sheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\source\NX-lims Softlines Command System\wwwroot\ExcelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31261A54-9A79-4479-986B-CEAC03ABBD89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1AA1F6B-4ED6-4DD6-8575-34C8FDEF5F82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="360" yWindow="2614" windowWidth="24686" windowHeight="13132" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Weight" sheetId="3" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="175">
   <si>
     <t>Test Report Number 报告编号:</t>
   </si>
@@ -1347,6 +1347,14 @@
   <si>
     <t>Snap 2</t>
     <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>Load：</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>16N</t>
+    <phoneticPr fontId="24" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1818,7 +1826,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1942,6 +1950,15 @@
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1996,26 +2013,14 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="22" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2026,17 +2031,23 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="22" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2046,9 +2057,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2072,28 +2080,31 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2373,7 +2384,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AB21"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.15"/>
   <cols>
     <col min="1" max="28" width="3" customWidth="1"/>
   </cols>
@@ -2387,25 +2398,25 @@
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
       <c r="I1" s="5"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="51"/>
-      <c r="V1" s="51"/>
-      <c r="W1" s="51"/>
-      <c r="X1" s="51"/>
-      <c r="Y1" s="51"/>
-      <c r="Z1" s="51"/>
-      <c r="AA1" s="51"/>
-      <c r="AB1" s="51"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="54"/>
+      <c r="R1" s="54"/>
+      <c r="S1" s="54"/>
+      <c r="T1" s="54"/>
+      <c r="U1" s="54"/>
+      <c r="V1" s="54"/>
+      <c r="W1" s="54"/>
+      <c r="X1" s="54"/>
+      <c r="Y1" s="54"/>
+      <c r="Z1" s="54"/>
+      <c r="AA1" s="54"/>
+      <c r="AB1" s="54"/>
     </row>
     <row r="2" spans="1:28">
       <c r="A2" s="8" t="s">
@@ -2437,18 +2448,18 @@
       <c r="AB2" s="3"/>
     </row>
     <row r="3" spans="1:28" ht="15.75" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
+      <c r="L3" s="71"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
@@ -2466,7 +2477,7 @@
       <c r="AA3" s="3"/>
       <c r="AB3" s="3"/>
     </row>
-    <row r="4" spans="1:28" ht="16.5">
+    <row r="4" spans="1:28" ht="16.75">
       <c r="A4" s="6" t="s">
         <v>5</v>
       </c>
@@ -2609,7 +2620,7 @@
       <c r="AA8" s="3"/>
       <c r="AB8" s="3"/>
     </row>
-    <row r="9" spans="1:28" ht="16.5">
+    <row r="9" spans="1:28" ht="16.75">
       <c r="A9" s="6" t="s">
         <v>6</v>
       </c>
@@ -2640,87 +2651,87 @@
       <c r="AA9" s="3"/>
       <c r="AB9" s="3"/>
     </row>
-    <row r="10" spans="1:28" ht="16.5">
-      <c r="A10" s="60" t="s">
+    <row r="10" spans="1:28" ht="16.75">
+      <c r="A10" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="61"/>
-      <c r="C10" s="61"/>
-      <c r="D10" s="62"/>
-      <c r="E10" s="52" t="s">
+      <c r="B10" s="64"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="65"/>
+      <c r="E10" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="53"/>
-      <c r="K10" s="53"/>
-      <c r="L10" s="53"/>
-      <c r="M10" s="53"/>
-      <c r="N10" s="53"/>
-      <c r="O10" s="53"/>
-      <c r="P10" s="53"/>
-      <c r="Q10" s="53"/>
-      <c r="R10" s="53"/>
-      <c r="S10" s="53"/>
-      <c r="T10" s="53"/>
-      <c r="U10" s="53"/>
-      <c r="V10" s="53"/>
-      <c r="W10" s="53"/>
-      <c r="X10" s="53"/>
-      <c r="Y10" s="54" t="s">
+      <c r="F10" s="56"/>
+      <c r="G10" s="56"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="56"/>
+      <c r="K10" s="56"/>
+      <c r="L10" s="56"/>
+      <c r="M10" s="56"/>
+      <c r="N10" s="56"/>
+      <c r="O10" s="56"/>
+      <c r="P10" s="56"/>
+      <c r="Q10" s="56"/>
+      <c r="R10" s="56"/>
+      <c r="S10" s="56"/>
+      <c r="T10" s="56"/>
+      <c r="U10" s="56"/>
+      <c r="V10" s="56"/>
+      <c r="W10" s="56"/>
+      <c r="X10" s="56"/>
+      <c r="Y10" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="Z10" s="55"/>
-      <c r="AA10" s="55"/>
-      <c r="AB10" s="56"/>
+      <c r="Z10" s="58"/>
+      <c r="AA10" s="58"/>
+      <c r="AB10" s="59"/>
     </row>
     <row r="11" spans="1:28">
-      <c r="A11" s="63"/>
-      <c r="B11" s="64"/>
-      <c r="C11" s="64"/>
-      <c r="D11" s="65"/>
-      <c r="E11" s="52" t="s">
+      <c r="A11" s="66"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="53"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="66"/>
-      <c r="I11" s="52" t="s">
+      <c r="F11" s="56"/>
+      <c r="G11" s="56"/>
+      <c r="H11" s="69"/>
+      <c r="I11" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="J11" s="53"/>
-      <c r="K11" s="53"/>
-      <c r="L11" s="66"/>
-      <c r="M11" s="52" t="s">
+      <c r="J11" s="56"/>
+      <c r="K11" s="56"/>
+      <c r="L11" s="69"/>
+      <c r="M11" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="N11" s="53"/>
-      <c r="O11" s="53"/>
-      <c r="P11" s="66"/>
-      <c r="Q11" s="52" t="s">
+      <c r="N11" s="56"/>
+      <c r="O11" s="56"/>
+      <c r="P11" s="69"/>
+      <c r="Q11" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="R11" s="53"/>
-      <c r="S11" s="53"/>
-      <c r="T11" s="66"/>
-      <c r="U11" s="52" t="s">
+      <c r="R11" s="56"/>
+      <c r="S11" s="56"/>
+      <c r="T11" s="69"/>
+      <c r="U11" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="V11" s="53"/>
-      <c r="W11" s="53"/>
-      <c r="X11" s="67"/>
-      <c r="Y11" s="57"/>
-      <c r="Z11" s="58"/>
-      <c r="AA11" s="58"/>
-      <c r="AB11" s="59"/>
+      <c r="V11" s="56"/>
+      <c r="W11" s="56"/>
+      <c r="X11" s="70"/>
+      <c r="Y11" s="60"/>
+      <c r="Z11" s="61"/>
+      <c r="AA11" s="61"/>
+      <c r="AB11" s="62"/>
     </row>
     <row r="12" spans="1:28">
-      <c r="A12" s="69"/>
-      <c r="B12" s="70"/>
-      <c r="C12" s="70"/>
-      <c r="D12" s="71"/>
+      <c r="A12" s="51"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="53"/>
       <c r="E12" s="1"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
@@ -2747,10 +2758,10 @@
       <c r="AB12" s="2"/>
     </row>
     <row r="13" spans="1:28">
-      <c r="A13" s="69"/>
-      <c r="B13" s="70"/>
-      <c r="C13" s="70"/>
-      <c r="D13" s="71"/>
+      <c r="A13" s="51"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="53"/>
       <c r="E13" s="1"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
@@ -2777,10 +2788,10 @@
       <c r="AB13" s="2"/>
     </row>
     <row r="14" spans="1:28">
-      <c r="A14" s="69"/>
-      <c r="B14" s="70"/>
-      <c r="C14" s="70"/>
-      <c r="D14" s="71"/>
+      <c r="A14" s="51"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="53"/>
       <c r="E14" s="1"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
@@ -2807,10 +2818,10 @@
       <c r="AB14" s="2"/>
     </row>
     <row r="15" spans="1:28">
-      <c r="A15" s="69"/>
-      <c r="B15" s="70"/>
-      <c r="C15" s="70"/>
-      <c r="D15" s="71"/>
+      <c r="A15" s="51"/>
+      <c r="B15" s="52"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="53"/>
       <c r="E15" s="1"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
@@ -2837,10 +2848,10 @@
       <c r="AB15" s="2"/>
     </row>
     <row r="16" spans="1:28">
-      <c r="A16" s="69"/>
-      <c r="B16" s="70"/>
-      <c r="C16" s="70"/>
-      <c r="D16" s="71"/>
+      <c r="A16" s="51"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="53"/>
       <c r="E16" s="1"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
@@ -3007,11 +3018,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A16:D16"/>
     <mergeCell ref="J1:AB1"/>
     <mergeCell ref="E10:X10"/>
     <mergeCell ref="Y10:AB11"/>
@@ -3022,6 +3028,11 @@
     <mergeCell ref="Q11:T11"/>
     <mergeCell ref="U11:X11"/>
     <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -3041,12 +3052,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79A966B5-BF06-44FD-908C-4467C7012DA9}">
   <dimension ref="A1:AL55"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.15"/>
   <cols>
-    <col min="1" max="7" width="2.375" customWidth="1"/>
+    <col min="1" max="7" width="2.35546875" customWidth="1"/>
     <col min="8" max="8" width="2" customWidth="1"/>
-    <col min="9" max="31" width="2.125" customWidth="1"/>
-    <col min="32" max="38" width="2.375" customWidth="1"/>
+    <col min="9" max="31" width="2.140625" customWidth="1"/>
+    <col min="32" max="38" width="2.35546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="15" customHeight="1">
@@ -3061,32 +3072,32 @@
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
-      <c r="M1" s="72"/>
-      <c r="N1" s="72"/>
-      <c r="O1" s="72"/>
-      <c r="P1" s="72"/>
-      <c r="Q1" s="72"/>
-      <c r="R1" s="72"/>
-      <c r="S1" s="72"/>
-      <c r="T1" s="72"/>
-      <c r="U1" s="72"/>
-      <c r="V1" s="72"/>
-      <c r="W1" s="72"/>
-      <c r="X1" s="72"/>
-      <c r="Y1" s="72"/>
-      <c r="Z1" s="72"/>
-      <c r="AA1" s="72"/>
-      <c r="AB1" s="72"/>
-      <c r="AC1" s="72"/>
-      <c r="AD1" s="72"/>
-      <c r="AE1" s="72"/>
-      <c r="AF1" s="72"/>
-      <c r="AG1" s="72"/>
-      <c r="AH1" s="72"/>
-      <c r="AI1" s="72"/>
-      <c r="AJ1" s="72"/>
-      <c r="AK1" s="72"/>
-      <c r="AL1" s="72"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="78"/>
+      <c r="AG1" s="78"/>
+      <c r="AH1" s="78"/>
+      <c r="AI1" s="78"/>
+      <c r="AJ1" s="78"/>
+      <c r="AK1" s="78"/>
+      <c r="AL1" s="78"/>
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1">
       <c r="A2" s="19" t="s">
@@ -3128,18 +3139,18 @@
       <c r="E3" s="3"/>
       <c r="F3" s="34"/>
       <c r="G3" s="34"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="82"/>
-      <c r="K3" s="82"/>
-      <c r="L3" s="82"/>
-      <c r="M3" s="82"/>
-      <c r="N3" s="82"/>
-      <c r="O3" s="82"/>
-      <c r="P3" s="82"/>
-      <c r="Q3" s="82"/>
-      <c r="R3" s="82"/>
-      <c r="S3" s="82"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="74"/>
+      <c r="K3" s="74"/>
+      <c r="L3" s="74"/>
+      <c r="M3" s="74"/>
+      <c r="N3" s="74"/>
+      <c r="O3" s="74"/>
+      <c r="P3" s="74"/>
+      <c r="Q3" s="74"/>
+      <c r="R3" s="74"/>
+      <c r="S3" s="74"/>
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
@@ -3158,8 +3169,8 @@
       <c r="A4" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="72"/>
-      <c r="E4" s="72"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
       <c r="F4" s="34" t="s">
         <v>43</v>
       </c>
@@ -3223,23 +3234,23 @@
       <c r="AK5" s="6"/>
     </row>
     <row r="6" spans="1:38" ht="15" customHeight="1">
-      <c r="A6" s="80" t="s">
+      <c r="A6" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="81"/>
-      <c r="C6" s="81"/>
-      <c r="D6" s="81"/>
-      <c r="E6" s="81"/>
-      <c r="F6" s="79" t="s">
+      <c r="B6" s="82"/>
+      <c r="C6" s="82"/>
+      <c r="D6" s="82"/>
+      <c r="E6" s="82"/>
+      <c r="F6" s="81" t="s">
         <v>44</v>
       </c>
-      <c r="G6" s="79"/>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
-      <c r="J6" s="79"/>
-      <c r="K6" s="79"/>
-      <c r="L6" s="79"/>
-      <c r="M6" s="79"/>
+      <c r="G6" s="81"/>
+      <c r="H6" s="81"/>
+      <c r="I6" s="81"/>
+      <c r="J6" s="81"/>
+      <c r="K6" s="81"/>
+      <c r="L6" s="81"/>
+      <c r="M6" s="81"/>
       <c r="N6" s="36"/>
       <c r="O6" s="36"/>
       <c r="P6" s="36"/>
@@ -3267,19 +3278,19 @@
       <c r="AL6" s="36"/>
     </row>
     <row r="7" spans="1:38" ht="15" customHeight="1">
-      <c r="A7" s="81"/>
-      <c r="B7" s="81"/>
-      <c r="C7" s="81"/>
-      <c r="D7" s="81"/>
-      <c r="E7" s="81"/>
-      <c r="F7" s="79"/>
-      <c r="G7" s="79"/>
-      <c r="H7" s="79"/>
-      <c r="I7" s="79"/>
-      <c r="J7" s="79"/>
-      <c r="K7" s="79"/>
-      <c r="L7" s="79"/>
-      <c r="M7" s="79"/>
+      <c r="A7" s="82"/>
+      <c r="B7" s="82"/>
+      <c r="C7" s="82"/>
+      <c r="D7" s="82"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="81"/>
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
+      <c r="J7" s="81"/>
+      <c r="K7" s="81"/>
+      <c r="L7" s="81"/>
+      <c r="M7" s="81"/>
       <c r="N7" s="36"/>
       <c r="O7" s="36"/>
       <c r="P7" s="36"/>
@@ -3306,20 +3317,20 @@
       <c r="AK7" s="36"/>
       <c r="AL7" s="36"/>
     </row>
-    <row r="8" spans="1:38" ht="21.2" customHeight="1">
-      <c r="A8" s="69"/>
-      <c r="B8" s="70"/>
-      <c r="C8" s="70"/>
-      <c r="D8" s="70"/>
-      <c r="E8" s="71"/>
-      <c r="F8" s="76"/>
-      <c r="G8" s="77"/>
-      <c r="H8" s="77"/>
-      <c r="I8" s="77"/>
-      <c r="J8" s="77"/>
-      <c r="K8" s="77"/>
-      <c r="L8" s="77"/>
-      <c r="M8" s="78"/>
+    <row r="8" spans="1:38" ht="21.25" customHeight="1">
+      <c r="A8" s="51"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="53"/>
+      <c r="F8" s="75"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="76"/>
+      <c r="J8" s="76"/>
+      <c r="K8" s="76"/>
+      <c r="L8" s="76"/>
+      <c r="M8" s="77"/>
       <c r="N8" s="36"/>
       <c r="O8" s="36"/>
       <c r="P8" s="36"/>
@@ -3346,20 +3357,20 @@
       <c r="AK8" s="36"/>
       <c r="AL8" s="36"/>
     </row>
-    <row r="9" spans="1:38" ht="21.2" customHeight="1">
-      <c r="A9" s="69"/>
-      <c r="B9" s="70"/>
-      <c r="C9" s="70"/>
-      <c r="D9" s="70"/>
-      <c r="E9" s="71"/>
-      <c r="F9" s="76"/>
-      <c r="G9" s="77"/>
-      <c r="H9" s="77"/>
-      <c r="I9" s="77"/>
-      <c r="J9" s="77"/>
-      <c r="K9" s="77"/>
-      <c r="L9" s="77"/>
-      <c r="M9" s="78"/>
+    <row r="9" spans="1:38" ht="21.25" customHeight="1">
+      <c r="A9" s="51"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="75"/>
+      <c r="G9" s="76"/>
+      <c r="H9" s="76"/>
+      <c r="I9" s="76"/>
+      <c r="J9" s="76"/>
+      <c r="K9" s="76"/>
+      <c r="L9" s="76"/>
+      <c r="M9" s="77"/>
       <c r="N9" s="36"/>
       <c r="O9" s="36"/>
       <c r="P9" s="36"/>
@@ -3386,20 +3397,20 @@
       <c r="AK9" s="36"/>
       <c r="AL9" s="36"/>
     </row>
-    <row r="10" spans="1:38" ht="21.2" customHeight="1">
+    <row r="10" spans="1:38" ht="21.25" customHeight="1">
       <c r="A10" s="73"/>
       <c r="B10" s="73"/>
       <c r="C10" s="73"/>
       <c r="D10" s="73"/>
       <c r="E10" s="73"/>
-      <c r="F10" s="79"/>
-      <c r="G10" s="79"/>
-      <c r="H10" s="79"/>
-      <c r="I10" s="79"/>
-      <c r="J10" s="79"/>
-      <c r="K10" s="79"/>
-      <c r="L10" s="79"/>
-      <c r="M10" s="79"/>
+      <c r="F10" s="81"/>
+      <c r="G10" s="81"/>
+      <c r="H10" s="81"/>
+      <c r="I10" s="81"/>
+      <c r="J10" s="81"/>
+      <c r="K10" s="81"/>
+      <c r="L10" s="81"/>
+      <c r="M10" s="81"/>
       <c r="N10" s="36"/>
       <c r="O10" s="36"/>
       <c r="P10" s="36"/>
@@ -3426,20 +3437,20 @@
       <c r="AK10" s="36"/>
       <c r="AL10" s="36"/>
     </row>
-    <row r="11" spans="1:38" ht="21.2" customHeight="1">
-      <c r="A11" s="74"/>
-      <c r="B11" s="74"/>
-      <c r="C11" s="74"/>
-      <c r="D11" s="74"/>
-      <c r="E11" s="74"/>
-      <c r="F11" s="79"/>
-      <c r="G11" s="79"/>
-      <c r="H11" s="79"/>
-      <c r="I11" s="79"/>
-      <c r="J11" s="79"/>
-      <c r="K11" s="79"/>
-      <c r="L11" s="79"/>
-      <c r="M11" s="79"/>
+    <row r="11" spans="1:38" ht="21.25" customHeight="1">
+      <c r="A11" s="79"/>
+      <c r="B11" s="79"/>
+      <c r="C11" s="79"/>
+      <c r="D11" s="79"/>
+      <c r="E11" s="79"/>
+      <c r="F11" s="81"/>
+      <c r="G11" s="81"/>
+      <c r="H11" s="81"/>
+      <c r="I11" s="81"/>
+      <c r="J11" s="81"/>
+      <c r="K11" s="81"/>
+      <c r="L11" s="81"/>
+      <c r="M11" s="81"/>
       <c r="N11" s="36"/>
       <c r="O11" s="36"/>
       <c r="P11" s="36"/>
@@ -3576,20 +3587,20 @@
       <c r="G15" s="34"/>
       <c r="H15" s="34"/>
       <c r="I15" s="34"/>
-      <c r="J15" s="75"/>
-      <c r="K15" s="75"/>
-      <c r="L15" s="75"/>
-      <c r="M15" s="75"/>
-      <c r="N15" s="75"/>
-      <c r="O15" s="75"/>
-      <c r="P15" s="75"/>
-      <c r="Q15" s="75"/>
-      <c r="R15" s="75"/>
-      <c r="S15" s="75"/>
-      <c r="T15" s="75"/>
-      <c r="U15" s="75"/>
-      <c r="V15" s="75"/>
-      <c r="W15" s="75"/>
+      <c r="J15" s="80"/>
+      <c r="K15" s="80"/>
+      <c r="L15" s="80"/>
+      <c r="M15" s="80"/>
+      <c r="N15" s="80"/>
+      <c r="O15" s="80"/>
+      <c r="P15" s="80"/>
+      <c r="Q15" s="80"/>
+      <c r="R15" s="80"/>
+      <c r="S15" s="80"/>
+      <c r="T15" s="80"/>
+      <c r="U15" s="80"/>
+      <c r="V15" s="80"/>
+      <c r="W15" s="80"/>
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
@@ -3634,8 +3645,8 @@
       <c r="A17" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="72"/>
-      <c r="D17" s="72"/>
+      <c r="C17" s="78"/>
+      <c r="D17" s="78"/>
       <c r="E17" s="34" t="s">
         <v>54</v>
       </c>
@@ -3701,18 +3712,18 @@
       <c r="AK18" s="6"/>
     </row>
     <row r="19" spans="1:38" ht="15" customHeight="1">
-      <c r="A19" s="80" t="s">
+      <c r="A19" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="80"/>
-      <c r="C19" s="80"/>
-      <c r="D19" s="80"/>
-      <c r="E19" s="80"/>
-      <c r="F19" s="80"/>
-      <c r="G19" s="80"/>
-      <c r="H19" s="80"/>
-      <c r="I19" s="80"/>
-      <c r="J19" s="80"/>
+      <c r="B19" s="72"/>
+      <c r="C19" s="72"/>
+      <c r="D19" s="72"/>
+      <c r="E19" s="72"/>
+      <c r="F19" s="72"/>
+      <c r="G19" s="72"/>
+      <c r="H19" s="72"/>
+      <c r="I19" s="72"/>
+      <c r="J19" s="72"/>
       <c r="K19" s="73"/>
       <c r="L19" s="73"/>
       <c r="M19" s="73"/>
@@ -3743,16 +3754,16 @@
       <c r="AL19" s="73"/>
     </row>
     <row r="20" spans="1:38" ht="15" customHeight="1">
-      <c r="A20" s="80"/>
-      <c r="B20" s="80"/>
-      <c r="C20" s="80"/>
-      <c r="D20" s="80"/>
-      <c r="E20" s="80"/>
-      <c r="F20" s="80"/>
-      <c r="G20" s="80"/>
-      <c r="H20" s="80"/>
-      <c r="I20" s="80"/>
-      <c r="J20" s="80"/>
+      <c r="A20" s="72"/>
+      <c r="B20" s="72"/>
+      <c r="C20" s="72"/>
+      <c r="D20" s="72"/>
+      <c r="E20" s="72"/>
+      <c r="F20" s="72"/>
+      <c r="G20" s="72"/>
+      <c r="H20" s="72"/>
+      <c r="I20" s="72"/>
+      <c r="J20" s="72"/>
       <c r="K20" s="73"/>
       <c r="L20" s="73"/>
       <c r="M20" s="73"/>
@@ -3783,168 +3794,168 @@
       <c r="AL20" s="73"/>
     </row>
     <row r="21" spans="1:38" ht="15" customHeight="1">
-      <c r="A21" s="80" t="s">
+      <c r="A21" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="B21" s="80"/>
-      <c r="C21" s="80"/>
-      <c r="D21" s="80"/>
-      <c r="E21" s="80"/>
-      <c r="F21" s="80"/>
-      <c r="G21" s="80"/>
-      <c r="H21" s="80"/>
-      <c r="I21" s="80"/>
-      <c r="J21" s="80"/>
-      <c r="K21" s="80"/>
-      <c r="L21" s="80"/>
-      <c r="M21" s="80"/>
-      <c r="N21" s="80"/>
-      <c r="O21" s="80"/>
-      <c r="P21" s="80"/>
-      <c r="Q21" s="80"/>
-      <c r="R21" s="80"/>
-      <c r="S21" s="80"/>
-      <c r="T21" s="80"/>
-      <c r="U21" s="80"/>
-      <c r="V21" s="80"/>
-      <c r="W21" s="80"/>
-      <c r="X21" s="80"/>
-      <c r="Y21" s="80"/>
-      <c r="Z21" s="80"/>
-      <c r="AA21" s="80"/>
-      <c r="AB21" s="80"/>
-      <c r="AC21" s="80"/>
-      <c r="AD21" s="80"/>
-      <c r="AE21" s="80"/>
-      <c r="AF21" s="80"/>
-      <c r="AG21" s="80"/>
-      <c r="AH21" s="80"/>
-      <c r="AI21" s="80"/>
-      <c r="AJ21" s="80"/>
-      <c r="AK21" s="80"/>
-      <c r="AL21" s="80"/>
+      <c r="B21" s="72"/>
+      <c r="C21" s="72"/>
+      <c r="D21" s="72"/>
+      <c r="E21" s="72"/>
+      <c r="F21" s="72"/>
+      <c r="G21" s="72"/>
+      <c r="H21" s="72"/>
+      <c r="I21" s="72"/>
+      <c r="J21" s="72"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="72"/>
+      <c r="M21" s="72"/>
+      <c r="N21" s="72"/>
+      <c r="O21" s="72"/>
+      <c r="P21" s="72"/>
+      <c r="Q21" s="72"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="72"/>
+      <c r="T21" s="72"/>
+      <c r="U21" s="72"/>
+      <c r="V21" s="72"/>
+      <c r="W21" s="72"/>
+      <c r="X21" s="72"/>
+      <c r="Y21" s="72"/>
+      <c r="Z21" s="72"/>
+      <c r="AA21" s="72"/>
+      <c r="AB21" s="72"/>
+      <c r="AC21" s="72"/>
+      <c r="AD21" s="72"/>
+      <c r="AE21" s="72"/>
+      <c r="AF21" s="72"/>
+      <c r="AG21" s="72"/>
+      <c r="AH21" s="72"/>
+      <c r="AI21" s="72"/>
+      <c r="AJ21" s="72"/>
+      <c r="AK21" s="72"/>
+      <c r="AL21" s="72"/>
     </row>
     <row r="22" spans="1:38" ht="15" customHeight="1">
-      <c r="A22" s="80"/>
-      <c r="B22" s="80"/>
-      <c r="C22" s="80"/>
-      <c r="D22" s="80"/>
-      <c r="E22" s="80"/>
-      <c r="F22" s="80"/>
-      <c r="G22" s="80"/>
-      <c r="H22" s="80"/>
-      <c r="I22" s="80"/>
-      <c r="J22" s="80"/>
-      <c r="K22" s="80"/>
-      <c r="L22" s="80"/>
-      <c r="M22" s="80"/>
-      <c r="N22" s="80"/>
-      <c r="O22" s="80"/>
-      <c r="P22" s="80"/>
-      <c r="Q22" s="80"/>
-      <c r="R22" s="80"/>
-      <c r="S22" s="80"/>
-      <c r="T22" s="80"/>
-      <c r="U22" s="80"/>
-      <c r="V22" s="80"/>
-      <c r="W22" s="80"/>
-      <c r="X22" s="80"/>
-      <c r="Y22" s="80"/>
-      <c r="Z22" s="80"/>
-      <c r="AA22" s="80"/>
-      <c r="AB22" s="80"/>
-      <c r="AC22" s="80"/>
-      <c r="AD22" s="80"/>
-      <c r="AE22" s="80"/>
-      <c r="AF22" s="80"/>
-      <c r="AG22" s="80"/>
-      <c r="AH22" s="80"/>
-      <c r="AI22" s="80"/>
-      <c r="AJ22" s="80"/>
-      <c r="AK22" s="80"/>
-      <c r="AL22" s="80"/>
+      <c r="A22" s="72"/>
+      <c r="B22" s="72"/>
+      <c r="C22" s="72"/>
+      <c r="D22" s="72"/>
+      <c r="E22" s="72"/>
+      <c r="F22" s="72"/>
+      <c r="G22" s="72"/>
+      <c r="H22" s="72"/>
+      <c r="I22" s="72"/>
+      <c r="J22" s="72"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="72"/>
+      <c r="M22" s="72"/>
+      <c r="N22" s="72"/>
+      <c r="O22" s="72"/>
+      <c r="P22" s="72"/>
+      <c r="Q22" s="72"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="72"/>
+      <c r="T22" s="72"/>
+      <c r="U22" s="72"/>
+      <c r="V22" s="72"/>
+      <c r="W22" s="72"/>
+      <c r="X22" s="72"/>
+      <c r="Y22" s="72"/>
+      <c r="Z22" s="72"/>
+      <c r="AA22" s="72"/>
+      <c r="AB22" s="72"/>
+      <c r="AC22" s="72"/>
+      <c r="AD22" s="72"/>
+      <c r="AE22" s="72"/>
+      <c r="AF22" s="72"/>
+      <c r="AG22" s="72"/>
+      <c r="AH22" s="72"/>
+      <c r="AI22" s="72"/>
+      <c r="AJ22" s="72"/>
+      <c r="AK22" s="72"/>
+      <c r="AL22" s="72"/>
     </row>
     <row r="23" spans="1:38" ht="15" customHeight="1">
-      <c r="A23" s="80" t="s">
+      <c r="A23" s="72" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="80"/>
-      <c r="C23" s="80"/>
-      <c r="D23" s="80"/>
-      <c r="E23" s="80"/>
-      <c r="F23" s="80"/>
-      <c r="G23" s="80"/>
-      <c r="H23" s="80"/>
-      <c r="I23" s="80"/>
-      <c r="J23" s="80"/>
-      <c r="K23" s="80"/>
-      <c r="L23" s="80"/>
-      <c r="M23" s="80"/>
-      <c r="N23" s="80"/>
-      <c r="O23" s="80"/>
-      <c r="P23" s="80"/>
-      <c r="Q23" s="80"/>
-      <c r="R23" s="80"/>
-      <c r="S23" s="80"/>
-      <c r="T23" s="80"/>
-      <c r="U23" s="80"/>
-      <c r="V23" s="80"/>
-      <c r="W23" s="80"/>
-      <c r="X23" s="80"/>
-      <c r="Y23" s="80"/>
-      <c r="Z23" s="80"/>
-      <c r="AA23" s="80"/>
-      <c r="AB23" s="80"/>
-      <c r="AC23" s="80"/>
-      <c r="AD23" s="80"/>
-      <c r="AE23" s="80"/>
-      <c r="AF23" s="80"/>
-      <c r="AG23" s="80"/>
-      <c r="AH23" s="80"/>
-      <c r="AI23" s="80"/>
-      <c r="AJ23" s="80"/>
-      <c r="AK23" s="80"/>
-      <c r="AL23" s="80"/>
+      <c r="B23" s="72"/>
+      <c r="C23" s="72"/>
+      <c r="D23" s="72"/>
+      <c r="E23" s="72"/>
+      <c r="F23" s="72"/>
+      <c r="G23" s="72"/>
+      <c r="H23" s="72"/>
+      <c r="I23" s="72"/>
+      <c r="J23" s="72"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="72"/>
+      <c r="M23" s="72"/>
+      <c r="N23" s="72"/>
+      <c r="O23" s="72"/>
+      <c r="P23" s="72"/>
+      <c r="Q23" s="72"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="72"/>
+      <c r="T23" s="72"/>
+      <c r="U23" s="72"/>
+      <c r="V23" s="72"/>
+      <c r="W23" s="72"/>
+      <c r="X23" s="72"/>
+      <c r="Y23" s="72"/>
+      <c r="Z23" s="72"/>
+      <c r="AA23" s="72"/>
+      <c r="AB23" s="72"/>
+      <c r="AC23" s="72"/>
+      <c r="AD23" s="72"/>
+      <c r="AE23" s="72"/>
+      <c r="AF23" s="72"/>
+      <c r="AG23" s="72"/>
+      <c r="AH23" s="72"/>
+      <c r="AI23" s="72"/>
+      <c r="AJ23" s="72"/>
+      <c r="AK23" s="72"/>
+      <c r="AL23" s="72"/>
     </row>
     <row r="24" spans="1:38" ht="15" customHeight="1">
-      <c r="A24" s="80"/>
-      <c r="B24" s="80"/>
-      <c r="C24" s="80"/>
-      <c r="D24" s="80"/>
-      <c r="E24" s="80"/>
-      <c r="F24" s="80"/>
-      <c r="G24" s="80"/>
-      <c r="H24" s="80"/>
-      <c r="I24" s="80"/>
-      <c r="J24" s="80"/>
-      <c r="K24" s="80"/>
-      <c r="L24" s="80"/>
-      <c r="M24" s="80"/>
-      <c r="N24" s="80"/>
-      <c r="O24" s="80"/>
-      <c r="P24" s="80"/>
-      <c r="Q24" s="80"/>
-      <c r="R24" s="80"/>
-      <c r="S24" s="80"/>
-      <c r="T24" s="80"/>
-      <c r="U24" s="80"/>
-      <c r="V24" s="80"/>
-      <c r="W24" s="80"/>
-      <c r="X24" s="80"/>
-      <c r="Y24" s="80"/>
-      <c r="Z24" s="80"/>
-      <c r="AA24" s="80"/>
-      <c r="AB24" s="80"/>
-      <c r="AC24" s="80"/>
-      <c r="AD24" s="80"/>
-      <c r="AE24" s="80"/>
-      <c r="AF24" s="80"/>
-      <c r="AG24" s="80"/>
-      <c r="AH24" s="80"/>
-      <c r="AI24" s="80"/>
-      <c r="AJ24" s="80"/>
-      <c r="AK24" s="80"/>
-      <c r="AL24" s="80"/>
+      <c r="A24" s="72"/>
+      <c r="B24" s="72"/>
+      <c r="C24" s="72"/>
+      <c r="D24" s="72"/>
+      <c r="E24" s="72"/>
+      <c r="F24" s="72"/>
+      <c r="G24" s="72"/>
+      <c r="H24" s="72"/>
+      <c r="I24" s="72"/>
+      <c r="J24" s="72"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="72"/>
+      <c r="M24" s="72"/>
+      <c r="N24" s="72"/>
+      <c r="O24" s="72"/>
+      <c r="P24" s="72"/>
+      <c r="Q24" s="72"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="72"/>
+      <c r="T24" s="72"/>
+      <c r="U24" s="72"/>
+      <c r="V24" s="72"/>
+      <c r="W24" s="72"/>
+      <c r="X24" s="72"/>
+      <c r="Y24" s="72"/>
+      <c r="Z24" s="72"/>
+      <c r="AA24" s="72"/>
+      <c r="AB24" s="72"/>
+      <c r="AC24" s="72"/>
+      <c r="AD24" s="72"/>
+      <c r="AE24" s="72"/>
+      <c r="AF24" s="72"/>
+      <c r="AG24" s="72"/>
+      <c r="AH24" s="72"/>
+      <c r="AI24" s="72"/>
+      <c r="AJ24" s="72"/>
+      <c r="AK24" s="72"/>
+      <c r="AL24" s="72"/>
     </row>
     <row r="25" spans="1:38" ht="15" customHeight="1">
       <c r="A25" s="34"/>
@@ -4849,7 +4860,7 @@
       <c r="AK46" s="41"/>
       <c r="AL46" s="41"/>
     </row>
-    <row r="47" spans="1:38" ht="13.9" customHeight="1">
+    <row r="47" spans="1:38" ht="13.95" customHeight="1">
       <c r="P47" s="39"/>
       <c r="Q47" s="39"/>
       <c r="R47" s="39"/>
@@ -4874,7 +4885,7 @@
       <c r="AK47" s="39"/>
       <c r="AL47" s="39"/>
     </row>
-    <row r="48" spans="1:38" ht="13.9" customHeight="1">
+    <row r="48" spans="1:38" ht="13.95" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
@@ -4913,7 +4924,7 @@
       <c r="AK48" s="39"/>
       <c r="AL48" s="39"/>
     </row>
-    <row r="49" spans="1:38" ht="13.9" customHeight="1">
+    <row r="49" spans="1:38" ht="13.95" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
@@ -5118,24 +5129,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A19:J20"/>
-    <mergeCell ref="K19:Q20"/>
-    <mergeCell ref="AF21:AL22"/>
-    <mergeCell ref="H3:S3"/>
-    <mergeCell ref="F9:M9"/>
-    <mergeCell ref="R19:X20"/>
-    <mergeCell ref="Y23:AE24"/>
-    <mergeCell ref="AF23:AL24"/>
-    <mergeCell ref="Y19:AE20"/>
-    <mergeCell ref="AF19:AL20"/>
-    <mergeCell ref="R23:X24"/>
-    <mergeCell ref="A23:J24"/>
-    <mergeCell ref="K23:Q24"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="A21:J22"/>
-    <mergeCell ref="K21:Q22"/>
-    <mergeCell ref="R21:X22"/>
-    <mergeCell ref="Y21:AE22"/>
     <mergeCell ref="M1:AL1"/>
     <mergeCell ref="A8:E8"/>
     <mergeCell ref="A10:E10"/>
@@ -5148,6 +5141,24 @@
     <mergeCell ref="F6:M7"/>
     <mergeCell ref="A6:E7"/>
     <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A23:J24"/>
+    <mergeCell ref="K23:Q24"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A21:J22"/>
+    <mergeCell ref="K21:Q22"/>
+    <mergeCell ref="Y23:AE24"/>
+    <mergeCell ref="AF23:AL24"/>
+    <mergeCell ref="Y19:AE20"/>
+    <mergeCell ref="AF19:AL20"/>
+    <mergeCell ref="R23:X24"/>
+    <mergeCell ref="R21:X22"/>
+    <mergeCell ref="Y21:AE22"/>
+    <mergeCell ref="A19:J20"/>
+    <mergeCell ref="K19:Q20"/>
+    <mergeCell ref="AF21:AL22"/>
+    <mergeCell ref="H3:S3"/>
+    <mergeCell ref="F9:M9"/>
+    <mergeCell ref="R19:X20"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -5167,12 +5178,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{626CC06E-9590-4323-BE24-60512668D6F0}">
   <dimension ref="A1:AN34"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.15"/>
   <cols>
-    <col min="1" max="7" width="2.375" customWidth="1"/>
+    <col min="1" max="7" width="2.35546875" customWidth="1"/>
     <col min="8" max="8" width="2" customWidth="1"/>
-    <col min="9" max="31" width="2.125" customWidth="1"/>
-    <col min="32" max="39" width="2.375" customWidth="1"/>
+    <col min="9" max="31" width="2.140625" customWidth="1"/>
+    <col min="32" max="39" width="2.35546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="15" customHeight="1">
@@ -5187,32 +5198,32 @@
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
-      <c r="M1" s="72"/>
-      <c r="N1" s="72"/>
-      <c r="O1" s="72"/>
-      <c r="P1" s="72"/>
-      <c r="Q1" s="72"/>
-      <c r="R1" s="72"/>
-      <c r="S1" s="72"/>
-      <c r="T1" s="72"/>
-      <c r="U1" s="72"/>
-      <c r="V1" s="72"/>
-      <c r="W1" s="72"/>
-      <c r="X1" s="72"/>
-      <c r="Y1" s="72"/>
-      <c r="Z1" s="72"/>
-      <c r="AA1" s="72"/>
-      <c r="AB1" s="72"/>
-      <c r="AC1" s="72"/>
-      <c r="AD1" s="72"/>
-      <c r="AE1" s="72"/>
-      <c r="AF1" s="72"/>
-      <c r="AG1" s="72"/>
-      <c r="AH1" s="72"/>
-      <c r="AI1" s="72"/>
-      <c r="AJ1" s="72"/>
-      <c r="AK1" s="72"/>
-      <c r="AL1" s="72"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="78"/>
+      <c r="AG1" s="78"/>
+      <c r="AH1" s="78"/>
+      <c r="AI1" s="78"/>
+      <c r="AJ1" s="78"/>
+      <c r="AK1" s="78"/>
+      <c r="AL1" s="78"/>
       <c r="AM1" s="33"/>
     </row>
     <row r="2" spans="1:39" ht="15" customHeight="1">
@@ -5249,17 +5260,17 @@
       <c r="AF2" s="3"/>
     </row>
     <row r="3" spans="1:39" ht="15" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
       <c r="L3" s="20"/>
       <c r="M3" s="20"/>
       <c r="N3" s="3"/>
@@ -5267,13 +5278,17 @@
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
+      <c r="S3" s="13" t="s">
+        <v>173</v>
+      </c>
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
-      <c r="W3" s="3"/>
-      <c r="X3" s="3"/>
-      <c r="Y3" s="3"/>
+      <c r="V3" s="104" t="s">
+        <v>174</v>
+      </c>
+      <c r="W3" s="104"/>
+      <c r="X3" s="104"/>
+      <c r="Y3" s="104"/>
       <c r="Z3" s="3"/>
       <c r="AA3" s="3"/>
       <c r="AB3" s="3"/>
@@ -5421,44 +5436,44 @@
       <c r="AM7" s="14"/>
     </row>
     <row r="8" spans="1:39" ht="15" customHeight="1">
-      <c r="A8" s="81" t="s">
+      <c r="A8" s="82" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="81"/>
-      <c r="C8" s="81"/>
-      <c r="D8" s="81"/>
-      <c r="E8" s="81"/>
-      <c r="F8" s="81"/>
-      <c r="G8" s="81"/>
-      <c r="H8" s="81"/>
-      <c r="I8" s="81"/>
-      <c r="J8" s="86" t="s">
+      <c r="B8" s="82"/>
+      <c r="C8" s="82"/>
+      <c r="D8" s="82"/>
+      <c r="E8" s="82"/>
+      <c r="F8" s="82"/>
+      <c r="G8" s="82"/>
+      <c r="H8" s="82"/>
+      <c r="I8" s="82"/>
+      <c r="J8" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="K8" s="86"/>
-      <c r="L8" s="86"/>
-      <c r="M8" s="86"/>
-      <c r="N8" s="86"/>
-      <c r="O8" s="86"/>
-      <c r="P8" s="86"/>
-      <c r="Q8" s="86"/>
-      <c r="R8" s="86"/>
-      <c r="S8" s="86"/>
-      <c r="T8" s="86"/>
-      <c r="U8" s="86"/>
-      <c r="V8" s="86"/>
-      <c r="W8" s="86"/>
-      <c r="X8" s="86"/>
-      <c r="Y8" s="86"/>
-      <c r="Z8" s="86"/>
-      <c r="AA8" s="86"/>
-      <c r="AB8" s="86"/>
-      <c r="AC8" s="86"/>
-      <c r="AD8" s="86"/>
-      <c r="AE8" s="86"/>
-      <c r="AF8" s="86"/>
-      <c r="AG8" s="86"/>
-      <c r="AH8" s="86"/>
+      <c r="K8" s="83"/>
+      <c r="L8" s="83"/>
+      <c r="M8" s="83"/>
+      <c r="N8" s="83"/>
+      <c r="O8" s="83"/>
+      <c r="P8" s="83"/>
+      <c r="Q8" s="83"/>
+      <c r="R8" s="83"/>
+      <c r="S8" s="83"/>
+      <c r="T8" s="83"/>
+      <c r="U8" s="83"/>
+      <c r="V8" s="83"/>
+      <c r="W8" s="83"/>
+      <c r="X8" s="83"/>
+      <c r="Y8" s="83"/>
+      <c r="Z8" s="83"/>
+      <c r="AA8" s="83"/>
+      <c r="AB8" s="83"/>
+      <c r="AC8" s="83"/>
+      <c r="AD8" s="83"/>
+      <c r="AE8" s="83"/>
+      <c r="AF8" s="83"/>
+      <c r="AG8" s="83"/>
+      <c r="AH8" s="83"/>
       <c r="AI8" s="87" t="s">
         <v>19</v>
       </c>
@@ -5468,50 +5483,50 @@
       <c r="AM8" s="14"/>
     </row>
     <row r="9" spans="1:39" ht="15" customHeight="1">
-      <c r="A9" s="81"/>
-      <c r="B9" s="81"/>
-      <c r="C9" s="81"/>
-      <c r="D9" s="81"/>
-      <c r="E9" s="81"/>
-      <c r="F9" s="81"/>
-      <c r="G9" s="81"/>
-      <c r="H9" s="81"/>
-      <c r="I9" s="81"/>
-      <c r="J9" s="86" t="s">
+      <c r="A9" s="82"/>
+      <c r="B9" s="82"/>
+      <c r="C9" s="82"/>
+      <c r="D9" s="82"/>
+      <c r="E9" s="82"/>
+      <c r="F9" s="82"/>
+      <c r="G9" s="82"/>
+      <c r="H9" s="82"/>
+      <c r="I9" s="82"/>
+      <c r="J9" s="83" t="s">
         <v>28</v>
       </c>
-      <c r="K9" s="86"/>
-      <c r="L9" s="86"/>
-      <c r="M9" s="86"/>
-      <c r="N9" s="86"/>
-      <c r="O9" s="86" t="s">
+      <c r="K9" s="83"/>
+      <c r="L9" s="83"/>
+      <c r="M9" s="83"/>
+      <c r="N9" s="83"/>
+      <c r="O9" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="P9" s="86"/>
-      <c r="Q9" s="86"/>
-      <c r="R9" s="86"/>
-      <c r="S9" s="86"/>
-      <c r="T9" s="86" t="s">
+      <c r="P9" s="83"/>
+      <c r="Q9" s="83"/>
+      <c r="R9" s="83"/>
+      <c r="S9" s="83"/>
+      <c r="T9" s="83" t="s">
         <v>30</v>
       </c>
-      <c r="U9" s="86"/>
-      <c r="V9" s="86"/>
-      <c r="W9" s="86"/>
-      <c r="X9" s="86"/>
-      <c r="Y9" s="86" t="s">
+      <c r="U9" s="83"/>
+      <c r="V9" s="83"/>
+      <c r="W9" s="83"/>
+      <c r="X9" s="83"/>
+      <c r="Y9" s="83" t="s">
         <v>31</v>
       </c>
-      <c r="Z9" s="86"/>
-      <c r="AA9" s="86"/>
-      <c r="AB9" s="86"/>
-      <c r="AC9" s="86"/>
-      <c r="AD9" s="86" t="s">
+      <c r="Z9" s="83"/>
+      <c r="AA9" s="83"/>
+      <c r="AB9" s="83"/>
+      <c r="AC9" s="83"/>
+      <c r="AD9" s="83" t="s">
         <v>32</v>
       </c>
-      <c r="AE9" s="86"/>
-      <c r="AF9" s="86"/>
-      <c r="AG9" s="86"/>
-      <c r="AH9" s="86"/>
+      <c r="AE9" s="83"/>
+      <c r="AF9" s="83"/>
+      <c r="AG9" s="83"/>
+      <c r="AH9" s="83"/>
       <c r="AI9" s="90"/>
       <c r="AJ9" s="91"/>
       <c r="AK9" s="91"/>
@@ -5522,172 +5537,172 @@
       <c r="A10" s="73"/>
       <c r="B10" s="73"/>
       <c r="C10" s="73"/>
-      <c r="D10" s="83" t="s">
+      <c r="D10" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="84"/>
-      <c r="F10" s="84"/>
-      <c r="G10" s="84"/>
-      <c r="H10" s="84"/>
-      <c r="I10" s="85"/>
-      <c r="J10" s="86"/>
-      <c r="K10" s="86"/>
-      <c r="L10" s="86"/>
-      <c r="M10" s="86"/>
-      <c r="N10" s="86"/>
-      <c r="O10" s="86"/>
-      <c r="P10" s="86"/>
-      <c r="Q10" s="86"/>
-      <c r="R10" s="86"/>
-      <c r="S10" s="86"/>
-      <c r="T10" s="86"/>
-      <c r="U10" s="86"/>
-      <c r="V10" s="86"/>
-      <c r="W10" s="86"/>
-      <c r="X10" s="86"/>
-      <c r="Y10" s="86"/>
-      <c r="Z10" s="86"/>
-      <c r="AA10" s="86"/>
-      <c r="AB10" s="86"/>
-      <c r="AC10" s="86"/>
-      <c r="AD10" s="86"/>
-      <c r="AE10" s="86"/>
-      <c r="AF10" s="86"/>
-      <c r="AG10" s="86"/>
-      <c r="AH10" s="86"/>
-      <c r="AI10" s="83"/>
-      <c r="AJ10" s="84"/>
-      <c r="AK10" s="84"/>
-      <c r="AL10" s="85"/>
+      <c r="E10" s="85"/>
+      <c r="F10" s="85"/>
+      <c r="G10" s="85"/>
+      <c r="H10" s="85"/>
+      <c r="I10" s="86"/>
+      <c r="J10" s="83"/>
+      <c r="K10" s="83"/>
+      <c r="L10" s="83"/>
+      <c r="M10" s="83"/>
+      <c r="N10" s="83"/>
+      <c r="O10" s="83"/>
+      <c r="P10" s="83"/>
+      <c r="Q10" s="83"/>
+      <c r="R10" s="83"/>
+      <c r="S10" s="83"/>
+      <c r="T10" s="83"/>
+      <c r="U10" s="83"/>
+      <c r="V10" s="83"/>
+      <c r="W10" s="83"/>
+      <c r="X10" s="83"/>
+      <c r="Y10" s="83"/>
+      <c r="Z10" s="83"/>
+      <c r="AA10" s="83"/>
+      <c r="AB10" s="83"/>
+      <c r="AC10" s="83"/>
+      <c r="AD10" s="83"/>
+      <c r="AE10" s="83"/>
+      <c r="AF10" s="83"/>
+      <c r="AG10" s="83"/>
+      <c r="AH10" s="83"/>
+      <c r="AI10" s="84"/>
+      <c r="AJ10" s="85"/>
+      <c r="AK10" s="85"/>
+      <c r="AL10" s="86"/>
       <c r="AM10" s="21"/>
     </row>
     <row r="11" spans="1:39" ht="15" customHeight="1">
       <c r="A11" s="73"/>
       <c r="B11" s="73"/>
       <c r="C11" s="73"/>
-      <c r="D11" s="83" t="s">
+      <c r="D11" s="84" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="84"/>
-      <c r="F11" s="84"/>
-      <c r="G11" s="84"/>
-      <c r="H11" s="84"/>
-      <c r="I11" s="85"/>
-      <c r="J11" s="86"/>
-      <c r="K11" s="86"/>
-      <c r="L11" s="86"/>
-      <c r="M11" s="86"/>
-      <c r="N11" s="86"/>
-      <c r="O11" s="86"/>
-      <c r="P11" s="86"/>
-      <c r="Q11" s="86"/>
-      <c r="R11" s="86"/>
-      <c r="S11" s="86"/>
-      <c r="T11" s="86"/>
-      <c r="U11" s="86"/>
-      <c r="V11" s="86"/>
-      <c r="W11" s="86"/>
-      <c r="X11" s="86"/>
-      <c r="Y11" s="86"/>
-      <c r="Z11" s="86"/>
-      <c r="AA11" s="86"/>
-      <c r="AB11" s="86"/>
-      <c r="AC11" s="86"/>
-      <c r="AD11" s="86"/>
-      <c r="AE11" s="86"/>
-      <c r="AF11" s="86"/>
-      <c r="AG11" s="86"/>
-      <c r="AH11" s="86"/>
-      <c r="AI11" s="83"/>
-      <c r="AJ11" s="84"/>
-      <c r="AK11" s="84"/>
-      <c r="AL11" s="85"/>
+      <c r="E11" s="85"/>
+      <c r="F11" s="85"/>
+      <c r="G11" s="85"/>
+      <c r="H11" s="85"/>
+      <c r="I11" s="86"/>
+      <c r="J11" s="83"/>
+      <c r="K11" s="83"/>
+      <c r="L11" s="83"/>
+      <c r="M11" s="83"/>
+      <c r="N11" s="83"/>
+      <c r="O11" s="83"/>
+      <c r="P11" s="83"/>
+      <c r="Q11" s="83"/>
+      <c r="R11" s="83"/>
+      <c r="S11" s="83"/>
+      <c r="T11" s="83"/>
+      <c r="U11" s="83"/>
+      <c r="V11" s="83"/>
+      <c r="W11" s="83"/>
+      <c r="X11" s="83"/>
+      <c r="Y11" s="83"/>
+      <c r="Z11" s="83"/>
+      <c r="AA11" s="83"/>
+      <c r="AB11" s="83"/>
+      <c r="AC11" s="83"/>
+      <c r="AD11" s="83"/>
+      <c r="AE11" s="83"/>
+      <c r="AF11" s="83"/>
+      <c r="AG11" s="83"/>
+      <c r="AH11" s="83"/>
+      <c r="AI11" s="84"/>
+      <c r="AJ11" s="85"/>
+      <c r="AK11" s="85"/>
+      <c r="AL11" s="86"/>
       <c r="AM11" s="21"/>
     </row>
     <row r="12" spans="1:39" ht="15" customHeight="1">
       <c r="A12" s="73"/>
       <c r="B12" s="73"/>
       <c r="C12" s="73"/>
-      <c r="D12" s="83" t="s">
+      <c r="D12" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="84"/>
-      <c r="F12" s="84"/>
-      <c r="G12" s="84"/>
-      <c r="H12" s="84"/>
-      <c r="I12" s="85"/>
-      <c r="J12" s="86"/>
-      <c r="K12" s="86"/>
-      <c r="L12" s="86"/>
-      <c r="M12" s="86"/>
-      <c r="N12" s="86"/>
-      <c r="O12" s="86"/>
-      <c r="P12" s="86"/>
-      <c r="Q12" s="86"/>
-      <c r="R12" s="86"/>
-      <c r="S12" s="86"/>
-      <c r="T12" s="86"/>
-      <c r="U12" s="86"/>
-      <c r="V12" s="86"/>
-      <c r="W12" s="86"/>
-      <c r="X12" s="86"/>
-      <c r="Y12" s="86"/>
-      <c r="Z12" s="86"/>
-      <c r="AA12" s="86"/>
-      <c r="AB12" s="86"/>
-      <c r="AC12" s="86"/>
-      <c r="AD12" s="86"/>
-      <c r="AE12" s="86"/>
-      <c r="AF12" s="86"/>
-      <c r="AG12" s="86"/>
-      <c r="AH12" s="86"/>
-      <c r="AI12" s="83"/>
-      <c r="AJ12" s="84"/>
-      <c r="AK12" s="84"/>
-      <c r="AL12" s="85"/>
+      <c r="E12" s="85"/>
+      <c r="F12" s="85"/>
+      <c r="G12" s="85"/>
+      <c r="H12" s="85"/>
+      <c r="I12" s="86"/>
+      <c r="J12" s="83"/>
+      <c r="K12" s="83"/>
+      <c r="L12" s="83"/>
+      <c r="M12" s="83"/>
+      <c r="N12" s="83"/>
+      <c r="O12" s="83"/>
+      <c r="P12" s="83"/>
+      <c r="Q12" s="83"/>
+      <c r="R12" s="83"/>
+      <c r="S12" s="83"/>
+      <c r="T12" s="83"/>
+      <c r="U12" s="83"/>
+      <c r="V12" s="83"/>
+      <c r="W12" s="83"/>
+      <c r="X12" s="83"/>
+      <c r="Y12" s="83"/>
+      <c r="Z12" s="83"/>
+      <c r="AA12" s="83"/>
+      <c r="AB12" s="83"/>
+      <c r="AC12" s="83"/>
+      <c r="AD12" s="83"/>
+      <c r="AE12" s="83"/>
+      <c r="AF12" s="83"/>
+      <c r="AG12" s="83"/>
+      <c r="AH12" s="83"/>
+      <c r="AI12" s="84"/>
+      <c r="AJ12" s="85"/>
+      <c r="AK12" s="85"/>
+      <c r="AL12" s="86"/>
       <c r="AM12" s="21"/>
     </row>
     <row r="13" spans="1:39" ht="15" customHeight="1">
       <c r="A13" s="73"/>
       <c r="B13" s="73"/>
       <c r="C13" s="73"/>
-      <c r="D13" s="83" t="s">
+      <c r="D13" s="84" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="84"/>
-      <c r="F13" s="84"/>
-      <c r="G13" s="84"/>
-      <c r="H13" s="84"/>
-      <c r="I13" s="85"/>
-      <c r="J13" s="86"/>
-      <c r="K13" s="86"/>
-      <c r="L13" s="86"/>
-      <c r="M13" s="86"/>
-      <c r="N13" s="86"/>
-      <c r="O13" s="86"/>
-      <c r="P13" s="86"/>
-      <c r="Q13" s="86"/>
-      <c r="R13" s="86"/>
-      <c r="S13" s="86"/>
-      <c r="T13" s="86"/>
-      <c r="U13" s="86"/>
-      <c r="V13" s="86"/>
-      <c r="W13" s="86"/>
-      <c r="X13" s="86"/>
-      <c r="Y13" s="86"/>
-      <c r="Z13" s="86"/>
-      <c r="AA13" s="86"/>
-      <c r="AB13" s="86"/>
-      <c r="AC13" s="86"/>
-      <c r="AD13" s="86"/>
-      <c r="AE13" s="86"/>
-      <c r="AF13" s="86"/>
-      <c r="AG13" s="86"/>
-      <c r="AH13" s="86"/>
-      <c r="AI13" s="83"/>
-      <c r="AJ13" s="84"/>
-      <c r="AK13" s="84"/>
-      <c r="AL13" s="85"/>
+      <c r="E13" s="85"/>
+      <c r="F13" s="85"/>
+      <c r="G13" s="85"/>
+      <c r="H13" s="85"/>
+      <c r="I13" s="86"/>
+      <c r="J13" s="83"/>
+      <c r="K13" s="83"/>
+      <c r="L13" s="83"/>
+      <c r="M13" s="83"/>
+      <c r="N13" s="83"/>
+      <c r="O13" s="83"/>
+      <c r="P13" s="83"/>
+      <c r="Q13" s="83"/>
+      <c r="R13" s="83"/>
+      <c r="S13" s="83"/>
+      <c r="T13" s="83"/>
+      <c r="U13" s="83"/>
+      <c r="V13" s="83"/>
+      <c r="W13" s="83"/>
+      <c r="X13" s="83"/>
+      <c r="Y13" s="83"/>
+      <c r="Z13" s="83"/>
+      <c r="AA13" s="83"/>
+      <c r="AB13" s="83"/>
+      <c r="AC13" s="83"/>
+      <c r="AD13" s="83"/>
+      <c r="AE13" s="83"/>
+      <c r="AF13" s="83"/>
+      <c r="AG13" s="83"/>
+      <c r="AH13" s="83"/>
+      <c r="AI13" s="84"/>
+      <c r="AJ13" s="85"/>
+      <c r="AK13" s="85"/>
+      <c r="AL13" s="86"/>
       <c r="AM13" s="21"/>
     </row>
     <row r="14" spans="1:39" ht="15" customHeight="1">
@@ -6349,8 +6364,8 @@
       <c r="AL30" s="7"/>
       <c r="AM30" s="7"/>
     </row>
-    <row r="31" spans="1:40" ht="13.9" customHeight="1"/>
-    <row r="32" spans="1:40" ht="13.9" customHeight="1">
+    <row r="31" spans="1:40" ht="13.95" customHeight="1"/>
+    <row r="32" spans="1:40" ht="13.95" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
@@ -6366,7 +6381,7 @@
       <c r="M32" s="15"/>
       <c r="N32" s="15"/>
     </row>
-    <row r="33" spans="1:14" ht="13.9" customHeight="1">
+    <row r="33" spans="1:14" ht="13.95" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
@@ -6399,15 +6414,24 @@
       <c r="N34" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="40">
-    <mergeCell ref="AD11:AH11"/>
-    <mergeCell ref="O12:S12"/>
-    <mergeCell ref="AI13:AL13"/>
-    <mergeCell ref="Y12:AC12"/>
-    <mergeCell ref="AD12:AH12"/>
-    <mergeCell ref="O11:S11"/>
-    <mergeCell ref="T11:X11"/>
-    <mergeCell ref="Y11:AC11"/>
+  <mergeCells count="41">
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="D13:I13"/>
+    <mergeCell ref="J8:AH8"/>
+    <mergeCell ref="O13:S13"/>
+    <mergeCell ref="T13:X13"/>
+    <mergeCell ref="A8:I9"/>
+    <mergeCell ref="A10:C11"/>
+    <mergeCell ref="A12:C13"/>
+    <mergeCell ref="J10:N10"/>
+    <mergeCell ref="J13:N13"/>
+    <mergeCell ref="J11:N11"/>
+    <mergeCell ref="Y13:AC13"/>
+    <mergeCell ref="AD13:AH13"/>
+    <mergeCell ref="J9:N9"/>
+    <mergeCell ref="O9:S9"/>
+    <mergeCell ref="T9:X9"/>
+    <mergeCell ref="Y9:AC9"/>
     <mergeCell ref="M1:AL1"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="AI10:AL10"/>
@@ -6424,22 +6448,14 @@
     <mergeCell ref="T10:X10"/>
     <mergeCell ref="Y10:AC10"/>
     <mergeCell ref="AD10:AH10"/>
-    <mergeCell ref="D13:I13"/>
-    <mergeCell ref="J8:AH8"/>
-    <mergeCell ref="O13:S13"/>
-    <mergeCell ref="T13:X13"/>
-    <mergeCell ref="A8:I9"/>
-    <mergeCell ref="A10:C11"/>
-    <mergeCell ref="A12:C13"/>
-    <mergeCell ref="J10:N10"/>
-    <mergeCell ref="J13:N13"/>
-    <mergeCell ref="J11:N11"/>
-    <mergeCell ref="Y13:AC13"/>
-    <mergeCell ref="AD13:AH13"/>
-    <mergeCell ref="J9:N9"/>
-    <mergeCell ref="O9:S9"/>
-    <mergeCell ref="T9:X9"/>
-    <mergeCell ref="Y9:AC9"/>
+    <mergeCell ref="AD11:AH11"/>
+    <mergeCell ref="O12:S12"/>
+    <mergeCell ref="AI13:AL13"/>
+    <mergeCell ref="Y12:AC12"/>
+    <mergeCell ref="AD12:AH12"/>
+    <mergeCell ref="O11:S11"/>
+    <mergeCell ref="T11:X11"/>
+    <mergeCell ref="Y11:AC11"/>
   </mergeCells>
   <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -6459,12 +6475,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ACC2EF5-C6BB-4CA4-98B8-CD887DC0BA25}">
   <dimension ref="A1:AM37"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.15"/>
   <cols>
-    <col min="1" max="7" width="2.375" customWidth="1"/>
+    <col min="1" max="7" width="2.35546875" customWidth="1"/>
     <col min="8" max="8" width="2" customWidth="1"/>
-    <col min="9" max="31" width="2.125" customWidth="1"/>
-    <col min="32" max="39" width="2.375" customWidth="1"/>
+    <col min="9" max="31" width="2.140625" customWidth="1"/>
+    <col min="32" max="39" width="2.35546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="15" customHeight="1">
@@ -6479,32 +6495,32 @@
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
-      <c r="M1" s="72"/>
-      <c r="N1" s="72"/>
-      <c r="O1" s="72"/>
-      <c r="P1" s="72"/>
-      <c r="Q1" s="72"/>
-      <c r="R1" s="72"/>
-      <c r="S1" s="72"/>
-      <c r="T1" s="72"/>
-      <c r="U1" s="72"/>
-      <c r="V1" s="72"/>
-      <c r="W1" s="72"/>
-      <c r="X1" s="72"/>
-      <c r="Y1" s="72"/>
-      <c r="Z1" s="72"/>
-      <c r="AA1" s="72"/>
-      <c r="AB1" s="72"/>
-      <c r="AC1" s="72"/>
-      <c r="AD1" s="72"/>
-      <c r="AE1" s="72"/>
-      <c r="AF1" s="72"/>
-      <c r="AG1" s="72"/>
-      <c r="AH1" s="72"/>
-      <c r="AI1" s="72"/>
-      <c r="AJ1" s="72"/>
-      <c r="AK1" s="72"/>
-      <c r="AL1" s="72"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="78"/>
+      <c r="AG1" s="78"/>
+      <c r="AH1" s="78"/>
+      <c r="AI1" s="78"/>
+      <c r="AJ1" s="78"/>
+      <c r="AK1" s="78"/>
+      <c r="AL1" s="78"/>
       <c r="AM1" s="33"/>
     </row>
     <row r="2" spans="1:39" ht="15" customHeight="1">
@@ -6540,17 +6556,17 @@
       <c r="AF2" s="3"/>
     </row>
     <row r="3" spans="1:39" ht="15" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
       <c r="L3" s="20"/>
       <c r="M3" s="20"/>
       <c r="N3" s="45" t="s">
@@ -7716,8 +7732,8 @@
       <c r="AL33" s="7"/>
       <c r="AM33" s="7"/>
     </row>
-    <row r="34" spans="1:39" ht="13.9" customHeight="1"/>
-    <row r="35" spans="1:39" ht="13.9" customHeight="1">
+    <row r="34" spans="1:39" ht="13.95" customHeight="1"/>
+    <row r="35" spans="1:39" ht="13.95" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
@@ -7733,7 +7749,7 @@
       <c r="M35" s="15"/>
       <c r="N35" s="15"/>
     </row>
-    <row r="36" spans="1:39" ht="13.9" customHeight="1">
+    <row r="36" spans="1:39" ht="13.95" customHeight="1">
       <c r="A36" s="10"/>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
@@ -7790,12 +7806,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05ADACB2-95B1-43B0-BEDC-E6A99EE22ABB}">
   <dimension ref="A1:AM68"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.15"/>
   <cols>
-    <col min="1" max="7" width="2.375" customWidth="1"/>
+    <col min="1" max="7" width="2.35546875" customWidth="1"/>
     <col min="8" max="8" width="2" customWidth="1"/>
-    <col min="9" max="31" width="2.125" customWidth="1"/>
-    <col min="32" max="39" width="2.375" customWidth="1"/>
+    <col min="9" max="31" width="2.140625" customWidth="1"/>
+    <col min="32" max="39" width="2.35546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="15" customHeight="1">
@@ -7810,32 +7826,32 @@
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
-      <c r="M1" s="72"/>
-      <c r="N1" s="72"/>
-      <c r="O1" s="72"/>
-      <c r="P1" s="72"/>
-      <c r="Q1" s="72"/>
-      <c r="R1" s="72"/>
-      <c r="S1" s="72"/>
-      <c r="T1" s="72"/>
-      <c r="U1" s="72"/>
-      <c r="V1" s="72"/>
-      <c r="W1" s="72"/>
-      <c r="X1" s="72"/>
-      <c r="Y1" s="72"/>
-      <c r="Z1" s="72"/>
-      <c r="AA1" s="72"/>
-      <c r="AB1" s="72"/>
-      <c r="AC1" s="72"/>
-      <c r="AD1" s="72"/>
-      <c r="AE1" s="72"/>
-      <c r="AF1" s="72"/>
-      <c r="AG1" s="72"/>
-      <c r="AH1" s="72"/>
-      <c r="AI1" s="72"/>
-      <c r="AJ1" s="72"/>
-      <c r="AK1" s="72"/>
-      <c r="AL1" s="72"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="78"/>
+      <c r="AG1" s="78"/>
+      <c r="AH1" s="78"/>
+      <c r="AI1" s="78"/>
+      <c r="AJ1" s="78"/>
+      <c r="AK1" s="78"/>
+      <c r="AL1" s="78"/>
       <c r="AM1" s="33"/>
     </row>
     <row r="2" spans="1:39" ht="15" customHeight="1">
@@ -7871,17 +7887,17 @@
       <c r="AF2" s="3"/>
     </row>
     <row r="3" spans="1:39" ht="15" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
       <c r="L3" s="20"/>
       <c r="M3" s="20"/>
       <c r="N3" s="16" t="s">
@@ -7906,7 +7922,7 @@
       <c r="AE3" s="3"/>
       <c r="AF3" s="3"/>
     </row>
-    <row r="4" spans="1:39" ht="5.85" customHeight="1">
+    <row r="4" spans="1:39" ht="5.9" customHeight="1">
       <c r="A4" s="5"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -7937,7 +7953,7 @@
       <c r="AE4" s="3"/>
       <c r="AF4" s="3"/>
     </row>
-    <row r="5" spans="1:39" ht="14.1" customHeight="1">
+    <row r="5" spans="1:39" ht="14.15" customHeight="1">
       <c r="A5" s="94" t="s">
         <v>171</v>
       </c>
@@ -7973,7 +7989,7 @@
       <c r="AE5" s="3"/>
       <c r="AF5" s="3"/>
     </row>
-    <row r="6" spans="1:39" ht="5.85" customHeight="1">
+    <row r="6" spans="1:39" ht="5.9" customHeight="1">
       <c r="A6" s="5"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -8040,7 +8056,7 @@
       <c r="AE7" s="3"/>
       <c r="AF7" s="3"/>
     </row>
-    <row r="8" spans="1:39" ht="5.85" customHeight="1">
+    <row r="8" spans="1:39" ht="5.9" customHeight="1">
       <c r="A8" s="21"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
@@ -8230,7 +8246,7 @@
       <c r="AL12" s="14"/>
       <c r="AM12" s="14"/>
     </row>
-    <row r="13" spans="1:39" ht="5.85" customHeight="1">
+    <row r="13" spans="1:39" ht="5.9" customHeight="1">
       <c r="A13" s="46"/>
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
@@ -8492,7 +8508,7 @@
       <c r="AL18" s="14"/>
       <c r="AM18" s="14"/>
     </row>
-    <row r="19" spans="1:39" ht="5.85" customHeight="1">
+    <row r="19" spans="1:39" ht="5.9" customHeight="1">
       <c r="A19" s="46"/>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
@@ -8711,7 +8727,7 @@
       <c r="AL23" s="14"/>
       <c r="AM23" s="14"/>
     </row>
-    <row r="24" spans="1:39" ht="5.85" customHeight="1">
+    <row r="24" spans="1:39" ht="5.9" customHeight="1">
       <c r="A24" s="46"/>
       <c r="B24" s="14"/>
       <c r="C24" s="14"/>
@@ -8930,7 +8946,7 @@
       <c r="AL28" s="14"/>
       <c r="AM28" s="14"/>
     </row>
-    <row r="29" spans="1:39" ht="5.85" customHeight="1">
+    <row r="29" spans="1:39" ht="5.9" customHeight="1">
       <c r="A29" s="21"/>
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
@@ -9061,7 +9077,7 @@
       <c r="AL31" s="14"/>
       <c r="AM31" s="14"/>
     </row>
-    <row r="32" spans="1:39" ht="8.4499999999999993" customHeight="1">
+    <row r="32" spans="1:39" ht="8.5" customHeight="1">
       <c r="A32" s="21"/>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
@@ -9293,7 +9309,7 @@
       <c r="AE37" s="3"/>
       <c r="AF37" s="3"/>
     </row>
-    <row r="38" spans="1:39" ht="5.85" customHeight="1">
+    <row r="38" spans="1:39" ht="5.9" customHeight="1">
       <c r="A38" s="25"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
@@ -9429,7 +9445,7 @@
       <c r="AE41" s="3"/>
       <c r="AF41" s="3"/>
     </row>
-    <row r="42" spans="1:39" ht="5.85" customHeight="1">
+    <row r="42" spans="1:39" ht="5.9" customHeight="1">
       <c r="A42" s="46"/>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
@@ -9594,7 +9610,7 @@
       <c r="AE46" s="3"/>
       <c r="AF46" s="3"/>
     </row>
-    <row r="47" spans="1:39" ht="5.85" customHeight="1">
+    <row r="47" spans="1:39" ht="5.9" customHeight="1">
       <c r="A47" s="46"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
@@ -9796,7 +9812,7 @@
       <c r="AE52" s="3"/>
       <c r="AF52" s="3"/>
     </row>
-    <row r="53" spans="1:39" ht="5.85" customHeight="1">
+    <row r="53" spans="1:39" ht="5.9" customHeight="1">
       <c r="A53" s="25"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
@@ -9827,7 +9843,7 @@
       <c r="AE53" s="3"/>
       <c r="AF53" s="3"/>
     </row>
-    <row r="54" spans="1:39" ht="14.1" customHeight="1">
+    <row r="54" spans="1:39" ht="14.15" customHeight="1">
       <c r="A54" s="46" t="s">
         <v>106</v>
       </c>
@@ -9862,7 +9878,7 @@
       <c r="AE54" s="3"/>
       <c r="AF54" s="3"/>
     </row>
-    <row r="55" spans="1:39" ht="14.1" customHeight="1">
+    <row r="55" spans="1:39" ht="14.15" customHeight="1">
       <c r="A55" s="46" t="s">
         <v>109</v>
       </c>
@@ -9897,7 +9913,7 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
     </row>
-    <row r="56" spans="1:39" ht="14.1" customHeight="1">
+    <row r="56" spans="1:39" ht="14.15" customHeight="1">
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
       <c r="G56" s="3"/>
@@ -9929,7 +9945,7 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
     </row>
-    <row r="57" spans="1:39" ht="14.1" customHeight="1">
+    <row r="57" spans="1:39" ht="14.15" customHeight="1">
       <c r="A57" s="25"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
@@ -9962,7 +9978,7 @@
       <c r="AE57" s="3"/>
       <c r="AF57" s="3"/>
     </row>
-    <row r="58" spans="1:39" ht="5.85" customHeight="1">
+    <row r="58" spans="1:39" ht="5.9" customHeight="1">
       <c r="A58" s="25"/>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
@@ -10221,8 +10237,8 @@
       <c r="AL64" s="7"/>
       <c r="AM64" s="7"/>
     </row>
-    <row r="65" spans="1:14" ht="13.9" customHeight="1"/>
-    <row r="66" spans="1:14" ht="13.9" customHeight="1">
+    <row r="65" spans="1:14" ht="13.95" customHeight="1"/>
+    <row r="66" spans="1:14" ht="13.95" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="15"/>
       <c r="C66" s="15"/>
@@ -10238,7 +10254,7 @@
       <c r="M66" s="15"/>
       <c r="N66" s="15"/>
     </row>
-    <row r="67" spans="1:14" ht="13.9" customHeight="1">
+    <row r="67" spans="1:14" ht="13.95" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="7"/>
       <c r="C67" s="7"/>
@@ -10295,12 +10311,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{309B97D2-0661-4F44-8203-7296258BC5D2}">
   <dimension ref="A1:AM60"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.15"/>
   <cols>
-    <col min="1" max="7" width="2.375" customWidth="1"/>
+    <col min="1" max="7" width="2.35546875" customWidth="1"/>
     <col min="8" max="8" width="2" customWidth="1"/>
-    <col min="9" max="31" width="2.125" customWidth="1"/>
-    <col min="32" max="39" width="2.375" customWidth="1"/>
+    <col min="9" max="31" width="2.140625" customWidth="1"/>
+    <col min="32" max="39" width="2.35546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="15" customHeight="1">
@@ -10315,60 +10331,60 @@
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
-      <c r="M1" s="72"/>
-      <c r="N1" s="72"/>
-      <c r="O1" s="72"/>
-      <c r="P1" s="72"/>
-      <c r="Q1" s="72"/>
-      <c r="R1" s="72"/>
-      <c r="S1" s="72"/>
-      <c r="T1" s="72"/>
-      <c r="U1" s="72"/>
-      <c r="V1" s="72"/>
-      <c r="W1" s="72"/>
-      <c r="X1" s="72"/>
-      <c r="Y1" s="72"/>
-      <c r="Z1" s="72"/>
-      <c r="AA1" s="72"/>
-      <c r="AB1" s="72"/>
-      <c r="AC1" s="72"/>
-      <c r="AD1" s="72"/>
-      <c r="AE1" s="72"/>
-      <c r="AF1" s="72"/>
-      <c r="AG1" s="72"/>
-      <c r="AH1" s="72"/>
-      <c r="AI1" s="72"/>
-      <c r="AJ1" s="72"/>
-      <c r="AK1" s="72"/>
-      <c r="AL1" s="72"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="78"/>
+      <c r="AG1" s="78"/>
+      <c r="AH1" s="78"/>
+      <c r="AI1" s="78"/>
+      <c r="AJ1" s="78"/>
+      <c r="AK1" s="78"/>
+      <c r="AL1" s="78"/>
       <c r="AM1" s="33"/>
     </row>
     <row r="2" spans="1:39" ht="15" customHeight="1">
-      <c r="A2" s="98" t="s">
+      <c r="A2" s="101" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="98"/>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
-      <c r="O2" s="98"/>
-      <c r="P2" s="98"/>
-      <c r="Q2" s="98"/>
-      <c r="R2" s="98"/>
-      <c r="S2" s="98"/>
-      <c r="T2" s="98"/>
-      <c r="U2" s="98"/>
-      <c r="V2" s="98"/>
-      <c r="W2" s="98"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="101"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="101"/>
+      <c r="L2" s="101"/>
+      <c r="M2" s="101"/>
+      <c r="N2" s="101"/>
+      <c r="O2" s="101"/>
+      <c r="P2" s="101"/>
+      <c r="Q2" s="101"/>
+      <c r="R2" s="101"/>
+      <c r="S2" s="101"/>
+      <c r="T2" s="101"/>
+      <c r="U2" s="101"/>
+      <c r="V2" s="101"/>
+      <c r="W2" s="101"/>
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
@@ -10415,7 +10431,7 @@
       <c r="AE3" s="3"/>
       <c r="AF3" s="3"/>
     </row>
-    <row r="4" spans="1:39" ht="8.4499999999999993" customHeight="1">
+    <row r="4" spans="1:39" ht="8.5" customHeight="1">
       <c r="A4" s="48"/>
       <c r="B4" s="46"/>
       <c r="C4" s="46"/>
@@ -10485,7 +10501,7 @@
       <c r="AE5" s="3"/>
       <c r="AF5" s="3"/>
     </row>
-    <row r="6" spans="1:39" ht="8.4499999999999993" customHeight="1">
+    <row r="6" spans="1:39" ht="8.5" customHeight="1">
       <c r="A6" s="5"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -10517,229 +10533,229 @@
       <c r="AF6" s="3"/>
     </row>
     <row r="7" spans="1:39" ht="15" customHeight="1">
-      <c r="A7" s="86"/>
-      <c r="B7" s="86"/>
-      <c r="C7" s="86"/>
-      <c r="D7" s="86"/>
-      <c r="E7" s="86"/>
-      <c r="F7" s="86"/>
-      <c r="G7" s="86"/>
-      <c r="H7" s="86"/>
-      <c r="I7" s="86"/>
-      <c r="J7" s="86"/>
-      <c r="K7" s="86"/>
-      <c r="L7" s="86"/>
-      <c r="M7" s="96" t="s">
+      <c r="A7" s="83"/>
+      <c r="B7" s="83"/>
+      <c r="C7" s="83"/>
+      <c r="D7" s="83"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="83"/>
+      <c r="H7" s="83"/>
+      <c r="I7" s="83"/>
+      <c r="J7" s="83"/>
+      <c r="K7" s="83"/>
+      <c r="L7" s="83"/>
+      <c r="M7" s="98" t="s">
         <v>115</v>
       </c>
-      <c r="N7" s="97"/>
-      <c r="O7" s="97"/>
-      <c r="P7" s="97"/>
-      <c r="Q7" s="97"/>
-      <c r="R7" s="97"/>
-      <c r="S7" s="97"/>
-      <c r="T7" s="97"/>
-      <c r="U7" s="97"/>
-      <c r="V7" s="96" t="s">
+      <c r="N7" s="99"/>
+      <c r="O7" s="99"/>
+      <c r="P7" s="99"/>
+      <c r="Q7" s="99"/>
+      <c r="R7" s="99"/>
+      <c r="S7" s="99"/>
+      <c r="T7" s="99"/>
+      <c r="U7" s="99"/>
+      <c r="V7" s="98" t="s">
         <v>116</v>
       </c>
-      <c r="W7" s="97"/>
-      <c r="X7" s="97"/>
-      <c r="Y7" s="97"/>
-      <c r="Z7" s="97"/>
-      <c r="AA7" s="97"/>
-      <c r="AB7" s="97"/>
-      <c r="AC7" s="97"/>
-      <c r="AD7" s="97"/>
-      <c r="AE7" s="96" t="s">
+      <c r="W7" s="99"/>
+      <c r="X7" s="99"/>
+      <c r="Y7" s="99"/>
+      <c r="Z7" s="99"/>
+      <c r="AA7" s="99"/>
+      <c r="AB7" s="99"/>
+      <c r="AC7" s="99"/>
+      <c r="AD7" s="99"/>
+      <c r="AE7" s="98" t="s">
         <v>117</v>
       </c>
-      <c r="AF7" s="97"/>
-      <c r="AG7" s="97"/>
-      <c r="AH7" s="97"/>
-      <c r="AI7" s="97"/>
-      <c r="AJ7" s="97"/>
-      <c r="AK7" s="97"/>
-      <c r="AL7" s="97"/>
-      <c r="AM7" s="97"/>
+      <c r="AF7" s="99"/>
+      <c r="AG7" s="99"/>
+      <c r="AH7" s="99"/>
+      <c r="AI7" s="99"/>
+      <c r="AJ7" s="99"/>
+      <c r="AK7" s="99"/>
+      <c r="AL7" s="99"/>
+      <c r="AM7" s="99"/>
     </row>
     <row r="8" spans="1:39" ht="15" customHeight="1">
-      <c r="A8" s="86"/>
-      <c r="B8" s="86"/>
-      <c r="C8" s="86"/>
-      <c r="D8" s="86"/>
-      <c r="E8" s="86"/>
-      <c r="F8" s="86"/>
-      <c r="G8" s="86"/>
-      <c r="H8" s="86"/>
-      <c r="I8" s="86"/>
-      <c r="J8" s="86"/>
-      <c r="K8" s="86"/>
-      <c r="L8" s="86"/>
-      <c r="M8" s="96" t="s">
+      <c r="A8" s="83"/>
+      <c r="B8" s="83"/>
+      <c r="C8" s="83"/>
+      <c r="D8" s="83"/>
+      <c r="E8" s="83"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="83"/>
+      <c r="I8" s="83"/>
+      <c r="J8" s="83"/>
+      <c r="K8" s="83"/>
+      <c r="L8" s="83"/>
+      <c r="M8" s="98" t="s">
         <v>118</v>
       </c>
-      <c r="N8" s="97"/>
-      <c r="O8" s="97"/>
-      <c r="P8" s="97"/>
-      <c r="Q8" s="97"/>
-      <c r="R8" s="97"/>
-      <c r="S8" s="97"/>
-      <c r="T8" s="97"/>
-      <c r="U8" s="97"/>
-      <c r="V8" s="96" t="s">
+      <c r="N8" s="99"/>
+      <c r="O8" s="99"/>
+      <c r="P8" s="99"/>
+      <c r="Q8" s="99"/>
+      <c r="R8" s="99"/>
+      <c r="S8" s="99"/>
+      <c r="T8" s="99"/>
+      <c r="U8" s="99"/>
+      <c r="V8" s="98" t="s">
         <v>119</v>
       </c>
-      <c r="W8" s="97"/>
-      <c r="X8" s="97"/>
-      <c r="Y8" s="97"/>
-      <c r="Z8" s="97"/>
-      <c r="AA8" s="97"/>
-      <c r="AB8" s="97"/>
-      <c r="AC8" s="97"/>
-      <c r="AD8" s="97"/>
-      <c r="AE8" s="96" t="s">
+      <c r="W8" s="99"/>
+      <c r="X8" s="99"/>
+      <c r="Y8" s="99"/>
+      <c r="Z8" s="99"/>
+      <c r="AA8" s="99"/>
+      <c r="AB8" s="99"/>
+      <c r="AC8" s="99"/>
+      <c r="AD8" s="99"/>
+      <c r="AE8" s="98" t="s">
         <v>120</v>
       </c>
-      <c r="AF8" s="97"/>
-      <c r="AG8" s="97"/>
-      <c r="AH8" s="97"/>
-      <c r="AI8" s="97"/>
-      <c r="AJ8" s="97"/>
-      <c r="AK8" s="97"/>
-      <c r="AL8" s="97"/>
-      <c r="AM8" s="97"/>
+      <c r="AF8" s="99"/>
+      <c r="AG8" s="99"/>
+      <c r="AH8" s="99"/>
+      <c r="AI8" s="99"/>
+      <c r="AJ8" s="99"/>
+      <c r="AK8" s="99"/>
+      <c r="AL8" s="99"/>
+      <c r="AM8" s="99"/>
     </row>
     <row r="9" spans="1:39" ht="15" customHeight="1">
-      <c r="A9" s="95" t="s">
+      <c r="A9" s="100" t="s">
         <v>113</v>
       </c>
-      <c r="B9" s="95"/>
-      <c r="C9" s="95"/>
-      <c r="D9" s="95"/>
-      <c r="E9" s="95"/>
-      <c r="F9" s="95"/>
-      <c r="G9" s="95"/>
-      <c r="H9" s="95"/>
-      <c r="I9" s="95"/>
-      <c r="J9" s="95"/>
-      <c r="K9" s="95"/>
-      <c r="L9" s="95"/>
-      <c r="M9" s="97"/>
-      <c r="N9" s="97"/>
-      <c r="O9" s="97"/>
-      <c r="P9" s="97"/>
-      <c r="Q9" s="97"/>
-      <c r="R9" s="97"/>
-      <c r="S9" s="97"/>
-      <c r="T9" s="97"/>
-      <c r="U9" s="97"/>
-      <c r="V9" s="97"/>
-      <c r="W9" s="97"/>
-      <c r="X9" s="97"/>
-      <c r="Y9" s="97"/>
-      <c r="Z9" s="97"/>
-      <c r="AA9" s="97"/>
-      <c r="AB9" s="97"/>
-      <c r="AC9" s="97"/>
-      <c r="AD9" s="97"/>
-      <c r="AE9" s="97"/>
-      <c r="AF9" s="97"/>
-      <c r="AG9" s="97"/>
-      <c r="AH9" s="97"/>
-      <c r="AI9" s="97"/>
-      <c r="AJ9" s="97"/>
-      <c r="AK9" s="97"/>
-      <c r="AL9" s="97"/>
-      <c r="AM9" s="97"/>
+      <c r="B9" s="100"/>
+      <c r="C9" s="100"/>
+      <c r="D9" s="100"/>
+      <c r="E9" s="100"/>
+      <c r="F9" s="100"/>
+      <c r="G9" s="100"/>
+      <c r="H9" s="100"/>
+      <c r="I9" s="100"/>
+      <c r="J9" s="100"/>
+      <c r="K9" s="100"/>
+      <c r="L9" s="100"/>
+      <c r="M9" s="99"/>
+      <c r="N9" s="99"/>
+      <c r="O9" s="99"/>
+      <c r="P9" s="99"/>
+      <c r="Q9" s="99"/>
+      <c r="R9" s="99"/>
+      <c r="S9" s="99"/>
+      <c r="T9" s="99"/>
+      <c r="U9" s="99"/>
+      <c r="V9" s="99"/>
+      <c r="W9" s="99"/>
+      <c r="X9" s="99"/>
+      <c r="Y9" s="99"/>
+      <c r="Z9" s="99"/>
+      <c r="AA9" s="99"/>
+      <c r="AB9" s="99"/>
+      <c r="AC9" s="99"/>
+      <c r="AD9" s="99"/>
+      <c r="AE9" s="99"/>
+      <c r="AF9" s="99"/>
+      <c r="AG9" s="99"/>
+      <c r="AH9" s="99"/>
+      <c r="AI9" s="99"/>
+      <c r="AJ9" s="99"/>
+      <c r="AK9" s="99"/>
+      <c r="AL9" s="99"/>
+      <c r="AM9" s="99"/>
     </row>
     <row r="10" spans="1:39" ht="15" customHeight="1">
-      <c r="A10" s="95" t="s">
+      <c r="A10" s="100" t="s">
         <v>112</v>
       </c>
-      <c r="B10" s="95"/>
-      <c r="C10" s="95"/>
-      <c r="D10" s="95"/>
-      <c r="E10" s="95"/>
-      <c r="F10" s="95"/>
-      <c r="G10" s="95"/>
-      <c r="H10" s="95"/>
-      <c r="I10" s="95"/>
-      <c r="J10" s="95"/>
-      <c r="K10" s="95"/>
-      <c r="L10" s="95"/>
-      <c r="M10" s="97"/>
-      <c r="N10" s="97"/>
-      <c r="O10" s="97"/>
-      <c r="P10" s="97"/>
-      <c r="Q10" s="97"/>
-      <c r="R10" s="97"/>
-      <c r="S10" s="97"/>
-      <c r="T10" s="97"/>
-      <c r="U10" s="97"/>
-      <c r="V10" s="97"/>
-      <c r="W10" s="97"/>
-      <c r="X10" s="97"/>
-      <c r="Y10" s="97"/>
-      <c r="Z10" s="97"/>
-      <c r="AA10" s="97"/>
-      <c r="AB10" s="97"/>
-      <c r="AC10" s="97"/>
-      <c r="AD10" s="97"/>
-      <c r="AE10" s="97"/>
-      <c r="AF10" s="97"/>
-      <c r="AG10" s="97"/>
-      <c r="AH10" s="97"/>
-      <c r="AI10" s="97"/>
-      <c r="AJ10" s="97"/>
-      <c r="AK10" s="97"/>
-      <c r="AL10" s="97"/>
-      <c r="AM10" s="97"/>
+      <c r="B10" s="100"/>
+      <c r="C10" s="100"/>
+      <c r="D10" s="100"/>
+      <c r="E10" s="100"/>
+      <c r="F10" s="100"/>
+      <c r="G10" s="100"/>
+      <c r="H10" s="100"/>
+      <c r="I10" s="100"/>
+      <c r="J10" s="100"/>
+      <c r="K10" s="100"/>
+      <c r="L10" s="100"/>
+      <c r="M10" s="99"/>
+      <c r="N10" s="99"/>
+      <c r="O10" s="99"/>
+      <c r="P10" s="99"/>
+      <c r="Q10" s="99"/>
+      <c r="R10" s="99"/>
+      <c r="S10" s="99"/>
+      <c r="T10" s="99"/>
+      <c r="U10" s="99"/>
+      <c r="V10" s="99"/>
+      <c r="W10" s="99"/>
+      <c r="X10" s="99"/>
+      <c r="Y10" s="99"/>
+      <c r="Z10" s="99"/>
+      <c r="AA10" s="99"/>
+      <c r="AB10" s="99"/>
+      <c r="AC10" s="99"/>
+      <c r="AD10" s="99"/>
+      <c r="AE10" s="99"/>
+      <c r="AF10" s="99"/>
+      <c r="AG10" s="99"/>
+      <c r="AH10" s="99"/>
+      <c r="AI10" s="99"/>
+      <c r="AJ10" s="99"/>
+      <c r="AK10" s="99"/>
+      <c r="AL10" s="99"/>
+      <c r="AM10" s="99"/>
     </row>
     <row r="11" spans="1:39" ht="15" customHeight="1">
-      <c r="A11" s="95" t="s">
+      <c r="A11" s="100" t="s">
         <v>114</v>
       </c>
-      <c r="B11" s="95"/>
-      <c r="C11" s="95"/>
-      <c r="D11" s="95"/>
-      <c r="E11" s="95"/>
-      <c r="F11" s="95"/>
-      <c r="G11" s="95"/>
-      <c r="H11" s="95"/>
-      <c r="I11" s="95"/>
-      <c r="J11" s="95"/>
-      <c r="K11" s="95"/>
-      <c r="L11" s="95"/>
-      <c r="M11" s="97"/>
-      <c r="N11" s="97"/>
-      <c r="O11" s="97"/>
-      <c r="P11" s="97"/>
-      <c r="Q11" s="97"/>
-      <c r="R11" s="97"/>
-      <c r="S11" s="97"/>
-      <c r="T11" s="97"/>
-      <c r="U11" s="97"/>
-      <c r="V11" s="97"/>
-      <c r="W11" s="97"/>
-      <c r="X11" s="97"/>
-      <c r="Y11" s="97"/>
-      <c r="Z11" s="97"/>
-      <c r="AA11" s="97"/>
-      <c r="AB11" s="97"/>
-      <c r="AC11" s="97"/>
-      <c r="AD11" s="97"/>
-      <c r="AE11" s="97"/>
-      <c r="AF11" s="97"/>
-      <c r="AG11" s="97"/>
-      <c r="AH11" s="97"/>
-      <c r="AI11" s="97"/>
-      <c r="AJ11" s="97"/>
-      <c r="AK11" s="97"/>
-      <c r="AL11" s="97"/>
-      <c r="AM11" s="97"/>
-    </row>
-    <row r="12" spans="1:39" ht="8.4499999999999993" customHeight="1">
+      <c r="B11" s="100"/>
+      <c r="C11" s="100"/>
+      <c r="D11" s="100"/>
+      <c r="E11" s="100"/>
+      <c r="F11" s="100"/>
+      <c r="G11" s="100"/>
+      <c r="H11" s="100"/>
+      <c r="I11" s="100"/>
+      <c r="J11" s="100"/>
+      <c r="K11" s="100"/>
+      <c r="L11" s="100"/>
+      <c r="M11" s="99"/>
+      <c r="N11" s="99"/>
+      <c r="O11" s="99"/>
+      <c r="P11" s="99"/>
+      <c r="Q11" s="99"/>
+      <c r="R11" s="99"/>
+      <c r="S11" s="99"/>
+      <c r="T11" s="99"/>
+      <c r="U11" s="99"/>
+      <c r="V11" s="99"/>
+      <c r="W11" s="99"/>
+      <c r="X11" s="99"/>
+      <c r="Y11" s="99"/>
+      <c r="Z11" s="99"/>
+      <c r="AA11" s="99"/>
+      <c r="AB11" s="99"/>
+      <c r="AC11" s="99"/>
+      <c r="AD11" s="99"/>
+      <c r="AE11" s="99"/>
+      <c r="AF11" s="99"/>
+      <c r="AG11" s="99"/>
+      <c r="AH11" s="99"/>
+      <c r="AI11" s="99"/>
+      <c r="AJ11" s="99"/>
+      <c r="AK11" s="99"/>
+      <c r="AL11" s="99"/>
+      <c r="AM11" s="99"/>
+    </row>
+    <row r="12" spans="1:39" ht="8.5" customHeight="1">
       <c r="A12" s="46"/>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
@@ -10823,7 +10839,7 @@
       <c r="AL13" s="14"/>
       <c r="AM13" s="14"/>
     </row>
-    <row r="14" spans="1:39" ht="8.4499999999999993" customHeight="1">
+    <row r="14" spans="1:39" ht="8.5" customHeight="1">
       <c r="A14" s="46"/>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
@@ -10908,605 +10924,605 @@
       <c r="AM15" s="14"/>
     </row>
     <row r="16" spans="1:39" ht="15" customHeight="1">
-      <c r="A16" s="99" t="s">
+      <c r="A16" s="95" t="s">
         <v>123</v>
       </c>
-      <c r="B16" s="99"/>
-      <c r="C16" s="99"/>
-      <c r="D16" s="99"/>
-      <c r="E16" s="99"/>
-      <c r="F16" s="99"/>
-      <c r="G16" s="99"/>
-      <c r="H16" s="99"/>
-      <c r="I16" s="99"/>
-      <c r="J16" s="99"/>
-      <c r="K16" s="99"/>
-      <c r="L16" s="99"/>
-      <c r="M16" s="99"/>
-      <c r="N16" s="99"/>
-      <c r="O16" s="99"/>
-      <c r="P16" s="99"/>
-      <c r="Q16" s="99"/>
-      <c r="R16" s="99"/>
-      <c r="S16" s="99"/>
-      <c r="T16" s="99"/>
-      <c r="U16" s="99"/>
-      <c r="V16" s="99"/>
-      <c r="W16" s="99"/>
-      <c r="X16" s="99"/>
-      <c r="Y16" s="99"/>
-      <c r="Z16" s="99"/>
-      <c r="AA16" s="99"/>
-      <c r="AB16" s="99"/>
-      <c r="AC16" s="99"/>
-      <c r="AD16" s="99"/>
-      <c r="AE16" s="99"/>
-      <c r="AF16" s="99"/>
-      <c r="AG16" s="99"/>
-      <c r="AH16" s="99"/>
-      <c r="AI16" s="99"/>
-      <c r="AJ16" s="99"/>
-      <c r="AK16" s="99"/>
-      <c r="AL16" s="99"/>
-      <c r="AM16" s="99"/>
+      <c r="B16" s="95"/>
+      <c r="C16" s="95"/>
+      <c r="D16" s="95"/>
+      <c r="E16" s="95"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="95"/>
+      <c r="I16" s="95"/>
+      <c r="J16" s="95"/>
+      <c r="K16" s="95"/>
+      <c r="L16" s="95"/>
+      <c r="M16" s="95"/>
+      <c r="N16" s="95"/>
+      <c r="O16" s="95"/>
+      <c r="P16" s="95"/>
+      <c r="Q16" s="95"/>
+      <c r="R16" s="95"/>
+      <c r="S16" s="95"/>
+      <c r="T16" s="95"/>
+      <c r="U16" s="95"/>
+      <c r="V16" s="95"/>
+      <c r="W16" s="95"/>
+      <c r="X16" s="95"/>
+      <c r="Y16" s="95"/>
+      <c r="Z16" s="95"/>
+      <c r="AA16" s="95"/>
+      <c r="AB16" s="95"/>
+      <c r="AC16" s="95"/>
+      <c r="AD16" s="95"/>
+      <c r="AE16" s="95"/>
+      <c r="AF16" s="95"/>
+      <c r="AG16" s="95"/>
+      <c r="AH16" s="95"/>
+      <c r="AI16" s="95"/>
+      <c r="AJ16" s="95"/>
+      <c r="AK16" s="95"/>
+      <c r="AL16" s="95"/>
+      <c r="AM16" s="95"/>
     </row>
     <row r="17" spans="1:39" ht="15" customHeight="1">
-      <c r="A17" s="99" t="s">
+      <c r="A17" s="95" t="s">
         <v>124</v>
       </c>
-      <c r="B17" s="99"/>
-      <c r="C17" s="99"/>
-      <c r="D17" s="99"/>
-      <c r="E17" s="99"/>
-      <c r="F17" s="99"/>
-      <c r="G17" s="99"/>
-      <c r="H17" s="99"/>
-      <c r="I17" s="99"/>
-      <c r="J17" s="99"/>
-      <c r="K17" s="99"/>
-      <c r="L17" s="99"/>
-      <c r="M17" s="99"/>
-      <c r="N17" s="99"/>
-      <c r="O17" s="99"/>
-      <c r="P17" s="99"/>
-      <c r="Q17" s="99"/>
-      <c r="R17" s="99"/>
-      <c r="S17" s="99"/>
-      <c r="T17" s="99"/>
-      <c r="U17" s="99"/>
-      <c r="V17" s="99"/>
-      <c r="W17" s="99"/>
-      <c r="X17" s="99"/>
-      <c r="Y17" s="99"/>
-      <c r="Z17" s="99"/>
-      <c r="AA17" s="99"/>
-      <c r="AB17" s="99"/>
-      <c r="AC17" s="99"/>
-      <c r="AD17" s="99"/>
-      <c r="AE17" s="99"/>
-      <c r="AF17" s="99"/>
-      <c r="AG17" s="99"/>
-      <c r="AH17" s="99"/>
-      <c r="AI17" s="99"/>
-      <c r="AJ17" s="99"/>
-      <c r="AK17" s="99"/>
-      <c r="AL17" s="99"/>
-      <c r="AM17" s="99"/>
+      <c r="B17" s="95"/>
+      <c r="C17" s="95"/>
+      <c r="D17" s="95"/>
+      <c r="E17" s="95"/>
+      <c r="F17" s="95"/>
+      <c r="G17" s="95"/>
+      <c r="H17" s="95"/>
+      <c r="I17" s="95"/>
+      <c r="J17" s="95"/>
+      <c r="K17" s="95"/>
+      <c r="L17" s="95"/>
+      <c r="M17" s="95"/>
+      <c r="N17" s="95"/>
+      <c r="O17" s="95"/>
+      <c r="P17" s="95"/>
+      <c r="Q17" s="95"/>
+      <c r="R17" s="95"/>
+      <c r="S17" s="95"/>
+      <c r="T17" s="95"/>
+      <c r="U17" s="95"/>
+      <c r="V17" s="95"/>
+      <c r="W17" s="95"/>
+      <c r="X17" s="95"/>
+      <c r="Y17" s="95"/>
+      <c r="Z17" s="95"/>
+      <c r="AA17" s="95"/>
+      <c r="AB17" s="95"/>
+      <c r="AC17" s="95"/>
+      <c r="AD17" s="95"/>
+      <c r="AE17" s="95"/>
+      <c r="AF17" s="95"/>
+      <c r="AG17" s="95"/>
+      <c r="AH17" s="95"/>
+      <c r="AI17" s="95"/>
+      <c r="AJ17" s="95"/>
+      <c r="AK17" s="95"/>
+      <c r="AL17" s="95"/>
+      <c r="AM17" s="95"/>
     </row>
     <row r="18" spans="1:39" ht="15" customHeight="1">
-      <c r="A18" s="96" t="s">
+      <c r="A18" s="98" t="s">
         <v>125</v>
       </c>
-      <c r="B18" s="96"/>
-      <c r="C18" s="96"/>
-      <c r="D18" s="96"/>
-      <c r="E18" s="96"/>
-      <c r="F18" s="96"/>
-      <c r="G18" s="96"/>
-      <c r="H18" s="96"/>
-      <c r="I18" s="96"/>
-      <c r="J18" s="96"/>
-      <c r="K18" s="96"/>
-      <c r="L18" s="96"/>
-      <c r="M18" s="96"/>
-      <c r="N18" s="96"/>
-      <c r="O18" s="96"/>
-      <c r="P18" s="96"/>
-      <c r="Q18" s="96"/>
-      <c r="R18" s="96"/>
-      <c r="S18" s="96"/>
-      <c r="T18" s="96"/>
-      <c r="U18" s="96"/>
-      <c r="V18" s="96"/>
-      <c r="W18" s="96"/>
-      <c r="X18" s="96"/>
-      <c r="Y18" s="96"/>
-      <c r="Z18" s="96"/>
-      <c r="AA18" s="96"/>
-      <c r="AB18" s="96"/>
-      <c r="AC18" s="96"/>
-      <c r="AD18" s="96"/>
-      <c r="AE18" s="96"/>
-      <c r="AF18" s="96"/>
-      <c r="AG18" s="96"/>
-      <c r="AH18" s="96"/>
-      <c r="AI18" s="96"/>
-      <c r="AJ18" s="96"/>
-      <c r="AK18" s="96"/>
-      <c r="AL18" s="96"/>
-      <c r="AM18" s="96"/>
+      <c r="B18" s="98"/>
+      <c r="C18" s="98"/>
+      <c r="D18" s="98"/>
+      <c r="E18" s="98"/>
+      <c r="F18" s="98"/>
+      <c r="G18" s="98"/>
+      <c r="H18" s="98"/>
+      <c r="I18" s="98"/>
+      <c r="J18" s="98"/>
+      <c r="K18" s="98"/>
+      <c r="L18" s="98"/>
+      <c r="M18" s="98"/>
+      <c r="N18" s="98"/>
+      <c r="O18" s="98"/>
+      <c r="P18" s="98"/>
+      <c r="Q18" s="98"/>
+      <c r="R18" s="98"/>
+      <c r="S18" s="98"/>
+      <c r="T18" s="98"/>
+      <c r="U18" s="98"/>
+      <c r="V18" s="98"/>
+      <c r="W18" s="98"/>
+      <c r="X18" s="98"/>
+      <c r="Y18" s="98"/>
+      <c r="Z18" s="98"/>
+      <c r="AA18" s="98"/>
+      <c r="AB18" s="98"/>
+      <c r="AC18" s="98"/>
+      <c r="AD18" s="98"/>
+      <c r="AE18" s="98"/>
+      <c r="AF18" s="98"/>
+      <c r="AG18" s="98"/>
+      <c r="AH18" s="98"/>
+      <c r="AI18" s="98"/>
+      <c r="AJ18" s="98"/>
+      <c r="AK18" s="98"/>
+      <c r="AL18" s="98"/>
+      <c r="AM18" s="98"/>
     </row>
     <row r="19" spans="1:39" ht="15" customHeight="1">
-      <c r="A19" s="96" t="s">
+      <c r="A19" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="96"/>
-      <c r="C19" s="96"/>
-      <c r="D19" s="96"/>
-      <c r="E19" s="96"/>
-      <c r="F19" s="96"/>
-      <c r="G19" s="96"/>
-      <c r="H19" s="96"/>
-      <c r="I19" s="96"/>
-      <c r="J19" s="96" t="s">
+      <c r="B19" s="98"/>
+      <c r="C19" s="98"/>
+      <c r="D19" s="98"/>
+      <c r="E19" s="98"/>
+      <c r="F19" s="98"/>
+      <c r="G19" s="98"/>
+      <c r="H19" s="98"/>
+      <c r="I19" s="98"/>
+      <c r="J19" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="K19" s="86"/>
-      <c r="L19" s="86"/>
-      <c r="M19" s="96" t="s">
+      <c r="K19" s="83"/>
+      <c r="L19" s="83"/>
+      <c r="M19" s="98" t="s">
         <v>10</v>
       </c>
-      <c r="N19" s="86"/>
-      <c r="O19" s="86"/>
-      <c r="P19" s="96" t="s">
+      <c r="N19" s="83"/>
+      <c r="O19" s="83"/>
+      <c r="P19" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="Q19" s="86"/>
-      <c r="R19" s="86"/>
-      <c r="S19" s="96" t="s">
+      <c r="Q19" s="83"/>
+      <c r="R19" s="83"/>
+      <c r="S19" s="98" t="s">
         <v>12</v>
       </c>
-      <c r="T19" s="86"/>
-      <c r="U19" s="86"/>
-      <c r="V19" s="96" t="s">
+      <c r="T19" s="83"/>
+      <c r="U19" s="83"/>
+      <c r="V19" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="W19" s="86"/>
-      <c r="X19" s="86"/>
-      <c r="Y19" s="96" t="s">
+      <c r="W19" s="83"/>
+      <c r="X19" s="83"/>
+      <c r="Y19" s="98" t="s">
         <v>128</v>
       </c>
-      <c r="Z19" s="86"/>
-      <c r="AA19" s="86"/>
-      <c r="AB19" s="96" t="s">
+      <c r="Z19" s="83"/>
+      <c r="AA19" s="83"/>
+      <c r="AB19" s="98" t="s">
         <v>129</v>
       </c>
-      <c r="AC19" s="86"/>
-      <c r="AD19" s="86"/>
-      <c r="AE19" s="96" t="s">
+      <c r="AC19" s="83"/>
+      <c r="AD19" s="83"/>
+      <c r="AE19" s="98" t="s">
         <v>130</v>
       </c>
-      <c r="AF19" s="86"/>
-      <c r="AG19" s="86"/>
-      <c r="AH19" s="96" t="s">
+      <c r="AF19" s="83"/>
+      <c r="AG19" s="83"/>
+      <c r="AH19" s="98" t="s">
         <v>131</v>
       </c>
-      <c r="AI19" s="86"/>
-      <c r="AJ19" s="86"/>
-      <c r="AK19" s="96" t="s">
+      <c r="AI19" s="83"/>
+      <c r="AJ19" s="83"/>
+      <c r="AK19" s="98" t="s">
         <v>132</v>
       </c>
-      <c r="AL19" s="86"/>
-      <c r="AM19" s="86"/>
+      <c r="AL19" s="83"/>
+      <c r="AM19" s="83"/>
     </row>
     <row r="20" spans="1:39" ht="15" customHeight="1">
-      <c r="A20" s="96" t="s">
+      <c r="A20" s="98" t="s">
         <v>127</v>
       </c>
-      <c r="B20" s="96"/>
-      <c r="C20" s="96"/>
-      <c r="D20" s="96"/>
-      <c r="E20" s="96"/>
-      <c r="F20" s="96"/>
-      <c r="G20" s="96"/>
-      <c r="H20" s="96"/>
-      <c r="I20" s="96"/>
-      <c r="J20" s="86"/>
-      <c r="K20" s="86"/>
-      <c r="L20" s="86"/>
-      <c r="M20" s="86"/>
-      <c r="N20" s="86"/>
-      <c r="O20" s="86"/>
-      <c r="P20" s="86"/>
-      <c r="Q20" s="86"/>
-      <c r="R20" s="86"/>
-      <c r="S20" s="86"/>
-      <c r="T20" s="86"/>
-      <c r="U20" s="86"/>
-      <c r="V20" s="86"/>
-      <c r="W20" s="86"/>
-      <c r="X20" s="86"/>
-      <c r="Y20" s="86"/>
-      <c r="Z20" s="86"/>
-      <c r="AA20" s="86"/>
-      <c r="AB20" s="86"/>
-      <c r="AC20" s="86"/>
-      <c r="AD20" s="86"/>
-      <c r="AE20" s="86"/>
-      <c r="AF20" s="86"/>
-      <c r="AG20" s="86"/>
-      <c r="AH20" s="86"/>
-      <c r="AI20" s="86"/>
-      <c r="AJ20" s="86"/>
-      <c r="AK20" s="86"/>
-      <c r="AL20" s="86"/>
-      <c r="AM20" s="86"/>
+      <c r="B20" s="98"/>
+      <c r="C20" s="98"/>
+      <c r="D20" s="98"/>
+      <c r="E20" s="98"/>
+      <c r="F20" s="98"/>
+      <c r="G20" s="98"/>
+      <c r="H20" s="98"/>
+      <c r="I20" s="98"/>
+      <c r="J20" s="83"/>
+      <c r="K20" s="83"/>
+      <c r="L20" s="83"/>
+      <c r="M20" s="83"/>
+      <c r="N20" s="83"/>
+      <c r="O20" s="83"/>
+      <c r="P20" s="83"/>
+      <c r="Q20" s="83"/>
+      <c r="R20" s="83"/>
+      <c r="S20" s="83"/>
+      <c r="T20" s="83"/>
+      <c r="U20" s="83"/>
+      <c r="V20" s="83"/>
+      <c r="W20" s="83"/>
+      <c r="X20" s="83"/>
+      <c r="Y20" s="83"/>
+      <c r="Z20" s="83"/>
+      <c r="AA20" s="83"/>
+      <c r="AB20" s="83"/>
+      <c r="AC20" s="83"/>
+      <c r="AD20" s="83"/>
+      <c r="AE20" s="83"/>
+      <c r="AF20" s="83"/>
+      <c r="AG20" s="83"/>
+      <c r="AH20" s="83"/>
+      <c r="AI20" s="83"/>
+      <c r="AJ20" s="83"/>
+      <c r="AK20" s="83"/>
+      <c r="AL20" s="83"/>
+      <c r="AM20" s="83"/>
     </row>
     <row r="21" spans="1:39" ht="15" customHeight="1">
-      <c r="A21" s="80" t="s">
+      <c r="A21" s="72" t="s">
         <v>126</v>
       </c>
-      <c r="B21" s="80"/>
-      <c r="C21" s="80"/>
-      <c r="D21" s="80"/>
-      <c r="E21" s="80"/>
-      <c r="F21" s="80"/>
-      <c r="G21" s="80"/>
-      <c r="H21" s="80"/>
-      <c r="I21" s="80"/>
-      <c r="J21" s="86"/>
-      <c r="K21" s="86"/>
-      <c r="L21" s="86"/>
-      <c r="M21" s="86"/>
-      <c r="N21" s="86"/>
-      <c r="O21" s="86"/>
-      <c r="P21" s="86"/>
-      <c r="Q21" s="86"/>
-      <c r="R21" s="86"/>
-      <c r="S21" s="86"/>
-      <c r="T21" s="86"/>
-      <c r="U21" s="86"/>
-      <c r="V21" s="86"/>
-      <c r="W21" s="86"/>
-      <c r="X21" s="86"/>
-      <c r="Y21" s="86"/>
-      <c r="Z21" s="86"/>
-      <c r="AA21" s="86"/>
-      <c r="AB21" s="86"/>
-      <c r="AC21" s="86"/>
-      <c r="AD21" s="86"/>
-      <c r="AE21" s="86"/>
-      <c r="AF21" s="86"/>
-      <c r="AG21" s="86"/>
-      <c r="AH21" s="86"/>
-      <c r="AI21" s="86"/>
-      <c r="AJ21" s="86"/>
-      <c r="AK21" s="86"/>
-      <c r="AL21" s="86"/>
-      <c r="AM21" s="86"/>
+      <c r="B21" s="72"/>
+      <c r="C21" s="72"/>
+      <c r="D21" s="72"/>
+      <c r="E21" s="72"/>
+      <c r="F21" s="72"/>
+      <c r="G21" s="72"/>
+      <c r="H21" s="72"/>
+      <c r="I21" s="72"/>
+      <c r="J21" s="83"/>
+      <c r="K21" s="83"/>
+      <c r="L21" s="83"/>
+      <c r="M21" s="83"/>
+      <c r="N21" s="83"/>
+      <c r="O21" s="83"/>
+      <c r="P21" s="83"/>
+      <c r="Q21" s="83"/>
+      <c r="R21" s="83"/>
+      <c r="S21" s="83"/>
+      <c r="T21" s="83"/>
+      <c r="U21" s="83"/>
+      <c r="V21" s="83"/>
+      <c r="W21" s="83"/>
+      <c r="X21" s="83"/>
+      <c r="Y21" s="83"/>
+      <c r="Z21" s="83"/>
+      <c r="AA21" s="83"/>
+      <c r="AB21" s="83"/>
+      <c r="AC21" s="83"/>
+      <c r="AD21" s="83"/>
+      <c r="AE21" s="83"/>
+      <c r="AF21" s="83"/>
+      <c r="AG21" s="83"/>
+      <c r="AH21" s="83"/>
+      <c r="AI21" s="83"/>
+      <c r="AJ21" s="83"/>
+      <c r="AK21" s="83"/>
+      <c r="AL21" s="83"/>
+      <c r="AM21" s="83"/>
     </row>
     <row r="22" spans="1:39" ht="15" customHeight="1">
-      <c r="A22" s="96" t="s">
+      <c r="A22" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="96"/>
-      <c r="C22" s="96"/>
-      <c r="D22" s="96"/>
-      <c r="E22" s="96"/>
-      <c r="F22" s="96"/>
-      <c r="G22" s="96"/>
-      <c r="H22" s="96"/>
-      <c r="I22" s="96"/>
-      <c r="J22" s="96" t="s">
+      <c r="B22" s="98"/>
+      <c r="C22" s="98"/>
+      <c r="D22" s="98"/>
+      <c r="E22" s="98"/>
+      <c r="F22" s="98"/>
+      <c r="G22" s="98"/>
+      <c r="H22" s="98"/>
+      <c r="I22" s="98"/>
+      <c r="J22" s="98" t="s">
         <v>133</v>
       </c>
-      <c r="K22" s="86"/>
-      <c r="L22" s="86"/>
-      <c r="M22" s="96" t="s">
+      <c r="K22" s="83"/>
+      <c r="L22" s="83"/>
+      <c r="M22" s="98" t="s">
         <v>134</v>
       </c>
-      <c r="N22" s="86"/>
-      <c r="O22" s="86"/>
-      <c r="P22" s="96" t="s">
+      <c r="N22" s="83"/>
+      <c r="O22" s="83"/>
+      <c r="P22" s="98" t="s">
         <v>135</v>
       </c>
-      <c r="Q22" s="86"/>
-      <c r="R22" s="86"/>
-      <c r="S22" s="96" t="s">
+      <c r="Q22" s="83"/>
+      <c r="R22" s="83"/>
+      <c r="S22" s="98" t="s">
         <v>136</v>
       </c>
-      <c r="T22" s="86"/>
-      <c r="U22" s="86"/>
-      <c r="V22" s="96" t="s">
+      <c r="T22" s="83"/>
+      <c r="U22" s="83"/>
+      <c r="V22" s="98" t="s">
         <v>137</v>
       </c>
-      <c r="W22" s="86"/>
-      <c r="X22" s="86"/>
-      <c r="Y22" s="96" t="s">
+      <c r="W22" s="83"/>
+      <c r="X22" s="83"/>
+      <c r="Y22" s="98" t="s">
         <v>138</v>
       </c>
-      <c r="Z22" s="86"/>
-      <c r="AA22" s="86"/>
-      <c r="AB22" s="96" t="s">
+      <c r="Z22" s="83"/>
+      <c r="AA22" s="83"/>
+      <c r="AB22" s="98" t="s">
         <v>139</v>
       </c>
-      <c r="AC22" s="86"/>
-      <c r="AD22" s="86"/>
-      <c r="AE22" s="96" t="s">
+      <c r="AC22" s="83"/>
+      <c r="AD22" s="83"/>
+      <c r="AE22" s="98" t="s">
         <v>140</v>
       </c>
-      <c r="AF22" s="86"/>
-      <c r="AG22" s="86"/>
-      <c r="AH22" s="96" t="s">
+      <c r="AF22" s="83"/>
+      <c r="AG22" s="83"/>
+      <c r="AH22" s="98" t="s">
         <v>141</v>
       </c>
-      <c r="AI22" s="86"/>
-      <c r="AJ22" s="86"/>
-      <c r="AK22" s="96" t="s">
+      <c r="AI22" s="83"/>
+      <c r="AJ22" s="83"/>
+      <c r="AK22" s="98" t="s">
         <v>142</v>
       </c>
-      <c r="AL22" s="86"/>
-      <c r="AM22" s="86"/>
+      <c r="AL22" s="83"/>
+      <c r="AM22" s="83"/>
     </row>
     <row r="23" spans="1:39" ht="15" customHeight="1">
-      <c r="A23" s="96" t="s">
+      <c r="A23" s="98" t="s">
         <v>127</v>
       </c>
-      <c r="B23" s="96"/>
-      <c r="C23" s="96"/>
-      <c r="D23" s="96"/>
-      <c r="E23" s="96"/>
-      <c r="F23" s="96"/>
-      <c r="G23" s="96"/>
-      <c r="H23" s="96"/>
-      <c r="I23" s="96"/>
-      <c r="J23" s="86"/>
-      <c r="K23" s="86"/>
-      <c r="L23" s="86"/>
-      <c r="M23" s="86"/>
-      <c r="N23" s="86"/>
-      <c r="O23" s="86"/>
-      <c r="P23" s="86"/>
-      <c r="Q23" s="86"/>
-      <c r="R23" s="86"/>
-      <c r="S23" s="86"/>
-      <c r="T23" s="86"/>
-      <c r="U23" s="86"/>
-      <c r="V23" s="86"/>
-      <c r="W23" s="86"/>
-      <c r="X23" s="86"/>
-      <c r="Y23" s="86"/>
-      <c r="Z23" s="86"/>
-      <c r="AA23" s="86"/>
-      <c r="AB23" s="86"/>
-      <c r="AC23" s="86"/>
-      <c r="AD23" s="86"/>
-      <c r="AE23" s="86"/>
-      <c r="AF23" s="86"/>
-      <c r="AG23" s="86"/>
-      <c r="AH23" s="86"/>
-      <c r="AI23" s="86"/>
-      <c r="AJ23" s="86"/>
-      <c r="AK23" s="86"/>
-      <c r="AL23" s="86"/>
-      <c r="AM23" s="86"/>
+      <c r="B23" s="98"/>
+      <c r="C23" s="98"/>
+      <c r="D23" s="98"/>
+      <c r="E23" s="98"/>
+      <c r="F23" s="98"/>
+      <c r="G23" s="98"/>
+      <c r="H23" s="98"/>
+      <c r="I23" s="98"/>
+      <c r="J23" s="83"/>
+      <c r="K23" s="83"/>
+      <c r="L23" s="83"/>
+      <c r="M23" s="83"/>
+      <c r="N23" s="83"/>
+      <c r="O23" s="83"/>
+      <c r="P23" s="83"/>
+      <c r="Q23" s="83"/>
+      <c r="R23" s="83"/>
+      <c r="S23" s="83"/>
+      <c r="T23" s="83"/>
+      <c r="U23" s="83"/>
+      <c r="V23" s="83"/>
+      <c r="W23" s="83"/>
+      <c r="X23" s="83"/>
+      <c r="Y23" s="83"/>
+      <c r="Z23" s="83"/>
+      <c r="AA23" s="83"/>
+      <c r="AB23" s="83"/>
+      <c r="AC23" s="83"/>
+      <c r="AD23" s="83"/>
+      <c r="AE23" s="83"/>
+      <c r="AF23" s="83"/>
+      <c r="AG23" s="83"/>
+      <c r="AH23" s="83"/>
+      <c r="AI23" s="83"/>
+      <c r="AJ23" s="83"/>
+      <c r="AK23" s="83"/>
+      <c r="AL23" s="83"/>
+      <c r="AM23" s="83"/>
     </row>
     <row r="24" spans="1:39" ht="15" customHeight="1">
-      <c r="A24" s="80" t="s">
+      <c r="A24" s="72" t="s">
         <v>126</v>
       </c>
-      <c r="B24" s="80"/>
-      <c r="C24" s="80"/>
-      <c r="D24" s="80"/>
-      <c r="E24" s="80"/>
-      <c r="F24" s="80"/>
-      <c r="G24" s="80"/>
-      <c r="H24" s="80"/>
-      <c r="I24" s="80"/>
-      <c r="J24" s="86"/>
-      <c r="K24" s="86"/>
-      <c r="L24" s="86"/>
-      <c r="M24" s="86"/>
-      <c r="N24" s="86"/>
-      <c r="O24" s="86"/>
-      <c r="P24" s="86"/>
-      <c r="Q24" s="86"/>
-      <c r="R24" s="86"/>
-      <c r="S24" s="86"/>
-      <c r="T24" s="86"/>
-      <c r="U24" s="86"/>
-      <c r="V24" s="86"/>
-      <c r="W24" s="86"/>
-      <c r="X24" s="86"/>
-      <c r="Y24" s="86"/>
-      <c r="Z24" s="86"/>
-      <c r="AA24" s="86"/>
-      <c r="AB24" s="86"/>
-      <c r="AC24" s="86"/>
-      <c r="AD24" s="86"/>
-      <c r="AE24" s="86"/>
-      <c r="AF24" s="86"/>
-      <c r="AG24" s="86"/>
-      <c r="AH24" s="86"/>
-      <c r="AI24" s="86"/>
-      <c r="AJ24" s="86"/>
-      <c r="AK24" s="86"/>
-      <c r="AL24" s="86"/>
-      <c r="AM24" s="86"/>
+      <c r="B24" s="72"/>
+      <c r="C24" s="72"/>
+      <c r="D24" s="72"/>
+      <c r="E24" s="72"/>
+      <c r="F24" s="72"/>
+      <c r="G24" s="72"/>
+      <c r="H24" s="72"/>
+      <c r="I24" s="72"/>
+      <c r="J24" s="83"/>
+      <c r="K24" s="83"/>
+      <c r="L24" s="83"/>
+      <c r="M24" s="83"/>
+      <c r="N24" s="83"/>
+      <c r="O24" s="83"/>
+      <c r="P24" s="83"/>
+      <c r="Q24" s="83"/>
+      <c r="R24" s="83"/>
+      <c r="S24" s="83"/>
+      <c r="T24" s="83"/>
+      <c r="U24" s="83"/>
+      <c r="V24" s="83"/>
+      <c r="W24" s="83"/>
+      <c r="X24" s="83"/>
+      <c r="Y24" s="83"/>
+      <c r="Z24" s="83"/>
+      <c r="AA24" s="83"/>
+      <c r="AB24" s="83"/>
+      <c r="AC24" s="83"/>
+      <c r="AD24" s="83"/>
+      <c r="AE24" s="83"/>
+      <c r="AF24" s="83"/>
+      <c r="AG24" s="83"/>
+      <c r="AH24" s="83"/>
+      <c r="AI24" s="83"/>
+      <c r="AJ24" s="83"/>
+      <c r="AK24" s="83"/>
+      <c r="AL24" s="83"/>
+      <c r="AM24" s="83"/>
     </row>
     <row r="25" spans="1:39" ht="15" customHeight="1">
-      <c r="A25" s="99" t="s">
+      <c r="A25" s="95" t="s">
         <v>143</v>
       </c>
-      <c r="B25" s="99"/>
-      <c r="C25" s="99"/>
-      <c r="D25" s="99"/>
-      <c r="E25" s="99"/>
-      <c r="F25" s="99"/>
-      <c r="G25" s="99"/>
-      <c r="H25" s="99"/>
-      <c r="I25" s="99"/>
-      <c r="J25" s="99"/>
-      <c r="K25" s="99"/>
-      <c r="L25" s="99"/>
-      <c r="M25" s="99"/>
-      <c r="N25" s="99"/>
-      <c r="O25" s="99"/>
-      <c r="P25" s="99"/>
-      <c r="Q25" s="99"/>
-      <c r="R25" s="99"/>
-      <c r="S25" s="99"/>
-      <c r="T25" s="99"/>
-      <c r="U25" s="99"/>
-      <c r="V25" s="99"/>
-      <c r="W25" s="99"/>
-      <c r="X25" s="99"/>
-      <c r="Y25" s="99"/>
-      <c r="Z25" s="99"/>
-      <c r="AA25" s="99"/>
-      <c r="AB25" s="99"/>
-      <c r="AC25" s="99"/>
-      <c r="AD25" s="99"/>
-      <c r="AE25" s="99"/>
-      <c r="AF25" s="99"/>
-      <c r="AG25" s="99"/>
-      <c r="AH25" s="99"/>
-      <c r="AI25" s="99"/>
-      <c r="AJ25" s="99"/>
-      <c r="AK25" s="99"/>
-      <c r="AL25" s="99"/>
-      <c r="AM25" s="99"/>
+      <c r="B25" s="95"/>
+      <c r="C25" s="95"/>
+      <c r="D25" s="95"/>
+      <c r="E25" s="95"/>
+      <c r="F25" s="95"/>
+      <c r="G25" s="95"/>
+      <c r="H25" s="95"/>
+      <c r="I25" s="95"/>
+      <c r="J25" s="95"/>
+      <c r="K25" s="95"/>
+      <c r="L25" s="95"/>
+      <c r="M25" s="95"/>
+      <c r="N25" s="95"/>
+      <c r="O25" s="95"/>
+      <c r="P25" s="95"/>
+      <c r="Q25" s="95"/>
+      <c r="R25" s="95"/>
+      <c r="S25" s="95"/>
+      <c r="T25" s="95"/>
+      <c r="U25" s="95"/>
+      <c r="V25" s="95"/>
+      <c r="W25" s="95"/>
+      <c r="X25" s="95"/>
+      <c r="Y25" s="95"/>
+      <c r="Z25" s="95"/>
+      <c r="AA25" s="95"/>
+      <c r="AB25" s="95"/>
+      <c r="AC25" s="95"/>
+      <c r="AD25" s="95"/>
+      <c r="AE25" s="95"/>
+      <c r="AF25" s="95"/>
+      <c r="AG25" s="95"/>
+      <c r="AH25" s="95"/>
+      <c r="AI25" s="95"/>
+      <c r="AJ25" s="95"/>
+      <c r="AK25" s="95"/>
+      <c r="AL25" s="95"/>
+      <c r="AM25" s="95"/>
     </row>
     <row r="26" spans="1:39" ht="15" customHeight="1">
-      <c r="A26" s="99" t="s">
+      <c r="A26" s="95" t="s">
         <v>144</v>
       </c>
-      <c r="B26" s="99"/>
-      <c r="C26" s="99"/>
-      <c r="D26" s="99"/>
-      <c r="E26" s="99"/>
-      <c r="F26" s="99"/>
-      <c r="G26" s="99"/>
-      <c r="H26" s="99"/>
-      <c r="I26" s="99"/>
-      <c r="J26" s="99"/>
-      <c r="K26" s="99"/>
-      <c r="L26" s="99"/>
-      <c r="M26" s="99"/>
-      <c r="N26" s="99"/>
-      <c r="O26" s="99"/>
-      <c r="P26" s="99"/>
-      <c r="Q26" s="99"/>
-      <c r="R26" s="99"/>
-      <c r="S26" s="99"/>
-      <c r="T26" s="99"/>
-      <c r="U26" s="99"/>
-      <c r="V26" s="99"/>
-      <c r="W26" s="99"/>
-      <c r="X26" s="99"/>
-      <c r="Y26" s="99"/>
-      <c r="Z26" s="99"/>
-      <c r="AA26" s="99"/>
-      <c r="AB26" s="99"/>
-      <c r="AC26" s="99"/>
-      <c r="AD26" s="99"/>
-      <c r="AE26" s="99"/>
-      <c r="AF26" s="99"/>
-      <c r="AG26" s="99"/>
-      <c r="AH26" s="99"/>
-      <c r="AI26" s="99"/>
-      <c r="AJ26" s="99"/>
-      <c r="AK26" s="99"/>
-      <c r="AL26" s="99"/>
-      <c r="AM26" s="99"/>
+      <c r="B26" s="95"/>
+      <c r="C26" s="95"/>
+      <c r="D26" s="95"/>
+      <c r="E26" s="95"/>
+      <c r="F26" s="95"/>
+      <c r="G26" s="95"/>
+      <c r="H26" s="95"/>
+      <c r="I26" s="95"/>
+      <c r="J26" s="95"/>
+      <c r="K26" s="95"/>
+      <c r="L26" s="95"/>
+      <c r="M26" s="95"/>
+      <c r="N26" s="95"/>
+      <c r="O26" s="95"/>
+      <c r="P26" s="95"/>
+      <c r="Q26" s="95"/>
+      <c r="R26" s="95"/>
+      <c r="S26" s="95"/>
+      <c r="T26" s="95"/>
+      <c r="U26" s="95"/>
+      <c r="V26" s="95"/>
+      <c r="W26" s="95"/>
+      <c r="X26" s="95"/>
+      <c r="Y26" s="95"/>
+      <c r="Z26" s="95"/>
+      <c r="AA26" s="95"/>
+      <c r="AB26" s="95"/>
+      <c r="AC26" s="95"/>
+      <c r="AD26" s="95"/>
+      <c r="AE26" s="95"/>
+      <c r="AF26" s="95"/>
+      <c r="AG26" s="95"/>
+      <c r="AH26" s="95"/>
+      <c r="AI26" s="95"/>
+      <c r="AJ26" s="95"/>
+      <c r="AK26" s="95"/>
+      <c r="AL26" s="95"/>
+      <c r="AM26" s="95"/>
     </row>
     <row r="27" spans="1:39" ht="15" customHeight="1">
-      <c r="A27" s="99" t="s">
+      <c r="A27" s="95" t="s">
         <v>145</v>
       </c>
-      <c r="B27" s="99"/>
-      <c r="C27" s="99"/>
-      <c r="D27" s="99"/>
-      <c r="E27" s="99"/>
-      <c r="F27" s="99"/>
-      <c r="G27" s="99"/>
-      <c r="H27" s="99"/>
-      <c r="I27" s="99"/>
-      <c r="J27" s="99"/>
-      <c r="K27" s="99"/>
-      <c r="L27" s="99"/>
-      <c r="M27" s="99"/>
-      <c r="N27" s="99"/>
-      <c r="O27" s="99"/>
-      <c r="P27" s="99"/>
-      <c r="Q27" s="99"/>
-      <c r="R27" s="99"/>
-      <c r="S27" s="99"/>
-      <c r="T27" s="99"/>
-      <c r="U27" s="99"/>
-      <c r="V27" s="99"/>
-      <c r="W27" s="99"/>
-      <c r="X27" s="99"/>
-      <c r="Y27" s="99"/>
-      <c r="Z27" s="99"/>
-      <c r="AA27" s="99"/>
-      <c r="AB27" s="99"/>
-      <c r="AC27" s="99"/>
-      <c r="AD27" s="99"/>
-      <c r="AE27" s="99"/>
-      <c r="AF27" s="99"/>
-      <c r="AG27" s="99"/>
-      <c r="AH27" s="99"/>
-      <c r="AI27" s="99"/>
-      <c r="AJ27" s="99"/>
-      <c r="AK27" s="99"/>
-      <c r="AL27" s="99"/>
-      <c r="AM27" s="99"/>
+      <c r="B27" s="95"/>
+      <c r="C27" s="95"/>
+      <c r="D27" s="95"/>
+      <c r="E27" s="95"/>
+      <c r="F27" s="95"/>
+      <c r="G27" s="95"/>
+      <c r="H27" s="95"/>
+      <c r="I27" s="95"/>
+      <c r="J27" s="95"/>
+      <c r="K27" s="95"/>
+      <c r="L27" s="95"/>
+      <c r="M27" s="95"/>
+      <c r="N27" s="95"/>
+      <c r="O27" s="95"/>
+      <c r="P27" s="95"/>
+      <c r="Q27" s="95"/>
+      <c r="R27" s="95"/>
+      <c r="S27" s="95"/>
+      <c r="T27" s="95"/>
+      <c r="U27" s="95"/>
+      <c r="V27" s="95"/>
+      <c r="W27" s="95"/>
+      <c r="X27" s="95"/>
+      <c r="Y27" s="95"/>
+      <c r="Z27" s="95"/>
+      <c r="AA27" s="95"/>
+      <c r="AB27" s="95"/>
+      <c r="AC27" s="95"/>
+      <c r="AD27" s="95"/>
+      <c r="AE27" s="95"/>
+      <c r="AF27" s="95"/>
+      <c r="AG27" s="95"/>
+      <c r="AH27" s="95"/>
+      <c r="AI27" s="95"/>
+      <c r="AJ27" s="95"/>
+      <c r="AK27" s="95"/>
+      <c r="AL27" s="95"/>
+      <c r="AM27" s="95"/>
     </row>
     <row r="28" spans="1:39" ht="15" customHeight="1">
-      <c r="A28" s="99" t="s">
+      <c r="A28" s="95" t="s">
         <v>146</v>
       </c>
-      <c r="B28" s="99"/>
-      <c r="C28" s="99"/>
-      <c r="D28" s="99"/>
-      <c r="E28" s="99"/>
-      <c r="F28" s="99"/>
-      <c r="G28" s="99"/>
-      <c r="H28" s="99"/>
-      <c r="I28" s="99"/>
-      <c r="J28" s="99"/>
-      <c r="K28" s="99"/>
-      <c r="L28" s="99"/>
-      <c r="M28" s="99"/>
-      <c r="N28" s="99"/>
-      <c r="O28" s="99"/>
-      <c r="P28" s="99"/>
-      <c r="Q28" s="99"/>
-      <c r="R28" s="99"/>
-      <c r="S28" s="99"/>
-      <c r="T28" s="99"/>
-      <c r="U28" s="99"/>
-      <c r="V28" s="99"/>
-      <c r="W28" s="99"/>
-      <c r="X28" s="99"/>
-      <c r="Y28" s="99"/>
-      <c r="Z28" s="99"/>
-      <c r="AA28" s="99"/>
-      <c r="AB28" s="99"/>
-      <c r="AC28" s="99"/>
-      <c r="AD28" s="99"/>
-      <c r="AE28" s="99"/>
-      <c r="AF28" s="99"/>
-      <c r="AG28" s="99"/>
-      <c r="AH28" s="99"/>
-      <c r="AI28" s="99"/>
-      <c r="AJ28" s="99"/>
-      <c r="AK28" s="99"/>
-      <c r="AL28" s="99"/>
-      <c r="AM28" s="99"/>
-    </row>
-    <row r="29" spans="1:39" ht="14.1" customHeight="1">
+      <c r="B28" s="95"/>
+      <c r="C28" s="95"/>
+      <c r="D28" s="95"/>
+      <c r="E28" s="95"/>
+      <c r="F28" s="95"/>
+      <c r="G28" s="95"/>
+      <c r="H28" s="95"/>
+      <c r="I28" s="95"/>
+      <c r="J28" s="95"/>
+      <c r="K28" s="95"/>
+      <c r="L28" s="95"/>
+      <c r="M28" s="95"/>
+      <c r="N28" s="95"/>
+      <c r="O28" s="95"/>
+      <c r="P28" s="95"/>
+      <c r="Q28" s="95"/>
+      <c r="R28" s="95"/>
+      <c r="S28" s="95"/>
+      <c r="T28" s="95"/>
+      <c r="U28" s="95"/>
+      <c r="V28" s="95"/>
+      <c r="W28" s="95"/>
+      <c r="X28" s="95"/>
+      <c r="Y28" s="95"/>
+      <c r="Z28" s="95"/>
+      <c r="AA28" s="95"/>
+      <c r="AB28" s="95"/>
+      <c r="AC28" s="95"/>
+      <c r="AD28" s="95"/>
+      <c r="AE28" s="95"/>
+      <c r="AF28" s="95"/>
+      <c r="AG28" s="95"/>
+      <c r="AH28" s="95"/>
+      <c r="AI28" s="95"/>
+      <c r="AJ28" s="95"/>
+      <c r="AK28" s="95"/>
+      <c r="AL28" s="95"/>
+      <c r="AM28" s="95"/>
+    </row>
+    <row r="29" spans="1:39" ht="14.15" customHeight="1">
       <c r="A29" s="46"/>
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
@@ -11548,886 +11564,886 @@
       <c r="AM29" s="14"/>
     </row>
     <row r="30" spans="1:39" ht="15" customHeight="1">
-      <c r="A30" s="99" t="s">
+      <c r="A30" s="95" t="s">
         <v>147</v>
       </c>
-      <c r="B30" s="99"/>
-      <c r="C30" s="99"/>
-      <c r="D30" s="99"/>
-      <c r="E30" s="99"/>
-      <c r="F30" s="99"/>
-      <c r="G30" s="99"/>
-      <c r="H30" s="99"/>
-      <c r="I30" s="99"/>
-      <c r="J30" s="99"/>
-      <c r="K30" s="99"/>
-      <c r="L30" s="99"/>
-      <c r="M30" s="99"/>
-      <c r="N30" s="99"/>
-      <c r="O30" s="99"/>
-      <c r="P30" s="99"/>
-      <c r="Q30" s="99"/>
-      <c r="R30" s="99"/>
-      <c r="S30" s="99"/>
-      <c r="T30" s="99"/>
-      <c r="U30" s="99"/>
-      <c r="V30" s="99"/>
-      <c r="W30" s="99"/>
-      <c r="X30" s="99"/>
-      <c r="Y30" s="99"/>
-      <c r="Z30" s="99"/>
-      <c r="AA30" s="99"/>
-      <c r="AB30" s="99"/>
-      <c r="AC30" s="99"/>
-      <c r="AD30" s="99"/>
-      <c r="AE30" s="99"/>
-      <c r="AF30" s="99"/>
-      <c r="AG30" s="99"/>
-      <c r="AH30" s="99"/>
-      <c r="AI30" s="99"/>
-      <c r="AJ30" s="99"/>
-      <c r="AK30" s="99"/>
-      <c r="AL30" s="99"/>
-      <c r="AM30" s="99"/>
+      <c r="B30" s="95"/>
+      <c r="C30" s="95"/>
+      <c r="D30" s="95"/>
+      <c r="E30" s="95"/>
+      <c r="F30" s="95"/>
+      <c r="G30" s="95"/>
+      <c r="H30" s="95"/>
+      <c r="I30" s="95"/>
+      <c r="J30" s="95"/>
+      <c r="K30" s="95"/>
+      <c r="L30" s="95"/>
+      <c r="M30" s="95"/>
+      <c r="N30" s="95"/>
+      <c r="O30" s="95"/>
+      <c r="P30" s="95"/>
+      <c r="Q30" s="95"/>
+      <c r="R30" s="95"/>
+      <c r="S30" s="95"/>
+      <c r="T30" s="95"/>
+      <c r="U30" s="95"/>
+      <c r="V30" s="95"/>
+      <c r="W30" s="95"/>
+      <c r="X30" s="95"/>
+      <c r="Y30" s="95"/>
+      <c r="Z30" s="95"/>
+      <c r="AA30" s="95"/>
+      <c r="AB30" s="95"/>
+      <c r="AC30" s="95"/>
+      <c r="AD30" s="95"/>
+      <c r="AE30" s="95"/>
+      <c r="AF30" s="95"/>
+      <c r="AG30" s="95"/>
+      <c r="AH30" s="95"/>
+      <c r="AI30" s="95"/>
+      <c r="AJ30" s="95"/>
+      <c r="AK30" s="95"/>
+      <c r="AL30" s="95"/>
+      <c r="AM30" s="95"/>
     </row>
     <row r="31" spans="1:39" ht="15" customHeight="1">
-      <c r="A31" s="99" t="s">
+      <c r="A31" s="95" t="s">
         <v>148</v>
       </c>
-      <c r="B31" s="99"/>
-      <c r="C31" s="99"/>
-      <c r="D31" s="99"/>
-      <c r="E31" s="99"/>
-      <c r="F31" s="99"/>
-      <c r="G31" s="99"/>
-      <c r="H31" s="99"/>
-      <c r="I31" s="99"/>
-      <c r="J31" s="99"/>
-      <c r="K31" s="99"/>
-      <c r="L31" s="99"/>
-      <c r="M31" s="99"/>
-      <c r="N31" s="99"/>
-      <c r="O31" s="99"/>
-      <c r="P31" s="99"/>
-      <c r="Q31" s="99"/>
-      <c r="R31" s="99"/>
-      <c r="S31" s="99"/>
-      <c r="T31" s="99"/>
-      <c r="U31" s="99"/>
-      <c r="V31" s="99"/>
-      <c r="W31" s="99"/>
-      <c r="X31" s="99"/>
-      <c r="Y31" s="99"/>
-      <c r="Z31" s="99"/>
-      <c r="AA31" s="99"/>
-      <c r="AB31" s="99"/>
-      <c r="AC31" s="99"/>
-      <c r="AD31" s="99"/>
-      <c r="AE31" s="99"/>
-      <c r="AF31" s="99"/>
-      <c r="AG31" s="99"/>
-      <c r="AH31" s="99"/>
-      <c r="AI31" s="99"/>
-      <c r="AJ31" s="99"/>
-      <c r="AK31" s="99"/>
-      <c r="AL31" s="99"/>
-      <c r="AM31" s="99"/>
+      <c r="B31" s="95"/>
+      <c r="C31" s="95"/>
+      <c r="D31" s="95"/>
+      <c r="E31" s="95"/>
+      <c r="F31" s="95"/>
+      <c r="G31" s="95"/>
+      <c r="H31" s="95"/>
+      <c r="I31" s="95"/>
+      <c r="J31" s="95"/>
+      <c r="K31" s="95"/>
+      <c r="L31" s="95"/>
+      <c r="M31" s="95"/>
+      <c r="N31" s="95"/>
+      <c r="O31" s="95"/>
+      <c r="P31" s="95"/>
+      <c r="Q31" s="95"/>
+      <c r="R31" s="95"/>
+      <c r="S31" s="95"/>
+      <c r="T31" s="95"/>
+      <c r="U31" s="95"/>
+      <c r="V31" s="95"/>
+      <c r="W31" s="95"/>
+      <c r="X31" s="95"/>
+      <c r="Y31" s="95"/>
+      <c r="Z31" s="95"/>
+      <c r="AA31" s="95"/>
+      <c r="AB31" s="95"/>
+      <c r="AC31" s="95"/>
+      <c r="AD31" s="95"/>
+      <c r="AE31" s="95"/>
+      <c r="AF31" s="95"/>
+      <c r="AG31" s="95"/>
+      <c r="AH31" s="95"/>
+      <c r="AI31" s="95"/>
+      <c r="AJ31" s="95"/>
+      <c r="AK31" s="95"/>
+      <c r="AL31" s="95"/>
+      <c r="AM31" s="95"/>
     </row>
     <row r="32" spans="1:39" ht="15" customHeight="1">
-      <c r="A32" s="96" t="s">
+      <c r="A32" s="98" t="s">
         <v>149</v>
       </c>
-      <c r="B32" s="96"/>
-      <c r="C32" s="96"/>
-      <c r="D32" s="96"/>
-      <c r="E32" s="96"/>
-      <c r="F32" s="96"/>
-      <c r="G32" s="96"/>
-      <c r="H32" s="96"/>
-      <c r="I32" s="96"/>
-      <c r="J32" s="96"/>
-      <c r="K32" s="96"/>
-      <c r="L32" s="96"/>
-      <c r="M32" s="96"/>
-      <c r="N32" s="96"/>
-      <c r="O32" s="96"/>
-      <c r="P32" s="96"/>
-      <c r="Q32" s="96"/>
-      <c r="R32" s="96"/>
-      <c r="S32" s="96"/>
-      <c r="T32" s="96"/>
-      <c r="U32" s="96"/>
-      <c r="V32" s="96"/>
-      <c r="W32" s="96"/>
-      <c r="X32" s="96"/>
-      <c r="Y32" s="96"/>
-      <c r="Z32" s="96"/>
-      <c r="AA32" s="96"/>
-      <c r="AB32" s="96"/>
-      <c r="AC32" s="96"/>
-      <c r="AD32" s="96"/>
-      <c r="AE32" s="96"/>
-      <c r="AF32" s="96"/>
-      <c r="AG32" s="96"/>
-      <c r="AH32" s="96"/>
-      <c r="AI32" s="96"/>
-      <c r="AJ32" s="96"/>
-      <c r="AK32" s="96"/>
-      <c r="AL32" s="96"/>
-      <c r="AM32" s="96"/>
+      <c r="B32" s="98"/>
+      <c r="C32" s="98"/>
+      <c r="D32" s="98"/>
+      <c r="E32" s="98"/>
+      <c r="F32" s="98"/>
+      <c r="G32" s="98"/>
+      <c r="H32" s="98"/>
+      <c r="I32" s="98"/>
+      <c r="J32" s="98"/>
+      <c r="K32" s="98"/>
+      <c r="L32" s="98"/>
+      <c r="M32" s="98"/>
+      <c r="N32" s="98"/>
+      <c r="O32" s="98"/>
+      <c r="P32" s="98"/>
+      <c r="Q32" s="98"/>
+      <c r="R32" s="98"/>
+      <c r="S32" s="98"/>
+      <c r="T32" s="98"/>
+      <c r="U32" s="98"/>
+      <c r="V32" s="98"/>
+      <c r="W32" s="98"/>
+      <c r="X32" s="98"/>
+      <c r="Y32" s="98"/>
+      <c r="Z32" s="98"/>
+      <c r="AA32" s="98"/>
+      <c r="AB32" s="98"/>
+      <c r="AC32" s="98"/>
+      <c r="AD32" s="98"/>
+      <c r="AE32" s="98"/>
+      <c r="AF32" s="98"/>
+      <c r="AG32" s="98"/>
+      <c r="AH32" s="98"/>
+      <c r="AI32" s="98"/>
+      <c r="AJ32" s="98"/>
+      <c r="AK32" s="98"/>
+      <c r="AL32" s="98"/>
+      <c r="AM32" s="98"/>
     </row>
     <row r="33" spans="1:39" ht="15" customHeight="1">
-      <c r="A33" s="96" t="s">
+      <c r="A33" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="96"/>
-      <c r="C33" s="96"/>
-      <c r="D33" s="96"/>
-      <c r="E33" s="96" t="s">
+      <c r="B33" s="98"/>
+      <c r="C33" s="98"/>
+      <c r="D33" s="98"/>
+      <c r="E33" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="F33" s="86"/>
-      <c r="G33" s="86"/>
-      <c r="H33" s="86"/>
-      <c r="I33" s="86"/>
-      <c r="J33" s="86"/>
-      <c r="K33" s="86"/>
-      <c r="L33" s="96" t="s">
+      <c r="F33" s="83"/>
+      <c r="G33" s="83"/>
+      <c r="H33" s="83"/>
+      <c r="I33" s="83"/>
+      <c r="J33" s="83"/>
+      <c r="K33" s="83"/>
+      <c r="L33" s="98" t="s">
         <v>10</v>
       </c>
-      <c r="M33" s="86"/>
-      <c r="N33" s="86"/>
-      <c r="O33" s="86"/>
-      <c r="P33" s="86"/>
-      <c r="Q33" s="86"/>
-      <c r="R33" s="86"/>
-      <c r="S33" s="96" t="s">
+      <c r="M33" s="83"/>
+      <c r="N33" s="83"/>
+      <c r="O33" s="83"/>
+      <c r="P33" s="83"/>
+      <c r="Q33" s="83"/>
+      <c r="R33" s="83"/>
+      <c r="S33" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="T33" s="86"/>
-      <c r="U33" s="86"/>
-      <c r="V33" s="86"/>
-      <c r="W33" s="86"/>
-      <c r="X33" s="86"/>
-      <c r="Y33" s="86"/>
-      <c r="Z33" s="96" t="s">
+      <c r="T33" s="83"/>
+      <c r="U33" s="83"/>
+      <c r="V33" s="83"/>
+      <c r="W33" s="83"/>
+      <c r="X33" s="83"/>
+      <c r="Y33" s="83"/>
+      <c r="Z33" s="98" t="s">
         <v>12</v>
       </c>
-      <c r="AA33" s="86"/>
-      <c r="AB33" s="86"/>
-      <c r="AC33" s="86"/>
-      <c r="AD33" s="86"/>
-      <c r="AE33" s="86"/>
-      <c r="AF33" s="86"/>
-      <c r="AG33" s="96" t="s">
+      <c r="AA33" s="83"/>
+      <c r="AB33" s="83"/>
+      <c r="AC33" s="83"/>
+      <c r="AD33" s="83"/>
+      <c r="AE33" s="83"/>
+      <c r="AF33" s="83"/>
+      <c r="AG33" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="AH33" s="86"/>
-      <c r="AI33" s="86"/>
-      <c r="AJ33" s="86"/>
-      <c r="AK33" s="86"/>
-      <c r="AL33" s="86"/>
-      <c r="AM33" s="86"/>
+      <c r="AH33" s="83"/>
+      <c r="AI33" s="83"/>
+      <c r="AJ33" s="83"/>
+      <c r="AK33" s="83"/>
+      <c r="AL33" s="83"/>
+      <c r="AM33" s="83"/>
     </row>
     <row r="34" spans="1:39" ht="15" customHeight="1">
-      <c r="A34" s="96"/>
-      <c r="B34" s="96"/>
-      <c r="C34" s="96"/>
-      <c r="D34" s="96"/>
-      <c r="E34" s="96"/>
-      <c r="F34" s="86"/>
-      <c r="G34" s="86"/>
-      <c r="H34" s="86"/>
-      <c r="I34" s="86"/>
-      <c r="J34" s="86"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="96"/>
-      <c r="M34" s="86"/>
-      <c r="N34" s="86"/>
-      <c r="O34" s="86"/>
-      <c r="P34" s="86"/>
-      <c r="Q34" s="86"/>
-      <c r="R34" s="86"/>
-      <c r="S34" s="96"/>
-      <c r="T34" s="86"/>
-      <c r="U34" s="86"/>
-      <c r="V34" s="86"/>
-      <c r="W34" s="86"/>
-      <c r="X34" s="86"/>
-      <c r="Y34" s="86"/>
-      <c r="Z34" s="96"/>
-      <c r="AA34" s="86"/>
-      <c r="AB34" s="86"/>
-      <c r="AC34" s="86"/>
-      <c r="AD34" s="86"/>
-      <c r="AE34" s="86"/>
-      <c r="AF34" s="86"/>
-      <c r="AG34" s="96"/>
-      <c r="AH34" s="86"/>
-      <c r="AI34" s="86"/>
-      <c r="AJ34" s="86"/>
-      <c r="AK34" s="86"/>
-      <c r="AL34" s="86"/>
-      <c r="AM34" s="86"/>
+      <c r="A34" s="98"/>
+      <c r="B34" s="98"/>
+      <c r="C34" s="98"/>
+      <c r="D34" s="98"/>
+      <c r="E34" s="98"/>
+      <c r="F34" s="83"/>
+      <c r="G34" s="83"/>
+      <c r="H34" s="83"/>
+      <c r="I34" s="83"/>
+      <c r="J34" s="83"/>
+      <c r="K34" s="83"/>
+      <c r="L34" s="98"/>
+      <c r="M34" s="83"/>
+      <c r="N34" s="83"/>
+      <c r="O34" s="83"/>
+      <c r="P34" s="83"/>
+      <c r="Q34" s="83"/>
+      <c r="R34" s="83"/>
+      <c r="S34" s="98"/>
+      <c r="T34" s="83"/>
+      <c r="U34" s="83"/>
+      <c r="V34" s="83"/>
+      <c r="W34" s="83"/>
+      <c r="X34" s="83"/>
+      <c r="Y34" s="83"/>
+      <c r="Z34" s="98"/>
+      <c r="AA34" s="83"/>
+      <c r="AB34" s="83"/>
+      <c r="AC34" s="83"/>
+      <c r="AD34" s="83"/>
+      <c r="AE34" s="83"/>
+      <c r="AF34" s="83"/>
+      <c r="AG34" s="98"/>
+      <c r="AH34" s="83"/>
+      <c r="AI34" s="83"/>
+      <c r="AJ34" s="83"/>
+      <c r="AK34" s="83"/>
+      <c r="AL34" s="83"/>
+      <c r="AM34" s="83"/>
     </row>
     <row r="35" spans="1:39" ht="15" customHeight="1">
-      <c r="A35" s="96"/>
-      <c r="B35" s="96"/>
-      <c r="C35" s="96"/>
-      <c r="D35" s="96"/>
-      <c r="E35" s="96"/>
-      <c r="F35" s="86"/>
-      <c r="G35" s="86"/>
-      <c r="H35" s="86"/>
-      <c r="I35" s="86"/>
-      <c r="J35" s="86"/>
-      <c r="K35" s="86"/>
-      <c r="L35" s="96"/>
-      <c r="M35" s="86"/>
-      <c r="N35" s="86"/>
-      <c r="O35" s="86"/>
-      <c r="P35" s="86"/>
-      <c r="Q35" s="86"/>
-      <c r="R35" s="86"/>
-      <c r="S35" s="96"/>
-      <c r="T35" s="86"/>
-      <c r="U35" s="86"/>
-      <c r="V35" s="86"/>
-      <c r="W35" s="86"/>
-      <c r="X35" s="86"/>
-      <c r="Y35" s="86"/>
-      <c r="Z35" s="96"/>
-      <c r="AA35" s="86"/>
-      <c r="AB35" s="86"/>
-      <c r="AC35" s="86"/>
-      <c r="AD35" s="86"/>
-      <c r="AE35" s="86"/>
-      <c r="AF35" s="86"/>
-      <c r="AG35" s="96"/>
-      <c r="AH35" s="86"/>
-      <c r="AI35" s="86"/>
-      <c r="AJ35" s="86"/>
-      <c r="AK35" s="86"/>
-      <c r="AL35" s="86"/>
-      <c r="AM35" s="86"/>
+      <c r="A35" s="98"/>
+      <c r="B35" s="98"/>
+      <c r="C35" s="98"/>
+      <c r="D35" s="98"/>
+      <c r="E35" s="98"/>
+      <c r="F35" s="83"/>
+      <c r="G35" s="83"/>
+      <c r="H35" s="83"/>
+      <c r="I35" s="83"/>
+      <c r="J35" s="83"/>
+      <c r="K35" s="83"/>
+      <c r="L35" s="98"/>
+      <c r="M35" s="83"/>
+      <c r="N35" s="83"/>
+      <c r="O35" s="83"/>
+      <c r="P35" s="83"/>
+      <c r="Q35" s="83"/>
+      <c r="R35" s="83"/>
+      <c r="S35" s="98"/>
+      <c r="T35" s="83"/>
+      <c r="U35" s="83"/>
+      <c r="V35" s="83"/>
+      <c r="W35" s="83"/>
+      <c r="X35" s="83"/>
+      <c r="Y35" s="83"/>
+      <c r="Z35" s="98"/>
+      <c r="AA35" s="83"/>
+      <c r="AB35" s="83"/>
+      <c r="AC35" s="83"/>
+      <c r="AD35" s="83"/>
+      <c r="AE35" s="83"/>
+      <c r="AF35" s="83"/>
+      <c r="AG35" s="98"/>
+      <c r="AH35" s="83"/>
+      <c r="AI35" s="83"/>
+      <c r="AJ35" s="83"/>
+      <c r="AK35" s="83"/>
+      <c r="AL35" s="83"/>
+      <c r="AM35" s="83"/>
     </row>
     <row r="36" spans="1:39" ht="15" customHeight="1">
-      <c r="A36" s="96" t="s">
+      <c r="A36" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="B36" s="96"/>
-      <c r="C36" s="96"/>
-      <c r="D36" s="96"/>
-      <c r="E36" s="96" t="s">
+      <c r="B36" s="98"/>
+      <c r="C36" s="98"/>
+      <c r="D36" s="98"/>
+      <c r="E36" s="98" t="s">
         <v>128</v>
       </c>
-      <c r="F36" s="86"/>
-      <c r="G36" s="86"/>
-      <c r="H36" s="86"/>
-      <c r="I36" s="86"/>
-      <c r="J36" s="86"/>
-      <c r="K36" s="86"/>
-      <c r="L36" s="96" t="s">
+      <c r="F36" s="83"/>
+      <c r="G36" s="83"/>
+      <c r="H36" s="83"/>
+      <c r="I36" s="83"/>
+      <c r="J36" s="83"/>
+      <c r="K36" s="83"/>
+      <c r="L36" s="98" t="s">
         <v>129</v>
       </c>
-      <c r="M36" s="86"/>
-      <c r="N36" s="86"/>
-      <c r="O36" s="86"/>
-      <c r="P36" s="86"/>
-      <c r="Q36" s="86"/>
-      <c r="R36" s="86"/>
-      <c r="S36" s="96" t="s">
+      <c r="M36" s="83"/>
+      <c r="N36" s="83"/>
+      <c r="O36" s="83"/>
+      <c r="P36" s="83"/>
+      <c r="Q36" s="83"/>
+      <c r="R36" s="83"/>
+      <c r="S36" s="98" t="s">
         <v>130</v>
       </c>
-      <c r="T36" s="86"/>
-      <c r="U36" s="86"/>
-      <c r="V36" s="86"/>
-      <c r="W36" s="86"/>
-      <c r="X36" s="86"/>
-      <c r="Y36" s="86"/>
-      <c r="Z36" s="96" t="s">
+      <c r="T36" s="83"/>
+      <c r="U36" s="83"/>
+      <c r="V36" s="83"/>
+      <c r="W36" s="83"/>
+      <c r="X36" s="83"/>
+      <c r="Y36" s="83"/>
+      <c r="Z36" s="98" t="s">
         <v>131</v>
       </c>
-      <c r="AA36" s="86"/>
-      <c r="AB36" s="86"/>
-      <c r="AC36" s="86"/>
-      <c r="AD36" s="86"/>
-      <c r="AE36" s="86"/>
-      <c r="AF36" s="86"/>
-      <c r="AG36" s="96" t="s">
+      <c r="AA36" s="83"/>
+      <c r="AB36" s="83"/>
+      <c r="AC36" s="83"/>
+      <c r="AD36" s="83"/>
+      <c r="AE36" s="83"/>
+      <c r="AF36" s="83"/>
+      <c r="AG36" s="98" t="s">
         <v>132</v>
       </c>
-      <c r="AH36" s="86"/>
-      <c r="AI36" s="86"/>
-      <c r="AJ36" s="86"/>
-      <c r="AK36" s="86"/>
-      <c r="AL36" s="86"/>
-      <c r="AM36" s="86"/>
+      <c r="AH36" s="83"/>
+      <c r="AI36" s="83"/>
+      <c r="AJ36" s="83"/>
+      <c r="AK36" s="83"/>
+      <c r="AL36" s="83"/>
+      <c r="AM36" s="83"/>
     </row>
     <row r="37" spans="1:39" ht="15" customHeight="1">
-      <c r="A37" s="96"/>
-      <c r="B37" s="96"/>
-      <c r="C37" s="96"/>
-      <c r="D37" s="96"/>
-      <c r="E37" s="96"/>
-      <c r="F37" s="86"/>
-      <c r="G37" s="86"/>
-      <c r="H37" s="86"/>
-      <c r="I37" s="86"/>
-      <c r="J37" s="86"/>
-      <c r="K37" s="86"/>
-      <c r="L37" s="96"/>
-      <c r="M37" s="86"/>
-      <c r="N37" s="86"/>
-      <c r="O37" s="86"/>
-      <c r="P37" s="86"/>
-      <c r="Q37" s="86"/>
-      <c r="R37" s="86"/>
-      <c r="S37" s="96"/>
-      <c r="T37" s="86"/>
-      <c r="U37" s="86"/>
-      <c r="V37" s="86"/>
-      <c r="W37" s="86"/>
-      <c r="X37" s="86"/>
-      <c r="Y37" s="86"/>
-      <c r="Z37" s="96"/>
-      <c r="AA37" s="86"/>
-      <c r="AB37" s="86"/>
-      <c r="AC37" s="86"/>
-      <c r="AD37" s="86"/>
-      <c r="AE37" s="86"/>
-      <c r="AF37" s="86"/>
-      <c r="AG37" s="96"/>
-      <c r="AH37" s="86"/>
-      <c r="AI37" s="86"/>
-      <c r="AJ37" s="86"/>
-      <c r="AK37" s="86"/>
-      <c r="AL37" s="86"/>
-      <c r="AM37" s="86"/>
+      <c r="A37" s="98"/>
+      <c r="B37" s="98"/>
+      <c r="C37" s="98"/>
+      <c r="D37" s="98"/>
+      <c r="E37" s="98"/>
+      <c r="F37" s="83"/>
+      <c r="G37" s="83"/>
+      <c r="H37" s="83"/>
+      <c r="I37" s="83"/>
+      <c r="J37" s="83"/>
+      <c r="K37" s="83"/>
+      <c r="L37" s="98"/>
+      <c r="M37" s="83"/>
+      <c r="N37" s="83"/>
+      <c r="O37" s="83"/>
+      <c r="P37" s="83"/>
+      <c r="Q37" s="83"/>
+      <c r="R37" s="83"/>
+      <c r="S37" s="98"/>
+      <c r="T37" s="83"/>
+      <c r="U37" s="83"/>
+      <c r="V37" s="83"/>
+      <c r="W37" s="83"/>
+      <c r="X37" s="83"/>
+      <c r="Y37" s="83"/>
+      <c r="Z37" s="98"/>
+      <c r="AA37" s="83"/>
+      <c r="AB37" s="83"/>
+      <c r="AC37" s="83"/>
+      <c r="AD37" s="83"/>
+      <c r="AE37" s="83"/>
+      <c r="AF37" s="83"/>
+      <c r="AG37" s="98"/>
+      <c r="AH37" s="83"/>
+      <c r="AI37" s="83"/>
+      <c r="AJ37" s="83"/>
+      <c r="AK37" s="83"/>
+      <c r="AL37" s="83"/>
+      <c r="AM37" s="83"/>
     </row>
     <row r="38" spans="1:39" ht="15" customHeight="1">
-      <c r="A38" s="96"/>
-      <c r="B38" s="96"/>
-      <c r="C38" s="96"/>
-      <c r="D38" s="96"/>
-      <c r="E38" s="96"/>
-      <c r="F38" s="86"/>
-      <c r="G38" s="86"/>
-      <c r="H38" s="86"/>
-      <c r="I38" s="86"/>
-      <c r="J38" s="86"/>
-      <c r="K38" s="86"/>
-      <c r="L38" s="96"/>
-      <c r="M38" s="86"/>
-      <c r="N38" s="86"/>
-      <c r="O38" s="86"/>
-      <c r="P38" s="86"/>
-      <c r="Q38" s="86"/>
-      <c r="R38" s="86"/>
-      <c r="S38" s="96"/>
-      <c r="T38" s="86"/>
-      <c r="U38" s="86"/>
-      <c r="V38" s="86"/>
-      <c r="W38" s="86"/>
-      <c r="X38" s="86"/>
-      <c r="Y38" s="86"/>
-      <c r="Z38" s="96"/>
-      <c r="AA38" s="86"/>
-      <c r="AB38" s="86"/>
-      <c r="AC38" s="86"/>
-      <c r="AD38" s="86"/>
-      <c r="AE38" s="86"/>
-      <c r="AF38" s="86"/>
-      <c r="AG38" s="96"/>
-      <c r="AH38" s="86"/>
-      <c r="AI38" s="86"/>
-      <c r="AJ38" s="86"/>
-      <c r="AK38" s="86"/>
-      <c r="AL38" s="86"/>
-      <c r="AM38" s="86"/>
+      <c r="A38" s="98"/>
+      <c r="B38" s="98"/>
+      <c r="C38" s="98"/>
+      <c r="D38" s="98"/>
+      <c r="E38" s="98"/>
+      <c r="F38" s="83"/>
+      <c r="G38" s="83"/>
+      <c r="H38" s="83"/>
+      <c r="I38" s="83"/>
+      <c r="J38" s="83"/>
+      <c r="K38" s="83"/>
+      <c r="L38" s="98"/>
+      <c r="M38" s="83"/>
+      <c r="N38" s="83"/>
+      <c r="O38" s="83"/>
+      <c r="P38" s="83"/>
+      <c r="Q38" s="83"/>
+      <c r="R38" s="83"/>
+      <c r="S38" s="98"/>
+      <c r="T38" s="83"/>
+      <c r="U38" s="83"/>
+      <c r="V38" s="83"/>
+      <c r="W38" s="83"/>
+      <c r="X38" s="83"/>
+      <c r="Y38" s="83"/>
+      <c r="Z38" s="98"/>
+      <c r="AA38" s="83"/>
+      <c r="AB38" s="83"/>
+      <c r="AC38" s="83"/>
+      <c r="AD38" s="83"/>
+      <c r="AE38" s="83"/>
+      <c r="AF38" s="83"/>
+      <c r="AG38" s="98"/>
+      <c r="AH38" s="83"/>
+      <c r="AI38" s="83"/>
+      <c r="AJ38" s="83"/>
+      <c r="AK38" s="83"/>
+      <c r="AL38" s="83"/>
+      <c r="AM38" s="83"/>
     </row>
     <row r="39" spans="1:39" ht="15" customHeight="1">
-      <c r="A39" s="96" t="s">
+      <c r="A39" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="B39" s="96"/>
-      <c r="C39" s="96"/>
-      <c r="D39" s="96"/>
-      <c r="E39" s="96" t="s">
+      <c r="B39" s="98"/>
+      <c r="C39" s="98"/>
+      <c r="D39" s="98"/>
+      <c r="E39" s="98" t="s">
         <v>133</v>
       </c>
-      <c r="F39" s="86"/>
-      <c r="G39" s="86"/>
-      <c r="H39" s="86"/>
-      <c r="I39" s="86"/>
-      <c r="J39" s="86"/>
-      <c r="K39" s="86"/>
-      <c r="L39" s="96" t="s">
+      <c r="F39" s="83"/>
+      <c r="G39" s="83"/>
+      <c r="H39" s="83"/>
+      <c r="I39" s="83"/>
+      <c r="J39" s="83"/>
+      <c r="K39" s="83"/>
+      <c r="L39" s="98" t="s">
         <v>134</v>
       </c>
-      <c r="M39" s="86"/>
-      <c r="N39" s="86"/>
-      <c r="O39" s="86"/>
-      <c r="P39" s="86"/>
-      <c r="Q39" s="86"/>
-      <c r="R39" s="86"/>
-      <c r="S39" s="96" t="s">
+      <c r="M39" s="83"/>
+      <c r="N39" s="83"/>
+      <c r="O39" s="83"/>
+      <c r="P39" s="83"/>
+      <c r="Q39" s="83"/>
+      <c r="R39" s="83"/>
+      <c r="S39" s="98" t="s">
         <v>135</v>
       </c>
-      <c r="T39" s="86"/>
-      <c r="U39" s="86"/>
-      <c r="V39" s="86"/>
-      <c r="W39" s="86"/>
-      <c r="X39" s="86"/>
-      <c r="Y39" s="86"/>
-      <c r="Z39" s="96" t="s">
+      <c r="T39" s="83"/>
+      <c r="U39" s="83"/>
+      <c r="V39" s="83"/>
+      <c r="W39" s="83"/>
+      <c r="X39" s="83"/>
+      <c r="Y39" s="83"/>
+      <c r="Z39" s="98" t="s">
         <v>136</v>
       </c>
-      <c r="AA39" s="86"/>
-      <c r="AB39" s="86"/>
-      <c r="AC39" s="86"/>
-      <c r="AD39" s="86"/>
-      <c r="AE39" s="86"/>
-      <c r="AF39" s="86"/>
-      <c r="AG39" s="96" t="s">
+      <c r="AA39" s="83"/>
+      <c r="AB39" s="83"/>
+      <c r="AC39" s="83"/>
+      <c r="AD39" s="83"/>
+      <c r="AE39" s="83"/>
+      <c r="AF39" s="83"/>
+      <c r="AG39" s="98" t="s">
         <v>137</v>
       </c>
-      <c r="AH39" s="86"/>
-      <c r="AI39" s="86"/>
-      <c r="AJ39" s="86"/>
-      <c r="AK39" s="86"/>
-      <c r="AL39" s="86"/>
-      <c r="AM39" s="86"/>
+      <c r="AH39" s="83"/>
+      <c r="AI39" s="83"/>
+      <c r="AJ39" s="83"/>
+      <c r="AK39" s="83"/>
+      <c r="AL39" s="83"/>
+      <c r="AM39" s="83"/>
     </row>
     <row r="40" spans="1:39" ht="15" customHeight="1">
-      <c r="A40" s="96"/>
-      <c r="B40" s="96"/>
-      <c r="C40" s="96"/>
-      <c r="D40" s="96"/>
-      <c r="E40" s="96"/>
-      <c r="F40" s="86"/>
-      <c r="G40" s="86"/>
-      <c r="H40" s="86"/>
-      <c r="I40" s="86"/>
-      <c r="J40" s="86"/>
-      <c r="K40" s="86"/>
-      <c r="L40" s="96"/>
-      <c r="M40" s="86"/>
-      <c r="N40" s="86"/>
-      <c r="O40" s="86"/>
-      <c r="P40" s="86"/>
-      <c r="Q40" s="86"/>
-      <c r="R40" s="86"/>
-      <c r="S40" s="96"/>
-      <c r="T40" s="86"/>
-      <c r="U40" s="86"/>
-      <c r="V40" s="86"/>
-      <c r="W40" s="86"/>
-      <c r="X40" s="86"/>
-      <c r="Y40" s="86"/>
-      <c r="Z40" s="96"/>
-      <c r="AA40" s="86"/>
-      <c r="AB40" s="86"/>
-      <c r="AC40" s="86"/>
-      <c r="AD40" s="86"/>
-      <c r="AE40" s="86"/>
-      <c r="AF40" s="86"/>
-      <c r="AG40" s="96"/>
-      <c r="AH40" s="86"/>
-      <c r="AI40" s="86"/>
-      <c r="AJ40" s="86"/>
-      <c r="AK40" s="86"/>
-      <c r="AL40" s="86"/>
-      <c r="AM40" s="86"/>
+      <c r="A40" s="98"/>
+      <c r="B40" s="98"/>
+      <c r="C40" s="98"/>
+      <c r="D40" s="98"/>
+      <c r="E40" s="98"/>
+      <c r="F40" s="83"/>
+      <c r="G40" s="83"/>
+      <c r="H40" s="83"/>
+      <c r="I40" s="83"/>
+      <c r="J40" s="83"/>
+      <c r="K40" s="83"/>
+      <c r="L40" s="98"/>
+      <c r="M40" s="83"/>
+      <c r="N40" s="83"/>
+      <c r="O40" s="83"/>
+      <c r="P40" s="83"/>
+      <c r="Q40" s="83"/>
+      <c r="R40" s="83"/>
+      <c r="S40" s="98"/>
+      <c r="T40" s="83"/>
+      <c r="U40" s="83"/>
+      <c r="V40" s="83"/>
+      <c r="W40" s="83"/>
+      <c r="X40" s="83"/>
+      <c r="Y40" s="83"/>
+      <c r="Z40" s="98"/>
+      <c r="AA40" s="83"/>
+      <c r="AB40" s="83"/>
+      <c r="AC40" s="83"/>
+      <c r="AD40" s="83"/>
+      <c r="AE40" s="83"/>
+      <c r="AF40" s="83"/>
+      <c r="AG40" s="98"/>
+      <c r="AH40" s="83"/>
+      <c r="AI40" s="83"/>
+      <c r="AJ40" s="83"/>
+      <c r="AK40" s="83"/>
+      <c r="AL40" s="83"/>
+      <c r="AM40" s="83"/>
     </row>
     <row r="41" spans="1:39" ht="15" customHeight="1">
-      <c r="A41" s="96"/>
-      <c r="B41" s="96"/>
-      <c r="C41" s="96"/>
-      <c r="D41" s="96"/>
-      <c r="E41" s="96"/>
-      <c r="F41" s="86"/>
-      <c r="G41" s="86"/>
-      <c r="H41" s="86"/>
-      <c r="I41" s="86"/>
-      <c r="J41" s="86"/>
-      <c r="K41" s="86"/>
-      <c r="L41" s="96"/>
-      <c r="M41" s="86"/>
-      <c r="N41" s="86"/>
-      <c r="O41" s="86"/>
-      <c r="P41" s="86"/>
-      <c r="Q41" s="86"/>
-      <c r="R41" s="86"/>
-      <c r="S41" s="96"/>
-      <c r="T41" s="86"/>
-      <c r="U41" s="86"/>
-      <c r="V41" s="86"/>
-      <c r="W41" s="86"/>
-      <c r="X41" s="86"/>
-      <c r="Y41" s="86"/>
-      <c r="Z41" s="96"/>
-      <c r="AA41" s="86"/>
-      <c r="AB41" s="86"/>
-      <c r="AC41" s="86"/>
-      <c r="AD41" s="86"/>
-      <c r="AE41" s="86"/>
-      <c r="AF41" s="86"/>
-      <c r="AG41" s="96"/>
-      <c r="AH41" s="86"/>
-      <c r="AI41" s="86"/>
-      <c r="AJ41" s="86"/>
-      <c r="AK41" s="86"/>
-      <c r="AL41" s="86"/>
-      <c r="AM41" s="86"/>
+      <c r="A41" s="98"/>
+      <c r="B41" s="98"/>
+      <c r="C41" s="98"/>
+      <c r="D41" s="98"/>
+      <c r="E41" s="98"/>
+      <c r="F41" s="83"/>
+      <c r="G41" s="83"/>
+      <c r="H41" s="83"/>
+      <c r="I41" s="83"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="83"/>
+      <c r="L41" s="98"/>
+      <c r="M41" s="83"/>
+      <c r="N41" s="83"/>
+      <c r="O41" s="83"/>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83"/>
+      <c r="R41" s="83"/>
+      <c r="S41" s="98"/>
+      <c r="T41" s="83"/>
+      <c r="U41" s="83"/>
+      <c r="V41" s="83"/>
+      <c r="W41" s="83"/>
+      <c r="X41" s="83"/>
+      <c r="Y41" s="83"/>
+      <c r="Z41" s="98"/>
+      <c r="AA41" s="83"/>
+      <c r="AB41" s="83"/>
+      <c r="AC41" s="83"/>
+      <c r="AD41" s="83"/>
+      <c r="AE41" s="83"/>
+      <c r="AF41" s="83"/>
+      <c r="AG41" s="98"/>
+      <c r="AH41" s="83"/>
+      <c r="AI41" s="83"/>
+      <c r="AJ41" s="83"/>
+      <c r="AK41" s="83"/>
+      <c r="AL41" s="83"/>
+      <c r="AM41" s="83"/>
     </row>
     <row r="42" spans="1:39" ht="15" customHeight="1">
-      <c r="A42" s="96" t="s">
+      <c r="A42" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="B42" s="96"/>
-      <c r="C42" s="96"/>
-      <c r="D42" s="96"/>
-      <c r="E42" s="96" t="s">
+      <c r="B42" s="98"/>
+      <c r="C42" s="98"/>
+      <c r="D42" s="98"/>
+      <c r="E42" s="98" t="s">
         <v>138</v>
       </c>
-      <c r="F42" s="86"/>
-      <c r="G42" s="86"/>
-      <c r="H42" s="86"/>
-      <c r="I42" s="86"/>
-      <c r="J42" s="86"/>
-      <c r="K42" s="86"/>
-      <c r="L42" s="96" t="s">
+      <c r="F42" s="83"/>
+      <c r="G42" s="83"/>
+      <c r="H42" s="83"/>
+      <c r="I42" s="83"/>
+      <c r="J42" s="83"/>
+      <c r="K42" s="83"/>
+      <c r="L42" s="98" t="s">
         <v>139</v>
       </c>
-      <c r="M42" s="86"/>
-      <c r="N42" s="86"/>
-      <c r="O42" s="86"/>
-      <c r="P42" s="86"/>
-      <c r="Q42" s="86"/>
-      <c r="R42" s="86"/>
-      <c r="S42" s="96" t="s">
+      <c r="M42" s="83"/>
+      <c r="N42" s="83"/>
+      <c r="O42" s="83"/>
+      <c r="P42" s="83"/>
+      <c r="Q42" s="83"/>
+      <c r="R42" s="83"/>
+      <c r="S42" s="98" t="s">
         <v>140</v>
       </c>
-      <c r="T42" s="86"/>
-      <c r="U42" s="86"/>
-      <c r="V42" s="86"/>
-      <c r="W42" s="86"/>
-      <c r="X42" s="86"/>
-      <c r="Y42" s="86"/>
-      <c r="Z42" s="96" t="s">
+      <c r="T42" s="83"/>
+      <c r="U42" s="83"/>
+      <c r="V42" s="83"/>
+      <c r="W42" s="83"/>
+      <c r="X42" s="83"/>
+      <c r="Y42" s="83"/>
+      <c r="Z42" s="98" t="s">
         <v>141</v>
       </c>
-      <c r="AA42" s="86"/>
-      <c r="AB42" s="86"/>
-      <c r="AC42" s="86"/>
-      <c r="AD42" s="86"/>
-      <c r="AE42" s="86"/>
-      <c r="AF42" s="86"/>
-      <c r="AG42" s="96" t="s">
+      <c r="AA42" s="83"/>
+      <c r="AB42" s="83"/>
+      <c r="AC42" s="83"/>
+      <c r="AD42" s="83"/>
+      <c r="AE42" s="83"/>
+      <c r="AF42" s="83"/>
+      <c r="AG42" s="98" t="s">
         <v>142</v>
       </c>
-      <c r="AH42" s="86"/>
-      <c r="AI42" s="86"/>
-      <c r="AJ42" s="86"/>
-      <c r="AK42" s="86"/>
-      <c r="AL42" s="86"/>
-      <c r="AM42" s="86"/>
+      <c r="AH42" s="83"/>
+      <c r="AI42" s="83"/>
+      <c r="AJ42" s="83"/>
+      <c r="AK42" s="83"/>
+      <c r="AL42" s="83"/>
+      <c r="AM42" s="83"/>
     </row>
     <row r="43" spans="1:39" ht="15" customHeight="1">
-      <c r="A43" s="96"/>
-      <c r="B43" s="96"/>
-      <c r="C43" s="96"/>
-      <c r="D43" s="96"/>
-      <c r="E43" s="96"/>
-      <c r="F43" s="86"/>
-      <c r="G43" s="86"/>
-      <c r="H43" s="86"/>
-      <c r="I43" s="86"/>
-      <c r="J43" s="86"/>
-      <c r="K43" s="86"/>
-      <c r="L43" s="96"/>
-      <c r="M43" s="86"/>
-      <c r="N43" s="86"/>
-      <c r="O43" s="86"/>
-      <c r="P43" s="86"/>
-      <c r="Q43" s="86"/>
-      <c r="R43" s="86"/>
-      <c r="S43" s="96"/>
-      <c r="T43" s="86"/>
-      <c r="U43" s="86"/>
-      <c r="V43" s="86"/>
-      <c r="W43" s="86"/>
-      <c r="X43" s="86"/>
-      <c r="Y43" s="86"/>
-      <c r="Z43" s="96"/>
-      <c r="AA43" s="86"/>
-      <c r="AB43" s="86"/>
-      <c r="AC43" s="86"/>
-      <c r="AD43" s="86"/>
-      <c r="AE43" s="86"/>
-      <c r="AF43" s="86"/>
-      <c r="AG43" s="96"/>
-      <c r="AH43" s="86"/>
-      <c r="AI43" s="86"/>
-      <c r="AJ43" s="86"/>
-      <c r="AK43" s="86"/>
-      <c r="AL43" s="86"/>
-      <c r="AM43" s="86"/>
+      <c r="A43" s="98"/>
+      <c r="B43" s="98"/>
+      <c r="C43" s="98"/>
+      <c r="D43" s="98"/>
+      <c r="E43" s="98"/>
+      <c r="F43" s="83"/>
+      <c r="G43" s="83"/>
+      <c r="H43" s="83"/>
+      <c r="I43" s="83"/>
+      <c r="J43" s="83"/>
+      <c r="K43" s="83"/>
+      <c r="L43" s="98"/>
+      <c r="M43" s="83"/>
+      <c r="N43" s="83"/>
+      <c r="O43" s="83"/>
+      <c r="P43" s="83"/>
+      <c r="Q43" s="83"/>
+      <c r="R43" s="83"/>
+      <c r="S43" s="98"/>
+      <c r="T43" s="83"/>
+      <c r="U43" s="83"/>
+      <c r="V43" s="83"/>
+      <c r="W43" s="83"/>
+      <c r="X43" s="83"/>
+      <c r="Y43" s="83"/>
+      <c r="Z43" s="98"/>
+      <c r="AA43" s="83"/>
+      <c r="AB43" s="83"/>
+      <c r="AC43" s="83"/>
+      <c r="AD43" s="83"/>
+      <c r="AE43" s="83"/>
+      <c r="AF43" s="83"/>
+      <c r="AG43" s="98"/>
+      <c r="AH43" s="83"/>
+      <c r="AI43" s="83"/>
+      <c r="AJ43" s="83"/>
+      <c r="AK43" s="83"/>
+      <c r="AL43" s="83"/>
+      <c r="AM43" s="83"/>
     </row>
     <row r="44" spans="1:39" ht="15" customHeight="1">
-      <c r="A44" s="96"/>
-      <c r="B44" s="96"/>
-      <c r="C44" s="96"/>
-      <c r="D44" s="96"/>
-      <c r="E44" s="96"/>
-      <c r="F44" s="86"/>
-      <c r="G44" s="86"/>
-      <c r="H44" s="86"/>
-      <c r="I44" s="86"/>
-      <c r="J44" s="86"/>
-      <c r="K44" s="86"/>
-      <c r="L44" s="96"/>
-      <c r="M44" s="86"/>
-      <c r="N44" s="86"/>
-      <c r="O44" s="86"/>
-      <c r="P44" s="86"/>
-      <c r="Q44" s="86"/>
-      <c r="R44" s="86"/>
-      <c r="S44" s="96"/>
-      <c r="T44" s="86"/>
-      <c r="U44" s="86"/>
-      <c r="V44" s="86"/>
-      <c r="W44" s="86"/>
-      <c r="X44" s="86"/>
-      <c r="Y44" s="86"/>
-      <c r="Z44" s="96"/>
-      <c r="AA44" s="86"/>
-      <c r="AB44" s="86"/>
-      <c r="AC44" s="86"/>
-      <c r="AD44" s="86"/>
-      <c r="AE44" s="86"/>
-      <c r="AF44" s="86"/>
-      <c r="AG44" s="96"/>
-      <c r="AH44" s="86"/>
-      <c r="AI44" s="86"/>
-      <c r="AJ44" s="86"/>
-      <c r="AK44" s="86"/>
-      <c r="AL44" s="86"/>
-      <c r="AM44" s="86"/>
+      <c r="A44" s="98"/>
+      <c r="B44" s="98"/>
+      <c r="C44" s="98"/>
+      <c r="D44" s="98"/>
+      <c r="E44" s="98"/>
+      <c r="F44" s="83"/>
+      <c r="G44" s="83"/>
+      <c r="H44" s="83"/>
+      <c r="I44" s="83"/>
+      <c r="J44" s="83"/>
+      <c r="K44" s="83"/>
+      <c r="L44" s="98"/>
+      <c r="M44" s="83"/>
+      <c r="N44" s="83"/>
+      <c r="O44" s="83"/>
+      <c r="P44" s="83"/>
+      <c r="Q44" s="83"/>
+      <c r="R44" s="83"/>
+      <c r="S44" s="98"/>
+      <c r="T44" s="83"/>
+      <c r="U44" s="83"/>
+      <c r="V44" s="83"/>
+      <c r="W44" s="83"/>
+      <c r="X44" s="83"/>
+      <c r="Y44" s="83"/>
+      <c r="Z44" s="98"/>
+      <c r="AA44" s="83"/>
+      <c r="AB44" s="83"/>
+      <c r="AC44" s="83"/>
+      <c r="AD44" s="83"/>
+      <c r="AE44" s="83"/>
+      <c r="AF44" s="83"/>
+      <c r="AG44" s="98"/>
+      <c r="AH44" s="83"/>
+      <c r="AI44" s="83"/>
+      <c r="AJ44" s="83"/>
+      <c r="AK44" s="83"/>
+      <c r="AL44" s="83"/>
+      <c r="AM44" s="83"/>
     </row>
     <row r="45" spans="1:39" ht="15" customHeight="1">
-      <c r="A45" s="99" t="s">
+      <c r="A45" s="95" t="s">
         <v>150</v>
       </c>
-      <c r="B45" s="99"/>
-      <c r="C45" s="99"/>
-      <c r="D45" s="99"/>
-      <c r="E45" s="99"/>
-      <c r="F45" s="99"/>
-      <c r="G45" s="99"/>
-      <c r="H45" s="99"/>
-      <c r="I45" s="99"/>
-      <c r="J45" s="99"/>
-      <c r="K45" s="99"/>
-      <c r="L45" s="99"/>
-      <c r="M45" s="99"/>
-      <c r="N45" s="99"/>
-      <c r="O45" s="99"/>
-      <c r="P45" s="99"/>
-      <c r="Q45" s="99"/>
-      <c r="R45" s="99"/>
-      <c r="S45" s="99"/>
-      <c r="T45" s="99"/>
-      <c r="U45" s="99"/>
-      <c r="V45" s="99"/>
-      <c r="W45" s="99"/>
-      <c r="X45" s="99"/>
-      <c r="Y45" s="99"/>
-      <c r="Z45" s="99"/>
-      <c r="AA45" s="99"/>
-      <c r="AB45" s="99"/>
-      <c r="AC45" s="99"/>
-      <c r="AD45" s="99"/>
-      <c r="AE45" s="99"/>
-      <c r="AF45" s="99"/>
-      <c r="AG45" s="99"/>
-      <c r="AH45" s="99"/>
-      <c r="AI45" s="99"/>
-      <c r="AJ45" s="99"/>
-      <c r="AK45" s="99"/>
-      <c r="AL45" s="99"/>
-      <c r="AM45" s="99"/>
+      <c r="B45" s="95"/>
+      <c r="C45" s="95"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
+      <c r="F45" s="95"/>
+      <c r="G45" s="95"/>
+      <c r="H45" s="95"/>
+      <c r="I45" s="95"/>
+      <c r="J45" s="95"/>
+      <c r="K45" s="95"/>
+      <c r="L45" s="95"/>
+      <c r="M45" s="95"/>
+      <c r="N45" s="95"/>
+      <c r="O45" s="95"/>
+      <c r="P45" s="95"/>
+      <c r="Q45" s="95"/>
+      <c r="R45" s="95"/>
+      <c r="S45" s="95"/>
+      <c r="T45" s="95"/>
+      <c r="U45" s="95"/>
+      <c r="V45" s="95"/>
+      <c r="W45" s="95"/>
+      <c r="X45" s="95"/>
+      <c r="Y45" s="95"/>
+      <c r="Z45" s="95"/>
+      <c r="AA45" s="95"/>
+      <c r="AB45" s="95"/>
+      <c r="AC45" s="95"/>
+      <c r="AD45" s="95"/>
+      <c r="AE45" s="95"/>
+      <c r="AF45" s="95"/>
+      <c r="AG45" s="95"/>
+      <c r="AH45" s="95"/>
+      <c r="AI45" s="95"/>
+      <c r="AJ45" s="95"/>
+      <c r="AK45" s="95"/>
+      <c r="AL45" s="95"/>
+      <c r="AM45" s="95"/>
     </row>
     <row r="46" spans="1:39" ht="15" customHeight="1">
-      <c r="A46" s="99" t="s">
+      <c r="A46" s="95" t="s">
         <v>151</v>
       </c>
-      <c r="B46" s="99"/>
-      <c r="C46" s="99"/>
-      <c r="D46" s="99"/>
-      <c r="E46" s="99"/>
-      <c r="F46" s="99"/>
-      <c r="G46" s="99"/>
-      <c r="H46" s="99"/>
-      <c r="I46" s="99"/>
-      <c r="J46" s="99"/>
-      <c r="K46" s="99"/>
-      <c r="L46" s="99"/>
-      <c r="M46" s="99"/>
-      <c r="N46" s="99"/>
-      <c r="O46" s="99"/>
-      <c r="P46" s="99"/>
-      <c r="Q46" s="99"/>
-      <c r="R46" s="99"/>
-      <c r="S46" s="99"/>
-      <c r="T46" s="99"/>
-      <c r="U46" s="99"/>
-      <c r="V46" s="99"/>
-      <c r="W46" s="99"/>
-      <c r="X46" s="99"/>
-      <c r="Y46" s="99"/>
-      <c r="Z46" s="99"/>
-      <c r="AA46" s="99"/>
-      <c r="AB46" s="99"/>
-      <c r="AC46" s="99"/>
-      <c r="AD46" s="99"/>
-      <c r="AE46" s="99"/>
-      <c r="AF46" s="99"/>
-      <c r="AG46" s="99"/>
-      <c r="AH46" s="99"/>
-      <c r="AI46" s="99"/>
-      <c r="AJ46" s="99"/>
-      <c r="AK46" s="99"/>
-      <c r="AL46" s="99"/>
-      <c r="AM46" s="99"/>
+      <c r="B46" s="95"/>
+      <c r="C46" s="95"/>
+      <c r="D46" s="95"/>
+      <c r="E46" s="95"/>
+      <c r="F46" s="95"/>
+      <c r="G46" s="95"/>
+      <c r="H46" s="95"/>
+      <c r="I46" s="95"/>
+      <c r="J46" s="95"/>
+      <c r="K46" s="95"/>
+      <c r="L46" s="95"/>
+      <c r="M46" s="95"/>
+      <c r="N46" s="95"/>
+      <c r="O46" s="95"/>
+      <c r="P46" s="95"/>
+      <c r="Q46" s="95"/>
+      <c r="R46" s="95"/>
+      <c r="S46" s="95"/>
+      <c r="T46" s="95"/>
+      <c r="U46" s="95"/>
+      <c r="V46" s="95"/>
+      <c r="W46" s="95"/>
+      <c r="X46" s="95"/>
+      <c r="Y46" s="95"/>
+      <c r="Z46" s="95"/>
+      <c r="AA46" s="95"/>
+      <c r="AB46" s="95"/>
+      <c r="AC46" s="95"/>
+      <c r="AD46" s="95"/>
+      <c r="AE46" s="95"/>
+      <c r="AF46" s="95"/>
+      <c r="AG46" s="95"/>
+      <c r="AH46" s="95"/>
+      <c r="AI46" s="95"/>
+      <c r="AJ46" s="95"/>
+      <c r="AK46" s="95"/>
+      <c r="AL46" s="95"/>
+      <c r="AM46" s="95"/>
     </row>
     <row r="47" spans="1:39" ht="15" customHeight="1">
-      <c r="A47" s="100" t="s">
+      <c r="A47" s="96" t="s">
         <v>152</v>
       </c>
-      <c r="B47" s="101"/>
-      <c r="C47" s="101"/>
-      <c r="D47" s="101"/>
-      <c r="E47" s="101"/>
-      <c r="F47" s="101"/>
-      <c r="G47" s="101"/>
-      <c r="H47" s="101"/>
-      <c r="I47" s="101"/>
-      <c r="J47" s="101"/>
-      <c r="K47" s="101"/>
-      <c r="L47" s="101"/>
-      <c r="M47" s="101"/>
-      <c r="N47" s="101"/>
-      <c r="O47" s="101"/>
-      <c r="P47" s="101"/>
-      <c r="Q47" s="101"/>
-      <c r="R47" s="101"/>
-      <c r="S47" s="101"/>
-      <c r="T47" s="101"/>
-      <c r="U47" s="101"/>
-      <c r="V47" s="101"/>
-      <c r="W47" s="101"/>
-      <c r="X47" s="101"/>
-      <c r="Y47" s="101"/>
-      <c r="Z47" s="101"/>
-      <c r="AA47" s="101"/>
-      <c r="AB47" s="101"/>
-      <c r="AC47" s="101"/>
-      <c r="AD47" s="101"/>
-      <c r="AE47" s="101"/>
-      <c r="AF47" s="101"/>
-      <c r="AG47" s="101"/>
-      <c r="AH47" s="101"/>
-      <c r="AI47" s="101"/>
-      <c r="AJ47" s="101"/>
-      <c r="AK47" s="101"/>
-      <c r="AL47" s="101"/>
-      <c r="AM47" s="101"/>
+      <c r="B47" s="97"/>
+      <c r="C47" s="97"/>
+      <c r="D47" s="97"/>
+      <c r="E47" s="97"/>
+      <c r="F47" s="97"/>
+      <c r="G47" s="97"/>
+      <c r="H47" s="97"/>
+      <c r="I47" s="97"/>
+      <c r="J47" s="97"/>
+      <c r="K47" s="97"/>
+      <c r="L47" s="97"/>
+      <c r="M47" s="97"/>
+      <c r="N47" s="97"/>
+      <c r="O47" s="97"/>
+      <c r="P47" s="97"/>
+      <c r="Q47" s="97"/>
+      <c r="R47" s="97"/>
+      <c r="S47" s="97"/>
+      <c r="T47" s="97"/>
+      <c r="U47" s="97"/>
+      <c r="V47" s="97"/>
+      <c r="W47" s="97"/>
+      <c r="X47" s="97"/>
+      <c r="Y47" s="97"/>
+      <c r="Z47" s="97"/>
+      <c r="AA47" s="97"/>
+      <c r="AB47" s="97"/>
+      <c r="AC47" s="97"/>
+      <c r="AD47" s="97"/>
+      <c r="AE47" s="97"/>
+      <c r="AF47" s="97"/>
+      <c r="AG47" s="97"/>
+      <c r="AH47" s="97"/>
+      <c r="AI47" s="97"/>
+      <c r="AJ47" s="97"/>
+      <c r="AK47" s="97"/>
+      <c r="AL47" s="97"/>
+      <c r="AM47" s="97"/>
     </row>
     <row r="48" spans="1:39" ht="15" customHeight="1">
-      <c r="A48" s="101"/>
-      <c r="B48" s="101"/>
-      <c r="C48" s="101"/>
-      <c r="D48" s="101"/>
-      <c r="E48" s="101"/>
-      <c r="F48" s="101"/>
-      <c r="G48" s="101"/>
-      <c r="H48" s="101"/>
-      <c r="I48" s="101"/>
-      <c r="J48" s="101"/>
-      <c r="K48" s="101"/>
-      <c r="L48" s="101"/>
-      <c r="M48" s="101"/>
-      <c r="N48" s="101"/>
-      <c r="O48" s="101"/>
-      <c r="P48" s="101"/>
-      <c r="Q48" s="101"/>
-      <c r="R48" s="101"/>
-      <c r="S48" s="101"/>
-      <c r="T48" s="101"/>
-      <c r="U48" s="101"/>
-      <c r="V48" s="101"/>
-      <c r="W48" s="101"/>
-      <c r="X48" s="101"/>
-      <c r="Y48" s="101"/>
-      <c r="Z48" s="101"/>
-      <c r="AA48" s="101"/>
-      <c r="AB48" s="101"/>
-      <c r="AC48" s="101"/>
-      <c r="AD48" s="101"/>
-      <c r="AE48" s="101"/>
-      <c r="AF48" s="101"/>
-      <c r="AG48" s="101"/>
-      <c r="AH48" s="101"/>
-      <c r="AI48" s="101"/>
-      <c r="AJ48" s="101"/>
-      <c r="AK48" s="101"/>
-      <c r="AL48" s="101"/>
-      <c r="AM48" s="101"/>
+      <c r="A48" s="97"/>
+      <c r="B48" s="97"/>
+      <c r="C48" s="97"/>
+      <c r="D48" s="97"/>
+      <c r="E48" s="97"/>
+      <c r="F48" s="97"/>
+      <c r="G48" s="97"/>
+      <c r="H48" s="97"/>
+      <c r="I48" s="97"/>
+      <c r="J48" s="97"/>
+      <c r="K48" s="97"/>
+      <c r="L48" s="97"/>
+      <c r="M48" s="97"/>
+      <c r="N48" s="97"/>
+      <c r="O48" s="97"/>
+      <c r="P48" s="97"/>
+      <c r="Q48" s="97"/>
+      <c r="R48" s="97"/>
+      <c r="S48" s="97"/>
+      <c r="T48" s="97"/>
+      <c r="U48" s="97"/>
+      <c r="V48" s="97"/>
+      <c r="W48" s="97"/>
+      <c r="X48" s="97"/>
+      <c r="Y48" s="97"/>
+      <c r="Z48" s="97"/>
+      <c r="AA48" s="97"/>
+      <c r="AB48" s="97"/>
+      <c r="AC48" s="97"/>
+      <c r="AD48" s="97"/>
+      <c r="AE48" s="97"/>
+      <c r="AF48" s="97"/>
+      <c r="AG48" s="97"/>
+      <c r="AH48" s="97"/>
+      <c r="AI48" s="97"/>
+      <c r="AJ48" s="97"/>
+      <c r="AK48" s="97"/>
+      <c r="AL48" s="97"/>
+      <c r="AM48" s="97"/>
     </row>
     <row r="49" spans="1:39" ht="15" customHeight="1">
-      <c r="A49" s="101"/>
-      <c r="B49" s="101"/>
-      <c r="C49" s="101"/>
-      <c r="D49" s="101"/>
-      <c r="E49" s="101"/>
-      <c r="F49" s="101"/>
-      <c r="G49" s="101"/>
-      <c r="H49" s="101"/>
-      <c r="I49" s="101"/>
-      <c r="J49" s="101"/>
-      <c r="K49" s="101"/>
-      <c r="L49" s="101"/>
-      <c r="M49" s="101"/>
-      <c r="N49" s="101"/>
-      <c r="O49" s="101"/>
-      <c r="P49" s="101"/>
-      <c r="Q49" s="101"/>
-      <c r="R49" s="101"/>
-      <c r="S49" s="101"/>
-      <c r="T49" s="101"/>
-      <c r="U49" s="101"/>
-      <c r="V49" s="101"/>
-      <c r="W49" s="101"/>
-      <c r="X49" s="101"/>
-      <c r="Y49" s="101"/>
-      <c r="Z49" s="101"/>
-      <c r="AA49" s="101"/>
-      <c r="AB49" s="101"/>
-      <c r="AC49" s="101"/>
-      <c r="AD49" s="101"/>
-      <c r="AE49" s="101"/>
-      <c r="AF49" s="101"/>
-      <c r="AG49" s="101"/>
-      <c r="AH49" s="101"/>
-      <c r="AI49" s="101"/>
-      <c r="AJ49" s="101"/>
-      <c r="AK49" s="101"/>
-      <c r="AL49" s="101"/>
-      <c r="AM49" s="101"/>
-    </row>
-    <row r="50" spans="1:39" ht="8.4499999999999993" customHeight="1">
+      <c r="A49" s="97"/>
+      <c r="B49" s="97"/>
+      <c r="C49" s="97"/>
+      <c r="D49" s="97"/>
+      <c r="E49" s="97"/>
+      <c r="F49" s="97"/>
+      <c r="G49" s="97"/>
+      <c r="H49" s="97"/>
+      <c r="I49" s="97"/>
+      <c r="J49" s="97"/>
+      <c r="K49" s="97"/>
+      <c r="L49" s="97"/>
+      <c r="M49" s="97"/>
+      <c r="N49" s="97"/>
+      <c r="O49" s="97"/>
+      <c r="P49" s="97"/>
+      <c r="Q49" s="97"/>
+      <c r="R49" s="97"/>
+      <c r="S49" s="97"/>
+      <c r="T49" s="97"/>
+      <c r="U49" s="97"/>
+      <c r="V49" s="97"/>
+      <c r="W49" s="97"/>
+      <c r="X49" s="97"/>
+      <c r="Y49" s="97"/>
+      <c r="Z49" s="97"/>
+      <c r="AA49" s="97"/>
+      <c r="AB49" s="97"/>
+      <c r="AC49" s="97"/>
+      <c r="AD49" s="97"/>
+      <c r="AE49" s="97"/>
+      <c r="AF49" s="97"/>
+      <c r="AG49" s="97"/>
+      <c r="AH49" s="97"/>
+      <c r="AI49" s="97"/>
+      <c r="AJ49" s="97"/>
+      <c r="AK49" s="97"/>
+      <c r="AL49" s="97"/>
+      <c r="AM49" s="97"/>
+    </row>
+    <row r="50" spans="1:39" ht="8.5" customHeight="1">
       <c r="A50" s="46"/>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
@@ -12686,8 +12702,8 @@
       <c r="AL56" s="7"/>
       <c r="AM56" s="7"/>
     </row>
-    <row r="57" spans="1:39" ht="13.9" customHeight="1"/>
-    <row r="58" spans="1:39" ht="13.9" customHeight="1">
+    <row r="57" spans="1:39" ht="13.95" customHeight="1"/>
+    <row r="58" spans="1:39" ht="13.95" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="15"/>
       <c r="C58" s="15"/>
@@ -12703,7 +12719,7 @@
       <c r="M58" s="15"/>
       <c r="N58" s="15"/>
     </row>
-    <row r="59" spans="1:39" ht="13.9" customHeight="1">
+    <row r="59" spans="1:39" ht="13.95" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="7"/>
       <c r="C59" s="7"/>
@@ -12737,132 +12753,32 @@
     </row>
   </sheetData>
   <mergeCells count="175">
-    <mergeCell ref="A45:AM45"/>
-    <mergeCell ref="A46:AM46"/>
-    <mergeCell ref="A47:AM49"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="E44:K44"/>
-    <mergeCell ref="L44:R44"/>
-    <mergeCell ref="S44:Y44"/>
-    <mergeCell ref="Z44:AF44"/>
-    <mergeCell ref="AG44:AM44"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="E43:K43"/>
-    <mergeCell ref="L43:R43"/>
-    <mergeCell ref="S43:Y43"/>
-    <mergeCell ref="Z43:AF43"/>
-    <mergeCell ref="AG43:AM43"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="E42:K42"/>
-    <mergeCell ref="L42:R42"/>
-    <mergeCell ref="S42:Y42"/>
-    <mergeCell ref="Z42:AF42"/>
-    <mergeCell ref="AG42:AM42"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="E41:K41"/>
-    <mergeCell ref="L41:R41"/>
-    <mergeCell ref="S41:Y41"/>
-    <mergeCell ref="Z41:AF41"/>
-    <mergeCell ref="AG41:AM41"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="E40:K40"/>
-    <mergeCell ref="L40:R40"/>
-    <mergeCell ref="S40:Y40"/>
-    <mergeCell ref="Z40:AF40"/>
-    <mergeCell ref="AG40:AM40"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="E39:K39"/>
-    <mergeCell ref="L39:R39"/>
-    <mergeCell ref="S39:Y39"/>
-    <mergeCell ref="Z39:AF39"/>
-    <mergeCell ref="AG39:AM39"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="E38:K38"/>
-    <mergeCell ref="L38:R38"/>
-    <mergeCell ref="S38:Y38"/>
-    <mergeCell ref="Z38:AF38"/>
-    <mergeCell ref="AG38:AM38"/>
-    <mergeCell ref="AG37:AM37"/>
-    <mergeCell ref="AG35:AM35"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="E36:K36"/>
-    <mergeCell ref="L36:R36"/>
-    <mergeCell ref="S36:Y36"/>
-    <mergeCell ref="Z36:AF36"/>
-    <mergeCell ref="AG36:AM36"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="E35:K35"/>
-    <mergeCell ref="L35:R35"/>
-    <mergeCell ref="S35:Y35"/>
-    <mergeCell ref="Z35:AF35"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="E37:K37"/>
-    <mergeCell ref="L37:R37"/>
-    <mergeCell ref="S37:Y37"/>
-    <mergeCell ref="Z37:AF37"/>
-    <mergeCell ref="A31:AM31"/>
-    <mergeCell ref="A32:AM32"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="E33:K33"/>
-    <mergeCell ref="L33:R33"/>
-    <mergeCell ref="S33:Y33"/>
-    <mergeCell ref="Z33:AF33"/>
-    <mergeCell ref="AG33:AM33"/>
-    <mergeCell ref="E34:K34"/>
-    <mergeCell ref="L34:R34"/>
-    <mergeCell ref="S34:Y34"/>
-    <mergeCell ref="Z34:AF34"/>
-    <mergeCell ref="AG34:AM34"/>
-    <mergeCell ref="V23:X23"/>
-    <mergeCell ref="A25:AM25"/>
-    <mergeCell ref="A26:AM26"/>
-    <mergeCell ref="A27:AM27"/>
-    <mergeCell ref="A28:AM28"/>
-    <mergeCell ref="A30:AM30"/>
-    <mergeCell ref="V24:X24"/>
-    <mergeCell ref="Y24:AA24"/>
-    <mergeCell ref="AB24:AD24"/>
-    <mergeCell ref="AE24:AG24"/>
-    <mergeCell ref="AH24:AJ24"/>
-    <mergeCell ref="AK24:AM24"/>
-    <mergeCell ref="A24:I24"/>
-    <mergeCell ref="J24:L24"/>
-    <mergeCell ref="M24:O24"/>
-    <mergeCell ref="P24:R24"/>
-    <mergeCell ref="S24:U24"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="M23:O23"/>
-    <mergeCell ref="P23:R23"/>
-    <mergeCell ref="S23:U23"/>
-    <mergeCell ref="AK22:AM22"/>
-    <mergeCell ref="Y20:AA20"/>
-    <mergeCell ref="AB20:AD20"/>
-    <mergeCell ref="AE20:AG20"/>
-    <mergeCell ref="AH20:AJ20"/>
-    <mergeCell ref="AK20:AM20"/>
-    <mergeCell ref="Y23:AA23"/>
-    <mergeCell ref="AB23:AD23"/>
-    <mergeCell ref="AE23:AG23"/>
-    <mergeCell ref="AH23:AJ23"/>
-    <mergeCell ref="AK23:AM23"/>
-    <mergeCell ref="A22:I22"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="M22:O22"/>
-    <mergeCell ref="P22:R22"/>
-    <mergeCell ref="S22:U22"/>
-    <mergeCell ref="Y19:AA19"/>
-    <mergeCell ref="AB19:AD19"/>
-    <mergeCell ref="AE19:AG19"/>
-    <mergeCell ref="AH19:AJ19"/>
-    <mergeCell ref="A20:I20"/>
-    <mergeCell ref="A19:I19"/>
-    <mergeCell ref="V22:X22"/>
-    <mergeCell ref="Y22:AA22"/>
-    <mergeCell ref="AB22:AD22"/>
-    <mergeCell ref="AE22:AG22"/>
-    <mergeCell ref="AH22:AJ22"/>
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="A10:L10"/>
+    <mergeCell ref="A11:L11"/>
+    <mergeCell ref="A9:L9"/>
+    <mergeCell ref="M7:U7"/>
+    <mergeCell ref="V7:AD7"/>
+    <mergeCell ref="AE7:AM7"/>
+    <mergeCell ref="M8:U8"/>
+    <mergeCell ref="V8:AD8"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="M11:U11"/>
+    <mergeCell ref="V11:AD11"/>
+    <mergeCell ref="AE11:AM11"/>
+    <mergeCell ref="A7:L7"/>
+    <mergeCell ref="A8:L8"/>
+    <mergeCell ref="A2:W2"/>
+    <mergeCell ref="A16:AM16"/>
+    <mergeCell ref="AE8:AM8"/>
+    <mergeCell ref="M9:U9"/>
+    <mergeCell ref="V9:AD9"/>
+    <mergeCell ref="AE9:AM9"/>
+    <mergeCell ref="M10:U10"/>
+    <mergeCell ref="V10:AD10"/>
+    <mergeCell ref="AE10:AM10"/>
+    <mergeCell ref="A17:AM17"/>
     <mergeCell ref="A18:AM18"/>
     <mergeCell ref="A21:I21"/>
     <mergeCell ref="J21:L21"/>
@@ -12886,32 +12802,132 @@
     <mergeCell ref="P19:R19"/>
     <mergeCell ref="S19:U19"/>
     <mergeCell ref="V19:X19"/>
-    <mergeCell ref="A16:AM16"/>
-    <mergeCell ref="AE8:AM8"/>
-    <mergeCell ref="M9:U9"/>
-    <mergeCell ref="V9:AD9"/>
-    <mergeCell ref="AE9:AM9"/>
-    <mergeCell ref="M10:U10"/>
-    <mergeCell ref="V10:AD10"/>
-    <mergeCell ref="AE10:AM10"/>
-    <mergeCell ref="A17:AM17"/>
-    <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="A10:L10"/>
-    <mergeCell ref="A11:L11"/>
-    <mergeCell ref="A9:L9"/>
-    <mergeCell ref="M7:U7"/>
-    <mergeCell ref="V7:AD7"/>
-    <mergeCell ref="AE7:AM7"/>
-    <mergeCell ref="M8:U8"/>
-    <mergeCell ref="V8:AD8"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="M11:U11"/>
-    <mergeCell ref="V11:AD11"/>
-    <mergeCell ref="AE11:AM11"/>
-    <mergeCell ref="A7:L7"/>
-    <mergeCell ref="A8:L8"/>
-    <mergeCell ref="A2:W2"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="M22:O22"/>
+    <mergeCell ref="P22:R22"/>
+    <mergeCell ref="S22:U22"/>
+    <mergeCell ref="Y19:AA19"/>
+    <mergeCell ref="AB19:AD19"/>
+    <mergeCell ref="AE19:AG19"/>
+    <mergeCell ref="AH19:AJ19"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="V22:X22"/>
+    <mergeCell ref="Y22:AA22"/>
+    <mergeCell ref="AB22:AD22"/>
+    <mergeCell ref="AE22:AG22"/>
+    <mergeCell ref="AH22:AJ22"/>
+    <mergeCell ref="AK22:AM22"/>
+    <mergeCell ref="Y20:AA20"/>
+    <mergeCell ref="AB20:AD20"/>
+    <mergeCell ref="AE20:AG20"/>
+    <mergeCell ref="AH20:AJ20"/>
+    <mergeCell ref="AK20:AM20"/>
+    <mergeCell ref="Y23:AA23"/>
+    <mergeCell ref="AB23:AD23"/>
+    <mergeCell ref="AE23:AG23"/>
+    <mergeCell ref="AH23:AJ23"/>
+    <mergeCell ref="AK23:AM23"/>
+    <mergeCell ref="V23:X23"/>
+    <mergeCell ref="A25:AM25"/>
+    <mergeCell ref="A26:AM26"/>
+    <mergeCell ref="A27:AM27"/>
+    <mergeCell ref="A28:AM28"/>
+    <mergeCell ref="A30:AM30"/>
+    <mergeCell ref="V24:X24"/>
+    <mergeCell ref="Y24:AA24"/>
+    <mergeCell ref="AB24:AD24"/>
+    <mergeCell ref="AE24:AG24"/>
+    <mergeCell ref="AH24:AJ24"/>
+    <mergeCell ref="AK24:AM24"/>
+    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="J24:L24"/>
+    <mergeCell ref="M24:O24"/>
+    <mergeCell ref="P24:R24"/>
+    <mergeCell ref="S24:U24"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="M23:O23"/>
+    <mergeCell ref="P23:R23"/>
+    <mergeCell ref="S23:U23"/>
+    <mergeCell ref="A31:AM31"/>
+    <mergeCell ref="A32:AM32"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="E33:K33"/>
+    <mergeCell ref="L33:R33"/>
+    <mergeCell ref="S33:Y33"/>
+    <mergeCell ref="Z33:AF33"/>
+    <mergeCell ref="AG33:AM33"/>
+    <mergeCell ref="E34:K34"/>
+    <mergeCell ref="L34:R34"/>
+    <mergeCell ref="S34:Y34"/>
+    <mergeCell ref="Z34:AF34"/>
+    <mergeCell ref="AG34:AM34"/>
+    <mergeCell ref="AG37:AM37"/>
+    <mergeCell ref="AG35:AM35"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="E36:K36"/>
+    <mergeCell ref="L36:R36"/>
+    <mergeCell ref="S36:Y36"/>
+    <mergeCell ref="Z36:AF36"/>
+    <mergeCell ref="AG36:AM36"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="E35:K35"/>
+    <mergeCell ref="L35:R35"/>
+    <mergeCell ref="S35:Y35"/>
+    <mergeCell ref="Z35:AF35"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="E37:K37"/>
+    <mergeCell ref="L37:R37"/>
+    <mergeCell ref="S37:Y37"/>
+    <mergeCell ref="Z37:AF37"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="E39:K39"/>
+    <mergeCell ref="L39:R39"/>
+    <mergeCell ref="S39:Y39"/>
+    <mergeCell ref="Z39:AF39"/>
+    <mergeCell ref="AG39:AM39"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="E38:K38"/>
+    <mergeCell ref="L38:R38"/>
+    <mergeCell ref="S38:Y38"/>
+    <mergeCell ref="Z38:AF38"/>
+    <mergeCell ref="AG38:AM38"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="E41:K41"/>
+    <mergeCell ref="L41:R41"/>
+    <mergeCell ref="S41:Y41"/>
+    <mergeCell ref="Z41:AF41"/>
+    <mergeCell ref="AG41:AM41"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="E40:K40"/>
+    <mergeCell ref="L40:R40"/>
+    <mergeCell ref="S40:Y40"/>
+    <mergeCell ref="Z40:AF40"/>
+    <mergeCell ref="AG40:AM40"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="E43:K43"/>
+    <mergeCell ref="L43:R43"/>
+    <mergeCell ref="S43:Y43"/>
+    <mergeCell ref="Z43:AF43"/>
+    <mergeCell ref="AG43:AM43"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="E42:K42"/>
+    <mergeCell ref="L42:R42"/>
+    <mergeCell ref="S42:Y42"/>
+    <mergeCell ref="Z42:AF42"/>
+    <mergeCell ref="AG42:AM42"/>
+    <mergeCell ref="A45:AM45"/>
+    <mergeCell ref="A46:AM46"/>
+    <mergeCell ref="A47:AM49"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="E44:K44"/>
+    <mergeCell ref="L44:R44"/>
+    <mergeCell ref="S44:Y44"/>
+    <mergeCell ref="Z44:AF44"/>
+    <mergeCell ref="AG44:AM44"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -12931,12 +12947,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BE5942F-1490-4247-AC39-F63BE022496D}">
   <dimension ref="A1:AM62"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.15"/>
   <cols>
-    <col min="1" max="7" width="2.375" customWidth="1"/>
+    <col min="1" max="7" width="2.35546875" customWidth="1"/>
     <col min="8" max="8" width="2" customWidth="1"/>
-    <col min="9" max="31" width="2.125" customWidth="1"/>
-    <col min="32" max="39" width="2.375" customWidth="1"/>
+    <col min="9" max="31" width="2.140625" customWidth="1"/>
+    <col min="32" max="39" width="2.35546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="15" customHeight="1">
@@ -12951,35 +12967,35 @@
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
-      <c r="M1" s="72"/>
-      <c r="N1" s="72"/>
-      <c r="O1" s="72"/>
-      <c r="P1" s="72"/>
-      <c r="Q1" s="72"/>
-      <c r="R1" s="72"/>
-      <c r="S1" s="72"/>
-      <c r="T1" s="72"/>
-      <c r="U1" s="72"/>
-      <c r="V1" s="72"/>
-      <c r="W1" s="72"/>
-      <c r="X1" s="72"/>
-      <c r="Y1" s="72"/>
-      <c r="Z1" s="72"/>
-      <c r="AA1" s="72"/>
-      <c r="AB1" s="72"/>
-      <c r="AC1" s="72"/>
-      <c r="AD1" s="72"/>
-      <c r="AE1" s="72"/>
-      <c r="AF1" s="72"/>
-      <c r="AG1" s="72"/>
-      <c r="AH1" s="72"/>
-      <c r="AI1" s="72"/>
-      <c r="AJ1" s="72"/>
-      <c r="AK1" s="72"/>
-      <c r="AL1" s="72"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="78"/>
+      <c r="AF1" s="78"/>
+      <c r="AG1" s="78"/>
+      <c r="AH1" s="78"/>
+      <c r="AI1" s="78"/>
+      <c r="AJ1" s="78"/>
+      <c r="AK1" s="78"/>
+      <c r="AL1" s="78"/>
       <c r="AM1" s="33"/>
     </row>
-    <row r="2" spans="1:39" ht="14.1" customHeight="1">
+    <row r="2" spans="1:39" ht="14.15" customHeight="1">
       <c r="A2" s="19" t="s">
         <v>153</v>
       </c>
@@ -13012,18 +13028,18 @@
       <c r="AE2" s="3"/>
       <c r="AF2" s="3"/>
     </row>
-    <row r="3" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
+    <row r="3" spans="1:39" ht="14.15" customHeight="1">
+      <c r="A3" s="71"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
@@ -13046,7 +13062,7 @@
       <c r="AE3" s="3"/>
       <c r="AF3" s="3"/>
     </row>
-    <row r="4" spans="1:39" ht="14.1" customHeight="1">
+    <row r="4" spans="1:39" ht="14.15" customHeight="1">
       <c r="A4" s="49"/>
       <c r="B4" s="49"/>
       <c r="C4" s="49"/>
@@ -13080,7 +13096,7 @@
       <c r="AE4" s="3"/>
       <c r="AF4" s="3"/>
     </row>
-    <row r="5" spans="1:39" ht="14.1" customHeight="1">
+    <row r="5" spans="1:39" ht="14.15" customHeight="1">
       <c r="A5" s="94" t="s">
         <v>171</v>
       </c>
@@ -13116,7 +13132,7 @@
       <c r="AE5" s="3"/>
       <c r="AF5" s="3"/>
     </row>
-    <row r="6" spans="1:39" ht="14.1" customHeight="1">
+    <row r="6" spans="1:39" ht="14.15" customHeight="1">
       <c r="A6" s="49"/>
       <c r="B6" s="49"/>
       <c r="C6" s="49"/>
@@ -13150,7 +13166,7 @@
       <c r="AE6" s="3"/>
       <c r="AF6" s="3"/>
     </row>
-    <row r="7" spans="1:39" ht="14.1" customHeight="1">
+    <row r="7" spans="1:39" ht="14.15" customHeight="1">
       <c r="A7" s="46" t="s">
         <v>154</v>
       </c>
@@ -13183,285 +13199,285 @@
       <c r="AE7" s="3"/>
       <c r="AF7" s="3"/>
     </row>
-    <row r="8" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A8" s="96" t="s">
+    <row r="8" spans="1:39" ht="14.15" customHeight="1">
+      <c r="A8" s="98" t="s">
         <v>155</v>
       </c>
-      <c r="B8" s="96"/>
-      <c r="C8" s="96"/>
-      <c r="D8" s="96"/>
-      <c r="E8" s="96"/>
-      <c r="F8" s="96" t="s">
+      <c r="B8" s="98"/>
+      <c r="C8" s="98"/>
+      <c r="D8" s="98"/>
+      <c r="E8" s="98"/>
+      <c r="F8" s="98" t="s">
         <v>158</v>
       </c>
-      <c r="G8" s="96"/>
-      <c r="H8" s="96"/>
-      <c r="I8" s="96"/>
-      <c r="J8" s="96"/>
-      <c r="K8" s="96"/>
-      <c r="L8" s="96"/>
-      <c r="M8" s="102" t="s">
+      <c r="G8" s="98"/>
+      <c r="H8" s="98"/>
+      <c r="I8" s="98"/>
+      <c r="J8" s="98"/>
+      <c r="K8" s="98"/>
+      <c r="L8" s="98"/>
+      <c r="M8" s="103" t="s">
         <v>172</v>
       </c>
-      <c r="N8" s="96"/>
-      <c r="O8" s="96"/>
-      <c r="P8" s="96"/>
-      <c r="Q8" s="96"/>
-      <c r="R8" s="96"/>
-      <c r="S8" s="96"/>
-      <c r="T8" s="96" t="s">
+      <c r="N8" s="98"/>
+      <c r="O8" s="98"/>
+      <c r="P8" s="98"/>
+      <c r="Q8" s="98"/>
+      <c r="R8" s="98"/>
+      <c r="S8" s="98"/>
+      <c r="T8" s="98" t="s">
         <v>160</v>
       </c>
-      <c r="U8" s="96"/>
-      <c r="V8" s="96"/>
-      <c r="W8" s="96"/>
-      <c r="X8" s="96"/>
-      <c r="Y8" s="96"/>
-      <c r="Z8" s="96"/>
-      <c r="AA8" s="96" t="s">
+      <c r="U8" s="98"/>
+      <c r="V8" s="98"/>
+      <c r="W8" s="98"/>
+      <c r="X8" s="98"/>
+      <c r="Y8" s="98"/>
+      <c r="Z8" s="98"/>
+      <c r="AA8" s="98" t="s">
         <v>161</v>
       </c>
-      <c r="AB8" s="96"/>
-      <c r="AC8" s="96"/>
-      <c r="AD8" s="96"/>
-      <c r="AE8" s="96"/>
-      <c r="AF8" s="96"/>
-      <c r="AG8" s="96"/>
-      <c r="AH8" s="96" t="s">
+      <c r="AB8" s="98"/>
+      <c r="AC8" s="98"/>
+      <c r="AD8" s="98"/>
+      <c r="AE8" s="98"/>
+      <c r="AF8" s="98"/>
+      <c r="AG8" s="98"/>
+      <c r="AH8" s="98" t="s">
         <v>162</v>
       </c>
-      <c r="AI8" s="96"/>
-      <c r="AJ8" s="96"/>
-      <c r="AK8" s="96"/>
-      <c r="AL8" s="96"/>
-      <c r="AM8" s="96"/>
-    </row>
-    <row r="9" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A9" s="96" t="s">
+      <c r="AI8" s="98"/>
+      <c r="AJ8" s="98"/>
+      <c r="AK8" s="98"/>
+      <c r="AL8" s="98"/>
+      <c r="AM8" s="98"/>
+    </row>
+    <row r="9" spans="1:39" ht="14.15" customHeight="1">
+      <c r="A9" s="98" t="s">
         <v>156</v>
       </c>
-      <c r="B9" s="96"/>
-      <c r="C9" s="96"/>
-      <c r="D9" s="96"/>
-      <c r="E9" s="96"/>
-      <c r="F9" s="96"/>
-      <c r="G9" s="96"/>
-      <c r="H9" s="96"/>
-      <c r="I9" s="96"/>
-      <c r="J9" s="96"/>
-      <c r="K9" s="96"/>
-      <c r="L9" s="96"/>
-      <c r="M9" s="96"/>
-      <c r="N9" s="96"/>
-      <c r="O9" s="96"/>
-      <c r="P9" s="96"/>
-      <c r="Q9" s="96"/>
-      <c r="R9" s="96"/>
-      <c r="S9" s="96"/>
-      <c r="T9" s="96"/>
-      <c r="U9" s="96"/>
-      <c r="V9" s="96"/>
-      <c r="W9" s="96"/>
-      <c r="X9" s="96"/>
-      <c r="Y9" s="96"/>
-      <c r="Z9" s="96"/>
-      <c r="AA9" s="96"/>
-      <c r="AB9" s="96"/>
-      <c r="AC9" s="96"/>
-      <c r="AD9" s="96"/>
-      <c r="AE9" s="96"/>
-      <c r="AF9" s="96"/>
-      <c r="AG9" s="96"/>
-      <c r="AH9" s="96"/>
-      <c r="AI9" s="96"/>
-      <c r="AJ9" s="96"/>
-      <c r="AK9" s="96"/>
-      <c r="AL9" s="96"/>
-      <c r="AM9" s="96"/>
-    </row>
-    <row r="10" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A10" s="96" t="s">
+      <c r="B9" s="98"/>
+      <c r="C9" s="98"/>
+      <c r="D9" s="98"/>
+      <c r="E9" s="98"/>
+      <c r="F9" s="98"/>
+      <c r="G9" s="98"/>
+      <c r="H9" s="98"/>
+      <c r="I9" s="98"/>
+      <c r="J9" s="98"/>
+      <c r="K9" s="98"/>
+      <c r="L9" s="98"/>
+      <c r="M9" s="98"/>
+      <c r="N9" s="98"/>
+      <c r="O9" s="98"/>
+      <c r="P9" s="98"/>
+      <c r="Q9" s="98"/>
+      <c r="R9" s="98"/>
+      <c r="S9" s="98"/>
+      <c r="T9" s="98"/>
+      <c r="U9" s="98"/>
+      <c r="V9" s="98"/>
+      <c r="W9" s="98"/>
+      <c r="X9" s="98"/>
+      <c r="Y9" s="98"/>
+      <c r="Z9" s="98"/>
+      <c r="AA9" s="98"/>
+      <c r="AB9" s="98"/>
+      <c r="AC9" s="98"/>
+      <c r="AD9" s="98"/>
+      <c r="AE9" s="98"/>
+      <c r="AF9" s="98"/>
+      <c r="AG9" s="98"/>
+      <c r="AH9" s="98"/>
+      <c r="AI9" s="98"/>
+      <c r="AJ9" s="98"/>
+      <c r="AK9" s="98"/>
+      <c r="AL9" s="98"/>
+      <c r="AM9" s="98"/>
+    </row>
+    <row r="10" spans="1:39" ht="14.15" customHeight="1">
+      <c r="A10" s="98" t="s">
         <v>157</v>
       </c>
-      <c r="B10" s="96"/>
-      <c r="C10" s="96"/>
-      <c r="D10" s="96"/>
-      <c r="E10" s="96"/>
-      <c r="F10" s="96"/>
-      <c r="G10" s="96"/>
-      <c r="H10" s="96"/>
-      <c r="I10" s="96"/>
-      <c r="J10" s="96"/>
-      <c r="K10" s="96"/>
-      <c r="L10" s="96"/>
-      <c r="M10" s="96"/>
-      <c r="N10" s="96"/>
-      <c r="O10" s="96"/>
-      <c r="P10" s="96"/>
-      <c r="Q10" s="96"/>
-      <c r="R10" s="96"/>
-      <c r="S10" s="96"/>
-      <c r="T10" s="96"/>
-      <c r="U10" s="96"/>
-      <c r="V10" s="96"/>
-      <c r="W10" s="96"/>
-      <c r="X10" s="96"/>
-      <c r="Y10" s="96"/>
-      <c r="Z10" s="96"/>
-      <c r="AA10" s="96"/>
-      <c r="AB10" s="96"/>
-      <c r="AC10" s="96"/>
-      <c r="AD10" s="96"/>
-      <c r="AE10" s="96"/>
-      <c r="AF10" s="96"/>
-      <c r="AG10" s="96"/>
-      <c r="AH10" s="96"/>
-      <c r="AI10" s="96"/>
-      <c r="AJ10" s="96"/>
-      <c r="AK10" s="96"/>
-      <c r="AL10" s="96"/>
-      <c r="AM10" s="96"/>
-    </row>
-    <row r="11" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A11" s="96" t="s">
+      <c r="B10" s="98"/>
+      <c r="C10" s="98"/>
+      <c r="D10" s="98"/>
+      <c r="E10" s="98"/>
+      <c r="F10" s="98"/>
+      <c r="G10" s="98"/>
+      <c r="H10" s="98"/>
+      <c r="I10" s="98"/>
+      <c r="J10" s="98"/>
+      <c r="K10" s="98"/>
+      <c r="L10" s="98"/>
+      <c r="M10" s="98"/>
+      <c r="N10" s="98"/>
+      <c r="O10" s="98"/>
+      <c r="P10" s="98"/>
+      <c r="Q10" s="98"/>
+      <c r="R10" s="98"/>
+      <c r="S10" s="98"/>
+      <c r="T10" s="98"/>
+      <c r="U10" s="98"/>
+      <c r="V10" s="98"/>
+      <c r="W10" s="98"/>
+      <c r="X10" s="98"/>
+      <c r="Y10" s="98"/>
+      <c r="Z10" s="98"/>
+      <c r="AA10" s="98"/>
+      <c r="AB10" s="98"/>
+      <c r="AC10" s="98"/>
+      <c r="AD10" s="98"/>
+      <c r="AE10" s="98"/>
+      <c r="AF10" s="98"/>
+      <c r="AG10" s="98"/>
+      <c r="AH10" s="98"/>
+      <c r="AI10" s="98"/>
+      <c r="AJ10" s="98"/>
+      <c r="AK10" s="98"/>
+      <c r="AL10" s="98"/>
+      <c r="AM10" s="98"/>
+    </row>
+    <row r="11" spans="1:39" ht="14.15" customHeight="1">
+      <c r="A11" s="98" t="s">
         <v>155</v>
       </c>
-      <c r="B11" s="96"/>
-      <c r="C11" s="96"/>
-      <c r="D11" s="96"/>
-      <c r="E11" s="96"/>
-      <c r="F11" s="96" t="s">
+      <c r="B11" s="98"/>
+      <c r="C11" s="98"/>
+      <c r="D11" s="98"/>
+      <c r="E11" s="98"/>
+      <c r="F11" s="98" t="s">
         <v>163</v>
       </c>
-      <c r="G11" s="96"/>
-      <c r="H11" s="96"/>
-      <c r="I11" s="96"/>
-      <c r="J11" s="96"/>
-      <c r="K11" s="96"/>
-      <c r="L11" s="96"/>
-      <c r="M11" s="96" t="s">
+      <c r="G11" s="98"/>
+      <c r="H11" s="98"/>
+      <c r="I11" s="98"/>
+      <c r="J11" s="98"/>
+      <c r="K11" s="98"/>
+      <c r="L11" s="98"/>
+      <c r="M11" s="98" t="s">
         <v>164</v>
       </c>
-      <c r="N11" s="96"/>
-      <c r="O11" s="96"/>
-      <c r="P11" s="96"/>
-      <c r="Q11" s="96"/>
-      <c r="R11" s="96"/>
-      <c r="S11" s="96"/>
-      <c r="T11" s="96" t="s">
+      <c r="N11" s="98"/>
+      <c r="O11" s="98"/>
+      <c r="P11" s="98"/>
+      <c r="Q11" s="98"/>
+      <c r="R11" s="98"/>
+      <c r="S11" s="98"/>
+      <c r="T11" s="98" t="s">
         <v>165</v>
       </c>
-      <c r="U11" s="96"/>
-      <c r="V11" s="96"/>
-      <c r="W11" s="96"/>
-      <c r="X11" s="96"/>
-      <c r="Y11" s="96"/>
-      <c r="Z11" s="96"/>
-      <c r="AA11" s="96" t="s">
+      <c r="U11" s="98"/>
+      <c r="V11" s="98"/>
+      <c r="W11" s="98"/>
+      <c r="X11" s="98"/>
+      <c r="Y11" s="98"/>
+      <c r="Z11" s="98"/>
+      <c r="AA11" s="98" t="s">
         <v>166</v>
       </c>
-      <c r="AB11" s="96"/>
-      <c r="AC11" s="96"/>
-      <c r="AD11" s="96"/>
-      <c r="AE11" s="96"/>
-      <c r="AF11" s="96"/>
-      <c r="AG11" s="96"/>
-      <c r="AH11" s="96" t="s">
+      <c r="AB11" s="98"/>
+      <c r="AC11" s="98"/>
+      <c r="AD11" s="98"/>
+      <c r="AE11" s="98"/>
+      <c r="AF11" s="98"/>
+      <c r="AG11" s="98"/>
+      <c r="AH11" s="98" t="s">
         <v>167</v>
       </c>
-      <c r="AI11" s="96"/>
-      <c r="AJ11" s="96"/>
-      <c r="AK11" s="96"/>
-      <c r="AL11" s="96"/>
-      <c r="AM11" s="96"/>
-    </row>
-    <row r="12" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A12" s="96" t="s">
+      <c r="AI11" s="98"/>
+      <c r="AJ11" s="98"/>
+      <c r="AK11" s="98"/>
+      <c r="AL11" s="98"/>
+      <c r="AM11" s="98"/>
+    </row>
+    <row r="12" spans="1:39" ht="14.15" customHeight="1">
+      <c r="A12" s="98" t="s">
         <v>156</v>
       </c>
-      <c r="B12" s="96"/>
-      <c r="C12" s="96"/>
-      <c r="D12" s="96"/>
-      <c r="E12" s="96"/>
-      <c r="F12" s="96"/>
-      <c r="G12" s="96"/>
-      <c r="H12" s="96"/>
-      <c r="I12" s="96"/>
-      <c r="J12" s="96"/>
-      <c r="K12" s="96"/>
-      <c r="L12" s="96"/>
-      <c r="M12" s="96"/>
-      <c r="N12" s="96"/>
-      <c r="O12" s="96"/>
-      <c r="P12" s="96"/>
-      <c r="Q12" s="96"/>
-      <c r="R12" s="96"/>
-      <c r="S12" s="96"/>
-      <c r="T12" s="96"/>
-      <c r="U12" s="96"/>
-      <c r="V12" s="96"/>
-      <c r="W12" s="96"/>
-      <c r="X12" s="96"/>
-      <c r="Y12" s="96"/>
-      <c r="Z12" s="96"/>
-      <c r="AA12" s="96"/>
-      <c r="AB12" s="96"/>
-      <c r="AC12" s="96"/>
-      <c r="AD12" s="96"/>
-      <c r="AE12" s="96"/>
-      <c r="AF12" s="96"/>
-      <c r="AG12" s="96"/>
-      <c r="AH12" s="96"/>
-      <c r="AI12" s="96"/>
-      <c r="AJ12" s="96"/>
-      <c r="AK12" s="96"/>
-      <c r="AL12" s="96"/>
-      <c r="AM12" s="96"/>
-    </row>
-    <row r="13" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A13" s="96" t="s">
+      <c r="B12" s="98"/>
+      <c r="C12" s="98"/>
+      <c r="D12" s="98"/>
+      <c r="E12" s="98"/>
+      <c r="F12" s="98"/>
+      <c r="G12" s="98"/>
+      <c r="H12" s="98"/>
+      <c r="I12" s="98"/>
+      <c r="J12" s="98"/>
+      <c r="K12" s="98"/>
+      <c r="L12" s="98"/>
+      <c r="M12" s="98"/>
+      <c r="N12" s="98"/>
+      <c r="O12" s="98"/>
+      <c r="P12" s="98"/>
+      <c r="Q12" s="98"/>
+      <c r="R12" s="98"/>
+      <c r="S12" s="98"/>
+      <c r="T12" s="98"/>
+      <c r="U12" s="98"/>
+      <c r="V12" s="98"/>
+      <c r="W12" s="98"/>
+      <c r="X12" s="98"/>
+      <c r="Y12" s="98"/>
+      <c r="Z12" s="98"/>
+      <c r="AA12" s="98"/>
+      <c r="AB12" s="98"/>
+      <c r="AC12" s="98"/>
+      <c r="AD12" s="98"/>
+      <c r="AE12" s="98"/>
+      <c r="AF12" s="98"/>
+      <c r="AG12" s="98"/>
+      <c r="AH12" s="98"/>
+      <c r="AI12" s="98"/>
+      <c r="AJ12" s="98"/>
+      <c r="AK12" s="98"/>
+      <c r="AL12" s="98"/>
+      <c r="AM12" s="98"/>
+    </row>
+    <row r="13" spans="1:39" ht="14.15" customHeight="1">
+      <c r="A13" s="98" t="s">
         <v>157</v>
       </c>
-      <c r="B13" s="96"/>
-      <c r="C13" s="96"/>
-      <c r="D13" s="96"/>
-      <c r="E13" s="96"/>
-      <c r="F13" s="96"/>
-      <c r="G13" s="96"/>
-      <c r="H13" s="96"/>
-      <c r="I13" s="96"/>
-      <c r="J13" s="96"/>
-      <c r="K13" s="96"/>
-      <c r="L13" s="96"/>
-      <c r="M13" s="96"/>
-      <c r="N13" s="96"/>
-      <c r="O13" s="96"/>
-      <c r="P13" s="96"/>
-      <c r="Q13" s="96"/>
-      <c r="R13" s="96"/>
-      <c r="S13" s="96"/>
-      <c r="T13" s="96"/>
-      <c r="U13" s="96"/>
-      <c r="V13" s="96"/>
-      <c r="W13" s="96"/>
-      <c r="X13" s="96"/>
-      <c r="Y13" s="96"/>
-      <c r="Z13" s="96"/>
-      <c r="AA13" s="96"/>
-      <c r="AB13" s="96"/>
-      <c r="AC13" s="96"/>
-      <c r="AD13" s="96"/>
-      <c r="AE13" s="96"/>
-      <c r="AF13" s="96"/>
-      <c r="AG13" s="96"/>
-      <c r="AH13" s="96"/>
-      <c r="AI13" s="96"/>
-      <c r="AJ13" s="96"/>
-      <c r="AK13" s="96"/>
-      <c r="AL13" s="96"/>
-      <c r="AM13" s="96"/>
-    </row>
-    <row r="14" spans="1:39" ht="14.1" customHeight="1">
+      <c r="B13" s="98"/>
+      <c r="C13" s="98"/>
+      <c r="D13" s="98"/>
+      <c r="E13" s="98"/>
+      <c r="F13" s="98"/>
+      <c r="G13" s="98"/>
+      <c r="H13" s="98"/>
+      <c r="I13" s="98"/>
+      <c r="J13" s="98"/>
+      <c r="K13" s="98"/>
+      <c r="L13" s="98"/>
+      <c r="M13" s="98"/>
+      <c r="N13" s="98"/>
+      <c r="O13" s="98"/>
+      <c r="P13" s="98"/>
+      <c r="Q13" s="98"/>
+      <c r="R13" s="98"/>
+      <c r="S13" s="98"/>
+      <c r="T13" s="98"/>
+      <c r="U13" s="98"/>
+      <c r="V13" s="98"/>
+      <c r="W13" s="98"/>
+      <c r="X13" s="98"/>
+      <c r="Y13" s="98"/>
+      <c r="Z13" s="98"/>
+      <c r="AA13" s="98"/>
+      <c r="AB13" s="98"/>
+      <c r="AC13" s="98"/>
+      <c r="AD13" s="98"/>
+      <c r="AE13" s="98"/>
+      <c r="AF13" s="98"/>
+      <c r="AG13" s="98"/>
+      <c r="AH13" s="98"/>
+      <c r="AI13" s="98"/>
+      <c r="AJ13" s="98"/>
+      <c r="AK13" s="98"/>
+      <c r="AL13" s="98"/>
+      <c r="AM13" s="98"/>
+    </row>
+    <row r="14" spans="1:39" ht="14.15" customHeight="1">
       <c r="A14" s="46"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
@@ -13492,7 +13508,7 @@
       <c r="AE14" s="3"/>
       <c r="AF14" s="3"/>
     </row>
-    <row r="15" spans="1:39" ht="14.1" customHeight="1">
+    <row r="15" spans="1:39" ht="14.15" customHeight="1">
       <c r="A15" s="46" t="s">
         <v>168</v>
       </c>
@@ -13525,285 +13541,285 @@
       <c r="AE15" s="3"/>
       <c r="AF15" s="3"/>
     </row>
-    <row r="16" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A16" s="96" t="s">
+    <row r="16" spans="1:39" ht="14.15" customHeight="1">
+      <c r="A16" s="98" t="s">
         <v>155</v>
       </c>
-      <c r="B16" s="96"/>
-      <c r="C16" s="96"/>
-      <c r="D16" s="96"/>
-      <c r="E16" s="96"/>
-      <c r="F16" s="96" t="s">
+      <c r="B16" s="98"/>
+      <c r="C16" s="98"/>
+      <c r="D16" s="98"/>
+      <c r="E16" s="98"/>
+      <c r="F16" s="98" t="s">
         <v>158</v>
       </c>
-      <c r="G16" s="96"/>
-      <c r="H16" s="96"/>
-      <c r="I16" s="96"/>
-      <c r="J16" s="96"/>
-      <c r="K16" s="96"/>
-      <c r="L16" s="96"/>
-      <c r="M16" s="96" t="s">
+      <c r="G16" s="98"/>
+      <c r="H16" s="98"/>
+      <c r="I16" s="98"/>
+      <c r="J16" s="98"/>
+      <c r="K16" s="98"/>
+      <c r="L16" s="98"/>
+      <c r="M16" s="98" t="s">
         <v>159</v>
       </c>
-      <c r="N16" s="96"/>
-      <c r="O16" s="96"/>
-      <c r="P16" s="96"/>
-      <c r="Q16" s="96"/>
-      <c r="R16" s="96"/>
-      <c r="S16" s="96"/>
-      <c r="T16" s="96" t="s">
+      <c r="N16" s="98"/>
+      <c r="O16" s="98"/>
+      <c r="P16" s="98"/>
+      <c r="Q16" s="98"/>
+      <c r="R16" s="98"/>
+      <c r="S16" s="98"/>
+      <c r="T16" s="98" t="s">
         <v>160</v>
       </c>
-      <c r="U16" s="96"/>
-      <c r="V16" s="96"/>
-      <c r="W16" s="96"/>
-      <c r="X16" s="96"/>
-      <c r="Y16" s="96"/>
-      <c r="Z16" s="96"/>
-      <c r="AA16" s="96" t="s">
+      <c r="U16" s="98"/>
+      <c r="V16" s="98"/>
+      <c r="W16" s="98"/>
+      <c r="X16" s="98"/>
+      <c r="Y16" s="98"/>
+      <c r="Z16" s="98"/>
+      <c r="AA16" s="98" t="s">
         <v>161</v>
       </c>
-      <c r="AB16" s="96"/>
-      <c r="AC16" s="96"/>
-      <c r="AD16" s="96"/>
-      <c r="AE16" s="96"/>
-      <c r="AF16" s="96"/>
-      <c r="AG16" s="96"/>
-      <c r="AH16" s="96" t="s">
+      <c r="AB16" s="98"/>
+      <c r="AC16" s="98"/>
+      <c r="AD16" s="98"/>
+      <c r="AE16" s="98"/>
+      <c r="AF16" s="98"/>
+      <c r="AG16" s="98"/>
+      <c r="AH16" s="98" t="s">
         <v>162</v>
       </c>
-      <c r="AI16" s="96"/>
-      <c r="AJ16" s="96"/>
-      <c r="AK16" s="96"/>
-      <c r="AL16" s="96"/>
-      <c r="AM16" s="96"/>
-    </row>
-    <row r="17" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A17" s="96" t="s">
+      <c r="AI16" s="98"/>
+      <c r="AJ16" s="98"/>
+      <c r="AK16" s="98"/>
+      <c r="AL16" s="98"/>
+      <c r="AM16" s="98"/>
+    </row>
+    <row r="17" spans="1:39" ht="14.15" customHeight="1">
+      <c r="A17" s="98" t="s">
         <v>156</v>
       </c>
-      <c r="B17" s="96"/>
-      <c r="C17" s="96"/>
-      <c r="D17" s="96"/>
-      <c r="E17" s="96"/>
-      <c r="F17" s="96"/>
-      <c r="G17" s="96"/>
-      <c r="H17" s="96"/>
-      <c r="I17" s="96"/>
-      <c r="J17" s="96"/>
-      <c r="K17" s="96"/>
-      <c r="L17" s="96"/>
-      <c r="M17" s="96"/>
-      <c r="N17" s="96"/>
-      <c r="O17" s="96"/>
-      <c r="P17" s="96"/>
-      <c r="Q17" s="96"/>
-      <c r="R17" s="96"/>
-      <c r="S17" s="96"/>
-      <c r="T17" s="96"/>
-      <c r="U17" s="96"/>
-      <c r="V17" s="96"/>
-      <c r="W17" s="96"/>
-      <c r="X17" s="96"/>
-      <c r="Y17" s="96"/>
-      <c r="Z17" s="96"/>
-      <c r="AA17" s="96"/>
-      <c r="AB17" s="96"/>
-      <c r="AC17" s="96"/>
-      <c r="AD17" s="96"/>
-      <c r="AE17" s="96"/>
-      <c r="AF17" s="96"/>
-      <c r="AG17" s="96"/>
-      <c r="AH17" s="96"/>
-      <c r="AI17" s="96"/>
-      <c r="AJ17" s="96"/>
-      <c r="AK17" s="96"/>
-      <c r="AL17" s="96"/>
-      <c r="AM17" s="96"/>
-    </row>
-    <row r="18" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A18" s="96" t="s">
+      <c r="B17" s="98"/>
+      <c r="C17" s="98"/>
+      <c r="D17" s="98"/>
+      <c r="E17" s="98"/>
+      <c r="F17" s="98"/>
+      <c r="G17" s="98"/>
+      <c r="H17" s="98"/>
+      <c r="I17" s="98"/>
+      <c r="J17" s="98"/>
+      <c r="K17" s="98"/>
+      <c r="L17" s="98"/>
+      <c r="M17" s="98"/>
+      <c r="N17" s="98"/>
+      <c r="O17" s="98"/>
+      <c r="P17" s="98"/>
+      <c r="Q17" s="98"/>
+      <c r="R17" s="98"/>
+      <c r="S17" s="98"/>
+      <c r="T17" s="98"/>
+      <c r="U17" s="98"/>
+      <c r="V17" s="98"/>
+      <c r="W17" s="98"/>
+      <c r="X17" s="98"/>
+      <c r="Y17" s="98"/>
+      <c r="Z17" s="98"/>
+      <c r="AA17" s="98"/>
+      <c r="AB17" s="98"/>
+      <c r="AC17" s="98"/>
+      <c r="AD17" s="98"/>
+      <c r="AE17" s="98"/>
+      <c r="AF17" s="98"/>
+      <c r="AG17" s="98"/>
+      <c r="AH17" s="98"/>
+      <c r="AI17" s="98"/>
+      <c r="AJ17" s="98"/>
+      <c r="AK17" s="98"/>
+      <c r="AL17" s="98"/>
+      <c r="AM17" s="98"/>
+    </row>
+    <row r="18" spans="1:39" ht="14.15" customHeight="1">
+      <c r="A18" s="98" t="s">
         <v>157</v>
       </c>
-      <c r="B18" s="96"/>
-      <c r="C18" s="96"/>
-      <c r="D18" s="96"/>
-      <c r="E18" s="96"/>
-      <c r="F18" s="96"/>
-      <c r="G18" s="96"/>
-      <c r="H18" s="96"/>
-      <c r="I18" s="96"/>
-      <c r="J18" s="96"/>
-      <c r="K18" s="96"/>
-      <c r="L18" s="96"/>
-      <c r="M18" s="96"/>
-      <c r="N18" s="96"/>
-      <c r="O18" s="96"/>
-      <c r="P18" s="96"/>
-      <c r="Q18" s="96"/>
-      <c r="R18" s="96"/>
-      <c r="S18" s="96"/>
-      <c r="T18" s="96"/>
-      <c r="U18" s="96"/>
-      <c r="V18" s="96"/>
-      <c r="W18" s="96"/>
-      <c r="X18" s="96"/>
-      <c r="Y18" s="96"/>
-      <c r="Z18" s="96"/>
-      <c r="AA18" s="96"/>
-      <c r="AB18" s="96"/>
-      <c r="AC18" s="96"/>
-      <c r="AD18" s="96"/>
-      <c r="AE18" s="96"/>
-      <c r="AF18" s="96"/>
-      <c r="AG18" s="96"/>
-      <c r="AH18" s="96"/>
-      <c r="AI18" s="96"/>
-      <c r="AJ18" s="96"/>
-      <c r="AK18" s="96"/>
-      <c r="AL18" s="96"/>
-      <c r="AM18" s="96"/>
-    </row>
-    <row r="19" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A19" s="96" t="s">
+      <c r="B18" s="98"/>
+      <c r="C18" s="98"/>
+      <c r="D18" s="98"/>
+      <c r="E18" s="98"/>
+      <c r="F18" s="98"/>
+      <c r="G18" s="98"/>
+      <c r="H18" s="98"/>
+      <c r="I18" s="98"/>
+      <c r="J18" s="98"/>
+      <c r="K18" s="98"/>
+      <c r="L18" s="98"/>
+      <c r="M18" s="98"/>
+      <c r="N18" s="98"/>
+      <c r="O18" s="98"/>
+      <c r="P18" s="98"/>
+      <c r="Q18" s="98"/>
+      <c r="R18" s="98"/>
+      <c r="S18" s="98"/>
+      <c r="T18" s="98"/>
+      <c r="U18" s="98"/>
+      <c r="V18" s="98"/>
+      <c r="W18" s="98"/>
+      <c r="X18" s="98"/>
+      <c r="Y18" s="98"/>
+      <c r="Z18" s="98"/>
+      <c r="AA18" s="98"/>
+      <c r="AB18" s="98"/>
+      <c r="AC18" s="98"/>
+      <c r="AD18" s="98"/>
+      <c r="AE18" s="98"/>
+      <c r="AF18" s="98"/>
+      <c r="AG18" s="98"/>
+      <c r="AH18" s="98"/>
+      <c r="AI18" s="98"/>
+      <c r="AJ18" s="98"/>
+      <c r="AK18" s="98"/>
+      <c r="AL18" s="98"/>
+      <c r="AM18" s="98"/>
+    </row>
+    <row r="19" spans="1:39" ht="14.15" customHeight="1">
+      <c r="A19" s="98" t="s">
         <v>155</v>
       </c>
-      <c r="B19" s="96"/>
-      <c r="C19" s="96"/>
-      <c r="D19" s="96"/>
-      <c r="E19" s="96"/>
-      <c r="F19" s="96" t="s">
+      <c r="B19" s="98"/>
+      <c r="C19" s="98"/>
+      <c r="D19" s="98"/>
+      <c r="E19" s="98"/>
+      <c r="F19" s="98" t="s">
         <v>163</v>
       </c>
-      <c r="G19" s="96"/>
-      <c r="H19" s="96"/>
-      <c r="I19" s="96"/>
-      <c r="J19" s="96"/>
-      <c r="K19" s="96"/>
-      <c r="L19" s="96"/>
-      <c r="M19" s="96" t="s">
+      <c r="G19" s="98"/>
+      <c r="H19" s="98"/>
+      <c r="I19" s="98"/>
+      <c r="J19" s="98"/>
+      <c r="K19" s="98"/>
+      <c r="L19" s="98"/>
+      <c r="M19" s="98" t="s">
         <v>164</v>
       </c>
-      <c r="N19" s="96"/>
-      <c r="O19" s="96"/>
-      <c r="P19" s="96"/>
-      <c r="Q19" s="96"/>
-      <c r="R19" s="96"/>
-      <c r="S19" s="96"/>
-      <c r="T19" s="96" t="s">
+      <c r="N19" s="98"/>
+      <c r="O19" s="98"/>
+      <c r="P19" s="98"/>
+      <c r="Q19" s="98"/>
+      <c r="R19" s="98"/>
+      <c r="S19" s="98"/>
+      <c r="T19" s="98" t="s">
         <v>165</v>
       </c>
-      <c r="U19" s="96"/>
-      <c r="V19" s="96"/>
-      <c r="W19" s="96"/>
-      <c r="X19" s="96"/>
-      <c r="Y19" s="96"/>
-      <c r="Z19" s="96"/>
-      <c r="AA19" s="96" t="s">
+      <c r="U19" s="98"/>
+      <c r="V19" s="98"/>
+      <c r="W19" s="98"/>
+      <c r="X19" s="98"/>
+      <c r="Y19" s="98"/>
+      <c r="Z19" s="98"/>
+      <c r="AA19" s="98" t="s">
         <v>166</v>
       </c>
-      <c r="AB19" s="96"/>
-      <c r="AC19" s="96"/>
-      <c r="AD19" s="96"/>
-      <c r="AE19" s="96"/>
-      <c r="AF19" s="96"/>
-      <c r="AG19" s="96"/>
-      <c r="AH19" s="96" t="s">
+      <c r="AB19" s="98"/>
+      <c r="AC19" s="98"/>
+      <c r="AD19" s="98"/>
+      <c r="AE19" s="98"/>
+      <c r="AF19" s="98"/>
+      <c r="AG19" s="98"/>
+      <c r="AH19" s="98" t="s">
         <v>167</v>
       </c>
-      <c r="AI19" s="96"/>
-      <c r="AJ19" s="96"/>
-      <c r="AK19" s="96"/>
-      <c r="AL19" s="96"/>
-      <c r="AM19" s="96"/>
-    </row>
-    <row r="20" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A20" s="96" t="s">
+      <c r="AI19" s="98"/>
+      <c r="AJ19" s="98"/>
+      <c r="AK19" s="98"/>
+      <c r="AL19" s="98"/>
+      <c r="AM19" s="98"/>
+    </row>
+    <row r="20" spans="1:39" ht="14.15" customHeight="1">
+      <c r="A20" s="98" t="s">
         <v>156</v>
       </c>
-      <c r="B20" s="96"/>
-      <c r="C20" s="96"/>
-      <c r="D20" s="96"/>
-      <c r="E20" s="96"/>
-      <c r="F20" s="96"/>
-      <c r="G20" s="96"/>
-      <c r="H20" s="96"/>
-      <c r="I20" s="96"/>
-      <c r="J20" s="96"/>
-      <c r="K20" s="96"/>
-      <c r="L20" s="96"/>
-      <c r="M20" s="96"/>
-      <c r="N20" s="96"/>
-      <c r="O20" s="96"/>
-      <c r="P20" s="96"/>
-      <c r="Q20" s="96"/>
-      <c r="R20" s="96"/>
-      <c r="S20" s="96"/>
-      <c r="T20" s="96"/>
-      <c r="U20" s="96"/>
-      <c r="V20" s="96"/>
-      <c r="W20" s="96"/>
-      <c r="X20" s="96"/>
-      <c r="Y20" s="96"/>
-      <c r="Z20" s="96"/>
-      <c r="AA20" s="96"/>
-      <c r="AB20" s="96"/>
-      <c r="AC20" s="96"/>
-      <c r="AD20" s="96"/>
-      <c r="AE20" s="96"/>
-      <c r="AF20" s="96"/>
-      <c r="AG20" s="96"/>
-      <c r="AH20" s="96"/>
-      <c r="AI20" s="96"/>
-      <c r="AJ20" s="96"/>
-      <c r="AK20" s="96"/>
-      <c r="AL20" s="96"/>
-      <c r="AM20" s="96"/>
-    </row>
-    <row r="21" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A21" s="96" t="s">
+      <c r="B20" s="98"/>
+      <c r="C20" s="98"/>
+      <c r="D20" s="98"/>
+      <c r="E20" s="98"/>
+      <c r="F20" s="98"/>
+      <c r="G20" s="98"/>
+      <c r="H20" s="98"/>
+      <c r="I20" s="98"/>
+      <c r="J20" s="98"/>
+      <c r="K20" s="98"/>
+      <c r="L20" s="98"/>
+      <c r="M20" s="98"/>
+      <c r="N20" s="98"/>
+      <c r="O20" s="98"/>
+      <c r="P20" s="98"/>
+      <c r="Q20" s="98"/>
+      <c r="R20" s="98"/>
+      <c r="S20" s="98"/>
+      <c r="T20" s="98"/>
+      <c r="U20" s="98"/>
+      <c r="V20" s="98"/>
+      <c r="W20" s="98"/>
+      <c r="X20" s="98"/>
+      <c r="Y20" s="98"/>
+      <c r="Z20" s="98"/>
+      <c r="AA20" s="98"/>
+      <c r="AB20" s="98"/>
+      <c r="AC20" s="98"/>
+      <c r="AD20" s="98"/>
+      <c r="AE20" s="98"/>
+      <c r="AF20" s="98"/>
+      <c r="AG20" s="98"/>
+      <c r="AH20" s="98"/>
+      <c r="AI20" s="98"/>
+      <c r="AJ20" s="98"/>
+      <c r="AK20" s="98"/>
+      <c r="AL20" s="98"/>
+      <c r="AM20" s="98"/>
+    </row>
+    <row r="21" spans="1:39" ht="14.15" customHeight="1">
+      <c r="A21" s="98" t="s">
         <v>157</v>
       </c>
-      <c r="B21" s="96"/>
-      <c r="C21" s="96"/>
-      <c r="D21" s="96"/>
-      <c r="E21" s="96"/>
-      <c r="F21" s="96"/>
-      <c r="G21" s="96"/>
-      <c r="H21" s="96"/>
-      <c r="I21" s="96"/>
-      <c r="J21" s="96"/>
-      <c r="K21" s="96"/>
-      <c r="L21" s="96"/>
-      <c r="M21" s="96"/>
-      <c r="N21" s="96"/>
-      <c r="O21" s="96"/>
-      <c r="P21" s="96"/>
-      <c r="Q21" s="96"/>
-      <c r="R21" s="96"/>
-      <c r="S21" s="96"/>
-      <c r="T21" s="96"/>
-      <c r="U21" s="96"/>
-      <c r="V21" s="96"/>
-      <c r="W21" s="96"/>
-      <c r="X21" s="96"/>
-      <c r="Y21" s="96"/>
-      <c r="Z21" s="96"/>
-      <c r="AA21" s="96"/>
-      <c r="AB21" s="96"/>
-      <c r="AC21" s="96"/>
-      <c r="AD21" s="96"/>
-      <c r="AE21" s="96"/>
-      <c r="AF21" s="96"/>
-      <c r="AG21" s="96"/>
-      <c r="AH21" s="96"/>
-      <c r="AI21" s="96"/>
-      <c r="AJ21" s="96"/>
-      <c r="AK21" s="96"/>
-      <c r="AL21" s="96"/>
-      <c r="AM21" s="96"/>
-    </row>
-    <row r="22" spans="1:39" ht="14.1" customHeight="1">
+      <c r="B21" s="98"/>
+      <c r="C21" s="98"/>
+      <c r="D21" s="98"/>
+      <c r="E21" s="98"/>
+      <c r="F21" s="98"/>
+      <c r="G21" s="98"/>
+      <c r="H21" s="98"/>
+      <c r="I21" s="98"/>
+      <c r="J21" s="98"/>
+      <c r="K21" s="98"/>
+      <c r="L21" s="98"/>
+      <c r="M21" s="98"/>
+      <c r="N21" s="98"/>
+      <c r="O21" s="98"/>
+      <c r="P21" s="98"/>
+      <c r="Q21" s="98"/>
+      <c r="R21" s="98"/>
+      <c r="S21" s="98"/>
+      <c r="T21" s="98"/>
+      <c r="U21" s="98"/>
+      <c r="V21" s="98"/>
+      <c r="W21" s="98"/>
+      <c r="X21" s="98"/>
+      <c r="Y21" s="98"/>
+      <c r="Z21" s="98"/>
+      <c r="AA21" s="98"/>
+      <c r="AB21" s="98"/>
+      <c r="AC21" s="98"/>
+      <c r="AD21" s="98"/>
+      <c r="AE21" s="98"/>
+      <c r="AF21" s="98"/>
+      <c r="AG21" s="98"/>
+      <c r="AH21" s="98"/>
+      <c r="AI21" s="98"/>
+      <c r="AJ21" s="98"/>
+      <c r="AK21" s="98"/>
+      <c r="AL21" s="98"/>
+      <c r="AM21" s="98"/>
+    </row>
+    <row r="22" spans="1:39" ht="14.15" customHeight="1">
       <c r="A22" s="46"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
@@ -13834,7 +13850,7 @@
       <c r="AE22" s="3"/>
       <c r="AF22" s="3"/>
     </row>
-    <row r="23" spans="1:39" ht="14.1" customHeight="1">
+    <row r="23" spans="1:39" ht="14.15" customHeight="1">
       <c r="A23" s="46" t="s">
         <v>17</v>
       </c>
@@ -13867,7 +13883,7 @@
       <c r="AE23" s="3"/>
       <c r="AF23" s="3"/>
     </row>
-    <row r="24" spans="1:39" ht="14.1" customHeight="1">
+    <row r="24" spans="1:39" ht="14.15" customHeight="1">
       <c r="A24" s="46"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
@@ -13898,7 +13914,7 @@
       <c r="AE24" s="3"/>
       <c r="AF24" s="3"/>
     </row>
-    <row r="25" spans="1:39" ht="14.1" customHeight="1">
+    <row r="25" spans="1:39" ht="14.15" customHeight="1">
       <c r="A25" s="19" t="s">
         <v>169</v>
       </c>
@@ -13931,18 +13947,18 @@
       <c r="AE25" s="3"/>
       <c r="AF25" s="3"/>
     </row>
-    <row r="26" spans="1:39" s="34" customFormat="1" ht="14.1" customHeight="1">
-      <c r="A26" s="103"/>
-      <c r="B26" s="103"/>
-      <c r="C26" s="103"/>
-      <c r="D26" s="103"/>
-      <c r="E26" s="103"/>
-      <c r="F26" s="103"/>
-      <c r="G26" s="103"/>
-      <c r="H26" s="103"/>
-      <c r="I26" s="103"/>
-      <c r="J26" s="103"/>
-      <c r="K26" s="103"/>
+    <row r="26" spans="1:39" s="34" customFormat="1" ht="14.15" customHeight="1">
+      <c r="A26" s="102"/>
+      <c r="B26" s="102"/>
+      <c r="C26" s="102"/>
+      <c r="D26" s="102"/>
+      <c r="E26" s="102"/>
+      <c r="F26" s="102"/>
+      <c r="G26" s="102"/>
+      <c r="H26" s="102"/>
+      <c r="I26" s="102"/>
+      <c r="J26" s="102"/>
+      <c r="K26" s="102"/>
       <c r="L26" s="46"/>
       <c r="M26" s="46"/>
       <c r="N26" s="46"/>
@@ -13965,7 +13981,7 @@
       <c r="AE26" s="46"/>
       <c r="AF26" s="46"/>
     </row>
-    <row r="28" spans="1:39" s="34" customFormat="1" ht="14.1" customHeight="1">
+    <row r="28" spans="1:39" s="34" customFormat="1" ht="14.15" customHeight="1">
       <c r="A28" s="34" t="s">
         <v>170</v>
       </c>
@@ -13998,285 +14014,285 @@
       <c r="AE28" s="46"/>
       <c r="AF28" s="46"/>
     </row>
-    <row r="29" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A29" s="96" t="s">
+    <row r="29" spans="1:39" ht="14.15" customHeight="1">
+      <c r="A29" s="98" t="s">
         <v>155</v>
       </c>
-      <c r="B29" s="96"/>
-      <c r="C29" s="96"/>
-      <c r="D29" s="96"/>
-      <c r="E29" s="96"/>
-      <c r="F29" s="96" t="s">
+      <c r="B29" s="98"/>
+      <c r="C29" s="98"/>
+      <c r="D29" s="98"/>
+      <c r="E29" s="98"/>
+      <c r="F29" s="98" t="s">
         <v>158</v>
       </c>
-      <c r="G29" s="96"/>
-      <c r="H29" s="96"/>
-      <c r="I29" s="96"/>
-      <c r="J29" s="96"/>
-      <c r="K29" s="96"/>
-      <c r="L29" s="96"/>
-      <c r="M29" s="96" t="s">
+      <c r="G29" s="98"/>
+      <c r="H29" s="98"/>
+      <c r="I29" s="98"/>
+      <c r="J29" s="98"/>
+      <c r="K29" s="98"/>
+      <c r="L29" s="98"/>
+      <c r="M29" s="98" t="s">
         <v>159</v>
       </c>
-      <c r="N29" s="96"/>
-      <c r="O29" s="96"/>
-      <c r="P29" s="96"/>
-      <c r="Q29" s="96"/>
-      <c r="R29" s="96"/>
-      <c r="S29" s="96"/>
-      <c r="T29" s="96" t="s">
+      <c r="N29" s="98"/>
+      <c r="O29" s="98"/>
+      <c r="P29" s="98"/>
+      <c r="Q29" s="98"/>
+      <c r="R29" s="98"/>
+      <c r="S29" s="98"/>
+      <c r="T29" s="98" t="s">
         <v>160</v>
       </c>
-      <c r="U29" s="96"/>
-      <c r="V29" s="96"/>
-      <c r="W29" s="96"/>
-      <c r="X29" s="96"/>
-      <c r="Y29" s="96"/>
-      <c r="Z29" s="96"/>
-      <c r="AA29" s="96" t="s">
+      <c r="U29" s="98"/>
+      <c r="V29" s="98"/>
+      <c r="W29" s="98"/>
+      <c r="X29" s="98"/>
+      <c r="Y29" s="98"/>
+      <c r="Z29" s="98"/>
+      <c r="AA29" s="98" t="s">
         <v>161</v>
       </c>
-      <c r="AB29" s="96"/>
-      <c r="AC29" s="96"/>
-      <c r="AD29" s="96"/>
-      <c r="AE29" s="96"/>
-      <c r="AF29" s="96"/>
-      <c r="AG29" s="96"/>
-      <c r="AH29" s="96" t="s">
+      <c r="AB29" s="98"/>
+      <c r="AC29" s="98"/>
+      <c r="AD29" s="98"/>
+      <c r="AE29" s="98"/>
+      <c r="AF29" s="98"/>
+      <c r="AG29" s="98"/>
+      <c r="AH29" s="98" t="s">
         <v>162</v>
       </c>
-      <c r="AI29" s="96"/>
-      <c r="AJ29" s="96"/>
-      <c r="AK29" s="96"/>
-      <c r="AL29" s="96"/>
-      <c r="AM29" s="96"/>
-    </row>
-    <row r="30" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A30" s="96" t="s">
+      <c r="AI29" s="98"/>
+      <c r="AJ29" s="98"/>
+      <c r="AK29" s="98"/>
+      <c r="AL29" s="98"/>
+      <c r="AM29" s="98"/>
+    </row>
+    <row r="30" spans="1:39" ht="14.15" customHeight="1">
+      <c r="A30" s="98" t="s">
         <v>156</v>
       </c>
-      <c r="B30" s="96"/>
-      <c r="C30" s="96"/>
-      <c r="D30" s="96"/>
-      <c r="E30" s="96"/>
-      <c r="F30" s="96"/>
-      <c r="G30" s="96"/>
-      <c r="H30" s="96"/>
-      <c r="I30" s="96"/>
-      <c r="J30" s="96"/>
-      <c r="K30" s="96"/>
-      <c r="L30" s="96"/>
-      <c r="M30" s="96"/>
-      <c r="N30" s="96"/>
-      <c r="O30" s="96"/>
-      <c r="P30" s="96"/>
-      <c r="Q30" s="96"/>
-      <c r="R30" s="96"/>
-      <c r="S30" s="96"/>
-      <c r="T30" s="96"/>
-      <c r="U30" s="96"/>
-      <c r="V30" s="96"/>
-      <c r="W30" s="96"/>
-      <c r="X30" s="96"/>
-      <c r="Y30" s="96"/>
-      <c r="Z30" s="96"/>
-      <c r="AA30" s="96"/>
-      <c r="AB30" s="96"/>
-      <c r="AC30" s="96"/>
-      <c r="AD30" s="96"/>
-      <c r="AE30" s="96"/>
-      <c r="AF30" s="96"/>
-      <c r="AG30" s="96"/>
-      <c r="AH30" s="96"/>
-      <c r="AI30" s="96"/>
-      <c r="AJ30" s="96"/>
-      <c r="AK30" s="96"/>
-      <c r="AL30" s="96"/>
-      <c r="AM30" s="96"/>
-    </row>
-    <row r="31" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A31" s="96" t="s">
+      <c r="B30" s="98"/>
+      <c r="C30" s="98"/>
+      <c r="D30" s="98"/>
+      <c r="E30" s="98"/>
+      <c r="F30" s="98"/>
+      <c r="G30" s="98"/>
+      <c r="H30" s="98"/>
+      <c r="I30" s="98"/>
+      <c r="J30" s="98"/>
+      <c r="K30" s="98"/>
+      <c r="L30" s="98"/>
+      <c r="M30" s="98"/>
+      <c r="N30" s="98"/>
+      <c r="O30" s="98"/>
+      <c r="P30" s="98"/>
+      <c r="Q30" s="98"/>
+      <c r="R30" s="98"/>
+      <c r="S30" s="98"/>
+      <c r="T30" s="98"/>
+      <c r="U30" s="98"/>
+      <c r="V30" s="98"/>
+      <c r="W30" s="98"/>
+      <c r="X30" s="98"/>
+      <c r="Y30" s="98"/>
+      <c r="Z30" s="98"/>
+      <c r="AA30" s="98"/>
+      <c r="AB30" s="98"/>
+      <c r="AC30" s="98"/>
+      <c r="AD30" s="98"/>
+      <c r="AE30" s="98"/>
+      <c r="AF30" s="98"/>
+      <c r="AG30" s="98"/>
+      <c r="AH30" s="98"/>
+      <c r="AI30" s="98"/>
+      <c r="AJ30" s="98"/>
+      <c r="AK30" s="98"/>
+      <c r="AL30" s="98"/>
+      <c r="AM30" s="98"/>
+    </row>
+    <row r="31" spans="1:39" ht="14.15" customHeight="1">
+      <c r="A31" s="98" t="s">
         <v>157</v>
       </c>
-      <c r="B31" s="96"/>
-      <c r="C31" s="96"/>
-      <c r="D31" s="96"/>
-      <c r="E31" s="96"/>
-      <c r="F31" s="96"/>
-      <c r="G31" s="96"/>
-      <c r="H31" s="96"/>
-      <c r="I31" s="96"/>
-      <c r="J31" s="96"/>
-      <c r="K31" s="96"/>
-      <c r="L31" s="96"/>
-      <c r="M31" s="96"/>
-      <c r="N31" s="96"/>
-      <c r="O31" s="96"/>
-      <c r="P31" s="96"/>
-      <c r="Q31" s="96"/>
-      <c r="R31" s="96"/>
-      <c r="S31" s="96"/>
-      <c r="T31" s="96"/>
-      <c r="U31" s="96"/>
-      <c r="V31" s="96"/>
-      <c r="W31" s="96"/>
-      <c r="X31" s="96"/>
-      <c r="Y31" s="96"/>
-      <c r="Z31" s="96"/>
-      <c r="AA31" s="96"/>
-      <c r="AB31" s="96"/>
-      <c r="AC31" s="96"/>
-      <c r="AD31" s="96"/>
-      <c r="AE31" s="96"/>
-      <c r="AF31" s="96"/>
-      <c r="AG31" s="96"/>
-      <c r="AH31" s="96"/>
-      <c r="AI31" s="96"/>
-      <c r="AJ31" s="96"/>
-      <c r="AK31" s="96"/>
-      <c r="AL31" s="96"/>
-      <c r="AM31" s="96"/>
-    </row>
-    <row r="32" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A32" s="96" t="s">
+      <c r="B31" s="98"/>
+      <c r="C31" s="98"/>
+      <c r="D31" s="98"/>
+      <c r="E31" s="98"/>
+      <c r="F31" s="98"/>
+      <c r="G31" s="98"/>
+      <c r="H31" s="98"/>
+      <c r="I31" s="98"/>
+      <c r="J31" s="98"/>
+      <c r="K31" s="98"/>
+      <c r="L31" s="98"/>
+      <c r="M31" s="98"/>
+      <c r="N31" s="98"/>
+      <c r="O31" s="98"/>
+      <c r="P31" s="98"/>
+      <c r="Q31" s="98"/>
+      <c r="R31" s="98"/>
+      <c r="S31" s="98"/>
+      <c r="T31" s="98"/>
+      <c r="U31" s="98"/>
+      <c r="V31" s="98"/>
+      <c r="W31" s="98"/>
+      <c r="X31" s="98"/>
+      <c r="Y31" s="98"/>
+      <c r="Z31" s="98"/>
+      <c r="AA31" s="98"/>
+      <c r="AB31" s="98"/>
+      <c r="AC31" s="98"/>
+      <c r="AD31" s="98"/>
+      <c r="AE31" s="98"/>
+      <c r="AF31" s="98"/>
+      <c r="AG31" s="98"/>
+      <c r="AH31" s="98"/>
+      <c r="AI31" s="98"/>
+      <c r="AJ31" s="98"/>
+      <c r="AK31" s="98"/>
+      <c r="AL31" s="98"/>
+      <c r="AM31" s="98"/>
+    </row>
+    <row r="32" spans="1:39" ht="14.15" customHeight="1">
+      <c r="A32" s="98" t="s">
         <v>155</v>
       </c>
-      <c r="B32" s="96"/>
-      <c r="C32" s="96"/>
-      <c r="D32" s="96"/>
-      <c r="E32" s="96"/>
-      <c r="F32" s="96" t="s">
+      <c r="B32" s="98"/>
+      <c r="C32" s="98"/>
+      <c r="D32" s="98"/>
+      <c r="E32" s="98"/>
+      <c r="F32" s="98" t="s">
         <v>163</v>
       </c>
-      <c r="G32" s="96"/>
-      <c r="H32" s="96"/>
-      <c r="I32" s="96"/>
-      <c r="J32" s="96"/>
-      <c r="K32" s="96"/>
-      <c r="L32" s="96"/>
-      <c r="M32" s="96" t="s">
+      <c r="G32" s="98"/>
+      <c r="H32" s="98"/>
+      <c r="I32" s="98"/>
+      <c r="J32" s="98"/>
+      <c r="K32" s="98"/>
+      <c r="L32" s="98"/>
+      <c r="M32" s="98" t="s">
         <v>164</v>
       </c>
-      <c r="N32" s="96"/>
-      <c r="O32" s="96"/>
-      <c r="P32" s="96"/>
-      <c r="Q32" s="96"/>
-      <c r="R32" s="96"/>
-      <c r="S32" s="96"/>
-      <c r="T32" s="96" t="s">
+      <c r="N32" s="98"/>
+      <c r="O32" s="98"/>
+      <c r="P32" s="98"/>
+      <c r="Q32" s="98"/>
+      <c r="R32" s="98"/>
+      <c r="S32" s="98"/>
+      <c r="T32" s="98" t="s">
         <v>165</v>
       </c>
-      <c r="U32" s="96"/>
-      <c r="V32" s="96"/>
-      <c r="W32" s="96"/>
-      <c r="X32" s="96"/>
-      <c r="Y32" s="96"/>
-      <c r="Z32" s="96"/>
-      <c r="AA32" s="96" t="s">
+      <c r="U32" s="98"/>
+      <c r="V32" s="98"/>
+      <c r="W32" s="98"/>
+      <c r="X32" s="98"/>
+      <c r="Y32" s="98"/>
+      <c r="Z32" s="98"/>
+      <c r="AA32" s="98" t="s">
         <v>166</v>
       </c>
-      <c r="AB32" s="96"/>
-      <c r="AC32" s="96"/>
-      <c r="AD32" s="96"/>
-      <c r="AE32" s="96"/>
-      <c r="AF32" s="96"/>
-      <c r="AG32" s="96"/>
-      <c r="AH32" s="96" t="s">
+      <c r="AB32" s="98"/>
+      <c r="AC32" s="98"/>
+      <c r="AD32" s="98"/>
+      <c r="AE32" s="98"/>
+      <c r="AF32" s="98"/>
+      <c r="AG32" s="98"/>
+      <c r="AH32" s="98" t="s">
         <v>167</v>
       </c>
-      <c r="AI32" s="96"/>
-      <c r="AJ32" s="96"/>
-      <c r="AK32" s="96"/>
-      <c r="AL32" s="96"/>
-      <c r="AM32" s="96"/>
-    </row>
-    <row r="33" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A33" s="96" t="s">
+      <c r="AI32" s="98"/>
+      <c r="AJ32" s="98"/>
+      <c r="AK32" s="98"/>
+      <c r="AL32" s="98"/>
+      <c r="AM32" s="98"/>
+    </row>
+    <row r="33" spans="1:39" ht="14.15" customHeight="1">
+      <c r="A33" s="98" t="s">
         <v>156</v>
       </c>
-      <c r="B33" s="96"/>
-      <c r="C33" s="96"/>
-      <c r="D33" s="96"/>
-      <c r="E33" s="96"/>
-      <c r="F33" s="96"/>
-      <c r="G33" s="96"/>
-      <c r="H33" s="96"/>
-      <c r="I33" s="96"/>
-      <c r="J33" s="96"/>
-      <c r="K33" s="96"/>
-      <c r="L33" s="96"/>
-      <c r="M33" s="96"/>
-      <c r="N33" s="96"/>
-      <c r="O33" s="96"/>
-      <c r="P33" s="96"/>
-      <c r="Q33" s="96"/>
-      <c r="R33" s="96"/>
-      <c r="S33" s="96"/>
-      <c r="T33" s="96"/>
-      <c r="U33" s="96"/>
-      <c r="V33" s="96"/>
-      <c r="W33" s="96"/>
-      <c r="X33" s="96"/>
-      <c r="Y33" s="96"/>
-      <c r="Z33" s="96"/>
-      <c r="AA33" s="96"/>
-      <c r="AB33" s="96"/>
-      <c r="AC33" s="96"/>
-      <c r="AD33" s="96"/>
-      <c r="AE33" s="96"/>
-      <c r="AF33" s="96"/>
-      <c r="AG33" s="96"/>
-      <c r="AH33" s="96"/>
-      <c r="AI33" s="96"/>
-      <c r="AJ33" s="96"/>
-      <c r="AK33" s="96"/>
-      <c r="AL33" s="96"/>
-      <c r="AM33" s="96"/>
-    </row>
-    <row r="34" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A34" s="96" t="s">
+      <c r="B33" s="98"/>
+      <c r="C33" s="98"/>
+      <c r="D33" s="98"/>
+      <c r="E33" s="98"/>
+      <c r="F33" s="98"/>
+      <c r="G33" s="98"/>
+      <c r="H33" s="98"/>
+      <c r="I33" s="98"/>
+      <c r="J33" s="98"/>
+      <c r="K33" s="98"/>
+      <c r="L33" s="98"/>
+      <c r="M33" s="98"/>
+      <c r="N33" s="98"/>
+      <c r="O33" s="98"/>
+      <c r="P33" s="98"/>
+      <c r="Q33" s="98"/>
+      <c r="R33" s="98"/>
+      <c r="S33" s="98"/>
+      <c r="T33" s="98"/>
+      <c r="U33" s="98"/>
+      <c r="V33" s="98"/>
+      <c r="W33" s="98"/>
+      <c r="X33" s="98"/>
+      <c r="Y33" s="98"/>
+      <c r="Z33" s="98"/>
+      <c r="AA33" s="98"/>
+      <c r="AB33" s="98"/>
+      <c r="AC33" s="98"/>
+      <c r="AD33" s="98"/>
+      <c r="AE33" s="98"/>
+      <c r="AF33" s="98"/>
+      <c r="AG33" s="98"/>
+      <c r="AH33" s="98"/>
+      <c r="AI33" s="98"/>
+      <c r="AJ33" s="98"/>
+      <c r="AK33" s="98"/>
+      <c r="AL33" s="98"/>
+      <c r="AM33" s="98"/>
+    </row>
+    <row r="34" spans="1:39" ht="14.15" customHeight="1">
+      <c r="A34" s="98" t="s">
         <v>157</v>
       </c>
-      <c r="B34" s="96"/>
-      <c r="C34" s="96"/>
-      <c r="D34" s="96"/>
-      <c r="E34" s="96"/>
-      <c r="F34" s="96"/>
-      <c r="G34" s="96"/>
-      <c r="H34" s="96"/>
-      <c r="I34" s="96"/>
-      <c r="J34" s="96"/>
-      <c r="K34" s="96"/>
-      <c r="L34" s="96"/>
-      <c r="M34" s="96"/>
-      <c r="N34" s="96"/>
-      <c r="O34" s="96"/>
-      <c r="P34" s="96"/>
-      <c r="Q34" s="96"/>
-      <c r="R34" s="96"/>
-      <c r="S34" s="96"/>
-      <c r="T34" s="96"/>
-      <c r="U34" s="96"/>
-      <c r="V34" s="96"/>
-      <c r="W34" s="96"/>
-      <c r="X34" s="96"/>
-      <c r="Y34" s="96"/>
-      <c r="Z34" s="96"/>
-      <c r="AA34" s="96"/>
-      <c r="AB34" s="96"/>
-      <c r="AC34" s="96"/>
-      <c r="AD34" s="96"/>
-      <c r="AE34" s="96"/>
-      <c r="AF34" s="96"/>
-      <c r="AG34" s="96"/>
-      <c r="AH34" s="96"/>
-      <c r="AI34" s="96"/>
-      <c r="AJ34" s="96"/>
-      <c r="AK34" s="96"/>
-      <c r="AL34" s="96"/>
-      <c r="AM34" s="96"/>
-    </row>
-    <row r="35" spans="1:39" ht="14.1" customHeight="1">
+      <c r="B34" s="98"/>
+      <c r="C34" s="98"/>
+      <c r="D34" s="98"/>
+      <c r="E34" s="98"/>
+      <c r="F34" s="98"/>
+      <c r="G34" s="98"/>
+      <c r="H34" s="98"/>
+      <c r="I34" s="98"/>
+      <c r="J34" s="98"/>
+      <c r="K34" s="98"/>
+      <c r="L34" s="98"/>
+      <c r="M34" s="98"/>
+      <c r="N34" s="98"/>
+      <c r="O34" s="98"/>
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="98"/>
+      <c r="S34" s="98"/>
+      <c r="T34" s="98"/>
+      <c r="U34" s="98"/>
+      <c r="V34" s="98"/>
+      <c r="W34" s="98"/>
+      <c r="X34" s="98"/>
+      <c r="Y34" s="98"/>
+      <c r="Z34" s="98"/>
+      <c r="AA34" s="98"/>
+      <c r="AB34" s="98"/>
+      <c r="AC34" s="98"/>
+      <c r="AD34" s="98"/>
+      <c r="AE34" s="98"/>
+      <c r="AF34" s="98"/>
+      <c r="AG34" s="98"/>
+      <c r="AH34" s="98"/>
+      <c r="AI34" s="98"/>
+      <c r="AJ34" s="98"/>
+      <c r="AK34" s="98"/>
+      <c r="AL34" s="98"/>
+      <c r="AM34" s="98"/>
+    </row>
+    <row r="35" spans="1:39" ht="14.15" customHeight="1">
       <c r="A35" s="46"/>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
@@ -14307,7 +14323,7 @@
       <c r="AE35" s="3"/>
       <c r="AF35" s="3"/>
     </row>
-    <row r="36" spans="1:39" ht="14.1" customHeight="1">
+    <row r="36" spans="1:39" ht="14.15" customHeight="1">
       <c r="A36" s="46" t="s">
         <v>17</v>
       </c>
@@ -14340,7 +14356,7 @@
       <c r="AE36" s="3"/>
       <c r="AF36" s="3"/>
     </row>
-    <row r="37" spans="1:39" ht="14.1" customHeight="1">
+    <row r="37" spans="1:39" ht="14.15" customHeight="1">
       <c r="A37" s="46"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
@@ -14371,7 +14387,7 @@
       <c r="AE37" s="3"/>
       <c r="AF37" s="3"/>
     </row>
-    <row r="38" spans="1:39" ht="14.1" customHeight="1">
+    <row r="38" spans="1:39" ht="14.15" customHeight="1">
       <c r="A38" s="46"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
@@ -14402,7 +14418,7 @@
       <c r="AE38" s="3"/>
       <c r="AF38" s="3"/>
     </row>
-    <row r="39" spans="1:39" ht="14.1" customHeight="1">
+    <row r="39" spans="1:39" ht="14.15" customHeight="1">
       <c r="A39" s="46"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
@@ -14433,7 +14449,7 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
     </row>
-    <row r="40" spans="1:39" ht="14.1" customHeight="1">
+    <row r="40" spans="1:39" ht="14.15" customHeight="1">
       <c r="A40" s="46"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
@@ -14464,7 +14480,7 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
     </row>
-    <row r="41" spans="1:39" ht="14.1" customHeight="1">
+    <row r="41" spans="1:39" ht="14.15" customHeight="1">
       <c r="A41" s="46"/>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
@@ -14495,7 +14511,7 @@
       <c r="AE41" s="3"/>
       <c r="AF41" s="3"/>
     </row>
-    <row r="42" spans="1:39" ht="14.1" customHeight="1">
+    <row r="42" spans="1:39" ht="14.15" customHeight="1">
       <c r="A42" s="46"/>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
@@ -14526,7 +14542,7 @@
       <c r="AE42" s="3"/>
       <c r="AF42" s="3"/>
     </row>
-    <row r="43" spans="1:39" ht="14.1" customHeight="1">
+    <row r="43" spans="1:39" ht="14.15" customHeight="1">
       <c r="A43" s="46"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
@@ -14557,7 +14573,7 @@
       <c r="AE43" s="3"/>
       <c r="AF43" s="3"/>
     </row>
-    <row r="44" spans="1:39" ht="14.1" customHeight="1">
+    <row r="44" spans="1:39" ht="14.15" customHeight="1">
       <c r="A44" s="46"/>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -14588,7 +14604,7 @@
       <c r="AE44" s="3"/>
       <c r="AF44" s="3"/>
     </row>
-    <row r="45" spans="1:39" ht="14.1" customHeight="1">
+    <row r="45" spans="1:39" ht="14.15" customHeight="1">
       <c r="A45" s="46"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
@@ -14619,7 +14635,7 @@
       <c r="AE45" s="3"/>
       <c r="AF45" s="3"/>
     </row>
-    <row r="46" spans="1:39" ht="14.1" customHeight="1">
+    <row r="46" spans="1:39" ht="14.15" customHeight="1">
       <c r="A46" s="46"/>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
@@ -14650,7 +14666,7 @@
       <c r="AE46" s="3"/>
       <c r="AF46" s="3"/>
     </row>
-    <row r="47" spans="1:39" ht="14.1" customHeight="1">
+    <row r="47" spans="1:39" ht="14.15" customHeight="1">
       <c r="A47" s="46"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
@@ -14681,7 +14697,7 @@
       <c r="AE47" s="3"/>
       <c r="AF47" s="3"/>
     </row>
-    <row r="48" spans="1:39" ht="14.1" customHeight="1">
+    <row r="48" spans="1:39" ht="14.15" customHeight="1">
       <c r="A48" s="46"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
@@ -14712,7 +14728,7 @@
       <c r="AE48" s="3"/>
       <c r="AF48" s="3"/>
     </row>
-    <row r="49" spans="1:39" ht="14.1" customHeight="1">
+    <row r="49" spans="1:39" ht="14.15" customHeight="1">
       <c r="A49" s="46"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
@@ -14743,7 +14759,7 @@
       <c r="AE49" s="3"/>
       <c r="AF49" s="3"/>
     </row>
-    <row r="50" spans="1:39" ht="14.1" customHeight="1">
+    <row r="50" spans="1:39" ht="14.15" customHeight="1">
       <c r="A50" s="46"/>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
@@ -14774,7 +14790,7 @@
       <c r="AE50" s="3"/>
       <c r="AF50" s="3"/>
     </row>
-    <row r="51" spans="1:39" ht="14.1" customHeight="1">
+    <row r="51" spans="1:39" ht="14.15" customHeight="1">
       <c r="A51" s="46"/>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
@@ -14805,7 +14821,7 @@
       <c r="AE51" s="3"/>
       <c r="AF51" s="3"/>
     </row>
-    <row r="52" spans="1:39" ht="14.1" customHeight="1">
+    <row r="52" spans="1:39" ht="14.15" customHeight="1">
       <c r="A52" s="46"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
@@ -15062,8 +15078,8 @@
       <c r="AL58" s="7"/>
       <c r="AM58" s="7"/>
     </row>
-    <row r="59" spans="1:39" ht="13.9" customHeight="1"/>
-    <row r="60" spans="1:39" ht="13.9" customHeight="1">
+    <row r="59" spans="1:39" ht="13.95" customHeight="1"/>
+    <row r="60" spans="1:39" ht="13.95" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="15"/>
       <c r="C60" s="15"/>
@@ -15079,7 +15095,7 @@
       <c r="M60" s="15"/>
       <c r="N60" s="15"/>
     </row>
-    <row r="61" spans="1:39" ht="13.9" customHeight="1">
+    <row r="61" spans="1:39" ht="13.95" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="7"/>
       <c r="C61" s="7"/>
@@ -15113,6 +15129,95 @@
     </row>
   </sheetData>
   <mergeCells count="113">
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="F11:L11"/>
+    <mergeCell ref="AH8:AM8"/>
+    <mergeCell ref="AA8:AG8"/>
+    <mergeCell ref="T8:Z8"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="AH9:AM9"/>
+    <mergeCell ref="F10:L10"/>
+    <mergeCell ref="M10:S10"/>
+    <mergeCell ref="T10:Z10"/>
+    <mergeCell ref="AA10:AG10"/>
+    <mergeCell ref="AH10:AM10"/>
+    <mergeCell ref="M8:S8"/>
+    <mergeCell ref="F8:L8"/>
+    <mergeCell ref="F9:L9"/>
+    <mergeCell ref="M9:S9"/>
+    <mergeCell ref="T9:Z9"/>
+    <mergeCell ref="AA9:AG9"/>
+    <mergeCell ref="M11:S11"/>
+    <mergeCell ref="T11:Z11"/>
+    <mergeCell ref="AA11:AG11"/>
+    <mergeCell ref="AH11:AM11"/>
+    <mergeCell ref="F12:L12"/>
+    <mergeCell ref="M12:S12"/>
+    <mergeCell ref="T12:Z12"/>
+    <mergeCell ref="AA12:AG12"/>
+    <mergeCell ref="AH12:AM12"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="F17:L17"/>
+    <mergeCell ref="M17:S17"/>
+    <mergeCell ref="T17:Z17"/>
+    <mergeCell ref="AA17:AG17"/>
+    <mergeCell ref="AH17:AM17"/>
+    <mergeCell ref="T13:Z13"/>
+    <mergeCell ref="AA13:AG13"/>
+    <mergeCell ref="AH13:AM13"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="F16:L16"/>
+    <mergeCell ref="M16:S16"/>
+    <mergeCell ref="T16:Z16"/>
+    <mergeCell ref="AA16:AG16"/>
+    <mergeCell ref="AH16:AM16"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="F13:L13"/>
+    <mergeCell ref="M13:S13"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="F19:L19"/>
+    <mergeCell ref="M19:S19"/>
+    <mergeCell ref="T19:Z19"/>
+    <mergeCell ref="AA19:AG19"/>
+    <mergeCell ref="AH19:AM19"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="F18:L18"/>
+    <mergeCell ref="M18:S18"/>
+    <mergeCell ref="T18:Z18"/>
+    <mergeCell ref="AA18:AG18"/>
+    <mergeCell ref="AH18:AM18"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="F21:L21"/>
+    <mergeCell ref="M21:S21"/>
+    <mergeCell ref="T21:Z21"/>
+    <mergeCell ref="AA21:AG21"/>
+    <mergeCell ref="AH21:AM21"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="F20:L20"/>
+    <mergeCell ref="M20:S20"/>
+    <mergeCell ref="T20:Z20"/>
+    <mergeCell ref="AA20:AG20"/>
+    <mergeCell ref="AH20:AM20"/>
+    <mergeCell ref="AH31:AM31"/>
+    <mergeCell ref="AA29:AG29"/>
+    <mergeCell ref="AH29:AM29"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="F30:L30"/>
+    <mergeCell ref="M30:S30"/>
+    <mergeCell ref="T30:Z30"/>
+    <mergeCell ref="AA30:AG30"/>
+    <mergeCell ref="AH30:AM30"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="F29:L29"/>
+    <mergeCell ref="M29:S29"/>
+    <mergeCell ref="T29:Z29"/>
     <mergeCell ref="A26:K26"/>
     <mergeCell ref="A34:E34"/>
     <mergeCell ref="F34:L34"/>
@@ -15137,95 +15242,6 @@
     <mergeCell ref="M31:S31"/>
     <mergeCell ref="T31:Z31"/>
     <mergeCell ref="AA31:AG31"/>
-    <mergeCell ref="AH31:AM31"/>
-    <mergeCell ref="AA29:AG29"/>
-    <mergeCell ref="AH29:AM29"/>
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="F30:L30"/>
-    <mergeCell ref="M30:S30"/>
-    <mergeCell ref="T30:Z30"/>
-    <mergeCell ref="AA30:AG30"/>
-    <mergeCell ref="AH30:AM30"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="F29:L29"/>
-    <mergeCell ref="M29:S29"/>
-    <mergeCell ref="T29:Z29"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="F21:L21"/>
-    <mergeCell ref="M21:S21"/>
-    <mergeCell ref="T21:Z21"/>
-    <mergeCell ref="AA21:AG21"/>
-    <mergeCell ref="AH21:AM21"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="F20:L20"/>
-    <mergeCell ref="M20:S20"/>
-    <mergeCell ref="T20:Z20"/>
-    <mergeCell ref="AA20:AG20"/>
-    <mergeCell ref="AH20:AM20"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="F19:L19"/>
-    <mergeCell ref="M19:S19"/>
-    <mergeCell ref="T19:Z19"/>
-    <mergeCell ref="AA19:AG19"/>
-    <mergeCell ref="AH19:AM19"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="F18:L18"/>
-    <mergeCell ref="M18:S18"/>
-    <mergeCell ref="T18:Z18"/>
-    <mergeCell ref="AA18:AG18"/>
-    <mergeCell ref="AH18:AM18"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="F17:L17"/>
-    <mergeCell ref="M17:S17"/>
-    <mergeCell ref="T17:Z17"/>
-    <mergeCell ref="AA17:AG17"/>
-    <mergeCell ref="AH17:AM17"/>
-    <mergeCell ref="T13:Z13"/>
-    <mergeCell ref="AA13:AG13"/>
-    <mergeCell ref="AH13:AM13"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="F16:L16"/>
-    <mergeCell ref="M16:S16"/>
-    <mergeCell ref="T16:Z16"/>
-    <mergeCell ref="AA16:AG16"/>
-    <mergeCell ref="AH16:AM16"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="F13:L13"/>
-    <mergeCell ref="M13:S13"/>
-    <mergeCell ref="AA9:AG9"/>
-    <mergeCell ref="M11:S11"/>
-    <mergeCell ref="T11:Z11"/>
-    <mergeCell ref="AA11:AG11"/>
-    <mergeCell ref="AH11:AM11"/>
-    <mergeCell ref="F12:L12"/>
-    <mergeCell ref="M12:S12"/>
-    <mergeCell ref="T12:Z12"/>
-    <mergeCell ref="AA12:AG12"/>
-    <mergeCell ref="AH12:AM12"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="F11:L11"/>
-    <mergeCell ref="AH8:AM8"/>
-    <mergeCell ref="AA8:AG8"/>
-    <mergeCell ref="T8:Z8"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="AH9:AM9"/>
-    <mergeCell ref="F10:L10"/>
-    <mergeCell ref="M10:S10"/>
-    <mergeCell ref="T10:Z10"/>
-    <mergeCell ref="AA10:AG10"/>
-    <mergeCell ref="AH10:AM10"/>
-    <mergeCell ref="M8:S8"/>
-    <mergeCell ref="F8:L8"/>
-    <mergeCell ref="F9:L9"/>
-    <mergeCell ref="M9:S9"/>
-    <mergeCell ref="T9:Z9"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/wwwroot/ExcelModel/CrazyLine_PHY_sheet.xlsx
+++ b/wwwroot/ExcelModel/CrazyLine_PHY_sheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\source\NX-lims Softlines Command System\wwwroot\ExcelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1AA1F6B-4ED6-4DD6-8575-34C8FDEF5F82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A88EFE9B-7892-43A3-9951-66D26C28215A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="2614" windowWidth="24686" windowHeight="13132" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Weight" sheetId="3" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="173">
   <si>
     <t>Test Report Number 报告编号:</t>
   </si>
@@ -1347,14 +1347,6 @@
   <si>
     <t>Snap 2</t>
     <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>Load：</t>
-    <phoneticPr fontId="24" type="noConversion"/>
-  </si>
-  <si>
-    <t>16N</t>
-    <phoneticPr fontId="24" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1826,7 +1818,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1950,15 +1942,6 @@
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2013,14 +1996,26 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="43" fontId="22" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2031,23 +2026,17 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="22" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2057,6 +2046,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2080,31 +2072,28 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2384,7 +2373,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AB21"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="28" width="3" customWidth="1"/>
   </cols>
@@ -2398,25 +2387,25 @@
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
       <c r="I1" s="5"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="54"/>
-      <c r="O1" s="54"/>
-      <c r="P1" s="54"/>
-      <c r="Q1" s="54"/>
-      <c r="R1" s="54"/>
-      <c r="S1" s="54"/>
-      <c r="T1" s="54"/>
-      <c r="U1" s="54"/>
-      <c r="V1" s="54"/>
-      <c r="W1" s="54"/>
-      <c r="X1" s="54"/>
-      <c r="Y1" s="54"/>
-      <c r="Z1" s="54"/>
-      <c r="AA1" s="54"/>
-      <c r="AB1" s="54"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51"/>
+      <c r="S1" s="51"/>
+      <c r="T1" s="51"/>
+      <c r="U1" s="51"/>
+      <c r="V1" s="51"/>
+      <c r="W1" s="51"/>
+      <c r="X1" s="51"/>
+      <c r="Y1" s="51"/>
+      <c r="Z1" s="51"/>
+      <c r="AA1" s="51"/>
+      <c r="AB1" s="51"/>
     </row>
     <row r="2" spans="1:28">
       <c r="A2" s="8" t="s">
@@ -2448,18 +2437,18 @@
       <c r="AB2" s="3"/>
     </row>
     <row r="3" spans="1:28" ht="15.75" customHeight="1">
-      <c r="A3" s="71"/>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="71"/>
-      <c r="K3" s="71"/>
-      <c r="L3" s="71"/>
+      <c r="A3" s="68"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="68"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
@@ -2477,7 +2466,7 @@
       <c r="AA3" s="3"/>
       <c r="AB3" s="3"/>
     </row>
-    <row r="4" spans="1:28" ht="16.75">
+    <row r="4" spans="1:28" ht="16.2">
       <c r="A4" s="6" t="s">
         <v>5</v>
       </c>
@@ -2620,7 +2609,7 @@
       <c r="AA8" s="3"/>
       <c r="AB8" s="3"/>
     </row>
-    <row r="9" spans="1:28" ht="16.75">
+    <row r="9" spans="1:28" ht="16.2">
       <c r="A9" s="6" t="s">
         <v>6</v>
       </c>
@@ -2651,87 +2640,87 @@
       <c r="AA9" s="3"/>
       <c r="AB9" s="3"/>
     </row>
-    <row r="10" spans="1:28" ht="16.75">
-      <c r="A10" s="63" t="s">
+    <row r="10" spans="1:28" ht="16.2">
+      <c r="A10" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="64"/>
-      <c r="C10" s="64"/>
-      <c r="D10" s="65"/>
-      <c r="E10" s="55" t="s">
+      <c r="B10" s="61"/>
+      <c r="C10" s="61"/>
+      <c r="D10" s="62"/>
+      <c r="E10" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="56"/>
-      <c r="G10" s="56"/>
-      <c r="H10" s="56"/>
-      <c r="I10" s="56"/>
-      <c r="J10" s="56"/>
-      <c r="K10" s="56"/>
-      <c r="L10" s="56"/>
-      <c r="M10" s="56"/>
-      <c r="N10" s="56"/>
-      <c r="O10" s="56"/>
-      <c r="P10" s="56"/>
-      <c r="Q10" s="56"/>
-      <c r="R10" s="56"/>
-      <c r="S10" s="56"/>
-      <c r="T10" s="56"/>
-      <c r="U10" s="56"/>
-      <c r="V10" s="56"/>
-      <c r="W10" s="56"/>
-      <c r="X10" s="56"/>
-      <c r="Y10" s="57" t="s">
+      <c r="F10" s="53"/>
+      <c r="G10" s="53"/>
+      <c r="H10" s="53"/>
+      <c r="I10" s="53"/>
+      <c r="J10" s="53"/>
+      <c r="K10" s="53"/>
+      <c r="L10" s="53"/>
+      <c r="M10" s="53"/>
+      <c r="N10" s="53"/>
+      <c r="O10" s="53"/>
+      <c r="P10" s="53"/>
+      <c r="Q10" s="53"/>
+      <c r="R10" s="53"/>
+      <c r="S10" s="53"/>
+      <c r="T10" s="53"/>
+      <c r="U10" s="53"/>
+      <c r="V10" s="53"/>
+      <c r="W10" s="53"/>
+      <c r="X10" s="53"/>
+      <c r="Y10" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="Z10" s="58"/>
-      <c r="AA10" s="58"/>
-      <c r="AB10" s="59"/>
+      <c r="Z10" s="55"/>
+      <c r="AA10" s="55"/>
+      <c r="AB10" s="56"/>
     </row>
     <row r="11" spans="1:28">
-      <c r="A11" s="66"/>
-      <c r="B11" s="67"/>
-      <c r="C11" s="67"/>
-      <c r="D11" s="68"/>
-      <c r="E11" s="55" t="s">
+      <c r="A11" s="63"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="65"/>
+      <c r="E11" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="56"/>
-      <c r="G11" s="56"/>
-      <c r="H11" s="69"/>
-      <c r="I11" s="55" t="s">
+      <c r="F11" s="53"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="66"/>
+      <c r="I11" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="J11" s="56"/>
-      <c r="K11" s="56"/>
-      <c r="L11" s="69"/>
-      <c r="M11" s="55" t="s">
+      <c r="J11" s="53"/>
+      <c r="K11" s="53"/>
+      <c r="L11" s="66"/>
+      <c r="M11" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="N11" s="56"/>
-      <c r="O11" s="56"/>
-      <c r="P11" s="69"/>
-      <c r="Q11" s="55" t="s">
+      <c r="N11" s="53"/>
+      <c r="O11" s="53"/>
+      <c r="P11" s="66"/>
+      <c r="Q11" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="R11" s="56"/>
-      <c r="S11" s="56"/>
-      <c r="T11" s="69"/>
-      <c r="U11" s="55" t="s">
+      <c r="R11" s="53"/>
+      <c r="S11" s="53"/>
+      <c r="T11" s="66"/>
+      <c r="U11" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="V11" s="56"/>
-      <c r="W11" s="56"/>
-      <c r="X11" s="70"/>
-      <c r="Y11" s="60"/>
-      <c r="Z11" s="61"/>
-      <c r="AA11" s="61"/>
-      <c r="AB11" s="62"/>
+      <c r="V11" s="53"/>
+      <c r="W11" s="53"/>
+      <c r="X11" s="67"/>
+      <c r="Y11" s="57"/>
+      <c r="Z11" s="58"/>
+      <c r="AA11" s="58"/>
+      <c r="AB11" s="59"/>
     </row>
     <row r="12" spans="1:28">
-      <c r="A12" s="51"/>
-      <c r="B12" s="52"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="53"/>
+      <c r="A12" s="69"/>
+      <c r="B12" s="70"/>
+      <c r="C12" s="70"/>
+      <c r="D12" s="71"/>
       <c r="E12" s="1"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
@@ -2758,10 +2747,10 @@
       <c r="AB12" s="2"/>
     </row>
     <row r="13" spans="1:28">
-      <c r="A13" s="51"/>
-      <c r="B13" s="52"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="53"/>
+      <c r="A13" s="69"/>
+      <c r="B13" s="70"/>
+      <c r="C13" s="70"/>
+      <c r="D13" s="71"/>
       <c r="E13" s="1"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
@@ -2788,10 +2777,10 @@
       <c r="AB13" s="2"/>
     </row>
     <row r="14" spans="1:28">
-      <c r="A14" s="51"/>
-      <c r="B14" s="52"/>
-      <c r="C14" s="52"/>
-      <c r="D14" s="53"/>
+      <c r="A14" s="69"/>
+      <c r="B14" s="70"/>
+      <c r="C14" s="70"/>
+      <c r="D14" s="71"/>
       <c r="E14" s="1"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
@@ -2818,10 +2807,10 @@
       <c r="AB14" s="2"/>
     </row>
     <row r="15" spans="1:28">
-      <c r="A15" s="51"/>
-      <c r="B15" s="52"/>
-      <c r="C15" s="52"/>
-      <c r="D15" s="53"/>
+      <c r="A15" s="69"/>
+      <c r="B15" s="70"/>
+      <c r="C15" s="70"/>
+      <c r="D15" s="71"/>
       <c r="E15" s="1"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
@@ -2848,10 +2837,10 @@
       <c r="AB15" s="2"/>
     </row>
     <row r="16" spans="1:28">
-      <c r="A16" s="51"/>
-      <c r="B16" s="52"/>
-      <c r="C16" s="52"/>
-      <c r="D16" s="53"/>
+      <c r="A16" s="69"/>
+      <c r="B16" s="70"/>
+      <c r="C16" s="70"/>
+      <c r="D16" s="71"/>
       <c r="E16" s="1"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
@@ -3018,6 +3007,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
     <mergeCell ref="J1:AB1"/>
     <mergeCell ref="E10:X10"/>
     <mergeCell ref="Y10:AB11"/>
@@ -3028,11 +3022,6 @@
     <mergeCell ref="Q11:T11"/>
     <mergeCell ref="U11:X11"/>
     <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A16:D16"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -3052,12 +3041,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79A966B5-BF06-44FD-908C-4467C7012DA9}">
   <dimension ref="A1:AL55"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="7" width="2.35546875" customWidth="1"/>
+    <col min="1" max="7" width="2.33203125" customWidth="1"/>
     <col min="8" max="8" width="2" customWidth="1"/>
-    <col min="9" max="31" width="2.140625" customWidth="1"/>
-    <col min="32" max="38" width="2.35546875" customWidth="1"/>
+    <col min="9" max="31" width="2.109375" customWidth="1"/>
+    <col min="32" max="38" width="2.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="15" customHeight="1">
@@ -3072,32 +3061,32 @@
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="78"/>
-      <c r="AG1" s="78"/>
-      <c r="AH1" s="78"/>
-      <c r="AI1" s="78"/>
-      <c r="AJ1" s="78"/>
-      <c r="AK1" s="78"/>
-      <c r="AL1" s="78"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="72"/>
+      <c r="O1" s="72"/>
+      <c r="P1" s="72"/>
+      <c r="Q1" s="72"/>
+      <c r="R1" s="72"/>
+      <c r="S1" s="72"/>
+      <c r="T1" s="72"/>
+      <c r="U1" s="72"/>
+      <c r="V1" s="72"/>
+      <c r="W1" s="72"/>
+      <c r="X1" s="72"/>
+      <c r="Y1" s="72"/>
+      <c r="Z1" s="72"/>
+      <c r="AA1" s="72"/>
+      <c r="AB1" s="72"/>
+      <c r="AC1" s="72"/>
+      <c r="AD1" s="72"/>
+      <c r="AE1" s="72"/>
+      <c r="AF1" s="72"/>
+      <c r="AG1" s="72"/>
+      <c r="AH1" s="72"/>
+      <c r="AI1" s="72"/>
+      <c r="AJ1" s="72"/>
+      <c r="AK1" s="72"/>
+      <c r="AL1" s="72"/>
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1">
       <c r="A2" s="19" t="s">
@@ -3139,18 +3128,18 @@
       <c r="E3" s="3"/>
       <c r="F3" s="34"/>
       <c r="G3" s="34"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="74"/>
-      <c r="K3" s="74"/>
-      <c r="L3" s="74"/>
-      <c r="M3" s="74"/>
-      <c r="N3" s="74"/>
-      <c r="O3" s="74"/>
-      <c r="P3" s="74"/>
-      <c r="Q3" s="74"/>
-      <c r="R3" s="74"/>
-      <c r="S3" s="74"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="82"/>
+      <c r="M3" s="82"/>
+      <c r="N3" s="82"/>
+      <c r="O3" s="82"/>
+      <c r="P3" s="82"/>
+      <c r="Q3" s="82"/>
+      <c r="R3" s="82"/>
+      <c r="S3" s="82"/>
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
@@ -3169,8 +3158,8 @@
       <c r="A4" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="78"/>
-      <c r="E4" s="78"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
       <c r="F4" s="34" t="s">
         <v>43</v>
       </c>
@@ -3234,23 +3223,23 @@
       <c r="AK5" s="6"/>
     </row>
     <row r="6" spans="1:38" ht="15" customHeight="1">
-      <c r="A6" s="72" t="s">
+      <c r="A6" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="82"/>
-      <c r="C6" s="82"/>
-      <c r="D6" s="82"/>
-      <c r="E6" s="82"/>
-      <c r="F6" s="81" t="s">
+      <c r="B6" s="81"/>
+      <c r="C6" s="81"/>
+      <c r="D6" s="81"/>
+      <c r="E6" s="81"/>
+      <c r="F6" s="79" t="s">
         <v>44</v>
       </c>
-      <c r="G6" s="81"/>
-      <c r="H6" s="81"/>
-      <c r="I6" s="81"/>
-      <c r="J6" s="81"/>
-      <c r="K6" s="81"/>
-      <c r="L6" s="81"/>
-      <c r="M6" s="81"/>
+      <c r="G6" s="79"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
+      <c r="J6" s="79"/>
+      <c r="K6" s="79"/>
+      <c r="L6" s="79"/>
+      <c r="M6" s="79"/>
       <c r="N6" s="36"/>
       <c r="O6" s="36"/>
       <c r="P6" s="36"/>
@@ -3278,19 +3267,19 @@
       <c r="AL6" s="36"/>
     </row>
     <row r="7" spans="1:38" ht="15" customHeight="1">
-      <c r="A7" s="82"/>
-      <c r="B7" s="82"/>
-      <c r="C7" s="82"/>
-      <c r="D7" s="82"/>
-      <c r="E7" s="82"/>
-      <c r="F7" s="81"/>
-      <c r="G7" s="81"/>
-      <c r="H7" s="81"/>
-      <c r="I7" s="81"/>
-      <c r="J7" s="81"/>
-      <c r="K7" s="81"/>
-      <c r="L7" s="81"/>
-      <c r="M7" s="81"/>
+      <c r="A7" s="81"/>
+      <c r="B7" s="81"/>
+      <c r="C7" s="81"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="79"/>
+      <c r="G7" s="79"/>
+      <c r="H7" s="79"/>
+      <c r="I7" s="79"/>
+      <c r="J7" s="79"/>
+      <c r="K7" s="79"/>
+      <c r="L7" s="79"/>
+      <c r="M7" s="79"/>
       <c r="N7" s="36"/>
       <c r="O7" s="36"/>
       <c r="P7" s="36"/>
@@ -3317,20 +3306,20 @@
       <c r="AK7" s="36"/>
       <c r="AL7" s="36"/>
     </row>
-    <row r="8" spans="1:38" ht="21.25" customHeight="1">
-      <c r="A8" s="51"/>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="75"/>
-      <c r="G8" s="76"/>
-      <c r="H8" s="76"/>
-      <c r="I8" s="76"/>
-      <c r="J8" s="76"/>
-      <c r="K8" s="76"/>
-      <c r="L8" s="76"/>
-      <c r="M8" s="77"/>
+    <row r="8" spans="1:38" ht="21.3" customHeight="1">
+      <c r="A8" s="69"/>
+      <c r="B8" s="70"/>
+      <c r="C8" s="70"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="71"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="77"/>
+      <c r="J8" s="77"/>
+      <c r="K8" s="77"/>
+      <c r="L8" s="77"/>
+      <c r="M8" s="78"/>
       <c r="N8" s="36"/>
       <c r="O8" s="36"/>
       <c r="P8" s="36"/>
@@ -3357,20 +3346,20 @@
       <c r="AK8" s="36"/>
       <c r="AL8" s="36"/>
     </row>
-    <row r="9" spans="1:38" ht="21.25" customHeight="1">
-      <c r="A9" s="51"/>
-      <c r="B9" s="52"/>
-      <c r="C9" s="52"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="75"/>
-      <c r="G9" s="76"/>
-      <c r="H9" s="76"/>
-      <c r="I9" s="76"/>
-      <c r="J9" s="76"/>
-      <c r="K9" s="76"/>
-      <c r="L9" s="76"/>
-      <c r="M9" s="77"/>
+    <row r="9" spans="1:38" ht="21.3" customHeight="1">
+      <c r="A9" s="69"/>
+      <c r="B9" s="70"/>
+      <c r="C9" s="70"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="77"/>
+      <c r="I9" s="77"/>
+      <c r="J9" s="77"/>
+      <c r="K9" s="77"/>
+      <c r="L9" s="77"/>
+      <c r="M9" s="78"/>
       <c r="N9" s="36"/>
       <c r="O9" s="36"/>
       <c r="P9" s="36"/>
@@ -3397,20 +3386,20 @@
       <c r="AK9" s="36"/>
       <c r="AL9" s="36"/>
     </row>
-    <row r="10" spans="1:38" ht="21.25" customHeight="1">
+    <row r="10" spans="1:38" ht="21.3" customHeight="1">
       <c r="A10" s="73"/>
       <c r="B10" s="73"/>
       <c r="C10" s="73"/>
       <c r="D10" s="73"/>
       <c r="E10" s="73"/>
-      <c r="F10" s="81"/>
-      <c r="G10" s="81"/>
-      <c r="H10" s="81"/>
-      <c r="I10" s="81"/>
-      <c r="J10" s="81"/>
-      <c r="K10" s="81"/>
-      <c r="L10" s="81"/>
-      <c r="M10" s="81"/>
+      <c r="F10" s="79"/>
+      <c r="G10" s="79"/>
+      <c r="H10" s="79"/>
+      <c r="I10" s="79"/>
+      <c r="J10" s="79"/>
+      <c r="K10" s="79"/>
+      <c r="L10" s="79"/>
+      <c r="M10" s="79"/>
       <c r="N10" s="36"/>
       <c r="O10" s="36"/>
       <c r="P10" s="36"/>
@@ -3437,20 +3426,20 @@
       <c r="AK10" s="36"/>
       <c r="AL10" s="36"/>
     </row>
-    <row r="11" spans="1:38" ht="21.25" customHeight="1">
-      <c r="A11" s="79"/>
-      <c r="B11" s="79"/>
-      <c r="C11" s="79"/>
-      <c r="D11" s="79"/>
-      <c r="E11" s="79"/>
-      <c r="F11" s="81"/>
-      <c r="G11" s="81"/>
-      <c r="H11" s="81"/>
-      <c r="I11" s="81"/>
-      <c r="J11" s="81"/>
-      <c r="K11" s="81"/>
-      <c r="L11" s="81"/>
-      <c r="M11" s="81"/>
+    <row r="11" spans="1:38" ht="21.3" customHeight="1">
+      <c r="A11" s="74"/>
+      <c r="B11" s="74"/>
+      <c r="C11" s="74"/>
+      <c r="D11" s="74"/>
+      <c r="E11" s="74"/>
+      <c r="F11" s="79"/>
+      <c r="G11" s="79"/>
+      <c r="H11" s="79"/>
+      <c r="I11" s="79"/>
+      <c r="J11" s="79"/>
+      <c r="K11" s="79"/>
+      <c r="L11" s="79"/>
+      <c r="M11" s="79"/>
       <c r="N11" s="36"/>
       <c r="O11" s="36"/>
       <c r="P11" s="36"/>
@@ -3587,20 +3576,20 @@
       <c r="G15" s="34"/>
       <c r="H15" s="34"/>
       <c r="I15" s="34"/>
-      <c r="J15" s="80"/>
-      <c r="K15" s="80"/>
-      <c r="L15" s="80"/>
-      <c r="M15" s="80"/>
-      <c r="N15" s="80"/>
-      <c r="O15" s="80"/>
-      <c r="P15" s="80"/>
-      <c r="Q15" s="80"/>
-      <c r="R15" s="80"/>
-      <c r="S15" s="80"/>
-      <c r="T15" s="80"/>
-      <c r="U15" s="80"/>
-      <c r="V15" s="80"/>
-      <c r="W15" s="80"/>
+      <c r="J15" s="75"/>
+      <c r="K15" s="75"/>
+      <c r="L15" s="75"/>
+      <c r="M15" s="75"/>
+      <c r="N15" s="75"/>
+      <c r="O15" s="75"/>
+      <c r="P15" s="75"/>
+      <c r="Q15" s="75"/>
+      <c r="R15" s="75"/>
+      <c r="S15" s="75"/>
+      <c r="T15" s="75"/>
+      <c r="U15" s="75"/>
+      <c r="V15" s="75"/>
+      <c r="W15" s="75"/>
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
@@ -3645,8 +3634,8 @@
       <c r="A17" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="78"/>
-      <c r="D17" s="78"/>
+      <c r="C17" s="72"/>
+      <c r="D17" s="72"/>
       <c r="E17" s="34" t="s">
         <v>54</v>
       </c>
@@ -3712,18 +3701,18 @@
       <c r="AK18" s="6"/>
     </row>
     <row r="19" spans="1:38" ht="15" customHeight="1">
-      <c r="A19" s="72" t="s">
+      <c r="A19" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="72"/>
-      <c r="C19" s="72"/>
-      <c r="D19" s="72"/>
-      <c r="E19" s="72"/>
-      <c r="F19" s="72"/>
-      <c r="G19" s="72"/>
-      <c r="H19" s="72"/>
-      <c r="I19" s="72"/>
-      <c r="J19" s="72"/>
+      <c r="B19" s="80"/>
+      <c r="C19" s="80"/>
+      <c r="D19" s="80"/>
+      <c r="E19" s="80"/>
+      <c r="F19" s="80"/>
+      <c r="G19" s="80"/>
+      <c r="H19" s="80"/>
+      <c r="I19" s="80"/>
+      <c r="J19" s="80"/>
       <c r="K19" s="73"/>
       <c r="L19" s="73"/>
       <c r="M19" s="73"/>
@@ -3754,16 +3743,16 @@
       <c r="AL19" s="73"/>
     </row>
     <row r="20" spans="1:38" ht="15" customHeight="1">
-      <c r="A20" s="72"/>
-      <c r="B20" s="72"/>
-      <c r="C20" s="72"/>
-      <c r="D20" s="72"/>
-      <c r="E20" s="72"/>
-      <c r="F20" s="72"/>
-      <c r="G20" s="72"/>
-      <c r="H20" s="72"/>
-      <c r="I20" s="72"/>
-      <c r="J20" s="72"/>
+      <c r="A20" s="80"/>
+      <c r="B20" s="80"/>
+      <c r="C20" s="80"/>
+      <c r="D20" s="80"/>
+      <c r="E20" s="80"/>
+      <c r="F20" s="80"/>
+      <c r="G20" s="80"/>
+      <c r="H20" s="80"/>
+      <c r="I20" s="80"/>
+      <c r="J20" s="80"/>
       <c r="K20" s="73"/>
       <c r="L20" s="73"/>
       <c r="M20" s="73"/>
@@ -3794,168 +3783,168 @@
       <c r="AL20" s="73"/>
     </row>
     <row r="21" spans="1:38" ht="15" customHeight="1">
-      <c r="A21" s="72" t="s">
+      <c r="A21" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="B21" s="72"/>
-      <c r="C21" s="72"/>
-      <c r="D21" s="72"/>
-      <c r="E21" s="72"/>
-      <c r="F21" s="72"/>
-      <c r="G21" s="72"/>
-      <c r="H21" s="72"/>
-      <c r="I21" s="72"/>
-      <c r="J21" s="72"/>
-      <c r="K21" s="72"/>
-      <c r="L21" s="72"/>
-      <c r="M21" s="72"/>
-      <c r="N21" s="72"/>
-      <c r="O21" s="72"/>
-      <c r="P21" s="72"/>
-      <c r="Q21" s="72"/>
-      <c r="R21" s="72"/>
-      <c r="S21" s="72"/>
-      <c r="T21" s="72"/>
-      <c r="U21" s="72"/>
-      <c r="V21" s="72"/>
-      <c r="W21" s="72"/>
-      <c r="X21" s="72"/>
-      <c r="Y21" s="72"/>
-      <c r="Z21" s="72"/>
-      <c r="AA21" s="72"/>
-      <c r="AB21" s="72"/>
-      <c r="AC21" s="72"/>
-      <c r="AD21" s="72"/>
-      <c r="AE21" s="72"/>
-      <c r="AF21" s="72"/>
-      <c r="AG21" s="72"/>
-      <c r="AH21" s="72"/>
-      <c r="AI21" s="72"/>
-      <c r="AJ21" s="72"/>
-      <c r="AK21" s="72"/>
-      <c r="AL21" s="72"/>
+      <c r="B21" s="80"/>
+      <c r="C21" s="80"/>
+      <c r="D21" s="80"/>
+      <c r="E21" s="80"/>
+      <c r="F21" s="80"/>
+      <c r="G21" s="80"/>
+      <c r="H21" s="80"/>
+      <c r="I21" s="80"/>
+      <c r="J21" s="80"/>
+      <c r="K21" s="80"/>
+      <c r="L21" s="80"/>
+      <c r="M21" s="80"/>
+      <c r="N21" s="80"/>
+      <c r="O21" s="80"/>
+      <c r="P21" s="80"/>
+      <c r="Q21" s="80"/>
+      <c r="R21" s="80"/>
+      <c r="S21" s="80"/>
+      <c r="T21" s="80"/>
+      <c r="U21" s="80"/>
+      <c r="V21" s="80"/>
+      <c r="W21" s="80"/>
+      <c r="X21" s="80"/>
+      <c r="Y21" s="80"/>
+      <c r="Z21" s="80"/>
+      <c r="AA21" s="80"/>
+      <c r="AB21" s="80"/>
+      <c r="AC21" s="80"/>
+      <c r="AD21" s="80"/>
+      <c r="AE21" s="80"/>
+      <c r="AF21" s="80"/>
+      <c r="AG21" s="80"/>
+      <c r="AH21" s="80"/>
+      <c r="AI21" s="80"/>
+      <c r="AJ21" s="80"/>
+      <c r="AK21" s="80"/>
+      <c r="AL21" s="80"/>
     </row>
     <row r="22" spans="1:38" ht="15" customHeight="1">
-      <c r="A22" s="72"/>
-      <c r="B22" s="72"/>
-      <c r="C22" s="72"/>
-      <c r="D22" s="72"/>
-      <c r="E22" s="72"/>
-      <c r="F22" s="72"/>
-      <c r="G22" s="72"/>
-      <c r="H22" s="72"/>
-      <c r="I22" s="72"/>
-      <c r="J22" s="72"/>
-      <c r="K22" s="72"/>
-      <c r="L22" s="72"/>
-      <c r="M22" s="72"/>
-      <c r="N22" s="72"/>
-      <c r="O22" s="72"/>
-      <c r="P22" s="72"/>
-      <c r="Q22" s="72"/>
-      <c r="R22" s="72"/>
-      <c r="S22" s="72"/>
-      <c r="T22" s="72"/>
-      <c r="U22" s="72"/>
-      <c r="V22" s="72"/>
-      <c r="W22" s="72"/>
-      <c r="X22" s="72"/>
-      <c r="Y22" s="72"/>
-      <c r="Z22" s="72"/>
-      <c r="AA22" s="72"/>
-      <c r="AB22" s="72"/>
-      <c r="AC22" s="72"/>
-      <c r="AD22" s="72"/>
-      <c r="AE22" s="72"/>
-      <c r="AF22" s="72"/>
-      <c r="AG22" s="72"/>
-      <c r="AH22" s="72"/>
-      <c r="AI22" s="72"/>
-      <c r="AJ22" s="72"/>
-      <c r="AK22" s="72"/>
-      <c r="AL22" s="72"/>
+      <c r="A22" s="80"/>
+      <c r="B22" s="80"/>
+      <c r="C22" s="80"/>
+      <c r="D22" s="80"/>
+      <c r="E22" s="80"/>
+      <c r="F22" s="80"/>
+      <c r="G22" s="80"/>
+      <c r="H22" s="80"/>
+      <c r="I22" s="80"/>
+      <c r="J22" s="80"/>
+      <c r="K22" s="80"/>
+      <c r="L22" s="80"/>
+      <c r="M22" s="80"/>
+      <c r="N22" s="80"/>
+      <c r="O22" s="80"/>
+      <c r="P22" s="80"/>
+      <c r="Q22" s="80"/>
+      <c r="R22" s="80"/>
+      <c r="S22" s="80"/>
+      <c r="T22" s="80"/>
+      <c r="U22" s="80"/>
+      <c r="V22" s="80"/>
+      <c r="W22" s="80"/>
+      <c r="X22" s="80"/>
+      <c r="Y22" s="80"/>
+      <c r="Z22" s="80"/>
+      <c r="AA22" s="80"/>
+      <c r="AB22" s="80"/>
+      <c r="AC22" s="80"/>
+      <c r="AD22" s="80"/>
+      <c r="AE22" s="80"/>
+      <c r="AF22" s="80"/>
+      <c r="AG22" s="80"/>
+      <c r="AH22" s="80"/>
+      <c r="AI22" s="80"/>
+      <c r="AJ22" s="80"/>
+      <c r="AK22" s="80"/>
+      <c r="AL22" s="80"/>
     </row>
     <row r="23" spans="1:38" ht="15" customHeight="1">
-      <c r="A23" s="72" t="s">
+      <c r="A23" s="80" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="72"/>
-      <c r="C23" s="72"/>
-      <c r="D23" s="72"/>
-      <c r="E23" s="72"/>
-      <c r="F23" s="72"/>
-      <c r="G23" s="72"/>
-      <c r="H23" s="72"/>
-      <c r="I23" s="72"/>
-      <c r="J23" s="72"/>
-      <c r="K23" s="72"/>
-      <c r="L23" s="72"/>
-      <c r="M23" s="72"/>
-      <c r="N23" s="72"/>
-      <c r="O23" s="72"/>
-      <c r="P23" s="72"/>
-      <c r="Q23" s="72"/>
-      <c r="R23" s="72"/>
-      <c r="S23" s="72"/>
-      <c r="T23" s="72"/>
-      <c r="U23" s="72"/>
-      <c r="V23" s="72"/>
-      <c r="W23" s="72"/>
-      <c r="X23" s="72"/>
-      <c r="Y23" s="72"/>
-      <c r="Z23" s="72"/>
-      <c r="AA23" s="72"/>
-      <c r="AB23" s="72"/>
-      <c r="AC23" s="72"/>
-      <c r="AD23" s="72"/>
-      <c r="AE23" s="72"/>
-      <c r="AF23" s="72"/>
-      <c r="AG23" s="72"/>
-      <c r="AH23" s="72"/>
-      <c r="AI23" s="72"/>
-      <c r="AJ23" s="72"/>
-      <c r="AK23" s="72"/>
-      <c r="AL23" s="72"/>
+      <c r="B23" s="80"/>
+      <c r="C23" s="80"/>
+      <c r="D23" s="80"/>
+      <c r="E23" s="80"/>
+      <c r="F23" s="80"/>
+      <c r="G23" s="80"/>
+      <c r="H23" s="80"/>
+      <c r="I23" s="80"/>
+      <c r="J23" s="80"/>
+      <c r="K23" s="80"/>
+      <c r="L23" s="80"/>
+      <c r="M23" s="80"/>
+      <c r="N23" s="80"/>
+      <c r="O23" s="80"/>
+      <c r="P23" s="80"/>
+      <c r="Q23" s="80"/>
+      <c r="R23" s="80"/>
+      <c r="S23" s="80"/>
+      <c r="T23" s="80"/>
+      <c r="U23" s="80"/>
+      <c r="V23" s="80"/>
+      <c r="W23" s="80"/>
+      <c r="X23" s="80"/>
+      <c r="Y23" s="80"/>
+      <c r="Z23" s="80"/>
+      <c r="AA23" s="80"/>
+      <c r="AB23" s="80"/>
+      <c r="AC23" s="80"/>
+      <c r="AD23" s="80"/>
+      <c r="AE23" s="80"/>
+      <c r="AF23" s="80"/>
+      <c r="AG23" s="80"/>
+      <c r="AH23" s="80"/>
+      <c r="AI23" s="80"/>
+      <c r="AJ23" s="80"/>
+      <c r="AK23" s="80"/>
+      <c r="AL23" s="80"/>
     </row>
     <row r="24" spans="1:38" ht="15" customHeight="1">
-      <c r="A24" s="72"/>
-      <c r="B24" s="72"/>
-      <c r="C24" s="72"/>
-      <c r="D24" s="72"/>
-      <c r="E24" s="72"/>
-      <c r="F24" s="72"/>
-      <c r="G24" s="72"/>
-      <c r="H24" s="72"/>
-      <c r="I24" s="72"/>
-      <c r="J24" s="72"/>
-      <c r="K24" s="72"/>
-      <c r="L24" s="72"/>
-      <c r="M24" s="72"/>
-      <c r="N24" s="72"/>
-      <c r="O24" s="72"/>
-      <c r="P24" s="72"/>
-      <c r="Q24" s="72"/>
-      <c r="R24" s="72"/>
-      <c r="S24" s="72"/>
-      <c r="T24" s="72"/>
-      <c r="U24" s="72"/>
-      <c r="V24" s="72"/>
-      <c r="W24" s="72"/>
-      <c r="X24" s="72"/>
-      <c r="Y24" s="72"/>
-      <c r="Z24" s="72"/>
-      <c r="AA24" s="72"/>
-      <c r="AB24" s="72"/>
-      <c r="AC24" s="72"/>
-      <c r="AD24" s="72"/>
-      <c r="AE24" s="72"/>
-      <c r="AF24" s="72"/>
-      <c r="AG24" s="72"/>
-      <c r="AH24" s="72"/>
-      <c r="AI24" s="72"/>
-      <c r="AJ24" s="72"/>
-      <c r="AK24" s="72"/>
-      <c r="AL24" s="72"/>
+      <c r="A24" s="80"/>
+      <c r="B24" s="80"/>
+      <c r="C24" s="80"/>
+      <c r="D24" s="80"/>
+      <c r="E24" s="80"/>
+      <c r="F24" s="80"/>
+      <c r="G24" s="80"/>
+      <c r="H24" s="80"/>
+      <c r="I24" s="80"/>
+      <c r="J24" s="80"/>
+      <c r="K24" s="80"/>
+      <c r="L24" s="80"/>
+      <c r="M24" s="80"/>
+      <c r="N24" s="80"/>
+      <c r="O24" s="80"/>
+      <c r="P24" s="80"/>
+      <c r="Q24" s="80"/>
+      <c r="R24" s="80"/>
+      <c r="S24" s="80"/>
+      <c r="T24" s="80"/>
+      <c r="U24" s="80"/>
+      <c r="V24" s="80"/>
+      <c r="W24" s="80"/>
+      <c r="X24" s="80"/>
+      <c r="Y24" s="80"/>
+      <c r="Z24" s="80"/>
+      <c r="AA24" s="80"/>
+      <c r="AB24" s="80"/>
+      <c r="AC24" s="80"/>
+      <c r="AD24" s="80"/>
+      <c r="AE24" s="80"/>
+      <c r="AF24" s="80"/>
+      <c r="AG24" s="80"/>
+      <c r="AH24" s="80"/>
+      <c r="AI24" s="80"/>
+      <c r="AJ24" s="80"/>
+      <c r="AK24" s="80"/>
+      <c r="AL24" s="80"/>
     </row>
     <row r="25" spans="1:38" ht="15" customHeight="1">
       <c r="A25" s="34"/>
@@ -5129,6 +5118,22 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="Y23:AE24"/>
+    <mergeCell ref="AF23:AL24"/>
+    <mergeCell ref="Y19:AE20"/>
+    <mergeCell ref="AF19:AL20"/>
+    <mergeCell ref="R23:X24"/>
+    <mergeCell ref="R21:X22"/>
+    <mergeCell ref="Y21:AE22"/>
+    <mergeCell ref="AF21:AL22"/>
+    <mergeCell ref="R19:X20"/>
+    <mergeCell ref="A23:J24"/>
+    <mergeCell ref="K23:Q24"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A21:J22"/>
+    <mergeCell ref="K21:Q22"/>
+    <mergeCell ref="A19:J20"/>
+    <mergeCell ref="K19:Q20"/>
     <mergeCell ref="M1:AL1"/>
     <mergeCell ref="A8:E8"/>
     <mergeCell ref="A10:E10"/>
@@ -5141,24 +5146,8 @@
     <mergeCell ref="F6:M7"/>
     <mergeCell ref="A6:E7"/>
     <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A23:J24"/>
-    <mergeCell ref="K23:Q24"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="A21:J22"/>
-    <mergeCell ref="K21:Q22"/>
-    <mergeCell ref="Y23:AE24"/>
-    <mergeCell ref="AF23:AL24"/>
-    <mergeCell ref="Y19:AE20"/>
-    <mergeCell ref="AF19:AL20"/>
-    <mergeCell ref="R23:X24"/>
-    <mergeCell ref="R21:X22"/>
-    <mergeCell ref="Y21:AE22"/>
-    <mergeCell ref="A19:J20"/>
-    <mergeCell ref="K19:Q20"/>
-    <mergeCell ref="AF21:AL22"/>
     <mergeCell ref="H3:S3"/>
     <mergeCell ref="F9:M9"/>
-    <mergeCell ref="R19:X20"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -5178,12 +5167,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{626CC06E-9590-4323-BE24-60512668D6F0}">
   <dimension ref="A1:AN34"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="7" width="2.35546875" customWidth="1"/>
+    <col min="1" max="7" width="2.33203125" customWidth="1"/>
     <col min="8" max="8" width="2" customWidth="1"/>
-    <col min="9" max="31" width="2.140625" customWidth="1"/>
-    <col min="32" max="39" width="2.35546875" customWidth="1"/>
+    <col min="9" max="31" width="2.109375" customWidth="1"/>
+    <col min="32" max="39" width="2.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="15" customHeight="1">
@@ -5198,32 +5187,32 @@
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="78"/>
-      <c r="AG1" s="78"/>
-      <c r="AH1" s="78"/>
-      <c r="AI1" s="78"/>
-      <c r="AJ1" s="78"/>
-      <c r="AK1" s="78"/>
-      <c r="AL1" s="78"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="72"/>
+      <c r="O1" s="72"/>
+      <c r="P1" s="72"/>
+      <c r="Q1" s="72"/>
+      <c r="R1" s="72"/>
+      <c r="S1" s="72"/>
+      <c r="T1" s="72"/>
+      <c r="U1" s="72"/>
+      <c r="V1" s="72"/>
+      <c r="W1" s="72"/>
+      <c r="X1" s="72"/>
+      <c r="Y1" s="72"/>
+      <c r="Z1" s="72"/>
+      <c r="AA1" s="72"/>
+      <c r="AB1" s="72"/>
+      <c r="AC1" s="72"/>
+      <c r="AD1" s="72"/>
+      <c r="AE1" s="72"/>
+      <c r="AF1" s="72"/>
+      <c r="AG1" s="72"/>
+      <c r="AH1" s="72"/>
+      <c r="AI1" s="72"/>
+      <c r="AJ1" s="72"/>
+      <c r="AK1" s="72"/>
+      <c r="AL1" s="72"/>
       <c r="AM1" s="33"/>
     </row>
     <row r="2" spans="1:39" ht="15" customHeight="1">
@@ -5260,17 +5249,17 @@
       <c r="AF2" s="3"/>
     </row>
     <row r="3" spans="1:39" ht="15" customHeight="1">
-      <c r="A3" s="71"/>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="71"/>
-      <c r="K3" s="71"/>
+      <c r="A3" s="68"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
       <c r="L3" s="20"/>
       <c r="M3" s="20"/>
       <c r="N3" s="3"/>
@@ -5278,24 +5267,16 @@
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
-      <c r="S3" s="13" t="s">
-        <v>173</v>
-      </c>
+      <c r="S3" s="13"/>
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
-      <c r="V3" s="104" t="s">
-        <v>174</v>
-      </c>
-      <c r="W3" s="104"/>
-      <c r="X3" s="104"/>
-      <c r="Y3" s="104"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
       <c r="AA3" s="3"/>
       <c r="AB3" s="3"/>
-      <c r="AC3" s="3"/>
-      <c r="AD3" s="3"/>
-      <c r="AE3" s="3"/>
-      <c r="AF3" s="3"/>
     </row>
     <row r="4" spans="1:39" ht="15" customHeight="1">
       <c r="A4" s="5"/>
@@ -5436,44 +5417,44 @@
       <c r="AM7" s="14"/>
     </row>
     <row r="8" spans="1:39" ht="15" customHeight="1">
-      <c r="A8" s="82" t="s">
+      <c r="A8" s="81" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="82"/>
-      <c r="C8" s="82"/>
-      <c r="D8" s="82"/>
-      <c r="E8" s="82"/>
-      <c r="F8" s="82"/>
-      <c r="G8" s="82"/>
-      <c r="H8" s="82"/>
-      <c r="I8" s="82"/>
-      <c r="J8" s="83" t="s">
+      <c r="B8" s="81"/>
+      <c r="C8" s="81"/>
+      <c r="D8" s="81"/>
+      <c r="E8" s="81"/>
+      <c r="F8" s="81"/>
+      <c r="G8" s="81"/>
+      <c r="H8" s="81"/>
+      <c r="I8" s="81"/>
+      <c r="J8" s="86" t="s">
         <v>18</v>
       </c>
-      <c r="K8" s="83"/>
-      <c r="L8" s="83"/>
-      <c r="M8" s="83"/>
-      <c r="N8" s="83"/>
-      <c r="O8" s="83"/>
-      <c r="P8" s="83"/>
-      <c r="Q8" s="83"/>
-      <c r="R8" s="83"/>
-      <c r="S8" s="83"/>
-      <c r="T8" s="83"/>
-      <c r="U8" s="83"/>
-      <c r="V8" s="83"/>
-      <c r="W8" s="83"/>
-      <c r="X8" s="83"/>
-      <c r="Y8" s="83"/>
-      <c r="Z8" s="83"/>
-      <c r="AA8" s="83"/>
-      <c r="AB8" s="83"/>
-      <c r="AC8" s="83"/>
-      <c r="AD8" s="83"/>
-      <c r="AE8" s="83"/>
-      <c r="AF8" s="83"/>
-      <c r="AG8" s="83"/>
-      <c r="AH8" s="83"/>
+      <c r="K8" s="86"/>
+      <c r="L8" s="86"/>
+      <c r="M8" s="86"/>
+      <c r="N8" s="86"/>
+      <c r="O8" s="86"/>
+      <c r="P8" s="86"/>
+      <c r="Q8" s="86"/>
+      <c r="R8" s="86"/>
+      <c r="S8" s="86"/>
+      <c r="T8" s="86"/>
+      <c r="U8" s="86"/>
+      <c r="V8" s="86"/>
+      <c r="W8" s="86"/>
+      <c r="X8" s="86"/>
+      <c r="Y8" s="86"/>
+      <c r="Z8" s="86"/>
+      <c r="AA8" s="86"/>
+      <c r="AB8" s="86"/>
+      <c r="AC8" s="86"/>
+      <c r="AD8" s="86"/>
+      <c r="AE8" s="86"/>
+      <c r="AF8" s="86"/>
+      <c r="AG8" s="86"/>
+      <c r="AH8" s="86"/>
       <c r="AI8" s="87" t="s">
         <v>19</v>
       </c>
@@ -5483,50 +5464,50 @@
       <c r="AM8" s="14"/>
     </row>
     <row r="9" spans="1:39" ht="15" customHeight="1">
-      <c r="A9" s="82"/>
-      <c r="B9" s="82"/>
-      <c r="C9" s="82"/>
-      <c r="D9" s="82"/>
-      <c r="E9" s="82"/>
-      <c r="F9" s="82"/>
-      <c r="G9" s="82"/>
-      <c r="H9" s="82"/>
-      <c r="I9" s="82"/>
-      <c r="J9" s="83" t="s">
+      <c r="A9" s="81"/>
+      <c r="B9" s="81"/>
+      <c r="C9" s="81"/>
+      <c r="D9" s="81"/>
+      <c r="E9" s="81"/>
+      <c r="F9" s="81"/>
+      <c r="G9" s="81"/>
+      <c r="H9" s="81"/>
+      <c r="I9" s="81"/>
+      <c r="J9" s="86" t="s">
         <v>28</v>
       </c>
-      <c r="K9" s="83"/>
-      <c r="L9" s="83"/>
-      <c r="M9" s="83"/>
-      <c r="N9" s="83"/>
-      <c r="O9" s="83" t="s">
+      <c r="K9" s="86"/>
+      <c r="L9" s="86"/>
+      <c r="M9" s="86"/>
+      <c r="N9" s="86"/>
+      <c r="O9" s="86" t="s">
         <v>29</v>
       </c>
-      <c r="P9" s="83"/>
-      <c r="Q9" s="83"/>
-      <c r="R9" s="83"/>
-      <c r="S9" s="83"/>
-      <c r="T9" s="83" t="s">
+      <c r="P9" s="86"/>
+      <c r="Q9" s="86"/>
+      <c r="R9" s="86"/>
+      <c r="S9" s="86"/>
+      <c r="T9" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="U9" s="83"/>
-      <c r="V9" s="83"/>
-      <c r="W9" s="83"/>
-      <c r="X9" s="83"/>
-      <c r="Y9" s="83" t="s">
+      <c r="U9" s="86"/>
+      <c r="V9" s="86"/>
+      <c r="W9" s="86"/>
+      <c r="X9" s="86"/>
+      <c r="Y9" s="86" t="s">
         <v>31</v>
       </c>
-      <c r="Z9" s="83"/>
-      <c r="AA9" s="83"/>
-      <c r="AB9" s="83"/>
-      <c r="AC9" s="83"/>
-      <c r="AD9" s="83" t="s">
+      <c r="Z9" s="86"/>
+      <c r="AA9" s="86"/>
+      <c r="AB9" s="86"/>
+      <c r="AC9" s="86"/>
+      <c r="AD9" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="AE9" s="83"/>
-      <c r="AF9" s="83"/>
-      <c r="AG9" s="83"/>
-      <c r="AH9" s="83"/>
+      <c r="AE9" s="86"/>
+      <c r="AF9" s="86"/>
+      <c r="AG9" s="86"/>
+      <c r="AH9" s="86"/>
       <c r="AI9" s="90"/>
       <c r="AJ9" s="91"/>
       <c r="AK9" s="91"/>
@@ -5537,172 +5518,172 @@
       <c r="A10" s="73"/>
       <c r="B10" s="73"/>
       <c r="C10" s="73"/>
-      <c r="D10" s="84" t="s">
+      <c r="D10" s="83" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="85"/>
-      <c r="F10" s="85"/>
-      <c r="G10" s="85"/>
-      <c r="H10" s="85"/>
-      <c r="I10" s="86"/>
-      <c r="J10" s="83"/>
-      <c r="K10" s="83"/>
-      <c r="L10" s="83"/>
-      <c r="M10" s="83"/>
-      <c r="N10" s="83"/>
-      <c r="O10" s="83"/>
-      <c r="P10" s="83"/>
-      <c r="Q10" s="83"/>
-      <c r="R10" s="83"/>
-      <c r="S10" s="83"/>
-      <c r="T10" s="83"/>
-      <c r="U10" s="83"/>
-      <c r="V10" s="83"/>
-      <c r="W10" s="83"/>
-      <c r="X10" s="83"/>
-      <c r="Y10" s="83"/>
-      <c r="Z10" s="83"/>
-      <c r="AA10" s="83"/>
-      <c r="AB10" s="83"/>
-      <c r="AC10" s="83"/>
-      <c r="AD10" s="83"/>
-      <c r="AE10" s="83"/>
-      <c r="AF10" s="83"/>
-      <c r="AG10" s="83"/>
-      <c r="AH10" s="83"/>
-      <c r="AI10" s="84"/>
-      <c r="AJ10" s="85"/>
-      <c r="AK10" s="85"/>
-      <c r="AL10" s="86"/>
+      <c r="E10" s="84"/>
+      <c r="F10" s="84"/>
+      <c r="G10" s="84"/>
+      <c r="H10" s="84"/>
+      <c r="I10" s="85"/>
+      <c r="J10" s="86"/>
+      <c r="K10" s="86"/>
+      <c r="L10" s="86"/>
+      <c r="M10" s="86"/>
+      <c r="N10" s="86"/>
+      <c r="O10" s="86"/>
+      <c r="P10" s="86"/>
+      <c r="Q10" s="86"/>
+      <c r="R10" s="86"/>
+      <c r="S10" s="86"/>
+      <c r="T10" s="86"/>
+      <c r="U10" s="86"/>
+      <c r="V10" s="86"/>
+      <c r="W10" s="86"/>
+      <c r="X10" s="86"/>
+      <c r="Y10" s="86"/>
+      <c r="Z10" s="86"/>
+      <c r="AA10" s="86"/>
+      <c r="AB10" s="86"/>
+      <c r="AC10" s="86"/>
+      <c r="AD10" s="86"/>
+      <c r="AE10" s="86"/>
+      <c r="AF10" s="86"/>
+      <c r="AG10" s="86"/>
+      <c r="AH10" s="86"/>
+      <c r="AI10" s="83"/>
+      <c r="AJ10" s="84"/>
+      <c r="AK10" s="84"/>
+      <c r="AL10" s="85"/>
       <c r="AM10" s="21"/>
     </row>
     <row r="11" spans="1:39" ht="15" customHeight="1">
       <c r="A11" s="73"/>
       <c r="B11" s="73"/>
       <c r="C11" s="73"/>
-      <c r="D11" s="84" t="s">
+      <c r="D11" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="85"/>
-      <c r="F11" s="85"/>
-      <c r="G11" s="85"/>
-      <c r="H11" s="85"/>
-      <c r="I11" s="86"/>
-      <c r="J11" s="83"/>
-      <c r="K11" s="83"/>
-      <c r="L11" s="83"/>
-      <c r="M11" s="83"/>
-      <c r="N11" s="83"/>
-      <c r="O11" s="83"/>
-      <c r="P11" s="83"/>
-      <c r="Q11" s="83"/>
-      <c r="R11" s="83"/>
-      <c r="S11" s="83"/>
-      <c r="T11" s="83"/>
-      <c r="U11" s="83"/>
-      <c r="V11" s="83"/>
-      <c r="W11" s="83"/>
-      <c r="X11" s="83"/>
-      <c r="Y11" s="83"/>
-      <c r="Z11" s="83"/>
-      <c r="AA11" s="83"/>
-      <c r="AB11" s="83"/>
-      <c r="AC11" s="83"/>
-      <c r="AD11" s="83"/>
-      <c r="AE11" s="83"/>
-      <c r="AF11" s="83"/>
-      <c r="AG11" s="83"/>
-      <c r="AH11" s="83"/>
-      <c r="AI11" s="84"/>
-      <c r="AJ11" s="85"/>
-      <c r="AK11" s="85"/>
-      <c r="AL11" s="86"/>
+      <c r="E11" s="84"/>
+      <c r="F11" s="84"/>
+      <c r="G11" s="84"/>
+      <c r="H11" s="84"/>
+      <c r="I11" s="85"/>
+      <c r="J11" s="86"/>
+      <c r="K11" s="86"/>
+      <c r="L11" s="86"/>
+      <c r="M11" s="86"/>
+      <c r="N11" s="86"/>
+      <c r="O11" s="86"/>
+      <c r="P11" s="86"/>
+      <c r="Q11" s="86"/>
+      <c r="R11" s="86"/>
+      <c r="S11" s="86"/>
+      <c r="T11" s="86"/>
+      <c r="U11" s="86"/>
+      <c r="V11" s="86"/>
+      <c r="W11" s="86"/>
+      <c r="X11" s="86"/>
+      <c r="Y11" s="86"/>
+      <c r="Z11" s="86"/>
+      <c r="AA11" s="86"/>
+      <c r="AB11" s="86"/>
+      <c r="AC11" s="86"/>
+      <c r="AD11" s="86"/>
+      <c r="AE11" s="86"/>
+      <c r="AF11" s="86"/>
+      <c r="AG11" s="86"/>
+      <c r="AH11" s="86"/>
+      <c r="AI11" s="83"/>
+      <c r="AJ11" s="84"/>
+      <c r="AK11" s="84"/>
+      <c r="AL11" s="85"/>
       <c r="AM11" s="21"/>
     </row>
     <row r="12" spans="1:39" ht="15" customHeight="1">
       <c r="A12" s="73"/>
       <c r="B12" s="73"/>
       <c r="C12" s="73"/>
-      <c r="D12" s="84" t="s">
+      <c r="D12" s="83" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="85"/>
-      <c r="F12" s="85"/>
-      <c r="G12" s="85"/>
-      <c r="H12" s="85"/>
-      <c r="I12" s="86"/>
-      <c r="J12" s="83"/>
-      <c r="K12" s="83"/>
-      <c r="L12" s="83"/>
-      <c r="M12" s="83"/>
-      <c r="N12" s="83"/>
-      <c r="O12" s="83"/>
-      <c r="P12" s="83"/>
-      <c r="Q12" s="83"/>
-      <c r="R12" s="83"/>
-      <c r="S12" s="83"/>
-      <c r="T12" s="83"/>
-      <c r="U12" s="83"/>
-      <c r="V12" s="83"/>
-      <c r="W12" s="83"/>
-      <c r="X12" s="83"/>
-      <c r="Y12" s="83"/>
-      <c r="Z12" s="83"/>
-      <c r="AA12" s="83"/>
-      <c r="AB12" s="83"/>
-      <c r="AC12" s="83"/>
-      <c r="AD12" s="83"/>
-      <c r="AE12" s="83"/>
-      <c r="AF12" s="83"/>
-      <c r="AG12" s="83"/>
-      <c r="AH12" s="83"/>
-      <c r="AI12" s="84"/>
-      <c r="AJ12" s="85"/>
-      <c r="AK12" s="85"/>
-      <c r="AL12" s="86"/>
+      <c r="E12" s="84"/>
+      <c r="F12" s="84"/>
+      <c r="G12" s="84"/>
+      <c r="H12" s="84"/>
+      <c r="I12" s="85"/>
+      <c r="J12" s="86"/>
+      <c r="K12" s="86"/>
+      <c r="L12" s="86"/>
+      <c r="M12" s="86"/>
+      <c r="N12" s="86"/>
+      <c r="O12" s="86"/>
+      <c r="P12" s="86"/>
+      <c r="Q12" s="86"/>
+      <c r="R12" s="86"/>
+      <c r="S12" s="86"/>
+      <c r="T12" s="86"/>
+      <c r="U12" s="86"/>
+      <c r="V12" s="86"/>
+      <c r="W12" s="86"/>
+      <c r="X12" s="86"/>
+      <c r="Y12" s="86"/>
+      <c r="Z12" s="86"/>
+      <c r="AA12" s="86"/>
+      <c r="AB12" s="86"/>
+      <c r="AC12" s="86"/>
+      <c r="AD12" s="86"/>
+      <c r="AE12" s="86"/>
+      <c r="AF12" s="86"/>
+      <c r="AG12" s="86"/>
+      <c r="AH12" s="86"/>
+      <c r="AI12" s="83"/>
+      <c r="AJ12" s="84"/>
+      <c r="AK12" s="84"/>
+      <c r="AL12" s="85"/>
       <c r="AM12" s="21"/>
     </row>
     <row r="13" spans="1:39" ht="15" customHeight="1">
       <c r="A13" s="73"/>
       <c r="B13" s="73"/>
       <c r="C13" s="73"/>
-      <c r="D13" s="84" t="s">
+      <c r="D13" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="85"/>
-      <c r="F13" s="85"/>
-      <c r="G13" s="85"/>
-      <c r="H13" s="85"/>
-      <c r="I13" s="86"/>
-      <c r="J13" s="83"/>
-      <c r="K13" s="83"/>
-      <c r="L13" s="83"/>
-      <c r="M13" s="83"/>
-      <c r="N13" s="83"/>
-      <c r="O13" s="83"/>
-      <c r="P13" s="83"/>
-      <c r="Q13" s="83"/>
-      <c r="R13" s="83"/>
-      <c r="S13" s="83"/>
-      <c r="T13" s="83"/>
-      <c r="U13" s="83"/>
-      <c r="V13" s="83"/>
-      <c r="W13" s="83"/>
-      <c r="X13" s="83"/>
-      <c r="Y13" s="83"/>
-      <c r="Z13" s="83"/>
-      <c r="AA13" s="83"/>
-      <c r="AB13" s="83"/>
-      <c r="AC13" s="83"/>
-      <c r="AD13" s="83"/>
-      <c r="AE13" s="83"/>
-      <c r="AF13" s="83"/>
-      <c r="AG13" s="83"/>
-      <c r="AH13" s="83"/>
-      <c r="AI13" s="84"/>
-      <c r="AJ13" s="85"/>
-      <c r="AK13" s="85"/>
-      <c r="AL13" s="86"/>
+      <c r="E13" s="84"/>
+      <c r="F13" s="84"/>
+      <c r="G13" s="84"/>
+      <c r="H13" s="84"/>
+      <c r="I13" s="85"/>
+      <c r="J13" s="86"/>
+      <c r="K13" s="86"/>
+      <c r="L13" s="86"/>
+      <c r="M13" s="86"/>
+      <c r="N13" s="86"/>
+      <c r="O13" s="86"/>
+      <c r="P13" s="86"/>
+      <c r="Q13" s="86"/>
+      <c r="R13" s="86"/>
+      <c r="S13" s="86"/>
+      <c r="T13" s="86"/>
+      <c r="U13" s="86"/>
+      <c r="V13" s="86"/>
+      <c r="W13" s="86"/>
+      <c r="X13" s="86"/>
+      <c r="Y13" s="86"/>
+      <c r="Z13" s="86"/>
+      <c r="AA13" s="86"/>
+      <c r="AB13" s="86"/>
+      <c r="AC13" s="86"/>
+      <c r="AD13" s="86"/>
+      <c r="AE13" s="86"/>
+      <c r="AF13" s="86"/>
+      <c r="AG13" s="86"/>
+      <c r="AH13" s="86"/>
+      <c r="AI13" s="83"/>
+      <c r="AJ13" s="84"/>
+      <c r="AK13" s="84"/>
+      <c r="AL13" s="85"/>
       <c r="AM13" s="21"/>
     </row>
     <row r="14" spans="1:39" ht="15" customHeight="1">
@@ -6414,8 +6395,32 @@
       <c r="N34" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="41">
-    <mergeCell ref="V3:Y3"/>
+  <mergeCells count="40">
+    <mergeCell ref="AI13:AL13"/>
+    <mergeCell ref="Y12:AC12"/>
+    <mergeCell ref="AD12:AH12"/>
+    <mergeCell ref="O11:S11"/>
+    <mergeCell ref="T11:X11"/>
+    <mergeCell ref="Y11:AC11"/>
+    <mergeCell ref="AI12:AL12"/>
+    <mergeCell ref="AI8:AL9"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="D12:I12"/>
+    <mergeCell ref="AD9:AH9"/>
+    <mergeCell ref="J12:N12"/>
+    <mergeCell ref="T12:X12"/>
+    <mergeCell ref="O10:S10"/>
+    <mergeCell ref="T10:X10"/>
+    <mergeCell ref="Y10:AC10"/>
+    <mergeCell ref="AD10:AH10"/>
+    <mergeCell ref="AD11:AH11"/>
+    <mergeCell ref="O12:S12"/>
+    <mergeCell ref="Y9:AC9"/>
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="AI10:AL10"/>
+    <mergeCell ref="AI11:AL11"/>
     <mergeCell ref="D13:I13"/>
     <mergeCell ref="J8:AH8"/>
     <mergeCell ref="O13:S13"/>
@@ -6431,31 +6436,6 @@
     <mergeCell ref="J9:N9"/>
     <mergeCell ref="O9:S9"/>
     <mergeCell ref="T9:X9"/>
-    <mergeCell ref="Y9:AC9"/>
-    <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="AI10:AL10"/>
-    <mergeCell ref="AI11:AL11"/>
-    <mergeCell ref="AI12:AL12"/>
-    <mergeCell ref="AI8:AL9"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="D12:I12"/>
-    <mergeCell ref="AD9:AH9"/>
-    <mergeCell ref="J12:N12"/>
-    <mergeCell ref="T12:X12"/>
-    <mergeCell ref="O10:S10"/>
-    <mergeCell ref="T10:X10"/>
-    <mergeCell ref="Y10:AC10"/>
-    <mergeCell ref="AD10:AH10"/>
-    <mergeCell ref="AD11:AH11"/>
-    <mergeCell ref="O12:S12"/>
-    <mergeCell ref="AI13:AL13"/>
-    <mergeCell ref="Y12:AC12"/>
-    <mergeCell ref="AD12:AH12"/>
-    <mergeCell ref="O11:S11"/>
-    <mergeCell ref="T11:X11"/>
-    <mergeCell ref="Y11:AC11"/>
   </mergeCells>
   <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -6475,12 +6455,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ACC2EF5-C6BB-4CA4-98B8-CD887DC0BA25}">
   <dimension ref="A1:AM37"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="7" width="2.35546875" customWidth="1"/>
+    <col min="1" max="7" width="2.33203125" customWidth="1"/>
     <col min="8" max="8" width="2" customWidth="1"/>
-    <col min="9" max="31" width="2.140625" customWidth="1"/>
-    <col min="32" max="39" width="2.35546875" customWidth="1"/>
+    <col min="9" max="31" width="2.109375" customWidth="1"/>
+    <col min="32" max="39" width="2.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="15" customHeight="1">
@@ -6495,32 +6475,32 @@
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="78"/>
-      <c r="AG1" s="78"/>
-      <c r="AH1" s="78"/>
-      <c r="AI1" s="78"/>
-      <c r="AJ1" s="78"/>
-      <c r="AK1" s="78"/>
-      <c r="AL1" s="78"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="72"/>
+      <c r="O1" s="72"/>
+      <c r="P1" s="72"/>
+      <c r="Q1" s="72"/>
+      <c r="R1" s="72"/>
+      <c r="S1" s="72"/>
+      <c r="T1" s="72"/>
+      <c r="U1" s="72"/>
+      <c r="V1" s="72"/>
+      <c r="W1" s="72"/>
+      <c r="X1" s="72"/>
+      <c r="Y1" s="72"/>
+      <c r="Z1" s="72"/>
+      <c r="AA1" s="72"/>
+      <c r="AB1" s="72"/>
+      <c r="AC1" s="72"/>
+      <c r="AD1" s="72"/>
+      <c r="AE1" s="72"/>
+      <c r="AF1" s="72"/>
+      <c r="AG1" s="72"/>
+      <c r="AH1" s="72"/>
+      <c r="AI1" s="72"/>
+      <c r="AJ1" s="72"/>
+      <c r="AK1" s="72"/>
+      <c r="AL1" s="72"/>
       <c r="AM1" s="33"/>
     </row>
     <row r="2" spans="1:39" ht="15" customHeight="1">
@@ -6556,17 +6536,17 @@
       <c r="AF2" s="3"/>
     </row>
     <row r="3" spans="1:39" ht="15" customHeight="1">
-      <c r="A3" s="71"/>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="71"/>
-      <c r="K3" s="71"/>
+      <c r="A3" s="68"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
       <c r="L3" s="20"/>
       <c r="M3" s="20"/>
       <c r="N3" s="45" t="s">
@@ -7806,12 +7786,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05ADACB2-95B1-43B0-BEDC-E6A99EE22ABB}">
   <dimension ref="A1:AM68"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="7" width="2.35546875" customWidth="1"/>
+    <col min="1" max="7" width="2.33203125" customWidth="1"/>
     <col min="8" max="8" width="2" customWidth="1"/>
-    <col min="9" max="31" width="2.140625" customWidth="1"/>
-    <col min="32" max="39" width="2.35546875" customWidth="1"/>
+    <col min="9" max="31" width="2.109375" customWidth="1"/>
+    <col min="32" max="39" width="2.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="15" customHeight="1">
@@ -7826,32 +7806,32 @@
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="78"/>
-      <c r="AG1" s="78"/>
-      <c r="AH1" s="78"/>
-      <c r="AI1" s="78"/>
-      <c r="AJ1" s="78"/>
-      <c r="AK1" s="78"/>
-      <c r="AL1" s="78"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="72"/>
+      <c r="O1" s="72"/>
+      <c r="P1" s="72"/>
+      <c r="Q1" s="72"/>
+      <c r="R1" s="72"/>
+      <c r="S1" s="72"/>
+      <c r="T1" s="72"/>
+      <c r="U1" s="72"/>
+      <c r="V1" s="72"/>
+      <c r="W1" s="72"/>
+      <c r="X1" s="72"/>
+      <c r="Y1" s="72"/>
+      <c r="Z1" s="72"/>
+      <c r="AA1" s="72"/>
+      <c r="AB1" s="72"/>
+      <c r="AC1" s="72"/>
+      <c r="AD1" s="72"/>
+      <c r="AE1" s="72"/>
+      <c r="AF1" s="72"/>
+      <c r="AG1" s="72"/>
+      <c r="AH1" s="72"/>
+      <c r="AI1" s="72"/>
+      <c r="AJ1" s="72"/>
+      <c r="AK1" s="72"/>
+      <c r="AL1" s="72"/>
       <c r="AM1" s="33"/>
     </row>
     <row r="2" spans="1:39" ht="15" customHeight="1">
@@ -7887,17 +7867,17 @@
       <c r="AF2" s="3"/>
     </row>
     <row r="3" spans="1:39" ht="15" customHeight="1">
-      <c r="A3" s="71"/>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="71"/>
-      <c r="K3" s="71"/>
+      <c r="A3" s="68"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
       <c r="L3" s="20"/>
       <c r="M3" s="20"/>
       <c r="N3" s="16" t="s">
@@ -7922,7 +7902,7 @@
       <c r="AE3" s="3"/>
       <c r="AF3" s="3"/>
     </row>
-    <row r="4" spans="1:39" ht="5.9" customHeight="1">
+    <row r="4" spans="1:39" ht="5.85" customHeight="1">
       <c r="A4" s="5"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -7953,7 +7933,7 @@
       <c r="AE4" s="3"/>
       <c r="AF4" s="3"/>
     </row>
-    <row r="5" spans="1:39" ht="14.15" customHeight="1">
+    <row r="5" spans="1:39" ht="14.1" customHeight="1">
       <c r="A5" s="94" t="s">
         <v>171</v>
       </c>
@@ -7989,7 +7969,7 @@
       <c r="AE5" s="3"/>
       <c r="AF5" s="3"/>
     </row>
-    <row r="6" spans="1:39" ht="5.9" customHeight="1">
+    <row r="6" spans="1:39" ht="5.85" customHeight="1">
       <c r="A6" s="5"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -8056,7 +8036,7 @@
       <c r="AE7" s="3"/>
       <c r="AF7" s="3"/>
     </row>
-    <row r="8" spans="1:39" ht="5.9" customHeight="1">
+    <row r="8" spans="1:39" ht="5.85" customHeight="1">
       <c r="A8" s="21"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
@@ -8246,7 +8226,7 @@
       <c r="AL12" s="14"/>
       <c r="AM12" s="14"/>
     </row>
-    <row r="13" spans="1:39" ht="5.9" customHeight="1">
+    <row r="13" spans="1:39" ht="5.85" customHeight="1">
       <c r="A13" s="46"/>
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
@@ -8508,7 +8488,7 @@
       <c r="AL18" s="14"/>
       <c r="AM18" s="14"/>
     </row>
-    <row r="19" spans="1:39" ht="5.9" customHeight="1">
+    <row r="19" spans="1:39" ht="5.85" customHeight="1">
       <c r="A19" s="46"/>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
@@ -8727,7 +8707,7 @@
       <c r="AL23" s="14"/>
       <c r="AM23" s="14"/>
     </row>
-    <row r="24" spans="1:39" ht="5.9" customHeight="1">
+    <row r="24" spans="1:39" ht="5.85" customHeight="1">
       <c r="A24" s="46"/>
       <c r="B24" s="14"/>
       <c r="C24" s="14"/>
@@ -8946,7 +8926,7 @@
       <c r="AL28" s="14"/>
       <c r="AM28" s="14"/>
     </row>
-    <row r="29" spans="1:39" ht="5.9" customHeight="1">
+    <row r="29" spans="1:39" ht="5.85" customHeight="1">
       <c r="A29" s="21"/>
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
@@ -9077,7 +9057,7 @@
       <c r="AL31" s="14"/>
       <c r="AM31" s="14"/>
     </row>
-    <row r="32" spans="1:39" ht="8.5" customHeight="1">
+    <row r="32" spans="1:39" ht="8.5500000000000007" customHeight="1">
       <c r="A32" s="21"/>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
@@ -9309,7 +9289,7 @@
       <c r="AE37" s="3"/>
       <c r="AF37" s="3"/>
     </row>
-    <row r="38" spans="1:39" ht="5.9" customHeight="1">
+    <row r="38" spans="1:39" ht="5.85" customHeight="1">
       <c r="A38" s="25"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
@@ -9445,7 +9425,7 @@
       <c r="AE41" s="3"/>
       <c r="AF41" s="3"/>
     </row>
-    <row r="42" spans="1:39" ht="5.9" customHeight="1">
+    <row r="42" spans="1:39" ht="5.85" customHeight="1">
       <c r="A42" s="46"/>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
@@ -9610,7 +9590,7 @@
       <c r="AE46" s="3"/>
       <c r="AF46" s="3"/>
     </row>
-    <row r="47" spans="1:39" ht="5.9" customHeight="1">
+    <row r="47" spans="1:39" ht="5.85" customHeight="1">
       <c r="A47" s="46"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
@@ -9812,7 +9792,7 @@
       <c r="AE52" s="3"/>
       <c r="AF52" s="3"/>
     </row>
-    <row r="53" spans="1:39" ht="5.9" customHeight="1">
+    <row r="53" spans="1:39" ht="5.85" customHeight="1">
       <c r="A53" s="25"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
@@ -9843,7 +9823,7 @@
       <c r="AE53" s="3"/>
       <c r="AF53" s="3"/>
     </row>
-    <row r="54" spans="1:39" ht="14.15" customHeight="1">
+    <row r="54" spans="1:39" ht="14.1" customHeight="1">
       <c r="A54" s="46" t="s">
         <v>106</v>
       </c>
@@ -9878,7 +9858,7 @@
       <c r="AE54" s="3"/>
       <c r="AF54" s="3"/>
     </row>
-    <row r="55" spans="1:39" ht="14.15" customHeight="1">
+    <row r="55" spans="1:39" ht="14.1" customHeight="1">
       <c r="A55" s="46" t="s">
         <v>109</v>
       </c>
@@ -9913,7 +9893,7 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
     </row>
-    <row r="56" spans="1:39" ht="14.15" customHeight="1">
+    <row r="56" spans="1:39" ht="14.1" customHeight="1">
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
       <c r="G56" s="3"/>
@@ -9945,7 +9925,7 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
     </row>
-    <row r="57" spans="1:39" ht="14.15" customHeight="1">
+    <row r="57" spans="1:39" ht="14.1" customHeight="1">
       <c r="A57" s="25"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
@@ -9978,7 +9958,7 @@
       <c r="AE57" s="3"/>
       <c r="AF57" s="3"/>
     </row>
-    <row r="58" spans="1:39" ht="5.9" customHeight="1">
+    <row r="58" spans="1:39" ht="5.85" customHeight="1">
       <c r="A58" s="25"/>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
@@ -10311,12 +10291,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{309B97D2-0661-4F44-8203-7296258BC5D2}">
   <dimension ref="A1:AM60"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="7" width="2.35546875" customWidth="1"/>
+    <col min="1" max="7" width="2.33203125" customWidth="1"/>
     <col min="8" max="8" width="2" customWidth="1"/>
-    <col min="9" max="31" width="2.140625" customWidth="1"/>
-    <col min="32" max="39" width="2.35546875" customWidth="1"/>
+    <col min="9" max="31" width="2.109375" customWidth="1"/>
+    <col min="32" max="39" width="2.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="15" customHeight="1">
@@ -10331,60 +10311,60 @@
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="78"/>
-      <c r="AG1" s="78"/>
-      <c r="AH1" s="78"/>
-      <c r="AI1" s="78"/>
-      <c r="AJ1" s="78"/>
-      <c r="AK1" s="78"/>
-      <c r="AL1" s="78"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="72"/>
+      <c r="O1" s="72"/>
+      <c r="P1" s="72"/>
+      <c r="Q1" s="72"/>
+      <c r="R1" s="72"/>
+      <c r="S1" s="72"/>
+      <c r="T1" s="72"/>
+      <c r="U1" s="72"/>
+      <c r="V1" s="72"/>
+      <c r="W1" s="72"/>
+      <c r="X1" s="72"/>
+      <c r="Y1" s="72"/>
+      <c r="Z1" s="72"/>
+      <c r="AA1" s="72"/>
+      <c r="AB1" s="72"/>
+      <c r="AC1" s="72"/>
+      <c r="AD1" s="72"/>
+      <c r="AE1" s="72"/>
+      <c r="AF1" s="72"/>
+      <c r="AG1" s="72"/>
+      <c r="AH1" s="72"/>
+      <c r="AI1" s="72"/>
+      <c r="AJ1" s="72"/>
+      <c r="AK1" s="72"/>
+      <c r="AL1" s="72"/>
       <c r="AM1" s="33"/>
     </row>
     <row r="2" spans="1:39" ht="15" customHeight="1">
-      <c r="A2" s="101" t="s">
+      <c r="A2" s="98" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="101"/>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="101"/>
-      <c r="H2" s="101"/>
-      <c r="I2" s="101"/>
-      <c r="J2" s="101"/>
-      <c r="K2" s="101"/>
-      <c r="L2" s="101"/>
-      <c r="M2" s="101"/>
-      <c r="N2" s="101"/>
-      <c r="O2" s="101"/>
-      <c r="P2" s="101"/>
-      <c r="Q2" s="101"/>
-      <c r="R2" s="101"/>
-      <c r="S2" s="101"/>
-      <c r="T2" s="101"/>
-      <c r="U2" s="101"/>
-      <c r="V2" s="101"/>
-      <c r="W2" s="101"/>
+      <c r="B2" s="98"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="98"/>
+      <c r="J2" s="98"/>
+      <c r="K2" s="98"/>
+      <c r="L2" s="98"/>
+      <c r="M2" s="98"/>
+      <c r="N2" s="98"/>
+      <c r="O2" s="98"/>
+      <c r="P2" s="98"/>
+      <c r="Q2" s="98"/>
+      <c r="R2" s="98"/>
+      <c r="S2" s="98"/>
+      <c r="T2" s="98"/>
+      <c r="U2" s="98"/>
+      <c r="V2" s="98"/>
+      <c r="W2" s="98"/>
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
@@ -10431,7 +10411,7 @@
       <c r="AE3" s="3"/>
       <c r="AF3" s="3"/>
     </row>
-    <row r="4" spans="1:39" ht="8.5" customHeight="1">
+    <row r="4" spans="1:39" ht="8.5500000000000007" customHeight="1">
       <c r="A4" s="48"/>
       <c r="B4" s="46"/>
       <c r="C4" s="46"/>
@@ -10501,7 +10481,7 @@
       <c r="AE5" s="3"/>
       <c r="AF5" s="3"/>
     </row>
-    <row r="6" spans="1:39" ht="8.5" customHeight="1">
+    <row r="6" spans="1:39" ht="8.5500000000000007" customHeight="1">
       <c r="A6" s="5"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -10533,229 +10513,229 @@
       <c r="AF6" s="3"/>
     </row>
     <row r="7" spans="1:39" ht="15" customHeight="1">
-      <c r="A7" s="83"/>
-      <c r="B7" s="83"/>
-      <c r="C7" s="83"/>
-      <c r="D7" s="83"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="83"/>
-      <c r="G7" s="83"/>
-      <c r="H7" s="83"/>
-      <c r="I7" s="83"/>
-      <c r="J7" s="83"/>
-      <c r="K7" s="83"/>
-      <c r="L7" s="83"/>
-      <c r="M7" s="98" t="s">
+      <c r="A7" s="86"/>
+      <c r="B7" s="86"/>
+      <c r="C7" s="86"/>
+      <c r="D7" s="86"/>
+      <c r="E7" s="86"/>
+      <c r="F7" s="86"/>
+      <c r="G7" s="86"/>
+      <c r="H7" s="86"/>
+      <c r="I7" s="86"/>
+      <c r="J7" s="86"/>
+      <c r="K7" s="86"/>
+      <c r="L7" s="86"/>
+      <c r="M7" s="96" t="s">
         <v>115</v>
       </c>
-      <c r="N7" s="99"/>
-      <c r="O7" s="99"/>
-      <c r="P7" s="99"/>
-      <c r="Q7" s="99"/>
-      <c r="R7" s="99"/>
-      <c r="S7" s="99"/>
-      <c r="T7" s="99"/>
-      <c r="U7" s="99"/>
-      <c r="V7" s="98" t="s">
+      <c r="N7" s="97"/>
+      <c r="O7" s="97"/>
+      <c r="P7" s="97"/>
+      <c r="Q7" s="97"/>
+      <c r="R7" s="97"/>
+      <c r="S7" s="97"/>
+      <c r="T7" s="97"/>
+      <c r="U7" s="97"/>
+      <c r="V7" s="96" t="s">
         <v>116</v>
       </c>
-      <c r="W7" s="99"/>
-      <c r="X7" s="99"/>
-      <c r="Y7" s="99"/>
-      <c r="Z7" s="99"/>
-      <c r="AA7" s="99"/>
-      <c r="AB7" s="99"/>
-      <c r="AC7" s="99"/>
-      <c r="AD7" s="99"/>
-      <c r="AE7" s="98" t="s">
+      <c r="W7" s="97"/>
+      <c r="X7" s="97"/>
+      <c r="Y7" s="97"/>
+      <c r="Z7" s="97"/>
+      <c r="AA7" s="97"/>
+      <c r="AB7" s="97"/>
+      <c r="AC7" s="97"/>
+      <c r="AD7" s="97"/>
+      <c r="AE7" s="96" t="s">
         <v>117</v>
       </c>
-      <c r="AF7" s="99"/>
-      <c r="AG7" s="99"/>
-      <c r="AH7" s="99"/>
-      <c r="AI7" s="99"/>
-      <c r="AJ7" s="99"/>
-      <c r="AK7" s="99"/>
-      <c r="AL7" s="99"/>
-      <c r="AM7" s="99"/>
+      <c r="AF7" s="97"/>
+      <c r="AG7" s="97"/>
+      <c r="AH7" s="97"/>
+      <c r="AI7" s="97"/>
+      <c r="AJ7" s="97"/>
+      <c r="AK7" s="97"/>
+      <c r="AL7" s="97"/>
+      <c r="AM7" s="97"/>
     </row>
     <row r="8" spans="1:39" ht="15" customHeight="1">
-      <c r="A8" s="83"/>
-      <c r="B8" s="83"/>
-      <c r="C8" s="83"/>
-      <c r="D8" s="83"/>
-      <c r="E8" s="83"/>
-      <c r="F8" s="83"/>
-      <c r="G8" s="83"/>
-      <c r="H8" s="83"/>
-      <c r="I8" s="83"/>
-      <c r="J8" s="83"/>
-      <c r="K8" s="83"/>
-      <c r="L8" s="83"/>
-      <c r="M8" s="98" t="s">
+      <c r="A8" s="86"/>
+      <c r="B8" s="86"/>
+      <c r="C8" s="86"/>
+      <c r="D8" s="86"/>
+      <c r="E8" s="86"/>
+      <c r="F8" s="86"/>
+      <c r="G8" s="86"/>
+      <c r="H8" s="86"/>
+      <c r="I8" s="86"/>
+      <c r="J8" s="86"/>
+      <c r="K8" s="86"/>
+      <c r="L8" s="86"/>
+      <c r="M8" s="96" t="s">
         <v>118</v>
       </c>
-      <c r="N8" s="99"/>
-      <c r="O8" s="99"/>
-      <c r="P8" s="99"/>
-      <c r="Q8" s="99"/>
-      <c r="R8" s="99"/>
-      <c r="S8" s="99"/>
-      <c r="T8" s="99"/>
-      <c r="U8" s="99"/>
-      <c r="V8" s="98" t="s">
+      <c r="N8" s="97"/>
+      <c r="O8" s="97"/>
+      <c r="P8" s="97"/>
+      <c r="Q8" s="97"/>
+      <c r="R8" s="97"/>
+      <c r="S8" s="97"/>
+      <c r="T8" s="97"/>
+      <c r="U8" s="97"/>
+      <c r="V8" s="96" t="s">
         <v>119</v>
       </c>
-      <c r="W8" s="99"/>
-      <c r="X8" s="99"/>
-      <c r="Y8" s="99"/>
-      <c r="Z8" s="99"/>
-      <c r="AA8" s="99"/>
-      <c r="AB8" s="99"/>
-      <c r="AC8" s="99"/>
-      <c r="AD8" s="99"/>
-      <c r="AE8" s="98" t="s">
+      <c r="W8" s="97"/>
+      <c r="X8" s="97"/>
+      <c r="Y8" s="97"/>
+      <c r="Z8" s="97"/>
+      <c r="AA8" s="97"/>
+      <c r="AB8" s="97"/>
+      <c r="AC8" s="97"/>
+      <c r="AD8" s="97"/>
+      <c r="AE8" s="96" t="s">
         <v>120</v>
       </c>
-      <c r="AF8" s="99"/>
-      <c r="AG8" s="99"/>
-      <c r="AH8" s="99"/>
-      <c r="AI8" s="99"/>
-      <c r="AJ8" s="99"/>
-      <c r="AK8" s="99"/>
-      <c r="AL8" s="99"/>
-      <c r="AM8" s="99"/>
+      <c r="AF8" s="97"/>
+      <c r="AG8" s="97"/>
+      <c r="AH8" s="97"/>
+      <c r="AI8" s="97"/>
+      <c r="AJ8" s="97"/>
+      <c r="AK8" s="97"/>
+      <c r="AL8" s="97"/>
+      <c r="AM8" s="97"/>
     </row>
     <row r="9" spans="1:39" ht="15" customHeight="1">
-      <c r="A9" s="100" t="s">
+      <c r="A9" s="95" t="s">
         <v>113</v>
       </c>
-      <c r="B9" s="100"/>
-      <c r="C9" s="100"/>
-      <c r="D9" s="100"/>
-      <c r="E9" s="100"/>
-      <c r="F9" s="100"/>
-      <c r="G9" s="100"/>
-      <c r="H9" s="100"/>
-      <c r="I9" s="100"/>
-      <c r="J9" s="100"/>
-      <c r="K9" s="100"/>
-      <c r="L9" s="100"/>
-      <c r="M9" s="99"/>
-      <c r="N9" s="99"/>
-      <c r="O9" s="99"/>
-      <c r="P9" s="99"/>
-      <c r="Q9" s="99"/>
-      <c r="R9" s="99"/>
-      <c r="S9" s="99"/>
-      <c r="T9" s="99"/>
-      <c r="U9" s="99"/>
-      <c r="V9" s="99"/>
-      <c r="W9" s="99"/>
-      <c r="X9" s="99"/>
-      <c r="Y9" s="99"/>
-      <c r="Z9" s="99"/>
-      <c r="AA9" s="99"/>
-      <c r="AB9" s="99"/>
-      <c r="AC9" s="99"/>
-      <c r="AD9" s="99"/>
-      <c r="AE9" s="99"/>
-      <c r="AF9" s="99"/>
-      <c r="AG9" s="99"/>
-      <c r="AH9" s="99"/>
-      <c r="AI9" s="99"/>
-      <c r="AJ9" s="99"/>
-      <c r="AK9" s="99"/>
-      <c r="AL9" s="99"/>
-      <c r="AM9" s="99"/>
+      <c r="B9" s="95"/>
+      <c r="C9" s="95"/>
+      <c r="D9" s="95"/>
+      <c r="E9" s="95"/>
+      <c r="F9" s="95"/>
+      <c r="G9" s="95"/>
+      <c r="H9" s="95"/>
+      <c r="I9" s="95"/>
+      <c r="J9" s="95"/>
+      <c r="K9" s="95"/>
+      <c r="L9" s="95"/>
+      <c r="M9" s="97"/>
+      <c r="N9" s="97"/>
+      <c r="O9" s="97"/>
+      <c r="P9" s="97"/>
+      <c r="Q9" s="97"/>
+      <c r="R9" s="97"/>
+      <c r="S9" s="97"/>
+      <c r="T9" s="97"/>
+      <c r="U9" s="97"/>
+      <c r="V9" s="97"/>
+      <c r="W9" s="97"/>
+      <c r="X9" s="97"/>
+      <c r="Y9" s="97"/>
+      <c r="Z9" s="97"/>
+      <c r="AA9" s="97"/>
+      <c r="AB9" s="97"/>
+      <c r="AC9" s="97"/>
+      <c r="AD9" s="97"/>
+      <c r="AE9" s="97"/>
+      <c r="AF9" s="97"/>
+      <c r="AG9" s="97"/>
+      <c r="AH9" s="97"/>
+      <c r="AI9" s="97"/>
+      <c r="AJ9" s="97"/>
+      <c r="AK9" s="97"/>
+      <c r="AL9" s="97"/>
+      <c r="AM9" s="97"/>
     </row>
     <row r="10" spans="1:39" ht="15" customHeight="1">
-      <c r="A10" s="100" t="s">
+      <c r="A10" s="95" t="s">
         <v>112</v>
       </c>
-      <c r="B10" s="100"/>
-      <c r="C10" s="100"/>
-      <c r="D10" s="100"/>
-      <c r="E10" s="100"/>
-      <c r="F10" s="100"/>
-      <c r="G10" s="100"/>
-      <c r="H10" s="100"/>
-      <c r="I10" s="100"/>
-      <c r="J10" s="100"/>
-      <c r="K10" s="100"/>
-      <c r="L10" s="100"/>
-      <c r="M10" s="99"/>
-      <c r="N10" s="99"/>
-      <c r="O10" s="99"/>
-      <c r="P10" s="99"/>
-      <c r="Q10" s="99"/>
-      <c r="R10" s="99"/>
-      <c r="S10" s="99"/>
-      <c r="T10" s="99"/>
-      <c r="U10" s="99"/>
-      <c r="V10" s="99"/>
-      <c r="W10" s="99"/>
-      <c r="X10" s="99"/>
-      <c r="Y10" s="99"/>
-      <c r="Z10" s="99"/>
-      <c r="AA10" s="99"/>
-      <c r="AB10" s="99"/>
-      <c r="AC10" s="99"/>
-      <c r="AD10" s="99"/>
-      <c r="AE10" s="99"/>
-      <c r="AF10" s="99"/>
-      <c r="AG10" s="99"/>
-      <c r="AH10" s="99"/>
-      <c r="AI10" s="99"/>
-      <c r="AJ10" s="99"/>
-      <c r="AK10" s="99"/>
-      <c r="AL10" s="99"/>
-      <c r="AM10" s="99"/>
+      <c r="B10" s="95"/>
+      <c r="C10" s="95"/>
+      <c r="D10" s="95"/>
+      <c r="E10" s="95"/>
+      <c r="F10" s="95"/>
+      <c r="G10" s="95"/>
+      <c r="H10" s="95"/>
+      <c r="I10" s="95"/>
+      <c r="J10" s="95"/>
+      <c r="K10" s="95"/>
+      <c r="L10" s="95"/>
+      <c r="M10" s="97"/>
+      <c r="N10" s="97"/>
+      <c r="O10" s="97"/>
+      <c r="P10" s="97"/>
+      <c r="Q10" s="97"/>
+      <c r="R10" s="97"/>
+      <c r="S10" s="97"/>
+      <c r="T10" s="97"/>
+      <c r="U10" s="97"/>
+      <c r="V10" s="97"/>
+      <c r="W10" s="97"/>
+      <c r="X10" s="97"/>
+      <c r="Y10" s="97"/>
+      <c r="Z10" s="97"/>
+      <c r="AA10" s="97"/>
+      <c r="AB10" s="97"/>
+      <c r="AC10" s="97"/>
+      <c r="AD10" s="97"/>
+      <c r="AE10" s="97"/>
+      <c r="AF10" s="97"/>
+      <c r="AG10" s="97"/>
+      <c r="AH10" s="97"/>
+      <c r="AI10" s="97"/>
+      <c r="AJ10" s="97"/>
+      <c r="AK10" s="97"/>
+      <c r="AL10" s="97"/>
+      <c r="AM10" s="97"/>
     </row>
     <row r="11" spans="1:39" ht="15" customHeight="1">
-      <c r="A11" s="100" t="s">
+      <c r="A11" s="95" t="s">
         <v>114</v>
       </c>
-      <c r="B11" s="100"/>
-      <c r="C11" s="100"/>
-      <c r="D11" s="100"/>
-      <c r="E11" s="100"/>
-      <c r="F11" s="100"/>
-      <c r="G11" s="100"/>
-      <c r="H11" s="100"/>
-      <c r="I11" s="100"/>
-      <c r="J11" s="100"/>
-      <c r="K11" s="100"/>
-      <c r="L11" s="100"/>
-      <c r="M11" s="99"/>
-      <c r="N11" s="99"/>
-      <c r="O11" s="99"/>
-      <c r="P11" s="99"/>
-      <c r="Q11" s="99"/>
-      <c r="R11" s="99"/>
-      <c r="S11" s="99"/>
-      <c r="T11" s="99"/>
-      <c r="U11" s="99"/>
-      <c r="V11" s="99"/>
-      <c r="W11" s="99"/>
-      <c r="X11" s="99"/>
-      <c r="Y11" s="99"/>
-      <c r="Z11" s="99"/>
-      <c r="AA11" s="99"/>
-      <c r="AB11" s="99"/>
-      <c r="AC11" s="99"/>
-      <c r="AD11" s="99"/>
-      <c r="AE11" s="99"/>
-      <c r="AF11" s="99"/>
-      <c r="AG11" s="99"/>
-      <c r="AH11" s="99"/>
-      <c r="AI11" s="99"/>
-      <c r="AJ11" s="99"/>
-      <c r="AK11" s="99"/>
-      <c r="AL11" s="99"/>
-      <c r="AM11" s="99"/>
-    </row>
-    <row r="12" spans="1:39" ht="8.5" customHeight="1">
+      <c r="B11" s="95"/>
+      <c r="C11" s="95"/>
+      <c r="D11" s="95"/>
+      <c r="E11" s="95"/>
+      <c r="F11" s="95"/>
+      <c r="G11" s="95"/>
+      <c r="H11" s="95"/>
+      <c r="I11" s="95"/>
+      <c r="J11" s="95"/>
+      <c r="K11" s="95"/>
+      <c r="L11" s="95"/>
+      <c r="M11" s="97"/>
+      <c r="N11" s="97"/>
+      <c r="O11" s="97"/>
+      <c r="P11" s="97"/>
+      <c r="Q11" s="97"/>
+      <c r="R11" s="97"/>
+      <c r="S11" s="97"/>
+      <c r="T11" s="97"/>
+      <c r="U11" s="97"/>
+      <c r="V11" s="97"/>
+      <c r="W11" s="97"/>
+      <c r="X11" s="97"/>
+      <c r="Y11" s="97"/>
+      <c r="Z11" s="97"/>
+      <c r="AA11" s="97"/>
+      <c r="AB11" s="97"/>
+      <c r="AC11" s="97"/>
+      <c r="AD11" s="97"/>
+      <c r="AE11" s="97"/>
+      <c r="AF11" s="97"/>
+      <c r="AG11" s="97"/>
+      <c r="AH11" s="97"/>
+      <c r="AI11" s="97"/>
+      <c r="AJ11" s="97"/>
+      <c r="AK11" s="97"/>
+      <c r="AL11" s="97"/>
+      <c r="AM11" s="97"/>
+    </row>
+    <row r="12" spans="1:39" ht="8.5500000000000007" customHeight="1">
       <c r="A12" s="46"/>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
@@ -10839,7 +10819,7 @@
       <c r="AL13" s="14"/>
       <c r="AM13" s="14"/>
     </row>
-    <row r="14" spans="1:39" ht="8.5" customHeight="1">
+    <row r="14" spans="1:39" ht="8.5500000000000007" customHeight="1">
       <c r="A14" s="46"/>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
@@ -10924,605 +10904,605 @@
       <c r="AM15" s="14"/>
     </row>
     <row r="16" spans="1:39" ht="15" customHeight="1">
-      <c r="A16" s="95" t="s">
+      <c r="A16" s="99" t="s">
         <v>123</v>
       </c>
-      <c r="B16" s="95"/>
-      <c r="C16" s="95"/>
-      <c r="D16" s="95"/>
-      <c r="E16" s="95"/>
-      <c r="F16" s="95"/>
-      <c r="G16" s="95"/>
-      <c r="H16" s="95"/>
-      <c r="I16" s="95"/>
-      <c r="J16" s="95"/>
-      <c r="K16" s="95"/>
-      <c r="L16" s="95"/>
-      <c r="M16" s="95"/>
-      <c r="N16" s="95"/>
-      <c r="O16" s="95"/>
-      <c r="P16" s="95"/>
-      <c r="Q16" s="95"/>
-      <c r="R16" s="95"/>
-      <c r="S16" s="95"/>
-      <c r="T16" s="95"/>
-      <c r="U16" s="95"/>
-      <c r="V16" s="95"/>
-      <c r="W16" s="95"/>
-      <c r="X16" s="95"/>
-      <c r="Y16" s="95"/>
-      <c r="Z16" s="95"/>
-      <c r="AA16" s="95"/>
-      <c r="AB16" s="95"/>
-      <c r="AC16" s="95"/>
-      <c r="AD16" s="95"/>
-      <c r="AE16" s="95"/>
-      <c r="AF16" s="95"/>
-      <c r="AG16" s="95"/>
-      <c r="AH16" s="95"/>
-      <c r="AI16" s="95"/>
-      <c r="AJ16" s="95"/>
-      <c r="AK16" s="95"/>
-      <c r="AL16" s="95"/>
-      <c r="AM16" s="95"/>
+      <c r="B16" s="99"/>
+      <c r="C16" s="99"/>
+      <c r="D16" s="99"/>
+      <c r="E16" s="99"/>
+      <c r="F16" s="99"/>
+      <c r="G16" s="99"/>
+      <c r="H16" s="99"/>
+      <c r="I16" s="99"/>
+      <c r="J16" s="99"/>
+      <c r="K16" s="99"/>
+      <c r="L16" s="99"/>
+      <c r="M16" s="99"/>
+      <c r="N16" s="99"/>
+      <c r="O16" s="99"/>
+      <c r="P16" s="99"/>
+      <c r="Q16" s="99"/>
+      <c r="R16" s="99"/>
+      <c r="S16" s="99"/>
+      <c r="T16" s="99"/>
+      <c r="U16" s="99"/>
+      <c r="V16" s="99"/>
+      <c r="W16" s="99"/>
+      <c r="X16" s="99"/>
+      <c r="Y16" s="99"/>
+      <c r="Z16" s="99"/>
+      <c r="AA16" s="99"/>
+      <c r="AB16" s="99"/>
+      <c r="AC16" s="99"/>
+      <c r="AD16" s="99"/>
+      <c r="AE16" s="99"/>
+      <c r="AF16" s="99"/>
+      <c r="AG16" s="99"/>
+      <c r="AH16" s="99"/>
+      <c r="AI16" s="99"/>
+      <c r="AJ16" s="99"/>
+      <c r="AK16" s="99"/>
+      <c r="AL16" s="99"/>
+      <c r="AM16" s="99"/>
     </row>
     <row r="17" spans="1:39" ht="15" customHeight="1">
-      <c r="A17" s="95" t="s">
+      <c r="A17" s="99" t="s">
         <v>124</v>
       </c>
-      <c r="B17" s="95"/>
-      <c r="C17" s="95"/>
-      <c r="D17" s="95"/>
-      <c r="E17" s="95"/>
-      <c r="F17" s="95"/>
-      <c r="G17" s="95"/>
-      <c r="H17" s="95"/>
-      <c r="I17" s="95"/>
-      <c r="J17" s="95"/>
-      <c r="K17" s="95"/>
-      <c r="L17" s="95"/>
-      <c r="M17" s="95"/>
-      <c r="N17" s="95"/>
-      <c r="O17" s="95"/>
-      <c r="P17" s="95"/>
-      <c r="Q17" s="95"/>
-      <c r="R17" s="95"/>
-      <c r="S17" s="95"/>
-      <c r="T17" s="95"/>
-      <c r="U17" s="95"/>
-      <c r="V17" s="95"/>
-      <c r="W17" s="95"/>
-      <c r="X17" s="95"/>
-      <c r="Y17" s="95"/>
-      <c r="Z17" s="95"/>
-      <c r="AA17" s="95"/>
-      <c r="AB17" s="95"/>
-      <c r="AC17" s="95"/>
-      <c r="AD17" s="95"/>
-      <c r="AE17" s="95"/>
-      <c r="AF17" s="95"/>
-      <c r="AG17" s="95"/>
-      <c r="AH17" s="95"/>
-      <c r="AI17" s="95"/>
-      <c r="AJ17" s="95"/>
-      <c r="AK17" s="95"/>
-      <c r="AL17" s="95"/>
-      <c r="AM17" s="95"/>
+      <c r="B17" s="99"/>
+      <c r="C17" s="99"/>
+      <c r="D17" s="99"/>
+      <c r="E17" s="99"/>
+      <c r="F17" s="99"/>
+      <c r="G17" s="99"/>
+      <c r="H17" s="99"/>
+      <c r="I17" s="99"/>
+      <c r="J17" s="99"/>
+      <c r="K17" s="99"/>
+      <c r="L17" s="99"/>
+      <c r="M17" s="99"/>
+      <c r="N17" s="99"/>
+      <c r="O17" s="99"/>
+      <c r="P17" s="99"/>
+      <c r="Q17" s="99"/>
+      <c r="R17" s="99"/>
+      <c r="S17" s="99"/>
+      <c r="T17" s="99"/>
+      <c r="U17" s="99"/>
+      <c r="V17" s="99"/>
+      <c r="W17" s="99"/>
+      <c r="X17" s="99"/>
+      <c r="Y17" s="99"/>
+      <c r="Z17" s="99"/>
+      <c r="AA17" s="99"/>
+      <c r="AB17" s="99"/>
+      <c r="AC17" s="99"/>
+      <c r="AD17" s="99"/>
+      <c r="AE17" s="99"/>
+      <c r="AF17" s="99"/>
+      <c r="AG17" s="99"/>
+      <c r="AH17" s="99"/>
+      <c r="AI17" s="99"/>
+      <c r="AJ17" s="99"/>
+      <c r="AK17" s="99"/>
+      <c r="AL17" s="99"/>
+      <c r="AM17" s="99"/>
     </row>
     <row r="18" spans="1:39" ht="15" customHeight="1">
-      <c r="A18" s="98" t="s">
+      <c r="A18" s="96" t="s">
         <v>125</v>
       </c>
-      <c r="B18" s="98"/>
-      <c r="C18" s="98"/>
-      <c r="D18" s="98"/>
-      <c r="E18" s="98"/>
-      <c r="F18" s="98"/>
-      <c r="G18" s="98"/>
-      <c r="H18" s="98"/>
-      <c r="I18" s="98"/>
-      <c r="J18" s="98"/>
-      <c r="K18" s="98"/>
-      <c r="L18" s="98"/>
-      <c r="M18" s="98"/>
-      <c r="N18" s="98"/>
-      <c r="O18" s="98"/>
-      <c r="P18" s="98"/>
-      <c r="Q18" s="98"/>
-      <c r="R18" s="98"/>
-      <c r="S18" s="98"/>
-      <c r="T18" s="98"/>
-      <c r="U18" s="98"/>
-      <c r="V18" s="98"/>
-      <c r="W18" s="98"/>
-      <c r="X18" s="98"/>
-      <c r="Y18" s="98"/>
-      <c r="Z18" s="98"/>
-      <c r="AA18" s="98"/>
-      <c r="AB18" s="98"/>
-      <c r="AC18" s="98"/>
-      <c r="AD18" s="98"/>
-      <c r="AE18" s="98"/>
-      <c r="AF18" s="98"/>
-      <c r="AG18" s="98"/>
-      <c r="AH18" s="98"/>
-      <c r="AI18" s="98"/>
-      <c r="AJ18" s="98"/>
-      <c r="AK18" s="98"/>
-      <c r="AL18" s="98"/>
-      <c r="AM18" s="98"/>
+      <c r="B18" s="96"/>
+      <c r="C18" s="96"/>
+      <c r="D18" s="96"/>
+      <c r="E18" s="96"/>
+      <c r="F18" s="96"/>
+      <c r="G18" s="96"/>
+      <c r="H18" s="96"/>
+      <c r="I18" s="96"/>
+      <c r="J18" s="96"/>
+      <c r="K18" s="96"/>
+      <c r="L18" s="96"/>
+      <c r="M18" s="96"/>
+      <c r="N18" s="96"/>
+      <c r="O18" s="96"/>
+      <c r="P18" s="96"/>
+      <c r="Q18" s="96"/>
+      <c r="R18" s="96"/>
+      <c r="S18" s="96"/>
+      <c r="T18" s="96"/>
+      <c r="U18" s="96"/>
+      <c r="V18" s="96"/>
+      <c r="W18" s="96"/>
+      <c r="X18" s="96"/>
+      <c r="Y18" s="96"/>
+      <c r="Z18" s="96"/>
+      <c r="AA18" s="96"/>
+      <c r="AB18" s="96"/>
+      <c r="AC18" s="96"/>
+      <c r="AD18" s="96"/>
+      <c r="AE18" s="96"/>
+      <c r="AF18" s="96"/>
+      <c r="AG18" s="96"/>
+      <c r="AH18" s="96"/>
+      <c r="AI18" s="96"/>
+      <c r="AJ18" s="96"/>
+      <c r="AK18" s="96"/>
+      <c r="AL18" s="96"/>
+      <c r="AM18" s="96"/>
     </row>
     <row r="19" spans="1:39" ht="15" customHeight="1">
-      <c r="A19" s="98" t="s">
+      <c r="A19" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="98"/>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
-      <c r="H19" s="98"/>
-      <c r="I19" s="98"/>
-      <c r="J19" s="98" t="s">
+      <c r="B19" s="96"/>
+      <c r="C19" s="96"/>
+      <c r="D19" s="96"/>
+      <c r="E19" s="96"/>
+      <c r="F19" s="96"/>
+      <c r="G19" s="96"/>
+      <c r="H19" s="96"/>
+      <c r="I19" s="96"/>
+      <c r="J19" s="96" t="s">
         <v>9</v>
       </c>
-      <c r="K19" s="83"/>
-      <c r="L19" s="83"/>
-      <c r="M19" s="98" t="s">
+      <c r="K19" s="86"/>
+      <c r="L19" s="86"/>
+      <c r="M19" s="96" t="s">
         <v>10</v>
       </c>
-      <c r="N19" s="83"/>
-      <c r="O19" s="83"/>
-      <c r="P19" s="98" t="s">
+      <c r="N19" s="86"/>
+      <c r="O19" s="86"/>
+      <c r="P19" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="Q19" s="83"/>
-      <c r="R19" s="83"/>
-      <c r="S19" s="98" t="s">
+      <c r="Q19" s="86"/>
+      <c r="R19" s="86"/>
+      <c r="S19" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="T19" s="83"/>
-      <c r="U19" s="83"/>
-      <c r="V19" s="98" t="s">
+      <c r="T19" s="86"/>
+      <c r="U19" s="86"/>
+      <c r="V19" s="96" t="s">
         <v>13</v>
       </c>
-      <c r="W19" s="83"/>
-      <c r="X19" s="83"/>
-      <c r="Y19" s="98" t="s">
+      <c r="W19" s="86"/>
+      <c r="X19" s="86"/>
+      <c r="Y19" s="96" t="s">
         <v>128</v>
       </c>
-      <c r="Z19" s="83"/>
-      <c r="AA19" s="83"/>
-      <c r="AB19" s="98" t="s">
+      <c r="Z19" s="86"/>
+      <c r="AA19" s="86"/>
+      <c r="AB19" s="96" t="s">
         <v>129</v>
       </c>
-      <c r="AC19" s="83"/>
-      <c r="AD19" s="83"/>
-      <c r="AE19" s="98" t="s">
+      <c r="AC19" s="86"/>
+      <c r="AD19" s="86"/>
+      <c r="AE19" s="96" t="s">
         <v>130</v>
       </c>
-      <c r="AF19" s="83"/>
-      <c r="AG19" s="83"/>
-      <c r="AH19" s="98" t="s">
+      <c r="AF19" s="86"/>
+      <c r="AG19" s="86"/>
+      <c r="AH19" s="96" t="s">
         <v>131</v>
       </c>
-      <c r="AI19" s="83"/>
-      <c r="AJ19" s="83"/>
-      <c r="AK19" s="98" t="s">
+      <c r="AI19" s="86"/>
+      <c r="AJ19" s="86"/>
+      <c r="AK19" s="96" t="s">
         <v>132</v>
       </c>
-      <c r="AL19" s="83"/>
-      <c r="AM19" s="83"/>
+      <c r="AL19" s="86"/>
+      <c r="AM19" s="86"/>
     </row>
     <row r="20" spans="1:39" ht="15" customHeight="1">
-      <c r="A20" s="98" t="s">
+      <c r="A20" s="96" t="s">
         <v>127</v>
       </c>
-      <c r="B20" s="98"/>
-      <c r="C20" s="98"/>
-      <c r="D20" s="98"/>
-      <c r="E20" s="98"/>
-      <c r="F20" s="98"/>
-      <c r="G20" s="98"/>
-      <c r="H20" s="98"/>
-      <c r="I20" s="98"/>
-      <c r="J20" s="83"/>
-      <c r="K20" s="83"/>
-      <c r="L20" s="83"/>
-      <c r="M20" s="83"/>
-      <c r="N20" s="83"/>
-      <c r="O20" s="83"/>
-      <c r="P20" s="83"/>
-      <c r="Q20" s="83"/>
-      <c r="R20" s="83"/>
-      <c r="S20" s="83"/>
-      <c r="T20" s="83"/>
-      <c r="U20" s="83"/>
-      <c r="V20" s="83"/>
-      <c r="W20" s="83"/>
-      <c r="X20" s="83"/>
-      <c r="Y20" s="83"/>
-      <c r="Z20" s="83"/>
-      <c r="AA20" s="83"/>
-      <c r="AB20" s="83"/>
-      <c r="AC20" s="83"/>
-      <c r="AD20" s="83"/>
-      <c r="AE20" s="83"/>
-      <c r="AF20" s="83"/>
-      <c r="AG20" s="83"/>
-      <c r="AH20" s="83"/>
-      <c r="AI20" s="83"/>
-      <c r="AJ20" s="83"/>
-      <c r="AK20" s="83"/>
-      <c r="AL20" s="83"/>
-      <c r="AM20" s="83"/>
+      <c r="B20" s="96"/>
+      <c r="C20" s="96"/>
+      <c r="D20" s="96"/>
+      <c r="E20" s="96"/>
+      <c r="F20" s="96"/>
+      <c r="G20" s="96"/>
+      <c r="H20" s="96"/>
+      <c r="I20" s="96"/>
+      <c r="J20" s="86"/>
+      <c r="K20" s="86"/>
+      <c r="L20" s="86"/>
+      <c r="M20" s="86"/>
+      <c r="N20" s="86"/>
+      <c r="O20" s="86"/>
+      <c r="P20" s="86"/>
+      <c r="Q20" s="86"/>
+      <c r="R20" s="86"/>
+      <c r="S20" s="86"/>
+      <c r="T20" s="86"/>
+      <c r="U20" s="86"/>
+      <c r="V20" s="86"/>
+      <c r="W20" s="86"/>
+      <c r="X20" s="86"/>
+      <c r="Y20" s="86"/>
+      <c r="Z20" s="86"/>
+      <c r="AA20" s="86"/>
+      <c r="AB20" s="86"/>
+      <c r="AC20" s="86"/>
+      <c r="AD20" s="86"/>
+      <c r="AE20" s="86"/>
+      <c r="AF20" s="86"/>
+      <c r="AG20" s="86"/>
+      <c r="AH20" s="86"/>
+      <c r="AI20" s="86"/>
+      <c r="AJ20" s="86"/>
+      <c r="AK20" s="86"/>
+      <c r="AL20" s="86"/>
+      <c r="AM20" s="86"/>
     </row>
     <row r="21" spans="1:39" ht="15" customHeight="1">
-      <c r="A21" s="72" t="s">
+      <c r="A21" s="80" t="s">
         <v>126</v>
       </c>
-      <c r="B21" s="72"/>
-      <c r="C21" s="72"/>
-      <c r="D21" s="72"/>
-      <c r="E21" s="72"/>
-      <c r="F21" s="72"/>
-      <c r="G21" s="72"/>
-      <c r="H21" s="72"/>
-      <c r="I21" s="72"/>
-      <c r="J21" s="83"/>
-      <c r="K21" s="83"/>
-      <c r="L21" s="83"/>
-      <c r="M21" s="83"/>
-      <c r="N21" s="83"/>
-      <c r="O21" s="83"/>
-      <c r="P21" s="83"/>
-      <c r="Q21" s="83"/>
-      <c r="R21" s="83"/>
-      <c r="S21" s="83"/>
-      <c r="T21" s="83"/>
-      <c r="U21" s="83"/>
-      <c r="V21" s="83"/>
-      <c r="W21" s="83"/>
-      <c r="X21" s="83"/>
-      <c r="Y21" s="83"/>
-      <c r="Z21" s="83"/>
-      <c r="AA21" s="83"/>
-      <c r="AB21" s="83"/>
-      <c r="AC21" s="83"/>
-      <c r="AD21" s="83"/>
-      <c r="AE21" s="83"/>
-      <c r="AF21" s="83"/>
-      <c r="AG21" s="83"/>
-      <c r="AH21" s="83"/>
-      <c r="AI21" s="83"/>
-      <c r="AJ21" s="83"/>
-      <c r="AK21" s="83"/>
-      <c r="AL21" s="83"/>
-      <c r="AM21" s="83"/>
+      <c r="B21" s="80"/>
+      <c r="C21" s="80"/>
+      <c r="D21" s="80"/>
+      <c r="E21" s="80"/>
+      <c r="F21" s="80"/>
+      <c r="G21" s="80"/>
+      <c r="H21" s="80"/>
+      <c r="I21" s="80"/>
+      <c r="J21" s="86"/>
+      <c r="K21" s="86"/>
+      <c r="L21" s="86"/>
+      <c r="M21" s="86"/>
+      <c r="N21" s="86"/>
+      <c r="O21" s="86"/>
+      <c r="P21" s="86"/>
+      <c r="Q21" s="86"/>
+      <c r="R21" s="86"/>
+      <c r="S21" s="86"/>
+      <c r="T21" s="86"/>
+      <c r="U21" s="86"/>
+      <c r="V21" s="86"/>
+      <c r="W21" s="86"/>
+      <c r="X21" s="86"/>
+      <c r="Y21" s="86"/>
+      <c r="Z21" s="86"/>
+      <c r="AA21" s="86"/>
+      <c r="AB21" s="86"/>
+      <c r="AC21" s="86"/>
+      <c r="AD21" s="86"/>
+      <c r="AE21" s="86"/>
+      <c r="AF21" s="86"/>
+      <c r="AG21" s="86"/>
+      <c r="AH21" s="86"/>
+      <c r="AI21" s="86"/>
+      <c r="AJ21" s="86"/>
+      <c r="AK21" s="86"/>
+      <c r="AL21" s="86"/>
+      <c r="AM21" s="86"/>
     </row>
     <row r="22" spans="1:39" ht="15" customHeight="1">
-      <c r="A22" s="98" t="s">
+      <c r="A22" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="98"/>
-      <c r="C22" s="98"/>
-      <c r="D22" s="98"/>
-      <c r="E22" s="98"/>
-      <c r="F22" s="98"/>
-      <c r="G22" s="98"/>
-      <c r="H22" s="98"/>
-      <c r="I22" s="98"/>
-      <c r="J22" s="98" t="s">
+      <c r="B22" s="96"/>
+      <c r="C22" s="96"/>
+      <c r="D22" s="96"/>
+      <c r="E22" s="96"/>
+      <c r="F22" s="96"/>
+      <c r="G22" s="96"/>
+      <c r="H22" s="96"/>
+      <c r="I22" s="96"/>
+      <c r="J22" s="96" t="s">
         <v>133</v>
       </c>
-      <c r="K22" s="83"/>
-      <c r="L22" s="83"/>
-      <c r="M22" s="98" t="s">
+      <c r="K22" s="86"/>
+      <c r="L22" s="86"/>
+      <c r="M22" s="96" t="s">
         <v>134</v>
       </c>
-      <c r="N22" s="83"/>
-      <c r="O22" s="83"/>
-      <c r="P22" s="98" t="s">
+      <c r="N22" s="86"/>
+      <c r="O22" s="86"/>
+      <c r="P22" s="96" t="s">
         <v>135</v>
       </c>
-      <c r="Q22" s="83"/>
-      <c r="R22" s="83"/>
-      <c r="S22" s="98" t="s">
+      <c r="Q22" s="86"/>
+      <c r="R22" s="86"/>
+      <c r="S22" s="96" t="s">
         <v>136</v>
       </c>
-      <c r="T22" s="83"/>
-      <c r="U22" s="83"/>
-      <c r="V22" s="98" t="s">
+      <c r="T22" s="86"/>
+      <c r="U22" s="86"/>
+      <c r="V22" s="96" t="s">
         <v>137</v>
       </c>
-      <c r="W22" s="83"/>
-      <c r="X22" s="83"/>
-      <c r="Y22" s="98" t="s">
+      <c r="W22" s="86"/>
+      <c r="X22" s="86"/>
+      <c r="Y22" s="96" t="s">
         <v>138</v>
       </c>
-      <c r="Z22" s="83"/>
-      <c r="AA22" s="83"/>
-      <c r="AB22" s="98" t="s">
+      <c r="Z22" s="86"/>
+      <c r="AA22" s="86"/>
+      <c r="AB22" s="96" t="s">
         <v>139</v>
       </c>
-      <c r="AC22" s="83"/>
-      <c r="AD22" s="83"/>
-      <c r="AE22" s="98" t="s">
+      <c r="AC22" s="86"/>
+      <c r="AD22" s="86"/>
+      <c r="AE22" s="96" t="s">
         <v>140</v>
       </c>
-      <c r="AF22" s="83"/>
-      <c r="AG22" s="83"/>
-      <c r="AH22" s="98" t="s">
+      <c r="AF22" s="86"/>
+      <c r="AG22" s="86"/>
+      <c r="AH22" s="96" t="s">
         <v>141</v>
       </c>
-      <c r="AI22" s="83"/>
-      <c r="AJ22" s="83"/>
-      <c r="AK22" s="98" t="s">
+      <c r="AI22" s="86"/>
+      <c r="AJ22" s="86"/>
+      <c r="AK22" s="96" t="s">
         <v>142</v>
       </c>
-      <c r="AL22" s="83"/>
-      <c r="AM22" s="83"/>
+      <c r="AL22" s="86"/>
+      <c r="AM22" s="86"/>
     </row>
     <row r="23" spans="1:39" ht="15" customHeight="1">
-      <c r="A23" s="98" t="s">
+      <c r="A23" s="96" t="s">
         <v>127</v>
       </c>
-      <c r="B23" s="98"/>
-      <c r="C23" s="98"/>
-      <c r="D23" s="98"/>
-      <c r="E23" s="98"/>
-      <c r="F23" s="98"/>
-      <c r="G23" s="98"/>
-      <c r="H23" s="98"/>
-      <c r="I23" s="98"/>
-      <c r="J23" s="83"/>
-      <c r="K23" s="83"/>
-      <c r="L23" s="83"/>
-      <c r="M23" s="83"/>
-      <c r="N23" s="83"/>
-      <c r="O23" s="83"/>
-      <c r="P23" s="83"/>
-      <c r="Q23" s="83"/>
-      <c r="R23" s="83"/>
-      <c r="S23" s="83"/>
-      <c r="T23" s="83"/>
-      <c r="U23" s="83"/>
-      <c r="V23" s="83"/>
-      <c r="W23" s="83"/>
-      <c r="X23" s="83"/>
-      <c r="Y23" s="83"/>
-      <c r="Z23" s="83"/>
-      <c r="AA23" s="83"/>
-      <c r="AB23" s="83"/>
-      <c r="AC23" s="83"/>
-      <c r="AD23" s="83"/>
-      <c r="AE23" s="83"/>
-      <c r="AF23" s="83"/>
-      <c r="AG23" s="83"/>
-      <c r="AH23" s="83"/>
-      <c r="AI23" s="83"/>
-      <c r="AJ23" s="83"/>
-      <c r="AK23" s="83"/>
-      <c r="AL23" s="83"/>
-      <c r="AM23" s="83"/>
+      <c r="B23" s="96"/>
+      <c r="C23" s="96"/>
+      <c r="D23" s="96"/>
+      <c r="E23" s="96"/>
+      <c r="F23" s="96"/>
+      <c r="G23" s="96"/>
+      <c r="H23" s="96"/>
+      <c r="I23" s="96"/>
+      <c r="J23" s="86"/>
+      <c r="K23" s="86"/>
+      <c r="L23" s="86"/>
+      <c r="M23" s="86"/>
+      <c r="N23" s="86"/>
+      <c r="O23" s="86"/>
+      <c r="P23" s="86"/>
+      <c r="Q23" s="86"/>
+      <c r="R23" s="86"/>
+      <c r="S23" s="86"/>
+      <c r="T23" s="86"/>
+      <c r="U23" s="86"/>
+      <c r="V23" s="86"/>
+      <c r="W23" s="86"/>
+      <c r="X23" s="86"/>
+      <c r="Y23" s="86"/>
+      <c r="Z23" s="86"/>
+      <c r="AA23" s="86"/>
+      <c r="AB23" s="86"/>
+      <c r="AC23" s="86"/>
+      <c r="AD23" s="86"/>
+      <c r="AE23" s="86"/>
+      <c r="AF23" s="86"/>
+      <c r="AG23" s="86"/>
+      <c r="AH23" s="86"/>
+      <c r="AI23" s="86"/>
+      <c r="AJ23" s="86"/>
+      <c r="AK23" s="86"/>
+      <c r="AL23" s="86"/>
+      <c r="AM23" s="86"/>
     </row>
     <row r="24" spans="1:39" ht="15" customHeight="1">
-      <c r="A24" s="72" t="s">
+      <c r="A24" s="80" t="s">
         <v>126</v>
       </c>
-      <c r="B24" s="72"/>
-      <c r="C24" s="72"/>
-      <c r="D24" s="72"/>
-      <c r="E24" s="72"/>
-      <c r="F24" s="72"/>
-      <c r="G24" s="72"/>
-      <c r="H24" s="72"/>
-      <c r="I24" s="72"/>
-      <c r="J24" s="83"/>
-      <c r="K24" s="83"/>
-      <c r="L24" s="83"/>
-      <c r="M24" s="83"/>
-      <c r="N24" s="83"/>
-      <c r="O24" s="83"/>
-      <c r="P24" s="83"/>
-      <c r="Q24" s="83"/>
-      <c r="R24" s="83"/>
-      <c r="S24" s="83"/>
-      <c r="T24" s="83"/>
-      <c r="U24" s="83"/>
-      <c r="V24" s="83"/>
-      <c r="W24" s="83"/>
-      <c r="X24" s="83"/>
-      <c r="Y24" s="83"/>
-      <c r="Z24" s="83"/>
-      <c r="AA24" s="83"/>
-      <c r="AB24" s="83"/>
-      <c r="AC24" s="83"/>
-      <c r="AD24" s="83"/>
-      <c r="AE24" s="83"/>
-      <c r="AF24" s="83"/>
-      <c r="AG24" s="83"/>
-      <c r="AH24" s="83"/>
-      <c r="AI24" s="83"/>
-      <c r="AJ24" s="83"/>
-      <c r="AK24" s="83"/>
-      <c r="AL24" s="83"/>
-      <c r="AM24" s="83"/>
+      <c r="B24" s="80"/>
+      <c r="C24" s="80"/>
+      <c r="D24" s="80"/>
+      <c r="E24" s="80"/>
+      <c r="F24" s="80"/>
+      <c r="G24" s="80"/>
+      <c r="H24" s="80"/>
+      <c r="I24" s="80"/>
+      <c r="J24" s="86"/>
+      <c r="K24" s="86"/>
+      <c r="L24" s="86"/>
+      <c r="M24" s="86"/>
+      <c r="N24" s="86"/>
+      <c r="O24" s="86"/>
+      <c r="P24" s="86"/>
+      <c r="Q24" s="86"/>
+      <c r="R24" s="86"/>
+      <c r="S24" s="86"/>
+      <c r="T24" s="86"/>
+      <c r="U24" s="86"/>
+      <c r="V24" s="86"/>
+      <c r="W24" s="86"/>
+      <c r="X24" s="86"/>
+      <c r="Y24" s="86"/>
+      <c r="Z24" s="86"/>
+      <c r="AA24" s="86"/>
+      <c r="AB24" s="86"/>
+      <c r="AC24" s="86"/>
+      <c r="AD24" s="86"/>
+      <c r="AE24" s="86"/>
+      <c r="AF24" s="86"/>
+      <c r="AG24" s="86"/>
+      <c r="AH24" s="86"/>
+      <c r="AI24" s="86"/>
+      <c r="AJ24" s="86"/>
+      <c r="AK24" s="86"/>
+      <c r="AL24" s="86"/>
+      <c r="AM24" s="86"/>
     </row>
     <row r="25" spans="1:39" ht="15" customHeight="1">
-      <c r="A25" s="95" t="s">
+      <c r="A25" s="99" t="s">
         <v>143</v>
       </c>
-      <c r="B25" s="95"/>
-      <c r="C25" s="95"/>
-      <c r="D25" s="95"/>
-      <c r="E25" s="95"/>
-      <c r="F25" s="95"/>
-      <c r="G25" s="95"/>
-      <c r="H25" s="95"/>
-      <c r="I25" s="95"/>
-      <c r="J25" s="95"/>
-      <c r="K25" s="95"/>
-      <c r="L25" s="95"/>
-      <c r="M25" s="95"/>
-      <c r="N25" s="95"/>
-      <c r="O25" s="95"/>
-      <c r="P25" s="95"/>
-      <c r="Q25" s="95"/>
-      <c r="R25" s="95"/>
-      <c r="S25" s="95"/>
-      <c r="T25" s="95"/>
-      <c r="U25" s="95"/>
-      <c r="V25" s="95"/>
-      <c r="W25" s="95"/>
-      <c r="X25" s="95"/>
-      <c r="Y25" s="95"/>
-      <c r="Z25" s="95"/>
-      <c r="AA25" s="95"/>
-      <c r="AB25" s="95"/>
-      <c r="AC25" s="95"/>
-      <c r="AD25" s="95"/>
-      <c r="AE25" s="95"/>
-      <c r="AF25" s="95"/>
-      <c r="AG25" s="95"/>
-      <c r="AH25" s="95"/>
-      <c r="AI25" s="95"/>
-      <c r="AJ25" s="95"/>
-      <c r="AK25" s="95"/>
-      <c r="AL25" s="95"/>
-      <c r="AM25" s="95"/>
+      <c r="B25" s="99"/>
+      <c r="C25" s="99"/>
+      <c r="D25" s="99"/>
+      <c r="E25" s="99"/>
+      <c r="F25" s="99"/>
+      <c r="G25" s="99"/>
+      <c r="H25" s="99"/>
+      <c r="I25" s="99"/>
+      <c r="J25" s="99"/>
+      <c r="K25" s="99"/>
+      <c r="L25" s="99"/>
+      <c r="M25" s="99"/>
+      <c r="N25" s="99"/>
+      <c r="O25" s="99"/>
+      <c r="P25" s="99"/>
+      <c r="Q25" s="99"/>
+      <c r="R25" s="99"/>
+      <c r="S25" s="99"/>
+      <c r="T25" s="99"/>
+      <c r="U25" s="99"/>
+      <c r="V25" s="99"/>
+      <c r="W25" s="99"/>
+      <c r="X25" s="99"/>
+      <c r="Y25" s="99"/>
+      <c r="Z25" s="99"/>
+      <c r="AA25" s="99"/>
+      <c r="AB25" s="99"/>
+      <c r="AC25" s="99"/>
+      <c r="AD25" s="99"/>
+      <c r="AE25" s="99"/>
+      <c r="AF25" s="99"/>
+      <c r="AG25" s="99"/>
+      <c r="AH25" s="99"/>
+      <c r="AI25" s="99"/>
+      <c r="AJ25" s="99"/>
+      <c r="AK25" s="99"/>
+      <c r="AL25" s="99"/>
+      <c r="AM25" s="99"/>
     </row>
     <row r="26" spans="1:39" ht="15" customHeight="1">
-      <c r="A26" s="95" t="s">
+      <c r="A26" s="99" t="s">
         <v>144</v>
       </c>
-      <c r="B26" s="95"/>
-      <c r="C26" s="95"/>
-      <c r="D26" s="95"/>
-      <c r="E26" s="95"/>
-      <c r="F26" s="95"/>
-      <c r="G26" s="95"/>
-      <c r="H26" s="95"/>
-      <c r="I26" s="95"/>
-      <c r="J26" s="95"/>
-      <c r="K26" s="95"/>
-      <c r="L26" s="95"/>
-      <c r="M26" s="95"/>
-      <c r="N26" s="95"/>
-      <c r="O26" s="95"/>
-      <c r="P26" s="95"/>
-      <c r="Q26" s="95"/>
-      <c r="R26" s="95"/>
-      <c r="S26" s="95"/>
-      <c r="T26" s="95"/>
-      <c r="U26" s="95"/>
-      <c r="V26" s="95"/>
-      <c r="W26" s="95"/>
-      <c r="X26" s="95"/>
-      <c r="Y26" s="95"/>
-      <c r="Z26" s="95"/>
-      <c r="AA26" s="95"/>
-      <c r="AB26" s="95"/>
-      <c r="AC26" s="95"/>
-      <c r="AD26" s="95"/>
-      <c r="AE26" s="95"/>
-      <c r="AF26" s="95"/>
-      <c r="AG26" s="95"/>
-      <c r="AH26" s="95"/>
-      <c r="AI26" s="95"/>
-      <c r="AJ26" s="95"/>
-      <c r="AK26" s="95"/>
-      <c r="AL26" s="95"/>
-      <c r="AM26" s="95"/>
+      <c r="B26" s="99"/>
+      <c r="C26" s="99"/>
+      <c r="D26" s="99"/>
+      <c r="E26" s="99"/>
+      <c r="F26" s="99"/>
+      <c r="G26" s="99"/>
+      <c r="H26" s="99"/>
+      <c r="I26" s="99"/>
+      <c r="J26" s="99"/>
+      <c r="K26" s="99"/>
+      <c r="L26" s="99"/>
+      <c r="M26" s="99"/>
+      <c r="N26" s="99"/>
+      <c r="O26" s="99"/>
+      <c r="P26" s="99"/>
+      <c r="Q26" s="99"/>
+      <c r="R26" s="99"/>
+      <c r="S26" s="99"/>
+      <c r="T26" s="99"/>
+      <c r="U26" s="99"/>
+      <c r="V26" s="99"/>
+      <c r="W26" s="99"/>
+      <c r="X26" s="99"/>
+      <c r="Y26" s="99"/>
+      <c r="Z26" s="99"/>
+      <c r="AA26" s="99"/>
+      <c r="AB26" s="99"/>
+      <c r="AC26" s="99"/>
+      <c r="AD26" s="99"/>
+      <c r="AE26" s="99"/>
+      <c r="AF26" s="99"/>
+      <c r="AG26" s="99"/>
+      <c r="AH26" s="99"/>
+      <c r="AI26" s="99"/>
+      <c r="AJ26" s="99"/>
+      <c r="AK26" s="99"/>
+      <c r="AL26" s="99"/>
+      <c r="AM26" s="99"/>
     </row>
     <row r="27" spans="1:39" ht="15" customHeight="1">
-      <c r="A27" s="95" t="s">
+      <c r="A27" s="99" t="s">
         <v>145</v>
       </c>
-      <c r="B27" s="95"/>
-      <c r="C27" s="95"/>
-      <c r="D27" s="95"/>
-      <c r="E27" s="95"/>
-      <c r="F27" s="95"/>
-      <c r="G27" s="95"/>
-      <c r="H27" s="95"/>
-      <c r="I27" s="95"/>
-      <c r="J27" s="95"/>
-      <c r="K27" s="95"/>
-      <c r="L27" s="95"/>
-      <c r="M27" s="95"/>
-      <c r="N27" s="95"/>
-      <c r="O27" s="95"/>
-      <c r="P27" s="95"/>
-      <c r="Q27" s="95"/>
-      <c r="R27" s="95"/>
-      <c r="S27" s="95"/>
-      <c r="T27" s="95"/>
-      <c r="U27" s="95"/>
-      <c r="V27" s="95"/>
-      <c r="W27" s="95"/>
-      <c r="X27" s="95"/>
-      <c r="Y27" s="95"/>
-      <c r="Z27" s="95"/>
-      <c r="AA27" s="95"/>
-      <c r="AB27" s="95"/>
-      <c r="AC27" s="95"/>
-      <c r="AD27" s="95"/>
-      <c r="AE27" s="95"/>
-      <c r="AF27" s="95"/>
-      <c r="AG27" s="95"/>
-      <c r="AH27" s="95"/>
-      <c r="AI27" s="95"/>
-      <c r="AJ27" s="95"/>
-      <c r="AK27" s="95"/>
-      <c r="AL27" s="95"/>
-      <c r="AM27" s="95"/>
+      <c r="B27" s="99"/>
+      <c r="C27" s="99"/>
+      <c r="D27" s="99"/>
+      <c r="E27" s="99"/>
+      <c r="F27" s="99"/>
+      <c r="G27" s="99"/>
+      <c r="H27" s="99"/>
+      <c r="I27" s="99"/>
+      <c r="J27" s="99"/>
+      <c r="K27" s="99"/>
+      <c r="L27" s="99"/>
+      <c r="M27" s="99"/>
+      <c r="N27" s="99"/>
+      <c r="O27" s="99"/>
+      <c r="P27" s="99"/>
+      <c r="Q27" s="99"/>
+      <c r="R27" s="99"/>
+      <c r="S27" s="99"/>
+      <c r="T27" s="99"/>
+      <c r="U27" s="99"/>
+      <c r="V27" s="99"/>
+      <c r="W27" s="99"/>
+      <c r="X27" s="99"/>
+      <c r="Y27" s="99"/>
+      <c r="Z27" s="99"/>
+      <c r="AA27" s="99"/>
+      <c r="AB27" s="99"/>
+      <c r="AC27" s="99"/>
+      <c r="AD27" s="99"/>
+      <c r="AE27" s="99"/>
+      <c r="AF27" s="99"/>
+      <c r="AG27" s="99"/>
+      <c r="AH27" s="99"/>
+      <c r="AI27" s="99"/>
+      <c r="AJ27" s="99"/>
+      <c r="AK27" s="99"/>
+      <c r="AL27" s="99"/>
+      <c r="AM27" s="99"/>
     </row>
     <row r="28" spans="1:39" ht="15" customHeight="1">
-      <c r="A28" s="95" t="s">
+      <c r="A28" s="99" t="s">
         <v>146</v>
       </c>
-      <c r="B28" s="95"/>
-      <c r="C28" s="95"/>
-      <c r="D28" s="95"/>
-      <c r="E28" s="95"/>
-      <c r="F28" s="95"/>
-      <c r="G28" s="95"/>
-      <c r="H28" s="95"/>
-      <c r="I28" s="95"/>
-      <c r="J28" s="95"/>
-      <c r="K28" s="95"/>
-      <c r="L28" s="95"/>
-      <c r="M28" s="95"/>
-      <c r="N28" s="95"/>
-      <c r="O28" s="95"/>
-      <c r="P28" s="95"/>
-      <c r="Q28" s="95"/>
-      <c r="R28" s="95"/>
-      <c r="S28" s="95"/>
-      <c r="T28" s="95"/>
-      <c r="U28" s="95"/>
-      <c r="V28" s="95"/>
-      <c r="W28" s="95"/>
-      <c r="X28" s="95"/>
-      <c r="Y28" s="95"/>
-      <c r="Z28" s="95"/>
-      <c r="AA28" s="95"/>
-      <c r="AB28" s="95"/>
-      <c r="AC28" s="95"/>
-      <c r="AD28" s="95"/>
-      <c r="AE28" s="95"/>
-      <c r="AF28" s="95"/>
-      <c r="AG28" s="95"/>
-      <c r="AH28" s="95"/>
-      <c r="AI28" s="95"/>
-      <c r="AJ28" s="95"/>
-      <c r="AK28" s="95"/>
-      <c r="AL28" s="95"/>
-      <c r="AM28" s="95"/>
-    </row>
-    <row r="29" spans="1:39" ht="14.15" customHeight="1">
+      <c r="B28" s="99"/>
+      <c r="C28" s="99"/>
+      <c r="D28" s="99"/>
+      <c r="E28" s="99"/>
+      <c r="F28" s="99"/>
+      <c r="G28" s="99"/>
+      <c r="H28" s="99"/>
+      <c r="I28" s="99"/>
+      <c r="J28" s="99"/>
+      <c r="K28" s="99"/>
+      <c r="L28" s="99"/>
+      <c r="M28" s="99"/>
+      <c r="N28" s="99"/>
+      <c r="O28" s="99"/>
+      <c r="P28" s="99"/>
+      <c r="Q28" s="99"/>
+      <c r="R28" s="99"/>
+      <c r="S28" s="99"/>
+      <c r="T28" s="99"/>
+      <c r="U28" s="99"/>
+      <c r="V28" s="99"/>
+      <c r="W28" s="99"/>
+      <c r="X28" s="99"/>
+      <c r="Y28" s="99"/>
+      <c r="Z28" s="99"/>
+      <c r="AA28" s="99"/>
+      <c r="AB28" s="99"/>
+      <c r="AC28" s="99"/>
+      <c r="AD28" s="99"/>
+      <c r="AE28" s="99"/>
+      <c r="AF28" s="99"/>
+      <c r="AG28" s="99"/>
+      <c r="AH28" s="99"/>
+      <c r="AI28" s="99"/>
+      <c r="AJ28" s="99"/>
+      <c r="AK28" s="99"/>
+      <c r="AL28" s="99"/>
+      <c r="AM28" s="99"/>
+    </row>
+    <row r="29" spans="1:39" ht="14.1" customHeight="1">
       <c r="A29" s="46"/>
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
@@ -11564,886 +11544,886 @@
       <c r="AM29" s="14"/>
     </row>
     <row r="30" spans="1:39" ht="15" customHeight="1">
-      <c r="A30" s="95" t="s">
+      <c r="A30" s="99" t="s">
         <v>147</v>
       </c>
-      <c r="B30" s="95"/>
-      <c r="C30" s="95"/>
-      <c r="D30" s="95"/>
-      <c r="E30" s="95"/>
-      <c r="F30" s="95"/>
-      <c r="G30" s="95"/>
-      <c r="H30" s="95"/>
-      <c r="I30" s="95"/>
-      <c r="J30" s="95"/>
-      <c r="K30" s="95"/>
-      <c r="L30" s="95"/>
-      <c r="M30" s="95"/>
-      <c r="N30" s="95"/>
-      <c r="O30" s="95"/>
-      <c r="P30" s="95"/>
-      <c r="Q30" s="95"/>
-      <c r="R30" s="95"/>
-      <c r="S30" s="95"/>
-      <c r="T30" s="95"/>
-      <c r="U30" s="95"/>
-      <c r="V30" s="95"/>
-      <c r="W30" s="95"/>
-      <c r="X30" s="95"/>
-      <c r="Y30" s="95"/>
-      <c r="Z30" s="95"/>
-      <c r="AA30" s="95"/>
-      <c r="AB30" s="95"/>
-      <c r="AC30" s="95"/>
-      <c r="AD30" s="95"/>
-      <c r="AE30" s="95"/>
-      <c r="AF30" s="95"/>
-      <c r="AG30" s="95"/>
-      <c r="AH30" s="95"/>
-      <c r="AI30" s="95"/>
-      <c r="AJ30" s="95"/>
-      <c r="AK30" s="95"/>
-      <c r="AL30" s="95"/>
-      <c r="AM30" s="95"/>
+      <c r="B30" s="99"/>
+      <c r="C30" s="99"/>
+      <c r="D30" s="99"/>
+      <c r="E30" s="99"/>
+      <c r="F30" s="99"/>
+      <c r="G30" s="99"/>
+      <c r="H30" s="99"/>
+      <c r="I30" s="99"/>
+      <c r="J30" s="99"/>
+      <c r="K30" s="99"/>
+      <c r="L30" s="99"/>
+      <c r="M30" s="99"/>
+      <c r="N30" s="99"/>
+      <c r="O30" s="99"/>
+      <c r="P30" s="99"/>
+      <c r="Q30" s="99"/>
+      <c r="R30" s="99"/>
+      <c r="S30" s="99"/>
+      <c r="T30" s="99"/>
+      <c r="U30" s="99"/>
+      <c r="V30" s="99"/>
+      <c r="W30" s="99"/>
+      <c r="X30" s="99"/>
+      <c r="Y30" s="99"/>
+      <c r="Z30" s="99"/>
+      <c r="AA30" s="99"/>
+      <c r="AB30" s="99"/>
+      <c r="AC30" s="99"/>
+      <c r="AD30" s="99"/>
+      <c r="AE30" s="99"/>
+      <c r="AF30" s="99"/>
+      <c r="AG30" s="99"/>
+      <c r="AH30" s="99"/>
+      <c r="AI30" s="99"/>
+      <c r="AJ30" s="99"/>
+      <c r="AK30" s="99"/>
+      <c r="AL30" s="99"/>
+      <c r="AM30" s="99"/>
     </row>
     <row r="31" spans="1:39" ht="15" customHeight="1">
-      <c r="A31" s="95" t="s">
+      <c r="A31" s="99" t="s">
         <v>148</v>
       </c>
-      <c r="B31" s="95"/>
-      <c r="C31" s="95"/>
-      <c r="D31" s="95"/>
-      <c r="E31" s="95"/>
-      <c r="F31" s="95"/>
-      <c r="G31" s="95"/>
-      <c r="H31" s="95"/>
-      <c r="I31" s="95"/>
-      <c r="J31" s="95"/>
-      <c r="K31" s="95"/>
-      <c r="L31" s="95"/>
-      <c r="M31" s="95"/>
-      <c r="N31" s="95"/>
-      <c r="O31" s="95"/>
-      <c r="P31" s="95"/>
-      <c r="Q31" s="95"/>
-      <c r="R31" s="95"/>
-      <c r="S31" s="95"/>
-      <c r="T31" s="95"/>
-      <c r="U31" s="95"/>
-      <c r="V31" s="95"/>
-      <c r="W31" s="95"/>
-      <c r="X31" s="95"/>
-      <c r="Y31" s="95"/>
-      <c r="Z31" s="95"/>
-      <c r="AA31" s="95"/>
-      <c r="AB31" s="95"/>
-      <c r="AC31" s="95"/>
-      <c r="AD31" s="95"/>
-      <c r="AE31" s="95"/>
-      <c r="AF31" s="95"/>
-      <c r="AG31" s="95"/>
-      <c r="AH31" s="95"/>
-      <c r="AI31" s="95"/>
-      <c r="AJ31" s="95"/>
-      <c r="AK31" s="95"/>
-      <c r="AL31" s="95"/>
-      <c r="AM31" s="95"/>
+      <c r="B31" s="99"/>
+      <c r="C31" s="99"/>
+      <c r="D31" s="99"/>
+      <c r="E31" s="99"/>
+      <c r="F31" s="99"/>
+      <c r="G31" s="99"/>
+      <c r="H31" s="99"/>
+      <c r="I31" s="99"/>
+      <c r="J31" s="99"/>
+      <c r="K31" s="99"/>
+      <c r="L31" s="99"/>
+      <c r="M31" s="99"/>
+      <c r="N31" s="99"/>
+      <c r="O31" s="99"/>
+      <c r="P31" s="99"/>
+      <c r="Q31" s="99"/>
+      <c r="R31" s="99"/>
+      <c r="S31" s="99"/>
+      <c r="T31" s="99"/>
+      <c r="U31" s="99"/>
+      <c r="V31" s="99"/>
+      <c r="W31" s="99"/>
+      <c r="X31" s="99"/>
+      <c r="Y31" s="99"/>
+      <c r="Z31" s="99"/>
+      <c r="AA31" s="99"/>
+      <c r="AB31" s="99"/>
+      <c r="AC31" s="99"/>
+      <c r="AD31" s="99"/>
+      <c r="AE31" s="99"/>
+      <c r="AF31" s="99"/>
+      <c r="AG31" s="99"/>
+      <c r="AH31" s="99"/>
+      <c r="AI31" s="99"/>
+      <c r="AJ31" s="99"/>
+      <c r="AK31" s="99"/>
+      <c r="AL31" s="99"/>
+      <c r="AM31" s="99"/>
     </row>
     <row r="32" spans="1:39" ht="15" customHeight="1">
-      <c r="A32" s="98" t="s">
+      <c r="A32" s="96" t="s">
         <v>149</v>
       </c>
-      <c r="B32" s="98"/>
-      <c r="C32" s="98"/>
-      <c r="D32" s="98"/>
-      <c r="E32" s="98"/>
-      <c r="F32" s="98"/>
-      <c r="G32" s="98"/>
-      <c r="H32" s="98"/>
-      <c r="I32" s="98"/>
-      <c r="J32" s="98"/>
-      <c r="K32" s="98"/>
-      <c r="L32" s="98"/>
-      <c r="M32" s="98"/>
-      <c r="N32" s="98"/>
-      <c r="O32" s="98"/>
-      <c r="P32" s="98"/>
-      <c r="Q32" s="98"/>
-      <c r="R32" s="98"/>
-      <c r="S32" s="98"/>
-      <c r="T32" s="98"/>
-      <c r="U32" s="98"/>
-      <c r="V32" s="98"/>
-      <c r="W32" s="98"/>
-      <c r="X32" s="98"/>
-      <c r="Y32" s="98"/>
-      <c r="Z32" s="98"/>
-      <c r="AA32" s="98"/>
-      <c r="AB32" s="98"/>
-      <c r="AC32" s="98"/>
-      <c r="AD32" s="98"/>
-      <c r="AE32" s="98"/>
-      <c r="AF32" s="98"/>
-      <c r="AG32" s="98"/>
-      <c r="AH32" s="98"/>
-      <c r="AI32" s="98"/>
-      <c r="AJ32" s="98"/>
-      <c r="AK32" s="98"/>
-      <c r="AL32" s="98"/>
-      <c r="AM32" s="98"/>
+      <c r="B32" s="96"/>
+      <c r="C32" s="96"/>
+      <c r="D32" s="96"/>
+      <c r="E32" s="96"/>
+      <c r="F32" s="96"/>
+      <c r="G32" s="96"/>
+      <c r="H32" s="96"/>
+      <c r="I32" s="96"/>
+      <c r="J32" s="96"/>
+      <c r="K32" s="96"/>
+      <c r="L32" s="96"/>
+      <c r="M32" s="96"/>
+      <c r="N32" s="96"/>
+      <c r="O32" s="96"/>
+      <c r="P32" s="96"/>
+      <c r="Q32" s="96"/>
+      <c r="R32" s="96"/>
+      <c r="S32" s="96"/>
+      <c r="T32" s="96"/>
+      <c r="U32" s="96"/>
+      <c r="V32" s="96"/>
+      <c r="W32" s="96"/>
+      <c r="X32" s="96"/>
+      <c r="Y32" s="96"/>
+      <c r="Z32" s="96"/>
+      <c r="AA32" s="96"/>
+      <c r="AB32" s="96"/>
+      <c r="AC32" s="96"/>
+      <c r="AD32" s="96"/>
+      <c r="AE32" s="96"/>
+      <c r="AF32" s="96"/>
+      <c r="AG32" s="96"/>
+      <c r="AH32" s="96"/>
+      <c r="AI32" s="96"/>
+      <c r="AJ32" s="96"/>
+      <c r="AK32" s="96"/>
+      <c r="AL32" s="96"/>
+      <c r="AM32" s="96"/>
     </row>
     <row r="33" spans="1:39" ht="15" customHeight="1">
-      <c r="A33" s="98" t="s">
+      <c r="A33" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="98"/>
-      <c r="C33" s="98"/>
-      <c r="D33" s="98"/>
-      <c r="E33" s="98" t="s">
+      <c r="B33" s="96"/>
+      <c r="C33" s="96"/>
+      <c r="D33" s="96"/>
+      <c r="E33" s="96" t="s">
         <v>9</v>
       </c>
-      <c r="F33" s="83"/>
-      <c r="G33" s="83"/>
-      <c r="H33" s="83"/>
-      <c r="I33" s="83"/>
-      <c r="J33" s="83"/>
-      <c r="K33" s="83"/>
-      <c r="L33" s="98" t="s">
+      <c r="F33" s="86"/>
+      <c r="G33" s="86"/>
+      <c r="H33" s="86"/>
+      <c r="I33" s="86"/>
+      <c r="J33" s="86"/>
+      <c r="K33" s="86"/>
+      <c r="L33" s="96" t="s">
         <v>10</v>
       </c>
-      <c r="M33" s="83"/>
-      <c r="N33" s="83"/>
-      <c r="O33" s="83"/>
-      <c r="P33" s="83"/>
-      <c r="Q33" s="83"/>
-      <c r="R33" s="83"/>
-      <c r="S33" s="98" t="s">
+      <c r="M33" s="86"/>
+      <c r="N33" s="86"/>
+      <c r="O33" s="86"/>
+      <c r="P33" s="86"/>
+      <c r="Q33" s="86"/>
+      <c r="R33" s="86"/>
+      <c r="S33" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="T33" s="83"/>
-      <c r="U33" s="83"/>
-      <c r="V33" s="83"/>
-      <c r="W33" s="83"/>
-      <c r="X33" s="83"/>
-      <c r="Y33" s="83"/>
-      <c r="Z33" s="98" t="s">
+      <c r="T33" s="86"/>
+      <c r="U33" s="86"/>
+      <c r="V33" s="86"/>
+      <c r="W33" s="86"/>
+      <c r="X33" s="86"/>
+      <c r="Y33" s="86"/>
+      <c r="Z33" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="AA33" s="83"/>
-      <c r="AB33" s="83"/>
-      <c r="AC33" s="83"/>
-      <c r="AD33" s="83"/>
-      <c r="AE33" s="83"/>
-      <c r="AF33" s="83"/>
-      <c r="AG33" s="98" t="s">
+      <c r="AA33" s="86"/>
+      <c r="AB33" s="86"/>
+      <c r="AC33" s="86"/>
+      <c r="AD33" s="86"/>
+      <c r="AE33" s="86"/>
+      <c r="AF33" s="86"/>
+      <c r="AG33" s="96" t="s">
         <v>13</v>
       </c>
-      <c r="AH33" s="83"/>
-      <c r="AI33" s="83"/>
-      <c r="AJ33" s="83"/>
-      <c r="AK33" s="83"/>
-      <c r="AL33" s="83"/>
-      <c r="AM33" s="83"/>
+      <c r="AH33" s="86"/>
+      <c r="AI33" s="86"/>
+      <c r="AJ33" s="86"/>
+      <c r="AK33" s="86"/>
+      <c r="AL33" s="86"/>
+      <c r="AM33" s="86"/>
     </row>
     <row r="34" spans="1:39" ht="15" customHeight="1">
-      <c r="A34" s="98"/>
-      <c r="B34" s="98"/>
-      <c r="C34" s="98"/>
-      <c r="D34" s="98"/>
-      <c r="E34" s="98"/>
-      <c r="F34" s="83"/>
-      <c r="G34" s="83"/>
-      <c r="H34" s="83"/>
-      <c r="I34" s="83"/>
-      <c r="J34" s="83"/>
-      <c r="K34" s="83"/>
-      <c r="L34" s="98"/>
-      <c r="M34" s="83"/>
-      <c r="N34" s="83"/>
-      <c r="O34" s="83"/>
-      <c r="P34" s="83"/>
-      <c r="Q34" s="83"/>
-      <c r="R34" s="83"/>
-      <c r="S34" s="98"/>
-      <c r="T34" s="83"/>
-      <c r="U34" s="83"/>
-      <c r="V34" s="83"/>
-      <c r="W34" s="83"/>
-      <c r="X34" s="83"/>
-      <c r="Y34" s="83"/>
-      <c r="Z34" s="98"/>
-      <c r="AA34" s="83"/>
-      <c r="AB34" s="83"/>
-      <c r="AC34" s="83"/>
-      <c r="AD34" s="83"/>
-      <c r="AE34" s="83"/>
-      <c r="AF34" s="83"/>
-      <c r="AG34" s="98"/>
-      <c r="AH34" s="83"/>
-      <c r="AI34" s="83"/>
-      <c r="AJ34" s="83"/>
-      <c r="AK34" s="83"/>
-      <c r="AL34" s="83"/>
-      <c r="AM34" s="83"/>
+      <c r="A34" s="96"/>
+      <c r="B34" s="96"/>
+      <c r="C34" s="96"/>
+      <c r="D34" s="96"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="86"/>
+      <c r="G34" s="86"/>
+      <c r="H34" s="86"/>
+      <c r="I34" s="86"/>
+      <c r="J34" s="86"/>
+      <c r="K34" s="86"/>
+      <c r="L34" s="96"/>
+      <c r="M34" s="86"/>
+      <c r="N34" s="86"/>
+      <c r="O34" s="86"/>
+      <c r="P34" s="86"/>
+      <c r="Q34" s="86"/>
+      <c r="R34" s="86"/>
+      <c r="S34" s="96"/>
+      <c r="T34" s="86"/>
+      <c r="U34" s="86"/>
+      <c r="V34" s="86"/>
+      <c r="W34" s="86"/>
+      <c r="X34" s="86"/>
+      <c r="Y34" s="86"/>
+      <c r="Z34" s="96"/>
+      <c r="AA34" s="86"/>
+      <c r="AB34" s="86"/>
+      <c r="AC34" s="86"/>
+      <c r="AD34" s="86"/>
+      <c r="AE34" s="86"/>
+      <c r="AF34" s="86"/>
+      <c r="AG34" s="96"/>
+      <c r="AH34" s="86"/>
+      <c r="AI34" s="86"/>
+      <c r="AJ34" s="86"/>
+      <c r="AK34" s="86"/>
+      <c r="AL34" s="86"/>
+      <c r="AM34" s="86"/>
     </row>
     <row r="35" spans="1:39" ht="15" customHeight="1">
-      <c r="A35" s="98"/>
-      <c r="B35" s="98"/>
-      <c r="C35" s="98"/>
-      <c r="D35" s="98"/>
-      <c r="E35" s="98"/>
-      <c r="F35" s="83"/>
-      <c r="G35" s="83"/>
-      <c r="H35" s="83"/>
-      <c r="I35" s="83"/>
-      <c r="J35" s="83"/>
-      <c r="K35" s="83"/>
-      <c r="L35" s="98"/>
-      <c r="M35" s="83"/>
-      <c r="N35" s="83"/>
-      <c r="O35" s="83"/>
-      <c r="P35" s="83"/>
-      <c r="Q35" s="83"/>
-      <c r="R35" s="83"/>
-      <c r="S35" s="98"/>
-      <c r="T35" s="83"/>
-      <c r="U35" s="83"/>
-      <c r="V35" s="83"/>
-      <c r="W35" s="83"/>
-      <c r="X35" s="83"/>
-      <c r="Y35" s="83"/>
-      <c r="Z35" s="98"/>
-      <c r="AA35" s="83"/>
-      <c r="AB35" s="83"/>
-      <c r="AC35" s="83"/>
-      <c r="AD35" s="83"/>
-      <c r="AE35" s="83"/>
-      <c r="AF35" s="83"/>
-      <c r="AG35" s="98"/>
-      <c r="AH35" s="83"/>
-      <c r="AI35" s="83"/>
-      <c r="AJ35" s="83"/>
-      <c r="AK35" s="83"/>
-      <c r="AL35" s="83"/>
-      <c r="AM35" s="83"/>
+      <c r="A35" s="96"/>
+      <c r="B35" s="96"/>
+      <c r="C35" s="96"/>
+      <c r="D35" s="96"/>
+      <c r="E35" s="96"/>
+      <c r="F35" s="86"/>
+      <c r="G35" s="86"/>
+      <c r="H35" s="86"/>
+      <c r="I35" s="86"/>
+      <c r="J35" s="86"/>
+      <c r="K35" s="86"/>
+      <c r="L35" s="96"/>
+      <c r="M35" s="86"/>
+      <c r="N35" s="86"/>
+      <c r="O35" s="86"/>
+      <c r="P35" s="86"/>
+      <c r="Q35" s="86"/>
+      <c r="R35" s="86"/>
+      <c r="S35" s="96"/>
+      <c r="T35" s="86"/>
+      <c r="U35" s="86"/>
+      <c r="V35" s="86"/>
+      <c r="W35" s="86"/>
+      <c r="X35" s="86"/>
+      <c r="Y35" s="86"/>
+      <c r="Z35" s="96"/>
+      <c r="AA35" s="86"/>
+      <c r="AB35" s="86"/>
+      <c r="AC35" s="86"/>
+      <c r="AD35" s="86"/>
+      <c r="AE35" s="86"/>
+      <c r="AF35" s="86"/>
+      <c r="AG35" s="96"/>
+      <c r="AH35" s="86"/>
+      <c r="AI35" s="86"/>
+      <c r="AJ35" s="86"/>
+      <c r="AK35" s="86"/>
+      <c r="AL35" s="86"/>
+      <c r="AM35" s="86"/>
     </row>
     <row r="36" spans="1:39" ht="15" customHeight="1">
-      <c r="A36" s="98" t="s">
+      <c r="A36" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="B36" s="98"/>
-      <c r="C36" s="98"/>
-      <c r="D36" s="98"/>
-      <c r="E36" s="98" t="s">
+      <c r="B36" s="96"/>
+      <c r="C36" s="96"/>
+      <c r="D36" s="96"/>
+      <c r="E36" s="96" t="s">
         <v>128</v>
       </c>
-      <c r="F36" s="83"/>
-      <c r="G36" s="83"/>
-      <c r="H36" s="83"/>
-      <c r="I36" s="83"/>
-      <c r="J36" s="83"/>
-      <c r="K36" s="83"/>
-      <c r="L36" s="98" t="s">
+      <c r="F36" s="86"/>
+      <c r="G36" s="86"/>
+      <c r="H36" s="86"/>
+      <c r="I36" s="86"/>
+      <c r="J36" s="86"/>
+      <c r="K36" s="86"/>
+      <c r="L36" s="96" t="s">
         <v>129</v>
       </c>
-      <c r="M36" s="83"/>
-      <c r="N36" s="83"/>
-      <c r="O36" s="83"/>
-      <c r="P36" s="83"/>
-      <c r="Q36" s="83"/>
-      <c r="R36" s="83"/>
-      <c r="S36" s="98" t="s">
+      <c r="M36" s="86"/>
+      <c r="N36" s="86"/>
+      <c r="O36" s="86"/>
+      <c r="P36" s="86"/>
+      <c r="Q36" s="86"/>
+      <c r="R36" s="86"/>
+      <c r="S36" s="96" t="s">
         <v>130</v>
       </c>
-      <c r="T36" s="83"/>
-      <c r="U36" s="83"/>
-      <c r="V36" s="83"/>
-      <c r="W36" s="83"/>
-      <c r="X36" s="83"/>
-      <c r="Y36" s="83"/>
-      <c r="Z36" s="98" t="s">
+      <c r="T36" s="86"/>
+      <c r="U36" s="86"/>
+      <c r="V36" s="86"/>
+      <c r="W36" s="86"/>
+      <c r="X36" s="86"/>
+      <c r="Y36" s="86"/>
+      <c r="Z36" s="96" t="s">
         <v>131</v>
       </c>
-      <c r="AA36" s="83"/>
-      <c r="AB36" s="83"/>
-      <c r="AC36" s="83"/>
-      <c r="AD36" s="83"/>
-      <c r="AE36" s="83"/>
-      <c r="AF36" s="83"/>
-      <c r="AG36" s="98" t="s">
+      <c r="AA36" s="86"/>
+      <c r="AB36" s="86"/>
+      <c r="AC36" s="86"/>
+      <c r="AD36" s="86"/>
+      <c r="AE36" s="86"/>
+      <c r="AF36" s="86"/>
+      <c r="AG36" s="96" t="s">
         <v>132</v>
       </c>
-      <c r="AH36" s="83"/>
-      <c r="AI36" s="83"/>
-      <c r="AJ36" s="83"/>
-      <c r="AK36" s="83"/>
-      <c r="AL36" s="83"/>
-      <c r="AM36" s="83"/>
+      <c r="AH36" s="86"/>
+      <c r="AI36" s="86"/>
+      <c r="AJ36" s="86"/>
+      <c r="AK36" s="86"/>
+      <c r="AL36" s="86"/>
+      <c r="AM36" s="86"/>
     </row>
     <row r="37" spans="1:39" ht="15" customHeight="1">
-      <c r="A37" s="98"/>
-      <c r="B37" s="98"/>
-      <c r="C37" s="98"/>
-      <c r="D37" s="98"/>
-      <c r="E37" s="98"/>
-      <c r="F37" s="83"/>
-      <c r="G37" s="83"/>
-      <c r="H37" s="83"/>
-      <c r="I37" s="83"/>
-      <c r="J37" s="83"/>
-      <c r="K37" s="83"/>
-      <c r="L37" s="98"/>
-      <c r="M37" s="83"/>
-      <c r="N37" s="83"/>
-      <c r="O37" s="83"/>
-      <c r="P37" s="83"/>
-      <c r="Q37" s="83"/>
-      <c r="R37" s="83"/>
-      <c r="S37" s="98"/>
-      <c r="T37" s="83"/>
-      <c r="U37" s="83"/>
-      <c r="V37" s="83"/>
-      <c r="W37" s="83"/>
-      <c r="X37" s="83"/>
-      <c r="Y37" s="83"/>
-      <c r="Z37" s="98"/>
-      <c r="AA37" s="83"/>
-      <c r="AB37" s="83"/>
-      <c r="AC37" s="83"/>
-      <c r="AD37" s="83"/>
-      <c r="AE37" s="83"/>
-      <c r="AF37" s="83"/>
-      <c r="AG37" s="98"/>
-      <c r="AH37" s="83"/>
-      <c r="AI37" s="83"/>
-      <c r="AJ37" s="83"/>
-      <c r="AK37" s="83"/>
-      <c r="AL37" s="83"/>
-      <c r="AM37" s="83"/>
+      <c r="A37" s="96"/>
+      <c r="B37" s="96"/>
+      <c r="C37" s="96"/>
+      <c r="D37" s="96"/>
+      <c r="E37" s="96"/>
+      <c r="F37" s="86"/>
+      <c r="G37" s="86"/>
+      <c r="H37" s="86"/>
+      <c r="I37" s="86"/>
+      <c r="J37" s="86"/>
+      <c r="K37" s="86"/>
+      <c r="L37" s="96"/>
+      <c r="M37" s="86"/>
+      <c r="N37" s="86"/>
+      <c r="O37" s="86"/>
+      <c r="P37" s="86"/>
+      <c r="Q37" s="86"/>
+      <c r="R37" s="86"/>
+      <c r="S37" s="96"/>
+      <c r="T37" s="86"/>
+      <c r="U37" s="86"/>
+      <c r="V37" s="86"/>
+      <c r="W37" s="86"/>
+      <c r="X37" s="86"/>
+      <c r="Y37" s="86"/>
+      <c r="Z37" s="96"/>
+      <c r="AA37" s="86"/>
+      <c r="AB37" s="86"/>
+      <c r="AC37" s="86"/>
+      <c r="AD37" s="86"/>
+      <c r="AE37" s="86"/>
+      <c r="AF37" s="86"/>
+      <c r="AG37" s="96"/>
+      <c r="AH37" s="86"/>
+      <c r="AI37" s="86"/>
+      <c r="AJ37" s="86"/>
+      <c r="AK37" s="86"/>
+      <c r="AL37" s="86"/>
+      <c r="AM37" s="86"/>
     </row>
     <row r="38" spans="1:39" ht="15" customHeight="1">
-      <c r="A38" s="98"/>
-      <c r="B38" s="98"/>
-      <c r="C38" s="98"/>
-      <c r="D38" s="98"/>
-      <c r="E38" s="98"/>
-      <c r="F38" s="83"/>
-      <c r="G38" s="83"/>
-      <c r="H38" s="83"/>
-      <c r="I38" s="83"/>
-      <c r="J38" s="83"/>
-      <c r="K38" s="83"/>
-      <c r="L38" s="98"/>
-      <c r="M38" s="83"/>
-      <c r="N38" s="83"/>
-      <c r="O38" s="83"/>
-      <c r="P38" s="83"/>
-      <c r="Q38" s="83"/>
-      <c r="R38" s="83"/>
-      <c r="S38" s="98"/>
-      <c r="T38" s="83"/>
-      <c r="U38" s="83"/>
-      <c r="V38" s="83"/>
-      <c r="W38" s="83"/>
-      <c r="X38" s="83"/>
-      <c r="Y38" s="83"/>
-      <c r="Z38" s="98"/>
-      <c r="AA38" s="83"/>
-      <c r="AB38" s="83"/>
-      <c r="AC38" s="83"/>
-      <c r="AD38" s="83"/>
-      <c r="AE38" s="83"/>
-      <c r="AF38" s="83"/>
-      <c r="AG38" s="98"/>
-      <c r="AH38" s="83"/>
-      <c r="AI38" s="83"/>
-      <c r="AJ38" s="83"/>
-      <c r="AK38" s="83"/>
-      <c r="AL38" s="83"/>
-      <c r="AM38" s="83"/>
+      <c r="A38" s="96"/>
+      <c r="B38" s="96"/>
+      <c r="C38" s="96"/>
+      <c r="D38" s="96"/>
+      <c r="E38" s="96"/>
+      <c r="F38" s="86"/>
+      <c r="G38" s="86"/>
+      <c r="H38" s="86"/>
+      <c r="I38" s="86"/>
+      <c r="J38" s="86"/>
+      <c r="K38" s="86"/>
+      <c r="L38" s="96"/>
+      <c r="M38" s="86"/>
+      <c r="N38" s="86"/>
+      <c r="O38" s="86"/>
+      <c r="P38" s="86"/>
+      <c r="Q38" s="86"/>
+      <c r="R38" s="86"/>
+      <c r="S38" s="96"/>
+      <c r="T38" s="86"/>
+      <c r="U38" s="86"/>
+      <c r="V38" s="86"/>
+      <c r="W38" s="86"/>
+      <c r="X38" s="86"/>
+      <c r="Y38" s="86"/>
+      <c r="Z38" s="96"/>
+      <c r="AA38" s="86"/>
+      <c r="AB38" s="86"/>
+      <c r="AC38" s="86"/>
+      <c r="AD38" s="86"/>
+      <c r="AE38" s="86"/>
+      <c r="AF38" s="86"/>
+      <c r="AG38" s="96"/>
+      <c r="AH38" s="86"/>
+      <c r="AI38" s="86"/>
+      <c r="AJ38" s="86"/>
+      <c r="AK38" s="86"/>
+      <c r="AL38" s="86"/>
+      <c r="AM38" s="86"/>
     </row>
     <row r="39" spans="1:39" ht="15" customHeight="1">
-      <c r="A39" s="98" t="s">
+      <c r="A39" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="B39" s="98"/>
-      <c r="C39" s="98"/>
-      <c r="D39" s="98"/>
-      <c r="E39" s="98" t="s">
+      <c r="B39" s="96"/>
+      <c r="C39" s="96"/>
+      <c r="D39" s="96"/>
+      <c r="E39" s="96" t="s">
         <v>133</v>
       </c>
-      <c r="F39" s="83"/>
-      <c r="G39" s="83"/>
-      <c r="H39" s="83"/>
-      <c r="I39" s="83"/>
-      <c r="J39" s="83"/>
-      <c r="K39" s="83"/>
-      <c r="L39" s="98" t="s">
+      <c r="F39" s="86"/>
+      <c r="G39" s="86"/>
+      <c r="H39" s="86"/>
+      <c r="I39" s="86"/>
+      <c r="J39" s="86"/>
+      <c r="K39" s="86"/>
+      <c r="L39" s="96" t="s">
         <v>134</v>
       </c>
-      <c r="M39" s="83"/>
-      <c r="N39" s="83"/>
-      <c r="O39" s="83"/>
-      <c r="P39" s="83"/>
-      <c r="Q39" s="83"/>
-      <c r="R39" s="83"/>
-      <c r="S39" s="98" t="s">
+      <c r="M39" s="86"/>
+      <c r="N39" s="86"/>
+      <c r="O39" s="86"/>
+      <c r="P39" s="86"/>
+      <c r="Q39" s="86"/>
+      <c r="R39" s="86"/>
+      <c r="S39" s="96" t="s">
         <v>135</v>
       </c>
-      <c r="T39" s="83"/>
-      <c r="U39" s="83"/>
-      <c r="V39" s="83"/>
-      <c r="W39" s="83"/>
-      <c r="X39" s="83"/>
-      <c r="Y39" s="83"/>
-      <c r="Z39" s="98" t="s">
+      <c r="T39" s="86"/>
+      <c r="U39" s="86"/>
+      <c r="V39" s="86"/>
+      <c r="W39" s="86"/>
+      <c r="X39" s="86"/>
+      <c r="Y39" s="86"/>
+      <c r="Z39" s="96" t="s">
         <v>136</v>
       </c>
-      <c r="AA39" s="83"/>
-      <c r="AB39" s="83"/>
-      <c r="AC39" s="83"/>
-      <c r="AD39" s="83"/>
-      <c r="AE39" s="83"/>
-      <c r="AF39" s="83"/>
-      <c r="AG39" s="98" t="s">
+      <c r="AA39" s="86"/>
+      <c r="AB39" s="86"/>
+      <c r="AC39" s="86"/>
+      <c r="AD39" s="86"/>
+      <c r="AE39" s="86"/>
+      <c r="AF39" s="86"/>
+      <c r="AG39" s="96" t="s">
         <v>137</v>
       </c>
-      <c r="AH39" s="83"/>
-      <c r="AI39" s="83"/>
-      <c r="AJ39" s="83"/>
-      <c r="AK39" s="83"/>
-      <c r="AL39" s="83"/>
-      <c r="AM39" s="83"/>
+      <c r="AH39" s="86"/>
+      <c r="AI39" s="86"/>
+      <c r="AJ39" s="86"/>
+      <c r="AK39" s="86"/>
+      <c r="AL39" s="86"/>
+      <c r="AM39" s="86"/>
     </row>
     <row r="40" spans="1:39" ht="15" customHeight="1">
-      <c r="A40" s="98"/>
-      <c r="B40" s="98"/>
-      <c r="C40" s="98"/>
-      <c r="D40" s="98"/>
-      <c r="E40" s="98"/>
-      <c r="F40" s="83"/>
-      <c r="G40" s="83"/>
-      <c r="H40" s="83"/>
-      <c r="I40" s="83"/>
-      <c r="J40" s="83"/>
-      <c r="K40" s="83"/>
-      <c r="L40" s="98"/>
-      <c r="M40" s="83"/>
-      <c r="N40" s="83"/>
-      <c r="O40" s="83"/>
-      <c r="P40" s="83"/>
-      <c r="Q40" s="83"/>
-      <c r="R40" s="83"/>
-      <c r="S40" s="98"/>
-      <c r="T40" s="83"/>
-      <c r="U40" s="83"/>
-      <c r="V40" s="83"/>
-      <c r="W40" s="83"/>
-      <c r="X40" s="83"/>
-      <c r="Y40" s="83"/>
-      <c r="Z40" s="98"/>
-      <c r="AA40" s="83"/>
-      <c r="AB40" s="83"/>
-      <c r="AC40" s="83"/>
-      <c r="AD40" s="83"/>
-      <c r="AE40" s="83"/>
-      <c r="AF40" s="83"/>
-      <c r="AG40" s="98"/>
-      <c r="AH40" s="83"/>
-      <c r="AI40" s="83"/>
-      <c r="AJ40" s="83"/>
-      <c r="AK40" s="83"/>
-      <c r="AL40" s="83"/>
-      <c r="AM40" s="83"/>
+      <c r="A40" s="96"/>
+      <c r="B40" s="96"/>
+      <c r="C40" s="96"/>
+      <c r="D40" s="96"/>
+      <c r="E40" s="96"/>
+      <c r="F40" s="86"/>
+      <c r="G40" s="86"/>
+      <c r="H40" s="86"/>
+      <c r="I40" s="86"/>
+      <c r="J40" s="86"/>
+      <c r="K40" s="86"/>
+      <c r="L40" s="96"/>
+      <c r="M40" s="86"/>
+      <c r="N40" s="86"/>
+      <c r="O40" s="86"/>
+      <c r="P40" s="86"/>
+      <c r="Q40" s="86"/>
+      <c r="R40" s="86"/>
+      <c r="S40" s="96"/>
+      <c r="T40" s="86"/>
+      <c r="U40" s="86"/>
+      <c r="V40" s="86"/>
+      <c r="W40" s="86"/>
+      <c r="X40" s="86"/>
+      <c r="Y40" s="86"/>
+      <c r="Z40" s="96"/>
+      <c r="AA40" s="86"/>
+      <c r="AB40" s="86"/>
+      <c r="AC40" s="86"/>
+      <c r="AD40" s="86"/>
+      <c r="AE40" s="86"/>
+      <c r="AF40" s="86"/>
+      <c r="AG40" s="96"/>
+      <c r="AH40" s="86"/>
+      <c r="AI40" s="86"/>
+      <c r="AJ40" s="86"/>
+      <c r="AK40" s="86"/>
+      <c r="AL40" s="86"/>
+      <c r="AM40" s="86"/>
     </row>
     <row r="41" spans="1:39" ht="15" customHeight="1">
-      <c r="A41" s="98"/>
-      <c r="B41" s="98"/>
-      <c r="C41" s="98"/>
-      <c r="D41" s="98"/>
-      <c r="E41" s="98"/>
-      <c r="F41" s="83"/>
-      <c r="G41" s="83"/>
-      <c r="H41" s="83"/>
-      <c r="I41" s="83"/>
-      <c r="J41" s="83"/>
-      <c r="K41" s="83"/>
-      <c r="L41" s="98"/>
-      <c r="M41" s="83"/>
-      <c r="N41" s="83"/>
-      <c r="O41" s="83"/>
-      <c r="P41" s="83"/>
-      <c r="Q41" s="83"/>
-      <c r="R41" s="83"/>
-      <c r="S41" s="98"/>
-      <c r="T41" s="83"/>
-      <c r="U41" s="83"/>
-      <c r="V41" s="83"/>
-      <c r="W41" s="83"/>
-      <c r="X41" s="83"/>
-      <c r="Y41" s="83"/>
-      <c r="Z41" s="98"/>
-      <c r="AA41" s="83"/>
-      <c r="AB41" s="83"/>
-      <c r="AC41" s="83"/>
-      <c r="AD41" s="83"/>
-      <c r="AE41" s="83"/>
-      <c r="AF41" s="83"/>
-      <c r="AG41" s="98"/>
-      <c r="AH41" s="83"/>
-      <c r="AI41" s="83"/>
-      <c r="AJ41" s="83"/>
-      <c r="AK41" s="83"/>
-      <c r="AL41" s="83"/>
-      <c r="AM41" s="83"/>
+      <c r="A41" s="96"/>
+      <c r="B41" s="96"/>
+      <c r="C41" s="96"/>
+      <c r="D41" s="96"/>
+      <c r="E41" s="96"/>
+      <c r="F41" s="86"/>
+      <c r="G41" s="86"/>
+      <c r="H41" s="86"/>
+      <c r="I41" s="86"/>
+      <c r="J41" s="86"/>
+      <c r="K41" s="86"/>
+      <c r="L41" s="96"/>
+      <c r="M41" s="86"/>
+      <c r="N41" s="86"/>
+      <c r="O41" s="86"/>
+      <c r="P41" s="86"/>
+      <c r="Q41" s="86"/>
+      <c r="R41" s="86"/>
+      <c r="S41" s="96"/>
+      <c r="T41" s="86"/>
+      <c r="U41" s="86"/>
+      <c r="V41" s="86"/>
+      <c r="W41" s="86"/>
+      <c r="X41" s="86"/>
+      <c r="Y41" s="86"/>
+      <c r="Z41" s="96"/>
+      <c r="AA41" s="86"/>
+      <c r="AB41" s="86"/>
+      <c r="AC41" s="86"/>
+      <c r="AD41" s="86"/>
+      <c r="AE41" s="86"/>
+      <c r="AF41" s="86"/>
+      <c r="AG41" s="96"/>
+      <c r="AH41" s="86"/>
+      <c r="AI41" s="86"/>
+      <c r="AJ41" s="86"/>
+      <c r="AK41" s="86"/>
+      <c r="AL41" s="86"/>
+      <c r="AM41" s="86"/>
     </row>
     <row r="42" spans="1:39" ht="15" customHeight="1">
-      <c r="A42" s="98" t="s">
+      <c r="A42" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="B42" s="98"/>
-      <c r="C42" s="98"/>
-      <c r="D42" s="98"/>
-      <c r="E42" s="98" t="s">
+      <c r="B42" s="96"/>
+      <c r="C42" s="96"/>
+      <c r="D42" s="96"/>
+      <c r="E42" s="96" t="s">
         <v>138</v>
       </c>
-      <c r="F42" s="83"/>
-      <c r="G42" s="83"/>
-      <c r="H42" s="83"/>
-      <c r="I42" s="83"/>
-      <c r="J42" s="83"/>
-      <c r="K42" s="83"/>
-      <c r="L42" s="98" t="s">
+      <c r="F42" s="86"/>
+      <c r="G42" s="86"/>
+      <c r="H42" s="86"/>
+      <c r="I42" s="86"/>
+      <c r="J42" s="86"/>
+      <c r="K42" s="86"/>
+      <c r="L42" s="96" t="s">
         <v>139</v>
       </c>
-      <c r="M42" s="83"/>
-      <c r="N42" s="83"/>
-      <c r="O42" s="83"/>
-      <c r="P42" s="83"/>
-      <c r="Q42" s="83"/>
-      <c r="R42" s="83"/>
-      <c r="S42" s="98" t="s">
+      <c r="M42" s="86"/>
+      <c r="N42" s="86"/>
+      <c r="O42" s="86"/>
+      <c r="P42" s="86"/>
+      <c r="Q42" s="86"/>
+      <c r="R42" s="86"/>
+      <c r="S42" s="96" t="s">
         <v>140</v>
       </c>
-      <c r="T42" s="83"/>
-      <c r="U42" s="83"/>
-      <c r="V42" s="83"/>
-      <c r="W42" s="83"/>
-      <c r="X42" s="83"/>
-      <c r="Y42" s="83"/>
-      <c r="Z42" s="98" t="s">
+      <c r="T42" s="86"/>
+      <c r="U42" s="86"/>
+      <c r="V42" s="86"/>
+      <c r="W42" s="86"/>
+      <c r="X42" s="86"/>
+      <c r="Y42" s="86"/>
+      <c r="Z42" s="96" t="s">
         <v>141</v>
       </c>
-      <c r="AA42" s="83"/>
-      <c r="AB42" s="83"/>
-      <c r="AC42" s="83"/>
-      <c r="AD42" s="83"/>
-      <c r="AE42" s="83"/>
-      <c r="AF42" s="83"/>
-      <c r="AG42" s="98" t="s">
+      <c r="AA42" s="86"/>
+      <c r="AB42" s="86"/>
+      <c r="AC42" s="86"/>
+      <c r="AD42" s="86"/>
+      <c r="AE42" s="86"/>
+      <c r="AF42" s="86"/>
+      <c r="AG42" s="96" t="s">
         <v>142</v>
       </c>
-      <c r="AH42" s="83"/>
-      <c r="AI42" s="83"/>
-      <c r="AJ42" s="83"/>
-      <c r="AK42" s="83"/>
-      <c r="AL42" s="83"/>
-      <c r="AM42" s="83"/>
+      <c r="AH42" s="86"/>
+      <c r="AI42" s="86"/>
+      <c r="AJ42" s="86"/>
+      <c r="AK42" s="86"/>
+      <c r="AL42" s="86"/>
+      <c r="AM42" s="86"/>
     </row>
     <row r="43" spans="1:39" ht="15" customHeight="1">
-      <c r="A43" s="98"/>
-      <c r="B43" s="98"/>
-      <c r="C43" s="98"/>
-      <c r="D43" s="98"/>
-      <c r="E43" s="98"/>
-      <c r="F43" s="83"/>
-      <c r="G43" s="83"/>
-      <c r="H43" s="83"/>
-      <c r="I43" s="83"/>
-      <c r="J43" s="83"/>
-      <c r="K43" s="83"/>
-      <c r="L43" s="98"/>
-      <c r="M43" s="83"/>
-      <c r="N43" s="83"/>
-      <c r="O43" s="83"/>
-      <c r="P43" s="83"/>
-      <c r="Q43" s="83"/>
-      <c r="R43" s="83"/>
-      <c r="S43" s="98"/>
-      <c r="T43" s="83"/>
-      <c r="U43" s="83"/>
-      <c r="V43" s="83"/>
-      <c r="W43" s="83"/>
-      <c r="X43" s="83"/>
-      <c r="Y43" s="83"/>
-      <c r="Z43" s="98"/>
-      <c r="AA43" s="83"/>
-      <c r="AB43" s="83"/>
-      <c r="AC43" s="83"/>
-      <c r="AD43" s="83"/>
-      <c r="AE43" s="83"/>
-      <c r="AF43" s="83"/>
-      <c r="AG43" s="98"/>
-      <c r="AH43" s="83"/>
-      <c r="AI43" s="83"/>
-      <c r="AJ43" s="83"/>
-      <c r="AK43" s="83"/>
-      <c r="AL43" s="83"/>
-      <c r="AM43" s="83"/>
+      <c r="A43" s="96"/>
+      <c r="B43" s="96"/>
+      <c r="C43" s="96"/>
+      <c r="D43" s="96"/>
+      <c r="E43" s="96"/>
+      <c r="F43" s="86"/>
+      <c r="G43" s="86"/>
+      <c r="H43" s="86"/>
+      <c r="I43" s="86"/>
+      <c r="J43" s="86"/>
+      <c r="K43" s="86"/>
+      <c r="L43" s="96"/>
+      <c r="M43" s="86"/>
+      <c r="N43" s="86"/>
+      <c r="O43" s="86"/>
+      <c r="P43" s="86"/>
+      <c r="Q43" s="86"/>
+      <c r="R43" s="86"/>
+      <c r="S43" s="96"/>
+      <c r="T43" s="86"/>
+      <c r="U43" s="86"/>
+      <c r="V43" s="86"/>
+      <c r="W43" s="86"/>
+      <c r="X43" s="86"/>
+      <c r="Y43" s="86"/>
+      <c r="Z43" s="96"/>
+      <c r="AA43" s="86"/>
+      <c r="AB43" s="86"/>
+      <c r="AC43" s="86"/>
+      <c r="AD43" s="86"/>
+      <c r="AE43" s="86"/>
+      <c r="AF43" s="86"/>
+      <c r="AG43" s="96"/>
+      <c r="AH43" s="86"/>
+      <c r="AI43" s="86"/>
+      <c r="AJ43" s="86"/>
+      <c r="AK43" s="86"/>
+      <c r="AL43" s="86"/>
+      <c r="AM43" s="86"/>
     </row>
     <row r="44" spans="1:39" ht="15" customHeight="1">
-      <c r="A44" s="98"/>
-      <c r="B44" s="98"/>
-      <c r="C44" s="98"/>
-      <c r="D44" s="98"/>
-      <c r="E44" s="98"/>
-      <c r="F44" s="83"/>
-      <c r="G44" s="83"/>
-      <c r="H44" s="83"/>
-      <c r="I44" s="83"/>
-      <c r="J44" s="83"/>
-      <c r="K44" s="83"/>
-      <c r="L44" s="98"/>
-      <c r="M44" s="83"/>
-      <c r="N44" s="83"/>
-      <c r="O44" s="83"/>
-      <c r="P44" s="83"/>
-      <c r="Q44" s="83"/>
-      <c r="R44" s="83"/>
-      <c r="S44" s="98"/>
-      <c r="T44" s="83"/>
-      <c r="U44" s="83"/>
-      <c r="V44" s="83"/>
-      <c r="W44" s="83"/>
-      <c r="X44" s="83"/>
-      <c r="Y44" s="83"/>
-      <c r="Z44" s="98"/>
-      <c r="AA44" s="83"/>
-      <c r="AB44" s="83"/>
-      <c r="AC44" s="83"/>
-      <c r="AD44" s="83"/>
-      <c r="AE44" s="83"/>
-      <c r="AF44" s="83"/>
-      <c r="AG44" s="98"/>
-      <c r="AH44" s="83"/>
-      <c r="AI44" s="83"/>
-      <c r="AJ44" s="83"/>
-      <c r="AK44" s="83"/>
-      <c r="AL44" s="83"/>
-      <c r="AM44" s="83"/>
+      <c r="A44" s="96"/>
+      <c r="B44" s="96"/>
+      <c r="C44" s="96"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
+      <c r="F44" s="86"/>
+      <c r="G44" s="86"/>
+      <c r="H44" s="86"/>
+      <c r="I44" s="86"/>
+      <c r="J44" s="86"/>
+      <c r="K44" s="86"/>
+      <c r="L44" s="96"/>
+      <c r="M44" s="86"/>
+      <c r="N44" s="86"/>
+      <c r="O44" s="86"/>
+      <c r="P44" s="86"/>
+      <c r="Q44" s="86"/>
+      <c r="R44" s="86"/>
+      <c r="S44" s="96"/>
+      <c r="T44" s="86"/>
+      <c r="U44" s="86"/>
+      <c r="V44" s="86"/>
+      <c r="W44" s="86"/>
+      <c r="X44" s="86"/>
+      <c r="Y44" s="86"/>
+      <c r="Z44" s="96"/>
+      <c r="AA44" s="86"/>
+      <c r="AB44" s="86"/>
+      <c r="AC44" s="86"/>
+      <c r="AD44" s="86"/>
+      <c r="AE44" s="86"/>
+      <c r="AF44" s="86"/>
+      <c r="AG44" s="96"/>
+      <c r="AH44" s="86"/>
+      <c r="AI44" s="86"/>
+      <c r="AJ44" s="86"/>
+      <c r="AK44" s="86"/>
+      <c r="AL44" s="86"/>
+      <c r="AM44" s="86"/>
     </row>
     <row r="45" spans="1:39" ht="15" customHeight="1">
-      <c r="A45" s="95" t="s">
+      <c r="A45" s="99" t="s">
         <v>150</v>
       </c>
-      <c r="B45" s="95"/>
-      <c r="C45" s="95"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
-      <c r="F45" s="95"/>
-      <c r="G45" s="95"/>
-      <c r="H45" s="95"/>
-      <c r="I45" s="95"/>
-      <c r="J45" s="95"/>
-      <c r="K45" s="95"/>
-      <c r="L45" s="95"/>
-      <c r="M45" s="95"/>
-      <c r="N45" s="95"/>
-      <c r="O45" s="95"/>
-      <c r="P45" s="95"/>
-      <c r="Q45" s="95"/>
-      <c r="R45" s="95"/>
-      <c r="S45" s="95"/>
-      <c r="T45" s="95"/>
-      <c r="U45" s="95"/>
-      <c r="V45" s="95"/>
-      <c r="W45" s="95"/>
-      <c r="X45" s="95"/>
-      <c r="Y45" s="95"/>
-      <c r="Z45" s="95"/>
-      <c r="AA45" s="95"/>
-      <c r="AB45" s="95"/>
-      <c r="AC45" s="95"/>
-      <c r="AD45" s="95"/>
-      <c r="AE45" s="95"/>
-      <c r="AF45" s="95"/>
-      <c r="AG45" s="95"/>
-      <c r="AH45" s="95"/>
-      <c r="AI45" s="95"/>
-      <c r="AJ45" s="95"/>
-      <c r="AK45" s="95"/>
-      <c r="AL45" s="95"/>
-      <c r="AM45" s="95"/>
+      <c r="B45" s="99"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
+      <c r="F45" s="99"/>
+      <c r="G45" s="99"/>
+      <c r="H45" s="99"/>
+      <c r="I45" s="99"/>
+      <c r="J45" s="99"/>
+      <c r="K45" s="99"/>
+      <c r="L45" s="99"/>
+      <c r="M45" s="99"/>
+      <c r="N45" s="99"/>
+      <c r="O45" s="99"/>
+      <c r="P45" s="99"/>
+      <c r="Q45" s="99"/>
+      <c r="R45" s="99"/>
+      <c r="S45" s="99"/>
+      <c r="T45" s="99"/>
+      <c r="U45" s="99"/>
+      <c r="V45" s="99"/>
+      <c r="W45" s="99"/>
+      <c r="X45" s="99"/>
+      <c r="Y45" s="99"/>
+      <c r="Z45" s="99"/>
+      <c r="AA45" s="99"/>
+      <c r="AB45" s="99"/>
+      <c r="AC45" s="99"/>
+      <c r="AD45" s="99"/>
+      <c r="AE45" s="99"/>
+      <c r="AF45" s="99"/>
+      <c r="AG45" s="99"/>
+      <c r="AH45" s="99"/>
+      <c r="AI45" s="99"/>
+      <c r="AJ45" s="99"/>
+      <c r="AK45" s="99"/>
+      <c r="AL45" s="99"/>
+      <c r="AM45" s="99"/>
     </row>
     <row r="46" spans="1:39" ht="15" customHeight="1">
-      <c r="A46" s="95" t="s">
+      <c r="A46" s="99" t="s">
         <v>151</v>
       </c>
-      <c r="B46" s="95"/>
-      <c r="C46" s="95"/>
-      <c r="D46" s="95"/>
-      <c r="E46" s="95"/>
-      <c r="F46" s="95"/>
-      <c r="G46" s="95"/>
-      <c r="H46" s="95"/>
-      <c r="I46" s="95"/>
-      <c r="J46" s="95"/>
-      <c r="K46" s="95"/>
-      <c r="L46" s="95"/>
-      <c r="M46" s="95"/>
-      <c r="N46" s="95"/>
-      <c r="O46" s="95"/>
-      <c r="P46" s="95"/>
-      <c r="Q46" s="95"/>
-      <c r="R46" s="95"/>
-      <c r="S46" s="95"/>
-      <c r="T46" s="95"/>
-      <c r="U46" s="95"/>
-      <c r="V46" s="95"/>
-      <c r="W46" s="95"/>
-      <c r="X46" s="95"/>
-      <c r="Y46" s="95"/>
-      <c r="Z46" s="95"/>
-      <c r="AA46" s="95"/>
-      <c r="AB46" s="95"/>
-      <c r="AC46" s="95"/>
-      <c r="AD46" s="95"/>
-      <c r="AE46" s="95"/>
-      <c r="AF46" s="95"/>
-      <c r="AG46" s="95"/>
-      <c r="AH46" s="95"/>
-      <c r="AI46" s="95"/>
-      <c r="AJ46" s="95"/>
-      <c r="AK46" s="95"/>
-      <c r="AL46" s="95"/>
-      <c r="AM46" s="95"/>
+      <c r="B46" s="99"/>
+      <c r="C46" s="99"/>
+      <c r="D46" s="99"/>
+      <c r="E46" s="99"/>
+      <c r="F46" s="99"/>
+      <c r="G46" s="99"/>
+      <c r="H46" s="99"/>
+      <c r="I46" s="99"/>
+      <c r="J46" s="99"/>
+      <c r="K46" s="99"/>
+      <c r="L46" s="99"/>
+      <c r="M46" s="99"/>
+      <c r="N46" s="99"/>
+      <c r="O46" s="99"/>
+      <c r="P46" s="99"/>
+      <c r="Q46" s="99"/>
+      <c r="R46" s="99"/>
+      <c r="S46" s="99"/>
+      <c r="T46" s="99"/>
+      <c r="U46" s="99"/>
+      <c r="V46" s="99"/>
+      <c r="W46" s="99"/>
+      <c r="X46" s="99"/>
+      <c r="Y46" s="99"/>
+      <c r="Z46" s="99"/>
+      <c r="AA46" s="99"/>
+      <c r="AB46" s="99"/>
+      <c r="AC46" s="99"/>
+      <c r="AD46" s="99"/>
+      <c r="AE46" s="99"/>
+      <c r="AF46" s="99"/>
+      <c r="AG46" s="99"/>
+      <c r="AH46" s="99"/>
+      <c r="AI46" s="99"/>
+      <c r="AJ46" s="99"/>
+      <c r="AK46" s="99"/>
+      <c r="AL46" s="99"/>
+      <c r="AM46" s="99"/>
     </row>
     <row r="47" spans="1:39" ht="15" customHeight="1">
-      <c r="A47" s="96" t="s">
+      <c r="A47" s="100" t="s">
         <v>152</v>
       </c>
-      <c r="B47" s="97"/>
-      <c r="C47" s="97"/>
-      <c r="D47" s="97"/>
-      <c r="E47" s="97"/>
-      <c r="F47" s="97"/>
-      <c r="G47" s="97"/>
-      <c r="H47" s="97"/>
-      <c r="I47" s="97"/>
-      <c r="J47" s="97"/>
-      <c r="K47" s="97"/>
-      <c r="L47" s="97"/>
-      <c r="M47" s="97"/>
-      <c r="N47" s="97"/>
-      <c r="O47" s="97"/>
-      <c r="P47" s="97"/>
-      <c r="Q47" s="97"/>
-      <c r="R47" s="97"/>
-      <c r="S47" s="97"/>
-      <c r="T47" s="97"/>
-      <c r="U47" s="97"/>
-      <c r="V47" s="97"/>
-      <c r="W47" s="97"/>
-      <c r="X47" s="97"/>
-      <c r="Y47" s="97"/>
-      <c r="Z47" s="97"/>
-      <c r="AA47" s="97"/>
-      <c r="AB47" s="97"/>
-      <c r="AC47" s="97"/>
-      <c r="AD47" s="97"/>
-      <c r="AE47" s="97"/>
-      <c r="AF47" s="97"/>
-      <c r="AG47" s="97"/>
-      <c r="AH47" s="97"/>
-      <c r="AI47" s="97"/>
-      <c r="AJ47" s="97"/>
-      <c r="AK47" s="97"/>
-      <c r="AL47" s="97"/>
-      <c r="AM47" s="97"/>
+      <c r="B47" s="101"/>
+      <c r="C47" s="101"/>
+      <c r="D47" s="101"/>
+      <c r="E47" s="101"/>
+      <c r="F47" s="101"/>
+      <c r="G47" s="101"/>
+      <c r="H47" s="101"/>
+      <c r="I47" s="101"/>
+      <c r="J47" s="101"/>
+      <c r="K47" s="101"/>
+      <c r="L47" s="101"/>
+      <c r="M47" s="101"/>
+      <c r="N47" s="101"/>
+      <c r="O47" s="101"/>
+      <c r="P47" s="101"/>
+      <c r="Q47" s="101"/>
+      <c r="R47" s="101"/>
+      <c r="S47" s="101"/>
+      <c r="T47" s="101"/>
+      <c r="U47" s="101"/>
+      <c r="V47" s="101"/>
+      <c r="W47" s="101"/>
+      <c r="X47" s="101"/>
+      <c r="Y47" s="101"/>
+      <c r="Z47" s="101"/>
+      <c r="AA47" s="101"/>
+      <c r="AB47" s="101"/>
+      <c r="AC47" s="101"/>
+      <c r="AD47" s="101"/>
+      <c r="AE47" s="101"/>
+      <c r="AF47" s="101"/>
+      <c r="AG47" s="101"/>
+      <c r="AH47" s="101"/>
+      <c r="AI47" s="101"/>
+      <c r="AJ47" s="101"/>
+      <c r="AK47" s="101"/>
+      <c r="AL47" s="101"/>
+      <c r="AM47" s="101"/>
     </row>
     <row r="48" spans="1:39" ht="15" customHeight="1">
-      <c r="A48" s="97"/>
-      <c r="B48" s="97"/>
-      <c r="C48" s="97"/>
-      <c r="D48" s="97"/>
-      <c r="E48" s="97"/>
-      <c r="F48" s="97"/>
-      <c r="G48" s="97"/>
-      <c r="H48" s="97"/>
-      <c r="I48" s="97"/>
-      <c r="J48" s="97"/>
-      <c r="K48" s="97"/>
-      <c r="L48" s="97"/>
-      <c r="M48" s="97"/>
-      <c r="N48" s="97"/>
-      <c r="O48" s="97"/>
-      <c r="P48" s="97"/>
-      <c r="Q48" s="97"/>
-      <c r="R48" s="97"/>
-      <c r="S48" s="97"/>
-      <c r="T48" s="97"/>
-      <c r="U48" s="97"/>
-      <c r="V48" s="97"/>
-      <c r="W48" s="97"/>
-      <c r="X48" s="97"/>
-      <c r="Y48" s="97"/>
-      <c r="Z48" s="97"/>
-      <c r="AA48" s="97"/>
-      <c r="AB48" s="97"/>
-      <c r="AC48" s="97"/>
-      <c r="AD48" s="97"/>
-      <c r="AE48" s="97"/>
-      <c r="AF48" s="97"/>
-      <c r="AG48" s="97"/>
-      <c r="AH48" s="97"/>
-      <c r="AI48" s="97"/>
-      <c r="AJ48" s="97"/>
-      <c r="AK48" s="97"/>
-      <c r="AL48" s="97"/>
-      <c r="AM48" s="97"/>
+      <c r="A48" s="101"/>
+      <c r="B48" s="101"/>
+      <c r="C48" s="101"/>
+      <c r="D48" s="101"/>
+      <c r="E48" s="101"/>
+      <c r="F48" s="101"/>
+      <c r="G48" s="101"/>
+      <c r="H48" s="101"/>
+      <c r="I48" s="101"/>
+      <c r="J48" s="101"/>
+      <c r="K48" s="101"/>
+      <c r="L48" s="101"/>
+      <c r="M48" s="101"/>
+      <c r="N48" s="101"/>
+      <c r="O48" s="101"/>
+      <c r="P48" s="101"/>
+      <c r="Q48" s="101"/>
+      <c r="R48" s="101"/>
+      <c r="S48" s="101"/>
+      <c r="T48" s="101"/>
+      <c r="U48" s="101"/>
+      <c r="V48" s="101"/>
+      <c r="W48" s="101"/>
+      <c r="X48" s="101"/>
+      <c r="Y48" s="101"/>
+      <c r="Z48" s="101"/>
+      <c r="AA48" s="101"/>
+      <c r="AB48" s="101"/>
+      <c r="AC48" s="101"/>
+      <c r="AD48" s="101"/>
+      <c r="AE48" s="101"/>
+      <c r="AF48" s="101"/>
+      <c r="AG48" s="101"/>
+      <c r="AH48" s="101"/>
+      <c r="AI48" s="101"/>
+      <c r="AJ48" s="101"/>
+      <c r="AK48" s="101"/>
+      <c r="AL48" s="101"/>
+      <c r="AM48" s="101"/>
     </row>
     <row r="49" spans="1:39" ht="15" customHeight="1">
-      <c r="A49" s="97"/>
-      <c r="B49" s="97"/>
-      <c r="C49" s="97"/>
-      <c r="D49" s="97"/>
-      <c r="E49" s="97"/>
-      <c r="F49" s="97"/>
-      <c r="G49" s="97"/>
-      <c r="H49" s="97"/>
-      <c r="I49" s="97"/>
-      <c r="J49" s="97"/>
-      <c r="K49" s="97"/>
-      <c r="L49" s="97"/>
-      <c r="M49" s="97"/>
-      <c r="N49" s="97"/>
-      <c r="O49" s="97"/>
-      <c r="P49" s="97"/>
-      <c r="Q49" s="97"/>
-      <c r="R49" s="97"/>
-      <c r="S49" s="97"/>
-      <c r="T49" s="97"/>
-      <c r="U49" s="97"/>
-      <c r="V49" s="97"/>
-      <c r="W49" s="97"/>
-      <c r="X49" s="97"/>
-      <c r="Y49" s="97"/>
-      <c r="Z49" s="97"/>
-      <c r="AA49" s="97"/>
-      <c r="AB49" s="97"/>
-      <c r="AC49" s="97"/>
-      <c r="AD49" s="97"/>
-      <c r="AE49" s="97"/>
-      <c r="AF49" s="97"/>
-      <c r="AG49" s="97"/>
-      <c r="AH49" s="97"/>
-      <c r="AI49" s="97"/>
-      <c r="AJ49" s="97"/>
-      <c r="AK49" s="97"/>
-      <c r="AL49" s="97"/>
-      <c r="AM49" s="97"/>
-    </row>
-    <row r="50" spans="1:39" ht="8.5" customHeight="1">
+      <c r="A49" s="101"/>
+      <c r="B49" s="101"/>
+      <c r="C49" s="101"/>
+      <c r="D49" s="101"/>
+      <c r="E49" s="101"/>
+      <c r="F49" s="101"/>
+      <c r="G49" s="101"/>
+      <c r="H49" s="101"/>
+      <c r="I49" s="101"/>
+      <c r="J49" s="101"/>
+      <c r="K49" s="101"/>
+      <c r="L49" s="101"/>
+      <c r="M49" s="101"/>
+      <c r="N49" s="101"/>
+      <c r="O49" s="101"/>
+      <c r="P49" s="101"/>
+      <c r="Q49" s="101"/>
+      <c r="R49" s="101"/>
+      <c r="S49" s="101"/>
+      <c r="T49" s="101"/>
+      <c r="U49" s="101"/>
+      <c r="V49" s="101"/>
+      <c r="W49" s="101"/>
+      <c r="X49" s="101"/>
+      <c r="Y49" s="101"/>
+      <c r="Z49" s="101"/>
+      <c r="AA49" s="101"/>
+      <c r="AB49" s="101"/>
+      <c r="AC49" s="101"/>
+      <c r="AD49" s="101"/>
+      <c r="AE49" s="101"/>
+      <c r="AF49" s="101"/>
+      <c r="AG49" s="101"/>
+      <c r="AH49" s="101"/>
+      <c r="AI49" s="101"/>
+      <c r="AJ49" s="101"/>
+      <c r="AK49" s="101"/>
+      <c r="AL49" s="101"/>
+      <c r="AM49" s="101"/>
+    </row>
+    <row r="50" spans="1:39" ht="8.5500000000000007" customHeight="1">
       <c r="A50" s="46"/>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
@@ -12753,32 +12733,132 @@
     </row>
   </sheetData>
   <mergeCells count="175">
-    <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="A10:L10"/>
-    <mergeCell ref="A11:L11"/>
-    <mergeCell ref="A9:L9"/>
-    <mergeCell ref="M7:U7"/>
-    <mergeCell ref="V7:AD7"/>
-    <mergeCell ref="AE7:AM7"/>
-    <mergeCell ref="M8:U8"/>
-    <mergeCell ref="V8:AD8"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="M11:U11"/>
-    <mergeCell ref="V11:AD11"/>
-    <mergeCell ref="AE11:AM11"/>
-    <mergeCell ref="A7:L7"/>
-    <mergeCell ref="A8:L8"/>
-    <mergeCell ref="A2:W2"/>
-    <mergeCell ref="A16:AM16"/>
-    <mergeCell ref="AE8:AM8"/>
-    <mergeCell ref="M9:U9"/>
-    <mergeCell ref="V9:AD9"/>
-    <mergeCell ref="AE9:AM9"/>
-    <mergeCell ref="M10:U10"/>
-    <mergeCell ref="V10:AD10"/>
-    <mergeCell ref="AE10:AM10"/>
-    <mergeCell ref="A17:AM17"/>
+    <mergeCell ref="A45:AM45"/>
+    <mergeCell ref="A46:AM46"/>
+    <mergeCell ref="A47:AM49"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="E44:K44"/>
+    <mergeCell ref="L44:R44"/>
+    <mergeCell ref="S44:Y44"/>
+    <mergeCell ref="Z44:AF44"/>
+    <mergeCell ref="AG44:AM44"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="E43:K43"/>
+    <mergeCell ref="L43:R43"/>
+    <mergeCell ref="S43:Y43"/>
+    <mergeCell ref="Z43:AF43"/>
+    <mergeCell ref="AG43:AM43"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="E42:K42"/>
+    <mergeCell ref="L42:R42"/>
+    <mergeCell ref="S42:Y42"/>
+    <mergeCell ref="Z42:AF42"/>
+    <mergeCell ref="AG42:AM42"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="E41:K41"/>
+    <mergeCell ref="L41:R41"/>
+    <mergeCell ref="S41:Y41"/>
+    <mergeCell ref="Z41:AF41"/>
+    <mergeCell ref="AG41:AM41"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="E40:K40"/>
+    <mergeCell ref="L40:R40"/>
+    <mergeCell ref="S40:Y40"/>
+    <mergeCell ref="Z40:AF40"/>
+    <mergeCell ref="AG40:AM40"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="E39:K39"/>
+    <mergeCell ref="L39:R39"/>
+    <mergeCell ref="S39:Y39"/>
+    <mergeCell ref="Z39:AF39"/>
+    <mergeCell ref="AG39:AM39"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="E38:K38"/>
+    <mergeCell ref="L38:R38"/>
+    <mergeCell ref="S38:Y38"/>
+    <mergeCell ref="Z38:AF38"/>
+    <mergeCell ref="AG38:AM38"/>
+    <mergeCell ref="AG37:AM37"/>
+    <mergeCell ref="AG35:AM35"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="E36:K36"/>
+    <mergeCell ref="L36:R36"/>
+    <mergeCell ref="S36:Y36"/>
+    <mergeCell ref="Z36:AF36"/>
+    <mergeCell ref="AG36:AM36"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="E35:K35"/>
+    <mergeCell ref="L35:R35"/>
+    <mergeCell ref="S35:Y35"/>
+    <mergeCell ref="Z35:AF35"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="E37:K37"/>
+    <mergeCell ref="L37:R37"/>
+    <mergeCell ref="S37:Y37"/>
+    <mergeCell ref="Z37:AF37"/>
+    <mergeCell ref="A31:AM31"/>
+    <mergeCell ref="A32:AM32"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="E33:K33"/>
+    <mergeCell ref="L33:R33"/>
+    <mergeCell ref="S33:Y33"/>
+    <mergeCell ref="Z33:AF33"/>
+    <mergeCell ref="AG33:AM33"/>
+    <mergeCell ref="E34:K34"/>
+    <mergeCell ref="L34:R34"/>
+    <mergeCell ref="S34:Y34"/>
+    <mergeCell ref="Z34:AF34"/>
+    <mergeCell ref="AG34:AM34"/>
+    <mergeCell ref="V23:X23"/>
+    <mergeCell ref="A25:AM25"/>
+    <mergeCell ref="A26:AM26"/>
+    <mergeCell ref="A27:AM27"/>
+    <mergeCell ref="A28:AM28"/>
+    <mergeCell ref="A30:AM30"/>
+    <mergeCell ref="V24:X24"/>
+    <mergeCell ref="Y24:AA24"/>
+    <mergeCell ref="AB24:AD24"/>
+    <mergeCell ref="AE24:AG24"/>
+    <mergeCell ref="AH24:AJ24"/>
+    <mergeCell ref="AK24:AM24"/>
+    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="J24:L24"/>
+    <mergeCell ref="M24:O24"/>
+    <mergeCell ref="P24:R24"/>
+    <mergeCell ref="S24:U24"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="M23:O23"/>
+    <mergeCell ref="P23:R23"/>
+    <mergeCell ref="S23:U23"/>
+    <mergeCell ref="AK22:AM22"/>
+    <mergeCell ref="Y20:AA20"/>
+    <mergeCell ref="AB20:AD20"/>
+    <mergeCell ref="AE20:AG20"/>
+    <mergeCell ref="AH20:AJ20"/>
+    <mergeCell ref="AK20:AM20"/>
+    <mergeCell ref="Y23:AA23"/>
+    <mergeCell ref="AB23:AD23"/>
+    <mergeCell ref="AE23:AG23"/>
+    <mergeCell ref="AH23:AJ23"/>
+    <mergeCell ref="AK23:AM23"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="M22:O22"/>
+    <mergeCell ref="P22:R22"/>
+    <mergeCell ref="S22:U22"/>
+    <mergeCell ref="Y19:AA19"/>
+    <mergeCell ref="AB19:AD19"/>
+    <mergeCell ref="AE19:AG19"/>
+    <mergeCell ref="AH19:AJ19"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="V22:X22"/>
+    <mergeCell ref="Y22:AA22"/>
+    <mergeCell ref="AB22:AD22"/>
+    <mergeCell ref="AE22:AG22"/>
+    <mergeCell ref="AH22:AJ22"/>
     <mergeCell ref="A18:AM18"/>
     <mergeCell ref="A21:I21"/>
     <mergeCell ref="J21:L21"/>
@@ -12802,132 +12882,32 @@
     <mergeCell ref="P19:R19"/>
     <mergeCell ref="S19:U19"/>
     <mergeCell ref="V19:X19"/>
-    <mergeCell ref="A22:I22"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="M22:O22"/>
-    <mergeCell ref="P22:R22"/>
-    <mergeCell ref="S22:U22"/>
-    <mergeCell ref="Y19:AA19"/>
-    <mergeCell ref="AB19:AD19"/>
-    <mergeCell ref="AE19:AG19"/>
-    <mergeCell ref="AH19:AJ19"/>
-    <mergeCell ref="A20:I20"/>
-    <mergeCell ref="A19:I19"/>
-    <mergeCell ref="V22:X22"/>
-    <mergeCell ref="Y22:AA22"/>
-    <mergeCell ref="AB22:AD22"/>
-    <mergeCell ref="AE22:AG22"/>
-    <mergeCell ref="AH22:AJ22"/>
-    <mergeCell ref="AK22:AM22"/>
-    <mergeCell ref="Y20:AA20"/>
-    <mergeCell ref="AB20:AD20"/>
-    <mergeCell ref="AE20:AG20"/>
-    <mergeCell ref="AH20:AJ20"/>
-    <mergeCell ref="AK20:AM20"/>
-    <mergeCell ref="Y23:AA23"/>
-    <mergeCell ref="AB23:AD23"/>
-    <mergeCell ref="AE23:AG23"/>
-    <mergeCell ref="AH23:AJ23"/>
-    <mergeCell ref="AK23:AM23"/>
-    <mergeCell ref="V23:X23"/>
-    <mergeCell ref="A25:AM25"/>
-    <mergeCell ref="A26:AM26"/>
-    <mergeCell ref="A27:AM27"/>
-    <mergeCell ref="A28:AM28"/>
-    <mergeCell ref="A30:AM30"/>
-    <mergeCell ref="V24:X24"/>
-    <mergeCell ref="Y24:AA24"/>
-    <mergeCell ref="AB24:AD24"/>
-    <mergeCell ref="AE24:AG24"/>
-    <mergeCell ref="AH24:AJ24"/>
-    <mergeCell ref="AK24:AM24"/>
-    <mergeCell ref="A24:I24"/>
-    <mergeCell ref="J24:L24"/>
-    <mergeCell ref="M24:O24"/>
-    <mergeCell ref="P24:R24"/>
-    <mergeCell ref="S24:U24"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="M23:O23"/>
-    <mergeCell ref="P23:R23"/>
-    <mergeCell ref="S23:U23"/>
-    <mergeCell ref="A31:AM31"/>
-    <mergeCell ref="A32:AM32"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="E33:K33"/>
-    <mergeCell ref="L33:R33"/>
-    <mergeCell ref="S33:Y33"/>
-    <mergeCell ref="Z33:AF33"/>
-    <mergeCell ref="AG33:AM33"/>
-    <mergeCell ref="E34:K34"/>
-    <mergeCell ref="L34:R34"/>
-    <mergeCell ref="S34:Y34"/>
-    <mergeCell ref="Z34:AF34"/>
-    <mergeCell ref="AG34:AM34"/>
-    <mergeCell ref="AG37:AM37"/>
-    <mergeCell ref="AG35:AM35"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="E36:K36"/>
-    <mergeCell ref="L36:R36"/>
-    <mergeCell ref="S36:Y36"/>
-    <mergeCell ref="Z36:AF36"/>
-    <mergeCell ref="AG36:AM36"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="E35:K35"/>
-    <mergeCell ref="L35:R35"/>
-    <mergeCell ref="S35:Y35"/>
-    <mergeCell ref="Z35:AF35"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="E37:K37"/>
-    <mergeCell ref="L37:R37"/>
-    <mergeCell ref="S37:Y37"/>
-    <mergeCell ref="Z37:AF37"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="E39:K39"/>
-    <mergeCell ref="L39:R39"/>
-    <mergeCell ref="S39:Y39"/>
-    <mergeCell ref="Z39:AF39"/>
-    <mergeCell ref="AG39:AM39"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="E38:K38"/>
-    <mergeCell ref="L38:R38"/>
-    <mergeCell ref="S38:Y38"/>
-    <mergeCell ref="Z38:AF38"/>
-    <mergeCell ref="AG38:AM38"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="E41:K41"/>
-    <mergeCell ref="L41:R41"/>
-    <mergeCell ref="S41:Y41"/>
-    <mergeCell ref="Z41:AF41"/>
-    <mergeCell ref="AG41:AM41"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="E40:K40"/>
-    <mergeCell ref="L40:R40"/>
-    <mergeCell ref="S40:Y40"/>
-    <mergeCell ref="Z40:AF40"/>
-    <mergeCell ref="AG40:AM40"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="E43:K43"/>
-    <mergeCell ref="L43:R43"/>
-    <mergeCell ref="S43:Y43"/>
-    <mergeCell ref="Z43:AF43"/>
-    <mergeCell ref="AG43:AM43"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="E42:K42"/>
-    <mergeCell ref="L42:R42"/>
-    <mergeCell ref="S42:Y42"/>
-    <mergeCell ref="Z42:AF42"/>
-    <mergeCell ref="AG42:AM42"/>
-    <mergeCell ref="A45:AM45"/>
-    <mergeCell ref="A46:AM46"/>
-    <mergeCell ref="A47:AM49"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="E44:K44"/>
-    <mergeCell ref="L44:R44"/>
-    <mergeCell ref="S44:Y44"/>
-    <mergeCell ref="Z44:AF44"/>
-    <mergeCell ref="AG44:AM44"/>
+    <mergeCell ref="A16:AM16"/>
+    <mergeCell ref="AE8:AM8"/>
+    <mergeCell ref="M9:U9"/>
+    <mergeCell ref="V9:AD9"/>
+    <mergeCell ref="AE9:AM9"/>
+    <mergeCell ref="M10:U10"/>
+    <mergeCell ref="V10:AD10"/>
+    <mergeCell ref="AE10:AM10"/>
+    <mergeCell ref="A17:AM17"/>
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="A10:L10"/>
+    <mergeCell ref="A11:L11"/>
+    <mergeCell ref="A9:L9"/>
+    <mergeCell ref="M7:U7"/>
+    <mergeCell ref="V7:AD7"/>
+    <mergeCell ref="AE7:AM7"/>
+    <mergeCell ref="M8:U8"/>
+    <mergeCell ref="V8:AD8"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="M11:U11"/>
+    <mergeCell ref="V11:AD11"/>
+    <mergeCell ref="AE11:AM11"/>
+    <mergeCell ref="A7:L7"/>
+    <mergeCell ref="A8:L8"/>
+    <mergeCell ref="A2:W2"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -12947,12 +12927,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BE5942F-1490-4247-AC39-F63BE022496D}">
   <dimension ref="A1:AM62"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="7" width="2.35546875" customWidth="1"/>
+    <col min="1" max="7" width="2.33203125" customWidth="1"/>
     <col min="8" max="8" width="2" customWidth="1"/>
-    <col min="9" max="31" width="2.140625" customWidth="1"/>
-    <col min="32" max="39" width="2.35546875" customWidth="1"/>
+    <col min="9" max="31" width="2.109375" customWidth="1"/>
+    <col min="32" max="39" width="2.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="15" customHeight="1">
@@ -12967,35 +12947,35 @@
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="78"/>
-      <c r="Z1" s="78"/>
-      <c r="AA1" s="78"/>
-      <c r="AB1" s="78"/>
-      <c r="AC1" s="78"/>
-      <c r="AD1" s="78"/>
-      <c r="AE1" s="78"/>
-      <c r="AF1" s="78"/>
-      <c r="AG1" s="78"/>
-      <c r="AH1" s="78"/>
-      <c r="AI1" s="78"/>
-      <c r="AJ1" s="78"/>
-      <c r="AK1" s="78"/>
-      <c r="AL1" s="78"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="72"/>
+      <c r="O1" s="72"/>
+      <c r="P1" s="72"/>
+      <c r="Q1" s="72"/>
+      <c r="R1" s="72"/>
+      <c r="S1" s="72"/>
+      <c r="T1" s="72"/>
+      <c r="U1" s="72"/>
+      <c r="V1" s="72"/>
+      <c r="W1" s="72"/>
+      <c r="X1" s="72"/>
+      <c r="Y1" s="72"/>
+      <c r="Z1" s="72"/>
+      <c r="AA1" s="72"/>
+      <c r="AB1" s="72"/>
+      <c r="AC1" s="72"/>
+      <c r="AD1" s="72"/>
+      <c r="AE1" s="72"/>
+      <c r="AF1" s="72"/>
+      <c r="AG1" s="72"/>
+      <c r="AH1" s="72"/>
+      <c r="AI1" s="72"/>
+      <c r="AJ1" s="72"/>
+      <c r="AK1" s="72"/>
+      <c r="AL1" s="72"/>
       <c r="AM1" s="33"/>
     </row>
-    <row r="2" spans="1:39" ht="14.15" customHeight="1">
+    <row r="2" spans="1:39" ht="14.1" customHeight="1">
       <c r="A2" s="19" t="s">
         <v>153</v>
       </c>
@@ -13028,18 +13008,18 @@
       <c r="AE2" s="3"/>
       <c r="AF2" s="3"/>
     </row>
-    <row r="3" spans="1:39" ht="14.15" customHeight="1">
-      <c r="A3" s="71"/>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="71"/>
-      <c r="K3" s="71"/>
+    <row r="3" spans="1:39" ht="14.1" customHeight="1">
+      <c r="A3" s="68"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
@@ -13062,7 +13042,7 @@
       <c r="AE3" s="3"/>
       <c r="AF3" s="3"/>
     </row>
-    <row r="4" spans="1:39" ht="14.15" customHeight="1">
+    <row r="4" spans="1:39" ht="14.1" customHeight="1">
       <c r="A4" s="49"/>
       <c r="B4" s="49"/>
       <c r="C4" s="49"/>
@@ -13096,7 +13076,7 @@
       <c r="AE4" s="3"/>
       <c r="AF4" s="3"/>
     </row>
-    <row r="5" spans="1:39" ht="14.15" customHeight="1">
+    <row r="5" spans="1:39" ht="14.1" customHeight="1">
       <c r="A5" s="94" t="s">
         <v>171</v>
       </c>
@@ -13132,7 +13112,7 @@
       <c r="AE5" s="3"/>
       <c r="AF5" s="3"/>
     </row>
-    <row r="6" spans="1:39" ht="14.15" customHeight="1">
+    <row r="6" spans="1:39" ht="14.1" customHeight="1">
       <c r="A6" s="49"/>
       <c r="B6" s="49"/>
       <c r="C6" s="49"/>
@@ -13166,7 +13146,7 @@
       <c r="AE6" s="3"/>
       <c r="AF6" s="3"/>
     </row>
-    <row r="7" spans="1:39" ht="14.15" customHeight="1">
+    <row r="7" spans="1:39" ht="14.1" customHeight="1">
       <c r="A7" s="46" t="s">
         <v>154</v>
       </c>
@@ -13199,285 +13179,285 @@
       <c r="AE7" s="3"/>
       <c r="AF7" s="3"/>
     </row>
-    <row r="8" spans="1:39" ht="14.15" customHeight="1">
-      <c r="A8" s="98" t="s">
+    <row r="8" spans="1:39" ht="14.1" customHeight="1">
+      <c r="A8" s="96" t="s">
         <v>155</v>
       </c>
-      <c r="B8" s="98"/>
-      <c r="C8" s="98"/>
-      <c r="D8" s="98"/>
-      <c r="E8" s="98"/>
-      <c r="F8" s="98" t="s">
+      <c r="B8" s="96"/>
+      <c r="C8" s="96"/>
+      <c r="D8" s="96"/>
+      <c r="E8" s="96"/>
+      <c r="F8" s="96" t="s">
         <v>158</v>
       </c>
-      <c r="G8" s="98"/>
-      <c r="H8" s="98"/>
-      <c r="I8" s="98"/>
-      <c r="J8" s="98"/>
-      <c r="K8" s="98"/>
-      <c r="L8" s="98"/>
-      <c r="M8" s="103" t="s">
+      <c r="G8" s="96"/>
+      <c r="H8" s="96"/>
+      <c r="I8" s="96"/>
+      <c r="J8" s="96"/>
+      <c r="K8" s="96"/>
+      <c r="L8" s="96"/>
+      <c r="M8" s="102" t="s">
         <v>172</v>
       </c>
-      <c r="N8" s="98"/>
-      <c r="O8" s="98"/>
-      <c r="P8" s="98"/>
-      <c r="Q8" s="98"/>
-      <c r="R8" s="98"/>
-      <c r="S8" s="98"/>
-      <c r="T8" s="98" t="s">
+      <c r="N8" s="96"/>
+      <c r="O8" s="96"/>
+      <c r="P8" s="96"/>
+      <c r="Q8" s="96"/>
+      <c r="R8" s="96"/>
+      <c r="S8" s="96"/>
+      <c r="T8" s="96" t="s">
         <v>160</v>
       </c>
-      <c r="U8" s="98"/>
-      <c r="V8" s="98"/>
-      <c r="W8" s="98"/>
-      <c r="X8" s="98"/>
-      <c r="Y8" s="98"/>
-      <c r="Z8" s="98"/>
-      <c r="AA8" s="98" t="s">
+      <c r="U8" s="96"/>
+      <c r="V8" s="96"/>
+      <c r="W8" s="96"/>
+      <c r="X8" s="96"/>
+      <c r="Y8" s="96"/>
+      <c r="Z8" s="96"/>
+      <c r="AA8" s="96" t="s">
         <v>161</v>
       </c>
-      <c r="AB8" s="98"/>
-      <c r="AC8" s="98"/>
-      <c r="AD8" s="98"/>
-      <c r="AE8" s="98"/>
-      <c r="AF8" s="98"/>
-      <c r="AG8" s="98"/>
-      <c r="AH8" s="98" t="s">
+      <c r="AB8" s="96"/>
+      <c r="AC8" s="96"/>
+      <c r="AD8" s="96"/>
+      <c r="AE8" s="96"/>
+      <c r="AF8" s="96"/>
+      <c r="AG8" s="96"/>
+      <c r="AH8" s="96" t="s">
         <v>162</v>
       </c>
-      <c r="AI8" s="98"/>
-      <c r="AJ8" s="98"/>
-      <c r="AK8" s="98"/>
-      <c r="AL8" s="98"/>
-      <c r="AM8" s="98"/>
-    </row>
-    <row r="9" spans="1:39" ht="14.15" customHeight="1">
-      <c r="A9" s="98" t="s">
+      <c r="AI8" s="96"/>
+      <c r="AJ8" s="96"/>
+      <c r="AK8" s="96"/>
+      <c r="AL8" s="96"/>
+      <c r="AM8" s="96"/>
+    </row>
+    <row r="9" spans="1:39" ht="14.1" customHeight="1">
+      <c r="A9" s="96" t="s">
         <v>156</v>
       </c>
-      <c r="B9" s="98"/>
-      <c r="C9" s="98"/>
-      <c r="D9" s="98"/>
-      <c r="E9" s="98"/>
-      <c r="F9" s="98"/>
-      <c r="G9" s="98"/>
-      <c r="H9" s="98"/>
-      <c r="I9" s="98"/>
-      <c r="J9" s="98"/>
-      <c r="K9" s="98"/>
-      <c r="L9" s="98"/>
-      <c r="M9" s="98"/>
-      <c r="N9" s="98"/>
-      <c r="O9" s="98"/>
-      <c r="P9" s="98"/>
-      <c r="Q9" s="98"/>
-      <c r="R9" s="98"/>
-      <c r="S9" s="98"/>
-      <c r="T9" s="98"/>
-      <c r="U9" s="98"/>
-      <c r="V9" s="98"/>
-      <c r="W9" s="98"/>
-      <c r="X9" s="98"/>
-      <c r="Y9" s="98"/>
-      <c r="Z9" s="98"/>
-      <c r="AA9" s="98"/>
-      <c r="AB9" s="98"/>
-      <c r="AC9" s="98"/>
-      <c r="AD9" s="98"/>
-      <c r="AE9" s="98"/>
-      <c r="AF9" s="98"/>
-      <c r="AG9" s="98"/>
-      <c r="AH9" s="98"/>
-      <c r="AI9" s="98"/>
-      <c r="AJ9" s="98"/>
-      <c r="AK9" s="98"/>
-      <c r="AL9" s="98"/>
-      <c r="AM9" s="98"/>
-    </row>
-    <row r="10" spans="1:39" ht="14.15" customHeight="1">
-      <c r="A10" s="98" t="s">
+      <c r="B9" s="96"/>
+      <c r="C9" s="96"/>
+      <c r="D9" s="96"/>
+      <c r="E9" s="96"/>
+      <c r="F9" s="96"/>
+      <c r="G9" s="96"/>
+      <c r="H9" s="96"/>
+      <c r="I9" s="96"/>
+      <c r="J9" s="96"/>
+      <c r="K9" s="96"/>
+      <c r="L9" s="96"/>
+      <c r="M9" s="96"/>
+      <c r="N9" s="96"/>
+      <c r="O9" s="96"/>
+      <c r="P9" s="96"/>
+      <c r="Q9" s="96"/>
+      <c r="R9" s="96"/>
+      <c r="S9" s="96"/>
+      <c r="T9" s="96"/>
+      <c r="U9" s="96"/>
+      <c r="V9" s="96"/>
+      <c r="W9" s="96"/>
+      <c r="X9" s="96"/>
+      <c r="Y9" s="96"/>
+      <c r="Z9" s="96"/>
+      <c r="AA9" s="96"/>
+      <c r="AB9" s="96"/>
+      <c r="AC9" s="96"/>
+      <c r="AD9" s="96"/>
+      <c r="AE9" s="96"/>
+      <c r="AF9" s="96"/>
+      <c r="AG9" s="96"/>
+      <c r="AH9" s="96"/>
+      <c r="AI9" s="96"/>
+      <c r="AJ9" s="96"/>
+      <c r="AK9" s="96"/>
+      <c r="AL9" s="96"/>
+      <c r="AM9" s="96"/>
+    </row>
+    <row r="10" spans="1:39" ht="14.1" customHeight="1">
+      <c r="A10" s="96" t="s">
         <v>157</v>
       </c>
-      <c r="B10" s="98"/>
-      <c r="C10" s="98"/>
-      <c r="D10" s="98"/>
-      <c r="E10" s="98"/>
-      <c r="F10" s="98"/>
-      <c r="G10" s="98"/>
-      <c r="H10" s="98"/>
-      <c r="I10" s="98"/>
-      <c r="J10" s="98"/>
-      <c r="K10" s="98"/>
-      <c r="L10" s="98"/>
-      <c r="M10" s="98"/>
-      <c r="N10" s="98"/>
-      <c r="O10" s="98"/>
-      <c r="P10" s="98"/>
-      <c r="Q10" s="98"/>
-      <c r="R10" s="98"/>
-      <c r="S10" s="98"/>
-      <c r="T10" s="98"/>
-      <c r="U10" s="98"/>
-      <c r="V10" s="98"/>
-      <c r="W10" s="98"/>
-      <c r="X10" s="98"/>
-      <c r="Y10" s="98"/>
-      <c r="Z10" s="98"/>
-      <c r="AA10" s="98"/>
-      <c r="AB10" s="98"/>
-      <c r="AC10" s="98"/>
-      <c r="AD10" s="98"/>
-      <c r="AE10" s="98"/>
-      <c r="AF10" s="98"/>
-      <c r="AG10" s="98"/>
-      <c r="AH10" s="98"/>
-      <c r="AI10" s="98"/>
-      <c r="AJ10" s="98"/>
-      <c r="AK10" s="98"/>
-      <c r="AL10" s="98"/>
-      <c r="AM10" s="98"/>
-    </row>
-    <row r="11" spans="1:39" ht="14.15" customHeight="1">
-      <c r="A11" s="98" t="s">
+      <c r="B10" s="96"/>
+      <c r="C10" s="96"/>
+      <c r="D10" s="96"/>
+      <c r="E10" s="96"/>
+      <c r="F10" s="96"/>
+      <c r="G10" s="96"/>
+      <c r="H10" s="96"/>
+      <c r="I10" s="96"/>
+      <c r="J10" s="96"/>
+      <c r="K10" s="96"/>
+      <c r="L10" s="96"/>
+      <c r="M10" s="96"/>
+      <c r="N10" s="96"/>
+      <c r="O10" s="96"/>
+      <c r="P10" s="96"/>
+      <c r="Q10" s="96"/>
+      <c r="R10" s="96"/>
+      <c r="S10" s="96"/>
+      <c r="T10" s="96"/>
+      <c r="U10" s="96"/>
+      <c r="V10" s="96"/>
+      <c r="W10" s="96"/>
+      <c r="X10" s="96"/>
+      <c r="Y10" s="96"/>
+      <c r="Z10" s="96"/>
+      <c r="AA10" s="96"/>
+      <c r="AB10" s="96"/>
+      <c r="AC10" s="96"/>
+      <c r="AD10" s="96"/>
+      <c r="AE10" s="96"/>
+      <c r="AF10" s="96"/>
+      <c r="AG10" s="96"/>
+      <c r="AH10" s="96"/>
+      <c r="AI10" s="96"/>
+      <c r="AJ10" s="96"/>
+      <c r="AK10" s="96"/>
+      <c r="AL10" s="96"/>
+      <c r="AM10" s="96"/>
+    </row>
+    <row r="11" spans="1:39" ht="14.1" customHeight="1">
+      <c r="A11" s="96" t="s">
         <v>155</v>
       </c>
-      <c r="B11" s="98"/>
-      <c r="C11" s="98"/>
-      <c r="D11" s="98"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="98" t="s">
+      <c r="B11" s="96"/>
+      <c r="C11" s="96"/>
+      <c r="D11" s="96"/>
+      <c r="E11" s="96"/>
+      <c r="F11" s="96" t="s">
         <v>163</v>
       </c>
-      <c r="G11" s="98"/>
-      <c r="H11" s="98"/>
-      <c r="I11" s="98"/>
-      <c r="J11" s="98"/>
-      <c r="K11" s="98"/>
-      <c r="L11" s="98"/>
-      <c r="M11" s="98" t="s">
+      <c r="G11" s="96"/>
+      <c r="H11" s="96"/>
+      <c r="I11" s="96"/>
+      <c r="J11" s="96"/>
+      <c r="K11" s="96"/>
+      <c r="L11" s="96"/>
+      <c r="M11" s="96" t="s">
         <v>164</v>
       </c>
-      <c r="N11" s="98"/>
-      <c r="O11" s="98"/>
-      <c r="P11" s="98"/>
-      <c r="Q11" s="98"/>
-      <c r="R11" s="98"/>
-      <c r="S11" s="98"/>
-      <c r="T11" s="98" t="s">
+      <c r="N11" s="96"/>
+      <c r="O11" s="96"/>
+      <c r="P11" s="96"/>
+      <c r="Q11" s="96"/>
+      <c r="R11" s="96"/>
+      <c r="S11" s="96"/>
+      <c r="T11" s="96" t="s">
         <v>165</v>
       </c>
-      <c r="U11" s="98"/>
-      <c r="V11" s="98"/>
-      <c r="W11" s="98"/>
-      <c r="X11" s="98"/>
-      <c r="Y11" s="98"/>
-      <c r="Z11" s="98"/>
-      <c r="AA11" s="98" t="s">
+      <c r="U11" s="96"/>
+      <c r="V11" s="96"/>
+      <c r="W11" s="96"/>
+      <c r="X11" s="96"/>
+      <c r="Y11" s="96"/>
+      <c r="Z11" s="96"/>
+      <c r="AA11" s="96" t="s">
         <v>166</v>
       </c>
-      <c r="AB11" s="98"/>
-      <c r="AC11" s="98"/>
-      <c r="AD11" s="98"/>
-      <c r="AE11" s="98"/>
-      <c r="AF11" s="98"/>
-      <c r="AG11" s="98"/>
-      <c r="AH11" s="98" t="s">
+      <c r="AB11" s="96"/>
+      <c r="AC11" s="96"/>
+      <c r="AD11" s="96"/>
+      <c r="AE11" s="96"/>
+      <c r="AF11" s="96"/>
+      <c r="AG11" s="96"/>
+      <c r="AH11" s="96" t="s">
         <v>167</v>
       </c>
-      <c r="AI11" s="98"/>
-      <c r="AJ11" s="98"/>
-      <c r="AK11" s="98"/>
-      <c r="AL11" s="98"/>
-      <c r="AM11" s="98"/>
-    </row>
-    <row r="12" spans="1:39" ht="14.15" customHeight="1">
-      <c r="A12" s="98" t="s">
+      <c r="AI11" s="96"/>
+      <c r="AJ11" s="96"/>
+      <c r="AK11" s="96"/>
+      <c r="AL11" s="96"/>
+      <c r="AM11" s="96"/>
+    </row>
+    <row r="12" spans="1:39" ht="14.1" customHeight="1">
+      <c r="A12" s="96" t="s">
         <v>156</v>
       </c>
-      <c r="B12" s="98"/>
-      <c r="C12" s="98"/>
-      <c r="D12" s="98"/>
-      <c r="E12" s="98"/>
-      <c r="F12" s="98"/>
-      <c r="G12" s="98"/>
-      <c r="H12" s="98"/>
-      <c r="I12" s="98"/>
-      <c r="J12" s="98"/>
-      <c r="K12" s="98"/>
-      <c r="L12" s="98"/>
-      <c r="M12" s="98"/>
-      <c r="N12" s="98"/>
-      <c r="O12" s="98"/>
-      <c r="P12" s="98"/>
-      <c r="Q12" s="98"/>
-      <c r="R12" s="98"/>
-      <c r="S12" s="98"/>
-      <c r="T12" s="98"/>
-      <c r="U12" s="98"/>
-      <c r="V12" s="98"/>
-      <c r="W12" s="98"/>
-      <c r="X12" s="98"/>
-      <c r="Y12" s="98"/>
-      <c r="Z12" s="98"/>
-      <c r="AA12" s="98"/>
-      <c r="AB12" s="98"/>
-      <c r="AC12" s="98"/>
-      <c r="AD12" s="98"/>
-      <c r="AE12" s="98"/>
-      <c r="AF12" s="98"/>
-      <c r="AG12" s="98"/>
-      <c r="AH12" s="98"/>
-      <c r="AI12" s="98"/>
-      <c r="AJ12" s="98"/>
-      <c r="AK12" s="98"/>
-      <c r="AL12" s="98"/>
-      <c r="AM12" s="98"/>
-    </row>
-    <row r="13" spans="1:39" ht="14.15" customHeight="1">
-      <c r="A13" s="98" t="s">
+      <c r="B12" s="96"/>
+      <c r="C12" s="96"/>
+      <c r="D12" s="96"/>
+      <c r="E12" s="96"/>
+      <c r="F12" s="96"/>
+      <c r="G12" s="96"/>
+      <c r="H12" s="96"/>
+      <c r="I12" s="96"/>
+      <c r="J12" s="96"/>
+      <c r="K12" s="96"/>
+      <c r="L12" s="96"/>
+      <c r="M12" s="96"/>
+      <c r="N12" s="96"/>
+      <c r="O12" s="96"/>
+      <c r="P12" s="96"/>
+      <c r="Q12" s="96"/>
+      <c r="R12" s="96"/>
+      <c r="S12" s="96"/>
+      <c r="T12" s="96"/>
+      <c r="U12" s="96"/>
+      <c r="V12" s="96"/>
+      <c r="W12" s="96"/>
+      <c r="X12" s="96"/>
+      <c r="Y12" s="96"/>
+      <c r="Z12" s="96"/>
+      <c r="AA12" s="96"/>
+      <c r="AB12" s="96"/>
+      <c r="AC12" s="96"/>
+      <c r="AD12" s="96"/>
+      <c r="AE12" s="96"/>
+      <c r="AF12" s="96"/>
+      <c r="AG12" s="96"/>
+      <c r="AH12" s="96"/>
+      <c r="AI12" s="96"/>
+      <c r="AJ12" s="96"/>
+      <c r="AK12" s="96"/>
+      <c r="AL12" s="96"/>
+      <c r="AM12" s="96"/>
+    </row>
+    <row r="13" spans="1:39" ht="14.1" customHeight="1">
+      <c r="A13" s="96" t="s">
         <v>157</v>
       </c>
-      <c r="B13" s="98"/>
-      <c r="C13" s="98"/>
-      <c r="D13" s="98"/>
-      <c r="E13" s="98"/>
-      <c r="F13" s="98"/>
-      <c r="G13" s="98"/>
-      <c r="H13" s="98"/>
-      <c r="I13" s="98"/>
-      <c r="J13" s="98"/>
-      <c r="K13" s="98"/>
-      <c r="L13" s="98"/>
-      <c r="M13" s="98"/>
-      <c r="N13" s="98"/>
-      <c r="O13" s="98"/>
-      <c r="P13" s="98"/>
-      <c r="Q13" s="98"/>
-      <c r="R13" s="98"/>
-      <c r="S13" s="98"/>
-      <c r="T13" s="98"/>
-      <c r="U13" s="98"/>
-      <c r="V13" s="98"/>
-      <c r="W13" s="98"/>
-      <c r="X13" s="98"/>
-      <c r="Y13" s="98"/>
-      <c r="Z13" s="98"/>
-      <c r="AA13" s="98"/>
-      <c r="AB13" s="98"/>
-      <c r="AC13" s="98"/>
-      <c r="AD13" s="98"/>
-      <c r="AE13" s="98"/>
-      <c r="AF13" s="98"/>
-      <c r="AG13" s="98"/>
-      <c r="AH13" s="98"/>
-      <c r="AI13" s="98"/>
-      <c r="AJ13" s="98"/>
-      <c r="AK13" s="98"/>
-      <c r="AL13" s="98"/>
-      <c r="AM13" s="98"/>
-    </row>
-    <row r="14" spans="1:39" ht="14.15" customHeight="1">
+      <c r="B13" s="96"/>
+      <c r="C13" s="96"/>
+      <c r="D13" s="96"/>
+      <c r="E13" s="96"/>
+      <c r="F13" s="96"/>
+      <c r="G13" s="96"/>
+      <c r="H13" s="96"/>
+      <c r="I13" s="96"/>
+      <c r="J13" s="96"/>
+      <c r="K13" s="96"/>
+      <c r="L13" s="96"/>
+      <c r="M13" s="96"/>
+      <c r="N13" s="96"/>
+      <c r="O13" s="96"/>
+      <c r="P13" s="96"/>
+      <c r="Q13" s="96"/>
+      <c r="R13" s="96"/>
+      <c r="S13" s="96"/>
+      <c r="T13" s="96"/>
+      <c r="U13" s="96"/>
+      <c r="V13" s="96"/>
+      <c r="W13" s="96"/>
+      <c r="X13" s="96"/>
+      <c r="Y13" s="96"/>
+      <c r="Z13" s="96"/>
+      <c r="AA13" s="96"/>
+      <c r="AB13" s="96"/>
+      <c r="AC13" s="96"/>
+      <c r="AD13" s="96"/>
+      <c r="AE13" s="96"/>
+      <c r="AF13" s="96"/>
+      <c r="AG13" s="96"/>
+      <c r="AH13" s="96"/>
+      <c r="AI13" s="96"/>
+      <c r="AJ13" s="96"/>
+      <c r="AK13" s="96"/>
+      <c r="AL13" s="96"/>
+      <c r="AM13" s="96"/>
+    </row>
+    <row r="14" spans="1:39" ht="14.1" customHeight="1">
       <c r="A14" s="46"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
@@ -13508,7 +13488,7 @@
       <c r="AE14" s="3"/>
       <c r="AF14" s="3"/>
     </row>
-    <row r="15" spans="1:39" ht="14.15" customHeight="1">
+    <row r="15" spans="1:39" ht="14.1" customHeight="1">
       <c r="A15" s="46" t="s">
         <v>168</v>
       </c>
@@ -13541,285 +13521,285 @@
       <c r="AE15" s="3"/>
       <c r="AF15" s="3"/>
     </row>
-    <row r="16" spans="1:39" ht="14.15" customHeight="1">
-      <c r="A16" s="98" t="s">
+    <row r="16" spans="1:39" ht="14.1" customHeight="1">
+      <c r="A16" s="96" t="s">
         <v>155</v>
       </c>
-      <c r="B16" s="98"/>
-      <c r="C16" s="98"/>
-      <c r="D16" s="98"/>
-      <c r="E16" s="98"/>
-      <c r="F16" s="98" t="s">
+      <c r="B16" s="96"/>
+      <c r="C16" s="96"/>
+      <c r="D16" s="96"/>
+      <c r="E16" s="96"/>
+      <c r="F16" s="96" t="s">
         <v>158</v>
       </c>
-      <c r="G16" s="98"/>
-      <c r="H16" s="98"/>
-      <c r="I16" s="98"/>
-      <c r="J16" s="98"/>
-      <c r="K16" s="98"/>
-      <c r="L16" s="98"/>
-      <c r="M16" s="98" t="s">
+      <c r="G16" s="96"/>
+      <c r="H16" s="96"/>
+      <c r="I16" s="96"/>
+      <c r="J16" s="96"/>
+      <c r="K16" s="96"/>
+      <c r="L16" s="96"/>
+      <c r="M16" s="96" t="s">
         <v>159</v>
       </c>
-      <c r="N16" s="98"/>
-      <c r="O16" s="98"/>
-      <c r="P16" s="98"/>
-      <c r="Q16" s="98"/>
-      <c r="R16" s="98"/>
-      <c r="S16" s="98"/>
-      <c r="T16" s="98" t="s">
+      <c r="N16" s="96"/>
+      <c r="O16" s="96"/>
+      <c r="P16" s="96"/>
+      <c r="Q16" s="96"/>
+      <c r="R16" s="96"/>
+      <c r="S16" s="96"/>
+      <c r="T16" s="96" t="s">
         <v>160</v>
       </c>
-      <c r="U16" s="98"/>
-      <c r="V16" s="98"/>
-      <c r="W16" s="98"/>
-      <c r="X16" s="98"/>
-      <c r="Y16" s="98"/>
-      <c r="Z16" s="98"/>
-      <c r="AA16" s="98" t="s">
+      <c r="U16" s="96"/>
+      <c r="V16" s="96"/>
+      <c r="W16" s="96"/>
+      <c r="X16" s="96"/>
+      <c r="Y16" s="96"/>
+      <c r="Z16" s="96"/>
+      <c r="AA16" s="96" t="s">
         <v>161</v>
       </c>
-      <c r="AB16" s="98"/>
-      <c r="AC16" s="98"/>
-      <c r="AD16" s="98"/>
-      <c r="AE16" s="98"/>
-      <c r="AF16" s="98"/>
-      <c r="AG16" s="98"/>
-      <c r="AH16" s="98" t="s">
+      <c r="AB16" s="96"/>
+      <c r="AC16" s="96"/>
+      <c r="AD16" s="96"/>
+      <c r="AE16" s="96"/>
+      <c r="AF16" s="96"/>
+      <c r="AG16" s="96"/>
+      <c r="AH16" s="96" t="s">
         <v>162</v>
       </c>
-      <c r="AI16" s="98"/>
-      <c r="AJ16" s="98"/>
-      <c r="AK16" s="98"/>
-      <c r="AL16" s="98"/>
-      <c r="AM16" s="98"/>
-    </row>
-    <row r="17" spans="1:39" ht="14.15" customHeight="1">
-      <c r="A17" s="98" t="s">
+      <c r="AI16" s="96"/>
+      <c r="AJ16" s="96"/>
+      <c r="AK16" s="96"/>
+      <c r="AL16" s="96"/>
+      <c r="AM16" s="96"/>
+    </row>
+    <row r="17" spans="1:39" ht="14.1" customHeight="1">
+      <c r="A17" s="96" t="s">
         <v>156</v>
       </c>
-      <c r="B17" s="98"/>
-      <c r="C17" s="98"/>
-      <c r="D17" s="98"/>
-      <c r="E17" s="98"/>
-      <c r="F17" s="98"/>
-      <c r="G17" s="98"/>
-      <c r="H17" s="98"/>
-      <c r="I17" s="98"/>
-      <c r="J17" s="98"/>
-      <c r="K17" s="98"/>
-      <c r="L17" s="98"/>
-      <c r="M17" s="98"/>
-      <c r="N17" s="98"/>
-      <c r="O17" s="98"/>
-      <c r="P17" s="98"/>
-      <c r="Q17" s="98"/>
-      <c r="R17" s="98"/>
-      <c r="S17" s="98"/>
-      <c r="T17" s="98"/>
-      <c r="U17" s="98"/>
-      <c r="V17" s="98"/>
-      <c r="W17" s="98"/>
-      <c r="X17" s="98"/>
-      <c r="Y17" s="98"/>
-      <c r="Z17" s="98"/>
-      <c r="AA17" s="98"/>
-      <c r="AB17" s="98"/>
-      <c r="AC17" s="98"/>
-      <c r="AD17" s="98"/>
-      <c r="AE17" s="98"/>
-      <c r="AF17" s="98"/>
-      <c r="AG17" s="98"/>
-      <c r="AH17" s="98"/>
-      <c r="AI17" s="98"/>
-      <c r="AJ17" s="98"/>
-      <c r="AK17" s="98"/>
-      <c r="AL17" s="98"/>
-      <c r="AM17" s="98"/>
-    </row>
-    <row r="18" spans="1:39" ht="14.15" customHeight="1">
-      <c r="A18" s="98" t="s">
+      <c r="B17" s="96"/>
+      <c r="C17" s="96"/>
+      <c r="D17" s="96"/>
+      <c r="E17" s="96"/>
+      <c r="F17" s="96"/>
+      <c r="G17" s="96"/>
+      <c r="H17" s="96"/>
+      <c r="I17" s="96"/>
+      <c r="J17" s="96"/>
+      <c r="K17" s="96"/>
+      <c r="L17" s="96"/>
+      <c r="M17" s="96"/>
+      <c r="N17" s="96"/>
+      <c r="O17" s="96"/>
+      <c r="P17" s="96"/>
+      <c r="Q17" s="96"/>
+      <c r="R17" s="96"/>
+      <c r="S17" s="96"/>
+      <c r="T17" s="96"/>
+      <c r="U17" s="96"/>
+      <c r="V17" s="96"/>
+      <c r="W17" s="96"/>
+      <c r="X17" s="96"/>
+      <c r="Y17" s="96"/>
+      <c r="Z17" s="96"/>
+      <c r="AA17" s="96"/>
+      <c r="AB17" s="96"/>
+      <c r="AC17" s="96"/>
+      <c r="AD17" s="96"/>
+      <c r="AE17" s="96"/>
+      <c r="AF17" s="96"/>
+      <c r="AG17" s="96"/>
+      <c r="AH17" s="96"/>
+      <c r="AI17" s="96"/>
+      <c r="AJ17" s="96"/>
+      <c r="AK17" s="96"/>
+      <c r="AL17" s="96"/>
+      <c r="AM17" s="96"/>
+    </row>
+    <row r="18" spans="1:39" ht="14.1" customHeight="1">
+      <c r="A18" s="96" t="s">
         <v>157</v>
       </c>
-      <c r="B18" s="98"/>
-      <c r="C18" s="98"/>
-      <c r="D18" s="98"/>
-      <c r="E18" s="98"/>
-      <c r="F18" s="98"/>
-      <c r="G18" s="98"/>
-      <c r="H18" s="98"/>
-      <c r="I18" s="98"/>
-      <c r="J18" s="98"/>
-      <c r="K18" s="98"/>
-      <c r="L18" s="98"/>
-      <c r="M18" s="98"/>
-      <c r="N18" s="98"/>
-      <c r="O18" s="98"/>
-      <c r="P18" s="98"/>
-      <c r="Q18" s="98"/>
-      <c r="R18" s="98"/>
-      <c r="S18" s="98"/>
-      <c r="T18" s="98"/>
-      <c r="U18" s="98"/>
-      <c r="V18" s="98"/>
-      <c r="W18" s="98"/>
-      <c r="X18" s="98"/>
-      <c r="Y18" s="98"/>
-      <c r="Z18" s="98"/>
-      <c r="AA18" s="98"/>
-      <c r="AB18" s="98"/>
-      <c r="AC18" s="98"/>
-      <c r="AD18" s="98"/>
-      <c r="AE18" s="98"/>
-      <c r="AF18" s="98"/>
-      <c r="AG18" s="98"/>
-      <c r="AH18" s="98"/>
-      <c r="AI18" s="98"/>
-      <c r="AJ18" s="98"/>
-      <c r="AK18" s="98"/>
-      <c r="AL18" s="98"/>
-      <c r="AM18" s="98"/>
-    </row>
-    <row r="19" spans="1:39" ht="14.15" customHeight="1">
-      <c r="A19" s="98" t="s">
+      <c r="B18" s="96"/>
+      <c r="C18" s="96"/>
+      <c r="D18" s="96"/>
+      <c r="E18" s="96"/>
+      <c r="F18" s="96"/>
+      <c r="G18" s="96"/>
+      <c r="H18" s="96"/>
+      <c r="I18" s="96"/>
+      <c r="J18" s="96"/>
+      <c r="K18" s="96"/>
+      <c r="L18" s="96"/>
+      <c r="M18" s="96"/>
+      <c r="N18" s="96"/>
+      <c r="O18" s="96"/>
+      <c r="P18" s="96"/>
+      <c r="Q18" s="96"/>
+      <c r="R18" s="96"/>
+      <c r="S18" s="96"/>
+      <c r="T18" s="96"/>
+      <c r="U18" s="96"/>
+      <c r="V18" s="96"/>
+      <c r="W18" s="96"/>
+      <c r="X18" s="96"/>
+      <c r="Y18" s="96"/>
+      <c r="Z18" s="96"/>
+      <c r="AA18" s="96"/>
+      <c r="AB18" s="96"/>
+      <c r="AC18" s="96"/>
+      <c r="AD18" s="96"/>
+      <c r="AE18" s="96"/>
+      <c r="AF18" s="96"/>
+      <c r="AG18" s="96"/>
+      <c r="AH18" s="96"/>
+      <c r="AI18" s="96"/>
+      <c r="AJ18" s="96"/>
+      <c r="AK18" s="96"/>
+      <c r="AL18" s="96"/>
+      <c r="AM18" s="96"/>
+    </row>
+    <row r="19" spans="1:39" ht="14.1" customHeight="1">
+      <c r="A19" s="96" t="s">
         <v>155</v>
       </c>
-      <c r="B19" s="98"/>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98" t="s">
+      <c r="B19" s="96"/>
+      <c r="C19" s="96"/>
+      <c r="D19" s="96"/>
+      <c r="E19" s="96"/>
+      <c r="F19" s="96" t="s">
         <v>163</v>
       </c>
-      <c r="G19" s="98"/>
-      <c r="H19" s="98"/>
-      <c r="I19" s="98"/>
-      <c r="J19" s="98"/>
-      <c r="K19" s="98"/>
-      <c r="L19" s="98"/>
-      <c r="M19" s="98" t="s">
+      <c r="G19" s="96"/>
+      <c r="H19" s="96"/>
+      <c r="I19" s="96"/>
+      <c r="J19" s="96"/>
+      <c r="K19" s="96"/>
+      <c r="L19" s="96"/>
+      <c r="M19" s="96" t="s">
         <v>164</v>
       </c>
-      <c r="N19" s="98"/>
-      <c r="O19" s="98"/>
-      <c r="P19" s="98"/>
-      <c r="Q19" s="98"/>
-      <c r="R19" s="98"/>
-      <c r="S19" s="98"/>
-      <c r="T19" s="98" t="s">
+      <c r="N19" s="96"/>
+      <c r="O19" s="96"/>
+      <c r="P19" s="96"/>
+      <c r="Q19" s="96"/>
+      <c r="R19" s="96"/>
+      <c r="S19" s="96"/>
+      <c r="T19" s="96" t="s">
         <v>165</v>
       </c>
-      <c r="U19" s="98"/>
-      <c r="V19" s="98"/>
-      <c r="W19" s="98"/>
-      <c r="X19" s="98"/>
-      <c r="Y19" s="98"/>
-      <c r="Z19" s="98"/>
-      <c r="AA19" s="98" t="s">
+      <c r="U19" s="96"/>
+      <c r="V19" s="96"/>
+      <c r="W19" s="96"/>
+      <c r="X19" s="96"/>
+      <c r="Y19" s="96"/>
+      <c r="Z19" s="96"/>
+      <c r="AA19" s="96" t="s">
         <v>166</v>
       </c>
-      <c r="AB19" s="98"/>
-      <c r="AC19" s="98"/>
-      <c r="AD19" s="98"/>
-      <c r="AE19" s="98"/>
-      <c r="AF19" s="98"/>
-      <c r="AG19" s="98"/>
-      <c r="AH19" s="98" t="s">
+      <c r="AB19" s="96"/>
+      <c r="AC19" s="96"/>
+      <c r="AD19" s="96"/>
+      <c r="AE19" s="96"/>
+      <c r="AF19" s="96"/>
+      <c r="AG19" s="96"/>
+      <c r="AH19" s="96" t="s">
         <v>167</v>
       </c>
-      <c r="AI19" s="98"/>
-      <c r="AJ19" s="98"/>
-      <c r="AK19" s="98"/>
-      <c r="AL19" s="98"/>
-      <c r="AM19" s="98"/>
-    </row>
-    <row r="20" spans="1:39" ht="14.15" customHeight="1">
-      <c r="A20" s="98" t="s">
+      <c r="AI19" s="96"/>
+      <c r="AJ19" s="96"/>
+      <c r="AK19" s="96"/>
+      <c r="AL19" s="96"/>
+      <c r="AM19" s="96"/>
+    </row>
+    <row r="20" spans="1:39" ht="14.1" customHeight="1">
+      <c r="A20" s="96" t="s">
         <v>156</v>
       </c>
-      <c r="B20" s="98"/>
-      <c r="C20" s="98"/>
-      <c r="D20" s="98"/>
-      <c r="E20" s="98"/>
-      <c r="F20" s="98"/>
-      <c r="G20" s="98"/>
-      <c r="H20" s="98"/>
-      <c r="I20" s="98"/>
-      <c r="J20" s="98"/>
-      <c r="K20" s="98"/>
-      <c r="L20" s="98"/>
-      <c r="M20" s="98"/>
-      <c r="N20" s="98"/>
-      <c r="O20" s="98"/>
-      <c r="P20" s="98"/>
-      <c r="Q20" s="98"/>
-      <c r="R20" s="98"/>
-      <c r="S20" s="98"/>
-      <c r="T20" s="98"/>
-      <c r="U20" s="98"/>
-      <c r="V20" s="98"/>
-      <c r="W20" s="98"/>
-      <c r="X20" s="98"/>
-      <c r="Y20" s="98"/>
-      <c r="Z20" s="98"/>
-      <c r="AA20" s="98"/>
-      <c r="AB20" s="98"/>
-      <c r="AC20" s="98"/>
-      <c r="AD20" s="98"/>
-      <c r="AE20" s="98"/>
-      <c r="AF20" s="98"/>
-      <c r="AG20" s="98"/>
-      <c r="AH20" s="98"/>
-      <c r="AI20" s="98"/>
-      <c r="AJ20" s="98"/>
-      <c r="AK20" s="98"/>
-      <c r="AL20" s="98"/>
-      <c r="AM20" s="98"/>
-    </row>
-    <row r="21" spans="1:39" ht="14.15" customHeight="1">
-      <c r="A21" s="98" t="s">
+      <c r="B20" s="96"/>
+      <c r="C20" s="96"/>
+      <c r="D20" s="96"/>
+      <c r="E20" s="96"/>
+      <c r="F20" s="96"/>
+      <c r="G20" s="96"/>
+      <c r="H20" s="96"/>
+      <c r="I20" s="96"/>
+      <c r="J20" s="96"/>
+      <c r="K20" s="96"/>
+      <c r="L20" s="96"/>
+      <c r="M20" s="96"/>
+      <c r="N20" s="96"/>
+      <c r="O20" s="96"/>
+      <c r="P20" s="96"/>
+      <c r="Q20" s="96"/>
+      <c r="R20" s="96"/>
+      <c r="S20" s="96"/>
+      <c r="T20" s="96"/>
+      <c r="U20" s="96"/>
+      <c r="V20" s="96"/>
+      <c r="W20" s="96"/>
+      <c r="X20" s="96"/>
+      <c r="Y20" s="96"/>
+      <c r="Z20" s="96"/>
+      <c r="AA20" s="96"/>
+      <c r="AB20" s="96"/>
+      <c r="AC20" s="96"/>
+      <c r="AD20" s="96"/>
+      <c r="AE20" s="96"/>
+      <c r="AF20" s="96"/>
+      <c r="AG20" s="96"/>
+      <c r="AH20" s="96"/>
+      <c r="AI20" s="96"/>
+      <c r="AJ20" s="96"/>
+      <c r="AK20" s="96"/>
+      <c r="AL20" s="96"/>
+      <c r="AM20" s="96"/>
+    </row>
+    <row r="21" spans="1:39" ht="14.1" customHeight="1">
+      <c r="A21" s="96" t="s">
         <v>157</v>
       </c>
-      <c r="B21" s="98"/>
-      <c r="C21" s="98"/>
-      <c r="D21" s="98"/>
-      <c r="E21" s="98"/>
-      <c r="F21" s="98"/>
-      <c r="G21" s="98"/>
-      <c r="H21" s="98"/>
-      <c r="I21" s="98"/>
-      <c r="J21" s="98"/>
-      <c r="K21" s="98"/>
-      <c r="L21" s="98"/>
-      <c r="M21" s="98"/>
-      <c r="N21" s="98"/>
-      <c r="O21" s="98"/>
-      <c r="P21" s="98"/>
-      <c r="Q21" s="98"/>
-      <c r="R21" s="98"/>
-      <c r="S21" s="98"/>
-      <c r="T21" s="98"/>
-      <c r="U21" s="98"/>
-      <c r="V21" s="98"/>
-      <c r="W21" s="98"/>
-      <c r="X21" s="98"/>
-      <c r="Y21" s="98"/>
-      <c r="Z21" s="98"/>
-      <c r="AA21" s="98"/>
-      <c r="AB21" s="98"/>
-      <c r="AC21" s="98"/>
-      <c r="AD21" s="98"/>
-      <c r="AE21" s="98"/>
-      <c r="AF21" s="98"/>
-      <c r="AG21" s="98"/>
-      <c r="AH21" s="98"/>
-      <c r="AI21" s="98"/>
-      <c r="AJ21" s="98"/>
-      <c r="AK21" s="98"/>
-      <c r="AL21" s="98"/>
-      <c r="AM21" s="98"/>
-    </row>
-    <row r="22" spans="1:39" ht="14.15" customHeight="1">
+      <c r="B21" s="96"/>
+      <c r="C21" s="96"/>
+      <c r="D21" s="96"/>
+      <c r="E21" s="96"/>
+      <c r="F21" s="96"/>
+      <c r="G21" s="96"/>
+      <c r="H21" s="96"/>
+      <c r="I21" s="96"/>
+      <c r="J21" s="96"/>
+      <c r="K21" s="96"/>
+      <c r="L21" s="96"/>
+      <c r="M21" s="96"/>
+      <c r="N21" s="96"/>
+      <c r="O21" s="96"/>
+      <c r="P21" s="96"/>
+      <c r="Q21" s="96"/>
+      <c r="R21" s="96"/>
+      <c r="S21" s="96"/>
+      <c r="T21" s="96"/>
+      <c r="U21" s="96"/>
+      <c r="V21" s="96"/>
+      <c r="W21" s="96"/>
+      <c r="X21" s="96"/>
+      <c r="Y21" s="96"/>
+      <c r="Z21" s="96"/>
+      <c r="AA21" s="96"/>
+      <c r="AB21" s="96"/>
+      <c r="AC21" s="96"/>
+      <c r="AD21" s="96"/>
+      <c r="AE21" s="96"/>
+      <c r="AF21" s="96"/>
+      <c r="AG21" s="96"/>
+      <c r="AH21" s="96"/>
+      <c r="AI21" s="96"/>
+      <c r="AJ21" s="96"/>
+      <c r="AK21" s="96"/>
+      <c r="AL21" s="96"/>
+      <c r="AM21" s="96"/>
+    </row>
+    <row r="22" spans="1:39" ht="14.1" customHeight="1">
       <c r="A22" s="46"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
@@ -13850,7 +13830,7 @@
       <c r="AE22" s="3"/>
       <c r="AF22" s="3"/>
     </row>
-    <row r="23" spans="1:39" ht="14.15" customHeight="1">
+    <row r="23" spans="1:39" ht="14.1" customHeight="1">
       <c r="A23" s="46" t="s">
         <v>17</v>
       </c>
@@ -13883,7 +13863,7 @@
       <c r="AE23" s="3"/>
       <c r="AF23" s="3"/>
     </row>
-    <row r="24" spans="1:39" ht="14.15" customHeight="1">
+    <row r="24" spans="1:39" ht="14.1" customHeight="1">
       <c r="A24" s="46"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
@@ -13914,7 +13894,7 @@
       <c r="AE24" s="3"/>
       <c r="AF24" s="3"/>
     </row>
-    <row r="25" spans="1:39" ht="14.15" customHeight="1">
+    <row r="25" spans="1:39" ht="14.1" customHeight="1">
       <c r="A25" s="19" t="s">
         <v>169</v>
       </c>
@@ -13947,18 +13927,18 @@
       <c r="AE25" s="3"/>
       <c r="AF25" s="3"/>
     </row>
-    <row r="26" spans="1:39" s="34" customFormat="1" ht="14.15" customHeight="1">
-      <c r="A26" s="102"/>
-      <c r="B26" s="102"/>
-      <c r="C26" s="102"/>
-      <c r="D26" s="102"/>
-      <c r="E26" s="102"/>
-      <c r="F26" s="102"/>
-      <c r="G26" s="102"/>
-      <c r="H26" s="102"/>
-      <c r="I26" s="102"/>
-      <c r="J26" s="102"/>
-      <c r="K26" s="102"/>
+    <row r="26" spans="1:39" s="34" customFormat="1" ht="14.1" customHeight="1">
+      <c r="A26" s="103"/>
+      <c r="B26" s="103"/>
+      <c r="C26" s="103"/>
+      <c r="D26" s="103"/>
+      <c r="E26" s="103"/>
+      <c r="F26" s="103"/>
+      <c r="G26" s="103"/>
+      <c r="H26" s="103"/>
+      <c r="I26" s="103"/>
+      <c r="J26" s="103"/>
+      <c r="K26" s="103"/>
       <c r="L26" s="46"/>
       <c r="M26" s="46"/>
       <c r="N26" s="46"/>
@@ -13981,7 +13961,7 @@
       <c r="AE26" s="46"/>
       <c r="AF26" s="46"/>
     </row>
-    <row r="28" spans="1:39" s="34" customFormat="1" ht="14.15" customHeight="1">
+    <row r="28" spans="1:39" s="34" customFormat="1" ht="14.1" customHeight="1">
       <c r="A28" s="34" t="s">
         <v>170</v>
       </c>
@@ -14014,285 +13994,285 @@
       <c r="AE28" s="46"/>
       <c r="AF28" s="46"/>
     </row>
-    <row r="29" spans="1:39" ht="14.15" customHeight="1">
-      <c r="A29" s="98" t="s">
+    <row r="29" spans="1:39" ht="14.1" customHeight="1">
+      <c r="A29" s="96" t="s">
         <v>155</v>
       </c>
-      <c r="B29" s="98"/>
-      <c r="C29" s="98"/>
-      <c r="D29" s="98"/>
-      <c r="E29" s="98"/>
-      <c r="F29" s="98" t="s">
+      <c r="B29" s="96"/>
+      <c r="C29" s="96"/>
+      <c r="D29" s="96"/>
+      <c r="E29" s="96"/>
+      <c r="F29" s="96" t="s">
         <v>158</v>
       </c>
-      <c r="G29" s="98"/>
-      <c r="H29" s="98"/>
-      <c r="I29" s="98"/>
-      <c r="J29" s="98"/>
-      <c r="K29" s="98"/>
-      <c r="L29" s="98"/>
-      <c r="M29" s="98" t="s">
+      <c r="G29" s="96"/>
+      <c r="H29" s="96"/>
+      <c r="I29" s="96"/>
+      <c r="J29" s="96"/>
+      <c r="K29" s="96"/>
+      <c r="L29" s="96"/>
+      <c r="M29" s="96" t="s">
         <v>159</v>
       </c>
-      <c r="N29" s="98"/>
-      <c r="O29" s="98"/>
-      <c r="P29" s="98"/>
-      <c r="Q29" s="98"/>
-      <c r="R29" s="98"/>
-      <c r="S29" s="98"/>
-      <c r="T29" s="98" t="s">
+      <c r="N29" s="96"/>
+      <c r="O29" s="96"/>
+      <c r="P29" s="96"/>
+      <c r="Q29" s="96"/>
+      <c r="R29" s="96"/>
+      <c r="S29" s="96"/>
+      <c r="T29" s="96" t="s">
         <v>160</v>
       </c>
-      <c r="U29" s="98"/>
-      <c r="V29" s="98"/>
-      <c r="W29" s="98"/>
-      <c r="X29" s="98"/>
-      <c r="Y29" s="98"/>
-      <c r="Z29" s="98"/>
-      <c r="AA29" s="98" t="s">
+      <c r="U29" s="96"/>
+      <c r="V29" s="96"/>
+      <c r="W29" s="96"/>
+      <c r="X29" s="96"/>
+      <c r="Y29" s="96"/>
+      <c r="Z29" s="96"/>
+      <c r="AA29" s="96" t="s">
         <v>161</v>
       </c>
-      <c r="AB29" s="98"/>
-      <c r="AC29" s="98"/>
-      <c r="AD29" s="98"/>
-      <c r="AE29" s="98"/>
-      <c r="AF29" s="98"/>
-      <c r="AG29" s="98"/>
-      <c r="AH29" s="98" t="s">
+      <c r="AB29" s="96"/>
+      <c r="AC29" s="96"/>
+      <c r="AD29" s="96"/>
+      <c r="AE29" s="96"/>
+      <c r="AF29" s="96"/>
+      <c r="AG29" s="96"/>
+      <c r="AH29" s="96" t="s">
         <v>162</v>
       </c>
-      <c r="AI29" s="98"/>
-      <c r="AJ29" s="98"/>
-      <c r="AK29" s="98"/>
-      <c r="AL29" s="98"/>
-      <c r="AM29" s="98"/>
-    </row>
-    <row r="30" spans="1:39" ht="14.15" customHeight="1">
-      <c r="A30" s="98" t="s">
+      <c r="AI29" s="96"/>
+      <c r="AJ29" s="96"/>
+      <c r="AK29" s="96"/>
+      <c r="AL29" s="96"/>
+      <c r="AM29" s="96"/>
+    </row>
+    <row r="30" spans="1:39" ht="14.1" customHeight="1">
+      <c r="A30" s="96" t="s">
         <v>156</v>
       </c>
-      <c r="B30" s="98"/>
-      <c r="C30" s="98"/>
-      <c r="D30" s="98"/>
-      <c r="E30" s="98"/>
-      <c r="F30" s="98"/>
-      <c r="G30" s="98"/>
-      <c r="H30" s="98"/>
-      <c r="I30" s="98"/>
-      <c r="J30" s="98"/>
-      <c r="K30" s="98"/>
-      <c r="L30" s="98"/>
-      <c r="M30" s="98"/>
-      <c r="N30" s="98"/>
-      <c r="O30" s="98"/>
-      <c r="P30" s="98"/>
-      <c r="Q30" s="98"/>
-      <c r="R30" s="98"/>
-      <c r="S30" s="98"/>
-      <c r="T30" s="98"/>
-      <c r="U30" s="98"/>
-      <c r="V30" s="98"/>
-      <c r="W30" s="98"/>
-      <c r="X30" s="98"/>
-      <c r="Y30" s="98"/>
-      <c r="Z30" s="98"/>
-      <c r="AA30" s="98"/>
-      <c r="AB30" s="98"/>
-      <c r="AC30" s="98"/>
-      <c r="AD30" s="98"/>
-      <c r="AE30" s="98"/>
-      <c r="AF30" s="98"/>
-      <c r="AG30" s="98"/>
-      <c r="AH30" s="98"/>
-      <c r="AI30" s="98"/>
-      <c r="AJ30" s="98"/>
-      <c r="AK30" s="98"/>
-      <c r="AL30" s="98"/>
-      <c r="AM30" s="98"/>
-    </row>
-    <row r="31" spans="1:39" ht="14.15" customHeight="1">
-      <c r="A31" s="98" t="s">
+      <c r="B30" s="96"/>
+      <c r="C30" s="96"/>
+      <c r="D30" s="96"/>
+      <c r="E30" s="96"/>
+      <c r="F30" s="96"/>
+      <c r="G30" s="96"/>
+      <c r="H30" s="96"/>
+      <c r="I30" s="96"/>
+      <c r="J30" s="96"/>
+      <c r="K30" s="96"/>
+      <c r="L30" s="96"/>
+      <c r="M30" s="96"/>
+      <c r="N30" s="96"/>
+      <c r="O30" s="96"/>
+      <c r="P30" s="96"/>
+      <c r="Q30" s="96"/>
+      <c r="R30" s="96"/>
+      <c r="S30" s="96"/>
+      <c r="T30" s="96"/>
+      <c r="U30" s="96"/>
+      <c r="V30" s="96"/>
+      <c r="W30" s="96"/>
+      <c r="X30" s="96"/>
+      <c r="Y30" s="96"/>
+      <c r="Z30" s="96"/>
+      <c r="AA30" s="96"/>
+      <c r="AB30" s="96"/>
+      <c r="AC30" s="96"/>
+      <c r="AD30" s="96"/>
+      <c r="AE30" s="96"/>
+      <c r="AF30" s="96"/>
+      <c r="AG30" s="96"/>
+      <c r="AH30" s="96"/>
+      <c r="AI30" s="96"/>
+      <c r="AJ30" s="96"/>
+      <c r="AK30" s="96"/>
+      <c r="AL30" s="96"/>
+      <c r="AM30" s="96"/>
+    </row>
+    <row r="31" spans="1:39" ht="14.1" customHeight="1">
+      <c r="A31" s="96" t="s">
         <v>157</v>
       </c>
-      <c r="B31" s="98"/>
-      <c r="C31" s="98"/>
-      <c r="D31" s="98"/>
-      <c r="E31" s="98"/>
-      <c r="F31" s="98"/>
-      <c r="G31" s="98"/>
-      <c r="H31" s="98"/>
-      <c r="I31" s="98"/>
-      <c r="J31" s="98"/>
-      <c r="K31" s="98"/>
-      <c r="L31" s="98"/>
-      <c r="M31" s="98"/>
-      <c r="N31" s="98"/>
-      <c r="O31" s="98"/>
-      <c r="P31" s="98"/>
-      <c r="Q31" s="98"/>
-      <c r="R31" s="98"/>
-      <c r="S31" s="98"/>
-      <c r="T31" s="98"/>
-      <c r="U31" s="98"/>
-      <c r="V31" s="98"/>
-      <c r="W31" s="98"/>
-      <c r="X31" s="98"/>
-      <c r="Y31" s="98"/>
-      <c r="Z31" s="98"/>
-      <c r="AA31" s="98"/>
-      <c r="AB31" s="98"/>
-      <c r="AC31" s="98"/>
-      <c r="AD31" s="98"/>
-      <c r="AE31" s="98"/>
-      <c r="AF31" s="98"/>
-      <c r="AG31" s="98"/>
-      <c r="AH31" s="98"/>
-      <c r="AI31" s="98"/>
-      <c r="AJ31" s="98"/>
-      <c r="AK31" s="98"/>
-      <c r="AL31" s="98"/>
-      <c r="AM31" s="98"/>
-    </row>
-    <row r="32" spans="1:39" ht="14.15" customHeight="1">
-      <c r="A32" s="98" t="s">
+      <c r="B31" s="96"/>
+      <c r="C31" s="96"/>
+      <c r="D31" s="96"/>
+      <c r="E31" s="96"/>
+      <c r="F31" s="96"/>
+      <c r="G31" s="96"/>
+      <c r="H31" s="96"/>
+      <c r="I31" s="96"/>
+      <c r="J31" s="96"/>
+      <c r="K31" s="96"/>
+      <c r="L31" s="96"/>
+      <c r="M31" s="96"/>
+      <c r="N31" s="96"/>
+      <c r="O31" s="96"/>
+      <c r="P31" s="96"/>
+      <c r="Q31" s="96"/>
+      <c r="R31" s="96"/>
+      <c r="S31" s="96"/>
+      <c r="T31" s="96"/>
+      <c r="U31" s="96"/>
+      <c r="V31" s="96"/>
+      <c r="W31" s="96"/>
+      <c r="X31" s="96"/>
+      <c r="Y31" s="96"/>
+      <c r="Z31" s="96"/>
+      <c r="AA31" s="96"/>
+      <c r="AB31" s="96"/>
+      <c r="AC31" s="96"/>
+      <c r="AD31" s="96"/>
+      <c r="AE31" s="96"/>
+      <c r="AF31" s="96"/>
+      <c r="AG31" s="96"/>
+      <c r="AH31" s="96"/>
+      <c r="AI31" s="96"/>
+      <c r="AJ31" s="96"/>
+      <c r="AK31" s="96"/>
+      <c r="AL31" s="96"/>
+      <c r="AM31" s="96"/>
+    </row>
+    <row r="32" spans="1:39" ht="14.1" customHeight="1">
+      <c r="A32" s="96" t="s">
         <v>155</v>
       </c>
-      <c r="B32" s="98"/>
-      <c r="C32" s="98"/>
-      <c r="D32" s="98"/>
-      <c r="E32" s="98"/>
-      <c r="F32" s="98" t="s">
+      <c r="B32" s="96"/>
+      <c r="C32" s="96"/>
+      <c r="D32" s="96"/>
+      <c r="E32" s="96"/>
+      <c r="F32" s="96" t="s">
         <v>163</v>
       </c>
-      <c r="G32" s="98"/>
-      <c r="H32" s="98"/>
-      <c r="I32" s="98"/>
-      <c r="J32" s="98"/>
-      <c r="K32" s="98"/>
-      <c r="L32" s="98"/>
-      <c r="M32" s="98" t="s">
+      <c r="G32" s="96"/>
+      <c r="H32" s="96"/>
+      <c r="I32" s="96"/>
+      <c r="J32" s="96"/>
+      <c r="K32" s="96"/>
+      <c r="L32" s="96"/>
+      <c r="M32" s="96" t="s">
         <v>164</v>
       </c>
-      <c r="N32" s="98"/>
-      <c r="O32" s="98"/>
-      <c r="P32" s="98"/>
-      <c r="Q32" s="98"/>
-      <c r="R32" s="98"/>
-      <c r="S32" s="98"/>
-      <c r="T32" s="98" t="s">
+      <c r="N32" s="96"/>
+      <c r="O32" s="96"/>
+      <c r="P32" s="96"/>
+      <c r="Q32" s="96"/>
+      <c r="R32" s="96"/>
+      <c r="S32" s="96"/>
+      <c r="T32" s="96" t="s">
         <v>165</v>
       </c>
-      <c r="U32" s="98"/>
-      <c r="V32" s="98"/>
-      <c r="W32" s="98"/>
-      <c r="X32" s="98"/>
-      <c r="Y32" s="98"/>
-      <c r="Z32" s="98"/>
-      <c r="AA32" s="98" t="s">
+      <c r="U32" s="96"/>
+      <c r="V32" s="96"/>
+      <c r="W32" s="96"/>
+      <c r="X32" s="96"/>
+      <c r="Y32" s="96"/>
+      <c r="Z32" s="96"/>
+      <c r="AA32" s="96" t="s">
         <v>166</v>
       </c>
-      <c r="AB32" s="98"/>
-      <c r="AC32" s="98"/>
-      <c r="AD32" s="98"/>
-      <c r="AE32" s="98"/>
-      <c r="AF32" s="98"/>
-      <c r="AG32" s="98"/>
-      <c r="AH32" s="98" t="s">
+      <c r="AB32" s="96"/>
+      <c r="AC32" s="96"/>
+      <c r="AD32" s="96"/>
+      <c r="AE32" s="96"/>
+      <c r="AF32" s="96"/>
+      <c r="AG32" s="96"/>
+      <c r="AH32" s="96" t="s">
         <v>167</v>
       </c>
-      <c r="AI32" s="98"/>
-      <c r="AJ32" s="98"/>
-      <c r="AK32" s="98"/>
-      <c r="AL32" s="98"/>
-      <c r="AM32" s="98"/>
-    </row>
-    <row r="33" spans="1:39" ht="14.15" customHeight="1">
-      <c r="A33" s="98" t="s">
+      <c r="AI32" s="96"/>
+      <c r="AJ32" s="96"/>
+      <c r="AK32" s="96"/>
+      <c r="AL32" s="96"/>
+      <c r="AM32" s="96"/>
+    </row>
+    <row r="33" spans="1:39" ht="14.1" customHeight="1">
+      <c r="A33" s="96" t="s">
         <v>156</v>
       </c>
-      <c r="B33" s="98"/>
-      <c r="C33" s="98"/>
-      <c r="D33" s="98"/>
-      <c r="E33" s="98"/>
-      <c r="F33" s="98"/>
-      <c r="G33" s="98"/>
-      <c r="H33" s="98"/>
-      <c r="I33" s="98"/>
-      <c r="J33" s="98"/>
-      <c r="K33" s="98"/>
-      <c r="L33" s="98"/>
-      <c r="M33" s="98"/>
-      <c r="N33" s="98"/>
-      <c r="O33" s="98"/>
-      <c r="P33" s="98"/>
-      <c r="Q33" s="98"/>
-      <c r="R33" s="98"/>
-      <c r="S33" s="98"/>
-      <c r="T33" s="98"/>
-      <c r="U33" s="98"/>
-      <c r="V33" s="98"/>
-      <c r="W33" s="98"/>
-      <c r="X33" s="98"/>
-      <c r="Y33" s="98"/>
-      <c r="Z33" s="98"/>
-      <c r="AA33" s="98"/>
-      <c r="AB33" s="98"/>
-      <c r="AC33" s="98"/>
-      <c r="AD33" s="98"/>
-      <c r="AE33" s="98"/>
-      <c r="AF33" s="98"/>
-      <c r="AG33" s="98"/>
-      <c r="AH33" s="98"/>
-      <c r="AI33" s="98"/>
-      <c r="AJ33" s="98"/>
-      <c r="AK33" s="98"/>
-      <c r="AL33" s="98"/>
-      <c r="AM33" s="98"/>
-    </row>
-    <row r="34" spans="1:39" ht="14.15" customHeight="1">
-      <c r="A34" s="98" t="s">
+      <c r="B33" s="96"/>
+      <c r="C33" s="96"/>
+      <c r="D33" s="96"/>
+      <c r="E33" s="96"/>
+      <c r="F33" s="96"/>
+      <c r="G33" s="96"/>
+      <c r="H33" s="96"/>
+      <c r="I33" s="96"/>
+      <c r="J33" s="96"/>
+      <c r="K33" s="96"/>
+      <c r="L33" s="96"/>
+      <c r="M33" s="96"/>
+      <c r="N33" s="96"/>
+      <c r="O33" s="96"/>
+      <c r="P33" s="96"/>
+      <c r="Q33" s="96"/>
+      <c r="R33" s="96"/>
+      <c r="S33" s="96"/>
+      <c r="T33" s="96"/>
+      <c r="U33" s="96"/>
+      <c r="V33" s="96"/>
+      <c r="W33" s="96"/>
+      <c r="X33" s="96"/>
+      <c r="Y33" s="96"/>
+      <c r="Z33" s="96"/>
+      <c r="AA33" s="96"/>
+      <c r="AB33" s="96"/>
+      <c r="AC33" s="96"/>
+      <c r="AD33" s="96"/>
+      <c r="AE33" s="96"/>
+      <c r="AF33" s="96"/>
+      <c r="AG33" s="96"/>
+      <c r="AH33" s="96"/>
+      <c r="AI33" s="96"/>
+      <c r="AJ33" s="96"/>
+      <c r="AK33" s="96"/>
+      <c r="AL33" s="96"/>
+      <c r="AM33" s="96"/>
+    </row>
+    <row r="34" spans="1:39" ht="14.1" customHeight="1">
+      <c r="A34" s="96" t="s">
         <v>157</v>
       </c>
-      <c r="B34" s="98"/>
-      <c r="C34" s="98"/>
-      <c r="D34" s="98"/>
-      <c r="E34" s="98"/>
-      <c r="F34" s="98"/>
-      <c r="G34" s="98"/>
-      <c r="H34" s="98"/>
-      <c r="I34" s="98"/>
-      <c r="J34" s="98"/>
-      <c r="K34" s="98"/>
-      <c r="L34" s="98"/>
-      <c r="M34" s="98"/>
-      <c r="N34" s="98"/>
-      <c r="O34" s="98"/>
-      <c r="P34" s="98"/>
-      <c r="Q34" s="98"/>
-      <c r="R34" s="98"/>
-      <c r="S34" s="98"/>
-      <c r="T34" s="98"/>
-      <c r="U34" s="98"/>
-      <c r="V34" s="98"/>
-      <c r="W34" s="98"/>
-      <c r="X34" s="98"/>
-      <c r="Y34" s="98"/>
-      <c r="Z34" s="98"/>
-      <c r="AA34" s="98"/>
-      <c r="AB34" s="98"/>
-      <c r="AC34" s="98"/>
-      <c r="AD34" s="98"/>
-      <c r="AE34" s="98"/>
-      <c r="AF34" s="98"/>
-      <c r="AG34" s="98"/>
-      <c r="AH34" s="98"/>
-      <c r="AI34" s="98"/>
-      <c r="AJ34" s="98"/>
-      <c r="AK34" s="98"/>
-      <c r="AL34" s="98"/>
-      <c r="AM34" s="98"/>
-    </row>
-    <row r="35" spans="1:39" ht="14.15" customHeight="1">
+      <c r="B34" s="96"/>
+      <c r="C34" s="96"/>
+      <c r="D34" s="96"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="96"/>
+      <c r="G34" s="96"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="96"/>
+      <c r="J34" s="96"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="96"/>
+      <c r="M34" s="96"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="96"/>
+      <c r="P34" s="96"/>
+      <c r="Q34" s="96"/>
+      <c r="R34" s="96"/>
+      <c r="S34" s="96"/>
+      <c r="T34" s="96"/>
+      <c r="U34" s="96"/>
+      <c r="V34" s="96"/>
+      <c r="W34" s="96"/>
+      <c r="X34" s="96"/>
+      <c r="Y34" s="96"/>
+      <c r="Z34" s="96"/>
+      <c r="AA34" s="96"/>
+      <c r="AB34" s="96"/>
+      <c r="AC34" s="96"/>
+      <c r="AD34" s="96"/>
+      <c r="AE34" s="96"/>
+      <c r="AF34" s="96"/>
+      <c r="AG34" s="96"/>
+      <c r="AH34" s="96"/>
+      <c r="AI34" s="96"/>
+      <c r="AJ34" s="96"/>
+      <c r="AK34" s="96"/>
+      <c r="AL34" s="96"/>
+      <c r="AM34" s="96"/>
+    </row>
+    <row r="35" spans="1:39" ht="14.1" customHeight="1">
       <c r="A35" s="46"/>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
@@ -14323,7 +14303,7 @@
       <c r="AE35" s="3"/>
       <c r="AF35" s="3"/>
     </row>
-    <row r="36" spans="1:39" ht="14.15" customHeight="1">
+    <row r="36" spans="1:39" ht="14.1" customHeight="1">
       <c r="A36" s="46" t="s">
         <v>17</v>
       </c>
@@ -14356,7 +14336,7 @@
       <c r="AE36" s="3"/>
       <c r="AF36" s="3"/>
     </row>
-    <row r="37" spans="1:39" ht="14.15" customHeight="1">
+    <row r="37" spans="1:39" ht="14.1" customHeight="1">
       <c r="A37" s="46"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
@@ -14387,7 +14367,7 @@
       <c r="AE37" s="3"/>
       <c r="AF37" s="3"/>
     </row>
-    <row r="38" spans="1:39" ht="14.15" customHeight="1">
+    <row r="38" spans="1:39" ht="14.1" customHeight="1">
       <c r="A38" s="46"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
@@ -14418,7 +14398,7 @@
       <c r="AE38" s="3"/>
       <c r="AF38" s="3"/>
     </row>
-    <row r="39" spans="1:39" ht="14.15" customHeight="1">
+    <row r="39" spans="1:39" ht="14.1" customHeight="1">
       <c r="A39" s="46"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
@@ -14449,7 +14429,7 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
     </row>
-    <row r="40" spans="1:39" ht="14.15" customHeight="1">
+    <row r="40" spans="1:39" ht="14.1" customHeight="1">
       <c r="A40" s="46"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
@@ -14480,7 +14460,7 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
     </row>
-    <row r="41" spans="1:39" ht="14.15" customHeight="1">
+    <row r="41" spans="1:39" ht="14.1" customHeight="1">
       <c r="A41" s="46"/>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
@@ -14511,7 +14491,7 @@
       <c r="AE41" s="3"/>
       <c r="AF41" s="3"/>
     </row>
-    <row r="42" spans="1:39" ht="14.15" customHeight="1">
+    <row r="42" spans="1:39" ht="14.1" customHeight="1">
       <c r="A42" s="46"/>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
@@ -14542,7 +14522,7 @@
       <c r="AE42" s="3"/>
       <c r="AF42" s="3"/>
     </row>
-    <row r="43" spans="1:39" ht="14.15" customHeight="1">
+    <row r="43" spans="1:39" ht="14.1" customHeight="1">
       <c r="A43" s="46"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
@@ -14573,7 +14553,7 @@
       <c r="AE43" s="3"/>
       <c r="AF43" s="3"/>
     </row>
-    <row r="44" spans="1:39" ht="14.15" customHeight="1">
+    <row r="44" spans="1:39" ht="14.1" customHeight="1">
       <c r="A44" s="46"/>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -14604,7 +14584,7 @@
       <c r="AE44" s="3"/>
       <c r="AF44" s="3"/>
     </row>
-    <row r="45" spans="1:39" ht="14.15" customHeight="1">
+    <row r="45" spans="1:39" ht="14.1" customHeight="1">
       <c r="A45" s="46"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
@@ -14635,7 +14615,7 @@
       <c r="AE45" s="3"/>
       <c r="AF45" s="3"/>
     </row>
-    <row r="46" spans="1:39" ht="14.15" customHeight="1">
+    <row r="46" spans="1:39" ht="14.1" customHeight="1">
       <c r="A46" s="46"/>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
@@ -14666,7 +14646,7 @@
       <c r="AE46" s="3"/>
       <c r="AF46" s="3"/>
     </row>
-    <row r="47" spans="1:39" ht="14.15" customHeight="1">
+    <row r="47" spans="1:39" ht="14.1" customHeight="1">
       <c r="A47" s="46"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
@@ -14697,7 +14677,7 @@
       <c r="AE47" s="3"/>
       <c r="AF47" s="3"/>
     </row>
-    <row r="48" spans="1:39" ht="14.15" customHeight="1">
+    <row r="48" spans="1:39" ht="14.1" customHeight="1">
       <c r="A48" s="46"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
@@ -14728,7 +14708,7 @@
       <c r="AE48" s="3"/>
       <c r="AF48" s="3"/>
     </row>
-    <row r="49" spans="1:39" ht="14.15" customHeight="1">
+    <row r="49" spans="1:39" ht="14.1" customHeight="1">
       <c r="A49" s="46"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
@@ -14759,7 +14739,7 @@
       <c r="AE49" s="3"/>
       <c r="AF49" s="3"/>
     </row>
-    <row r="50" spans="1:39" ht="14.15" customHeight="1">
+    <row r="50" spans="1:39" ht="14.1" customHeight="1">
       <c r="A50" s="46"/>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
@@ -14790,7 +14770,7 @@
       <c r="AE50" s="3"/>
       <c r="AF50" s="3"/>
     </row>
-    <row r="51" spans="1:39" ht="14.15" customHeight="1">
+    <row r="51" spans="1:39" ht="14.1" customHeight="1">
       <c r="A51" s="46"/>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
@@ -14821,7 +14801,7 @@
       <c r="AE51" s="3"/>
       <c r="AF51" s="3"/>
     </row>
-    <row r="52" spans="1:39" ht="14.15" customHeight="1">
+    <row r="52" spans="1:39" ht="14.1" customHeight="1">
       <c r="A52" s="46"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
@@ -15129,6 +15109,95 @@
     </row>
   </sheetData>
   <mergeCells count="113">
+    <mergeCell ref="A26:K26"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="F34:L34"/>
+    <mergeCell ref="M34:S34"/>
+    <mergeCell ref="T34:Z34"/>
+    <mergeCell ref="AA34:AG34"/>
+    <mergeCell ref="AH34:AM34"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="F33:L33"/>
+    <mergeCell ref="M33:S33"/>
+    <mergeCell ref="T33:Z33"/>
+    <mergeCell ref="AA33:AG33"/>
+    <mergeCell ref="AH33:AM33"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="F32:L32"/>
+    <mergeCell ref="M32:S32"/>
+    <mergeCell ref="T32:Z32"/>
+    <mergeCell ref="AA32:AG32"/>
+    <mergeCell ref="AH32:AM32"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="F31:L31"/>
+    <mergeCell ref="M31:S31"/>
+    <mergeCell ref="T31:Z31"/>
+    <mergeCell ref="AA31:AG31"/>
+    <mergeCell ref="AH31:AM31"/>
+    <mergeCell ref="AA29:AG29"/>
+    <mergeCell ref="AH29:AM29"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="F30:L30"/>
+    <mergeCell ref="M30:S30"/>
+    <mergeCell ref="T30:Z30"/>
+    <mergeCell ref="AA30:AG30"/>
+    <mergeCell ref="AH30:AM30"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="F29:L29"/>
+    <mergeCell ref="M29:S29"/>
+    <mergeCell ref="T29:Z29"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="F21:L21"/>
+    <mergeCell ref="M21:S21"/>
+    <mergeCell ref="T21:Z21"/>
+    <mergeCell ref="AA21:AG21"/>
+    <mergeCell ref="AH21:AM21"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="F20:L20"/>
+    <mergeCell ref="M20:S20"/>
+    <mergeCell ref="T20:Z20"/>
+    <mergeCell ref="AA20:AG20"/>
+    <mergeCell ref="AH20:AM20"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="F19:L19"/>
+    <mergeCell ref="M19:S19"/>
+    <mergeCell ref="T19:Z19"/>
+    <mergeCell ref="AA19:AG19"/>
+    <mergeCell ref="AH19:AM19"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="F18:L18"/>
+    <mergeCell ref="M18:S18"/>
+    <mergeCell ref="T18:Z18"/>
+    <mergeCell ref="AA18:AG18"/>
+    <mergeCell ref="AH18:AM18"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="F17:L17"/>
+    <mergeCell ref="M17:S17"/>
+    <mergeCell ref="T17:Z17"/>
+    <mergeCell ref="AA17:AG17"/>
+    <mergeCell ref="AH17:AM17"/>
+    <mergeCell ref="T13:Z13"/>
+    <mergeCell ref="AA13:AG13"/>
+    <mergeCell ref="AH13:AM13"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="F16:L16"/>
+    <mergeCell ref="M16:S16"/>
+    <mergeCell ref="T16:Z16"/>
+    <mergeCell ref="AA16:AG16"/>
+    <mergeCell ref="AH16:AM16"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="F13:L13"/>
+    <mergeCell ref="M13:S13"/>
+    <mergeCell ref="AA9:AG9"/>
+    <mergeCell ref="M11:S11"/>
+    <mergeCell ref="T11:Z11"/>
+    <mergeCell ref="AA11:AG11"/>
+    <mergeCell ref="AH11:AM11"/>
+    <mergeCell ref="F12:L12"/>
+    <mergeCell ref="M12:S12"/>
+    <mergeCell ref="T12:Z12"/>
+    <mergeCell ref="AA12:AG12"/>
+    <mergeCell ref="AH12:AM12"/>
     <mergeCell ref="A12:E12"/>
     <mergeCell ref="M1:AL1"/>
     <mergeCell ref="A5:C5"/>
@@ -15153,95 +15222,6 @@
     <mergeCell ref="F9:L9"/>
     <mergeCell ref="M9:S9"/>
     <mergeCell ref="T9:Z9"/>
-    <mergeCell ref="AA9:AG9"/>
-    <mergeCell ref="M11:S11"/>
-    <mergeCell ref="T11:Z11"/>
-    <mergeCell ref="AA11:AG11"/>
-    <mergeCell ref="AH11:AM11"/>
-    <mergeCell ref="F12:L12"/>
-    <mergeCell ref="M12:S12"/>
-    <mergeCell ref="T12:Z12"/>
-    <mergeCell ref="AA12:AG12"/>
-    <mergeCell ref="AH12:AM12"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="F17:L17"/>
-    <mergeCell ref="M17:S17"/>
-    <mergeCell ref="T17:Z17"/>
-    <mergeCell ref="AA17:AG17"/>
-    <mergeCell ref="AH17:AM17"/>
-    <mergeCell ref="T13:Z13"/>
-    <mergeCell ref="AA13:AG13"/>
-    <mergeCell ref="AH13:AM13"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="F16:L16"/>
-    <mergeCell ref="M16:S16"/>
-    <mergeCell ref="T16:Z16"/>
-    <mergeCell ref="AA16:AG16"/>
-    <mergeCell ref="AH16:AM16"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="F13:L13"/>
-    <mergeCell ref="M13:S13"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="F19:L19"/>
-    <mergeCell ref="M19:S19"/>
-    <mergeCell ref="T19:Z19"/>
-    <mergeCell ref="AA19:AG19"/>
-    <mergeCell ref="AH19:AM19"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="F18:L18"/>
-    <mergeCell ref="M18:S18"/>
-    <mergeCell ref="T18:Z18"/>
-    <mergeCell ref="AA18:AG18"/>
-    <mergeCell ref="AH18:AM18"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="F21:L21"/>
-    <mergeCell ref="M21:S21"/>
-    <mergeCell ref="T21:Z21"/>
-    <mergeCell ref="AA21:AG21"/>
-    <mergeCell ref="AH21:AM21"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="F20:L20"/>
-    <mergeCell ref="M20:S20"/>
-    <mergeCell ref="T20:Z20"/>
-    <mergeCell ref="AA20:AG20"/>
-    <mergeCell ref="AH20:AM20"/>
-    <mergeCell ref="AH31:AM31"/>
-    <mergeCell ref="AA29:AG29"/>
-    <mergeCell ref="AH29:AM29"/>
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="F30:L30"/>
-    <mergeCell ref="M30:S30"/>
-    <mergeCell ref="T30:Z30"/>
-    <mergeCell ref="AA30:AG30"/>
-    <mergeCell ref="AH30:AM30"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="F29:L29"/>
-    <mergeCell ref="M29:S29"/>
-    <mergeCell ref="T29:Z29"/>
-    <mergeCell ref="A26:K26"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="F34:L34"/>
-    <mergeCell ref="M34:S34"/>
-    <mergeCell ref="T34:Z34"/>
-    <mergeCell ref="AA34:AG34"/>
-    <mergeCell ref="AH34:AM34"/>
-    <mergeCell ref="A33:E33"/>
-    <mergeCell ref="F33:L33"/>
-    <mergeCell ref="M33:S33"/>
-    <mergeCell ref="T33:Z33"/>
-    <mergeCell ref="AA33:AG33"/>
-    <mergeCell ref="AH33:AM33"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="F32:L32"/>
-    <mergeCell ref="M32:S32"/>
-    <mergeCell ref="T32:Z32"/>
-    <mergeCell ref="AA32:AG32"/>
-    <mergeCell ref="AH32:AM32"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="F31:L31"/>
-    <mergeCell ref="M31:S31"/>
-    <mergeCell ref="T31:Z31"/>
-    <mergeCell ref="AA31:AG31"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/wwwroot/ExcelModel/CrazyLine_PHY_sheet.xlsx
+++ b/wwwroot/ExcelModel/CrazyLine_PHY_sheet.xlsx
@@ -1,34 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\source\NX-lims Softlines Command System\wwwroot\ExcelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A88EFE9B-7892-43A3-9951-66D26C28215A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA51F920-27D9-462C-8699-6A7342BC641F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Weight" sheetId="3" r:id="rId1"/>
     <sheet name="Pilling&amp;Snagging" sheetId="16" r:id="rId2"/>
-    <sheet name="Seam Slippage" sheetId="21" r:id="rId3"/>
-    <sheet name="Zipper Strength-ASTM D2061" sheetId="23" r:id="rId4"/>
-    <sheet name="Zipper Strength-EN 16732" sheetId="24" r:id="rId5"/>
-    <sheet name="Small Part" sheetId="25" r:id="rId6"/>
-    <sheet name="Snapping &amp; Unsnapping" sheetId="26" r:id="rId7"/>
+    <sheet name="Water Repellency" sheetId="27" r:id="rId3"/>
+    <sheet name="Seam Slippage" sheetId="21" r:id="rId4"/>
+    <sheet name="Zipper Strength-ASTM D2061" sheetId="23" r:id="rId5"/>
+    <sheet name="Zipper Strength-EN 16732" sheetId="24" r:id="rId6"/>
+    <sheet name="Small Part" sheetId="25" r:id="rId7"/>
+    <sheet name="Snapping &amp; Unsnapping" sheetId="26" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="ReportNumber" localSheetId="1">'Pilling&amp;Snagging'!$M$1</definedName>
-    <definedName name="ReportNumber" localSheetId="2">'Seam Slippage'!$M$1</definedName>
-    <definedName name="ReportNumber" localSheetId="5">'Small Part'!$M$1</definedName>
-    <definedName name="ReportNumber" localSheetId="6">'Snapping &amp; Unsnapping'!$M$1</definedName>
+    <definedName name="ReportNumber" localSheetId="3">'Seam Slippage'!$M$1</definedName>
+    <definedName name="ReportNumber" localSheetId="6">'Small Part'!$M$1</definedName>
+    <definedName name="ReportNumber" localSheetId="7">'Snapping &amp; Unsnapping'!$M$1</definedName>
+    <definedName name="ReportNumber" localSheetId="2">'Water Repellency'!$M$1</definedName>
     <definedName name="ReportNumber" localSheetId="0">Weight!$J$1</definedName>
-    <definedName name="ReportNumber" localSheetId="3">'Zipper Strength-ASTM D2061'!$M$1</definedName>
-    <definedName name="ReportNumber" localSheetId="4">'Zipper Strength-EN 16732'!$M$1</definedName>
+    <definedName name="ReportNumber" localSheetId="4">'Zipper Strength-ASTM D2061'!$M$1</definedName>
+    <definedName name="ReportNumber" localSheetId="5">'Zipper Strength-EN 16732'!$M$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="194">
   <si>
     <t>Test Report Number 报告编号:</t>
   </si>
@@ -1348,6 +1350,92 @@
     <t>Snap 2</t>
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
+  <si>
+    <t>Water Repellency</t>
+  </si>
+  <si>
+    <t>Original</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>AATCC 22  Spray Rating</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Other Standard Spray Rating </t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">100 No sticking or wetting of upper surface    </t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>100/ISO 5No sticking or wetting of the specimen</t>
+  </si>
+  <si>
+    <t>90 Slight random sticking or wetting of specimen surface</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>90/ISO 4Slight random sticking or wetting the specimen face</t>
+  </si>
+  <si>
+    <t>80 Wetting of specimen face at spray points</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>80/ISO 3Wetting of specimen face at spray</t>
+  </si>
+  <si>
+    <t>70 Partial wetting of specimen face beyond the spray</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>70/ISO 2Partial wetting of the specimen face beyond</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>points</t>
+  </si>
+  <si>
+    <t>the points</t>
+  </si>
+  <si>
+    <t>50 Complete wetting of the entire specimen face beyond</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">50/ISO 1Complete wetting of the entire specimen face </t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>the spray points</t>
+  </si>
+  <si>
+    <t>beyond the spray points</t>
+  </si>
+  <si>
+    <t>0 Complete wetting of the entire face of the specimen</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>0/ISO0 Complete wetting of the entire face of specimen</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Equipment No: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>SFL-NGB-EQP-</t>
+    </r>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1356,7 +1444,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="42">
+  <fonts count="48">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1675,6 +1763,61 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1807,7 +1950,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1817,8 +1960,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1942,6 +2091,15 @@
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1996,19 +2154,13 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="22" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2027,9 +2179,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2072,33 +2221,113 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="3" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="3" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="3" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="3" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="3" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="3" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="3" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="3" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="5">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="2" xr:uid="{B926554C-D793-41B2-A366-631BCC55C3AD}"/>
+    <cellStyle name="常规 2 2" xfId="4" xr:uid="{31DF57E0-5069-4182-AB58-B4E259F0EB7E}"/>
+    <cellStyle name="常规 3" xfId="3" xr:uid="{3E9DDF7F-854F-440D-ACDA-FA5306E6D92F}"/>
     <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2387,25 +2616,25 @@
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
       <c r="I1" s="5"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="51"/>
-      <c r="V1" s="51"/>
-      <c r="W1" s="51"/>
-      <c r="X1" s="51"/>
-      <c r="Y1" s="51"/>
-      <c r="Z1" s="51"/>
-      <c r="AA1" s="51"/>
-      <c r="AB1" s="51"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="54"/>
+      <c r="R1" s="54"/>
+      <c r="S1" s="54"/>
+      <c r="T1" s="54"/>
+      <c r="U1" s="54"/>
+      <c r="V1" s="54"/>
+      <c r="W1" s="54"/>
+      <c r="X1" s="54"/>
+      <c r="Y1" s="54"/>
+      <c r="Z1" s="54"/>
+      <c r="AA1" s="54"/>
+      <c r="AB1" s="54"/>
     </row>
     <row r="2" spans="1:28">
       <c r="A2" s="8" t="s">
@@ -2437,18 +2666,18 @@
       <c r="AB2" s="3"/>
     </row>
     <row r="3" spans="1:28" ht="15.75" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
+      <c r="L3" s="71"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
@@ -2641,86 +2870,86 @@
       <c r="AB9" s="3"/>
     </row>
     <row r="10" spans="1:28" ht="16.2">
-      <c r="A10" s="60" t="s">
+      <c r="A10" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="61"/>
-      <c r="C10" s="61"/>
-      <c r="D10" s="62"/>
-      <c r="E10" s="52" t="s">
+      <c r="B10" s="64"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="65"/>
+      <c r="E10" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="53"/>
-      <c r="K10" s="53"/>
-      <c r="L10" s="53"/>
-      <c r="M10" s="53"/>
-      <c r="N10" s="53"/>
-      <c r="O10" s="53"/>
-      <c r="P10" s="53"/>
-      <c r="Q10" s="53"/>
-      <c r="R10" s="53"/>
-      <c r="S10" s="53"/>
-      <c r="T10" s="53"/>
-      <c r="U10" s="53"/>
-      <c r="V10" s="53"/>
-      <c r="W10" s="53"/>
-      <c r="X10" s="53"/>
-      <c r="Y10" s="54" t="s">
+      <c r="F10" s="56"/>
+      <c r="G10" s="56"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="56"/>
+      <c r="K10" s="56"/>
+      <c r="L10" s="56"/>
+      <c r="M10" s="56"/>
+      <c r="N10" s="56"/>
+      <c r="O10" s="56"/>
+      <c r="P10" s="56"/>
+      <c r="Q10" s="56"/>
+      <c r="R10" s="56"/>
+      <c r="S10" s="56"/>
+      <c r="T10" s="56"/>
+      <c r="U10" s="56"/>
+      <c r="V10" s="56"/>
+      <c r="W10" s="56"/>
+      <c r="X10" s="56"/>
+      <c r="Y10" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="Z10" s="55"/>
-      <c r="AA10" s="55"/>
-      <c r="AB10" s="56"/>
+      <c r="Z10" s="58"/>
+      <c r="AA10" s="58"/>
+      <c r="AB10" s="59"/>
     </row>
     <row r="11" spans="1:28">
-      <c r="A11" s="63"/>
-      <c r="B11" s="64"/>
-      <c r="C11" s="64"/>
-      <c r="D11" s="65"/>
-      <c r="E11" s="52" t="s">
+      <c r="A11" s="66"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="53"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="66"/>
-      <c r="I11" s="52" t="s">
+      <c r="F11" s="56"/>
+      <c r="G11" s="56"/>
+      <c r="H11" s="69"/>
+      <c r="I11" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="J11" s="53"/>
-      <c r="K11" s="53"/>
-      <c r="L11" s="66"/>
-      <c r="M11" s="52" t="s">
+      <c r="J11" s="56"/>
+      <c r="K11" s="56"/>
+      <c r="L11" s="69"/>
+      <c r="M11" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="N11" s="53"/>
-      <c r="O11" s="53"/>
-      <c r="P11" s="66"/>
-      <c r="Q11" s="52" t="s">
+      <c r="N11" s="56"/>
+      <c r="O11" s="56"/>
+      <c r="P11" s="69"/>
+      <c r="Q11" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="R11" s="53"/>
-      <c r="S11" s="53"/>
-      <c r="T11" s="66"/>
-      <c r="U11" s="52" t="s">
+      <c r="R11" s="56"/>
+      <c r="S11" s="56"/>
+      <c r="T11" s="69"/>
+      <c r="U11" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="V11" s="53"/>
-      <c r="W11" s="53"/>
-      <c r="X11" s="67"/>
-      <c r="Y11" s="57"/>
-      <c r="Z11" s="58"/>
-      <c r="AA11" s="58"/>
-      <c r="AB11" s="59"/>
+      <c r="V11" s="56"/>
+      <c r="W11" s="56"/>
+      <c r="X11" s="70"/>
+      <c r="Y11" s="60"/>
+      <c r="Z11" s="61"/>
+      <c r="AA11" s="61"/>
+      <c r="AB11" s="62"/>
     </row>
     <row r="12" spans="1:28">
-      <c r="A12" s="69"/>
-      <c r="B12" s="70"/>
-      <c r="C12" s="70"/>
-      <c r="D12" s="71"/>
+      <c r="A12" s="51"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="53"/>
       <c r="E12" s="1"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
@@ -2747,10 +2976,10 @@
       <c r="AB12" s="2"/>
     </row>
     <row r="13" spans="1:28">
-      <c r="A13" s="69"/>
-      <c r="B13" s="70"/>
-      <c r="C13" s="70"/>
-      <c r="D13" s="71"/>
+      <c r="A13" s="51"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="53"/>
       <c r="E13" s="1"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
@@ -2777,10 +3006,10 @@
       <c r="AB13" s="2"/>
     </row>
     <row r="14" spans="1:28">
-      <c r="A14" s="69"/>
-      <c r="B14" s="70"/>
-      <c r="C14" s="70"/>
-      <c r="D14" s="71"/>
+      <c r="A14" s="51"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="53"/>
       <c r="E14" s="1"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
@@ -2807,10 +3036,10 @@
       <c r="AB14" s="2"/>
     </row>
     <row r="15" spans="1:28">
-      <c r="A15" s="69"/>
-      <c r="B15" s="70"/>
-      <c r="C15" s="70"/>
-      <c r="D15" s="71"/>
+      <c r="A15" s="51"/>
+      <c r="B15" s="52"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="53"/>
       <c r="E15" s="1"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
@@ -2837,10 +3066,10 @@
       <c r="AB15" s="2"/>
     </row>
     <row r="16" spans="1:28">
-      <c r="A16" s="69"/>
-      <c r="B16" s="70"/>
-      <c r="C16" s="70"/>
-      <c r="D16" s="71"/>
+      <c r="A16" s="51"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="53"/>
       <c r="E16" s="1"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
@@ -3007,11 +3236,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A16:D16"/>
     <mergeCell ref="J1:AB1"/>
     <mergeCell ref="E10:X10"/>
     <mergeCell ref="Y10:AB11"/>
@@ -3022,6 +3246,11 @@
     <mergeCell ref="Q11:T11"/>
     <mergeCell ref="U11:X11"/>
     <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -3061,32 +3290,32 @@
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
-      <c r="M1" s="72"/>
-      <c r="N1" s="72"/>
-      <c r="O1" s="72"/>
-      <c r="P1" s="72"/>
-      <c r="Q1" s="72"/>
-      <c r="R1" s="72"/>
-      <c r="S1" s="72"/>
-      <c r="T1" s="72"/>
-      <c r="U1" s="72"/>
-      <c r="V1" s="72"/>
-      <c r="W1" s="72"/>
-      <c r="X1" s="72"/>
-      <c r="Y1" s="72"/>
-      <c r="Z1" s="72"/>
-      <c r="AA1" s="72"/>
-      <c r="AB1" s="72"/>
-      <c r="AC1" s="72"/>
-      <c r="AD1" s="72"/>
-      <c r="AE1" s="72"/>
-      <c r="AF1" s="72"/>
-      <c r="AG1" s="72"/>
-      <c r="AH1" s="72"/>
-      <c r="AI1" s="72"/>
-      <c r="AJ1" s="72"/>
-      <c r="AK1" s="72"/>
-      <c r="AL1" s="72"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="74"/>
+      <c r="P1" s="74"/>
+      <c r="Q1" s="74"/>
+      <c r="R1" s="74"/>
+      <c r="S1" s="74"/>
+      <c r="T1" s="74"/>
+      <c r="U1" s="74"/>
+      <c r="V1" s="74"/>
+      <c r="W1" s="74"/>
+      <c r="X1" s="74"/>
+      <c r="Y1" s="74"/>
+      <c r="Z1" s="74"/>
+      <c r="AA1" s="74"/>
+      <c r="AB1" s="74"/>
+      <c r="AC1" s="74"/>
+      <c r="AD1" s="74"/>
+      <c r="AE1" s="74"/>
+      <c r="AF1" s="74"/>
+      <c r="AG1" s="74"/>
+      <c r="AH1" s="74"/>
+      <c r="AI1" s="74"/>
+      <c r="AJ1" s="74"/>
+      <c r="AK1" s="74"/>
+      <c r="AL1" s="74"/>
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1">
       <c r="A2" s="19" t="s">
@@ -3158,8 +3387,8 @@
       <c r="A4" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="72"/>
-      <c r="E4" s="72"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
       <c r="F4" s="34" t="s">
         <v>43</v>
       </c>
@@ -3223,23 +3452,23 @@
       <c r="AK5" s="6"/>
     </row>
     <row r="6" spans="1:38" ht="15" customHeight="1">
-      <c r="A6" s="80" t="s">
+      <c r="A6" s="72" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="81"/>
       <c r="C6" s="81"/>
       <c r="D6" s="81"/>
       <c r="E6" s="81"/>
-      <c r="F6" s="79" t="s">
+      <c r="F6" s="80" t="s">
         <v>44</v>
       </c>
-      <c r="G6" s="79"/>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
-      <c r="J6" s="79"/>
-      <c r="K6" s="79"/>
-      <c r="L6" s="79"/>
-      <c r="M6" s="79"/>
+      <c r="G6" s="80"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
+      <c r="J6" s="80"/>
+      <c r="K6" s="80"/>
+      <c r="L6" s="80"/>
+      <c r="M6" s="80"/>
       <c r="N6" s="36"/>
       <c r="O6" s="36"/>
       <c r="P6" s="36"/>
@@ -3272,14 +3501,14 @@
       <c r="C7" s="81"/>
       <c r="D7" s="81"/>
       <c r="E7" s="81"/>
-      <c r="F7" s="79"/>
-      <c r="G7" s="79"/>
-      <c r="H7" s="79"/>
-      <c r="I7" s="79"/>
-      <c r="J7" s="79"/>
-      <c r="K7" s="79"/>
-      <c r="L7" s="79"/>
-      <c r="M7" s="79"/>
+      <c r="F7" s="80"/>
+      <c r="G7" s="80"/>
+      <c r="H7" s="80"/>
+      <c r="I7" s="80"/>
+      <c r="J7" s="80"/>
+      <c r="K7" s="80"/>
+      <c r="L7" s="80"/>
+      <c r="M7" s="80"/>
       <c r="N7" s="36"/>
       <c r="O7" s="36"/>
       <c r="P7" s="36"/>
@@ -3307,19 +3536,19 @@
       <c r="AL7" s="36"/>
     </row>
     <row r="8" spans="1:38" ht="21.3" customHeight="1">
-      <c r="A8" s="69"/>
-      <c r="B8" s="70"/>
-      <c r="C8" s="70"/>
-      <c r="D8" s="70"/>
-      <c r="E8" s="71"/>
-      <c r="F8" s="76"/>
-      <c r="G8" s="77"/>
-      <c r="H8" s="77"/>
-      <c r="I8" s="77"/>
-      <c r="J8" s="77"/>
-      <c r="K8" s="77"/>
-      <c r="L8" s="77"/>
-      <c r="M8" s="78"/>
+      <c r="A8" s="51"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="53"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="78"/>
+      <c r="H8" s="78"/>
+      <c r="I8" s="78"/>
+      <c r="J8" s="78"/>
+      <c r="K8" s="78"/>
+      <c r="L8" s="78"/>
+      <c r="M8" s="79"/>
       <c r="N8" s="36"/>
       <c r="O8" s="36"/>
       <c r="P8" s="36"/>
@@ -3347,19 +3576,19 @@
       <c r="AL8" s="36"/>
     </row>
     <row r="9" spans="1:38" ht="21.3" customHeight="1">
-      <c r="A9" s="69"/>
-      <c r="B9" s="70"/>
-      <c r="C9" s="70"/>
-      <c r="D9" s="70"/>
-      <c r="E9" s="71"/>
-      <c r="F9" s="76"/>
-      <c r="G9" s="77"/>
-      <c r="H9" s="77"/>
-      <c r="I9" s="77"/>
-      <c r="J9" s="77"/>
-      <c r="K9" s="77"/>
-      <c r="L9" s="77"/>
-      <c r="M9" s="78"/>
+      <c r="A9" s="51"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="78"/>
+      <c r="I9" s="78"/>
+      <c r="J9" s="78"/>
+      <c r="K9" s="78"/>
+      <c r="L9" s="78"/>
+      <c r="M9" s="79"/>
       <c r="N9" s="36"/>
       <c r="O9" s="36"/>
       <c r="P9" s="36"/>
@@ -3392,14 +3621,14 @@
       <c r="C10" s="73"/>
       <c r="D10" s="73"/>
       <c r="E10" s="73"/>
-      <c r="F10" s="79"/>
-      <c r="G10" s="79"/>
-      <c r="H10" s="79"/>
-      <c r="I10" s="79"/>
-      <c r="J10" s="79"/>
-      <c r="K10" s="79"/>
-      <c r="L10" s="79"/>
-      <c r="M10" s="79"/>
+      <c r="F10" s="80"/>
+      <c r="G10" s="80"/>
+      <c r="H10" s="80"/>
+      <c r="I10" s="80"/>
+      <c r="J10" s="80"/>
+      <c r="K10" s="80"/>
+      <c r="L10" s="80"/>
+      <c r="M10" s="80"/>
       <c r="N10" s="36"/>
       <c r="O10" s="36"/>
       <c r="P10" s="36"/>
@@ -3427,19 +3656,19 @@
       <c r="AL10" s="36"/>
     </row>
     <row r="11" spans="1:38" ht="21.3" customHeight="1">
-      <c r="A11" s="74"/>
-      <c r="B11" s="74"/>
-      <c r="C11" s="74"/>
-      <c r="D11" s="74"/>
-      <c r="E11" s="74"/>
-      <c r="F11" s="79"/>
-      <c r="G11" s="79"/>
-      <c r="H11" s="79"/>
-      <c r="I11" s="79"/>
-      <c r="J11" s="79"/>
-      <c r="K11" s="79"/>
-      <c r="L11" s="79"/>
-      <c r="M11" s="79"/>
+      <c r="A11" s="75"/>
+      <c r="B11" s="75"/>
+      <c r="C11" s="75"/>
+      <c r="D11" s="75"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="80"/>
+      <c r="G11" s="80"/>
+      <c r="H11" s="80"/>
+      <c r="I11" s="80"/>
+      <c r="J11" s="80"/>
+      <c r="K11" s="80"/>
+      <c r="L11" s="80"/>
+      <c r="M11" s="80"/>
       <c r="N11" s="36"/>
       <c r="O11" s="36"/>
       <c r="P11" s="36"/>
@@ -3576,20 +3805,20 @@
       <c r="G15" s="34"/>
       <c r="H15" s="34"/>
       <c r="I15" s="34"/>
-      <c r="J15" s="75"/>
-      <c r="K15" s="75"/>
-      <c r="L15" s="75"/>
-      <c r="M15" s="75"/>
-      <c r="N15" s="75"/>
-      <c r="O15" s="75"/>
-      <c r="P15" s="75"/>
-      <c r="Q15" s="75"/>
-      <c r="R15" s="75"/>
-      <c r="S15" s="75"/>
-      <c r="T15" s="75"/>
-      <c r="U15" s="75"/>
-      <c r="V15" s="75"/>
-      <c r="W15" s="75"/>
+      <c r="J15" s="76"/>
+      <c r="K15" s="76"/>
+      <c r="L15" s="76"/>
+      <c r="M15" s="76"/>
+      <c r="N15" s="76"/>
+      <c r="O15" s="76"/>
+      <c r="P15" s="76"/>
+      <c r="Q15" s="76"/>
+      <c r="R15" s="76"/>
+      <c r="S15" s="76"/>
+      <c r="T15" s="76"/>
+      <c r="U15" s="76"/>
+      <c r="V15" s="76"/>
+      <c r="W15" s="76"/>
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
@@ -3634,8 +3863,8 @@
       <c r="A17" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="72"/>
-      <c r="D17" s="72"/>
+      <c r="C17" s="74"/>
+      <c r="D17" s="74"/>
       <c r="E17" s="34" t="s">
         <v>54</v>
       </c>
@@ -3701,18 +3930,18 @@
       <c r="AK18" s="6"/>
     </row>
     <row r="19" spans="1:38" ht="15" customHeight="1">
-      <c r="A19" s="80" t="s">
+      <c r="A19" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="80"/>
-      <c r="C19" s="80"/>
-      <c r="D19" s="80"/>
-      <c r="E19" s="80"/>
-      <c r="F19" s="80"/>
-      <c r="G19" s="80"/>
-      <c r="H19" s="80"/>
-      <c r="I19" s="80"/>
-      <c r="J19" s="80"/>
+      <c r="B19" s="72"/>
+      <c r="C19" s="72"/>
+      <c r="D19" s="72"/>
+      <c r="E19" s="72"/>
+      <c r="F19" s="72"/>
+      <c r="G19" s="72"/>
+      <c r="H19" s="72"/>
+      <c r="I19" s="72"/>
+      <c r="J19" s="72"/>
       <c r="K19" s="73"/>
       <c r="L19" s="73"/>
       <c r="M19" s="73"/>
@@ -3743,16 +3972,16 @@
       <c r="AL19" s="73"/>
     </row>
     <row r="20" spans="1:38" ht="15" customHeight="1">
-      <c r="A20" s="80"/>
-      <c r="B20" s="80"/>
-      <c r="C20" s="80"/>
-      <c r="D20" s="80"/>
-      <c r="E20" s="80"/>
-      <c r="F20" s="80"/>
-      <c r="G20" s="80"/>
-      <c r="H20" s="80"/>
-      <c r="I20" s="80"/>
-      <c r="J20" s="80"/>
+      <c r="A20" s="72"/>
+      <c r="B20" s="72"/>
+      <c r="C20" s="72"/>
+      <c r="D20" s="72"/>
+      <c r="E20" s="72"/>
+      <c r="F20" s="72"/>
+      <c r="G20" s="72"/>
+      <c r="H20" s="72"/>
+      <c r="I20" s="72"/>
+      <c r="J20" s="72"/>
       <c r="K20" s="73"/>
       <c r="L20" s="73"/>
       <c r="M20" s="73"/>
@@ -3783,168 +4012,168 @@
       <c r="AL20" s="73"/>
     </row>
     <row r="21" spans="1:38" ht="15" customHeight="1">
-      <c r="A21" s="80" t="s">
+      <c r="A21" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="B21" s="80"/>
-      <c r="C21" s="80"/>
-      <c r="D21" s="80"/>
-      <c r="E21" s="80"/>
-      <c r="F21" s="80"/>
-      <c r="G21" s="80"/>
-      <c r="H21" s="80"/>
-      <c r="I21" s="80"/>
-      <c r="J21" s="80"/>
-      <c r="K21" s="80"/>
-      <c r="L21" s="80"/>
-      <c r="M21" s="80"/>
-      <c r="N21" s="80"/>
-      <c r="O21" s="80"/>
-      <c r="P21" s="80"/>
-      <c r="Q21" s="80"/>
-      <c r="R21" s="80"/>
-      <c r="S21" s="80"/>
-      <c r="T21" s="80"/>
-      <c r="U21" s="80"/>
-      <c r="V21" s="80"/>
-      <c r="W21" s="80"/>
-      <c r="X21" s="80"/>
-      <c r="Y21" s="80"/>
-      <c r="Z21" s="80"/>
-      <c r="AA21" s="80"/>
-      <c r="AB21" s="80"/>
-      <c r="AC21" s="80"/>
-      <c r="AD21" s="80"/>
-      <c r="AE21" s="80"/>
-      <c r="AF21" s="80"/>
-      <c r="AG21" s="80"/>
-      <c r="AH21" s="80"/>
-      <c r="AI21" s="80"/>
-      <c r="AJ21" s="80"/>
-      <c r="AK21" s="80"/>
-      <c r="AL21" s="80"/>
+      <c r="B21" s="72"/>
+      <c r="C21" s="72"/>
+      <c r="D21" s="72"/>
+      <c r="E21" s="72"/>
+      <c r="F21" s="72"/>
+      <c r="G21" s="72"/>
+      <c r="H21" s="72"/>
+      <c r="I21" s="72"/>
+      <c r="J21" s="72"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="72"/>
+      <c r="M21" s="72"/>
+      <c r="N21" s="72"/>
+      <c r="O21" s="72"/>
+      <c r="P21" s="72"/>
+      <c r="Q21" s="72"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="72"/>
+      <c r="T21" s="72"/>
+      <c r="U21" s="72"/>
+      <c r="V21" s="72"/>
+      <c r="W21" s="72"/>
+      <c r="X21" s="72"/>
+      <c r="Y21" s="72"/>
+      <c r="Z21" s="72"/>
+      <c r="AA21" s="72"/>
+      <c r="AB21" s="72"/>
+      <c r="AC21" s="72"/>
+      <c r="AD21" s="72"/>
+      <c r="AE21" s="72"/>
+      <c r="AF21" s="72"/>
+      <c r="AG21" s="72"/>
+      <c r="AH21" s="72"/>
+      <c r="AI21" s="72"/>
+      <c r="AJ21" s="72"/>
+      <c r="AK21" s="72"/>
+      <c r="AL21" s="72"/>
     </row>
     <row r="22" spans="1:38" ht="15" customHeight="1">
-      <c r="A22" s="80"/>
-      <c r="B22" s="80"/>
-      <c r="C22" s="80"/>
-      <c r="D22" s="80"/>
-      <c r="E22" s="80"/>
-      <c r="F22" s="80"/>
-      <c r="G22" s="80"/>
-      <c r="H22" s="80"/>
-      <c r="I22" s="80"/>
-      <c r="J22" s="80"/>
-      <c r="K22" s="80"/>
-      <c r="L22" s="80"/>
-      <c r="M22" s="80"/>
-      <c r="N22" s="80"/>
-      <c r="O22" s="80"/>
-      <c r="P22" s="80"/>
-      <c r="Q22" s="80"/>
-      <c r="R22" s="80"/>
-      <c r="S22" s="80"/>
-      <c r="T22" s="80"/>
-      <c r="U22" s="80"/>
-      <c r="V22" s="80"/>
-      <c r="W22" s="80"/>
-      <c r="X22" s="80"/>
-      <c r="Y22" s="80"/>
-      <c r="Z22" s="80"/>
-      <c r="AA22" s="80"/>
-      <c r="AB22" s="80"/>
-      <c r="AC22" s="80"/>
-      <c r="AD22" s="80"/>
-      <c r="AE22" s="80"/>
-      <c r="AF22" s="80"/>
-      <c r="AG22" s="80"/>
-      <c r="AH22" s="80"/>
-      <c r="AI22" s="80"/>
-      <c r="AJ22" s="80"/>
-      <c r="AK22" s="80"/>
-      <c r="AL22" s="80"/>
+      <c r="A22" s="72"/>
+      <c r="B22" s="72"/>
+      <c r="C22" s="72"/>
+      <c r="D22" s="72"/>
+      <c r="E22" s="72"/>
+      <c r="F22" s="72"/>
+      <c r="G22" s="72"/>
+      <c r="H22" s="72"/>
+      <c r="I22" s="72"/>
+      <c r="J22" s="72"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="72"/>
+      <c r="M22" s="72"/>
+      <c r="N22" s="72"/>
+      <c r="O22" s="72"/>
+      <c r="P22" s="72"/>
+      <c r="Q22" s="72"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="72"/>
+      <c r="T22" s="72"/>
+      <c r="U22" s="72"/>
+      <c r="V22" s="72"/>
+      <c r="W22" s="72"/>
+      <c r="X22" s="72"/>
+      <c r="Y22" s="72"/>
+      <c r="Z22" s="72"/>
+      <c r="AA22" s="72"/>
+      <c r="AB22" s="72"/>
+      <c r="AC22" s="72"/>
+      <c r="AD22" s="72"/>
+      <c r="AE22" s="72"/>
+      <c r="AF22" s="72"/>
+      <c r="AG22" s="72"/>
+      <c r="AH22" s="72"/>
+      <c r="AI22" s="72"/>
+      <c r="AJ22" s="72"/>
+      <c r="AK22" s="72"/>
+      <c r="AL22" s="72"/>
     </row>
     <row r="23" spans="1:38" ht="15" customHeight="1">
-      <c r="A23" s="80" t="s">
+      <c r="A23" s="72" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="80"/>
-      <c r="C23" s="80"/>
-      <c r="D23" s="80"/>
-      <c r="E23" s="80"/>
-      <c r="F23" s="80"/>
-      <c r="G23" s="80"/>
-      <c r="H23" s="80"/>
-      <c r="I23" s="80"/>
-      <c r="J23" s="80"/>
-      <c r="K23" s="80"/>
-      <c r="L23" s="80"/>
-      <c r="M23" s="80"/>
-      <c r="N23" s="80"/>
-      <c r="O23" s="80"/>
-      <c r="P23" s="80"/>
-      <c r="Q23" s="80"/>
-      <c r="R23" s="80"/>
-      <c r="S23" s="80"/>
-      <c r="T23" s="80"/>
-      <c r="U23" s="80"/>
-      <c r="V23" s="80"/>
-      <c r="W23" s="80"/>
-      <c r="X23" s="80"/>
-      <c r="Y23" s="80"/>
-      <c r="Z23" s="80"/>
-      <c r="AA23" s="80"/>
-      <c r="AB23" s="80"/>
-      <c r="AC23" s="80"/>
-      <c r="AD23" s="80"/>
-      <c r="AE23" s="80"/>
-      <c r="AF23" s="80"/>
-      <c r="AG23" s="80"/>
-      <c r="AH23" s="80"/>
-      <c r="AI23" s="80"/>
-      <c r="AJ23" s="80"/>
-      <c r="AK23" s="80"/>
-      <c r="AL23" s="80"/>
+      <c r="B23" s="72"/>
+      <c r="C23" s="72"/>
+      <c r="D23" s="72"/>
+      <c r="E23" s="72"/>
+      <c r="F23" s="72"/>
+      <c r="G23" s="72"/>
+      <c r="H23" s="72"/>
+      <c r="I23" s="72"/>
+      <c r="J23" s="72"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="72"/>
+      <c r="M23" s="72"/>
+      <c r="N23" s="72"/>
+      <c r="O23" s="72"/>
+      <c r="P23" s="72"/>
+      <c r="Q23" s="72"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="72"/>
+      <c r="T23" s="72"/>
+      <c r="U23" s="72"/>
+      <c r="V23" s="72"/>
+      <c r="W23" s="72"/>
+      <c r="X23" s="72"/>
+      <c r="Y23" s="72"/>
+      <c r="Z23" s="72"/>
+      <c r="AA23" s="72"/>
+      <c r="AB23" s="72"/>
+      <c r="AC23" s="72"/>
+      <c r="AD23" s="72"/>
+      <c r="AE23" s="72"/>
+      <c r="AF23" s="72"/>
+      <c r="AG23" s="72"/>
+      <c r="AH23" s="72"/>
+      <c r="AI23" s="72"/>
+      <c r="AJ23" s="72"/>
+      <c r="AK23" s="72"/>
+      <c r="AL23" s="72"/>
     </row>
     <row r="24" spans="1:38" ht="15" customHeight="1">
-      <c r="A24" s="80"/>
-      <c r="B24" s="80"/>
-      <c r="C24" s="80"/>
-      <c r="D24" s="80"/>
-      <c r="E24" s="80"/>
-      <c r="F24" s="80"/>
-      <c r="G24" s="80"/>
-      <c r="H24" s="80"/>
-      <c r="I24" s="80"/>
-      <c r="J24" s="80"/>
-      <c r="K24" s="80"/>
-      <c r="L24" s="80"/>
-      <c r="M24" s="80"/>
-      <c r="N24" s="80"/>
-      <c r="O24" s="80"/>
-      <c r="P24" s="80"/>
-      <c r="Q24" s="80"/>
-      <c r="R24" s="80"/>
-      <c r="S24" s="80"/>
-      <c r="T24" s="80"/>
-      <c r="U24" s="80"/>
-      <c r="V24" s="80"/>
-      <c r="W24" s="80"/>
-      <c r="X24" s="80"/>
-      <c r="Y24" s="80"/>
-      <c r="Z24" s="80"/>
-      <c r="AA24" s="80"/>
-      <c r="AB24" s="80"/>
-      <c r="AC24" s="80"/>
-      <c r="AD24" s="80"/>
-      <c r="AE24" s="80"/>
-      <c r="AF24" s="80"/>
-      <c r="AG24" s="80"/>
-      <c r="AH24" s="80"/>
-      <c r="AI24" s="80"/>
-      <c r="AJ24" s="80"/>
-      <c r="AK24" s="80"/>
-      <c r="AL24" s="80"/>
+      <c r="A24" s="72"/>
+      <c r="B24" s="72"/>
+      <c r="C24" s="72"/>
+      <c r="D24" s="72"/>
+      <c r="E24" s="72"/>
+      <c r="F24" s="72"/>
+      <c r="G24" s="72"/>
+      <c r="H24" s="72"/>
+      <c r="I24" s="72"/>
+      <c r="J24" s="72"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="72"/>
+      <c r="M24" s="72"/>
+      <c r="N24" s="72"/>
+      <c r="O24" s="72"/>
+      <c r="P24" s="72"/>
+      <c r="Q24" s="72"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="72"/>
+      <c r="T24" s="72"/>
+      <c r="U24" s="72"/>
+      <c r="V24" s="72"/>
+      <c r="W24" s="72"/>
+      <c r="X24" s="72"/>
+      <c r="Y24" s="72"/>
+      <c r="Z24" s="72"/>
+      <c r="AA24" s="72"/>
+      <c r="AB24" s="72"/>
+      <c r="AC24" s="72"/>
+      <c r="AD24" s="72"/>
+      <c r="AE24" s="72"/>
+      <c r="AF24" s="72"/>
+      <c r="AG24" s="72"/>
+      <c r="AH24" s="72"/>
+      <c r="AI24" s="72"/>
+      <c r="AJ24" s="72"/>
+      <c r="AK24" s="72"/>
+      <c r="AL24" s="72"/>
     </row>
     <row r="25" spans="1:38" ht="15" customHeight="1">
       <c r="A25" s="34"/>
@@ -5118,22 +5347,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="Y23:AE24"/>
-    <mergeCell ref="AF23:AL24"/>
-    <mergeCell ref="Y19:AE20"/>
-    <mergeCell ref="AF19:AL20"/>
-    <mergeCell ref="R23:X24"/>
-    <mergeCell ref="R21:X22"/>
-    <mergeCell ref="Y21:AE22"/>
-    <mergeCell ref="AF21:AL22"/>
-    <mergeCell ref="R19:X20"/>
-    <mergeCell ref="A23:J24"/>
-    <mergeCell ref="K23:Q24"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="A21:J22"/>
-    <mergeCell ref="K21:Q22"/>
-    <mergeCell ref="A19:J20"/>
-    <mergeCell ref="K19:Q20"/>
     <mergeCell ref="M1:AL1"/>
     <mergeCell ref="A8:E8"/>
     <mergeCell ref="A10:E10"/>
@@ -5148,6 +5361,22 @@
     <mergeCell ref="A9:E9"/>
     <mergeCell ref="H3:S3"/>
     <mergeCell ref="F9:M9"/>
+    <mergeCell ref="A23:J24"/>
+    <mergeCell ref="K23:Q24"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A21:J22"/>
+    <mergeCell ref="K21:Q22"/>
+    <mergeCell ref="A19:J20"/>
+    <mergeCell ref="K19:Q20"/>
+    <mergeCell ref="Y23:AE24"/>
+    <mergeCell ref="AF23:AL24"/>
+    <mergeCell ref="Y19:AE20"/>
+    <mergeCell ref="AF19:AL20"/>
+    <mergeCell ref="R23:X24"/>
+    <mergeCell ref="R21:X22"/>
+    <mergeCell ref="Y21:AE22"/>
+    <mergeCell ref="AF21:AL22"/>
+    <mergeCell ref="R19:X20"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -5165,6 +5394,981 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62AEB005-62B5-454C-BFA5-C6B6E8554821}">
+  <dimension ref="A1:AL30"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="2.33203125" style="105" customWidth="1"/>
+    <col min="2" max="2" width="2.5546875" style="105" customWidth="1"/>
+    <col min="3" max="7" width="2.33203125" style="105" customWidth="1"/>
+    <col min="8" max="8" width="2" style="105" customWidth="1"/>
+    <col min="9" max="31" width="2.109375" style="105" customWidth="1"/>
+    <col min="32" max="38" width="2.33203125" style="105" customWidth="1"/>
+    <col min="39" max="16384" width="8.88671875" style="105"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:38" ht="15" customHeight="1">
+      <c r="A1" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="104"/>
+      <c r="F1" s="104"/>
+      <c r="G1" s="104"/>
+      <c r="H1" s="104"/>
+      <c r="I1" s="104"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
+      <c r="V1" s="107"/>
+      <c r="W1" s="107"/>
+      <c r="X1" s="107"/>
+      <c r="Y1" s="107"/>
+      <c r="Z1" s="107"/>
+      <c r="AA1" s="107"/>
+      <c r="AB1" s="107"/>
+      <c r="AC1" s="107"/>
+      <c r="AD1" s="107"/>
+      <c r="AE1" s="107"/>
+      <c r="AF1" s="107"/>
+      <c r="AG1" s="107"/>
+      <c r="AH1" s="107"/>
+      <c r="AI1" s="107"/>
+      <c r="AJ1" s="107"/>
+      <c r="AK1" s="107"/>
+      <c r="AL1" s="107"/>
+    </row>
+    <row r="2" spans="1:38" ht="15" customHeight="1">
+      <c r="A2" s="108" t="s">
+        <v>173</v>
+      </c>
+      <c r="E2" s="104"/>
+      <c r="F2" s="104"/>
+      <c r="G2" s="104"/>
+      <c r="H2" s="104"/>
+      <c r="I2" s="104"/>
+      <c r="J2" s="104"/>
+      <c r="K2" s="104"/>
+      <c r="L2" s="109"/>
+      <c r="M2" s="109"/>
+      <c r="N2" s="109"/>
+      <c r="O2" s="109"/>
+      <c r="P2" s="109"/>
+      <c r="Q2" s="109"/>
+      <c r="R2" s="109"/>
+      <c r="S2" s="109"/>
+      <c r="T2" s="109"/>
+      <c r="AA2" s="110"/>
+      <c r="AB2" s="110"/>
+      <c r="AC2" s="110"/>
+      <c r="AD2" s="110"/>
+      <c r="AE2" s="111"/>
+      <c r="AF2" s="111"/>
+      <c r="AG2" s="111"/>
+      <c r="AH2" s="111"/>
+      <c r="AI2" s="109"/>
+      <c r="AJ2" s="109"/>
+      <c r="AK2" s="109"/>
+      <c r="AL2" s="112"/>
+    </row>
+    <row r="3" spans="1:38" ht="15" customHeight="1">
+      <c r="A3" s="113"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="113"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="113"/>
+      <c r="G3" s="113"/>
+      <c r="H3" s="113"/>
+      <c r="I3" s="113"/>
+      <c r="J3" s="113"/>
+      <c r="K3" s="113"/>
+    </row>
+    <row r="4" spans="1:38" ht="9" customHeight="1"/>
+    <row r="5" spans="1:38" ht="15" customHeight="1">
+      <c r="A5" s="114" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="6" spans="1:38" ht="15" customHeight="1">
+      <c r="A6" s="115" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="116"/>
+      <c r="C6" s="116"/>
+      <c r="D6" s="116"/>
+      <c r="E6" s="116"/>
+      <c r="F6" s="116"/>
+      <c r="G6" s="116"/>
+      <c r="H6" s="116"/>
+      <c r="I6" s="116"/>
+      <c r="J6" s="116"/>
+      <c r="K6" s="117"/>
+      <c r="L6" s="118" t="s">
+        <v>18</v>
+      </c>
+      <c r="M6" s="119"/>
+      <c r="N6" s="119"/>
+      <c r="O6" s="119"/>
+      <c r="P6" s="119"/>
+      <c r="Q6" s="119"/>
+      <c r="R6" s="119"/>
+      <c r="S6" s="119"/>
+      <c r="T6" s="119"/>
+      <c r="U6" s="119"/>
+      <c r="V6" s="119"/>
+      <c r="W6" s="119"/>
+      <c r="X6" s="119"/>
+      <c r="Y6" s="119"/>
+      <c r="Z6" s="119"/>
+      <c r="AA6" s="119"/>
+      <c r="AB6" s="119"/>
+      <c r="AC6" s="119"/>
+      <c r="AD6" s="119"/>
+      <c r="AE6" s="119"/>
+      <c r="AF6" s="119"/>
+      <c r="AG6" s="119"/>
+      <c r="AH6" s="119"/>
+      <c r="AI6" s="119"/>
+      <c r="AJ6" s="119"/>
+      <c r="AK6" s="119"/>
+      <c r="AL6" s="120"/>
+    </row>
+    <row r="7" spans="1:38" ht="13.95" customHeight="1">
+      <c r="A7" s="121"/>
+      <c r="B7" s="122"/>
+      <c r="C7" s="122"/>
+      <c r="D7" s="122"/>
+      <c r="E7" s="122"/>
+      <c r="F7" s="122"/>
+      <c r="G7" s="122"/>
+      <c r="H7" s="122"/>
+      <c r="I7" s="122"/>
+      <c r="J7" s="122"/>
+      <c r="K7" s="123"/>
+      <c r="L7" s="118">
+        <v>1</v>
+      </c>
+      <c r="M7" s="119"/>
+      <c r="N7" s="119"/>
+      <c r="O7" s="119"/>
+      <c r="P7" s="119"/>
+      <c r="Q7" s="119"/>
+      <c r="R7" s="119"/>
+      <c r="S7" s="119"/>
+      <c r="T7" s="120"/>
+      <c r="U7" s="118">
+        <v>2</v>
+      </c>
+      <c r="V7" s="119"/>
+      <c r="W7" s="119"/>
+      <c r="X7" s="119"/>
+      <c r="Y7" s="119"/>
+      <c r="Z7" s="119"/>
+      <c r="AA7" s="119"/>
+      <c r="AB7" s="119"/>
+      <c r="AC7" s="120"/>
+      <c r="AD7" s="118">
+        <v>3</v>
+      </c>
+      <c r="AE7" s="119"/>
+      <c r="AF7" s="119"/>
+      <c r="AG7" s="119"/>
+      <c r="AH7" s="119"/>
+      <c r="AI7" s="119"/>
+      <c r="AJ7" s="119"/>
+      <c r="AK7" s="119"/>
+      <c r="AL7" s="120"/>
+    </row>
+    <row r="8" spans="1:38" ht="13.95" customHeight="1">
+      <c r="A8" s="124"/>
+      <c r="B8" s="125"/>
+      <c r="C8" s="125"/>
+      <c r="D8" s="125"/>
+      <c r="E8" s="125"/>
+      <c r="F8" s="125"/>
+      <c r="G8" s="125"/>
+      <c r="H8" s="125"/>
+      <c r="I8" s="125"/>
+      <c r="J8" s="125"/>
+      <c r="K8" s="126"/>
+      <c r="L8" s="118"/>
+      <c r="M8" s="119"/>
+      <c r="N8" s="119"/>
+      <c r="O8" s="119"/>
+      <c r="P8" s="119"/>
+      <c r="Q8" s="119"/>
+      <c r="R8" s="119"/>
+      <c r="S8" s="119"/>
+      <c r="T8" s="120"/>
+      <c r="U8" s="118"/>
+      <c r="V8" s="119"/>
+      <c r="W8" s="119"/>
+      <c r="X8" s="119"/>
+      <c r="Y8" s="119"/>
+      <c r="Z8" s="119"/>
+      <c r="AA8" s="119"/>
+      <c r="AB8" s="119"/>
+      <c r="AC8" s="120"/>
+      <c r="AD8" s="118"/>
+      <c r="AE8" s="119"/>
+      <c r="AF8" s="119"/>
+      <c r="AG8" s="119"/>
+      <c r="AH8" s="119"/>
+      <c r="AI8" s="119"/>
+      <c r="AJ8" s="119"/>
+      <c r="AK8" s="119"/>
+      <c r="AL8" s="120"/>
+    </row>
+    <row r="9" spans="1:38" ht="13.95" customHeight="1">
+      <c r="A9" s="124"/>
+      <c r="B9" s="125"/>
+      <c r="C9" s="125"/>
+      <c r="D9" s="125"/>
+      <c r="E9" s="125"/>
+      <c r="F9" s="125"/>
+      <c r="G9" s="125"/>
+      <c r="H9" s="125"/>
+      <c r="I9" s="125"/>
+      <c r="J9" s="125"/>
+      <c r="K9" s="126"/>
+      <c r="L9" s="118"/>
+      <c r="M9" s="119"/>
+      <c r="N9" s="119"/>
+      <c r="O9" s="119"/>
+      <c r="P9" s="119"/>
+      <c r="Q9" s="119"/>
+      <c r="R9" s="119"/>
+      <c r="S9" s="119"/>
+      <c r="T9" s="120"/>
+      <c r="U9" s="118"/>
+      <c r="V9" s="119"/>
+      <c r="W9" s="119"/>
+      <c r="X9" s="119"/>
+      <c r="Y9" s="119"/>
+      <c r="Z9" s="119"/>
+      <c r="AA9" s="119"/>
+      <c r="AB9" s="119"/>
+      <c r="AC9" s="120"/>
+      <c r="AD9" s="118"/>
+      <c r="AE9" s="119"/>
+      <c r="AF9" s="119"/>
+      <c r="AG9" s="119"/>
+      <c r="AH9" s="119"/>
+      <c r="AI9" s="119"/>
+      <c r="AJ9" s="119"/>
+      <c r="AK9" s="119"/>
+      <c r="AL9" s="120"/>
+    </row>
+    <row r="10" spans="1:38">
+      <c r="A10" s="124"/>
+      <c r="B10" s="125"/>
+      <c r="C10" s="125"/>
+      <c r="D10" s="125"/>
+      <c r="E10" s="125"/>
+      <c r="F10" s="125"/>
+      <c r="G10" s="125"/>
+      <c r="H10" s="125"/>
+      <c r="I10" s="125"/>
+      <c r="J10" s="125"/>
+      <c r="K10" s="126"/>
+      <c r="L10" s="118"/>
+      <c r="M10" s="119"/>
+      <c r="N10" s="119"/>
+      <c r="O10" s="119"/>
+      <c r="P10" s="119"/>
+      <c r="Q10" s="119"/>
+      <c r="R10" s="119"/>
+      <c r="S10" s="119"/>
+      <c r="T10" s="120"/>
+      <c r="U10" s="118"/>
+      <c r="V10" s="119"/>
+      <c r="W10" s="119"/>
+      <c r="X10" s="119"/>
+      <c r="Y10" s="119"/>
+      <c r="Z10" s="119"/>
+      <c r="AA10" s="119"/>
+      <c r="AB10" s="119"/>
+      <c r="AC10" s="120"/>
+      <c r="AD10" s="118"/>
+      <c r="AE10" s="119"/>
+      <c r="AF10" s="119"/>
+      <c r="AG10" s="119"/>
+      <c r="AH10" s="119"/>
+      <c r="AI10" s="119"/>
+      <c r="AJ10" s="119"/>
+      <c r="AK10" s="119"/>
+      <c r="AL10" s="120"/>
+    </row>
+    <row r="11" spans="1:38" ht="9" customHeight="1"/>
+    <row r="12" spans="1:38">
+      <c r="A12" s="114" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="13" spans="1:38">
+      <c r="A13" s="115" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="116"/>
+      <c r="C13" s="116"/>
+      <c r="D13" s="116"/>
+      <c r="E13" s="116"/>
+      <c r="F13" s="116"/>
+      <c r="G13" s="116"/>
+      <c r="H13" s="116"/>
+      <c r="I13" s="116"/>
+      <c r="J13" s="116"/>
+      <c r="K13" s="117"/>
+      <c r="L13" s="118" t="s">
+        <v>18</v>
+      </c>
+      <c r="M13" s="119"/>
+      <c r="N13" s="119"/>
+      <c r="O13" s="119"/>
+      <c r="P13" s="119"/>
+      <c r="Q13" s="119"/>
+      <c r="R13" s="119"/>
+      <c r="S13" s="119"/>
+      <c r="T13" s="119"/>
+      <c r="U13" s="119"/>
+      <c r="V13" s="119"/>
+      <c r="W13" s="119"/>
+      <c r="X13" s="119"/>
+      <c r="Y13" s="119"/>
+      <c r="Z13" s="119"/>
+      <c r="AA13" s="119"/>
+      <c r="AB13" s="119"/>
+      <c r="AC13" s="119"/>
+      <c r="AD13" s="119"/>
+      <c r="AE13" s="119"/>
+      <c r="AF13" s="119"/>
+      <c r="AG13" s="119"/>
+      <c r="AH13" s="119"/>
+      <c r="AI13" s="119"/>
+      <c r="AJ13" s="119"/>
+      <c r="AK13" s="119"/>
+      <c r="AL13" s="120"/>
+    </row>
+    <row r="14" spans="1:38">
+      <c r="A14" s="121"/>
+      <c r="B14" s="122"/>
+      <c r="C14" s="122"/>
+      <c r="D14" s="122"/>
+      <c r="E14" s="122"/>
+      <c r="F14" s="122"/>
+      <c r="G14" s="122"/>
+      <c r="H14" s="122"/>
+      <c r="I14" s="122"/>
+      <c r="J14" s="122"/>
+      <c r="K14" s="123"/>
+      <c r="L14" s="118">
+        <v>1</v>
+      </c>
+      <c r="M14" s="119"/>
+      <c r="N14" s="119"/>
+      <c r="O14" s="119"/>
+      <c r="P14" s="119"/>
+      <c r="Q14" s="119"/>
+      <c r="R14" s="119"/>
+      <c r="S14" s="119"/>
+      <c r="T14" s="120"/>
+      <c r="U14" s="118">
+        <v>2</v>
+      </c>
+      <c r="V14" s="119"/>
+      <c r="W14" s="119"/>
+      <c r="X14" s="119"/>
+      <c r="Y14" s="119"/>
+      <c r="Z14" s="119"/>
+      <c r="AA14" s="119"/>
+      <c r="AB14" s="119"/>
+      <c r="AC14" s="120"/>
+      <c r="AD14" s="118">
+        <v>3</v>
+      </c>
+      <c r="AE14" s="119"/>
+      <c r="AF14" s="119"/>
+      <c r="AG14" s="119"/>
+      <c r="AH14" s="119"/>
+      <c r="AI14" s="119"/>
+      <c r="AJ14" s="119"/>
+      <c r="AK14" s="119"/>
+      <c r="AL14" s="120"/>
+    </row>
+    <row r="15" spans="1:38">
+      <c r="A15" s="124"/>
+      <c r="B15" s="125"/>
+      <c r="C15" s="125"/>
+      <c r="D15" s="125"/>
+      <c r="E15" s="125"/>
+      <c r="F15" s="125"/>
+      <c r="G15" s="125"/>
+      <c r="H15" s="125"/>
+      <c r="I15" s="125"/>
+      <c r="J15" s="125"/>
+      <c r="K15" s="126"/>
+      <c r="L15" s="118"/>
+      <c r="M15" s="119"/>
+      <c r="N15" s="119"/>
+      <c r="O15" s="119"/>
+      <c r="P15" s="119"/>
+      <c r="Q15" s="119"/>
+      <c r="R15" s="119"/>
+      <c r="S15" s="119"/>
+      <c r="T15" s="120"/>
+      <c r="U15" s="118"/>
+      <c r="V15" s="119"/>
+      <c r="W15" s="119"/>
+      <c r="X15" s="119"/>
+      <c r="Y15" s="119"/>
+      <c r="Z15" s="119"/>
+      <c r="AA15" s="119"/>
+      <c r="AB15" s="119"/>
+      <c r="AC15" s="120"/>
+      <c r="AD15" s="118"/>
+      <c r="AE15" s="119"/>
+      <c r="AF15" s="119"/>
+      <c r="AG15" s="119"/>
+      <c r="AH15" s="119"/>
+      <c r="AI15" s="119"/>
+      <c r="AJ15" s="119"/>
+      <c r="AK15" s="119"/>
+      <c r="AL15" s="120"/>
+    </row>
+    <row r="16" spans="1:38">
+      <c r="A16" s="124"/>
+      <c r="B16" s="125"/>
+      <c r="C16" s="125"/>
+      <c r="D16" s="125"/>
+      <c r="E16" s="125"/>
+      <c r="F16" s="125"/>
+      <c r="G16" s="125"/>
+      <c r="H16" s="125"/>
+      <c r="I16" s="125"/>
+      <c r="J16" s="125"/>
+      <c r="K16" s="126"/>
+      <c r="L16" s="118"/>
+      <c r="M16" s="119"/>
+      <c r="N16" s="119"/>
+      <c r="O16" s="119"/>
+      <c r="P16" s="119"/>
+      <c r="Q16" s="119"/>
+      <c r="R16" s="119"/>
+      <c r="S16" s="119"/>
+      <c r="T16" s="120"/>
+      <c r="U16" s="118"/>
+      <c r="V16" s="119"/>
+      <c r="W16" s="119"/>
+      <c r="X16" s="119"/>
+      <c r="Y16" s="119"/>
+      <c r="Z16" s="119"/>
+      <c r="AA16" s="119"/>
+      <c r="AB16" s="119"/>
+      <c r="AC16" s="120"/>
+      <c r="AD16" s="118"/>
+      <c r="AE16" s="119"/>
+      <c r="AF16" s="119"/>
+      <c r="AG16" s="119"/>
+      <c r="AH16" s="119"/>
+      <c r="AI16" s="119"/>
+      <c r="AJ16" s="119"/>
+      <c r="AK16" s="119"/>
+      <c r="AL16" s="120"/>
+    </row>
+    <row r="17" spans="1:38">
+      <c r="A17" s="124"/>
+      <c r="B17" s="125"/>
+      <c r="C17" s="125"/>
+      <c r="D17" s="125"/>
+      <c r="E17" s="125"/>
+      <c r="F17" s="125"/>
+      <c r="G17" s="125"/>
+      <c r="H17" s="125"/>
+      <c r="I17" s="125"/>
+      <c r="J17" s="125"/>
+      <c r="K17" s="126"/>
+      <c r="L17" s="118"/>
+      <c r="M17" s="119"/>
+      <c r="N17" s="119"/>
+      <c r="O17" s="119"/>
+      <c r="P17" s="119"/>
+      <c r="Q17" s="119"/>
+      <c r="R17" s="119"/>
+      <c r="S17" s="119"/>
+      <c r="T17" s="120"/>
+      <c r="U17" s="118"/>
+      <c r="V17" s="119"/>
+      <c r="W17" s="119"/>
+      <c r="X17" s="119"/>
+      <c r="Y17" s="119"/>
+      <c r="Z17" s="119"/>
+      <c r="AA17" s="119"/>
+      <c r="AB17" s="119"/>
+      <c r="AC17" s="120"/>
+      <c r="AD17" s="118"/>
+      <c r="AE17" s="119"/>
+      <c r="AF17" s="119"/>
+      <c r="AG17" s="119"/>
+      <c r="AH17" s="119"/>
+      <c r="AI17" s="119"/>
+      <c r="AJ17" s="119"/>
+      <c r="AK17" s="119"/>
+      <c r="AL17" s="120"/>
+    </row>
+    <row r="18" spans="1:38">
+      <c r="A18" s="105" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="19" spans="1:38" ht="6.6" customHeight="1"/>
+    <row r="20" spans="1:38">
+      <c r="A20" s="130" t="s">
+        <v>175</v>
+      </c>
+      <c r="B20" s="131"/>
+      <c r="C20" s="131"/>
+      <c r="D20" s="131"/>
+      <c r="E20" s="131"/>
+      <c r="F20" s="131"/>
+      <c r="G20" s="131"/>
+      <c r="H20" s="131"/>
+      <c r="I20" s="131"/>
+      <c r="J20" s="131"/>
+      <c r="K20" s="131"/>
+      <c r="L20" s="131"/>
+      <c r="M20" s="131"/>
+      <c r="N20" s="131"/>
+      <c r="O20" s="131"/>
+      <c r="P20" s="131"/>
+      <c r="Q20" s="131"/>
+      <c r="R20" s="131"/>
+      <c r="S20" s="131"/>
+      <c r="T20" s="130" t="s">
+        <v>176</v>
+      </c>
+      <c r="U20" s="131"/>
+      <c r="V20" s="131"/>
+      <c r="W20" s="131"/>
+      <c r="X20" s="131"/>
+      <c r="Y20" s="131"/>
+      <c r="Z20" s="131"/>
+      <c r="AA20" s="131"/>
+      <c r="AB20" s="131"/>
+      <c r="AC20" s="131"/>
+      <c r="AD20" s="131"/>
+      <c r="AE20" s="131"/>
+      <c r="AF20" s="131"/>
+      <c r="AG20" s="127"/>
+      <c r="AH20" s="127"/>
+      <c r="AI20" s="127"/>
+      <c r="AJ20" s="127"/>
+    </row>
+    <row r="21" spans="1:38">
+      <c r="A21" s="128" t="s">
+        <v>177</v>
+      </c>
+      <c r="B21" s="128"/>
+      <c r="C21" s="128"/>
+      <c r="D21" s="128"/>
+      <c r="E21" s="128"/>
+      <c r="F21" s="128"/>
+      <c r="G21" s="128"/>
+      <c r="H21" s="128"/>
+      <c r="I21" s="128"/>
+      <c r="J21" s="128"/>
+      <c r="K21" s="128"/>
+      <c r="L21" s="128"/>
+      <c r="M21" s="128"/>
+      <c r="N21" s="128"/>
+      <c r="O21" s="128"/>
+      <c r="P21" s="128"/>
+      <c r="Q21" s="128"/>
+      <c r="R21" s="128"/>
+      <c r="S21" s="128"/>
+      <c r="T21" s="128" t="s">
+        <v>178</v>
+      </c>
+      <c r="U21" s="128"/>
+      <c r="V21" s="128"/>
+      <c r="W21" s="128"/>
+      <c r="X21" s="128"/>
+      <c r="Y21" s="128"/>
+      <c r="Z21" s="128"/>
+      <c r="AA21" s="128"/>
+      <c r="AB21" s="128"/>
+      <c r="AC21" s="128"/>
+      <c r="AD21" s="128"/>
+      <c r="AE21" s="128"/>
+      <c r="AF21" s="128"/>
+      <c r="AG21" s="128"/>
+      <c r="AH21" s="128"/>
+      <c r="AI21" s="128"/>
+      <c r="AJ21" s="128"/>
+    </row>
+    <row r="22" spans="1:38">
+      <c r="A22" s="128" t="s">
+        <v>179</v>
+      </c>
+      <c r="B22" s="128"/>
+      <c r="C22" s="128"/>
+      <c r="D22" s="128"/>
+      <c r="E22" s="128"/>
+      <c r="F22" s="128"/>
+      <c r="G22" s="128"/>
+      <c r="H22" s="128"/>
+      <c r="I22" s="128"/>
+      <c r="J22" s="128"/>
+      <c r="K22" s="128"/>
+      <c r="L22" s="128"/>
+      <c r="M22" s="128"/>
+      <c r="N22" s="128"/>
+      <c r="O22" s="128"/>
+      <c r="P22" s="128"/>
+      <c r="Q22" s="128"/>
+      <c r="R22" s="128"/>
+      <c r="S22" s="128"/>
+      <c r="T22" s="128" t="s">
+        <v>180</v>
+      </c>
+      <c r="U22" s="128"/>
+      <c r="V22" s="128"/>
+      <c r="W22" s="128"/>
+      <c r="X22" s="128"/>
+      <c r="Y22" s="128"/>
+      <c r="Z22" s="128"/>
+      <c r="AA22" s="128"/>
+      <c r="AB22" s="128"/>
+      <c r="AC22" s="128"/>
+      <c r="AD22" s="128"/>
+      <c r="AE22" s="128"/>
+      <c r="AF22" s="128"/>
+      <c r="AG22" s="128"/>
+      <c r="AH22" s="128"/>
+      <c r="AI22" s="128"/>
+      <c r="AJ22" s="128"/>
+    </row>
+    <row r="23" spans="1:38">
+      <c r="A23" s="128" t="s">
+        <v>181</v>
+      </c>
+      <c r="B23" s="128"/>
+      <c r="C23" s="128"/>
+      <c r="D23" s="128"/>
+      <c r="E23" s="128"/>
+      <c r="F23" s="128"/>
+      <c r="G23" s="128"/>
+      <c r="H23" s="128"/>
+      <c r="I23" s="128"/>
+      <c r="J23" s="128"/>
+      <c r="K23" s="128"/>
+      <c r="L23" s="128"/>
+      <c r="M23" s="128"/>
+      <c r="N23" s="128"/>
+      <c r="O23" s="128"/>
+      <c r="P23" s="128"/>
+      <c r="Q23" s="128"/>
+      <c r="R23" s="128"/>
+      <c r="S23" s="128"/>
+      <c r="T23" s="128" t="s">
+        <v>182</v>
+      </c>
+      <c r="U23" s="128"/>
+      <c r="V23" s="128"/>
+      <c r="W23" s="128"/>
+      <c r="X23" s="128"/>
+      <c r="Y23" s="128"/>
+      <c r="Z23" s="128"/>
+      <c r="AA23" s="128"/>
+      <c r="AB23" s="128"/>
+      <c r="AC23" s="128"/>
+      <c r="AD23" s="128"/>
+      <c r="AE23" s="128"/>
+      <c r="AF23" s="128"/>
+      <c r="AG23" s="128"/>
+      <c r="AH23" s="128"/>
+      <c r="AI23" s="128"/>
+      <c r="AJ23" s="128"/>
+    </row>
+    <row r="24" spans="1:38">
+      <c r="A24" s="128" t="s">
+        <v>183</v>
+      </c>
+      <c r="B24" s="128"/>
+      <c r="C24" s="128"/>
+      <c r="D24" s="128"/>
+      <c r="E24" s="128"/>
+      <c r="F24" s="128"/>
+      <c r="G24" s="128"/>
+      <c r="H24" s="128"/>
+      <c r="I24" s="128"/>
+      <c r="J24" s="128"/>
+      <c r="K24" s="128"/>
+      <c r="L24" s="128"/>
+      <c r="M24" s="128"/>
+      <c r="N24" s="128"/>
+      <c r="O24" s="128"/>
+      <c r="P24" s="128"/>
+      <c r="Q24" s="128"/>
+      <c r="R24" s="128"/>
+      <c r="S24" s="128"/>
+      <c r="T24" s="128" t="s">
+        <v>184</v>
+      </c>
+      <c r="U24" s="128"/>
+      <c r="V24" s="128"/>
+      <c r="W24" s="128"/>
+      <c r="X24" s="128"/>
+      <c r="Y24" s="128"/>
+      <c r="Z24" s="128"/>
+      <c r="AA24" s="128"/>
+      <c r="AB24" s="128"/>
+      <c r="AC24" s="128"/>
+      <c r="AD24" s="128"/>
+      <c r="AE24" s="128"/>
+      <c r="AF24" s="128"/>
+      <c r="AG24" s="128"/>
+      <c r="AH24" s="128"/>
+      <c r="AI24" s="128"/>
+      <c r="AJ24" s="128"/>
+    </row>
+    <row r="25" spans="1:38">
+      <c r="A25" s="128" t="s">
+        <v>185</v>
+      </c>
+      <c r="B25" s="128"/>
+      <c r="C25" s="128"/>
+      <c r="D25" s="128"/>
+      <c r="E25" s="128"/>
+      <c r="F25" s="128"/>
+      <c r="G25" s="128"/>
+      <c r="H25" s="128"/>
+      <c r="I25" s="128"/>
+      <c r="J25" s="128"/>
+      <c r="K25" s="128"/>
+      <c r="L25" s="128"/>
+      <c r="M25" s="128"/>
+      <c r="N25" s="128"/>
+      <c r="O25" s="128"/>
+      <c r="P25" s="128"/>
+      <c r="Q25" s="128"/>
+      <c r="R25" s="128"/>
+      <c r="S25" s="128"/>
+      <c r="T25" s="128" t="s">
+        <v>186</v>
+      </c>
+      <c r="U25" s="128"/>
+      <c r="V25" s="128"/>
+      <c r="W25" s="128"/>
+      <c r="X25" s="128"/>
+      <c r="Y25" s="128"/>
+      <c r="Z25" s="128"/>
+      <c r="AA25" s="128"/>
+      <c r="AB25" s="128"/>
+      <c r="AC25" s="128"/>
+      <c r="AD25" s="128"/>
+      <c r="AE25" s="128"/>
+      <c r="AF25" s="128"/>
+      <c r="AG25" s="128"/>
+      <c r="AH25" s="128"/>
+      <c r="AI25" s="128"/>
+      <c r="AJ25" s="128"/>
+    </row>
+    <row r="26" spans="1:38">
+      <c r="A26" s="128" t="s">
+        <v>187</v>
+      </c>
+      <c r="B26" s="128"/>
+      <c r="C26" s="128"/>
+      <c r="D26" s="128"/>
+      <c r="E26" s="128"/>
+      <c r="F26" s="128"/>
+      <c r="G26" s="128"/>
+      <c r="H26" s="128"/>
+      <c r="I26" s="128"/>
+      <c r="J26" s="128"/>
+      <c r="K26" s="128"/>
+      <c r="L26" s="128"/>
+      <c r="M26" s="128"/>
+      <c r="N26" s="128"/>
+      <c r="O26" s="128"/>
+      <c r="P26" s="128"/>
+      <c r="Q26" s="128"/>
+      <c r="R26" s="128"/>
+      <c r="S26" s="128"/>
+      <c r="T26" s="128" t="s">
+        <v>188</v>
+      </c>
+      <c r="U26" s="128"/>
+      <c r="V26" s="128"/>
+      <c r="W26" s="128"/>
+      <c r="X26" s="128"/>
+      <c r="Y26" s="128"/>
+      <c r="Z26" s="128"/>
+      <c r="AA26" s="128"/>
+      <c r="AB26" s="128"/>
+      <c r="AC26" s="128"/>
+      <c r="AD26" s="128"/>
+      <c r="AE26" s="128"/>
+      <c r="AF26" s="128"/>
+      <c r="AG26" s="128"/>
+      <c r="AH26" s="128"/>
+      <c r="AI26" s="128"/>
+      <c r="AJ26" s="128"/>
+    </row>
+    <row r="27" spans="1:38">
+      <c r="A27" s="128" t="s">
+        <v>189</v>
+      </c>
+      <c r="B27" s="128"/>
+      <c r="C27" s="128"/>
+      <c r="D27" s="128"/>
+      <c r="E27" s="128"/>
+      <c r="F27" s="128"/>
+      <c r="G27" s="128"/>
+      <c r="H27" s="128"/>
+      <c r="I27" s="128"/>
+      <c r="J27" s="128"/>
+      <c r="K27" s="128"/>
+      <c r="L27" s="128"/>
+      <c r="M27" s="128"/>
+      <c r="N27" s="128"/>
+      <c r="O27" s="128"/>
+      <c r="P27" s="128"/>
+      <c r="Q27" s="128"/>
+      <c r="R27" s="128"/>
+      <c r="S27" s="128"/>
+      <c r="T27" s="128" t="s">
+        <v>190</v>
+      </c>
+      <c r="U27" s="128"/>
+      <c r="V27" s="128"/>
+      <c r="W27" s="128"/>
+      <c r="X27" s="128"/>
+      <c r="Y27" s="128"/>
+      <c r="Z27" s="128"/>
+      <c r="AA27" s="128"/>
+      <c r="AB27" s="128"/>
+      <c r="AC27" s="128"/>
+      <c r="AD27" s="128"/>
+      <c r="AE27" s="128"/>
+      <c r="AF27" s="128"/>
+      <c r="AG27" s="128"/>
+      <c r="AH27" s="128"/>
+      <c r="AI27" s="128"/>
+      <c r="AJ27" s="128"/>
+    </row>
+    <row r="28" spans="1:38">
+      <c r="A28" s="128" t="s">
+        <v>191</v>
+      </c>
+      <c r="B28" s="128"/>
+      <c r="C28" s="128"/>
+      <c r="D28" s="128"/>
+      <c r="E28" s="128"/>
+      <c r="F28" s="128"/>
+      <c r="G28" s="128"/>
+      <c r="H28" s="128"/>
+      <c r="I28" s="128"/>
+      <c r="J28" s="128"/>
+      <c r="K28" s="128"/>
+      <c r="L28" s="128"/>
+      <c r="M28" s="128"/>
+      <c r="N28" s="128"/>
+      <c r="O28" s="128"/>
+      <c r="P28" s="128"/>
+      <c r="Q28" s="128"/>
+      <c r="R28" s="128"/>
+      <c r="S28" s="128"/>
+      <c r="T28" s="128" t="s">
+        <v>192</v>
+      </c>
+      <c r="U28" s="128"/>
+      <c r="V28" s="128"/>
+      <c r="W28" s="128"/>
+      <c r="X28" s="128"/>
+      <c r="Y28" s="128"/>
+      <c r="Z28" s="128"/>
+      <c r="AA28" s="128"/>
+      <c r="AB28" s="128"/>
+      <c r="AC28" s="128"/>
+      <c r="AD28" s="128"/>
+      <c r="AE28" s="128"/>
+      <c r="AF28" s="128"/>
+      <c r="AG28" s="128"/>
+      <c r="AH28" s="128"/>
+      <c r="AI28" s="128"/>
+      <c r="AJ28" s="128"/>
+    </row>
+    <row r="29" spans="1:38" ht="6.6" customHeight="1"/>
+    <row r="30" spans="1:38">
+      <c r="A30" s="129" t="s">
+        <v>193</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="36">
+    <mergeCell ref="A17:K17"/>
+    <mergeCell ref="L17:T17"/>
+    <mergeCell ref="U17:AC17"/>
+    <mergeCell ref="AD17:AL17"/>
+    <mergeCell ref="A15:K15"/>
+    <mergeCell ref="L15:T15"/>
+    <mergeCell ref="U15:AC15"/>
+    <mergeCell ref="AD15:AL15"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="L16:T16"/>
+    <mergeCell ref="U16:AC16"/>
+    <mergeCell ref="AD16:AL16"/>
+    <mergeCell ref="A10:K10"/>
+    <mergeCell ref="L10:T10"/>
+    <mergeCell ref="U10:AC10"/>
+    <mergeCell ref="AD10:AL10"/>
+    <mergeCell ref="A13:K14"/>
+    <mergeCell ref="L13:AL13"/>
+    <mergeCell ref="L14:T14"/>
+    <mergeCell ref="U14:AC14"/>
+    <mergeCell ref="AD14:AL14"/>
+    <mergeCell ref="A8:K8"/>
+    <mergeCell ref="L8:T8"/>
+    <mergeCell ref="U8:AC8"/>
+    <mergeCell ref="AD8:AL8"/>
+    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="L9:T9"/>
+    <mergeCell ref="U9:AC9"/>
+    <mergeCell ref="AD9:AL9"/>
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A6:K7"/>
+    <mergeCell ref="L6:AL6"/>
+    <mergeCell ref="L7:T7"/>
+    <mergeCell ref="U7:AC7"/>
+    <mergeCell ref="AD7:AL7"/>
+  </mergeCells>
+  <phoneticPr fontId="16" type="noConversion"/>
+  <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.82677165354330695" bottom="0.98425196850393704" header="0.31496062992126" footer="0.31496062992126"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;L
+Form Code表格编号: NGB_SFL_F_7.8_OVS-PHY_0020_CS_A.0&amp;R&amp;G</oddHeader>
+    <oddFooter>&amp;L测试/日期Conducted by/Date:
+&amp;U                                                   &amp;U.&amp;C复核/日期Checked by/Date:
+&amp;U                                            &amp;U.&amp;R测试环境Test Condition:
+&amp;U                &amp;U ℃,&amp;U                 &amp;U%RH</oddFooter>
+  </headerFooter>
+  <legacyDrawingHF r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{626CC06E-9590-4323-BE24-60512668D6F0}">
   <dimension ref="A1:AN34"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
@@ -5187,32 +6391,32 @@
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
-      <c r="M1" s="72"/>
-      <c r="N1" s="72"/>
-      <c r="O1" s="72"/>
-      <c r="P1" s="72"/>
-      <c r="Q1" s="72"/>
-      <c r="R1" s="72"/>
-      <c r="S1" s="72"/>
-      <c r="T1" s="72"/>
-      <c r="U1" s="72"/>
-      <c r="V1" s="72"/>
-      <c r="W1" s="72"/>
-      <c r="X1" s="72"/>
-      <c r="Y1" s="72"/>
-      <c r="Z1" s="72"/>
-      <c r="AA1" s="72"/>
-      <c r="AB1" s="72"/>
-      <c r="AC1" s="72"/>
-      <c r="AD1" s="72"/>
-      <c r="AE1" s="72"/>
-      <c r="AF1" s="72"/>
-      <c r="AG1" s="72"/>
-      <c r="AH1" s="72"/>
-      <c r="AI1" s="72"/>
-      <c r="AJ1" s="72"/>
-      <c r="AK1" s="72"/>
-      <c r="AL1" s="72"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="74"/>
+      <c r="P1" s="74"/>
+      <c r="Q1" s="74"/>
+      <c r="R1" s="74"/>
+      <c r="S1" s="74"/>
+      <c r="T1" s="74"/>
+      <c r="U1" s="74"/>
+      <c r="V1" s="74"/>
+      <c r="W1" s="74"/>
+      <c r="X1" s="74"/>
+      <c r="Y1" s="74"/>
+      <c r="Z1" s="74"/>
+      <c r="AA1" s="74"/>
+      <c r="AB1" s="74"/>
+      <c r="AC1" s="74"/>
+      <c r="AD1" s="74"/>
+      <c r="AE1" s="74"/>
+      <c r="AF1" s="74"/>
+      <c r="AG1" s="74"/>
+      <c r="AH1" s="74"/>
+      <c r="AI1" s="74"/>
+      <c r="AJ1" s="74"/>
+      <c r="AK1" s="74"/>
+      <c r="AL1" s="74"/>
       <c r="AM1" s="33"/>
     </row>
     <row r="2" spans="1:39" ht="15" customHeight="1">
@@ -5249,17 +6453,17 @@
       <c r="AF2" s="3"/>
     </row>
     <row r="3" spans="1:39" ht="15" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
       <c r="L3" s="20"/>
       <c r="M3" s="20"/>
       <c r="N3" s="3"/>
@@ -6396,27 +7600,7 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="AI13:AL13"/>
-    <mergeCell ref="Y12:AC12"/>
-    <mergeCell ref="AD12:AH12"/>
-    <mergeCell ref="O11:S11"/>
-    <mergeCell ref="T11:X11"/>
-    <mergeCell ref="Y11:AC11"/>
-    <mergeCell ref="AI12:AL12"/>
-    <mergeCell ref="AI8:AL9"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="D12:I12"/>
-    <mergeCell ref="AD9:AH9"/>
-    <mergeCell ref="J12:N12"/>
-    <mergeCell ref="T12:X12"/>
-    <mergeCell ref="O10:S10"/>
-    <mergeCell ref="T10:X10"/>
-    <mergeCell ref="Y10:AC10"/>
-    <mergeCell ref="AD10:AH10"/>
-    <mergeCell ref="AD11:AH11"/>
-    <mergeCell ref="O12:S12"/>
-    <mergeCell ref="Y9:AC9"/>
+    <mergeCell ref="T9:X9"/>
     <mergeCell ref="M1:AL1"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="AI10:AL10"/>
@@ -6433,9 +7617,29 @@
     <mergeCell ref="J11:N11"/>
     <mergeCell ref="Y13:AC13"/>
     <mergeCell ref="AD13:AH13"/>
+    <mergeCell ref="AI8:AL9"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="D12:I12"/>
+    <mergeCell ref="AD9:AH9"/>
+    <mergeCell ref="J12:N12"/>
+    <mergeCell ref="T12:X12"/>
+    <mergeCell ref="O10:S10"/>
+    <mergeCell ref="T10:X10"/>
+    <mergeCell ref="Y10:AC10"/>
+    <mergeCell ref="AD10:AH10"/>
+    <mergeCell ref="AD11:AH11"/>
+    <mergeCell ref="O12:S12"/>
+    <mergeCell ref="Y9:AC9"/>
     <mergeCell ref="J9:N9"/>
     <mergeCell ref="O9:S9"/>
-    <mergeCell ref="T9:X9"/>
+    <mergeCell ref="AI13:AL13"/>
+    <mergeCell ref="Y12:AC12"/>
+    <mergeCell ref="AD12:AH12"/>
+    <mergeCell ref="O11:S11"/>
+    <mergeCell ref="T11:X11"/>
+    <mergeCell ref="Y11:AC11"/>
+    <mergeCell ref="AI12:AL12"/>
   </mergeCells>
   <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -6452,7 +7656,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ACC2EF5-C6BB-4CA4-98B8-CD887DC0BA25}">
   <dimension ref="A1:AM37"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
@@ -6475,32 +7679,32 @@
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
-      <c r="M1" s="72"/>
-      <c r="N1" s="72"/>
-      <c r="O1" s="72"/>
-      <c r="P1" s="72"/>
-      <c r="Q1" s="72"/>
-      <c r="R1" s="72"/>
-      <c r="S1" s="72"/>
-      <c r="T1" s="72"/>
-      <c r="U1" s="72"/>
-      <c r="V1" s="72"/>
-      <c r="W1" s="72"/>
-      <c r="X1" s="72"/>
-      <c r="Y1" s="72"/>
-      <c r="Z1" s="72"/>
-      <c r="AA1" s="72"/>
-      <c r="AB1" s="72"/>
-      <c r="AC1" s="72"/>
-      <c r="AD1" s="72"/>
-      <c r="AE1" s="72"/>
-      <c r="AF1" s="72"/>
-      <c r="AG1" s="72"/>
-      <c r="AH1" s="72"/>
-      <c r="AI1" s="72"/>
-      <c r="AJ1" s="72"/>
-      <c r="AK1" s="72"/>
-      <c r="AL1" s="72"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="74"/>
+      <c r="P1" s="74"/>
+      <c r="Q1" s="74"/>
+      <c r="R1" s="74"/>
+      <c r="S1" s="74"/>
+      <c r="T1" s="74"/>
+      <c r="U1" s="74"/>
+      <c r="V1" s="74"/>
+      <c r="W1" s="74"/>
+      <c r="X1" s="74"/>
+      <c r="Y1" s="74"/>
+      <c r="Z1" s="74"/>
+      <c r="AA1" s="74"/>
+      <c r="AB1" s="74"/>
+      <c r="AC1" s="74"/>
+      <c r="AD1" s="74"/>
+      <c r="AE1" s="74"/>
+      <c r="AF1" s="74"/>
+      <c r="AG1" s="74"/>
+      <c r="AH1" s="74"/>
+      <c r="AI1" s="74"/>
+      <c r="AJ1" s="74"/>
+      <c r="AK1" s="74"/>
+      <c r="AL1" s="74"/>
       <c r="AM1" s="33"/>
     </row>
     <row r="2" spans="1:39" ht="15" customHeight="1">
@@ -6536,17 +7740,17 @@
       <c r="AF2" s="3"/>
     </row>
     <row r="3" spans="1:39" ht="15" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
       <c r="L3" s="20"/>
       <c r="M3" s="20"/>
       <c r="N3" s="45" t="s">
@@ -7783,7 +8987,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05ADACB2-95B1-43B0-BEDC-E6A99EE22ABB}">
   <dimension ref="A1:AM68"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
@@ -7806,32 +9010,32 @@
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
-      <c r="M1" s="72"/>
-      <c r="N1" s="72"/>
-      <c r="O1" s="72"/>
-      <c r="P1" s="72"/>
-      <c r="Q1" s="72"/>
-      <c r="R1" s="72"/>
-      <c r="S1" s="72"/>
-      <c r="T1" s="72"/>
-      <c r="U1" s="72"/>
-      <c r="V1" s="72"/>
-      <c r="W1" s="72"/>
-      <c r="X1" s="72"/>
-      <c r="Y1" s="72"/>
-      <c r="Z1" s="72"/>
-      <c r="AA1" s="72"/>
-      <c r="AB1" s="72"/>
-      <c r="AC1" s="72"/>
-      <c r="AD1" s="72"/>
-      <c r="AE1" s="72"/>
-      <c r="AF1" s="72"/>
-      <c r="AG1" s="72"/>
-      <c r="AH1" s="72"/>
-      <c r="AI1" s="72"/>
-      <c r="AJ1" s="72"/>
-      <c r="AK1" s="72"/>
-      <c r="AL1" s="72"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="74"/>
+      <c r="P1" s="74"/>
+      <c r="Q1" s="74"/>
+      <c r="R1" s="74"/>
+      <c r="S1" s="74"/>
+      <c r="T1" s="74"/>
+      <c r="U1" s="74"/>
+      <c r="V1" s="74"/>
+      <c r="W1" s="74"/>
+      <c r="X1" s="74"/>
+      <c r="Y1" s="74"/>
+      <c r="Z1" s="74"/>
+      <c r="AA1" s="74"/>
+      <c r="AB1" s="74"/>
+      <c r="AC1" s="74"/>
+      <c r="AD1" s="74"/>
+      <c r="AE1" s="74"/>
+      <c r="AF1" s="74"/>
+      <c r="AG1" s="74"/>
+      <c r="AH1" s="74"/>
+      <c r="AI1" s="74"/>
+      <c r="AJ1" s="74"/>
+      <c r="AK1" s="74"/>
+      <c r="AL1" s="74"/>
       <c r="AM1" s="33"/>
     </row>
     <row r="2" spans="1:39" ht="15" customHeight="1">
@@ -7867,17 +9071,17 @@
       <c r="AF2" s="3"/>
     </row>
     <row r="3" spans="1:39" ht="15" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
       <c r="L3" s="20"/>
       <c r="M3" s="20"/>
       <c r="N3" s="16" t="s">
@@ -10288,7 +11492,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{309B97D2-0661-4F44-8203-7296258BC5D2}">
   <dimension ref="A1:AM60"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
@@ -10311,60 +11515,60 @@
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
-      <c r="M1" s="72"/>
-      <c r="N1" s="72"/>
-      <c r="O1" s="72"/>
-      <c r="P1" s="72"/>
-      <c r="Q1" s="72"/>
-      <c r="R1" s="72"/>
-      <c r="S1" s="72"/>
-      <c r="T1" s="72"/>
-      <c r="U1" s="72"/>
-      <c r="V1" s="72"/>
-      <c r="W1" s="72"/>
-      <c r="X1" s="72"/>
-      <c r="Y1" s="72"/>
-      <c r="Z1" s="72"/>
-      <c r="AA1" s="72"/>
-      <c r="AB1" s="72"/>
-      <c r="AC1" s="72"/>
-      <c r="AD1" s="72"/>
-      <c r="AE1" s="72"/>
-      <c r="AF1" s="72"/>
-      <c r="AG1" s="72"/>
-      <c r="AH1" s="72"/>
-      <c r="AI1" s="72"/>
-      <c r="AJ1" s="72"/>
-      <c r="AK1" s="72"/>
-      <c r="AL1" s="72"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="74"/>
+      <c r="P1" s="74"/>
+      <c r="Q1" s="74"/>
+      <c r="R1" s="74"/>
+      <c r="S1" s="74"/>
+      <c r="T1" s="74"/>
+      <c r="U1" s="74"/>
+      <c r="V1" s="74"/>
+      <c r="W1" s="74"/>
+      <c r="X1" s="74"/>
+      <c r="Y1" s="74"/>
+      <c r="Z1" s="74"/>
+      <c r="AA1" s="74"/>
+      <c r="AB1" s="74"/>
+      <c r="AC1" s="74"/>
+      <c r="AD1" s="74"/>
+      <c r="AE1" s="74"/>
+      <c r="AF1" s="74"/>
+      <c r="AG1" s="74"/>
+      <c r="AH1" s="74"/>
+      <c r="AI1" s="74"/>
+      <c r="AJ1" s="74"/>
+      <c r="AK1" s="74"/>
+      <c r="AL1" s="74"/>
       <c r="AM1" s="33"/>
     </row>
     <row r="2" spans="1:39" ht="15" customHeight="1">
-      <c r="A2" s="98" t="s">
+      <c r="A2" s="101" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="98"/>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
-      <c r="O2" s="98"/>
-      <c r="P2" s="98"/>
-      <c r="Q2" s="98"/>
-      <c r="R2" s="98"/>
-      <c r="S2" s="98"/>
-      <c r="T2" s="98"/>
-      <c r="U2" s="98"/>
-      <c r="V2" s="98"/>
-      <c r="W2" s="98"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="101"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="101"/>
+      <c r="L2" s="101"/>
+      <c r="M2" s="101"/>
+      <c r="N2" s="101"/>
+      <c r="O2" s="101"/>
+      <c r="P2" s="101"/>
+      <c r="Q2" s="101"/>
+      <c r="R2" s="101"/>
+      <c r="S2" s="101"/>
+      <c r="T2" s="101"/>
+      <c r="U2" s="101"/>
+      <c r="V2" s="101"/>
+      <c r="W2" s="101"/>
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
@@ -10525,39 +11729,39 @@
       <c r="J7" s="86"/>
       <c r="K7" s="86"/>
       <c r="L7" s="86"/>
-      <c r="M7" s="96" t="s">
+      <c r="M7" s="98" t="s">
         <v>115</v>
       </c>
-      <c r="N7" s="97"/>
-      <c r="O7" s="97"/>
-      <c r="P7" s="97"/>
-      <c r="Q7" s="97"/>
-      <c r="R7" s="97"/>
-      <c r="S7" s="97"/>
-      <c r="T7" s="97"/>
-      <c r="U7" s="97"/>
-      <c r="V7" s="96" t="s">
+      <c r="N7" s="99"/>
+      <c r="O7" s="99"/>
+      <c r="P7" s="99"/>
+      <c r="Q7" s="99"/>
+      <c r="R7" s="99"/>
+      <c r="S7" s="99"/>
+      <c r="T7" s="99"/>
+      <c r="U7" s="99"/>
+      <c r="V7" s="98" t="s">
         <v>116</v>
       </c>
-      <c r="W7" s="97"/>
-      <c r="X7" s="97"/>
-      <c r="Y7" s="97"/>
-      <c r="Z7" s="97"/>
-      <c r="AA7" s="97"/>
-      <c r="AB7" s="97"/>
-      <c r="AC7" s="97"/>
-      <c r="AD7" s="97"/>
-      <c r="AE7" s="96" t="s">
+      <c r="W7" s="99"/>
+      <c r="X7" s="99"/>
+      <c r="Y7" s="99"/>
+      <c r="Z7" s="99"/>
+      <c r="AA7" s="99"/>
+      <c r="AB7" s="99"/>
+      <c r="AC7" s="99"/>
+      <c r="AD7" s="99"/>
+      <c r="AE7" s="98" t="s">
         <v>117</v>
       </c>
-      <c r="AF7" s="97"/>
-      <c r="AG7" s="97"/>
-      <c r="AH7" s="97"/>
-      <c r="AI7" s="97"/>
-      <c r="AJ7" s="97"/>
-      <c r="AK7" s="97"/>
-      <c r="AL7" s="97"/>
-      <c r="AM7" s="97"/>
+      <c r="AF7" s="99"/>
+      <c r="AG7" s="99"/>
+      <c r="AH7" s="99"/>
+      <c r="AI7" s="99"/>
+      <c r="AJ7" s="99"/>
+      <c r="AK7" s="99"/>
+      <c r="AL7" s="99"/>
+      <c r="AM7" s="99"/>
     </row>
     <row r="8" spans="1:39" ht="15" customHeight="1">
       <c r="A8" s="86"/>
@@ -10572,168 +11776,168 @@
       <c r="J8" s="86"/>
       <c r="K8" s="86"/>
       <c r="L8" s="86"/>
-      <c r="M8" s="96" t="s">
+      <c r="M8" s="98" t="s">
         <v>118</v>
       </c>
-      <c r="N8" s="97"/>
-      <c r="O8" s="97"/>
-      <c r="P8" s="97"/>
-      <c r="Q8" s="97"/>
-      <c r="R8" s="97"/>
-      <c r="S8" s="97"/>
-      <c r="T8" s="97"/>
-      <c r="U8" s="97"/>
-      <c r="V8" s="96" t="s">
+      <c r="N8" s="99"/>
+      <c r="O8" s="99"/>
+      <c r="P8" s="99"/>
+      <c r="Q8" s="99"/>
+      <c r="R8" s="99"/>
+      <c r="S8" s="99"/>
+      <c r="T8" s="99"/>
+      <c r="U8" s="99"/>
+      <c r="V8" s="98" t="s">
         <v>119</v>
       </c>
-      <c r="W8" s="97"/>
-      <c r="X8" s="97"/>
-      <c r="Y8" s="97"/>
-      <c r="Z8" s="97"/>
-      <c r="AA8" s="97"/>
-      <c r="AB8" s="97"/>
-      <c r="AC8" s="97"/>
-      <c r="AD8" s="97"/>
-      <c r="AE8" s="96" t="s">
+      <c r="W8" s="99"/>
+      <c r="X8" s="99"/>
+      <c r="Y8" s="99"/>
+      <c r="Z8" s="99"/>
+      <c r="AA8" s="99"/>
+      <c r="AB8" s="99"/>
+      <c r="AC8" s="99"/>
+      <c r="AD8" s="99"/>
+      <c r="AE8" s="98" t="s">
         <v>120</v>
       </c>
-      <c r="AF8" s="97"/>
-      <c r="AG8" s="97"/>
-      <c r="AH8" s="97"/>
-      <c r="AI8" s="97"/>
-      <c r="AJ8" s="97"/>
-      <c r="AK8" s="97"/>
-      <c r="AL8" s="97"/>
-      <c r="AM8" s="97"/>
+      <c r="AF8" s="99"/>
+      <c r="AG8" s="99"/>
+      <c r="AH8" s="99"/>
+      <c r="AI8" s="99"/>
+      <c r="AJ8" s="99"/>
+      <c r="AK8" s="99"/>
+      <c r="AL8" s="99"/>
+      <c r="AM8" s="99"/>
     </row>
     <row r="9" spans="1:39" ht="15" customHeight="1">
-      <c r="A9" s="95" t="s">
+      <c r="A9" s="100" t="s">
         <v>113</v>
       </c>
-      <c r="B9" s="95"/>
-      <c r="C9" s="95"/>
-      <c r="D9" s="95"/>
-      <c r="E9" s="95"/>
-      <c r="F9" s="95"/>
-      <c r="G9" s="95"/>
-      <c r="H9" s="95"/>
-      <c r="I9" s="95"/>
-      <c r="J9" s="95"/>
-      <c r="K9" s="95"/>
-      <c r="L9" s="95"/>
-      <c r="M9" s="97"/>
-      <c r="N9" s="97"/>
-      <c r="O9" s="97"/>
-      <c r="P9" s="97"/>
-      <c r="Q9" s="97"/>
-      <c r="R9" s="97"/>
-      <c r="S9" s="97"/>
-      <c r="T9" s="97"/>
-      <c r="U9" s="97"/>
-      <c r="V9" s="97"/>
-      <c r="W9" s="97"/>
-      <c r="X9" s="97"/>
-      <c r="Y9" s="97"/>
-      <c r="Z9" s="97"/>
-      <c r="AA9" s="97"/>
-      <c r="AB9" s="97"/>
-      <c r="AC9" s="97"/>
-      <c r="AD9" s="97"/>
-      <c r="AE9" s="97"/>
-      <c r="AF9" s="97"/>
-      <c r="AG9" s="97"/>
-      <c r="AH9" s="97"/>
-      <c r="AI9" s="97"/>
-      <c r="AJ9" s="97"/>
-      <c r="AK9" s="97"/>
-      <c r="AL9" s="97"/>
-      <c r="AM9" s="97"/>
+      <c r="B9" s="100"/>
+      <c r="C9" s="100"/>
+      <c r="D9" s="100"/>
+      <c r="E9" s="100"/>
+      <c r="F9" s="100"/>
+      <c r="G9" s="100"/>
+      <c r="H9" s="100"/>
+      <c r="I9" s="100"/>
+      <c r="J9" s="100"/>
+      <c r="K9" s="100"/>
+      <c r="L9" s="100"/>
+      <c r="M9" s="99"/>
+      <c r="N9" s="99"/>
+      <c r="O9" s="99"/>
+      <c r="P9" s="99"/>
+      <c r="Q9" s="99"/>
+      <c r="R9" s="99"/>
+      <c r="S9" s="99"/>
+      <c r="T9" s="99"/>
+      <c r="U9" s="99"/>
+      <c r="V9" s="99"/>
+      <c r="W9" s="99"/>
+      <c r="X9" s="99"/>
+      <c r="Y9" s="99"/>
+      <c r="Z9" s="99"/>
+      <c r="AA9" s="99"/>
+      <c r="AB9" s="99"/>
+      <c r="AC9" s="99"/>
+      <c r="AD9" s="99"/>
+      <c r="AE9" s="99"/>
+      <c r="AF9" s="99"/>
+      <c r="AG9" s="99"/>
+      <c r="AH9" s="99"/>
+      <c r="AI9" s="99"/>
+      <c r="AJ9" s="99"/>
+      <c r="AK9" s="99"/>
+      <c r="AL9" s="99"/>
+      <c r="AM9" s="99"/>
     </row>
     <row r="10" spans="1:39" ht="15" customHeight="1">
-      <c r="A10" s="95" t="s">
+      <c r="A10" s="100" t="s">
         <v>112</v>
       </c>
-      <c r="B10" s="95"/>
-      <c r="C10" s="95"/>
-      <c r="D10" s="95"/>
-      <c r="E10" s="95"/>
-      <c r="F10" s="95"/>
-      <c r="G10" s="95"/>
-      <c r="H10" s="95"/>
-      <c r="I10" s="95"/>
-      <c r="J10" s="95"/>
-      <c r="K10" s="95"/>
-      <c r="L10" s="95"/>
-      <c r="M10" s="97"/>
-      <c r="N10" s="97"/>
-      <c r="O10" s="97"/>
-      <c r="P10" s="97"/>
-      <c r="Q10" s="97"/>
-      <c r="R10" s="97"/>
-      <c r="S10" s="97"/>
-      <c r="T10" s="97"/>
-      <c r="U10" s="97"/>
-      <c r="V10" s="97"/>
-      <c r="W10" s="97"/>
-      <c r="X10" s="97"/>
-      <c r="Y10" s="97"/>
-      <c r="Z10" s="97"/>
-      <c r="AA10" s="97"/>
-      <c r="AB10" s="97"/>
-      <c r="AC10" s="97"/>
-      <c r="AD10" s="97"/>
-      <c r="AE10" s="97"/>
-      <c r="AF10" s="97"/>
-      <c r="AG10" s="97"/>
-      <c r="AH10" s="97"/>
-      <c r="AI10" s="97"/>
-      <c r="AJ10" s="97"/>
-      <c r="AK10" s="97"/>
-      <c r="AL10" s="97"/>
-      <c r="AM10" s="97"/>
+      <c r="B10" s="100"/>
+      <c r="C10" s="100"/>
+      <c r="D10" s="100"/>
+      <c r="E10" s="100"/>
+      <c r="F10" s="100"/>
+      <c r="G10" s="100"/>
+      <c r="H10" s="100"/>
+      <c r="I10" s="100"/>
+      <c r="J10" s="100"/>
+      <c r="K10" s="100"/>
+      <c r="L10" s="100"/>
+      <c r="M10" s="99"/>
+      <c r="N10" s="99"/>
+      <c r="O10" s="99"/>
+      <c r="P10" s="99"/>
+      <c r="Q10" s="99"/>
+      <c r="R10" s="99"/>
+      <c r="S10" s="99"/>
+      <c r="T10" s="99"/>
+      <c r="U10" s="99"/>
+      <c r="V10" s="99"/>
+      <c r="W10" s="99"/>
+      <c r="X10" s="99"/>
+      <c r="Y10" s="99"/>
+      <c r="Z10" s="99"/>
+      <c r="AA10" s="99"/>
+      <c r="AB10" s="99"/>
+      <c r="AC10" s="99"/>
+      <c r="AD10" s="99"/>
+      <c r="AE10" s="99"/>
+      <c r="AF10" s="99"/>
+      <c r="AG10" s="99"/>
+      <c r="AH10" s="99"/>
+      <c r="AI10" s="99"/>
+      <c r="AJ10" s="99"/>
+      <c r="AK10" s="99"/>
+      <c r="AL10" s="99"/>
+      <c r="AM10" s="99"/>
     </row>
     <row r="11" spans="1:39" ht="15" customHeight="1">
-      <c r="A11" s="95" t="s">
+      <c r="A11" s="100" t="s">
         <v>114</v>
       </c>
-      <c r="B11" s="95"/>
-      <c r="C11" s="95"/>
-      <c r="D11" s="95"/>
-      <c r="E11" s="95"/>
-      <c r="F11" s="95"/>
-      <c r="G11" s="95"/>
-      <c r="H11" s="95"/>
-      <c r="I11" s="95"/>
-      <c r="J11" s="95"/>
-      <c r="K11" s="95"/>
-      <c r="L11" s="95"/>
-      <c r="M11" s="97"/>
-      <c r="N11" s="97"/>
-      <c r="O11" s="97"/>
-      <c r="P11" s="97"/>
-      <c r="Q11" s="97"/>
-      <c r="R11" s="97"/>
-      <c r="S11" s="97"/>
-      <c r="T11" s="97"/>
-      <c r="U11" s="97"/>
-      <c r="V11" s="97"/>
-      <c r="W11" s="97"/>
-      <c r="X11" s="97"/>
-      <c r="Y11" s="97"/>
-      <c r="Z11" s="97"/>
-      <c r="AA11" s="97"/>
-      <c r="AB11" s="97"/>
-      <c r="AC11" s="97"/>
-      <c r="AD11" s="97"/>
-      <c r="AE11" s="97"/>
-      <c r="AF11" s="97"/>
-      <c r="AG11" s="97"/>
-      <c r="AH11" s="97"/>
-      <c r="AI11" s="97"/>
-      <c r="AJ11" s="97"/>
-      <c r="AK11" s="97"/>
-      <c r="AL11" s="97"/>
-      <c r="AM11" s="97"/>
+      <c r="B11" s="100"/>
+      <c r="C11" s="100"/>
+      <c r="D11" s="100"/>
+      <c r="E11" s="100"/>
+      <c r="F11" s="100"/>
+      <c r="G11" s="100"/>
+      <c r="H11" s="100"/>
+      <c r="I11" s="100"/>
+      <c r="J11" s="100"/>
+      <c r="K11" s="100"/>
+      <c r="L11" s="100"/>
+      <c r="M11" s="99"/>
+      <c r="N11" s="99"/>
+      <c r="O11" s="99"/>
+      <c r="P11" s="99"/>
+      <c r="Q11" s="99"/>
+      <c r="R11" s="99"/>
+      <c r="S11" s="99"/>
+      <c r="T11" s="99"/>
+      <c r="U11" s="99"/>
+      <c r="V11" s="99"/>
+      <c r="W11" s="99"/>
+      <c r="X11" s="99"/>
+      <c r="Y11" s="99"/>
+      <c r="Z11" s="99"/>
+      <c r="AA11" s="99"/>
+      <c r="AB11" s="99"/>
+      <c r="AC11" s="99"/>
+      <c r="AD11" s="99"/>
+      <c r="AE11" s="99"/>
+      <c r="AF11" s="99"/>
+      <c r="AG11" s="99"/>
+      <c r="AH11" s="99"/>
+      <c r="AI11" s="99"/>
+      <c r="AJ11" s="99"/>
+      <c r="AK11" s="99"/>
+      <c r="AL11" s="99"/>
+      <c r="AM11" s="99"/>
     </row>
     <row r="12" spans="1:39" ht="8.5500000000000007" customHeight="1">
       <c r="A12" s="46"/>
@@ -10904,209 +12108,209 @@
       <c r="AM15" s="14"/>
     </row>
     <row r="16" spans="1:39" ht="15" customHeight="1">
-      <c r="A16" s="99" t="s">
+      <c r="A16" s="95" t="s">
         <v>123</v>
       </c>
-      <c r="B16" s="99"/>
-      <c r="C16" s="99"/>
-      <c r="D16" s="99"/>
-      <c r="E16" s="99"/>
-      <c r="F16" s="99"/>
-      <c r="G16" s="99"/>
-      <c r="H16" s="99"/>
-      <c r="I16" s="99"/>
-      <c r="J16" s="99"/>
-      <c r="K16" s="99"/>
-      <c r="L16" s="99"/>
-      <c r="M16" s="99"/>
-      <c r="N16" s="99"/>
-      <c r="O16" s="99"/>
-      <c r="P16" s="99"/>
-      <c r="Q16" s="99"/>
-      <c r="R16" s="99"/>
-      <c r="S16" s="99"/>
-      <c r="T16" s="99"/>
-      <c r="U16" s="99"/>
-      <c r="V16" s="99"/>
-      <c r="W16" s="99"/>
-      <c r="X16" s="99"/>
-      <c r="Y16" s="99"/>
-      <c r="Z16" s="99"/>
-      <c r="AA16" s="99"/>
-      <c r="AB16" s="99"/>
-      <c r="AC16" s="99"/>
-      <c r="AD16" s="99"/>
-      <c r="AE16" s="99"/>
-      <c r="AF16" s="99"/>
-      <c r="AG16" s="99"/>
-      <c r="AH16" s="99"/>
-      <c r="AI16" s="99"/>
-      <c r="AJ16" s="99"/>
-      <c r="AK16" s="99"/>
-      <c r="AL16" s="99"/>
-      <c r="AM16" s="99"/>
+      <c r="B16" s="95"/>
+      <c r="C16" s="95"/>
+      <c r="D16" s="95"/>
+      <c r="E16" s="95"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="95"/>
+      <c r="I16" s="95"/>
+      <c r="J16" s="95"/>
+      <c r="K16" s="95"/>
+      <c r="L16" s="95"/>
+      <c r="M16" s="95"/>
+      <c r="N16" s="95"/>
+      <c r="O16" s="95"/>
+      <c r="P16" s="95"/>
+      <c r="Q16" s="95"/>
+      <c r="R16" s="95"/>
+      <c r="S16" s="95"/>
+      <c r="T16" s="95"/>
+      <c r="U16" s="95"/>
+      <c r="V16" s="95"/>
+      <c r="W16" s="95"/>
+      <c r="X16" s="95"/>
+      <c r="Y16" s="95"/>
+      <c r="Z16" s="95"/>
+      <c r="AA16" s="95"/>
+      <c r="AB16" s="95"/>
+      <c r="AC16" s="95"/>
+      <c r="AD16" s="95"/>
+      <c r="AE16" s="95"/>
+      <c r="AF16" s="95"/>
+      <c r="AG16" s="95"/>
+      <c r="AH16" s="95"/>
+      <c r="AI16" s="95"/>
+      <c r="AJ16" s="95"/>
+      <c r="AK16" s="95"/>
+      <c r="AL16" s="95"/>
+      <c r="AM16" s="95"/>
     </row>
     <row r="17" spans="1:39" ht="15" customHeight="1">
-      <c r="A17" s="99" t="s">
+      <c r="A17" s="95" t="s">
         <v>124</v>
       </c>
-      <c r="B17" s="99"/>
-      <c r="C17" s="99"/>
-      <c r="D17" s="99"/>
-      <c r="E17" s="99"/>
-      <c r="F17" s="99"/>
-      <c r="G17" s="99"/>
-      <c r="H17" s="99"/>
-      <c r="I17" s="99"/>
-      <c r="J17" s="99"/>
-      <c r="K17" s="99"/>
-      <c r="L17" s="99"/>
-      <c r="M17" s="99"/>
-      <c r="N17" s="99"/>
-      <c r="O17" s="99"/>
-      <c r="P17" s="99"/>
-      <c r="Q17" s="99"/>
-      <c r="R17" s="99"/>
-      <c r="S17" s="99"/>
-      <c r="T17" s="99"/>
-      <c r="U17" s="99"/>
-      <c r="V17" s="99"/>
-      <c r="W17" s="99"/>
-      <c r="X17" s="99"/>
-      <c r="Y17" s="99"/>
-      <c r="Z17" s="99"/>
-      <c r="AA17" s="99"/>
-      <c r="AB17" s="99"/>
-      <c r="AC17" s="99"/>
-      <c r="AD17" s="99"/>
-      <c r="AE17" s="99"/>
-      <c r="AF17" s="99"/>
-      <c r="AG17" s="99"/>
-      <c r="AH17" s="99"/>
-      <c r="AI17" s="99"/>
-      <c r="AJ17" s="99"/>
-      <c r="AK17" s="99"/>
-      <c r="AL17" s="99"/>
-      <c r="AM17" s="99"/>
+      <c r="B17" s="95"/>
+      <c r="C17" s="95"/>
+      <c r="D17" s="95"/>
+      <c r="E17" s="95"/>
+      <c r="F17" s="95"/>
+      <c r="G17" s="95"/>
+      <c r="H17" s="95"/>
+      <c r="I17" s="95"/>
+      <c r="J17" s="95"/>
+      <c r="K17" s="95"/>
+      <c r="L17" s="95"/>
+      <c r="M17" s="95"/>
+      <c r="N17" s="95"/>
+      <c r="O17" s="95"/>
+      <c r="P17" s="95"/>
+      <c r="Q17" s="95"/>
+      <c r="R17" s="95"/>
+      <c r="S17" s="95"/>
+      <c r="T17" s="95"/>
+      <c r="U17" s="95"/>
+      <c r="V17" s="95"/>
+      <c r="W17" s="95"/>
+      <c r="X17" s="95"/>
+      <c r="Y17" s="95"/>
+      <c r="Z17" s="95"/>
+      <c r="AA17" s="95"/>
+      <c r="AB17" s="95"/>
+      <c r="AC17" s="95"/>
+      <c r="AD17" s="95"/>
+      <c r="AE17" s="95"/>
+      <c r="AF17" s="95"/>
+      <c r="AG17" s="95"/>
+      <c r="AH17" s="95"/>
+      <c r="AI17" s="95"/>
+      <c r="AJ17" s="95"/>
+      <c r="AK17" s="95"/>
+      <c r="AL17" s="95"/>
+      <c r="AM17" s="95"/>
     </row>
     <row r="18" spans="1:39" ht="15" customHeight="1">
-      <c r="A18" s="96" t="s">
+      <c r="A18" s="98" t="s">
         <v>125</v>
       </c>
-      <c r="B18" s="96"/>
-      <c r="C18" s="96"/>
-      <c r="D18" s="96"/>
-      <c r="E18" s="96"/>
-      <c r="F18" s="96"/>
-      <c r="G18" s="96"/>
-      <c r="H18" s="96"/>
-      <c r="I18" s="96"/>
-      <c r="J18" s="96"/>
-      <c r="K18" s="96"/>
-      <c r="L18" s="96"/>
-      <c r="M18" s="96"/>
-      <c r="N18" s="96"/>
-      <c r="O18" s="96"/>
-      <c r="P18" s="96"/>
-      <c r="Q18" s="96"/>
-      <c r="R18" s="96"/>
-      <c r="S18" s="96"/>
-      <c r="T18" s="96"/>
-      <c r="U18" s="96"/>
-      <c r="V18" s="96"/>
-      <c r="W18" s="96"/>
-      <c r="X18" s="96"/>
-      <c r="Y18" s="96"/>
-      <c r="Z18" s="96"/>
-      <c r="AA18" s="96"/>
-      <c r="AB18" s="96"/>
-      <c r="AC18" s="96"/>
-      <c r="AD18" s="96"/>
-      <c r="AE18" s="96"/>
-      <c r="AF18" s="96"/>
-      <c r="AG18" s="96"/>
-      <c r="AH18" s="96"/>
-      <c r="AI18" s="96"/>
-      <c r="AJ18" s="96"/>
-      <c r="AK18" s="96"/>
-      <c r="AL18" s="96"/>
-      <c r="AM18" s="96"/>
+      <c r="B18" s="98"/>
+      <c r="C18" s="98"/>
+      <c r="D18" s="98"/>
+      <c r="E18" s="98"/>
+      <c r="F18" s="98"/>
+      <c r="G18" s="98"/>
+      <c r="H18" s="98"/>
+      <c r="I18" s="98"/>
+      <c r="J18" s="98"/>
+      <c r="K18" s="98"/>
+      <c r="L18" s="98"/>
+      <c r="M18" s="98"/>
+      <c r="N18" s="98"/>
+      <c r="O18" s="98"/>
+      <c r="P18" s="98"/>
+      <c r="Q18" s="98"/>
+      <c r="R18" s="98"/>
+      <c r="S18" s="98"/>
+      <c r="T18" s="98"/>
+      <c r="U18" s="98"/>
+      <c r="V18" s="98"/>
+      <c r="W18" s="98"/>
+      <c r="X18" s="98"/>
+      <c r="Y18" s="98"/>
+      <c r="Z18" s="98"/>
+      <c r="AA18" s="98"/>
+      <c r="AB18" s="98"/>
+      <c r="AC18" s="98"/>
+      <c r="AD18" s="98"/>
+      <c r="AE18" s="98"/>
+      <c r="AF18" s="98"/>
+      <c r="AG18" s="98"/>
+      <c r="AH18" s="98"/>
+      <c r="AI18" s="98"/>
+      <c r="AJ18" s="98"/>
+      <c r="AK18" s="98"/>
+      <c r="AL18" s="98"/>
+      <c r="AM18" s="98"/>
     </row>
     <row r="19" spans="1:39" ht="15" customHeight="1">
-      <c r="A19" s="96" t="s">
+      <c r="A19" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="96"/>
-      <c r="C19" s="96"/>
-      <c r="D19" s="96"/>
-      <c r="E19" s="96"/>
-      <c r="F19" s="96"/>
-      <c r="G19" s="96"/>
-      <c r="H19" s="96"/>
-      <c r="I19" s="96"/>
-      <c r="J19" s="96" t="s">
+      <c r="B19" s="98"/>
+      <c r="C19" s="98"/>
+      <c r="D19" s="98"/>
+      <c r="E19" s="98"/>
+      <c r="F19" s="98"/>
+      <c r="G19" s="98"/>
+      <c r="H19" s="98"/>
+      <c r="I19" s="98"/>
+      <c r="J19" s="98" t="s">
         <v>9</v>
       </c>
       <c r="K19" s="86"/>
       <c r="L19" s="86"/>
-      <c r="M19" s="96" t="s">
+      <c r="M19" s="98" t="s">
         <v>10</v>
       </c>
       <c r="N19" s="86"/>
       <c r="O19" s="86"/>
-      <c r="P19" s="96" t="s">
+      <c r="P19" s="98" t="s">
         <v>11</v>
       </c>
       <c r="Q19" s="86"/>
       <c r="R19" s="86"/>
-      <c r="S19" s="96" t="s">
+      <c r="S19" s="98" t="s">
         <v>12</v>
       </c>
       <c r="T19" s="86"/>
       <c r="U19" s="86"/>
-      <c r="V19" s="96" t="s">
+      <c r="V19" s="98" t="s">
         <v>13</v>
       </c>
       <c r="W19" s="86"/>
       <c r="X19" s="86"/>
-      <c r="Y19" s="96" t="s">
+      <c r="Y19" s="98" t="s">
         <v>128</v>
       </c>
       <c r="Z19" s="86"/>
       <c r="AA19" s="86"/>
-      <c r="AB19" s="96" t="s">
+      <c r="AB19" s="98" t="s">
         <v>129</v>
       </c>
       <c r="AC19" s="86"/>
       <c r="AD19" s="86"/>
-      <c r="AE19" s="96" t="s">
+      <c r="AE19" s="98" t="s">
         <v>130</v>
       </c>
       <c r="AF19" s="86"/>
       <c r="AG19" s="86"/>
-      <c r="AH19" s="96" t="s">
+      <c r="AH19" s="98" t="s">
         <v>131</v>
       </c>
       <c r="AI19" s="86"/>
       <c r="AJ19" s="86"/>
-      <c r="AK19" s="96" t="s">
+      <c r="AK19" s="98" t="s">
         <v>132</v>
       </c>
       <c r="AL19" s="86"/>
       <c r="AM19" s="86"/>
     </row>
     <row r="20" spans="1:39" ht="15" customHeight="1">
-      <c r="A20" s="96" t="s">
+      <c r="A20" s="98" t="s">
         <v>127</v>
       </c>
-      <c r="B20" s="96"/>
-      <c r="C20" s="96"/>
-      <c r="D20" s="96"/>
-      <c r="E20" s="96"/>
-      <c r="F20" s="96"/>
-      <c r="G20" s="96"/>
-      <c r="H20" s="96"/>
-      <c r="I20" s="96"/>
+      <c r="B20" s="98"/>
+      <c r="C20" s="98"/>
+      <c r="D20" s="98"/>
+      <c r="E20" s="98"/>
+      <c r="F20" s="98"/>
+      <c r="G20" s="98"/>
+      <c r="H20" s="98"/>
+      <c r="I20" s="98"/>
       <c r="J20" s="86"/>
       <c r="K20" s="86"/>
       <c r="L20" s="86"/>
@@ -11139,17 +12343,17 @@
       <c r="AM20" s="86"/>
     </row>
     <row r="21" spans="1:39" ht="15" customHeight="1">
-      <c r="A21" s="80" t="s">
+      <c r="A21" s="72" t="s">
         <v>126</v>
       </c>
-      <c r="B21" s="80"/>
-      <c r="C21" s="80"/>
-      <c r="D21" s="80"/>
-      <c r="E21" s="80"/>
-      <c r="F21" s="80"/>
-      <c r="G21" s="80"/>
-      <c r="H21" s="80"/>
-      <c r="I21" s="80"/>
+      <c r="B21" s="72"/>
+      <c r="C21" s="72"/>
+      <c r="D21" s="72"/>
+      <c r="E21" s="72"/>
+      <c r="F21" s="72"/>
+      <c r="G21" s="72"/>
+      <c r="H21" s="72"/>
+      <c r="I21" s="72"/>
       <c r="J21" s="86"/>
       <c r="K21" s="86"/>
       <c r="L21" s="86"/>
@@ -11182,80 +12386,80 @@
       <c r="AM21" s="86"/>
     </row>
     <row r="22" spans="1:39" ht="15" customHeight="1">
-      <c r="A22" s="96" t="s">
+      <c r="A22" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="96"/>
-      <c r="C22" s="96"/>
-      <c r="D22" s="96"/>
-      <c r="E22" s="96"/>
-      <c r="F22" s="96"/>
-      <c r="G22" s="96"/>
-      <c r="H22" s="96"/>
-      <c r="I22" s="96"/>
-      <c r="J22" s="96" t="s">
+      <c r="B22" s="98"/>
+      <c r="C22" s="98"/>
+      <c r="D22" s="98"/>
+      <c r="E22" s="98"/>
+      <c r="F22" s="98"/>
+      <c r="G22" s="98"/>
+      <c r="H22" s="98"/>
+      <c r="I22" s="98"/>
+      <c r="J22" s="98" t="s">
         <v>133</v>
       </c>
       <c r="K22" s="86"/>
       <c r="L22" s="86"/>
-      <c r="M22" s="96" t="s">
+      <c r="M22" s="98" t="s">
         <v>134</v>
       </c>
       <c r="N22" s="86"/>
       <c r="O22" s="86"/>
-      <c r="P22" s="96" t="s">
+      <c r="P22" s="98" t="s">
         <v>135</v>
       </c>
       <c r="Q22" s="86"/>
       <c r="R22" s="86"/>
-      <c r="S22" s="96" t="s">
+      <c r="S22" s="98" t="s">
         <v>136</v>
       </c>
       <c r="T22" s="86"/>
       <c r="U22" s="86"/>
-      <c r="V22" s="96" t="s">
+      <c r="V22" s="98" t="s">
         <v>137</v>
       </c>
       <c r="W22" s="86"/>
       <c r="X22" s="86"/>
-      <c r="Y22" s="96" t="s">
+      <c r="Y22" s="98" t="s">
         <v>138</v>
       </c>
       <c r="Z22" s="86"/>
       <c r="AA22" s="86"/>
-      <c r="AB22" s="96" t="s">
+      <c r="AB22" s="98" t="s">
         <v>139</v>
       </c>
       <c r="AC22" s="86"/>
       <c r="AD22" s="86"/>
-      <c r="AE22" s="96" t="s">
+      <c r="AE22" s="98" t="s">
         <v>140</v>
       </c>
       <c r="AF22" s="86"/>
       <c r="AG22" s="86"/>
-      <c r="AH22" s="96" t="s">
+      <c r="AH22" s="98" t="s">
         <v>141</v>
       </c>
       <c r="AI22" s="86"/>
       <c r="AJ22" s="86"/>
-      <c r="AK22" s="96" t="s">
+      <c r="AK22" s="98" t="s">
         <v>142</v>
       </c>
       <c r="AL22" s="86"/>
       <c r="AM22" s="86"/>
     </row>
     <row r="23" spans="1:39" ht="15" customHeight="1">
-      <c r="A23" s="96" t="s">
+      <c r="A23" s="98" t="s">
         <v>127</v>
       </c>
-      <c r="B23" s="96"/>
-      <c r="C23" s="96"/>
-      <c r="D23" s="96"/>
-      <c r="E23" s="96"/>
-      <c r="F23" s="96"/>
-      <c r="G23" s="96"/>
-      <c r="H23" s="96"/>
-      <c r="I23" s="96"/>
+      <c r="B23" s="98"/>
+      <c r="C23" s="98"/>
+      <c r="D23" s="98"/>
+      <c r="E23" s="98"/>
+      <c r="F23" s="98"/>
+      <c r="G23" s="98"/>
+      <c r="H23" s="98"/>
+      <c r="I23" s="98"/>
       <c r="J23" s="86"/>
       <c r="K23" s="86"/>
       <c r="L23" s="86"/>
@@ -11288,17 +12492,17 @@
       <c r="AM23" s="86"/>
     </row>
     <row r="24" spans="1:39" ht="15" customHeight="1">
-      <c r="A24" s="80" t="s">
+      <c r="A24" s="72" t="s">
         <v>126</v>
       </c>
-      <c r="B24" s="80"/>
-      <c r="C24" s="80"/>
-      <c r="D24" s="80"/>
-      <c r="E24" s="80"/>
-      <c r="F24" s="80"/>
-      <c r="G24" s="80"/>
-      <c r="H24" s="80"/>
-      <c r="I24" s="80"/>
+      <c r="B24" s="72"/>
+      <c r="C24" s="72"/>
+      <c r="D24" s="72"/>
+      <c r="E24" s="72"/>
+      <c r="F24" s="72"/>
+      <c r="G24" s="72"/>
+      <c r="H24" s="72"/>
+      <c r="I24" s="72"/>
       <c r="J24" s="86"/>
       <c r="K24" s="86"/>
       <c r="L24" s="86"/>
@@ -11331,176 +12535,176 @@
       <c r="AM24" s="86"/>
     </row>
     <row r="25" spans="1:39" ht="15" customHeight="1">
-      <c r="A25" s="99" t="s">
+      <c r="A25" s="95" t="s">
         <v>143</v>
       </c>
-      <c r="B25" s="99"/>
-      <c r="C25" s="99"/>
-      <c r="D25" s="99"/>
-      <c r="E25" s="99"/>
-      <c r="F25" s="99"/>
-      <c r="G25" s="99"/>
-      <c r="H25" s="99"/>
-      <c r="I25" s="99"/>
-      <c r="J25" s="99"/>
-      <c r="K25" s="99"/>
-      <c r="L25" s="99"/>
-      <c r="M25" s="99"/>
-      <c r="N25" s="99"/>
-      <c r="O25" s="99"/>
-      <c r="P25" s="99"/>
-      <c r="Q25" s="99"/>
-      <c r="R25" s="99"/>
-      <c r="S25" s="99"/>
-      <c r="T25" s="99"/>
-      <c r="U25" s="99"/>
-      <c r="V25" s="99"/>
-      <c r="W25" s="99"/>
-      <c r="X25" s="99"/>
-      <c r="Y25" s="99"/>
-      <c r="Z25" s="99"/>
-      <c r="AA25" s="99"/>
-      <c r="AB25" s="99"/>
-      <c r="AC25" s="99"/>
-      <c r="AD25" s="99"/>
-      <c r="AE25" s="99"/>
-      <c r="AF25" s="99"/>
-      <c r="AG25" s="99"/>
-      <c r="AH25" s="99"/>
-      <c r="AI25" s="99"/>
-      <c r="AJ25" s="99"/>
-      <c r="AK25" s="99"/>
-      <c r="AL25" s="99"/>
-      <c r="AM25" s="99"/>
+      <c r="B25" s="95"/>
+      <c r="C25" s="95"/>
+      <c r="D25" s="95"/>
+      <c r="E25" s="95"/>
+      <c r="F25" s="95"/>
+      <c r="G25" s="95"/>
+      <c r="H25" s="95"/>
+      <c r="I25" s="95"/>
+      <c r="J25" s="95"/>
+      <c r="K25" s="95"/>
+      <c r="L25" s="95"/>
+      <c r="M25" s="95"/>
+      <c r="N25" s="95"/>
+      <c r="O25" s="95"/>
+      <c r="P25" s="95"/>
+      <c r="Q25" s="95"/>
+      <c r="R25" s="95"/>
+      <c r="S25" s="95"/>
+      <c r="T25" s="95"/>
+      <c r="U25" s="95"/>
+      <c r="V25" s="95"/>
+      <c r="W25" s="95"/>
+      <c r="X25" s="95"/>
+      <c r="Y25" s="95"/>
+      <c r="Z25" s="95"/>
+      <c r="AA25" s="95"/>
+      <c r="AB25" s="95"/>
+      <c r="AC25" s="95"/>
+      <c r="AD25" s="95"/>
+      <c r="AE25" s="95"/>
+      <c r="AF25" s="95"/>
+      <c r="AG25" s="95"/>
+      <c r="AH25" s="95"/>
+      <c r="AI25" s="95"/>
+      <c r="AJ25" s="95"/>
+      <c r="AK25" s="95"/>
+      <c r="AL25" s="95"/>
+      <c r="AM25" s="95"/>
     </row>
     <row r="26" spans="1:39" ht="15" customHeight="1">
-      <c r="A26" s="99" t="s">
+      <c r="A26" s="95" t="s">
         <v>144</v>
       </c>
-      <c r="B26" s="99"/>
-      <c r="C26" s="99"/>
-      <c r="D26" s="99"/>
-      <c r="E26" s="99"/>
-      <c r="F26" s="99"/>
-      <c r="G26" s="99"/>
-      <c r="H26" s="99"/>
-      <c r="I26" s="99"/>
-      <c r="J26" s="99"/>
-      <c r="K26" s="99"/>
-      <c r="L26" s="99"/>
-      <c r="M26" s="99"/>
-      <c r="N26" s="99"/>
-      <c r="O26" s="99"/>
-      <c r="P26" s="99"/>
-      <c r="Q26" s="99"/>
-      <c r="R26" s="99"/>
-      <c r="S26" s="99"/>
-      <c r="T26" s="99"/>
-      <c r="U26" s="99"/>
-      <c r="V26" s="99"/>
-      <c r="W26" s="99"/>
-      <c r="X26" s="99"/>
-      <c r="Y26" s="99"/>
-      <c r="Z26" s="99"/>
-      <c r="AA26" s="99"/>
-      <c r="AB26" s="99"/>
-      <c r="AC26" s="99"/>
-      <c r="AD26" s="99"/>
-      <c r="AE26" s="99"/>
-      <c r="AF26" s="99"/>
-      <c r="AG26" s="99"/>
-      <c r="AH26" s="99"/>
-      <c r="AI26" s="99"/>
-      <c r="AJ26" s="99"/>
-      <c r="AK26" s="99"/>
-      <c r="AL26" s="99"/>
-      <c r="AM26" s="99"/>
+      <c r="B26" s="95"/>
+      <c r="C26" s="95"/>
+      <c r="D26" s="95"/>
+      <c r="E26" s="95"/>
+      <c r="F26" s="95"/>
+      <c r="G26" s="95"/>
+      <c r="H26" s="95"/>
+      <c r="I26" s="95"/>
+      <c r="J26" s="95"/>
+      <c r="K26" s="95"/>
+      <c r="L26" s="95"/>
+      <c r="M26" s="95"/>
+      <c r="N26" s="95"/>
+      <c r="O26" s="95"/>
+      <c r="P26" s="95"/>
+      <c r="Q26" s="95"/>
+      <c r="R26" s="95"/>
+      <c r="S26" s="95"/>
+      <c r="T26" s="95"/>
+      <c r="U26" s="95"/>
+      <c r="V26" s="95"/>
+      <c r="W26" s="95"/>
+      <c r="X26" s="95"/>
+      <c r="Y26" s="95"/>
+      <c r="Z26" s="95"/>
+      <c r="AA26" s="95"/>
+      <c r="AB26" s="95"/>
+      <c r="AC26" s="95"/>
+      <c r="AD26" s="95"/>
+      <c r="AE26" s="95"/>
+      <c r="AF26" s="95"/>
+      <c r="AG26" s="95"/>
+      <c r="AH26" s="95"/>
+      <c r="AI26" s="95"/>
+      <c r="AJ26" s="95"/>
+      <c r="AK26" s="95"/>
+      <c r="AL26" s="95"/>
+      <c r="AM26" s="95"/>
     </row>
     <row r="27" spans="1:39" ht="15" customHeight="1">
-      <c r="A27" s="99" t="s">
+      <c r="A27" s="95" t="s">
         <v>145</v>
       </c>
-      <c r="B27" s="99"/>
-      <c r="C27" s="99"/>
-      <c r="D27" s="99"/>
-      <c r="E27" s="99"/>
-      <c r="F27" s="99"/>
-      <c r="G27" s="99"/>
-      <c r="H27" s="99"/>
-      <c r="I27" s="99"/>
-      <c r="J27" s="99"/>
-      <c r="K27" s="99"/>
-      <c r="L27" s="99"/>
-      <c r="M27" s="99"/>
-      <c r="N27" s="99"/>
-      <c r="O27" s="99"/>
-      <c r="P27" s="99"/>
-      <c r="Q27" s="99"/>
-      <c r="R27" s="99"/>
-      <c r="S27" s="99"/>
-      <c r="T27" s="99"/>
-      <c r="U27" s="99"/>
-      <c r="V27" s="99"/>
-      <c r="W27" s="99"/>
-      <c r="X27" s="99"/>
-      <c r="Y27" s="99"/>
-      <c r="Z27" s="99"/>
-      <c r="AA27" s="99"/>
-      <c r="AB27" s="99"/>
-      <c r="AC27" s="99"/>
-      <c r="AD27" s="99"/>
-      <c r="AE27" s="99"/>
-      <c r="AF27" s="99"/>
-      <c r="AG27" s="99"/>
-      <c r="AH27" s="99"/>
-      <c r="AI27" s="99"/>
-      <c r="AJ27" s="99"/>
-      <c r="AK27" s="99"/>
-      <c r="AL27" s="99"/>
-      <c r="AM27" s="99"/>
+      <c r="B27" s="95"/>
+      <c r="C27" s="95"/>
+      <c r="D27" s="95"/>
+      <c r="E27" s="95"/>
+      <c r="F27" s="95"/>
+      <c r="G27" s="95"/>
+      <c r="H27" s="95"/>
+      <c r="I27" s="95"/>
+      <c r="J27" s="95"/>
+      <c r="K27" s="95"/>
+      <c r="L27" s="95"/>
+      <c r="M27" s="95"/>
+      <c r="N27" s="95"/>
+      <c r="O27" s="95"/>
+      <c r="P27" s="95"/>
+      <c r="Q27" s="95"/>
+      <c r="R27" s="95"/>
+      <c r="S27" s="95"/>
+      <c r="T27" s="95"/>
+      <c r="U27" s="95"/>
+      <c r="V27" s="95"/>
+      <c r="W27" s="95"/>
+      <c r="X27" s="95"/>
+      <c r="Y27" s="95"/>
+      <c r="Z27" s="95"/>
+      <c r="AA27" s="95"/>
+      <c r="AB27" s="95"/>
+      <c r="AC27" s="95"/>
+      <c r="AD27" s="95"/>
+      <c r="AE27" s="95"/>
+      <c r="AF27" s="95"/>
+      <c r="AG27" s="95"/>
+      <c r="AH27" s="95"/>
+      <c r="AI27" s="95"/>
+      <c r="AJ27" s="95"/>
+      <c r="AK27" s="95"/>
+      <c r="AL27" s="95"/>
+      <c r="AM27" s="95"/>
     </row>
     <row r="28" spans="1:39" ht="15" customHeight="1">
-      <c r="A28" s="99" t="s">
+      <c r="A28" s="95" t="s">
         <v>146</v>
       </c>
-      <c r="B28" s="99"/>
-      <c r="C28" s="99"/>
-      <c r="D28" s="99"/>
-      <c r="E28" s="99"/>
-      <c r="F28" s="99"/>
-      <c r="G28" s="99"/>
-      <c r="H28" s="99"/>
-      <c r="I28" s="99"/>
-      <c r="J28" s="99"/>
-      <c r="K28" s="99"/>
-      <c r="L28" s="99"/>
-      <c r="M28" s="99"/>
-      <c r="N28" s="99"/>
-      <c r="O28" s="99"/>
-      <c r="P28" s="99"/>
-      <c r="Q28" s="99"/>
-      <c r="R28" s="99"/>
-      <c r="S28" s="99"/>
-      <c r="T28" s="99"/>
-      <c r="U28" s="99"/>
-      <c r="V28" s="99"/>
-      <c r="W28" s="99"/>
-      <c r="X28" s="99"/>
-      <c r="Y28" s="99"/>
-      <c r="Z28" s="99"/>
-      <c r="AA28" s="99"/>
-      <c r="AB28" s="99"/>
-      <c r="AC28" s="99"/>
-      <c r="AD28" s="99"/>
-      <c r="AE28" s="99"/>
-      <c r="AF28" s="99"/>
-      <c r="AG28" s="99"/>
-      <c r="AH28" s="99"/>
-      <c r="AI28" s="99"/>
-      <c r="AJ28" s="99"/>
-      <c r="AK28" s="99"/>
-      <c r="AL28" s="99"/>
-      <c r="AM28" s="99"/>
+      <c r="B28" s="95"/>
+      <c r="C28" s="95"/>
+      <c r="D28" s="95"/>
+      <c r="E28" s="95"/>
+      <c r="F28" s="95"/>
+      <c r="G28" s="95"/>
+      <c r="H28" s="95"/>
+      <c r="I28" s="95"/>
+      <c r="J28" s="95"/>
+      <c r="K28" s="95"/>
+      <c r="L28" s="95"/>
+      <c r="M28" s="95"/>
+      <c r="N28" s="95"/>
+      <c r="O28" s="95"/>
+      <c r="P28" s="95"/>
+      <c r="Q28" s="95"/>
+      <c r="R28" s="95"/>
+      <c r="S28" s="95"/>
+      <c r="T28" s="95"/>
+      <c r="U28" s="95"/>
+      <c r="V28" s="95"/>
+      <c r="W28" s="95"/>
+      <c r="X28" s="95"/>
+      <c r="Y28" s="95"/>
+      <c r="Z28" s="95"/>
+      <c r="AA28" s="95"/>
+      <c r="AB28" s="95"/>
+      <c r="AC28" s="95"/>
+      <c r="AD28" s="95"/>
+      <c r="AE28" s="95"/>
+      <c r="AF28" s="95"/>
+      <c r="AG28" s="95"/>
+      <c r="AH28" s="95"/>
+      <c r="AI28" s="95"/>
+      <c r="AJ28" s="95"/>
+      <c r="AK28" s="95"/>
+      <c r="AL28" s="95"/>
+      <c r="AM28" s="95"/>
     </row>
     <row r="29" spans="1:39" ht="14.1" customHeight="1">
       <c r="A29" s="46"/>
@@ -11544,142 +12748,142 @@
       <c r="AM29" s="14"/>
     </row>
     <row r="30" spans="1:39" ht="15" customHeight="1">
-      <c r="A30" s="99" t="s">
+      <c r="A30" s="95" t="s">
         <v>147</v>
       </c>
-      <c r="B30" s="99"/>
-      <c r="C30" s="99"/>
-      <c r="D30" s="99"/>
-      <c r="E30" s="99"/>
-      <c r="F30" s="99"/>
-      <c r="G30" s="99"/>
-      <c r="H30" s="99"/>
-      <c r="I30" s="99"/>
-      <c r="J30" s="99"/>
-      <c r="K30" s="99"/>
-      <c r="L30" s="99"/>
-      <c r="M30" s="99"/>
-      <c r="N30" s="99"/>
-      <c r="O30" s="99"/>
-      <c r="P30" s="99"/>
-      <c r="Q30" s="99"/>
-      <c r="R30" s="99"/>
-      <c r="S30" s="99"/>
-      <c r="T30" s="99"/>
-      <c r="U30" s="99"/>
-      <c r="V30" s="99"/>
-      <c r="W30" s="99"/>
-      <c r="X30" s="99"/>
-      <c r="Y30" s="99"/>
-      <c r="Z30" s="99"/>
-      <c r="AA30" s="99"/>
-      <c r="AB30" s="99"/>
-      <c r="AC30" s="99"/>
-      <c r="AD30" s="99"/>
-      <c r="AE30" s="99"/>
-      <c r="AF30" s="99"/>
-      <c r="AG30" s="99"/>
-      <c r="AH30" s="99"/>
-      <c r="AI30" s="99"/>
-      <c r="AJ30" s="99"/>
-      <c r="AK30" s="99"/>
-      <c r="AL30" s="99"/>
-      <c r="AM30" s="99"/>
+      <c r="B30" s="95"/>
+      <c r="C30" s="95"/>
+      <c r="D30" s="95"/>
+      <c r="E30" s="95"/>
+      <c r="F30" s="95"/>
+      <c r="G30" s="95"/>
+      <c r="H30" s="95"/>
+      <c r="I30" s="95"/>
+      <c r="J30" s="95"/>
+      <c r="K30" s="95"/>
+      <c r="L30" s="95"/>
+      <c r="M30" s="95"/>
+      <c r="N30" s="95"/>
+      <c r="O30" s="95"/>
+      <c r="P30" s="95"/>
+      <c r="Q30" s="95"/>
+      <c r="R30" s="95"/>
+      <c r="S30" s="95"/>
+      <c r="T30" s="95"/>
+      <c r="U30" s="95"/>
+      <c r="V30" s="95"/>
+      <c r="W30" s="95"/>
+      <c r="X30" s="95"/>
+      <c r="Y30" s="95"/>
+      <c r="Z30" s="95"/>
+      <c r="AA30" s="95"/>
+      <c r="AB30" s="95"/>
+      <c r="AC30" s="95"/>
+      <c r="AD30" s="95"/>
+      <c r="AE30" s="95"/>
+      <c r="AF30" s="95"/>
+      <c r="AG30" s="95"/>
+      <c r="AH30" s="95"/>
+      <c r="AI30" s="95"/>
+      <c r="AJ30" s="95"/>
+      <c r="AK30" s="95"/>
+      <c r="AL30" s="95"/>
+      <c r="AM30" s="95"/>
     </row>
     <row r="31" spans="1:39" ht="15" customHeight="1">
-      <c r="A31" s="99" t="s">
+      <c r="A31" s="95" t="s">
         <v>148</v>
       </c>
-      <c r="B31" s="99"/>
-      <c r="C31" s="99"/>
-      <c r="D31" s="99"/>
-      <c r="E31" s="99"/>
-      <c r="F31" s="99"/>
-      <c r="G31" s="99"/>
-      <c r="H31" s="99"/>
-      <c r="I31" s="99"/>
-      <c r="J31" s="99"/>
-      <c r="K31" s="99"/>
-      <c r="L31" s="99"/>
-      <c r="M31" s="99"/>
-      <c r="N31" s="99"/>
-      <c r="O31" s="99"/>
-      <c r="P31" s="99"/>
-      <c r="Q31" s="99"/>
-      <c r="R31" s="99"/>
-      <c r="S31" s="99"/>
-      <c r="T31" s="99"/>
-      <c r="U31" s="99"/>
-      <c r="V31" s="99"/>
-      <c r="W31" s="99"/>
-      <c r="X31" s="99"/>
-      <c r="Y31" s="99"/>
-      <c r="Z31" s="99"/>
-      <c r="AA31" s="99"/>
-      <c r="AB31" s="99"/>
-      <c r="AC31" s="99"/>
-      <c r="AD31" s="99"/>
-      <c r="AE31" s="99"/>
-      <c r="AF31" s="99"/>
-      <c r="AG31" s="99"/>
-      <c r="AH31" s="99"/>
-      <c r="AI31" s="99"/>
-      <c r="AJ31" s="99"/>
-      <c r="AK31" s="99"/>
-      <c r="AL31" s="99"/>
-      <c r="AM31" s="99"/>
+      <c r="B31" s="95"/>
+      <c r="C31" s="95"/>
+      <c r="D31" s="95"/>
+      <c r="E31" s="95"/>
+      <c r="F31" s="95"/>
+      <c r="G31" s="95"/>
+      <c r="H31" s="95"/>
+      <c r="I31" s="95"/>
+      <c r="J31" s="95"/>
+      <c r="K31" s="95"/>
+      <c r="L31" s="95"/>
+      <c r="M31" s="95"/>
+      <c r="N31" s="95"/>
+      <c r="O31" s="95"/>
+      <c r="P31" s="95"/>
+      <c r="Q31" s="95"/>
+      <c r="R31" s="95"/>
+      <c r="S31" s="95"/>
+      <c r="T31" s="95"/>
+      <c r="U31" s="95"/>
+      <c r="V31" s="95"/>
+      <c r="W31" s="95"/>
+      <c r="X31" s="95"/>
+      <c r="Y31" s="95"/>
+      <c r="Z31" s="95"/>
+      <c r="AA31" s="95"/>
+      <c r="AB31" s="95"/>
+      <c r="AC31" s="95"/>
+      <c r="AD31" s="95"/>
+      <c r="AE31" s="95"/>
+      <c r="AF31" s="95"/>
+      <c r="AG31" s="95"/>
+      <c r="AH31" s="95"/>
+      <c r="AI31" s="95"/>
+      <c r="AJ31" s="95"/>
+      <c r="AK31" s="95"/>
+      <c r="AL31" s="95"/>
+      <c r="AM31" s="95"/>
     </row>
     <row r="32" spans="1:39" ht="15" customHeight="1">
-      <c r="A32" s="96" t="s">
+      <c r="A32" s="98" t="s">
         <v>149</v>
       </c>
-      <c r="B32" s="96"/>
-      <c r="C32" s="96"/>
-      <c r="D32" s="96"/>
-      <c r="E32" s="96"/>
-      <c r="F32" s="96"/>
-      <c r="G32" s="96"/>
-      <c r="H32" s="96"/>
-      <c r="I32" s="96"/>
-      <c r="J32" s="96"/>
-      <c r="K32" s="96"/>
-      <c r="L32" s="96"/>
-      <c r="M32" s="96"/>
-      <c r="N32" s="96"/>
-      <c r="O32" s="96"/>
-      <c r="P32" s="96"/>
-      <c r="Q32" s="96"/>
-      <c r="R32" s="96"/>
-      <c r="S32" s="96"/>
-      <c r="T32" s="96"/>
-      <c r="U32" s="96"/>
-      <c r="V32" s="96"/>
-      <c r="W32" s="96"/>
-      <c r="X32" s="96"/>
-      <c r="Y32" s="96"/>
-      <c r="Z32" s="96"/>
-      <c r="AA32" s="96"/>
-      <c r="AB32" s="96"/>
-      <c r="AC32" s="96"/>
-      <c r="AD32" s="96"/>
-      <c r="AE32" s="96"/>
-      <c r="AF32" s="96"/>
-      <c r="AG32" s="96"/>
-      <c r="AH32" s="96"/>
-      <c r="AI32" s="96"/>
-      <c r="AJ32" s="96"/>
-      <c r="AK32" s="96"/>
-      <c r="AL32" s="96"/>
-      <c r="AM32" s="96"/>
+      <c r="B32" s="98"/>
+      <c r="C32" s="98"/>
+      <c r="D32" s="98"/>
+      <c r="E32" s="98"/>
+      <c r="F32" s="98"/>
+      <c r="G32" s="98"/>
+      <c r="H32" s="98"/>
+      <c r="I32" s="98"/>
+      <c r="J32" s="98"/>
+      <c r="K32" s="98"/>
+      <c r="L32" s="98"/>
+      <c r="M32" s="98"/>
+      <c r="N32" s="98"/>
+      <c r="O32" s="98"/>
+      <c r="P32" s="98"/>
+      <c r="Q32" s="98"/>
+      <c r="R32" s="98"/>
+      <c r="S32" s="98"/>
+      <c r="T32" s="98"/>
+      <c r="U32" s="98"/>
+      <c r="V32" s="98"/>
+      <c r="W32" s="98"/>
+      <c r="X32" s="98"/>
+      <c r="Y32" s="98"/>
+      <c r="Z32" s="98"/>
+      <c r="AA32" s="98"/>
+      <c r="AB32" s="98"/>
+      <c r="AC32" s="98"/>
+      <c r="AD32" s="98"/>
+      <c r="AE32" s="98"/>
+      <c r="AF32" s="98"/>
+      <c r="AG32" s="98"/>
+      <c r="AH32" s="98"/>
+      <c r="AI32" s="98"/>
+      <c r="AJ32" s="98"/>
+      <c r="AK32" s="98"/>
+      <c r="AL32" s="98"/>
+      <c r="AM32" s="98"/>
     </row>
     <row r="33" spans="1:39" ht="15" customHeight="1">
-      <c r="A33" s="96" t="s">
+      <c r="A33" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="96"/>
-      <c r="C33" s="96"/>
-      <c r="D33" s="96"/>
-      <c r="E33" s="96" t="s">
+      <c r="B33" s="98"/>
+      <c r="C33" s="98"/>
+      <c r="D33" s="98"/>
+      <c r="E33" s="98" t="s">
         <v>9</v>
       </c>
       <c r="F33" s="86"/>
@@ -11688,7 +12892,7 @@
       <c r="I33" s="86"/>
       <c r="J33" s="86"/>
       <c r="K33" s="86"/>
-      <c r="L33" s="96" t="s">
+      <c r="L33" s="98" t="s">
         <v>10</v>
       </c>
       <c r="M33" s="86"/>
@@ -11697,7 +12901,7 @@
       <c r="P33" s="86"/>
       <c r="Q33" s="86"/>
       <c r="R33" s="86"/>
-      <c r="S33" s="96" t="s">
+      <c r="S33" s="98" t="s">
         <v>11</v>
       </c>
       <c r="T33" s="86"/>
@@ -11706,7 +12910,7 @@
       <c r="W33" s="86"/>
       <c r="X33" s="86"/>
       <c r="Y33" s="86"/>
-      <c r="Z33" s="96" t="s">
+      <c r="Z33" s="98" t="s">
         <v>12</v>
       </c>
       <c r="AA33" s="86"/>
@@ -11715,7 +12919,7 @@
       <c r="AD33" s="86"/>
       <c r="AE33" s="86"/>
       <c r="AF33" s="86"/>
-      <c r="AG33" s="96" t="s">
+      <c r="AG33" s="98" t="s">
         <v>13</v>
       </c>
       <c r="AH33" s="86"/>
@@ -11726,39 +12930,39 @@
       <c r="AM33" s="86"/>
     </row>
     <row r="34" spans="1:39" ht="15" customHeight="1">
-      <c r="A34" s="96"/>
-      <c r="B34" s="96"/>
-      <c r="C34" s="96"/>
-      <c r="D34" s="96"/>
-      <c r="E34" s="96"/>
+      <c r="A34" s="98"/>
+      <c r="B34" s="98"/>
+      <c r="C34" s="98"/>
+      <c r="D34" s="98"/>
+      <c r="E34" s="98"/>
       <c r="F34" s="86"/>
       <c r="G34" s="86"/>
       <c r="H34" s="86"/>
       <c r="I34" s="86"/>
       <c r="J34" s="86"/>
       <c r="K34" s="86"/>
-      <c r="L34" s="96"/>
+      <c r="L34" s="98"/>
       <c r="M34" s="86"/>
       <c r="N34" s="86"/>
       <c r="O34" s="86"/>
       <c r="P34" s="86"/>
       <c r="Q34" s="86"/>
       <c r="R34" s="86"/>
-      <c r="S34" s="96"/>
+      <c r="S34" s="98"/>
       <c r="T34" s="86"/>
       <c r="U34" s="86"/>
       <c r="V34" s="86"/>
       <c r="W34" s="86"/>
       <c r="X34" s="86"/>
       <c r="Y34" s="86"/>
-      <c r="Z34" s="96"/>
+      <c r="Z34" s="98"/>
       <c r="AA34" s="86"/>
       <c r="AB34" s="86"/>
       <c r="AC34" s="86"/>
       <c r="AD34" s="86"/>
       <c r="AE34" s="86"/>
       <c r="AF34" s="86"/>
-      <c r="AG34" s="96"/>
+      <c r="AG34" s="98"/>
       <c r="AH34" s="86"/>
       <c r="AI34" s="86"/>
       <c r="AJ34" s="86"/>
@@ -11767,39 +12971,39 @@
       <c r="AM34" s="86"/>
     </row>
     <row r="35" spans="1:39" ht="15" customHeight="1">
-      <c r="A35" s="96"/>
-      <c r="B35" s="96"/>
-      <c r="C35" s="96"/>
-      <c r="D35" s="96"/>
-      <c r="E35" s="96"/>
+      <c r="A35" s="98"/>
+      <c r="B35" s="98"/>
+      <c r="C35" s="98"/>
+      <c r="D35" s="98"/>
+      <c r="E35" s="98"/>
       <c r="F35" s="86"/>
       <c r="G35" s="86"/>
       <c r="H35" s="86"/>
       <c r="I35" s="86"/>
       <c r="J35" s="86"/>
       <c r="K35" s="86"/>
-      <c r="L35" s="96"/>
+      <c r="L35" s="98"/>
       <c r="M35" s="86"/>
       <c r="N35" s="86"/>
       <c r="O35" s="86"/>
       <c r="P35" s="86"/>
       <c r="Q35" s="86"/>
       <c r="R35" s="86"/>
-      <c r="S35" s="96"/>
+      <c r="S35" s="98"/>
       <c r="T35" s="86"/>
       <c r="U35" s="86"/>
       <c r="V35" s="86"/>
       <c r="W35" s="86"/>
       <c r="X35" s="86"/>
       <c r="Y35" s="86"/>
-      <c r="Z35" s="96"/>
+      <c r="Z35" s="98"/>
       <c r="AA35" s="86"/>
       <c r="AB35" s="86"/>
       <c r="AC35" s="86"/>
       <c r="AD35" s="86"/>
       <c r="AE35" s="86"/>
       <c r="AF35" s="86"/>
-      <c r="AG35" s="96"/>
+      <c r="AG35" s="98"/>
       <c r="AH35" s="86"/>
       <c r="AI35" s="86"/>
       <c r="AJ35" s="86"/>
@@ -11808,13 +13012,13 @@
       <c r="AM35" s="86"/>
     </row>
     <row r="36" spans="1:39" ht="15" customHeight="1">
-      <c r="A36" s="96" t="s">
+      <c r="A36" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="B36" s="96"/>
-      <c r="C36" s="96"/>
-      <c r="D36" s="96"/>
-      <c r="E36" s="96" t="s">
+      <c r="B36" s="98"/>
+      <c r="C36" s="98"/>
+      <c r="D36" s="98"/>
+      <c r="E36" s="98" t="s">
         <v>128</v>
       </c>
       <c r="F36" s="86"/>
@@ -11823,7 +13027,7 @@
       <c r="I36" s="86"/>
       <c r="J36" s="86"/>
       <c r="K36" s="86"/>
-      <c r="L36" s="96" t="s">
+      <c r="L36" s="98" t="s">
         <v>129</v>
       </c>
       <c r="M36" s="86"/>
@@ -11832,7 +13036,7 @@
       <c r="P36" s="86"/>
       <c r="Q36" s="86"/>
       <c r="R36" s="86"/>
-      <c r="S36" s="96" t="s">
+      <c r="S36" s="98" t="s">
         <v>130</v>
       </c>
       <c r="T36" s="86"/>
@@ -11841,7 +13045,7 @@
       <c r="W36" s="86"/>
       <c r="X36" s="86"/>
       <c r="Y36" s="86"/>
-      <c r="Z36" s="96" t="s">
+      <c r="Z36" s="98" t="s">
         <v>131</v>
       </c>
       <c r="AA36" s="86"/>
@@ -11850,7 +13054,7 @@
       <c r="AD36" s="86"/>
       <c r="AE36" s="86"/>
       <c r="AF36" s="86"/>
-      <c r="AG36" s="96" t="s">
+      <c r="AG36" s="98" t="s">
         <v>132</v>
       </c>
       <c r="AH36" s="86"/>
@@ -11861,39 +13065,39 @@
       <c r="AM36" s="86"/>
     </row>
     <row r="37" spans="1:39" ht="15" customHeight="1">
-      <c r="A37" s="96"/>
-      <c r="B37" s="96"/>
-      <c r="C37" s="96"/>
-      <c r="D37" s="96"/>
-      <c r="E37" s="96"/>
+      <c r="A37" s="98"/>
+      <c r="B37" s="98"/>
+      <c r="C37" s="98"/>
+      <c r="D37" s="98"/>
+      <c r="E37" s="98"/>
       <c r="F37" s="86"/>
       <c r="G37" s="86"/>
       <c r="H37" s="86"/>
       <c r="I37" s="86"/>
       <c r="J37" s="86"/>
       <c r="K37" s="86"/>
-      <c r="L37" s="96"/>
+      <c r="L37" s="98"/>
       <c r="M37" s="86"/>
       <c r="N37" s="86"/>
       <c r="O37" s="86"/>
       <c r="P37" s="86"/>
       <c r="Q37" s="86"/>
       <c r="R37" s="86"/>
-      <c r="S37" s="96"/>
+      <c r="S37" s="98"/>
       <c r="T37" s="86"/>
       <c r="U37" s="86"/>
       <c r="V37" s="86"/>
       <c r="W37" s="86"/>
       <c r="X37" s="86"/>
       <c r="Y37" s="86"/>
-      <c r="Z37" s="96"/>
+      <c r="Z37" s="98"/>
       <c r="AA37" s="86"/>
       <c r="AB37" s="86"/>
       <c r="AC37" s="86"/>
       <c r="AD37" s="86"/>
       <c r="AE37" s="86"/>
       <c r="AF37" s="86"/>
-      <c r="AG37" s="96"/>
+      <c r="AG37" s="98"/>
       <c r="AH37" s="86"/>
       <c r="AI37" s="86"/>
       <c r="AJ37" s="86"/>
@@ -11902,39 +13106,39 @@
       <c r="AM37" s="86"/>
     </row>
     <row r="38" spans="1:39" ht="15" customHeight="1">
-      <c r="A38" s="96"/>
-      <c r="B38" s="96"/>
-      <c r="C38" s="96"/>
-      <c r="D38" s="96"/>
-      <c r="E38" s="96"/>
+      <c r="A38" s="98"/>
+      <c r="B38" s="98"/>
+      <c r="C38" s="98"/>
+      <c r="D38" s="98"/>
+      <c r="E38" s="98"/>
       <c r="F38" s="86"/>
       <c r="G38" s="86"/>
       <c r="H38" s="86"/>
       <c r="I38" s="86"/>
       <c r="J38" s="86"/>
       <c r="K38" s="86"/>
-      <c r="L38" s="96"/>
+      <c r="L38" s="98"/>
       <c r="M38" s="86"/>
       <c r="N38" s="86"/>
       <c r="O38" s="86"/>
       <c r="P38" s="86"/>
       <c r="Q38" s="86"/>
       <c r="R38" s="86"/>
-      <c r="S38" s="96"/>
+      <c r="S38" s="98"/>
       <c r="T38" s="86"/>
       <c r="U38" s="86"/>
       <c r="V38" s="86"/>
       <c r="W38" s="86"/>
       <c r="X38" s="86"/>
       <c r="Y38" s="86"/>
-      <c r="Z38" s="96"/>
+      <c r="Z38" s="98"/>
       <c r="AA38" s="86"/>
       <c r="AB38" s="86"/>
       <c r="AC38" s="86"/>
       <c r="AD38" s="86"/>
       <c r="AE38" s="86"/>
       <c r="AF38" s="86"/>
-      <c r="AG38" s="96"/>
+      <c r="AG38" s="98"/>
       <c r="AH38" s="86"/>
       <c r="AI38" s="86"/>
       <c r="AJ38" s="86"/>
@@ -11943,13 +13147,13 @@
       <c r="AM38" s="86"/>
     </row>
     <row r="39" spans="1:39" ht="15" customHeight="1">
-      <c r="A39" s="96" t="s">
+      <c r="A39" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="B39" s="96"/>
-      <c r="C39" s="96"/>
-      <c r="D39" s="96"/>
-      <c r="E39" s="96" t="s">
+      <c r="B39" s="98"/>
+      <c r="C39" s="98"/>
+      <c r="D39" s="98"/>
+      <c r="E39" s="98" t="s">
         <v>133</v>
       </c>
       <c r="F39" s="86"/>
@@ -11958,7 +13162,7 @@
       <c r="I39" s="86"/>
       <c r="J39" s="86"/>
       <c r="K39" s="86"/>
-      <c r="L39" s="96" t="s">
+      <c r="L39" s="98" t="s">
         <v>134</v>
       </c>
       <c r="M39" s="86"/>
@@ -11967,7 +13171,7 @@
       <c r="P39" s="86"/>
       <c r="Q39" s="86"/>
       <c r="R39" s="86"/>
-      <c r="S39" s="96" t="s">
+      <c r="S39" s="98" t="s">
         <v>135</v>
       </c>
       <c r="T39" s="86"/>
@@ -11976,7 +13180,7 @@
       <c r="W39" s="86"/>
       <c r="X39" s="86"/>
       <c r="Y39" s="86"/>
-      <c r="Z39" s="96" t="s">
+      <c r="Z39" s="98" t="s">
         <v>136</v>
       </c>
       <c r="AA39" s="86"/>
@@ -11985,7 +13189,7 @@
       <c r="AD39" s="86"/>
       <c r="AE39" s="86"/>
       <c r="AF39" s="86"/>
-      <c r="AG39" s="96" t="s">
+      <c r="AG39" s="98" t="s">
         <v>137</v>
       </c>
       <c r="AH39" s="86"/>
@@ -11996,39 +13200,39 @@
       <c r="AM39" s="86"/>
     </row>
     <row r="40" spans="1:39" ht="15" customHeight="1">
-      <c r="A40" s="96"/>
-      <c r="B40" s="96"/>
-      <c r="C40" s="96"/>
-      <c r="D40" s="96"/>
-      <c r="E40" s="96"/>
+      <c r="A40" s="98"/>
+      <c r="B40" s="98"/>
+      <c r="C40" s="98"/>
+      <c r="D40" s="98"/>
+      <c r="E40" s="98"/>
       <c r="F40" s="86"/>
       <c r="G40" s="86"/>
       <c r="H40" s="86"/>
       <c r="I40" s="86"/>
       <c r="J40" s="86"/>
       <c r="K40" s="86"/>
-      <c r="L40" s="96"/>
+      <c r="L40" s="98"/>
       <c r="M40" s="86"/>
       <c r="N40" s="86"/>
       <c r="O40" s="86"/>
       <c r="P40" s="86"/>
       <c r="Q40" s="86"/>
       <c r="R40" s="86"/>
-      <c r="S40" s="96"/>
+      <c r="S40" s="98"/>
       <c r="T40" s="86"/>
       <c r="U40" s="86"/>
       <c r="V40" s="86"/>
       <c r="W40" s="86"/>
       <c r="X40" s="86"/>
       <c r="Y40" s="86"/>
-      <c r="Z40" s="96"/>
+      <c r="Z40" s="98"/>
       <c r="AA40" s="86"/>
       <c r="AB40" s="86"/>
       <c r="AC40" s="86"/>
       <c r="AD40" s="86"/>
       <c r="AE40" s="86"/>
       <c r="AF40" s="86"/>
-      <c r="AG40" s="96"/>
+      <c r="AG40" s="98"/>
       <c r="AH40" s="86"/>
       <c r="AI40" s="86"/>
       <c r="AJ40" s="86"/>
@@ -12037,39 +13241,39 @@
       <c r="AM40" s="86"/>
     </row>
     <row r="41" spans="1:39" ht="15" customHeight="1">
-      <c r="A41" s="96"/>
-      <c r="B41" s="96"/>
-      <c r="C41" s="96"/>
-      <c r="D41" s="96"/>
-      <c r="E41" s="96"/>
+      <c r="A41" s="98"/>
+      <c r="B41" s="98"/>
+      <c r="C41" s="98"/>
+      <c r="D41" s="98"/>
+      <c r="E41" s="98"/>
       <c r="F41" s="86"/>
       <c r="G41" s="86"/>
       <c r="H41" s="86"/>
       <c r="I41" s="86"/>
       <c r="J41" s="86"/>
       <c r="K41" s="86"/>
-      <c r="L41" s="96"/>
+      <c r="L41" s="98"/>
       <c r="M41" s="86"/>
       <c r="N41" s="86"/>
       <c r="O41" s="86"/>
       <c r="P41" s="86"/>
       <c r="Q41" s="86"/>
       <c r="R41" s="86"/>
-      <c r="S41" s="96"/>
+      <c r="S41" s="98"/>
       <c r="T41" s="86"/>
       <c r="U41" s="86"/>
       <c r="V41" s="86"/>
       <c r="W41" s="86"/>
       <c r="X41" s="86"/>
       <c r="Y41" s="86"/>
-      <c r="Z41" s="96"/>
+      <c r="Z41" s="98"/>
       <c r="AA41" s="86"/>
       <c r="AB41" s="86"/>
       <c r="AC41" s="86"/>
       <c r="AD41" s="86"/>
       <c r="AE41" s="86"/>
       <c r="AF41" s="86"/>
-      <c r="AG41" s="96"/>
+      <c r="AG41" s="98"/>
       <c r="AH41" s="86"/>
       <c r="AI41" s="86"/>
       <c r="AJ41" s="86"/>
@@ -12078,13 +13282,13 @@
       <c r="AM41" s="86"/>
     </row>
     <row r="42" spans="1:39" ht="15" customHeight="1">
-      <c r="A42" s="96" t="s">
+      <c r="A42" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="B42" s="96"/>
-      <c r="C42" s="96"/>
-      <c r="D42" s="96"/>
-      <c r="E42" s="96" t="s">
+      <c r="B42" s="98"/>
+      <c r="C42" s="98"/>
+      <c r="D42" s="98"/>
+      <c r="E42" s="98" t="s">
         <v>138</v>
       </c>
       <c r="F42" s="86"/>
@@ -12093,7 +13297,7 @@
       <c r="I42" s="86"/>
       <c r="J42" s="86"/>
       <c r="K42" s="86"/>
-      <c r="L42" s="96" t="s">
+      <c r="L42" s="98" t="s">
         <v>139</v>
       </c>
       <c r="M42" s="86"/>
@@ -12102,7 +13306,7 @@
       <c r="P42" s="86"/>
       <c r="Q42" s="86"/>
       <c r="R42" s="86"/>
-      <c r="S42" s="96" t="s">
+      <c r="S42" s="98" t="s">
         <v>140</v>
       </c>
       <c r="T42" s="86"/>
@@ -12111,7 +13315,7 @@
       <c r="W42" s="86"/>
       <c r="X42" s="86"/>
       <c r="Y42" s="86"/>
-      <c r="Z42" s="96" t="s">
+      <c r="Z42" s="98" t="s">
         <v>141</v>
       </c>
       <c r="AA42" s="86"/>
@@ -12120,7 +13324,7 @@
       <c r="AD42" s="86"/>
       <c r="AE42" s="86"/>
       <c r="AF42" s="86"/>
-      <c r="AG42" s="96" t="s">
+      <c r="AG42" s="98" t="s">
         <v>142</v>
       </c>
       <c r="AH42" s="86"/>
@@ -12131,39 +13335,39 @@
       <c r="AM42" s="86"/>
     </row>
     <row r="43" spans="1:39" ht="15" customHeight="1">
-      <c r="A43" s="96"/>
-      <c r="B43" s="96"/>
-      <c r="C43" s="96"/>
-      <c r="D43" s="96"/>
-      <c r="E43" s="96"/>
+      <c r="A43" s="98"/>
+      <c r="B43" s="98"/>
+      <c r="C43" s="98"/>
+      <c r="D43" s="98"/>
+      <c r="E43" s="98"/>
       <c r="F43" s="86"/>
       <c r="G43" s="86"/>
       <c r="H43" s="86"/>
       <c r="I43" s="86"/>
       <c r="J43" s="86"/>
       <c r="K43" s="86"/>
-      <c r="L43" s="96"/>
+      <c r="L43" s="98"/>
       <c r="M43" s="86"/>
       <c r="N43" s="86"/>
       <c r="O43" s="86"/>
       <c r="P43" s="86"/>
       <c r="Q43" s="86"/>
       <c r="R43" s="86"/>
-      <c r="S43" s="96"/>
+      <c r="S43" s="98"/>
       <c r="T43" s="86"/>
       <c r="U43" s="86"/>
       <c r="V43" s="86"/>
       <c r="W43" s="86"/>
       <c r="X43" s="86"/>
       <c r="Y43" s="86"/>
-      <c r="Z43" s="96"/>
+      <c r="Z43" s="98"/>
       <c r="AA43" s="86"/>
       <c r="AB43" s="86"/>
       <c r="AC43" s="86"/>
       <c r="AD43" s="86"/>
       <c r="AE43" s="86"/>
       <c r="AF43" s="86"/>
-      <c r="AG43" s="96"/>
+      <c r="AG43" s="98"/>
       <c r="AH43" s="86"/>
       <c r="AI43" s="86"/>
       <c r="AJ43" s="86"/>
@@ -12172,39 +13376,39 @@
       <c r="AM43" s="86"/>
     </row>
     <row r="44" spans="1:39" ht="15" customHeight="1">
-      <c r="A44" s="96"/>
-      <c r="B44" s="96"/>
-      <c r="C44" s="96"/>
-      <c r="D44" s="96"/>
-      <c r="E44" s="96"/>
+      <c r="A44" s="98"/>
+      <c r="B44" s="98"/>
+      <c r="C44" s="98"/>
+      <c r="D44" s="98"/>
+      <c r="E44" s="98"/>
       <c r="F44" s="86"/>
       <c r="G44" s="86"/>
       <c r="H44" s="86"/>
       <c r="I44" s="86"/>
       <c r="J44" s="86"/>
       <c r="K44" s="86"/>
-      <c r="L44" s="96"/>
+      <c r="L44" s="98"/>
       <c r="M44" s="86"/>
       <c r="N44" s="86"/>
       <c r="O44" s="86"/>
       <c r="P44" s="86"/>
       <c r="Q44" s="86"/>
       <c r="R44" s="86"/>
-      <c r="S44" s="96"/>
+      <c r="S44" s="98"/>
       <c r="T44" s="86"/>
       <c r="U44" s="86"/>
       <c r="V44" s="86"/>
       <c r="W44" s="86"/>
       <c r="X44" s="86"/>
       <c r="Y44" s="86"/>
-      <c r="Z44" s="96"/>
+      <c r="Z44" s="98"/>
       <c r="AA44" s="86"/>
       <c r="AB44" s="86"/>
       <c r="AC44" s="86"/>
       <c r="AD44" s="86"/>
       <c r="AE44" s="86"/>
       <c r="AF44" s="86"/>
-      <c r="AG44" s="96"/>
+      <c r="AG44" s="98"/>
       <c r="AH44" s="86"/>
       <c r="AI44" s="86"/>
       <c r="AJ44" s="86"/>
@@ -12213,215 +13417,215 @@
       <c r="AM44" s="86"/>
     </row>
     <row r="45" spans="1:39" ht="15" customHeight="1">
-      <c r="A45" s="99" t="s">
+      <c r="A45" s="95" t="s">
         <v>150</v>
       </c>
-      <c r="B45" s="99"/>
-      <c r="C45" s="99"/>
-      <c r="D45" s="99"/>
-      <c r="E45" s="99"/>
-      <c r="F45" s="99"/>
-      <c r="G45" s="99"/>
-      <c r="H45" s="99"/>
-      <c r="I45" s="99"/>
-      <c r="J45" s="99"/>
-      <c r="K45" s="99"/>
-      <c r="L45" s="99"/>
-      <c r="M45" s="99"/>
-      <c r="N45" s="99"/>
-      <c r="O45" s="99"/>
-      <c r="P45" s="99"/>
-      <c r="Q45" s="99"/>
-      <c r="R45" s="99"/>
-      <c r="S45" s="99"/>
-      <c r="T45" s="99"/>
-      <c r="U45" s="99"/>
-      <c r="V45" s="99"/>
-      <c r="W45" s="99"/>
-      <c r="X45" s="99"/>
-      <c r="Y45" s="99"/>
-      <c r="Z45" s="99"/>
-      <c r="AA45" s="99"/>
-      <c r="AB45" s="99"/>
-      <c r="AC45" s="99"/>
-      <c r="AD45" s="99"/>
-      <c r="AE45" s="99"/>
-      <c r="AF45" s="99"/>
-      <c r="AG45" s="99"/>
-      <c r="AH45" s="99"/>
-      <c r="AI45" s="99"/>
-      <c r="AJ45" s="99"/>
-      <c r="AK45" s="99"/>
-      <c r="AL45" s="99"/>
-      <c r="AM45" s="99"/>
+      <c r="B45" s="95"/>
+      <c r="C45" s="95"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
+      <c r="F45" s="95"/>
+      <c r="G45" s="95"/>
+      <c r="H45" s="95"/>
+      <c r="I45" s="95"/>
+      <c r="J45" s="95"/>
+      <c r="K45" s="95"/>
+      <c r="L45" s="95"/>
+      <c r="M45" s="95"/>
+      <c r="N45" s="95"/>
+      <c r="O45" s="95"/>
+      <c r="P45" s="95"/>
+      <c r="Q45" s="95"/>
+      <c r="R45" s="95"/>
+      <c r="S45" s="95"/>
+      <c r="T45" s="95"/>
+      <c r="U45" s="95"/>
+      <c r="V45" s="95"/>
+      <c r="W45" s="95"/>
+      <c r="X45" s="95"/>
+      <c r="Y45" s="95"/>
+      <c r="Z45" s="95"/>
+      <c r="AA45" s="95"/>
+      <c r="AB45" s="95"/>
+      <c r="AC45" s="95"/>
+      <c r="AD45" s="95"/>
+      <c r="AE45" s="95"/>
+      <c r="AF45" s="95"/>
+      <c r="AG45" s="95"/>
+      <c r="AH45" s="95"/>
+      <c r="AI45" s="95"/>
+      <c r="AJ45" s="95"/>
+      <c r="AK45" s="95"/>
+      <c r="AL45" s="95"/>
+      <c r="AM45" s="95"/>
     </row>
     <row r="46" spans="1:39" ht="15" customHeight="1">
-      <c r="A46" s="99" t="s">
+      <c r="A46" s="95" t="s">
         <v>151</v>
       </c>
-      <c r="B46" s="99"/>
-      <c r="C46" s="99"/>
-      <c r="D46" s="99"/>
-      <c r="E46" s="99"/>
-      <c r="F46" s="99"/>
-      <c r="G46" s="99"/>
-      <c r="H46" s="99"/>
-      <c r="I46" s="99"/>
-      <c r="J46" s="99"/>
-      <c r="K46" s="99"/>
-      <c r="L46" s="99"/>
-      <c r="M46" s="99"/>
-      <c r="N46" s="99"/>
-      <c r="O46" s="99"/>
-      <c r="P46" s="99"/>
-      <c r="Q46" s="99"/>
-      <c r="R46" s="99"/>
-      <c r="S46" s="99"/>
-      <c r="T46" s="99"/>
-      <c r="U46" s="99"/>
-      <c r="V46" s="99"/>
-      <c r="W46" s="99"/>
-      <c r="X46" s="99"/>
-      <c r="Y46" s="99"/>
-      <c r="Z46" s="99"/>
-      <c r="AA46" s="99"/>
-      <c r="AB46" s="99"/>
-      <c r="AC46" s="99"/>
-      <c r="AD46" s="99"/>
-      <c r="AE46" s="99"/>
-      <c r="AF46" s="99"/>
-      <c r="AG46" s="99"/>
-      <c r="AH46" s="99"/>
-      <c r="AI46" s="99"/>
-      <c r="AJ46" s="99"/>
-      <c r="AK46" s="99"/>
-      <c r="AL46" s="99"/>
-      <c r="AM46" s="99"/>
+      <c r="B46" s="95"/>
+      <c r="C46" s="95"/>
+      <c r="D46" s="95"/>
+      <c r="E46" s="95"/>
+      <c r="F46" s="95"/>
+      <c r="G46" s="95"/>
+      <c r="H46" s="95"/>
+      <c r="I46" s="95"/>
+      <c r="J46" s="95"/>
+      <c r="K46" s="95"/>
+      <c r="L46" s="95"/>
+      <c r="M46" s="95"/>
+      <c r="N46" s="95"/>
+      <c r="O46" s="95"/>
+      <c r="P46" s="95"/>
+      <c r="Q46" s="95"/>
+      <c r="R46" s="95"/>
+      <c r="S46" s="95"/>
+      <c r="T46" s="95"/>
+      <c r="U46" s="95"/>
+      <c r="V46" s="95"/>
+      <c r="W46" s="95"/>
+      <c r="X46" s="95"/>
+      <c r="Y46" s="95"/>
+      <c r="Z46" s="95"/>
+      <c r="AA46" s="95"/>
+      <c r="AB46" s="95"/>
+      <c r="AC46" s="95"/>
+      <c r="AD46" s="95"/>
+      <c r="AE46" s="95"/>
+      <c r="AF46" s="95"/>
+      <c r="AG46" s="95"/>
+      <c r="AH46" s="95"/>
+      <c r="AI46" s="95"/>
+      <c r="AJ46" s="95"/>
+      <c r="AK46" s="95"/>
+      <c r="AL46" s="95"/>
+      <c r="AM46" s="95"/>
     </row>
     <row r="47" spans="1:39" ht="15" customHeight="1">
-      <c r="A47" s="100" t="s">
+      <c r="A47" s="96" t="s">
         <v>152</v>
       </c>
-      <c r="B47" s="101"/>
-      <c r="C47" s="101"/>
-      <c r="D47" s="101"/>
-      <c r="E47" s="101"/>
-      <c r="F47" s="101"/>
-      <c r="G47" s="101"/>
-      <c r="H47" s="101"/>
-      <c r="I47" s="101"/>
-      <c r="J47" s="101"/>
-      <c r="K47" s="101"/>
-      <c r="L47" s="101"/>
-      <c r="M47" s="101"/>
-      <c r="N47" s="101"/>
-      <c r="O47" s="101"/>
-      <c r="P47" s="101"/>
-      <c r="Q47" s="101"/>
-      <c r="R47" s="101"/>
-      <c r="S47" s="101"/>
-      <c r="T47" s="101"/>
-      <c r="U47" s="101"/>
-      <c r="V47" s="101"/>
-      <c r="W47" s="101"/>
-      <c r="X47" s="101"/>
-      <c r="Y47" s="101"/>
-      <c r="Z47" s="101"/>
-      <c r="AA47" s="101"/>
-      <c r="AB47" s="101"/>
-      <c r="AC47" s="101"/>
-      <c r="AD47" s="101"/>
-      <c r="AE47" s="101"/>
-      <c r="AF47" s="101"/>
-      <c r="AG47" s="101"/>
-      <c r="AH47" s="101"/>
-      <c r="AI47" s="101"/>
-      <c r="AJ47" s="101"/>
-      <c r="AK47" s="101"/>
-      <c r="AL47" s="101"/>
-      <c r="AM47" s="101"/>
+      <c r="B47" s="97"/>
+      <c r="C47" s="97"/>
+      <c r="D47" s="97"/>
+      <c r="E47" s="97"/>
+      <c r="F47" s="97"/>
+      <c r="G47" s="97"/>
+      <c r="H47" s="97"/>
+      <c r="I47" s="97"/>
+      <c r="J47" s="97"/>
+      <c r="K47" s="97"/>
+      <c r="L47" s="97"/>
+      <c r="M47" s="97"/>
+      <c r="N47" s="97"/>
+      <c r="O47" s="97"/>
+      <c r="P47" s="97"/>
+      <c r="Q47" s="97"/>
+      <c r="R47" s="97"/>
+      <c r="S47" s="97"/>
+      <c r="T47" s="97"/>
+      <c r="U47" s="97"/>
+      <c r="V47" s="97"/>
+      <c r="W47" s="97"/>
+      <c r="X47" s="97"/>
+      <c r="Y47" s="97"/>
+      <c r="Z47" s="97"/>
+      <c r="AA47" s="97"/>
+      <c r="AB47" s="97"/>
+      <c r="AC47" s="97"/>
+      <c r="AD47" s="97"/>
+      <c r="AE47" s="97"/>
+      <c r="AF47" s="97"/>
+      <c r="AG47" s="97"/>
+      <c r="AH47" s="97"/>
+      <c r="AI47" s="97"/>
+      <c r="AJ47" s="97"/>
+      <c r="AK47" s="97"/>
+      <c r="AL47" s="97"/>
+      <c r="AM47" s="97"/>
     </row>
     <row r="48" spans="1:39" ht="15" customHeight="1">
-      <c r="A48" s="101"/>
-      <c r="B48" s="101"/>
-      <c r="C48" s="101"/>
-      <c r="D48" s="101"/>
-      <c r="E48" s="101"/>
-      <c r="F48" s="101"/>
-      <c r="G48" s="101"/>
-      <c r="H48" s="101"/>
-      <c r="I48" s="101"/>
-      <c r="J48" s="101"/>
-      <c r="K48" s="101"/>
-      <c r="L48" s="101"/>
-      <c r="M48" s="101"/>
-      <c r="N48" s="101"/>
-      <c r="O48" s="101"/>
-      <c r="P48" s="101"/>
-      <c r="Q48" s="101"/>
-      <c r="R48" s="101"/>
-      <c r="S48" s="101"/>
-      <c r="T48" s="101"/>
-      <c r="U48" s="101"/>
-      <c r="V48" s="101"/>
-      <c r="W48" s="101"/>
-      <c r="X48" s="101"/>
-      <c r="Y48" s="101"/>
-      <c r="Z48" s="101"/>
-      <c r="AA48" s="101"/>
-      <c r="AB48" s="101"/>
-      <c r="AC48" s="101"/>
-      <c r="AD48" s="101"/>
-      <c r="AE48" s="101"/>
-      <c r="AF48" s="101"/>
-      <c r="AG48" s="101"/>
-      <c r="AH48" s="101"/>
-      <c r="AI48" s="101"/>
-      <c r="AJ48" s="101"/>
-      <c r="AK48" s="101"/>
-      <c r="AL48" s="101"/>
-      <c r="AM48" s="101"/>
+      <c r="A48" s="97"/>
+      <c r="B48" s="97"/>
+      <c r="C48" s="97"/>
+      <c r="D48" s="97"/>
+      <c r="E48" s="97"/>
+      <c r="F48" s="97"/>
+      <c r="G48" s="97"/>
+      <c r="H48" s="97"/>
+      <c r="I48" s="97"/>
+      <c r="J48" s="97"/>
+      <c r="K48" s="97"/>
+      <c r="L48" s="97"/>
+      <c r="M48" s="97"/>
+      <c r="N48" s="97"/>
+      <c r="O48" s="97"/>
+      <c r="P48" s="97"/>
+      <c r="Q48" s="97"/>
+      <c r="R48" s="97"/>
+      <c r="S48" s="97"/>
+      <c r="T48" s="97"/>
+      <c r="U48" s="97"/>
+      <c r="V48" s="97"/>
+      <c r="W48" s="97"/>
+      <c r="X48" s="97"/>
+      <c r="Y48" s="97"/>
+      <c r="Z48" s="97"/>
+      <c r="AA48" s="97"/>
+      <c r="AB48" s="97"/>
+      <c r="AC48" s="97"/>
+      <c r="AD48" s="97"/>
+      <c r="AE48" s="97"/>
+      <c r="AF48" s="97"/>
+      <c r="AG48" s="97"/>
+      <c r="AH48" s="97"/>
+      <c r="AI48" s="97"/>
+      <c r="AJ48" s="97"/>
+      <c r="AK48" s="97"/>
+      <c r="AL48" s="97"/>
+      <c r="AM48" s="97"/>
     </row>
     <row r="49" spans="1:39" ht="15" customHeight="1">
-      <c r="A49" s="101"/>
-      <c r="B49" s="101"/>
-      <c r="C49" s="101"/>
-      <c r="D49" s="101"/>
-      <c r="E49" s="101"/>
-      <c r="F49" s="101"/>
-      <c r="G49" s="101"/>
-      <c r="H49" s="101"/>
-      <c r="I49" s="101"/>
-      <c r="J49" s="101"/>
-      <c r="K49" s="101"/>
-      <c r="L49" s="101"/>
-      <c r="M49" s="101"/>
-      <c r="N49" s="101"/>
-      <c r="O49" s="101"/>
-      <c r="P49" s="101"/>
-      <c r="Q49" s="101"/>
-      <c r="R49" s="101"/>
-      <c r="S49" s="101"/>
-      <c r="T49" s="101"/>
-      <c r="U49" s="101"/>
-      <c r="V49" s="101"/>
-      <c r="W49" s="101"/>
-      <c r="X49" s="101"/>
-      <c r="Y49" s="101"/>
-      <c r="Z49" s="101"/>
-      <c r="AA49" s="101"/>
-      <c r="AB49" s="101"/>
-      <c r="AC49" s="101"/>
-      <c r="AD49" s="101"/>
-      <c r="AE49" s="101"/>
-      <c r="AF49" s="101"/>
-      <c r="AG49" s="101"/>
-      <c r="AH49" s="101"/>
-      <c r="AI49" s="101"/>
-      <c r="AJ49" s="101"/>
-      <c r="AK49" s="101"/>
-      <c r="AL49" s="101"/>
-      <c r="AM49" s="101"/>
+      <c r="A49" s="97"/>
+      <c r="B49" s="97"/>
+      <c r="C49" s="97"/>
+      <c r="D49" s="97"/>
+      <c r="E49" s="97"/>
+      <c r="F49" s="97"/>
+      <c r="G49" s="97"/>
+      <c r="H49" s="97"/>
+      <c r="I49" s="97"/>
+      <c r="J49" s="97"/>
+      <c r="K49" s="97"/>
+      <c r="L49" s="97"/>
+      <c r="M49" s="97"/>
+      <c r="N49" s="97"/>
+      <c r="O49" s="97"/>
+      <c r="P49" s="97"/>
+      <c r="Q49" s="97"/>
+      <c r="R49" s="97"/>
+      <c r="S49" s="97"/>
+      <c r="T49" s="97"/>
+      <c r="U49" s="97"/>
+      <c r="V49" s="97"/>
+      <c r="W49" s="97"/>
+      <c r="X49" s="97"/>
+      <c r="Y49" s="97"/>
+      <c r="Z49" s="97"/>
+      <c r="AA49" s="97"/>
+      <c r="AB49" s="97"/>
+      <c r="AC49" s="97"/>
+      <c r="AD49" s="97"/>
+      <c r="AE49" s="97"/>
+      <c r="AF49" s="97"/>
+      <c r="AG49" s="97"/>
+      <c r="AH49" s="97"/>
+      <c r="AI49" s="97"/>
+      <c r="AJ49" s="97"/>
+      <c r="AK49" s="97"/>
+      <c r="AL49" s="97"/>
+      <c r="AM49" s="97"/>
     </row>
     <row r="50" spans="1:39" ht="8.5500000000000007" customHeight="1">
       <c r="A50" s="46"/>
@@ -12733,132 +13937,32 @@
     </row>
   </sheetData>
   <mergeCells count="175">
-    <mergeCell ref="A45:AM45"/>
-    <mergeCell ref="A46:AM46"/>
-    <mergeCell ref="A47:AM49"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="E44:K44"/>
-    <mergeCell ref="L44:R44"/>
-    <mergeCell ref="S44:Y44"/>
-    <mergeCell ref="Z44:AF44"/>
-    <mergeCell ref="AG44:AM44"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="E43:K43"/>
-    <mergeCell ref="L43:R43"/>
-    <mergeCell ref="S43:Y43"/>
-    <mergeCell ref="Z43:AF43"/>
-    <mergeCell ref="AG43:AM43"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="E42:K42"/>
-    <mergeCell ref="L42:R42"/>
-    <mergeCell ref="S42:Y42"/>
-    <mergeCell ref="Z42:AF42"/>
-    <mergeCell ref="AG42:AM42"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="E41:K41"/>
-    <mergeCell ref="L41:R41"/>
-    <mergeCell ref="S41:Y41"/>
-    <mergeCell ref="Z41:AF41"/>
-    <mergeCell ref="AG41:AM41"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="E40:K40"/>
-    <mergeCell ref="L40:R40"/>
-    <mergeCell ref="S40:Y40"/>
-    <mergeCell ref="Z40:AF40"/>
-    <mergeCell ref="AG40:AM40"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="E39:K39"/>
-    <mergeCell ref="L39:R39"/>
-    <mergeCell ref="S39:Y39"/>
-    <mergeCell ref="Z39:AF39"/>
-    <mergeCell ref="AG39:AM39"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="E38:K38"/>
-    <mergeCell ref="L38:R38"/>
-    <mergeCell ref="S38:Y38"/>
-    <mergeCell ref="Z38:AF38"/>
-    <mergeCell ref="AG38:AM38"/>
-    <mergeCell ref="AG37:AM37"/>
-    <mergeCell ref="AG35:AM35"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="E36:K36"/>
-    <mergeCell ref="L36:R36"/>
-    <mergeCell ref="S36:Y36"/>
-    <mergeCell ref="Z36:AF36"/>
-    <mergeCell ref="AG36:AM36"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="E35:K35"/>
-    <mergeCell ref="L35:R35"/>
-    <mergeCell ref="S35:Y35"/>
-    <mergeCell ref="Z35:AF35"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="E37:K37"/>
-    <mergeCell ref="L37:R37"/>
-    <mergeCell ref="S37:Y37"/>
-    <mergeCell ref="Z37:AF37"/>
-    <mergeCell ref="A31:AM31"/>
-    <mergeCell ref="A32:AM32"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="E33:K33"/>
-    <mergeCell ref="L33:R33"/>
-    <mergeCell ref="S33:Y33"/>
-    <mergeCell ref="Z33:AF33"/>
-    <mergeCell ref="AG33:AM33"/>
-    <mergeCell ref="E34:K34"/>
-    <mergeCell ref="L34:R34"/>
-    <mergeCell ref="S34:Y34"/>
-    <mergeCell ref="Z34:AF34"/>
-    <mergeCell ref="AG34:AM34"/>
-    <mergeCell ref="V23:X23"/>
-    <mergeCell ref="A25:AM25"/>
-    <mergeCell ref="A26:AM26"/>
-    <mergeCell ref="A27:AM27"/>
-    <mergeCell ref="A28:AM28"/>
-    <mergeCell ref="A30:AM30"/>
-    <mergeCell ref="V24:X24"/>
-    <mergeCell ref="Y24:AA24"/>
-    <mergeCell ref="AB24:AD24"/>
-    <mergeCell ref="AE24:AG24"/>
-    <mergeCell ref="AH24:AJ24"/>
-    <mergeCell ref="AK24:AM24"/>
-    <mergeCell ref="A24:I24"/>
-    <mergeCell ref="J24:L24"/>
-    <mergeCell ref="M24:O24"/>
-    <mergeCell ref="P24:R24"/>
-    <mergeCell ref="S24:U24"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="M23:O23"/>
-    <mergeCell ref="P23:R23"/>
-    <mergeCell ref="S23:U23"/>
-    <mergeCell ref="AK22:AM22"/>
-    <mergeCell ref="Y20:AA20"/>
-    <mergeCell ref="AB20:AD20"/>
-    <mergeCell ref="AE20:AG20"/>
-    <mergeCell ref="AH20:AJ20"/>
-    <mergeCell ref="AK20:AM20"/>
-    <mergeCell ref="Y23:AA23"/>
-    <mergeCell ref="AB23:AD23"/>
-    <mergeCell ref="AE23:AG23"/>
-    <mergeCell ref="AH23:AJ23"/>
-    <mergeCell ref="AK23:AM23"/>
-    <mergeCell ref="A22:I22"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="M22:O22"/>
-    <mergeCell ref="P22:R22"/>
-    <mergeCell ref="S22:U22"/>
-    <mergeCell ref="Y19:AA19"/>
-    <mergeCell ref="AB19:AD19"/>
-    <mergeCell ref="AE19:AG19"/>
-    <mergeCell ref="AH19:AJ19"/>
-    <mergeCell ref="A20:I20"/>
-    <mergeCell ref="A19:I19"/>
-    <mergeCell ref="V22:X22"/>
-    <mergeCell ref="Y22:AA22"/>
-    <mergeCell ref="AB22:AD22"/>
-    <mergeCell ref="AE22:AG22"/>
-    <mergeCell ref="AH22:AJ22"/>
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="A10:L10"/>
+    <mergeCell ref="A11:L11"/>
+    <mergeCell ref="A9:L9"/>
+    <mergeCell ref="M7:U7"/>
+    <mergeCell ref="V7:AD7"/>
+    <mergeCell ref="AE7:AM7"/>
+    <mergeCell ref="M8:U8"/>
+    <mergeCell ref="V8:AD8"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="M11:U11"/>
+    <mergeCell ref="V11:AD11"/>
+    <mergeCell ref="AE11:AM11"/>
+    <mergeCell ref="A7:L7"/>
+    <mergeCell ref="A8:L8"/>
+    <mergeCell ref="A2:W2"/>
+    <mergeCell ref="A16:AM16"/>
+    <mergeCell ref="AE8:AM8"/>
+    <mergeCell ref="M9:U9"/>
+    <mergeCell ref="V9:AD9"/>
+    <mergeCell ref="AE9:AM9"/>
+    <mergeCell ref="M10:U10"/>
+    <mergeCell ref="V10:AD10"/>
+    <mergeCell ref="AE10:AM10"/>
+    <mergeCell ref="A17:AM17"/>
     <mergeCell ref="A18:AM18"/>
     <mergeCell ref="A21:I21"/>
     <mergeCell ref="J21:L21"/>
@@ -12882,32 +13986,132 @@
     <mergeCell ref="P19:R19"/>
     <mergeCell ref="S19:U19"/>
     <mergeCell ref="V19:X19"/>
-    <mergeCell ref="A16:AM16"/>
-    <mergeCell ref="AE8:AM8"/>
-    <mergeCell ref="M9:U9"/>
-    <mergeCell ref="V9:AD9"/>
-    <mergeCell ref="AE9:AM9"/>
-    <mergeCell ref="M10:U10"/>
-    <mergeCell ref="V10:AD10"/>
-    <mergeCell ref="AE10:AM10"/>
-    <mergeCell ref="A17:AM17"/>
-    <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="A10:L10"/>
-    <mergeCell ref="A11:L11"/>
-    <mergeCell ref="A9:L9"/>
-    <mergeCell ref="M7:U7"/>
-    <mergeCell ref="V7:AD7"/>
-    <mergeCell ref="AE7:AM7"/>
-    <mergeCell ref="M8:U8"/>
-    <mergeCell ref="V8:AD8"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="M11:U11"/>
-    <mergeCell ref="V11:AD11"/>
-    <mergeCell ref="AE11:AM11"/>
-    <mergeCell ref="A7:L7"/>
-    <mergeCell ref="A8:L8"/>
-    <mergeCell ref="A2:W2"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="M22:O22"/>
+    <mergeCell ref="P22:R22"/>
+    <mergeCell ref="S22:U22"/>
+    <mergeCell ref="Y19:AA19"/>
+    <mergeCell ref="AB19:AD19"/>
+    <mergeCell ref="AE19:AG19"/>
+    <mergeCell ref="AH19:AJ19"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="V22:X22"/>
+    <mergeCell ref="Y22:AA22"/>
+    <mergeCell ref="AB22:AD22"/>
+    <mergeCell ref="AE22:AG22"/>
+    <mergeCell ref="AH22:AJ22"/>
+    <mergeCell ref="AK22:AM22"/>
+    <mergeCell ref="Y20:AA20"/>
+    <mergeCell ref="AB20:AD20"/>
+    <mergeCell ref="AE20:AG20"/>
+    <mergeCell ref="AH20:AJ20"/>
+    <mergeCell ref="AK20:AM20"/>
+    <mergeCell ref="Y23:AA23"/>
+    <mergeCell ref="AB23:AD23"/>
+    <mergeCell ref="AE23:AG23"/>
+    <mergeCell ref="AH23:AJ23"/>
+    <mergeCell ref="AK23:AM23"/>
+    <mergeCell ref="V23:X23"/>
+    <mergeCell ref="A25:AM25"/>
+    <mergeCell ref="A26:AM26"/>
+    <mergeCell ref="A27:AM27"/>
+    <mergeCell ref="A28:AM28"/>
+    <mergeCell ref="A30:AM30"/>
+    <mergeCell ref="V24:X24"/>
+    <mergeCell ref="Y24:AA24"/>
+    <mergeCell ref="AB24:AD24"/>
+    <mergeCell ref="AE24:AG24"/>
+    <mergeCell ref="AH24:AJ24"/>
+    <mergeCell ref="AK24:AM24"/>
+    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="J24:L24"/>
+    <mergeCell ref="M24:O24"/>
+    <mergeCell ref="P24:R24"/>
+    <mergeCell ref="S24:U24"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="M23:O23"/>
+    <mergeCell ref="P23:R23"/>
+    <mergeCell ref="S23:U23"/>
+    <mergeCell ref="A31:AM31"/>
+    <mergeCell ref="A32:AM32"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="E33:K33"/>
+    <mergeCell ref="L33:R33"/>
+    <mergeCell ref="S33:Y33"/>
+    <mergeCell ref="Z33:AF33"/>
+    <mergeCell ref="AG33:AM33"/>
+    <mergeCell ref="E34:K34"/>
+    <mergeCell ref="L34:R34"/>
+    <mergeCell ref="S34:Y34"/>
+    <mergeCell ref="Z34:AF34"/>
+    <mergeCell ref="AG34:AM34"/>
+    <mergeCell ref="AG37:AM37"/>
+    <mergeCell ref="AG35:AM35"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="E36:K36"/>
+    <mergeCell ref="L36:R36"/>
+    <mergeCell ref="S36:Y36"/>
+    <mergeCell ref="Z36:AF36"/>
+    <mergeCell ref="AG36:AM36"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="E35:K35"/>
+    <mergeCell ref="L35:R35"/>
+    <mergeCell ref="S35:Y35"/>
+    <mergeCell ref="Z35:AF35"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="E37:K37"/>
+    <mergeCell ref="L37:R37"/>
+    <mergeCell ref="S37:Y37"/>
+    <mergeCell ref="Z37:AF37"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="E39:K39"/>
+    <mergeCell ref="L39:R39"/>
+    <mergeCell ref="S39:Y39"/>
+    <mergeCell ref="Z39:AF39"/>
+    <mergeCell ref="AG39:AM39"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="E38:K38"/>
+    <mergeCell ref="L38:R38"/>
+    <mergeCell ref="S38:Y38"/>
+    <mergeCell ref="Z38:AF38"/>
+    <mergeCell ref="AG38:AM38"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="E41:K41"/>
+    <mergeCell ref="L41:R41"/>
+    <mergeCell ref="S41:Y41"/>
+    <mergeCell ref="Z41:AF41"/>
+    <mergeCell ref="AG41:AM41"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="E40:K40"/>
+    <mergeCell ref="L40:R40"/>
+    <mergeCell ref="S40:Y40"/>
+    <mergeCell ref="Z40:AF40"/>
+    <mergeCell ref="AG40:AM40"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="E43:K43"/>
+    <mergeCell ref="L43:R43"/>
+    <mergeCell ref="S43:Y43"/>
+    <mergeCell ref="Z43:AF43"/>
+    <mergeCell ref="AG43:AM43"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="E42:K42"/>
+    <mergeCell ref="L42:R42"/>
+    <mergeCell ref="S42:Y42"/>
+    <mergeCell ref="Z42:AF42"/>
+    <mergeCell ref="AG42:AM42"/>
+    <mergeCell ref="A45:AM45"/>
+    <mergeCell ref="A46:AM46"/>
+    <mergeCell ref="A47:AM49"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="E44:K44"/>
+    <mergeCell ref="L44:R44"/>
+    <mergeCell ref="S44:Y44"/>
+    <mergeCell ref="Z44:AF44"/>
+    <mergeCell ref="AG44:AM44"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -12924,7 +14128,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BE5942F-1490-4247-AC39-F63BE022496D}">
   <dimension ref="A1:AM62"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
@@ -12947,32 +14151,32 @@
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
-      <c r="M1" s="72"/>
-      <c r="N1" s="72"/>
-      <c r="O1" s="72"/>
-      <c r="P1" s="72"/>
-      <c r="Q1" s="72"/>
-      <c r="R1" s="72"/>
-      <c r="S1" s="72"/>
-      <c r="T1" s="72"/>
-      <c r="U1" s="72"/>
-      <c r="V1" s="72"/>
-      <c r="W1" s="72"/>
-      <c r="X1" s="72"/>
-      <c r="Y1" s="72"/>
-      <c r="Z1" s="72"/>
-      <c r="AA1" s="72"/>
-      <c r="AB1" s="72"/>
-      <c r="AC1" s="72"/>
-      <c r="AD1" s="72"/>
-      <c r="AE1" s="72"/>
-      <c r="AF1" s="72"/>
-      <c r="AG1" s="72"/>
-      <c r="AH1" s="72"/>
-      <c r="AI1" s="72"/>
-      <c r="AJ1" s="72"/>
-      <c r="AK1" s="72"/>
-      <c r="AL1" s="72"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="74"/>
+      <c r="P1" s="74"/>
+      <c r="Q1" s="74"/>
+      <c r="R1" s="74"/>
+      <c r="S1" s="74"/>
+      <c r="T1" s="74"/>
+      <c r="U1" s="74"/>
+      <c r="V1" s="74"/>
+      <c r="W1" s="74"/>
+      <c r="X1" s="74"/>
+      <c r="Y1" s="74"/>
+      <c r="Z1" s="74"/>
+      <c r="AA1" s="74"/>
+      <c r="AB1" s="74"/>
+      <c r="AC1" s="74"/>
+      <c r="AD1" s="74"/>
+      <c r="AE1" s="74"/>
+      <c r="AF1" s="74"/>
+      <c r="AG1" s="74"/>
+      <c r="AH1" s="74"/>
+      <c r="AI1" s="74"/>
+      <c r="AJ1" s="74"/>
+      <c r="AK1" s="74"/>
+      <c r="AL1" s="74"/>
       <c r="AM1" s="33"/>
     </row>
     <row r="2" spans="1:39" ht="14.1" customHeight="1">
@@ -13009,17 +14213,17 @@
       <c r="AF2" s="3"/>
     </row>
     <row r="3" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
@@ -13180,282 +14384,282 @@
       <c r="AF7" s="3"/>
     </row>
     <row r="8" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A8" s="96" t="s">
+      <c r="A8" s="98" t="s">
         <v>155</v>
       </c>
-      <c r="B8" s="96"/>
-      <c r="C8" s="96"/>
-      <c r="D8" s="96"/>
-      <c r="E8" s="96"/>
-      <c r="F8" s="96" t="s">
+      <c r="B8" s="98"/>
+      <c r="C8" s="98"/>
+      <c r="D8" s="98"/>
+      <c r="E8" s="98"/>
+      <c r="F8" s="98" t="s">
         <v>158</v>
       </c>
-      <c r="G8" s="96"/>
-      <c r="H8" s="96"/>
-      <c r="I8" s="96"/>
-      <c r="J8" s="96"/>
-      <c r="K8" s="96"/>
-      <c r="L8" s="96"/>
-      <c r="M8" s="102" t="s">
+      <c r="G8" s="98"/>
+      <c r="H8" s="98"/>
+      <c r="I8" s="98"/>
+      <c r="J8" s="98"/>
+      <c r="K8" s="98"/>
+      <c r="L8" s="98"/>
+      <c r="M8" s="103" t="s">
         <v>172</v>
       </c>
-      <c r="N8" s="96"/>
-      <c r="O8" s="96"/>
-      <c r="P8" s="96"/>
-      <c r="Q8" s="96"/>
-      <c r="R8" s="96"/>
-      <c r="S8" s="96"/>
-      <c r="T8" s="96" t="s">
+      <c r="N8" s="98"/>
+      <c r="O8" s="98"/>
+      <c r="P8" s="98"/>
+      <c r="Q8" s="98"/>
+      <c r="R8" s="98"/>
+      <c r="S8" s="98"/>
+      <c r="T8" s="98" t="s">
         <v>160</v>
       </c>
-      <c r="U8" s="96"/>
-      <c r="V8" s="96"/>
-      <c r="W8" s="96"/>
-      <c r="X8" s="96"/>
-      <c r="Y8" s="96"/>
-      <c r="Z8" s="96"/>
-      <c r="AA8" s="96" t="s">
+      <c r="U8" s="98"/>
+      <c r="V8" s="98"/>
+      <c r="W8" s="98"/>
+      <c r="X8" s="98"/>
+      <c r="Y8" s="98"/>
+      <c r="Z8" s="98"/>
+      <c r="AA8" s="98" t="s">
         <v>161</v>
       </c>
-      <c r="AB8" s="96"/>
-      <c r="AC8" s="96"/>
-      <c r="AD8" s="96"/>
-      <c r="AE8" s="96"/>
-      <c r="AF8" s="96"/>
-      <c r="AG8" s="96"/>
-      <c r="AH8" s="96" t="s">
+      <c r="AB8" s="98"/>
+      <c r="AC8" s="98"/>
+      <c r="AD8" s="98"/>
+      <c r="AE8" s="98"/>
+      <c r="AF8" s="98"/>
+      <c r="AG8" s="98"/>
+      <c r="AH8" s="98" t="s">
         <v>162</v>
       </c>
-      <c r="AI8" s="96"/>
-      <c r="AJ8" s="96"/>
-      <c r="AK8" s="96"/>
-      <c r="AL8" s="96"/>
-      <c r="AM8" s="96"/>
+      <c r="AI8" s="98"/>
+      <c r="AJ8" s="98"/>
+      <c r="AK8" s="98"/>
+      <c r="AL8" s="98"/>
+      <c r="AM8" s="98"/>
     </row>
     <row r="9" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A9" s="96" t="s">
+      <c r="A9" s="98" t="s">
         <v>156</v>
       </c>
-      <c r="B9" s="96"/>
-      <c r="C9" s="96"/>
-      <c r="D9" s="96"/>
-      <c r="E9" s="96"/>
-      <c r="F9" s="96"/>
-      <c r="G9" s="96"/>
-      <c r="H9" s="96"/>
-      <c r="I9" s="96"/>
-      <c r="J9" s="96"/>
-      <c r="K9" s="96"/>
-      <c r="L9" s="96"/>
-      <c r="M9" s="96"/>
-      <c r="N9" s="96"/>
-      <c r="O9" s="96"/>
-      <c r="P9" s="96"/>
-      <c r="Q9" s="96"/>
-      <c r="R9" s="96"/>
-      <c r="S9" s="96"/>
-      <c r="T9" s="96"/>
-      <c r="U9" s="96"/>
-      <c r="V9" s="96"/>
-      <c r="W9" s="96"/>
-      <c r="X9" s="96"/>
-      <c r="Y9" s="96"/>
-      <c r="Z9" s="96"/>
-      <c r="AA9" s="96"/>
-      <c r="AB9" s="96"/>
-      <c r="AC9" s="96"/>
-      <c r="AD9" s="96"/>
-      <c r="AE9" s="96"/>
-      <c r="AF9" s="96"/>
-      <c r="AG9" s="96"/>
-      <c r="AH9" s="96"/>
-      <c r="AI9" s="96"/>
-      <c r="AJ9" s="96"/>
-      <c r="AK9" s="96"/>
-      <c r="AL9" s="96"/>
-      <c r="AM9" s="96"/>
+      <c r="B9" s="98"/>
+      <c r="C9" s="98"/>
+      <c r="D9" s="98"/>
+      <c r="E9" s="98"/>
+      <c r="F9" s="98"/>
+      <c r="G9" s="98"/>
+      <c r="H9" s="98"/>
+      <c r="I9" s="98"/>
+      <c r="J9" s="98"/>
+      <c r="K9" s="98"/>
+      <c r="L9" s="98"/>
+      <c r="M9" s="98"/>
+      <c r="N9" s="98"/>
+      <c r="O9" s="98"/>
+      <c r="P9" s="98"/>
+      <c r="Q9" s="98"/>
+      <c r="R9" s="98"/>
+      <c r="S9" s="98"/>
+      <c r="T9" s="98"/>
+      <c r="U9" s="98"/>
+      <c r="V9" s="98"/>
+      <c r="W9" s="98"/>
+      <c r="X9" s="98"/>
+      <c r="Y9" s="98"/>
+      <c r="Z9" s="98"/>
+      <c r="AA9" s="98"/>
+      <c r="AB9" s="98"/>
+      <c r="AC9" s="98"/>
+      <c r="AD9" s="98"/>
+      <c r="AE9" s="98"/>
+      <c r="AF9" s="98"/>
+      <c r="AG9" s="98"/>
+      <c r="AH9" s="98"/>
+      <c r="AI9" s="98"/>
+      <c r="AJ9" s="98"/>
+      <c r="AK9" s="98"/>
+      <c r="AL9" s="98"/>
+      <c r="AM9" s="98"/>
     </row>
     <row r="10" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A10" s="96" t="s">
+      <c r="A10" s="98" t="s">
         <v>157</v>
       </c>
-      <c r="B10" s="96"/>
-      <c r="C10" s="96"/>
-      <c r="D10" s="96"/>
-      <c r="E10" s="96"/>
-      <c r="F10" s="96"/>
-      <c r="G10" s="96"/>
-      <c r="H10" s="96"/>
-      <c r="I10" s="96"/>
-      <c r="J10" s="96"/>
-      <c r="K10" s="96"/>
-      <c r="L10" s="96"/>
-      <c r="M10" s="96"/>
-      <c r="N10" s="96"/>
-      <c r="O10" s="96"/>
-      <c r="P10" s="96"/>
-      <c r="Q10" s="96"/>
-      <c r="R10" s="96"/>
-      <c r="S10" s="96"/>
-      <c r="T10" s="96"/>
-      <c r="U10" s="96"/>
-      <c r="V10" s="96"/>
-      <c r="W10" s="96"/>
-      <c r="X10" s="96"/>
-      <c r="Y10" s="96"/>
-      <c r="Z10" s="96"/>
-      <c r="AA10" s="96"/>
-      <c r="AB10" s="96"/>
-      <c r="AC10" s="96"/>
-      <c r="AD10" s="96"/>
-      <c r="AE10" s="96"/>
-      <c r="AF10" s="96"/>
-      <c r="AG10" s="96"/>
-      <c r="AH10" s="96"/>
-      <c r="AI10" s="96"/>
-      <c r="AJ10" s="96"/>
-      <c r="AK10" s="96"/>
-      <c r="AL10" s="96"/>
-      <c r="AM10" s="96"/>
+      <c r="B10" s="98"/>
+      <c r="C10" s="98"/>
+      <c r="D10" s="98"/>
+      <c r="E10" s="98"/>
+      <c r="F10" s="98"/>
+      <c r="G10" s="98"/>
+      <c r="H10" s="98"/>
+      <c r="I10" s="98"/>
+      <c r="J10" s="98"/>
+      <c r="K10" s="98"/>
+      <c r="L10" s="98"/>
+      <c r="M10" s="98"/>
+      <c r="N10" s="98"/>
+      <c r="O10" s="98"/>
+      <c r="P10" s="98"/>
+      <c r="Q10" s="98"/>
+      <c r="R10" s="98"/>
+      <c r="S10" s="98"/>
+      <c r="T10" s="98"/>
+      <c r="U10" s="98"/>
+      <c r="V10" s="98"/>
+      <c r="W10" s="98"/>
+      <c r="X10" s="98"/>
+      <c r="Y10" s="98"/>
+      <c r="Z10" s="98"/>
+      <c r="AA10" s="98"/>
+      <c r="AB10" s="98"/>
+      <c r="AC10" s="98"/>
+      <c r="AD10" s="98"/>
+      <c r="AE10" s="98"/>
+      <c r="AF10" s="98"/>
+      <c r="AG10" s="98"/>
+      <c r="AH10" s="98"/>
+      <c r="AI10" s="98"/>
+      <c r="AJ10" s="98"/>
+      <c r="AK10" s="98"/>
+      <c r="AL10" s="98"/>
+      <c r="AM10" s="98"/>
     </row>
     <row r="11" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A11" s="96" t="s">
+      <c r="A11" s="98" t="s">
         <v>155</v>
       </c>
-      <c r="B11" s="96"/>
-      <c r="C11" s="96"/>
-      <c r="D11" s="96"/>
-      <c r="E11" s="96"/>
-      <c r="F11" s="96" t="s">
+      <c r="B11" s="98"/>
+      <c r="C11" s="98"/>
+      <c r="D11" s="98"/>
+      <c r="E11" s="98"/>
+      <c r="F11" s="98" t="s">
         <v>163</v>
       </c>
-      <c r="G11" s="96"/>
-      <c r="H11" s="96"/>
-      <c r="I11" s="96"/>
-      <c r="J11" s="96"/>
-      <c r="K11" s="96"/>
-      <c r="L11" s="96"/>
-      <c r="M11" s="96" t="s">
+      <c r="G11" s="98"/>
+      <c r="H11" s="98"/>
+      <c r="I11" s="98"/>
+      <c r="J11" s="98"/>
+      <c r="K11" s="98"/>
+      <c r="L11" s="98"/>
+      <c r="M11" s="98" t="s">
         <v>164</v>
       </c>
-      <c r="N11" s="96"/>
-      <c r="O11" s="96"/>
-      <c r="P11" s="96"/>
-      <c r="Q11" s="96"/>
-      <c r="R11" s="96"/>
-      <c r="S11" s="96"/>
-      <c r="T11" s="96" t="s">
+      <c r="N11" s="98"/>
+      <c r="O11" s="98"/>
+      <c r="P11" s="98"/>
+      <c r="Q11" s="98"/>
+      <c r="R11" s="98"/>
+      <c r="S11" s="98"/>
+      <c r="T11" s="98" t="s">
         <v>165</v>
       </c>
-      <c r="U11" s="96"/>
-      <c r="V11" s="96"/>
-      <c r="W11" s="96"/>
-      <c r="X11" s="96"/>
-      <c r="Y11" s="96"/>
-      <c r="Z11" s="96"/>
-      <c r="AA11" s="96" t="s">
+      <c r="U11" s="98"/>
+      <c r="V11" s="98"/>
+      <c r="W11" s="98"/>
+      <c r="X11" s="98"/>
+      <c r="Y11" s="98"/>
+      <c r="Z11" s="98"/>
+      <c r="AA11" s="98" t="s">
         <v>166</v>
       </c>
-      <c r="AB11" s="96"/>
-      <c r="AC11" s="96"/>
-      <c r="AD11" s="96"/>
-      <c r="AE11" s="96"/>
-      <c r="AF11" s="96"/>
-      <c r="AG11" s="96"/>
-      <c r="AH11" s="96" t="s">
+      <c r="AB11" s="98"/>
+      <c r="AC11" s="98"/>
+      <c r="AD11" s="98"/>
+      <c r="AE11" s="98"/>
+      <c r="AF11" s="98"/>
+      <c r="AG11" s="98"/>
+      <c r="AH11" s="98" t="s">
         <v>167</v>
       </c>
-      <c r="AI11" s="96"/>
-      <c r="AJ11" s="96"/>
-      <c r="AK11" s="96"/>
-      <c r="AL11" s="96"/>
-      <c r="AM11" s="96"/>
+      <c r="AI11" s="98"/>
+      <c r="AJ11" s="98"/>
+      <c r="AK11" s="98"/>
+      <c r="AL11" s="98"/>
+      <c r="AM11" s="98"/>
     </row>
     <row r="12" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A12" s="96" t="s">
+      <c r="A12" s="98" t="s">
         <v>156</v>
       </c>
-      <c r="B12" s="96"/>
-      <c r="C12" s="96"/>
-      <c r="D12" s="96"/>
-      <c r="E12" s="96"/>
-      <c r="F12" s="96"/>
-      <c r="G12" s="96"/>
-      <c r="H12" s="96"/>
-      <c r="I12" s="96"/>
-      <c r="J12" s="96"/>
-      <c r="K12" s="96"/>
-      <c r="L12" s="96"/>
-      <c r="M12" s="96"/>
-      <c r="N12" s="96"/>
-      <c r="O12" s="96"/>
-      <c r="P12" s="96"/>
-      <c r="Q12" s="96"/>
-      <c r="R12" s="96"/>
-      <c r="S12" s="96"/>
-      <c r="T12" s="96"/>
-      <c r="U12" s="96"/>
-      <c r="V12" s="96"/>
-      <c r="W12" s="96"/>
-      <c r="X12" s="96"/>
-      <c r="Y12" s="96"/>
-      <c r="Z12" s="96"/>
-      <c r="AA12" s="96"/>
-      <c r="AB12" s="96"/>
-      <c r="AC12" s="96"/>
-      <c r="AD12" s="96"/>
-      <c r="AE12" s="96"/>
-      <c r="AF12" s="96"/>
-      <c r="AG12" s="96"/>
-      <c r="AH12" s="96"/>
-      <c r="AI12" s="96"/>
-      <c r="AJ12" s="96"/>
-      <c r="AK12" s="96"/>
-      <c r="AL12" s="96"/>
-      <c r="AM12" s="96"/>
+      <c r="B12" s="98"/>
+      <c r="C12" s="98"/>
+      <c r="D12" s="98"/>
+      <c r="E12" s="98"/>
+      <c r="F12" s="98"/>
+      <c r="G12" s="98"/>
+      <c r="H12" s="98"/>
+      <c r="I12" s="98"/>
+      <c r="J12" s="98"/>
+      <c r="K12" s="98"/>
+      <c r="L12" s="98"/>
+      <c r="M12" s="98"/>
+      <c r="N12" s="98"/>
+      <c r="O12" s="98"/>
+      <c r="P12" s="98"/>
+      <c r="Q12" s="98"/>
+      <c r="R12" s="98"/>
+      <c r="S12" s="98"/>
+      <c r="T12" s="98"/>
+      <c r="U12" s="98"/>
+      <c r="V12" s="98"/>
+      <c r="W12" s="98"/>
+      <c r="X12" s="98"/>
+      <c r="Y12" s="98"/>
+      <c r="Z12" s="98"/>
+      <c r="AA12" s="98"/>
+      <c r="AB12" s="98"/>
+      <c r="AC12" s="98"/>
+      <c r="AD12" s="98"/>
+      <c r="AE12" s="98"/>
+      <c r="AF12" s="98"/>
+      <c r="AG12" s="98"/>
+      <c r="AH12" s="98"/>
+      <c r="AI12" s="98"/>
+      <c r="AJ12" s="98"/>
+      <c r="AK12" s="98"/>
+      <c r="AL12" s="98"/>
+      <c r="AM12" s="98"/>
     </row>
     <row r="13" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A13" s="96" t="s">
+      <c r="A13" s="98" t="s">
         <v>157</v>
       </c>
-      <c r="B13" s="96"/>
-      <c r="C13" s="96"/>
-      <c r="D13" s="96"/>
-      <c r="E13" s="96"/>
-      <c r="F13" s="96"/>
-      <c r="G13" s="96"/>
-      <c r="H13" s="96"/>
-      <c r="I13" s="96"/>
-      <c r="J13" s="96"/>
-      <c r="K13" s="96"/>
-      <c r="L13" s="96"/>
-      <c r="M13" s="96"/>
-      <c r="N13" s="96"/>
-      <c r="O13" s="96"/>
-      <c r="P13" s="96"/>
-      <c r="Q13" s="96"/>
-      <c r="R13" s="96"/>
-      <c r="S13" s="96"/>
-      <c r="T13" s="96"/>
-      <c r="U13" s="96"/>
-      <c r="V13" s="96"/>
-      <c r="W13" s="96"/>
-      <c r="X13" s="96"/>
-      <c r="Y13" s="96"/>
-      <c r="Z13" s="96"/>
-      <c r="AA13" s="96"/>
-      <c r="AB13" s="96"/>
-      <c r="AC13" s="96"/>
-      <c r="AD13" s="96"/>
-      <c r="AE13" s="96"/>
-      <c r="AF13" s="96"/>
-      <c r="AG13" s="96"/>
-      <c r="AH13" s="96"/>
-      <c r="AI13" s="96"/>
-      <c r="AJ13" s="96"/>
-      <c r="AK13" s="96"/>
-      <c r="AL13" s="96"/>
-      <c r="AM13" s="96"/>
+      <c r="B13" s="98"/>
+      <c r="C13" s="98"/>
+      <c r="D13" s="98"/>
+      <c r="E13" s="98"/>
+      <c r="F13" s="98"/>
+      <c r="G13" s="98"/>
+      <c r="H13" s="98"/>
+      <c r="I13" s="98"/>
+      <c r="J13" s="98"/>
+      <c r="K13" s="98"/>
+      <c r="L13" s="98"/>
+      <c r="M13" s="98"/>
+      <c r="N13" s="98"/>
+      <c r="O13" s="98"/>
+      <c r="P13" s="98"/>
+      <c r="Q13" s="98"/>
+      <c r="R13" s="98"/>
+      <c r="S13" s="98"/>
+      <c r="T13" s="98"/>
+      <c r="U13" s="98"/>
+      <c r="V13" s="98"/>
+      <c r="W13" s="98"/>
+      <c r="X13" s="98"/>
+      <c r="Y13" s="98"/>
+      <c r="Z13" s="98"/>
+      <c r="AA13" s="98"/>
+      <c r="AB13" s="98"/>
+      <c r="AC13" s="98"/>
+      <c r="AD13" s="98"/>
+      <c r="AE13" s="98"/>
+      <c r="AF13" s="98"/>
+      <c r="AG13" s="98"/>
+      <c r="AH13" s="98"/>
+      <c r="AI13" s="98"/>
+      <c r="AJ13" s="98"/>
+      <c r="AK13" s="98"/>
+      <c r="AL13" s="98"/>
+      <c r="AM13" s="98"/>
     </row>
     <row r="14" spans="1:39" ht="14.1" customHeight="1">
       <c r="A14" s="46"/>
@@ -13522,282 +14726,282 @@
       <c r="AF15" s="3"/>
     </row>
     <row r="16" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A16" s="96" t="s">
+      <c r="A16" s="98" t="s">
         <v>155</v>
       </c>
-      <c r="B16" s="96"/>
-      <c r="C16" s="96"/>
-      <c r="D16" s="96"/>
-      <c r="E16" s="96"/>
-      <c r="F16" s="96" t="s">
+      <c r="B16" s="98"/>
+      <c r="C16" s="98"/>
+      <c r="D16" s="98"/>
+      <c r="E16" s="98"/>
+      <c r="F16" s="98" t="s">
         <v>158</v>
       </c>
-      <c r="G16" s="96"/>
-      <c r="H16" s="96"/>
-      <c r="I16" s="96"/>
-      <c r="J16" s="96"/>
-      <c r="K16" s="96"/>
-      <c r="L16" s="96"/>
-      <c r="M16" s="96" t="s">
+      <c r="G16" s="98"/>
+      <c r="H16" s="98"/>
+      <c r="I16" s="98"/>
+      <c r="J16" s="98"/>
+      <c r="K16" s="98"/>
+      <c r="L16" s="98"/>
+      <c r="M16" s="98" t="s">
         <v>159</v>
       </c>
-      <c r="N16" s="96"/>
-      <c r="O16" s="96"/>
-      <c r="P16" s="96"/>
-      <c r="Q16" s="96"/>
-      <c r="R16" s="96"/>
-      <c r="S16" s="96"/>
-      <c r="T16" s="96" t="s">
+      <c r="N16" s="98"/>
+      <c r="O16" s="98"/>
+      <c r="P16" s="98"/>
+      <c r="Q16" s="98"/>
+      <c r="R16" s="98"/>
+      <c r="S16" s="98"/>
+      <c r="T16" s="98" t="s">
         <v>160</v>
       </c>
-      <c r="U16" s="96"/>
-      <c r="V16" s="96"/>
-      <c r="W16" s="96"/>
-      <c r="X16" s="96"/>
-      <c r="Y16" s="96"/>
-      <c r="Z16" s="96"/>
-      <c r="AA16" s="96" t="s">
+      <c r="U16" s="98"/>
+      <c r="V16" s="98"/>
+      <c r="W16" s="98"/>
+      <c r="X16" s="98"/>
+      <c r="Y16" s="98"/>
+      <c r="Z16" s="98"/>
+      <c r="AA16" s="98" t="s">
         <v>161</v>
       </c>
-      <c r="AB16" s="96"/>
-      <c r="AC16" s="96"/>
-      <c r="AD16" s="96"/>
-      <c r="AE16" s="96"/>
-      <c r="AF16" s="96"/>
-      <c r="AG16" s="96"/>
-      <c r="AH16" s="96" t="s">
+      <c r="AB16" s="98"/>
+      <c r="AC16" s="98"/>
+      <c r="AD16" s="98"/>
+      <c r="AE16" s="98"/>
+      <c r="AF16" s="98"/>
+      <c r="AG16" s="98"/>
+      <c r="AH16" s="98" t="s">
         <v>162</v>
       </c>
-      <c r="AI16" s="96"/>
-      <c r="AJ16" s="96"/>
-      <c r="AK16" s="96"/>
-      <c r="AL16" s="96"/>
-      <c r="AM16" s="96"/>
+      <c r="AI16" s="98"/>
+      <c r="AJ16" s="98"/>
+      <c r="AK16" s="98"/>
+      <c r="AL16" s="98"/>
+      <c r="AM16" s="98"/>
     </row>
     <row r="17" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A17" s="96" t="s">
+      <c r="A17" s="98" t="s">
         <v>156</v>
       </c>
-      <c r="B17" s="96"/>
-      <c r="C17" s="96"/>
-      <c r="D17" s="96"/>
-      <c r="E17" s="96"/>
-      <c r="F17" s="96"/>
-      <c r="G17" s="96"/>
-      <c r="H17" s="96"/>
-      <c r="I17" s="96"/>
-      <c r="J17" s="96"/>
-      <c r="K17" s="96"/>
-      <c r="L17" s="96"/>
-      <c r="M17" s="96"/>
-      <c r="N17" s="96"/>
-      <c r="O17" s="96"/>
-      <c r="P17" s="96"/>
-      <c r="Q17" s="96"/>
-      <c r="R17" s="96"/>
-      <c r="S17" s="96"/>
-      <c r="T17" s="96"/>
-      <c r="U17" s="96"/>
-      <c r="V17" s="96"/>
-      <c r="W17" s="96"/>
-      <c r="X17" s="96"/>
-      <c r="Y17" s="96"/>
-      <c r="Z17" s="96"/>
-      <c r="AA17" s="96"/>
-      <c r="AB17" s="96"/>
-      <c r="AC17" s="96"/>
-      <c r="AD17" s="96"/>
-      <c r="AE17" s="96"/>
-      <c r="AF17" s="96"/>
-      <c r="AG17" s="96"/>
-      <c r="AH17" s="96"/>
-      <c r="AI17" s="96"/>
-      <c r="AJ17" s="96"/>
-      <c r="AK17" s="96"/>
-      <c r="AL17" s="96"/>
-      <c r="AM17" s="96"/>
+      <c r="B17" s="98"/>
+      <c r="C17" s="98"/>
+      <c r="D17" s="98"/>
+      <c r="E17" s="98"/>
+      <c r="F17" s="98"/>
+      <c r="G17" s="98"/>
+      <c r="H17" s="98"/>
+      <c r="I17" s="98"/>
+      <c r="J17" s="98"/>
+      <c r="K17" s="98"/>
+      <c r="L17" s="98"/>
+      <c r="M17" s="98"/>
+      <c r="N17" s="98"/>
+      <c r="O17" s="98"/>
+      <c r="P17" s="98"/>
+      <c r="Q17" s="98"/>
+      <c r="R17" s="98"/>
+      <c r="S17" s="98"/>
+      <c r="T17" s="98"/>
+      <c r="U17" s="98"/>
+      <c r="V17" s="98"/>
+      <c r="W17" s="98"/>
+      <c r="X17" s="98"/>
+      <c r="Y17" s="98"/>
+      <c r="Z17" s="98"/>
+      <c r="AA17" s="98"/>
+      <c r="AB17" s="98"/>
+      <c r="AC17" s="98"/>
+      <c r="AD17" s="98"/>
+      <c r="AE17" s="98"/>
+      <c r="AF17" s="98"/>
+      <c r="AG17" s="98"/>
+      <c r="AH17" s="98"/>
+      <c r="AI17" s="98"/>
+      <c r="AJ17" s="98"/>
+      <c r="AK17" s="98"/>
+      <c r="AL17" s="98"/>
+      <c r="AM17" s="98"/>
     </row>
     <row r="18" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A18" s="96" t="s">
+      <c r="A18" s="98" t="s">
         <v>157</v>
       </c>
-      <c r="B18" s="96"/>
-      <c r="C18" s="96"/>
-      <c r="D18" s="96"/>
-      <c r="E18" s="96"/>
-      <c r="F18" s="96"/>
-      <c r="G18" s="96"/>
-      <c r="H18" s="96"/>
-      <c r="I18" s="96"/>
-      <c r="J18" s="96"/>
-      <c r="K18" s="96"/>
-      <c r="L18" s="96"/>
-      <c r="M18" s="96"/>
-      <c r="N18" s="96"/>
-      <c r="O18" s="96"/>
-      <c r="P18" s="96"/>
-      <c r="Q18" s="96"/>
-      <c r="R18" s="96"/>
-      <c r="S18" s="96"/>
-      <c r="T18" s="96"/>
-      <c r="U18" s="96"/>
-      <c r="V18" s="96"/>
-      <c r="W18" s="96"/>
-      <c r="X18" s="96"/>
-      <c r="Y18" s="96"/>
-      <c r="Z18" s="96"/>
-      <c r="AA18" s="96"/>
-      <c r="AB18" s="96"/>
-      <c r="AC18" s="96"/>
-      <c r="AD18" s="96"/>
-      <c r="AE18" s="96"/>
-      <c r="AF18" s="96"/>
-      <c r="AG18" s="96"/>
-      <c r="AH18" s="96"/>
-      <c r="AI18" s="96"/>
-      <c r="AJ18" s="96"/>
-      <c r="AK18" s="96"/>
-      <c r="AL18" s="96"/>
-      <c r="AM18" s="96"/>
+      <c r="B18" s="98"/>
+      <c r="C18" s="98"/>
+      <c r="D18" s="98"/>
+      <c r="E18" s="98"/>
+      <c r="F18" s="98"/>
+      <c r="G18" s="98"/>
+      <c r="H18" s="98"/>
+      <c r="I18" s="98"/>
+      <c r="J18" s="98"/>
+      <c r="K18" s="98"/>
+      <c r="L18" s="98"/>
+      <c r="M18" s="98"/>
+      <c r="N18" s="98"/>
+      <c r="O18" s="98"/>
+      <c r="P18" s="98"/>
+      <c r="Q18" s="98"/>
+      <c r="R18" s="98"/>
+      <c r="S18" s="98"/>
+      <c r="T18" s="98"/>
+      <c r="U18" s="98"/>
+      <c r="V18" s="98"/>
+      <c r="W18" s="98"/>
+      <c r="X18" s="98"/>
+      <c r="Y18" s="98"/>
+      <c r="Z18" s="98"/>
+      <c r="AA18" s="98"/>
+      <c r="AB18" s="98"/>
+      <c r="AC18" s="98"/>
+      <c r="AD18" s="98"/>
+      <c r="AE18" s="98"/>
+      <c r="AF18" s="98"/>
+      <c r="AG18" s="98"/>
+      <c r="AH18" s="98"/>
+      <c r="AI18" s="98"/>
+      <c r="AJ18" s="98"/>
+      <c r="AK18" s="98"/>
+      <c r="AL18" s="98"/>
+      <c r="AM18" s="98"/>
     </row>
     <row r="19" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A19" s="96" t="s">
+      <c r="A19" s="98" t="s">
         <v>155</v>
       </c>
-      <c r="B19" s="96"/>
-      <c r="C19" s="96"/>
-      <c r="D19" s="96"/>
-      <c r="E19" s="96"/>
-      <c r="F19" s="96" t="s">
+      <c r="B19" s="98"/>
+      <c r="C19" s="98"/>
+      <c r="D19" s="98"/>
+      <c r="E19" s="98"/>
+      <c r="F19" s="98" t="s">
         <v>163</v>
       </c>
-      <c r="G19" s="96"/>
-      <c r="H19" s="96"/>
-      <c r="I19" s="96"/>
-      <c r="J19" s="96"/>
-      <c r="K19" s="96"/>
-      <c r="L19" s="96"/>
-      <c r="M19" s="96" t="s">
+      <c r="G19" s="98"/>
+      <c r="H19" s="98"/>
+      <c r="I19" s="98"/>
+      <c r="J19" s="98"/>
+      <c r="K19" s="98"/>
+      <c r="L19" s="98"/>
+      <c r="M19" s="98" t="s">
         <v>164</v>
       </c>
-      <c r="N19" s="96"/>
-      <c r="O19" s="96"/>
-      <c r="P19" s="96"/>
-      <c r="Q19" s="96"/>
-      <c r="R19" s="96"/>
-      <c r="S19" s="96"/>
-      <c r="T19" s="96" t="s">
+      <c r="N19" s="98"/>
+      <c r="O19" s="98"/>
+      <c r="P19" s="98"/>
+      <c r="Q19" s="98"/>
+      <c r="R19" s="98"/>
+      <c r="S19" s="98"/>
+      <c r="T19" s="98" t="s">
         <v>165</v>
       </c>
-      <c r="U19" s="96"/>
-      <c r="V19" s="96"/>
-      <c r="W19" s="96"/>
-      <c r="X19" s="96"/>
-      <c r="Y19" s="96"/>
-      <c r="Z19" s="96"/>
-      <c r="AA19" s="96" t="s">
+      <c r="U19" s="98"/>
+      <c r="V19" s="98"/>
+      <c r="W19" s="98"/>
+      <c r="X19" s="98"/>
+      <c r="Y19" s="98"/>
+      <c r="Z19" s="98"/>
+      <c r="AA19" s="98" t="s">
         <v>166</v>
       </c>
-      <c r="AB19" s="96"/>
-      <c r="AC19" s="96"/>
-      <c r="AD19" s="96"/>
-      <c r="AE19" s="96"/>
-      <c r="AF19" s="96"/>
-      <c r="AG19" s="96"/>
-      <c r="AH19" s="96" t="s">
+      <c r="AB19" s="98"/>
+      <c r="AC19" s="98"/>
+      <c r="AD19" s="98"/>
+      <c r="AE19" s="98"/>
+      <c r="AF19" s="98"/>
+      <c r="AG19" s="98"/>
+      <c r="AH19" s="98" t="s">
         <v>167</v>
       </c>
-      <c r="AI19" s="96"/>
-      <c r="AJ19" s="96"/>
-      <c r="AK19" s="96"/>
-      <c r="AL19" s="96"/>
-      <c r="AM19" s="96"/>
+      <c r="AI19" s="98"/>
+      <c r="AJ19" s="98"/>
+      <c r="AK19" s="98"/>
+      <c r="AL19" s="98"/>
+      <c r="AM19" s="98"/>
     </row>
     <row r="20" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A20" s="96" t="s">
+      <c r="A20" s="98" t="s">
         <v>156</v>
       </c>
-      <c r="B20" s="96"/>
-      <c r="C20" s="96"/>
-      <c r="D20" s="96"/>
-      <c r="E20" s="96"/>
-      <c r="F20" s="96"/>
-      <c r="G20" s="96"/>
-      <c r="H20" s="96"/>
-      <c r="I20" s="96"/>
-      <c r="J20" s="96"/>
-      <c r="K20" s="96"/>
-      <c r="L20" s="96"/>
-      <c r="M20" s="96"/>
-      <c r="N20" s="96"/>
-      <c r="O20" s="96"/>
-      <c r="P20" s="96"/>
-      <c r="Q20" s="96"/>
-      <c r="R20" s="96"/>
-      <c r="S20" s="96"/>
-      <c r="T20" s="96"/>
-      <c r="U20" s="96"/>
-      <c r="V20" s="96"/>
-      <c r="W20" s="96"/>
-      <c r="X20" s="96"/>
-      <c r="Y20" s="96"/>
-      <c r="Z20" s="96"/>
-      <c r="AA20" s="96"/>
-      <c r="AB20" s="96"/>
-      <c r="AC20" s="96"/>
-      <c r="AD20" s="96"/>
-      <c r="AE20" s="96"/>
-      <c r="AF20" s="96"/>
-      <c r="AG20" s="96"/>
-      <c r="AH20" s="96"/>
-      <c r="AI20" s="96"/>
-      <c r="AJ20" s="96"/>
-      <c r="AK20" s="96"/>
-      <c r="AL20" s="96"/>
-      <c r="AM20" s="96"/>
+      <c r="B20" s="98"/>
+      <c r="C20" s="98"/>
+      <c r="D20" s="98"/>
+      <c r="E20" s="98"/>
+      <c r="F20" s="98"/>
+      <c r="G20" s="98"/>
+      <c r="H20" s="98"/>
+      <c r="I20" s="98"/>
+      <c r="J20" s="98"/>
+      <c r="K20" s="98"/>
+      <c r="L20" s="98"/>
+      <c r="M20" s="98"/>
+      <c r="N20" s="98"/>
+      <c r="O20" s="98"/>
+      <c r="P20" s="98"/>
+      <c r="Q20" s="98"/>
+      <c r="R20" s="98"/>
+      <c r="S20" s="98"/>
+      <c r="T20" s="98"/>
+      <c r="U20" s="98"/>
+      <c r="V20" s="98"/>
+      <c r="W20" s="98"/>
+      <c r="X20" s="98"/>
+      <c r="Y20" s="98"/>
+      <c r="Z20" s="98"/>
+      <c r="AA20" s="98"/>
+      <c r="AB20" s="98"/>
+      <c r="AC20" s="98"/>
+      <c r="AD20" s="98"/>
+      <c r="AE20" s="98"/>
+      <c r="AF20" s="98"/>
+      <c r="AG20" s="98"/>
+      <c r="AH20" s="98"/>
+      <c r="AI20" s="98"/>
+      <c r="AJ20" s="98"/>
+      <c r="AK20" s="98"/>
+      <c r="AL20" s="98"/>
+      <c r="AM20" s="98"/>
     </row>
     <row r="21" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A21" s="96" t="s">
+      <c r="A21" s="98" t="s">
         <v>157</v>
       </c>
-      <c r="B21" s="96"/>
-      <c r="C21" s="96"/>
-      <c r="D21" s="96"/>
-      <c r="E21" s="96"/>
-      <c r="F21" s="96"/>
-      <c r="G21" s="96"/>
-      <c r="H21" s="96"/>
-      <c r="I21" s="96"/>
-      <c r="J21" s="96"/>
-      <c r="K21" s="96"/>
-      <c r="L21" s="96"/>
-      <c r="M21" s="96"/>
-      <c r="N21" s="96"/>
-      <c r="O21" s="96"/>
-      <c r="P21" s="96"/>
-      <c r="Q21" s="96"/>
-      <c r="R21" s="96"/>
-      <c r="S21" s="96"/>
-      <c r="T21" s="96"/>
-      <c r="U21" s="96"/>
-      <c r="V21" s="96"/>
-      <c r="W21" s="96"/>
-      <c r="X21" s="96"/>
-      <c r="Y21" s="96"/>
-      <c r="Z21" s="96"/>
-      <c r="AA21" s="96"/>
-      <c r="AB21" s="96"/>
-      <c r="AC21" s="96"/>
-      <c r="AD21" s="96"/>
-      <c r="AE21" s="96"/>
-      <c r="AF21" s="96"/>
-      <c r="AG21" s="96"/>
-      <c r="AH21" s="96"/>
-      <c r="AI21" s="96"/>
-      <c r="AJ21" s="96"/>
-      <c r="AK21" s="96"/>
-      <c r="AL21" s="96"/>
-      <c r="AM21" s="96"/>
+      <c r="B21" s="98"/>
+      <c r="C21" s="98"/>
+      <c r="D21" s="98"/>
+      <c r="E21" s="98"/>
+      <c r="F21" s="98"/>
+      <c r="G21" s="98"/>
+      <c r="H21" s="98"/>
+      <c r="I21" s="98"/>
+      <c r="J21" s="98"/>
+      <c r="K21" s="98"/>
+      <c r="L21" s="98"/>
+      <c r="M21" s="98"/>
+      <c r="N21" s="98"/>
+      <c r="O21" s="98"/>
+      <c r="P21" s="98"/>
+      <c r="Q21" s="98"/>
+      <c r="R21" s="98"/>
+      <c r="S21" s="98"/>
+      <c r="T21" s="98"/>
+      <c r="U21" s="98"/>
+      <c r="V21" s="98"/>
+      <c r="W21" s="98"/>
+      <c r="X21" s="98"/>
+      <c r="Y21" s="98"/>
+      <c r="Z21" s="98"/>
+      <c r="AA21" s="98"/>
+      <c r="AB21" s="98"/>
+      <c r="AC21" s="98"/>
+      <c r="AD21" s="98"/>
+      <c r="AE21" s="98"/>
+      <c r="AF21" s="98"/>
+      <c r="AG21" s="98"/>
+      <c r="AH21" s="98"/>
+      <c r="AI21" s="98"/>
+      <c r="AJ21" s="98"/>
+      <c r="AK21" s="98"/>
+      <c r="AL21" s="98"/>
+      <c r="AM21" s="98"/>
     </row>
     <row r="22" spans="1:39" ht="14.1" customHeight="1">
       <c r="A22" s="46"/>
@@ -13928,17 +15132,17 @@
       <c r="AF25" s="3"/>
     </row>
     <row r="26" spans="1:39" s="34" customFormat="1" ht="14.1" customHeight="1">
-      <c r="A26" s="103"/>
-      <c r="B26" s="103"/>
-      <c r="C26" s="103"/>
-      <c r="D26" s="103"/>
-      <c r="E26" s="103"/>
-      <c r="F26" s="103"/>
-      <c r="G26" s="103"/>
-      <c r="H26" s="103"/>
-      <c r="I26" s="103"/>
-      <c r="J26" s="103"/>
-      <c r="K26" s="103"/>
+      <c r="A26" s="102"/>
+      <c r="B26" s="102"/>
+      <c r="C26" s="102"/>
+      <c r="D26" s="102"/>
+      <c r="E26" s="102"/>
+      <c r="F26" s="102"/>
+      <c r="G26" s="102"/>
+      <c r="H26" s="102"/>
+      <c r="I26" s="102"/>
+      <c r="J26" s="102"/>
+      <c r="K26" s="102"/>
       <c r="L26" s="46"/>
       <c r="M26" s="46"/>
       <c r="N26" s="46"/>
@@ -13995,282 +15199,282 @@
       <c r="AF28" s="46"/>
     </row>
     <row r="29" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A29" s="96" t="s">
+      <c r="A29" s="98" t="s">
         <v>155</v>
       </c>
-      <c r="B29" s="96"/>
-      <c r="C29" s="96"/>
-      <c r="D29" s="96"/>
-      <c r="E29" s="96"/>
-      <c r="F29" s="96" t="s">
+      <c r="B29" s="98"/>
+      <c r="C29" s="98"/>
+      <c r="D29" s="98"/>
+      <c r="E29" s="98"/>
+      <c r="F29" s="98" t="s">
         <v>158</v>
       </c>
-      <c r="G29" s="96"/>
-      <c r="H29" s="96"/>
-      <c r="I29" s="96"/>
-      <c r="J29" s="96"/>
-      <c r="K29" s="96"/>
-      <c r="L29" s="96"/>
-      <c r="M29" s="96" t="s">
+      <c r="G29" s="98"/>
+      <c r="H29" s="98"/>
+      <c r="I29" s="98"/>
+      <c r="J29" s="98"/>
+      <c r="K29" s="98"/>
+      <c r="L29" s="98"/>
+      <c r="M29" s="98" t="s">
         <v>159</v>
       </c>
-      <c r="N29" s="96"/>
-      <c r="O29" s="96"/>
-      <c r="P29" s="96"/>
-      <c r="Q29" s="96"/>
-      <c r="R29" s="96"/>
-      <c r="S29" s="96"/>
-      <c r="T29" s="96" t="s">
+      <c r="N29" s="98"/>
+      <c r="O29" s="98"/>
+      <c r="P29" s="98"/>
+      <c r="Q29" s="98"/>
+      <c r="R29" s="98"/>
+      <c r="S29" s="98"/>
+      <c r="T29" s="98" t="s">
         <v>160</v>
       </c>
-      <c r="U29" s="96"/>
-      <c r="V29" s="96"/>
-      <c r="W29" s="96"/>
-      <c r="X29" s="96"/>
-      <c r="Y29" s="96"/>
-      <c r="Z29" s="96"/>
-      <c r="AA29" s="96" t="s">
+      <c r="U29" s="98"/>
+      <c r="V29" s="98"/>
+      <c r="W29" s="98"/>
+      <c r="X29" s="98"/>
+      <c r="Y29" s="98"/>
+      <c r="Z29" s="98"/>
+      <c r="AA29" s="98" t="s">
         <v>161</v>
       </c>
-      <c r="AB29" s="96"/>
-      <c r="AC29" s="96"/>
-      <c r="AD29" s="96"/>
-      <c r="AE29" s="96"/>
-      <c r="AF29" s="96"/>
-      <c r="AG29" s="96"/>
-      <c r="AH29" s="96" t="s">
+      <c r="AB29" s="98"/>
+      <c r="AC29" s="98"/>
+      <c r="AD29" s="98"/>
+      <c r="AE29" s="98"/>
+      <c r="AF29" s="98"/>
+      <c r="AG29" s="98"/>
+      <c r="AH29" s="98" t="s">
         <v>162</v>
       </c>
-      <c r="AI29" s="96"/>
-      <c r="AJ29" s="96"/>
-      <c r="AK29" s="96"/>
-      <c r="AL29" s="96"/>
-      <c r="AM29" s="96"/>
+      <c r="AI29" s="98"/>
+      <c r="AJ29" s="98"/>
+      <c r="AK29" s="98"/>
+      <c r="AL29" s="98"/>
+      <c r="AM29" s="98"/>
     </row>
     <row r="30" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A30" s="96" t="s">
+      <c r="A30" s="98" t="s">
         <v>156</v>
       </c>
-      <c r="B30" s="96"/>
-      <c r="C30" s="96"/>
-      <c r="D30" s="96"/>
-      <c r="E30" s="96"/>
-      <c r="F30" s="96"/>
-      <c r="G30" s="96"/>
-      <c r="H30" s="96"/>
-      <c r="I30" s="96"/>
-      <c r="J30" s="96"/>
-      <c r="K30" s="96"/>
-      <c r="L30" s="96"/>
-      <c r="M30" s="96"/>
-      <c r="N30" s="96"/>
-      <c r="O30" s="96"/>
-      <c r="P30" s="96"/>
-      <c r="Q30" s="96"/>
-      <c r="R30" s="96"/>
-      <c r="S30" s="96"/>
-      <c r="T30" s="96"/>
-      <c r="U30" s="96"/>
-      <c r="V30" s="96"/>
-      <c r="W30" s="96"/>
-      <c r="X30" s="96"/>
-      <c r="Y30" s="96"/>
-      <c r="Z30" s="96"/>
-      <c r="AA30" s="96"/>
-      <c r="AB30" s="96"/>
-      <c r="AC30" s="96"/>
-      <c r="AD30" s="96"/>
-      <c r="AE30" s="96"/>
-      <c r="AF30" s="96"/>
-      <c r="AG30" s="96"/>
-      <c r="AH30" s="96"/>
-      <c r="AI30" s="96"/>
-      <c r="AJ30" s="96"/>
-      <c r="AK30" s="96"/>
-      <c r="AL30" s="96"/>
-      <c r="AM30" s="96"/>
+      <c r="B30" s="98"/>
+      <c r="C30" s="98"/>
+      <c r="D30" s="98"/>
+      <c r="E30" s="98"/>
+      <c r="F30" s="98"/>
+      <c r="G30" s="98"/>
+      <c r="H30" s="98"/>
+      <c r="I30" s="98"/>
+      <c r="J30" s="98"/>
+      <c r="K30" s="98"/>
+      <c r="L30" s="98"/>
+      <c r="M30" s="98"/>
+      <c r="N30" s="98"/>
+      <c r="O30" s="98"/>
+      <c r="P30" s="98"/>
+      <c r="Q30" s="98"/>
+      <c r="R30" s="98"/>
+      <c r="S30" s="98"/>
+      <c r="T30" s="98"/>
+      <c r="U30" s="98"/>
+      <c r="V30" s="98"/>
+      <c r="W30" s="98"/>
+      <c r="X30" s="98"/>
+      <c r="Y30" s="98"/>
+      <c r="Z30" s="98"/>
+      <c r="AA30" s="98"/>
+      <c r="AB30" s="98"/>
+      <c r="AC30" s="98"/>
+      <c r="AD30" s="98"/>
+      <c r="AE30" s="98"/>
+      <c r="AF30" s="98"/>
+      <c r="AG30" s="98"/>
+      <c r="AH30" s="98"/>
+      <c r="AI30" s="98"/>
+      <c r="AJ30" s="98"/>
+      <c r="AK30" s="98"/>
+      <c r="AL30" s="98"/>
+      <c r="AM30" s="98"/>
     </row>
     <row r="31" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A31" s="96" t="s">
+      <c r="A31" s="98" t="s">
         <v>157</v>
       </c>
-      <c r="B31" s="96"/>
-      <c r="C31" s="96"/>
-      <c r="D31" s="96"/>
-      <c r="E31" s="96"/>
-      <c r="F31" s="96"/>
-      <c r="G31" s="96"/>
-      <c r="H31" s="96"/>
-      <c r="I31" s="96"/>
-      <c r="J31" s="96"/>
-      <c r="K31" s="96"/>
-      <c r="L31" s="96"/>
-      <c r="M31" s="96"/>
-      <c r="N31" s="96"/>
-      <c r="O31" s="96"/>
-      <c r="P31" s="96"/>
-      <c r="Q31" s="96"/>
-      <c r="R31" s="96"/>
-      <c r="S31" s="96"/>
-      <c r="T31" s="96"/>
-      <c r="U31" s="96"/>
-      <c r="V31" s="96"/>
-      <c r="W31" s="96"/>
-      <c r="X31" s="96"/>
-      <c r="Y31" s="96"/>
-      <c r="Z31" s="96"/>
-      <c r="AA31" s="96"/>
-      <c r="AB31" s="96"/>
-      <c r="AC31" s="96"/>
-      <c r="AD31" s="96"/>
-      <c r="AE31" s="96"/>
-      <c r="AF31" s="96"/>
-      <c r="AG31" s="96"/>
-      <c r="AH31" s="96"/>
-      <c r="AI31" s="96"/>
-      <c r="AJ31" s="96"/>
-      <c r="AK31" s="96"/>
-      <c r="AL31" s="96"/>
-      <c r="AM31" s="96"/>
+      <c r="B31" s="98"/>
+      <c r="C31" s="98"/>
+      <c r="D31" s="98"/>
+      <c r="E31" s="98"/>
+      <c r="F31" s="98"/>
+      <c r="G31" s="98"/>
+      <c r="H31" s="98"/>
+      <c r="I31" s="98"/>
+      <c r="J31" s="98"/>
+      <c r="K31" s="98"/>
+      <c r="L31" s="98"/>
+      <c r="M31" s="98"/>
+      <c r="N31" s="98"/>
+      <c r="O31" s="98"/>
+      <c r="P31" s="98"/>
+      <c r="Q31" s="98"/>
+      <c r="R31" s="98"/>
+      <c r="S31" s="98"/>
+      <c r="T31" s="98"/>
+      <c r="U31" s="98"/>
+      <c r="V31" s="98"/>
+      <c r="W31" s="98"/>
+      <c r="X31" s="98"/>
+      <c r="Y31" s="98"/>
+      <c r="Z31" s="98"/>
+      <c r="AA31" s="98"/>
+      <c r="AB31" s="98"/>
+      <c r="AC31" s="98"/>
+      <c r="AD31" s="98"/>
+      <c r="AE31" s="98"/>
+      <c r="AF31" s="98"/>
+      <c r="AG31" s="98"/>
+      <c r="AH31" s="98"/>
+      <c r="AI31" s="98"/>
+      <c r="AJ31" s="98"/>
+      <c r="AK31" s="98"/>
+      <c r="AL31" s="98"/>
+      <c r="AM31" s="98"/>
     </row>
     <row r="32" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A32" s="96" t="s">
+      <c r="A32" s="98" t="s">
         <v>155</v>
       </c>
-      <c r="B32" s="96"/>
-      <c r="C32" s="96"/>
-      <c r="D32" s="96"/>
-      <c r="E32" s="96"/>
-      <c r="F32" s="96" t="s">
+      <c r="B32" s="98"/>
+      <c r="C32" s="98"/>
+      <c r="D32" s="98"/>
+      <c r="E32" s="98"/>
+      <c r="F32" s="98" t="s">
         <v>163</v>
       </c>
-      <c r="G32" s="96"/>
-      <c r="H32" s="96"/>
-      <c r="I32" s="96"/>
-      <c r="J32" s="96"/>
-      <c r="K32" s="96"/>
-      <c r="L32" s="96"/>
-      <c r="M32" s="96" t="s">
+      <c r="G32" s="98"/>
+      <c r="H32" s="98"/>
+      <c r="I32" s="98"/>
+      <c r="J32" s="98"/>
+      <c r="K32" s="98"/>
+      <c r="L32" s="98"/>
+      <c r="M32" s="98" t="s">
         <v>164</v>
       </c>
-      <c r="N32" s="96"/>
-      <c r="O32" s="96"/>
-      <c r="P32" s="96"/>
-      <c r="Q32" s="96"/>
-      <c r="R32" s="96"/>
-      <c r="S32" s="96"/>
-      <c r="T32" s="96" t="s">
+      <c r="N32" s="98"/>
+      <c r="O32" s="98"/>
+      <c r="P32" s="98"/>
+      <c r="Q32" s="98"/>
+      <c r="R32" s="98"/>
+      <c r="S32" s="98"/>
+      <c r="T32" s="98" t="s">
         <v>165</v>
       </c>
-      <c r="U32" s="96"/>
-      <c r="V32" s="96"/>
-      <c r="W32" s="96"/>
-      <c r="X32" s="96"/>
-      <c r="Y32" s="96"/>
-      <c r="Z32" s="96"/>
-      <c r="AA32" s="96" t="s">
+      <c r="U32" s="98"/>
+      <c r="V32" s="98"/>
+      <c r="W32" s="98"/>
+      <c r="X32" s="98"/>
+      <c r="Y32" s="98"/>
+      <c r="Z32" s="98"/>
+      <c r="AA32" s="98" t="s">
         <v>166</v>
       </c>
-      <c r="AB32" s="96"/>
-      <c r="AC32" s="96"/>
-      <c r="AD32" s="96"/>
-      <c r="AE32" s="96"/>
-      <c r="AF32" s="96"/>
-      <c r="AG32" s="96"/>
-      <c r="AH32" s="96" t="s">
+      <c r="AB32" s="98"/>
+      <c r="AC32" s="98"/>
+      <c r="AD32" s="98"/>
+      <c r="AE32" s="98"/>
+      <c r="AF32" s="98"/>
+      <c r="AG32" s="98"/>
+      <c r="AH32" s="98" t="s">
         <v>167</v>
       </c>
-      <c r="AI32" s="96"/>
-      <c r="AJ32" s="96"/>
-      <c r="AK32" s="96"/>
-      <c r="AL32" s="96"/>
-      <c r="AM32" s="96"/>
+      <c r="AI32" s="98"/>
+      <c r="AJ32" s="98"/>
+      <c r="AK32" s="98"/>
+      <c r="AL32" s="98"/>
+      <c r="AM32" s="98"/>
     </row>
     <row r="33" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A33" s="96" t="s">
+      <c r="A33" s="98" t="s">
         <v>156</v>
       </c>
-      <c r="B33" s="96"/>
-      <c r="C33" s="96"/>
-      <c r="D33" s="96"/>
-      <c r="E33" s="96"/>
-      <c r="F33" s="96"/>
-      <c r="G33" s="96"/>
-      <c r="H33" s="96"/>
-      <c r="I33" s="96"/>
-      <c r="J33" s="96"/>
-      <c r="K33" s="96"/>
-      <c r="L33" s="96"/>
-      <c r="M33" s="96"/>
-      <c r="N33" s="96"/>
-      <c r="O33" s="96"/>
-      <c r="P33" s="96"/>
-      <c r="Q33" s="96"/>
-      <c r="R33" s="96"/>
-      <c r="S33" s="96"/>
-      <c r="T33" s="96"/>
-      <c r="U33" s="96"/>
-      <c r="V33" s="96"/>
-      <c r="W33" s="96"/>
-      <c r="X33" s="96"/>
-      <c r="Y33" s="96"/>
-      <c r="Z33" s="96"/>
-      <c r="AA33" s="96"/>
-      <c r="AB33" s="96"/>
-      <c r="AC33" s="96"/>
-      <c r="AD33" s="96"/>
-      <c r="AE33" s="96"/>
-      <c r="AF33" s="96"/>
-      <c r="AG33" s="96"/>
-      <c r="AH33" s="96"/>
-      <c r="AI33" s="96"/>
-      <c r="AJ33" s="96"/>
-      <c r="AK33" s="96"/>
-      <c r="AL33" s="96"/>
-      <c r="AM33" s="96"/>
+      <c r="B33" s="98"/>
+      <c r="C33" s="98"/>
+      <c r="D33" s="98"/>
+      <c r="E33" s="98"/>
+      <c r="F33" s="98"/>
+      <c r="G33" s="98"/>
+      <c r="H33" s="98"/>
+      <c r="I33" s="98"/>
+      <c r="J33" s="98"/>
+      <c r="K33" s="98"/>
+      <c r="L33" s="98"/>
+      <c r="M33" s="98"/>
+      <c r="N33" s="98"/>
+      <c r="O33" s="98"/>
+      <c r="P33" s="98"/>
+      <c r="Q33" s="98"/>
+      <c r="R33" s="98"/>
+      <c r="S33" s="98"/>
+      <c r="T33" s="98"/>
+      <c r="U33" s="98"/>
+      <c r="V33" s="98"/>
+      <c r="W33" s="98"/>
+      <c r="X33" s="98"/>
+      <c r="Y33" s="98"/>
+      <c r="Z33" s="98"/>
+      <c r="AA33" s="98"/>
+      <c r="AB33" s="98"/>
+      <c r="AC33" s="98"/>
+      <c r="AD33" s="98"/>
+      <c r="AE33" s="98"/>
+      <c r="AF33" s="98"/>
+      <c r="AG33" s="98"/>
+      <c r="AH33" s="98"/>
+      <c r="AI33" s="98"/>
+      <c r="AJ33" s="98"/>
+      <c r="AK33" s="98"/>
+      <c r="AL33" s="98"/>
+      <c r="AM33" s="98"/>
     </row>
     <row r="34" spans="1:39" ht="14.1" customHeight="1">
-      <c r="A34" s="96" t="s">
+      <c r="A34" s="98" t="s">
         <v>157</v>
       </c>
-      <c r="B34" s="96"/>
-      <c r="C34" s="96"/>
-      <c r="D34" s="96"/>
-      <c r="E34" s="96"/>
-      <c r="F34" s="96"/>
-      <c r="G34" s="96"/>
-      <c r="H34" s="96"/>
-      <c r="I34" s="96"/>
-      <c r="J34" s="96"/>
-      <c r="K34" s="96"/>
-      <c r="L34" s="96"/>
-      <c r="M34" s="96"/>
-      <c r="N34" s="96"/>
-      <c r="O34" s="96"/>
-      <c r="P34" s="96"/>
-      <c r="Q34" s="96"/>
-      <c r="R34" s="96"/>
-      <c r="S34" s="96"/>
-      <c r="T34" s="96"/>
-      <c r="U34" s="96"/>
-      <c r="V34" s="96"/>
-      <c r="W34" s="96"/>
-      <c r="X34" s="96"/>
-      <c r="Y34" s="96"/>
-      <c r="Z34" s="96"/>
-      <c r="AA34" s="96"/>
-      <c r="AB34" s="96"/>
-      <c r="AC34" s="96"/>
-      <c r="AD34" s="96"/>
-      <c r="AE34" s="96"/>
-      <c r="AF34" s="96"/>
-      <c r="AG34" s="96"/>
-      <c r="AH34" s="96"/>
-      <c r="AI34" s="96"/>
-      <c r="AJ34" s="96"/>
-      <c r="AK34" s="96"/>
-      <c r="AL34" s="96"/>
-      <c r="AM34" s="96"/>
+      <c r="B34" s="98"/>
+      <c r="C34" s="98"/>
+      <c r="D34" s="98"/>
+      <c r="E34" s="98"/>
+      <c r="F34" s="98"/>
+      <c r="G34" s="98"/>
+      <c r="H34" s="98"/>
+      <c r="I34" s="98"/>
+      <c r="J34" s="98"/>
+      <c r="K34" s="98"/>
+      <c r="L34" s="98"/>
+      <c r="M34" s="98"/>
+      <c r="N34" s="98"/>
+      <c r="O34" s="98"/>
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="98"/>
+      <c r="S34" s="98"/>
+      <c r="T34" s="98"/>
+      <c r="U34" s="98"/>
+      <c r="V34" s="98"/>
+      <c r="W34" s="98"/>
+      <c r="X34" s="98"/>
+      <c r="Y34" s="98"/>
+      <c r="Z34" s="98"/>
+      <c r="AA34" s="98"/>
+      <c r="AB34" s="98"/>
+      <c r="AC34" s="98"/>
+      <c r="AD34" s="98"/>
+      <c r="AE34" s="98"/>
+      <c r="AF34" s="98"/>
+      <c r="AG34" s="98"/>
+      <c r="AH34" s="98"/>
+      <c r="AI34" s="98"/>
+      <c r="AJ34" s="98"/>
+      <c r="AK34" s="98"/>
+      <c r="AL34" s="98"/>
+      <c r="AM34" s="98"/>
     </row>
     <row r="35" spans="1:39" ht="14.1" customHeight="1">
       <c r="A35" s="46"/>
@@ -15109,6 +16313,95 @@
     </row>
   </sheetData>
   <mergeCells count="113">
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="M1:AL1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="F11:L11"/>
+    <mergeCell ref="AH8:AM8"/>
+    <mergeCell ref="AA8:AG8"/>
+    <mergeCell ref="T8:Z8"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="AH9:AM9"/>
+    <mergeCell ref="F10:L10"/>
+    <mergeCell ref="M10:S10"/>
+    <mergeCell ref="T10:Z10"/>
+    <mergeCell ref="AA10:AG10"/>
+    <mergeCell ref="AH10:AM10"/>
+    <mergeCell ref="M8:S8"/>
+    <mergeCell ref="F8:L8"/>
+    <mergeCell ref="F9:L9"/>
+    <mergeCell ref="M9:S9"/>
+    <mergeCell ref="T9:Z9"/>
+    <mergeCell ref="AA9:AG9"/>
+    <mergeCell ref="M11:S11"/>
+    <mergeCell ref="T11:Z11"/>
+    <mergeCell ref="AA11:AG11"/>
+    <mergeCell ref="AH11:AM11"/>
+    <mergeCell ref="F12:L12"/>
+    <mergeCell ref="M12:S12"/>
+    <mergeCell ref="T12:Z12"/>
+    <mergeCell ref="AA12:AG12"/>
+    <mergeCell ref="AH12:AM12"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="F17:L17"/>
+    <mergeCell ref="M17:S17"/>
+    <mergeCell ref="T17:Z17"/>
+    <mergeCell ref="AA17:AG17"/>
+    <mergeCell ref="AH17:AM17"/>
+    <mergeCell ref="T13:Z13"/>
+    <mergeCell ref="AA13:AG13"/>
+    <mergeCell ref="AH13:AM13"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="F16:L16"/>
+    <mergeCell ref="M16:S16"/>
+    <mergeCell ref="T16:Z16"/>
+    <mergeCell ref="AA16:AG16"/>
+    <mergeCell ref="AH16:AM16"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="F13:L13"/>
+    <mergeCell ref="M13:S13"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="F19:L19"/>
+    <mergeCell ref="M19:S19"/>
+    <mergeCell ref="T19:Z19"/>
+    <mergeCell ref="AA19:AG19"/>
+    <mergeCell ref="AH19:AM19"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="F18:L18"/>
+    <mergeCell ref="M18:S18"/>
+    <mergeCell ref="T18:Z18"/>
+    <mergeCell ref="AA18:AG18"/>
+    <mergeCell ref="AH18:AM18"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="F21:L21"/>
+    <mergeCell ref="M21:S21"/>
+    <mergeCell ref="T21:Z21"/>
+    <mergeCell ref="AA21:AG21"/>
+    <mergeCell ref="AH21:AM21"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="F20:L20"/>
+    <mergeCell ref="M20:S20"/>
+    <mergeCell ref="T20:Z20"/>
+    <mergeCell ref="AA20:AG20"/>
+    <mergeCell ref="AH20:AM20"/>
+    <mergeCell ref="AH31:AM31"/>
+    <mergeCell ref="AA29:AG29"/>
+    <mergeCell ref="AH29:AM29"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="F30:L30"/>
+    <mergeCell ref="M30:S30"/>
+    <mergeCell ref="T30:Z30"/>
+    <mergeCell ref="AA30:AG30"/>
+    <mergeCell ref="AH30:AM30"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="F29:L29"/>
+    <mergeCell ref="M29:S29"/>
+    <mergeCell ref="T29:Z29"/>
     <mergeCell ref="A26:K26"/>
     <mergeCell ref="A34:E34"/>
     <mergeCell ref="F34:L34"/>
@@ -15133,95 +16426,6 @@
     <mergeCell ref="M31:S31"/>
     <mergeCell ref="T31:Z31"/>
     <mergeCell ref="AA31:AG31"/>
-    <mergeCell ref="AH31:AM31"/>
-    <mergeCell ref="AA29:AG29"/>
-    <mergeCell ref="AH29:AM29"/>
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="F30:L30"/>
-    <mergeCell ref="M30:S30"/>
-    <mergeCell ref="T30:Z30"/>
-    <mergeCell ref="AA30:AG30"/>
-    <mergeCell ref="AH30:AM30"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="F29:L29"/>
-    <mergeCell ref="M29:S29"/>
-    <mergeCell ref="T29:Z29"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="F21:L21"/>
-    <mergeCell ref="M21:S21"/>
-    <mergeCell ref="T21:Z21"/>
-    <mergeCell ref="AA21:AG21"/>
-    <mergeCell ref="AH21:AM21"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="F20:L20"/>
-    <mergeCell ref="M20:S20"/>
-    <mergeCell ref="T20:Z20"/>
-    <mergeCell ref="AA20:AG20"/>
-    <mergeCell ref="AH20:AM20"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="F19:L19"/>
-    <mergeCell ref="M19:S19"/>
-    <mergeCell ref="T19:Z19"/>
-    <mergeCell ref="AA19:AG19"/>
-    <mergeCell ref="AH19:AM19"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="F18:L18"/>
-    <mergeCell ref="M18:S18"/>
-    <mergeCell ref="T18:Z18"/>
-    <mergeCell ref="AA18:AG18"/>
-    <mergeCell ref="AH18:AM18"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="F17:L17"/>
-    <mergeCell ref="M17:S17"/>
-    <mergeCell ref="T17:Z17"/>
-    <mergeCell ref="AA17:AG17"/>
-    <mergeCell ref="AH17:AM17"/>
-    <mergeCell ref="T13:Z13"/>
-    <mergeCell ref="AA13:AG13"/>
-    <mergeCell ref="AH13:AM13"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="F16:L16"/>
-    <mergeCell ref="M16:S16"/>
-    <mergeCell ref="T16:Z16"/>
-    <mergeCell ref="AA16:AG16"/>
-    <mergeCell ref="AH16:AM16"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="F13:L13"/>
-    <mergeCell ref="M13:S13"/>
-    <mergeCell ref="AA9:AG9"/>
-    <mergeCell ref="M11:S11"/>
-    <mergeCell ref="T11:Z11"/>
-    <mergeCell ref="AA11:AG11"/>
-    <mergeCell ref="AH11:AM11"/>
-    <mergeCell ref="F12:L12"/>
-    <mergeCell ref="M12:S12"/>
-    <mergeCell ref="T12:Z12"/>
-    <mergeCell ref="AA12:AG12"/>
-    <mergeCell ref="AH12:AM12"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="F11:L11"/>
-    <mergeCell ref="AH8:AM8"/>
-    <mergeCell ref="AA8:AG8"/>
-    <mergeCell ref="T8:Z8"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="AH9:AM9"/>
-    <mergeCell ref="F10:L10"/>
-    <mergeCell ref="M10:S10"/>
-    <mergeCell ref="T10:Z10"/>
-    <mergeCell ref="AA10:AG10"/>
-    <mergeCell ref="AH10:AM10"/>
-    <mergeCell ref="M8:S8"/>
-    <mergeCell ref="F8:L8"/>
-    <mergeCell ref="F9:L9"/>
-    <mergeCell ref="M9:S9"/>
-    <mergeCell ref="T9:Z9"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
